--- a/Excel/GAF2-Generated-Template_v01.xlsx
+++ b/Excel/GAF2-Generated-Template_v01.xlsx
@@ -2842,7 +2842,7 @@
 </file>
 
 <file path=customXml/item4.xml><?xml version="1.0" encoding="utf-8"?>
-<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5ACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIABGAG8AcgAgAEQAYQBpAHIAeQBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAF8ARABhAGkAcgB5AF8AMwBfAEIAXwAxAF8AYQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXABuAEEAIAA9ACAAYQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAZQB4AHAAcgBlAHMAcwBlAGQAIABhAHMAIABhACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXwBEAGEAaQByAHkAXwAzAF8AQgBfADEAXwBhAF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQAgAD0AIABhAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABlAHgAcAByAGUAcwBzAGUAZAAgAGEAcwAgAGEAIABmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXwBEAGEAaQByAHkAXwAzAF8AQgBfADEAXwBhAF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAcQB1AGEAdABpAG8AbgAgADMALgBCAC4AMQBhAF8AMgBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAF8ARABhAGkAcgB5AF8AMwBfAEIAXwAxAF8AYQBfAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBCADAAIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAF8ARABhAGkAcgB5AF8AMwBfAEIAXwAxAF8AYQBfAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAF8ARABhAGkAcgB5AF8AMwBfAEIAXwAxAF8AYQBfAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAcQB1AGEAdABpAG8AbgAgADMALgBCAC4AMQBhAF8AMgBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIANAApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADEAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABcAG4AVABhAGIAbABlACAAQQA1AC4ANQAuADEALgAxACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAATICAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AMQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBMAGkAdgBlAFcAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADEAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgABMgIABMAGkAdgBlAHcAZQBpAGcAaAB0AFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAxAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEwAaQB2AGUAVwBlAGkAZwBoAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADEAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgA6ACAAVABhAGIAbABlACAAQQA1AC4ANQAuADEALgAxAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAxAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEwAaQB2AGUAVwBlAGkAZwBoAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABpAG0AZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAXAAiAE0AaQBsAGsAaQBuAGcAIABDAG8AdwBzAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAYwAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBlADEAXAAiACwAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGMAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAMgAwADIAMAATIDIAMAAyADMAXAAiACwAIAA1ADUAMAAsACAAMwA3ADAALAAgADEANwA5ACwAIAA2ADAAMAAsACAAMgAyADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAFwAbgBUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADIAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgABMgIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgAgACgAawBnAC8AZABhAHkAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAyAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEwAaQB2AGUAVwBlAGkAZwBoAHQARwBhAGkAbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQA1AC4ANQAuADEALgAyACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAATICAATABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAyADoAIABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADIAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAaQBtAGUAIABwAGUAcgBpAG8AZABcACIALAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGUAMQBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAMAAyADAAEyAyADAAMgAzAFwAIgAsACAAMAAuADAAMQA2ACwAIAAwAC4ANgAsACAAMAAuADUANwAsACAAMAAuADEALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAzAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAFMAdABhAG4AZABhAHIAZABSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAFwAbgBUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADMAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgABMgIABTAHQAYQBuAGQAYQByAGQAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADMAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADMAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgABMgIABTAHQAYQBuAGQAYQByAGQAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADMAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAzAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAFMAdABhAG4AZABhAHIAZABSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgA6ACAAVABhAGIAbABlACAAQQA1AC4ANQAuADEALgAzAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAzAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAFMAdABhAG4AZABhAHIAZABSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGkAbQBlACAAcABlAHIAaQBvAGQAXAAiACwAIABcACIATQBpAGwAawBpAG4AZwAgAEMAbwB3AHMAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBlADEAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGUAMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAYwAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAyADAAMgAwABMgMgAwADIAMwBcACIALAAgADUAOQAwACwAIAA1ADkAMAAsACAANQA5ADAALAAgADcANwAwACwAIAA3ADcAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANABfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBEAE0ARABBAG4AZABDAFAAXABuAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4ANAAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAEyAgAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAYQBuAGQAIABjAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANABfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBEAE0ARABBAG4AZABDAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4ANAAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAEyAgAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAYQBuAGQAIABjAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANABfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBEAE0ARABBAG4AZABDAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADQAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUARABNAEQAQQBuAGQAQwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAyADoAIABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADQAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADQAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUARABNAEQAQQBuAGQAQwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBEAE0ARABcACIALAAgAFwAIgBDAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsAFwAIgAsACAANwA1ACwAIAAyADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADUAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUAByAGUAVwBlAGEAbgBlAGQARABhAHQAYQBcAG4AVABhAGIAbABlACAAQQA1AC4ANQAuADEALgA1ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAATICAARABhAHQAYQAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGMAYQBsAHYAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADUAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUAByAGUAVwBlAGEAbgBlAGQARABhAHQAYQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQA1AC4ANQAuADEALgA1ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAATICAARABhAHQAYQAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGMAYQBsAHYAZQBzAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA1AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAFAAcgBlAFcAZQBhAG4AZQBkAEQAYQB0AGEAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBQAHIAZQBXAGUAYQBuAGUAZABEAGEAdABhAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAyADoAIABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADUAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADUAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUAByAGUAVwBlAGEAbgBlAGQARABhAHQAYQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABlACAAcgBhAG4AZwBlAFwAIgAsACAAXAAiAEMAbABhAHMAcwBcACIALAAgAFwAIgBDAEgANAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIARgBhAGUAYwBhAGwAIABOAFwAIgAsACAAXAAiAFUAcgBpAG4AYQByAHkAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAyADAAMAA1ACsAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwBcAHUAMAAwADMAYwAxAFwAIgAsACAAMAAuADAAMQA3ADYALAAgADAALgAyADYAOAA1ACwAIAAwAC4AMAAwADUANQAsACAAMAAuADAAMAA4ADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIAB5AGUAYQByAHMAXAAiACwAIABcACIAQgB1AGwAbABzAFwAdQAwADAAMwBjADEAXAAiACwAIAAwAC4AMAAyADAANAAsACAAMAAuADMAMAAwADMALAAgADAALgAwADAANQAwACwAIAAwAC4AMAAwADQAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBNAEMARgBzAEYAbwByAE0ATQBTAFwAbgBUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADcAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgABMgIABNAEMARgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADcAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATQBDAEYAcwBGAG8AcgBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQA1AC4ANQAuADEALgA3ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAATICAATQBDAEYAcwBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBNAEMARgBzAEYAbwByAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADcAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATQBDAEYAcwBGAG8AcgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgA6ACAAVABhAGIAbABlACAAQQA1AC4ANQAuADEALgA3AFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA3AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAE0AQwBGAHMARgBvAHIATQBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAOQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXAAiACwAXAAiAEEAQwBUAFwAIgAsAFwAIgBOAFMAVwBcACIALABcACIATgBUAFwAIgAsAFwAIgBRAEwARABcACIALABcACIAUwBBAFwAIgAsAFwAIgBUAEEAUwBcACIALABcACIAVgBJAEMAXAAiACwAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAxACwAMAAuADAAMQAsADAALgAwADIALAAwAC4AMAAxACwAMAAuADAAMQAsADAALgAwADEALAAwAC4AMAAxACwAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsADAALgA3ADIALAAwAC4ANwA2ACwAMAAuADgALAAwAC4ANwA4ACwAMAAuADcANAAsADAALgA2ADkALAAwAC4ANwAzACwAMAAuADcANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAHMAIAAoAGIAKQBcACIALAAwAC4AMAAwADUALAAwAC4AMAAwADUALAAwAC4AMAAxACwAMAAuADAAMAA1ACwAMAAuADAAMAA1ACwAMAAuADAAMAAxACwAMAAuADAAMAA1ACwAMAAuADAAMAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawBzACAAKABjACkAXAAiACwAMAAuADEANQAsADAALgAxADgALAAwAC4ANQAwACwAMAAuADIANAAsADAALgAxADcALAAwAC4AMQAzACwAMAAuADEANwAsADAALgAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQBcACIALAAwAC4AMAAyACwAMAAuADAAMgAsADAALgAwADIALAAwAC4AMAAyACwAMAAuADAAMgAsADAALgAwADIALAAwAC4AMAAyACwAMAAuADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AOQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBOAE8AMgBFAEYAQQBuAGQARgByAGEAYwBOAFwAbgBUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADkAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgABMgIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIABhAG4AZAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAE4ATwAyAEUARgBBAG4AZABGAHIAYQBjAE4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4AOQAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAEyAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGEAbgBkACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAE4ATwAyAEUARgBBAG4AZABGAHIAYQBjAE4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZQB4AGMAcgBlAHQAZQBkAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAE4ATwAyAEUARgBBAG4AZABGAHIAYQBjAE4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADIAOgAgAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4AOQBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AOQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBOAE8AMgBFAEYAQQBuAGQARgByAGEAYwBOAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAFwAIgAsAFwAIgBFAEYAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAKQBcACIALABcACIARgByAGEAYwBHAEEAUwBNAG0AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBvAGkAZAAgAGEAdAAgAFAAYQBzAHQAdQByAGUAXAAiACwAMAAsADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAwACwAMAAuADMANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAAgABMgIABTAHUAbQBwACAAYQBuAGQAIABEAGkAcwBwAGUAcgBzAGEAbABcACIALAAwACwAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAAgABMgIABEAHIAYQBpAG4AcwAgAHQAbwAgAFAAYQBkAGQAbwBjAGsAXAAiACwAMAAsADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAMAAuADAAMAA1ACwAMAAuADMAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIAAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8AUwB0AGEAdABlAFQAZQByAHIAaQB0AG8AcgB5AFwAbgBUAGEAYgBsAGUAIAA1AC4AMgAgAFMAeQBtAGIAbwBsAHMAIAB1AHMAZQBkACAAaQBuACAAYQBsAGcAbwByAGkAdABoAG0AcwAgAGYAbwByACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAFMAdABhAHQAZQBUAGUAcgByAGkAdABvAHIAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAANQAuADIAIABTAHkAbQBiAG8AbABzACAAdQBzAGUAZAAgAGkAbgAgAGEAbABnAG8AcgBpAHQAaABtAHMAIABmAG8AcgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5ACAAKABpACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBTAHQAYQB0AGUAVABlAHIAcgBpAHQAbwByAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBTAHQAYQB0AGUAVABlAHIAcgBpAHQAbwByAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAFMAdABhAHQAZQBUAGUAcgByAGkAdABvAHIAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAFMAdABhAHQAZQBUAGUAcgByAGkAdABvAHIAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHkAbQBiAG8AbABcACIALAAgAFwAIgBTAHQAYQB0AGUALwAgAHQAZQByAHIAaQB0AG8AcgB5ACAAKABpACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAzACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADQALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAA1ACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAA2ACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADcALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADgALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEMAbABhAHMAcwBlAHMAXABuAFQAYQBiAGwAZQAgADUALgAyACAAUwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEMAbABhAHMAcwBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAyACAAUwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGMAbABhAHMAcwBlAHMAIAAoAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBDAGwAYQBzAHMAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEMAbABhAHMAcwBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBDAGwAYQBzAHMAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEMAbABhAHMAcwBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIAUwB0AGEAdABlAC8AIAB0AGUAcgByAGkAdABvAHIAeQAgACgAaQApAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxACwAIABcACIATQBpAGwAawBpAG4AZwAgAGMAbwB3AHMAXAAiACwAIABcACIATQBpAGwAawBpAG4AZwAgAGMAbwB3AHMAIAAoADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAZQAgADEAIAB5AGUAYQByAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAZQAgADEAIAB5AGUAYQByACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADMALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAIAAxACAAeQBlAGEAcgBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAIAAxACAAeQBlAGEAcgAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAA0ACwAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGUAIAAxACAAeQBlAGEAcgBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAgADEAIAB5AGUAYQByACAAKAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADUALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAYwAgADEAIAB5AGUAYQByAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjACAAMQAgAHkAZQBhAHIAIAAoADUAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAgACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAbABsAG8AYwBhAHQAaQBvAG4ATwBmAFcAYQBzAHQAZQBUAG8ATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4AOAAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAEyAgAEEAbABsAG8AYwBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAIAB0AG8AIABNAE0AUwAgABMgIABNAGkAbABrAGkAbgBnACAAYwBvAHcAcwAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAbABsAG8AYwBhAHQAaQBvAG4ATwBmAFcAYQBzAHQAZQBUAG8ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4AOAAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAEyAgAEEAbABsAG8AYwBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAIAB0AG8AIABNAE0AUwAgABMgIABNAGkAbABrAGkAbgBnACAAYwBvAHcAcwAgACgAcABlAHIAIABjAGUAbgB0ACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAGwAbABvAGMAYQB0AGkAbwBuAE8AZgBXAGEAcwB0AGUAVABvAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAbABsAG8AYwBhAHQAaQBvAG4ATwBmAFcAYQBzAHQAZQBUAG8ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgBjAGUAbgB0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBsAGwAbwBjAGEAdABpAG8AbgBPAGYAVwBhAHMAdABlAFQAbwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgAgAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4AOABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAbABsAG8AYwBhAHQAaQBvAG4ATwBmAFcAYQBzAHQAZQBUAG8ATQBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMQAwACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBTAHkAbQBiAG8AbABcACIALAAgAFwAIgBNAE0AUwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBOAFQAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIABcACIAUwBBAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAANwA4AC4ANgAsACAANwA4AC4ANgAsACAANwA4AC4ANwAsACAANwA4AC4ANwAsACAAOAAwAC4ANQAsACAAOAA2AC4ANQAsACAAOAAzAC4AOQAsACAANwA5AC4AOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAOQAuADAALAAgADkALgAwACwAIAA3AC4AMwAsACAANwAuADMALAAgADEAMAAuADQALAAgADgALgA0ACwAIAAxADAALgA4ACwAIAAxADAALgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIARABhAGkAbAB5ACAAUwBwAHIAZQBhAGQAOgAgAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsAFwAIgAsACAAMgAuADAALAAgADIALgAwACwAIAAzAC4AMwAsACAAMwAuADMALAAgADEALgA0ACwAIAAyAC4ANAAsACAAMAAuADkALAAgADEALgA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARABhAGkAbAB5ACAAUwBwAHIAZQBhAGQAOgAgAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawBzAFwAIgAsACAAMQAuADkALAAgADEALgA5ACwAIAAyAC4ANAAsACAAMgAuADQALAAgADAALgA4ACwAIAAwAC4AOAAsACAAMAAuADIALAAgADAALgA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA0AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAA4AC4ANAAsACAAOAAuADQALAAgADgALgA0ACwAIAA4AC4ANAAsACAANgAuADkALAAgADIALgAwACwAIAA0AC4AMgAsACAANwAuADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzACAAaQBuAGMAbAB1AGQAaQBuAGcAIABsAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgACAAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA1AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAIAAoAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAKQBcACIALAAgAFwAIgBGAHUAZQBsACAAdQBuAGkAdABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAE8AMgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAEgANABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABOADIATwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAG8AbQBiAGkAbgBlAGQAIABnAGEAcwBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAyACwAIAAwAC4AMAAzACwAIAA1ADEALgA2ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAbQBpAG4AZQAgAHcAYQBzAHQAZQAgAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4AOQAsACAANAAuADYALAAgADAALgAzACwAIAA1ADYALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAoAHIAZQB2AGUAcgB0AGkAbgBnACAAdABvACAAcwB0AGEAbgBkAGEAcgBkACAAYwBvAG4AZABpAHQAaQBvAG4AcwApAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQBuAHAAcgBvAGMAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAA2ADIAOQAsACAAXAAiAG0AMwBcACIALAAgADUANgAuADUALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANgAuADUANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBrAGUAIABvAHYAZQBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAxADgAMQAsACAAXAAiAG0AMwBcACIALAAgADMANwAuADAALAAgADAALgAwADMALAAgADAALgAwADUALAAgADMANwAuADAAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABhAHMAdAAgAGYAdQByAG4AYQBjAGUAIABnAGEAcwBcACIALAAgADAALgAwADAANAAwACwAIABcACIAbQAzAFwAIgAsACAAMgAzADQALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAAyACwAIAAyADMANAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADAANAAsACAAMAAuADAAMwAsACAANgAwAC4AMgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBMAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAGUAbwB1AHMAIABmAG8AcwBzAGkAbAAgAGYAdQBlAGwAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA5ADAALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABhAG4AZABmAGkAbABsACAAYgBpAG8AZwBhAHMAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtAGUAdABoAGEAbgBlACAAbwBuAGwAeQApAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAsACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAwAC4AMAAzADcAMAAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAG0AZQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAAMAAuADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAeQBkAHIAbwBnAGUAbgBcACIALAAgADAALgAwADEAMgAyACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADAALgAwACwAIAAwAC4ANQAsACAAMAAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIAAxACwAIABcACIARwBKAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIAB3AGUAcgBlACAAYQBkAGQAZQBkACwAIABlAGEAYwBoACAAdwBpAHQAaAAgAGEAbgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAMQAgAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwALgAgAFQAaABpAHMAIABpAHMAIABmAG8AcgAgAHUAcwBlAHIAcwAgAHcAaABvACAAaABhAHYAZQAgAGYAdQBlAGwAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABkAGEAdABhACAAaQBuACAARwBKACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbQAzAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA2AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAdABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE0AZQB0AHIAbwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAATgBhAHQAdQByAGEAbAAgAEcAYQBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgBvAG4AIAAtACAATQBlAHQAcgBvAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADQALgAwACwAIAA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIAA4AC4AOAAsACAANwAuADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADEAMAAuADcALAAgADEAMAAuADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAA0AC4AMQAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgADQALgAxACwAIAA0AC4AMABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE4AUwBXACAAYQBuAGQAIABBAEMAVAAgAHMAcABsAGkAdAAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIAByAG8AdwBzAC4AIABcAHUAMAAwADIANwBDAFwAdQAwADAAMgA3ACAAVgBhAGwAdQBlAHMAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAGEAbgBkACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAdABoAG8AcwBlACAAZgBvAHIAIABWAGkAYwB0AG8AcgBpAGEAIABhAG4AZAAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AIAAoAFMAZQBlACAAYQBwAHAAZQBuAGQAaQBjAGUAcwApAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEEAcwAgAFMAYwBvAHAAZQAgADMAIABmAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAYQB0ACAAdABoAGUAIABwAG8AaQBuAHQAIAB3AGgAZQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABpAHMAIABkAGUAbABpAHYAZQByAGUAZAAgAHQAbwAgAGUAbgBkACAAdQBzAGUAcgBzACwAIABpAHQAIABpAHMAIABuAGUAYwBlAHMAcwBhAHIAeQAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQB0ACAAZQBhAGMAaAAgAG8AZgAgAHQAaABlACAAbABvAGEAZAAgAGMAZQBuAHQAcgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBHAGEAcwAgAHIAZQBhAGMAaABlAHMAIABlAG4AZAAgAHUAcwBlAHIAcwAgAGUAaQB0AGgAZQByACAAZgByAG8AbQAgAHQAaABlACAAbQBlAHQAcgBvACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABuAGUAdAB3AG8AcgBrAHMAIABvAHIAIABkAGkAcgBlAGMAdAAgAGYAcgBvAG0AIAB0AGgAZQAgAGgAaQBnAGgAIAAtACAAcAByAGUAcwBzAHUAcgBlACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABwAGkAcABlAGwAaQBuAGUAcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAEgAbwB1AHMAZQBoAG8AbABkAHMAIABhAG4AZAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB1AHMAZQByAHMAIAB0AGUAbgBkACAAdABvACAAYgBlACAAcwBlAHIAdgBlAGQAIABiAHkAIAB0AGgAZQAgAGYAbwByAG0AZQByACwAIABhAG4AZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABhAG4AZAAgAGwAYQByAGcAZQAgAGkAbgBkAHUAcwB0AHIAaQBhAGwAIABwAGwAYQBuAHQAcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGwAYQB0AHQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBNAGUAdAByAG8AIABpAHMAIABkAGUAZgBpAG4AZQBkACAAYQBzACAAbABvAGMAYQB0AGUAZAAgAG8AbgAgAG8AcgAgAGUAYQBzAHQAIABvAGYAIAB0AGgAZQAgAGQAaQB2AGkAZABpAG4AZwAgAHIAYQBuAGcAZQAgAGkAbgAgAE4AUwBXACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAEMAYQBuAGIAZQByAHIAYQAgAGEAbgBkACAAUQB1AGUAYQBuAGIAZQB5AGEAbgAsACAATQBlAGwAYgBvAHUAcgBuAGUALAAgAEIAcgBpAHMAYgBhAG4AZQAsACAAQQBkAGUAbABhAGkAZABlACAAbwByACAAUABlAHIAdABoAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIATwB0AGgAZQByAHcAaQBzAGUALAAgAHQAaABlACAAbgBvAG4AIAAtACAAbQBlAHQAcgBvACAAZgBhAGMAdABvAHIAIABzAGgAbwB1AGwAZAAgAGIAZQAgAHUAcwBlAGQALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEYAYQBjAHQAbwByAHMAIABhAHIAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAGEAbABsACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAHcAaABpAGMAaAAgAG0AYQB5ACAAaQBuAGMAbAB1AGQAZQAgAGMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIAVABhAGIAbABlACAANgAgAGkAcwAgAG4AbwB0ACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHQAbwAgAGUAdABoAGEAbgBlAC4AIABTAGUAZQAgAFQAYQBiAGwAZQAgADcAIABJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEMAIAA9ACAAQwBvAG4AZgBpAGQAZQBuAHQAaQBhAGwALgAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAHQAaABlACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIABhAHIAZQAgAG4AbwB0ACAAYQB2AGEAaQBsAGEAYgBsAGUAIABkAHUAZQAgAHQAbwAgAGMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAGkAdAB5ACAAYwBvAG4AcwB0AHIAYQBpAG4AdABzACAAdABoAGEAdAAgAGEAcgBpAHMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGEAIABsAGkAbQBpAHQAZQBkACAAbgB1AG0AYgBlAHIAIABvAGYAIABOAEcARQBSACAAZABhAHQAYQAgAGkAbgBwAHUAdABzAC4AIABJAHQAIABpAHMAIABzAHUAZwBnAGUAcwB0AGUAZAAgAHQAaABhAHQAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAHQAaABlACAAdQBzAGUAIABvAGYAIAB0AGgAZQAgAFYAaQBjAHQAbwByAGkAYQBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGkAcwAgAGEAcABwAHIAbwBwAHIAaQBhAHQAZQAsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAHcAaABpAGwAZQAgAGYAbwByACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZABvACAAbgBvAHQAIABpAG4AYwBsAHUAZABlACAAZgB1AGcAaQB0AGkAdgBlACAAZQBtAGkAcwBzAGkAbwBuACAAbABlAGEAawBhAGcAZQAgAGYAcgBvAG0AIABsAG8AdwAgAHAAcgBlAHMAcwB1AHIAZQAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlACAAbgBlAHQAdwBvAHIAawBzACAAdwBoAGkAbABlACAAdABoAG8AcwBlACAAZgByAG8AbQAgAGgAaQBnAGgAIABwAHIAZQBzAHMAdQByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZwBhAHMAIABuAGUAdAB3AG8AcgBrAHMAIABhAHIAZQAgAGMAbwBuAHMAaQBkAGUAcgBlAGQAIABuAGUAZwBsAGkAZwBpAGIAbABlAC4AXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAYwBlAHIAdABhAGkAbgAgAHAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMALgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA4AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADUALAAgADgALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsAHMAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsACAAdQBzAGUAZAAgAGEAcwAgAGYAdQBlAGwAKQAsACAAZQAuAGcALgAgAGwAdQBiAHIAaQBjAGEAbgB0AHMAXAAiACwAIAAzADgALgA4ACwAIABcACIAawBsAFwAIgAsACAAMQAzAC4AOQAsACAAMAAuADAALAAgADAALgAwACwAIAAxADMALgA5ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABnAHIAZQBhAHMAZQBzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADMALgA1ACwAIAAwAC4AMAAsACAAMAAuADAALAAgADMALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAHUAZABlACAAbwBpAGwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAcgB1AGQAZQAgAG8AaQBsACAAYwBvAG4AZABlAG4AcwBhAHQAZQBzAFwAIgAsACAANAA1AC4AMwAsACAAXAAiAHQAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgA5AC4AOAA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADYALgA1ACwAIABcACIAdABcACIALAAgADYAMQAuADAALAAgADAALgAwADgALAAgADAALgAyACwAIAA2ADEALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB1AHQAbwBtAG8AdABpAHYAZQAgAGcAYQBzAG8AbABpAG4AZQAgAC8AIABwAGUAdAByAG8AbAAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA4ADAALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIABnAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADMALgAxACwAIABcACIAawBMAFwAIgAsACAANgA3ACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYANwAuADQAMAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADcALgA1ACwAIABcACIAawBMAFwAIgAsACAANgA4AC4AOQAsACAAMAAuADAAMQAsACAAMAAuADIALAAgADYAOQAuADEAMQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgAgAHQAdQByAGIAaQBuAGUAIABmAHUAZQBsACAALwAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdABpAG4AZwAgAG8AaQBsAFwAIgAsACAAMwA3AC4AMwAsACAAXAAiAGsATABcACIALAAgADYAOQAuADUALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA3ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAxACwAIAAwAC4AMgAsACAANwAwAC4AMgAwACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAwADQALAAgADAALgAyACwAIAA3ADMALgA4ADQALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAGEAcgBvAG0AYQB0AGkAYwAgAGgAeQBkAHIAbwBjAGEAcgBiAG8AbgBzAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADcALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA5ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbAB2AGUAbgB0AHMAOgAgAG0AaQBuAGUAcgBhAGwAIAB0AHUAcgBwAGUAbgB0AGkAbgBlACAAbwByACAAdwBoAGkAdABlACAAcwBwAGkAcgBpAHQAcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABwAGUAdAByAG8AbABlAHUAbQAgAGcAYQBzACAAKABMAFAARwApAFwAIgAsACAAMgA1AC4ANwAsACAAXAAiAGsATABcACIALAAgADYAMAAuADIALAAgADAALgAyACwAIAAwAC4AMgAsACAANgAwAC4ANgAwACwAIAAyADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHAAaAB0AGgAYQBcACIALAAgADMAMQAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAA2ADkALgA4ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAZgBpAG4AZQByAHkAIABnAGEAcwAgAGEAbgBkACAAbABpAHEAdQBpAGQAcwBcACIALAAgADQAMgAuADkALAAgAFwAIgB0AFwAIgAsACAANQA0AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAANQA0AC4ANwA2ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAYwBvAGsAZQBcACIALAAgADMANAAuADIALAAgAFwAIgB0AFwAIgAsACAAOQAyAC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADkAMgAuADgAOAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMgAsACAAMAAuADEALAAgADYAOQAuADkAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA0AC4ANgAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAHQAaABhAG4AbwBsACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGEAIABmAHUAZQBsACAAaQBuACAAYQBuACAAaQBuAHQAZQByAG4AYQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGUAbgBnAGkAbgBlAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQAgAGEAbgBkACAAYgBlAGwAbwB3AFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADAALgAyADIALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMwAwACwAIABcACIATgBFAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwAgAGkAbgAgAGQAaQBmAGYAZQByAGUAbgB0ACAAdAByAGEAbgBzAHAAbwByAHQAIABlAHEAdQBpAHAAbQBlAG4AdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAOQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAXAAiACwAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBsAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYANwAuADYAMgAsACAAMQA3AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAANwAwAC4ANAAxACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAHAAZQB0AHIAbwBsAGUAdQBtACAAZwBhAHMAIAAoAEwAUABHACkAXAAiACwAIAAyADYALgAyACwAIABcACIAawBsAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADUALAAgADAALgAzACwAIAA2ADEALgAwADAALAAgADIAMAAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAGwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4ANQAsACAANwA0AC4AMQA4ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBFAHQAaABhAG4AbwBsAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADIALAAgADAALgA0ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQgBpAG8AZABpAGUAcwBlAGwAXAAiACwAIAAzADQALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgA4ACwAIAAxAC4ANwAsACAAMgAuADUALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAAMAAuADUAMQAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAE8AdABoAGUAcgAgAGIAaQBvAGYAdQBlAGwAcwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAZwBoAHQAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADcALgAzACwAIAAwAC4AMwAsACAANQA5AC4AMAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBDAG8AbQBwAHIAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAyAC4AOAAsACAAMAAuADMALAAgADUANAAuADUALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsAbABcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADAANwAsACAAMAAuADQALAAgADcAMAAuADMANwAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADEALAAgADAALgA0ACwAIAA3ADAALgA0ACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANAAsACAANwAwAC4ANQAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADcALAAgADAALgA0ACwAIAAwAC4ANAA3ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4ANAAsACAAMAAuADUALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADQALAAgADAALgA2ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdABcACIALAAgADMAMwAuADEALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgAwACwAIAAwAC4AMAA2ACwAIAAwAC4ANgAsACAANgA3AC4ANgA2ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwA2AC4AOAAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADYALAAgADAALgAwADEALAAgADAALgA2ACwAIAA3ADAALgAyADEALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA2ACwAIAAwAC4ANgAxACwAIABcACIATgBFAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgAOgAgAEYAdQBlAGwAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA4AC4AMQAgAEYAdQBlAGwAIABVAHMAZQAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsACAARQBDACwAIABFAEYALABcAG4AIAAgACAAIABRACAAKgAgAEUAQwAgACoAIABFAEYAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEALAAgAEUAQwAsACAARQBGACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEALAAgAEUAQwAsACAARQBGACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADgALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADMAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFACAAPQAgAFEAIAAqACAARQBDACAAKgAgAEUARgAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAcQBcACIALAAgAFwAIgBBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAFYAYQByAGkAZQBzACAAYgBhAHMAZQBkACAAbwBuACAAZgB1AGUAbAAgAHQAeQBwAGUAOgAgAGsATAAsACAAbQAzACwAIABHAEoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBUAHIAYQBuAHMALABxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAFQAcgBhAG4AcwAsADEALABxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlACAALwAgAEcASgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAFwAIgAsACAAXAAiAFQAcgBhAG4AcwBwAG8AcgB0ACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQBcACIALAAgAFwAIgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAdQBzAGUAZAAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzACAAOgAgAGsATABcAG4ARQBDACAAOgAgAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwAgADoAIABrAGcAIABDAE8AMgBlACAALwAgAEcASgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEALAAgAEUAQwAsACAARQBGACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEALAAgAEUAQwAsACAARQBGACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADgALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMgAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABzAG8AdQByAGMAZQBzACAALQAgAEMAYQBsAGMAdQBsAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAIAA9ACAAUQAgACoAIABFAEMAIAAqACAARQBGACAAKgAgADEAMAAgAF4AIAAtACAAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAFMAQwAsAHEAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBHAEoAIAAvACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBTAEMALAAxACwAcQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEMAXAAiACwAIABcACIAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMgBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAGcAZQBuAGUAcgBpAGMAIABmAHUAZQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAHcAaABlAHIAZQAgAHQAaABlACAAdQBzAGEAZwBlACAAaQBzACAAbgBvAHQAIABrAG4AbwB3AG4AXABuAFEAIAA6ACAAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABnAGUAbgBlAHIAaQBjACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABHAEoALwBrAEwAXABuAEUARgAgADoAIABTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEALAAgAEUAQwAsACAARQBGACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEALAAgAEUAQwAsACAARQBGACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAGcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBVAHMAZQBzACAAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkALAAgADgALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApACAAYQBuAGQAIABlAHYAZQByAGEAZwBlAHMAIAB0AGgAZQAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAYQBuAGQAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMgAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABnAGUAbgBlAHIAaQBjACAAZQBuAGUAcgBnAHkAIABzAG8AdQByAGMAZQBzACAALQAgAEMAYQBsAGMAdQBsAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAIABhAG4AZAAgADIALgAzACAARQBzAHQAaQBtAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQAgAD0AIABRACAAKgAgAEUAQwAgACoAIABFAEYAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABnAGUAbgBlAHIAaQBjACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEcAQwAsAHEAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBHAEoAIAAvACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBHAEMALAAxACwAcQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEMAXAAiACwAIABcACIARwBlAG4AZQByAGkAYwAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEYAZQByAHQAaQBsAGkAcwBlAHIAUAByAG8AZAB1AGMAdABMAG8AbwBrAHUAcABcAG4APQBMAEEATQBCAEQAQQAoAFAAcgBvAGQAdQBjAHQALAAgAFAAcgBvAGQAdQBjAHQAQQB0AHQAcgBpAGIAdQB0AGUALAAgAFAAcgBvAGQAdQBjAHQAQQByAHIAYQB5ACwAIABQAHIAbwBkAHUAYwB0AEEAcgByAGEAeQBDAG8AbAB1AG0AbgAsACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkASABlAGEAZABlAHIAcwAsAFwAbgAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIABYAE0AQQBUAEMASAAoAFQAUgBJAE0AKABQAHIAbwBkAHUAYwB0ACkALAAgAFAAcgBvAGQAdQBjAHQAQQByAHIAYQB5AEMAbwBsAHUAbQBuACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABUAFIASQBNACgAUAByAG8AZAB1AGMAdABBAHQAdAByAGkAYgB1AHQAZQApACwAIABQAHIAbwBkAHUAYwB0AEEAcgByAGEAeQBIAGUAYQBkAGUAcgBzACwAIAAwACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAFwAIgBcACIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATABvAG8AawB1AHAAVABhAHIAZwBlAHQAMQAsAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFsATABvAG8AawB1AHAAVABhAHIAZwBlAHQAMgBdACwAWwBMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABUAGEAcgBnAGUAdAAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATABvAG8AawB1AHAAVABhAHIAZwBlAHQAMgApACwAMQAsAC0ALQAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVABhAHIAZwBlAHQAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABBAHAAcABsAGkAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0ACwAXABuACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0ACkAXABuACkAOwBcAG4AXABuAFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEEAcABwAGwAaQBlAGQAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANABdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADYAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALAAgACgAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAqAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsACAAKABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACoAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAIAAoAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKgBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzACkALAAgAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANAAsACAAKABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACoAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANAApACwAIABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADUALAAgACgAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAqAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAKQAsACAAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAIAAoAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKgBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2ACkALAAgACAAXABuACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMQAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxAFwAbgAgACAAIAAgACkAKwBcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAyAFwAbgAgACAAIAAgACkALAAgADAAKQArAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMAXABuACAAIAAgACAAKQAsACAAMAApACsAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANABcAG4AIAAgACAAIAApACwAIAAwACkAKwBcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA1AFwAbgAgACAAIAAgACkALAAgADAAKQArAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA2ACwAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADYAXABuACAAIAAgACAAKQAsACAAMAApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAHQAQQBwAHAAbABpAGUAZABCAHkAUwBvAHUAcgBjAGUAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAxAFMAbwB1AHIAYwBlACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAyAFMAbwB1AHIAYwBlAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADMAUwBvAHUAcgBjAGUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANABdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANABTAG8AdQByAGMAZQBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA1AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANQBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA1AFMAbwB1AHIAYwBlAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADYAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADYAUwBvAHUAcgBjAGUAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALAAgACgAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAqAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsACAAKABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACoAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAIAAoAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKgBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzACkALAAgAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANAAsACAAKABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACoAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANAApACwAIABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADUALAAgACgAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAqAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAKQAsACAAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAIAAoAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKgBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2ACkALAAgACAAXABuACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMQAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxACwAIABTAG8AdQByAGMAZQAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEAUwBvAHUAcgBjAGUAXABuACAAIAAgACAAKQArAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAyACwAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADIALAAgAFMAbwB1AHIAYwBlACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgBTAG8AdQByAGMAZQBcAG4AIAAgACAAIAApACwAIAAwACkAKwBcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAIABTAG8AdQByAGMAZQAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADMAUwBvAHUAcgBjAGUAXABuACAAIAAgACAAKQAsACAAMAApACsAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANAAsACAAUwBvAHUAcgBjAGUALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACkALAAgADAAKQArAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA1ACwAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADUALAAgAFMAbwB1AHIAYwBlACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQBTAG8AdQByAGMAZQBcAG4AIAAgACAAIAApACwAIAAwACkAKwBcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAIABTAG8AdQByAGMAZQAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADYAUwBvAHUAcgBjAGUAXABuACAAIAAgACAAKQAsACAAMAApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEcAZQB0AFMAYwBvAHAAZQAzAEUARgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFMAYwBvAHAAZQAzAEEAcgByAGEAeQAsACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsACAAUwBvAHUAcgBjAGUALAAgAFMAbwB1AHIAYwBlAFIAbwB3ACwAXABuACAAIAAgACAASQBOAEQARQBYACgAUwBjAG8AcABlADMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAATQBBAFQAQwBIACgAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAATQBBAFQAQwBIACgAUwBvAHUAcgBjAGUALAAgAFMAbwB1AHIAYwBlAFIAbwB3ACwAIAAwACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEcAZQB0AEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQARQBsAGUAbQBlAG4AdABGAHIAYQBjAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABFAGwAZQBtAGUAbgB0ACwAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEEAcgByAGEAeQAsACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsACAARQBsAGUAbQBlAG4AdABSAG8AdwAsAFwAbgAgACAAIAAgAEkATgBEAEUAWAAoAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgAE0AQQBUAEMASAAoAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQwBvAGwAdQBtAG4ALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABNAEEAVABDAEgAKABFAGwAZQBtAGUAbgB0ACwAIABFAGwAZQBtAGUAbgB0AFIAbwB3ACwAIAAwACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAYQBzAHMAbwBjAGkAYQB0AGUAZAAgAHcAaQB0AGgAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAbgBkACAAbABvAHMAcwBlAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwApACAAbABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGEAcwBzAG8AYwBpAGEAdABlAGQAIAB3AGkAdABoACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABhAG4AZAAgAGwAbwBzAHMAZQBzACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABvAHIAIABhAGMAcQB1AGkAcgBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAAxAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALAAgAFQAZQByAHIAaQB0AG8AcgB5ACAAbwByACAAZwByAGkAZAAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAAwAC4ANwA4ACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgADAALgA2ADcALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADAALgAyADIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdAAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABTAFcASQBTACkAXAAiACwAIAAwAC4ANQAwACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAZQByAG4AIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgATgBXAEkAUwApAFwAIgAsACAAMAAuADUANgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgADAALgAyADAALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQAgAC0AIABEAGEAcgB3AGkAbgAgAEsAYQB0AGgAZQByAGkAbgBlACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAEQASwBJAFMAKQBcACIALAAgADAALgA1ADYALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdABpAG8AbgBhAGwAXAAiACwAIAAwAC4ANgAyACwAIAAwAC4AMAA3AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAATgBTAFcAIABhAG4AZAAgAEEAQwBUACAAcwBwAGwAaQB0ACAAaQBuAHQAbwAgAHMAZQBwAGEAcgBhAHQAZQAgAHIAbwB3AHMALgBcACIAKQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADAAOgAgAFMAYwBvAHAAZQAgADIAOgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAFAAdQByAGMAaABhAHMAZQBkACAARQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADAAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAyAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXABuAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4AUQBlAGwAZQBjACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkACAAOgAgAGsAVwBoAFwAbgBFAEYAMgAsAGUAbABlAGMAIAA6ACAATABvAGMAYQB0AGkAbwBuACAALQAgAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAAawBXAGgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAGUAbABlAGMALAAgAEUARgAyAGUAbABlAGMALABcAG4AIAAgACAAIABRAGUAbABlAGMAIAAqACAARQBGADIAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQAyAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADAALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgADIALgAyACAARQBzAHQAaQBtAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABlAG4AZQByAGcAeQAgAHMAbwB1AHIAYwBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAMgAsAGUAbABlAGMAIAA9ACAAUQBlAGwAZQBjACAAKgAgAEUARgAyACwAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBlAGwAZQBjAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAMgAsAGUAbABlAGMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAALQAgAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAAawBXAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMgBcACIALAAgAFwAIgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAyAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXABuAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4AUQBlAGwAZQBjACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkACAAOgAgAGsAVwBoAFwAbgBFAEYAMwAsAGUAbABlAGMAIAA6ACAATABvAGMAYQB0AGkAbwBuACAALQAgAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAAawBXAGgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBlAGwAZQBjACwAIABFAEYAMwBlAGwAZQBjACwAXABuACAAIAAgACAAUQBlAGwAZQBjACAAKgAgAEUARgAzAGUAbABlAGMAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AOQBfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADMARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQAzAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwA5AF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMgAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABzAG8AdQByAGMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwA5AF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQAzACwAZQBsAGUAYwAgAD0AIABRAGUAbABlAGMAIAAqACAARQBGADMALABlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtACAAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AOQBfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADMARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBlAGwAZQBjAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAMwAsAGUAbABlAGMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAALQAgAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAAawBXAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwBcACIALAAgAFwAIgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQQBwAHAAZQBuAGQAaQB4ACAAMgAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsAHMAOgAgAFQAYQBiAGwAZQAgADIAMwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAEEAcABwAGUAbgBkAGkAeAAgADIAIAAtACAAVABhAGIAbABlACAAMgAzAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzADkALAAgADUALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBoAGUAbQBpAGMAYQBsACAAZgBvAHIAbQB1AGwAYQBcACIALAAgAFwAIgBHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgACgAQQBSADUAKQBcACIALAAgAFwAIgBHAGEAcwAgAC0AIABGAEMAIABuAGEAbQBlAFwAIgAsACAAXAAiAEEAZABpAHQAaQBvAG4AYQBsACAAZABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQBcACIALAAgAFwAIgBDAE8AMgBcACIALAAgADEALAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ACwAIABcACIAQwBIADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQBcACIALAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ACwAIABcACIATgAyAE8AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGwAcABoAHUAcgAgAGgAZQB4AGEAZgBsAHUAbwByAGkAZABlAFwAIgAsACAAXAAiAFMARgA2AFwAIgAsACAAMgAzADUAMAAwACwAIABcACIAUwBGADYAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADMAIAAoAFIALQAyADMAKQBcACIALAAgAFwAIgBDAEgARgAzAFwAIgAsACAAIAAxADIANAAwADAALAAgAFwAIgBIAEYAQwAtADIAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADMAMgAgACgAUgAtADMAMgApAFwAIgAsACAAXAAiAEMASAAyAEYAMgBcACIALAAgADYANwA3ACwAIABcACIASABGAEMALQAzADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQA0ADEAIAAoAFIALQA0ADEAKQBcACIALAAgAFwAIgBDAEgAMwBGAFwAIgAsACAAIAAxADEANgAsACAAXAAiAEgARgBDAC0ANAAxAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0ANAAzAC0AMQAwAG0AZQBlACAAKABSAC0ANAAzADEAMABtAGUAZQApAFwAIgAsACAAXAAiAEMANQBIADIARgAxADAAXAAiACwAIAAxADYANQAwACwAIABcACIASABGAEMALQA0ADMALQAxADAAbQBlAGUAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADIANQAgACgAUgAtADEAMgA1ACkAXAAiACwAIABcACIAQwAyAEgARgA1AFwAIgAsACAAIAAzADEANwAwACwAIABcACIASABGAEMALQAxADIANQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMwA0ACAAKABSAC0AMQAzADQAKQBcACIALAAgAFwAIgBDADIASAAyAEYANAAgACgAQwBIAEYAMgBDAEgARgAyACkAXAAiACwAIAAgADEAMQAyADAALAAgAFwAIgBIAEYAQwAtADEAMwA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAzADQAYQAgACgAUgAtADEAMwA0AGEAKQBcACIALAAgAFwAIgBDADIASAAyAEYANAAgACgAQwBIADIARgBDAEYAMwApAFwAIgAsACAAMQAzADAAMAAsACAAXAAiAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEANAAzACAAKABSAC0AMQA0ADMAKQBcACIALAAgAFwAIgBDADIASAAzAEYAMwAgACgAQwBIAEYAMgBDAEgAMgBGACkAXAAiACwAIAAzADIAOAAsACAAXAAiAEgARgBDAC0AMQA0ADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADQAMwBhACAAKABSAC0AMQA0ADMAYQApAFwAIgAsACAAXAAiAEMAMgBIADMARgAzACAAKABDAEYAMwBDAEgAMwApAFwAIgAsACAANAA4ADAAMAAsACAAXAAiAEgARgBDAC0AMQA0ADMAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEANQAyAGEAIAAoAFIALQAxADUAMgBhACkAXAAiACwAIABcACIAQwAyAEgANABGADIAIAAoAEMASAAzAEMASABGADIAKQBcACIALAAgADEAMwA4ACwAIABcACIASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgAyADcAZQBhACAAKABSAC0AMgAyADcAZQBhACkAXAAiACwAIABcACIAQwAzAEgARgA3AFwAIgAsACAAMwAzADUAMAAsACAAXAAiAEgARgBDAC0AMgAyADcAZQBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgAzADYAZgBhACAAKABSAC0AMgAzADYAZgBhACkAXAAiACwAIABcACIAQwAzAEgAMgBGADYAXAAiACwAIAA4ADAANgAwACwAIABcACIASABGAEMALQAyADMANgBmAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADQANQBjAGEAIAAoAFIALQAyADQANQBjAGEAKQBcACIALAAgAFwAIgBDADMASAAzAEYANQBcACIALAAgADcAMQA2ACwAIABcACIASABGAEMALQAyADQANQBjAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADQANQBmAGEAIAAoAFIALQAyADQANQBmAGEAKQBcACIALAAgAFwAIgBDAEgARgAyAEMASAAyAEMARgAzAFwAIgAsACAAOAA1ADgALAAgAFwAIgBIAEYAQwAtADIANAA1AGYAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADMANgA1AG0AZgBjACAAKABSAC0AMwA2ADUAbQBmAGMAKQBcACIALAAgAFwAIgBDAEgAMwBDAEYAMgBDAEgAMgBDAEYAMwBcACIALAAgADgAMAA0ACwAIABcACIASABGAEMALQAzADYANQBtAGYAYwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMgAyACAAKABSAC0AMgAyACkAXAAiACwAIABcACIAQwBIAEMAbABGADIAXAAiACwAIAAxADcANgAwACwAIABcACIASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQAyADMAIAAoAFIALQAxADIAMwApAFwAIgAsACAAXAAiAEMASABDAGwAMgAyAEMARgAzAFwAIgAsACAANwA5ACwAIABcACIASABDAEYAQwAtADEAMgAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADIANAAgACgAUgAtADEAMgA0ACkAXAAiACwAIABcACIAQwBIAEMAbABGAEMARgAzAFwAIgAsACAANQAyADcALAAgAFwAIgBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEANAAxAGIAIAAoAFIALQAxADQAMQBiACkAXAAiACwAIABcACIAQwBIADMAQwBDAGwAMgBGAFwAIgAsACAANwA4ADIALAAgAFwAIgBIAEMARgBDAC0AMQA0ADEAYgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQA0ADIAYgAgACgAUgAtADEANAAyAGIAKQBcACIALAAgAFwAIgBDAEgAMgBDAEMAbABGADIAXAAiACwAIAAxADkAOAAwACwAIABcACIASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADIAMgA1AGMAYQAgACgAUgAtADIAMgA1AGMAYQApAFwAIgAsACAAXAAiAEMASABDAGwAMgBDAEYAMgBDAEYAMwBcACIALAAgADEAMgA3ACwAIABcACIASABDAEYAQwAtADIAMgA1AGMAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBiACAAKABSAC0AMgAyADUAYwBiACkAXAAiACwAIABcACIAQwBIAEMAbABGAEMARgAyAEMAQwBJAEYAMgBcACIALAAgADUAMgA1ACwAIABcACIASABDAEYAQwAtADIAMgA1AGMAYgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADEANAAgAFAAZQByAGYAbAB1AG8AcgBvAG0AZQB0AGgAYQBuAGUAIAAoAHQAZQB0AHIAYQBmAGwAdQBvAHIAbwBtAGUAdABoAGEAbgBlACkAXAAiACwAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwACwAIABcACIAUABGAEMALQAxADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAxADEANgAgAFAAZQByAGYAbAB1AG8AcgBvAGUAdABoAGEAbgBlACAAKABoAGUAeABhAGYAbAB1AG8AcgBvAGUAdABoAGEAbgBlACkAXAAiACwAIABcACIAQwAyAEYANgBcACIALAAgADEAMQAxADAAMAAsACAAXAAiAFAARgBDAC0AMQAxADYAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAyADEAOAAgAFAAZQByAGYAbAB1AG8AcgBvAHAAcgBvAHAAYQBuAGUAXAAiACwAIABcACIAQwAzAEYAOABcACIALAAgADgAOQAwADAALAAgAFwAIgBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMwAxAC0AMQAwACAAUABlAHIAZgBsAHUAbwByAG8AYgB1AHQAYQBuAGUAXAAiACwAIABcACIAQwA0AEYAMQAwAFwAIgAsACAAOQAyADAAMAAsACAAXAAiAFAARgBDAC0AMwAxAC0AMQAwAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMwAxADgAIABQAGUAcgBmAGwAdQBvAHIAbwBjAHkAYwBsAG8AYgB1AHQAYQBuAGUAXAAiACwAIABcACIAYwAtAEMANABGADgAXAAiACwAIAA5ADUANAAwACwAIABcACIAUABGAEMALQAzADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADQAMQAtADEAMgAgAFAAZQByAGYAbAB1AG8AcgBvAHAAZQBuAHQAYQBuAGUAXAAiACwAIABcACIAQwA1AEYAMQAyAFwAIgAsACAAOAA1ADUAMAAsACAAXAAiAFAARgBDAC0ANAAxAC0AMQAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0ANQAxAC0AMQA0ACAAUABlAHIAZgBsAHUAbwByAG8AaABlAHgAYQBuAGUAXAAiACwAIABcACIAQwA2AEYAMQA0AFwAIgAsACAANwA5ADEAMAAsACAAXAAiAFAARgBDAC0ANQAxAC0AMQA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AOQAxAC0AMQA4ACAAUABlAHIAZgBsAHUAbgBhAGYAZQBuAGUAXAAiACwAIABcACIAQwAxADAARgAxADgAXAAiACwAIAA3ADEAOQAwACwAIABcACIAUABGAEMALQA5ADEALQAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADIAXAAiACwAIABcACIAQwBDAGwAMgBGADIAXAAiACwAIAAxADAAMgAwADAALAAgAFwAIgBDAEYAQwAtADEAMgBcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAzAFwAIgAsACAAXAAiAEMAQwBsAEYAMwBcACIALAAgADEAMwA5ADAAMAAsACAAXAAiAEMARgBDAC0AMQAzAFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADEANABcACIALAAgAFwAIgBDAEMAbABGADIAQwBDAGwARgAyAFwAIgAsACAAOAA1ADkAMAAsACAAXAAiAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMQA1AFwAIgAsACAAXAAiAEMAQwBsAEYAMgBDAEYAMwBcACIALAAgADcANgA3ADAALAAgAFwAIgBDAEYAQwAtADEAMQA1AFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AEcAQQBTACAALQAgAEYAQwAgAG4AYQBtAGUAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIAB0AHIAdQBuAGMAYQB0AGUAZAAgAGcAYQBzACAAbgBhAG0AZQAgAHQAbwAgAGEAbABsAG8AdwAgAG0AYQB0AGMAaABpAG4AZwAgAHcAaQB0AGgAIABvAHQAaABlAHIAIAB0AGEAYgBsAGUAcwAuACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAZwBhAHMAZQBzACAAZgByAG8AbQAgAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AEEAZABkAGkAdABpAG8AbgBhAGwAIABkAGEAdABhACAAcwBvAHUAcgBjAGUAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAuAFwAIgApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQQBwAHAAZQBuAGQAaQB4ACAAMgAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsAHMAOgAgAEIAbABlAG4AZABlAGQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBCAGwAZQBuAGQAZQBkACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAIAAoAG0AYQBuAHkAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAASABGAEMAUwAgAGEAbgBkAC8AbwByACAAUABGAEMAUwApAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAQQBwAHAAZQBuAGQAaQB4ACAAMgAgAC0AIABUAGEAYgBsAGUAIAAyADQAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUAMQAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGwAZQBuAGQAXAAiACwAIABcACIAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AHMAXAAiACwAIABcACIAQwBvAG0AcABvAHMAaQB0AGkAbwBuACAAKAAlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAwAFwAIgAsACAAXAAiAEMARgBDAC0AMQAyAC8AQwBGAEMALQAxADEANABcACIALAAgAFwAIgBSAC0ANAAwADAAIABjAGEAbgAgAGgAYQB2AGUAIAB2AGEAcgBpAG8AdQBzACAAcAByAG8AcABvAHIAdABpAG8AbgBzACAAbwBmACAAQwBGAEMALQAxADIAIABhAG4AZAAgAEMARgBDAC0AMQAxADQALgAgAFQAaABlACAAZQB4AGEAYwB0ACAAYwBvAG0AcABvAHMAaQB0AGkAbwBuACAAbgBlAGUAZABzACAAdABvACAAYgBlACAAcwBwAGUAYwBpAGYAaQBlAGQALAAgAGUALgBnAC4ALAAgAFIALQA0ADAAMAAgACgANgAwAC8ANAAwACkALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgANQAzAC4AMAAvADEAMwAuADAALwAzADQALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADYAMQAuADAALwAxADEALgAwAC8AMgA4AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBDAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAAzADMALgAwAC8AMQA1AC4AMAAvADUAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADIAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiACgANgAwAC4AMAAvADIALgAwAC8AMwA4AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMgBCAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAAzADgALgAwAC8AMgAuADAALwA2ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAzAEEAXAAiACwAIABcACIASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADUALgAwAC8ANwA1AC4AMAAvADIAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADMAQgBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANQAuADAALwA1ADYALgAwAC8AMwA5AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANABBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEANAAzAGEALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAA0ADQALgAwAC8ANQAyAC4AMAAvADQALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA1AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvACAASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEANAAyAGIALwBQAEYAQwAtADMAMQA4AFwAIgAsACAAXAAiACgANAA1AC4AMAAvADcALgAwAC8ANQAuADUALwA0ADIALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA2AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUANQAuADAALwAxADQALgAwAC8ANAAxAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADIAMAAuADAALwA0ADAALgAwAC8ANAAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANwBCAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADEAMAAuADAALwA3ADAALgAwAC8AMgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANwBDAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADIAMwAuADAALwAyADUALgAwAC8ANQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANwBEAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADEANQAuADAALwAxADUALgAwAC8ANwAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANwBFAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADIANQAuADAALwAxADUALgAwAC8ANgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAOABBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEANAAzAGEALwBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiACgANwAuADAALwA0ADYALgAwAC8ANAA3AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAOQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEMARgBDAC0AMQAyADQALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADYAMAAuADAALwAyADUALgAwAC8AMQA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAOQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEMARgBDAC0AMQAyADQALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADYANQAuADAALwAyADUALgAwAC8AMQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMABBAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQBcACIALAAgAFwAIgAoADUAMAAuADAALwA1ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAwAEIAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiACgANAA1AC4AMAAvADUANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADEAQQBcACIALAAgAFwAIgBIAEMALQAxADIANwAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADEALgA1AC8AOAA3AC4ANQAvADEAMQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADEAQgBcACIALAAgAFwAIgBIAEMALQAxADIANwAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADMALgAwAC8AOQA0AC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAxAEMAXAAiACwAIABcACIASABDAC0AMQAyADcAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAzAC4AMAAvADkANQAuADUALwAxAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMgBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA3ADAALgAwAC8ANQAuADAALwAyADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAzAEEAXAAiACwAIABcACIAUABGAEMALQAyADEAOAAvAEgARgBDAC0AMQAzADQAYQAvAEgAQwAtADYAMAAwAGEAXAAiACwAIABcACIAKAA5AC4AMAAvADgAOAAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANABBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEMARgBDAC0AMQAyADQALwBIAEMALQA2ADAAMABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA1ADEALgAwAC8AMgA4AC4ANQAvADQALgAwAC8AMQA2AC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANABCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEMARgBDAC0AMQAyADQALwBIAEMALQA2ADAAMABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA1ADAALgAwAC8AMwA5AC4AMAAvADEALgA1AC8AOQAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADUAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAOAAyAC4AMAAvADEAOAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADUAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMgA1AC4AMAAvADcANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADYAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMwA0AGEALwBIAEMARgBDAC0AMQAyADQALwBIAEMALQA2ADAAMABcACIALAAgAFwAIgAoADUAOQAuADAALwAzADkALgA1AC8AMQAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADcAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAXAAiACwAIABcACIAKAA0ADYALgA2AC8ANQAwAC4AMAAvADMALgA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA4AEEAXAAiACwAIABcACIASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMQAuADUALwA5ADYALgAwAC8AMgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADkAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABFAC0ARQAxADcAMABcACIALAAgAFwAIgAoADcANwAuADAALwAxADkALgAwAC8ANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADAAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMwA0AGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADgAOAAuADAALwAxADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMgAxAEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADUAOAAuADAALwA0ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMgAyAEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgAQwAtADYAMAAwAGEAXAAiACwAIABcACIAKAA4ADUALgAxAC8AMQAxAC4ANQAvADMALgA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMgAyAEIAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgAQwAtADYAMAAwAGEAXAAiACwAIABcACIAKAA1ADUALgAwAC8ANAAyAC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMgAyAEMAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgAQwAtADYAMAAwAGEAXAAiACwAIABcACIAKAA4ADIALgAwAC8AMQA1AC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAwAFwAIgAsACAAXAAiAEMARgBDAC0AMQAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgANwAzAC4AOAAvADIANgAuADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiACgANwA1AC4AMAAvADIANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAKAA0ADgALgA4AC8ANQAxAC4AMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMwBcACIALAAgAFwAIgBIAEYAQwAtADIAMwAvAEMARgBDAC0AMQAzAFwAIgAsACAAXAAiACgANAAwAC4AMQAvADUAOQAuADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADQAXAAiACwAIABcACIASABGAEMALQAzADIALwBDAEYAQwAtADEAMQA1AFwAIgAsACAAXAAiACgANAA4AC4AMgAvADUAMQAuADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADUAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBIAEMARgBDAC0AMwAxAFwAIgAsACAAXAAiACgANwA4AC4AMAAvADIAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADYAXAAiACwAIABcACIAQwBGAEMALQAzADEALwBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiACgANQA1AC4AMQAvADQANAAuADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADcAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADQAMwBhAFwAIgAsACAAXAAiACgANQAwAC4AMAAvADUAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADgAQQBcACIALAAgAFwAIgBIAEYAQwAtADIAMwAvAFAARgBDAC0AMQAxADYAXAAiACwAIABcACIAKAAzADkALgAwAC8ANgAxAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOABCAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AUABGAEMALQAxADEANgBcACIALAAgAFwAIgAoADQANgAuADAALwA1ADQALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA5AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA0ADQALgAwAC8ANQA2AC4AMAApAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAGMAaABhAG4AZwBlAGQAIABIAEMANgAwADAAYQAgAHQAbwAgAEgAQwAtADYAMAAwAGEAIABmAG8AcgAgAGIAbABlAG4AZAAgAFIALQA0ADEANABCAC4AIABGAGkAeABlAGQAIAB0AHkAcABvACAAZgBvAHIAIABiAGwAZQBuAGQAIABSAC0ANAAwADUAQQAgAC0AIABDAGgAYQBuAGcAZQBkACAASABDAEYAQwAxADQAMgBiACAAdABvACAASABDAEYAQwAtADEANAAyAGIALgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBMAGUAYQBrAGEAZwBlACAAcgBhAHQAZQBzACAAZgBvAHIAIABjAG8AbQBtAG8AbgAgAHIAZQBmAHIAaQBnAGUAcgBhAHQAaQBvAG4AIABhAG4AZAAgAGEAaQByAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQBjAGEAdABpAHYAZQAgAGwAZQBhAGsAYQBnAGUAIAByAGEAdABlAHMAIABmAG8AcgAgAGMAbwBtAG0AbwBuACAAcgBlAGYAcgBpAGcAZQByAGEAdABpAG8AbgAgAGEAbgBkACAAYQBpAHIAIAAtACAAYwBvAG4AZABpAHQAaQBvAG4AaQBuAGcAIABlAHEAdQBpAHAAbQBlAG4AdABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAAxADAAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAxACwAIAAyACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIABsAGUAYQBrAGEAZwBlACAAcgBhAHQAZQAgACgAJQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAHIAZQBmAHIAaQBnAGUAcgBhAHQAbwByAHMAXAAiACwAIAAxAC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBwAG8AcgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAdABpAG8AbgBcACIALAAgADEANQAuADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHAAbwByAHQAYQBiAGwAZQBcACIALAAgADIALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABzAHAAbABpAHQAXAAiACwAIAAzAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcABhAGMAawBhAGcAZQBkAFwAIgAsACAAMgAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAZwBoAHQAIAB2AGUAaABpAGMAbABlACAAQQAvAEMAXAAiACwAIAA2AC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAHYAZQBoAGkAYwBsAGUAIABBAC8AQwBcACIALAAgADEAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AOQA6ACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AOQAuADEAIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBcAG4AVABoAGUAIAB0AG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAaQBuAGcAIABkAHUAcgBpAG4AZwAgAG8AcABlAHIAYQB0AGkAbwBuACAAKABuAG8AdAAgAGQAdQByAGkAbgBnACAAaQBuAHMAdABhAGwAbABhAHQAaQBvAG4AIABvAHIAIABkAGkAcwBwAG8AcwBhAGwAKQBcAG4ARwBXAFAAUgAgADoAIABHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIAA6ACAARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AYwBoAGEAcgBnAGUAUgBhACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAOgAgAGsAZwBcAG4AbABlAGEAawBhAGcAZQByAGEAdABlAGEAIAA6ACAAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByACAAOgAgAFAAZQByAGMAZQBuAHQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEcAVwBQAFIALAAgAGMAaABhAHIAZwBlAFIAYQAsACAAbABlAGEAawBhAGcAZQByAGEAdABlAGEALABcAG4AIAAgACAAIABHAFcAUABSACAAKgAgAGMAaABhAHIAZwBlAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBhAC8AMQAwADAAKQAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMwAuADEAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAaQBuAGQAdQBzAHQAcgBpAGEAbAAgAHAAcgBvAGMAZQBzAHMAZQBzACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAtACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBhAGcAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABSACAAKgAgAGMAaABhAHIAZwBlAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBhAC8AMQAwADAAKQAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABSAFwAIgAsACAAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgBcACIALAAgAFwAIgBEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAGgAYQByAGcAZQBSAGEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSACAAYwBvAG4AdABhAGkAbgBlAGQAIABpAG4AIABhAHAAcABsAGkAYQBuAGMAZQAgAGEAXAAiACwAIABcACIAawBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBsAGUAYQBrAGEAZwBlAHIAYQB0AGUAYQBcACIALAAgAFwAIgBQAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAHQAbwB0AGEAbAAgAGMAaABhAHIAZwBlACAAbABlAGEAawBlAGQAIABmAHIAbwBtACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAZQBhAGMAaAAgAHkAZQBhAHIAXAAiACwAIABcACIAUABlAHIAYwBlAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYQBcACIALAAgAFwAIgBBAHAAcABsAGkAYQBuAGMAZQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBcACIALAAgAFwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAXAAiACwAIABcACIAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADEAIABJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAcwAgAGYAIAB0AG8AIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAbgBFAE4AMgBPAFwAbgB0ACAAQwBPADIALQBlAFwAbgBNAE4AagBmACAAOgAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqACAAOgAgAGsAZwAgAE4AXABuAEUARgBqAE4AMgBPACAAOgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcAG4AQwBnAE4AMgBPACAAOgAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAGoAIAA6ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBmACAAOgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXABuAEcAVwBQAE4AMgBPACAAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAOgAgAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPAFwAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBHAFcAUABcAG4AIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBOADIATwAsAEcAVwBQAE4AMgBPACwAXABuACAAIAAgACAAIAAoAEUATgAyAE8AIAAqACAARwBXAFAATgAyAE8AKQBcAG4AIAAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBqAGYALAAgAEUARgBqAE4AMgBPACwAIABDAGcATgAyAE8ALABcAG4AIAAgACAAIABNAE4AagBmACAAKgAgAEUARgBqAE4AMgBPACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAIABeAC0AMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQAsACAAMgAwADIAMwA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBBAF8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAD0AIABNAE4AagBmACAAKgAgAEUARgBqAE4AMgBPACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAGoAZgBcACIALABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGkAbgAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAIAA6ACAAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGoATgAyAE8AXAAiACwAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBnAE4AMgBPAFwAIgAsAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAOgAgAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABcAG4ATQBOAGoAZgBcAG4AawBnACAATgBcAG4AVABNAGoAZgAgADoAIABUAG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagAgADoAIABrAGcAXABuAEYATgBpAG4AbwByAGcAYQBuAGkAYwBmACAAOgAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAOgAgAGsAZwAgAE4ALwBrAGcAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABNAGoAZgAsACAARgBOAGkAbgBvAHIAZwBhAG4AaQBjAGYALABcAG4AIAAgACAAIABUAE0AagBmACAAKgAgAEYATgBpAG4AbwByAGcAYQBuAGkAYwBmAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQAsACAAMgAwADIAMwA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBBAF8AMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBqAGYAIAA9ACAAVABNAGoAZgAgACoAIABGAE4AaQBuAG8AcgBnAGEAbgBpAGMAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABNAGoAZgBcACIALABcACIAVABvAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAIAA6ACAAawBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAE4AaQBuAG8AcgBnAGEAbgBpAGMAZgBcACIALABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIAA6ACAAawBnACAATgAvAGsAZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAG4AbwByAGcAYQBuAGkAYwBcACIALAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAFUAcgBlAGEARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAEMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcgBlAHMAdQBsAHQAaQBuAGcAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACwAIAB1AHIAZQBhAC0AYgBhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAbgBFAGoAZgBDAE8AMgBcAG4AdAAgAEMATwAyAFwAbgBNAFUAagBmACAAOgAgAG0AYQBzAHMAIABvAGYAIAB1AHIAZQBhACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagAgADoAIABrAGcAIAB1AHIAZQBhAFwAbgBFAEYAdQByAGUAYQBDAE8AMgAgADoAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBhAHIAYgBvAG4AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHIAZQBhAC0AYgBhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzACAAOgAgAGsAZwAgAEMALwBrAGcAIAB1AHIAZQBhACAAXABuAEMAZwBDAE8AMgAgADoAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAA6ACAAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AVQBqAGYALAAgAEUARgB1AHIAZQBhAEMATwAyACwAIABDAGcAQwBPADIALABcAG4AIAAgACAAIABNAFUAagBmACAAKgAgAEUARgB1AHIAZQBhAEMATwAyACAAKgAgAEMAZwBDAE8AMgAgACoAIAAxADAAIABeAC0AMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8AVQByAGUAYQBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMALAAgAHUAcgBlAGEALQBiAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAGoAZgBDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAFUAcgBlAGEARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8AVQByAGUAYQBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxACwAIAAyADAAMgAzADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ASABfADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBqAGYAQwBPADIAIAA9ACAATQBVAGoAZgAgAHgAIABFAEYAdQByAGUAYQBDAE8AMgAgAHgAIABDAGcAQwBPADIAIAB4ACAAMQAwAF4ALQAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8AVQByAGUAYQBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGoAZgAsAEMATwAyAH0APQB7AE0AVQB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB1AHIAZQBhACwAQwBPADIAfQBcAFwAIABcAFwAdABpAG0AZQBzAFwAXAAgAEMAXwB7AGcALABDAE8AMgB9AFwAXAB0AGkAbQBlAHMAewAxADAAfQBeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFUAagBmAFwAIgAsAFwAIgBNAGEAcwBzACAAbwBmACAAdQByAGUAYQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAIAA6ACAAawBnACAAdQByAGUAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAHUAcgBlAGEAQwBPADIAXAAiACwAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAGEAcgBiAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHUAcgBlAGEALQBiAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIAA6ACAAawBnACAAQwAvAGsAZwAgAHUAcgBlAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAZwBDAE8AMgBcACIALABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALABcACIARgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFwAbgBNAGEAcwBzACAAbwBmACAAdQByAGUAYQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAXABuAE0AVQBqAGYAXABuAGsAZwAgAHUAcgBlAGEAXABuAFQATQBqAGYAIAA6ACAAdABoAGUAIAB0AG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagAgADoAIABrAGcAXABuAEYAVQBmACAAOgAgAHQAaABlACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdQByAGUAYQAgAGkAbgAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgADoAIABrAGcAIAB1AHIAZQBhAC8AawBnAFwAbgBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAE0AagBmACwAIABGAFUAZgAsAFwAbgAgACAAIAAgAFQATQBqAGYAIAAqACAARgBVAGYAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAdQByAGUAYQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBVAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAdQByAGUAYQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AVQBqAGYAIAA9ACAAVABNAGoAZgAgANcAIABGAFUAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAE0AagBmAFwAIgAsAFwAIgB0AGgAZQAgAHQAbwB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqACAAOgAgAGsAZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBVAGYAXAAiACwAXAAiAHQAaABlACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdQByAGUAYQAgAGkAbgAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgADoAIABrAGcAIAB1AHIAZQBhAC8AawBnAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALABcACIARgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMgAgAE8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAGEAbABsACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcAG4ARQBOADIATwBcAG4AdAAgAEMATwAyAC0AZQBcAG4ATQBOAFMAbwBpAGwAagBmACAAOgAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGkAbgAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAIAA6ACAAawBnACAATgBcAG4ARQBGAGkATgAyAE8AIAA6ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGQAaQByAGUAYwB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBDAGcATgAyAE8AIAA6ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwA6ACAAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AagAgADoAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXABuAGYAIAA6ACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAbgBpACAAOgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAbgBHAFcAUABOADIATwAgADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgADoAIAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBHAFcAUABcAG4AIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBOADIATwAsAEcAVwBQAE4AMgBPACwAXABuACAAIAAgACAAIAAoAEUATgAyAE8AIAAqACAARwBXAFAATgAyAE8AKQBcAG4AIAAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAFMAbwBpAGwAagBmACwAIABFAEYAaQBOADIATwAsACAAQwBnAE4AMgBPACwAXABuACAAIAAgACAATQBOAFMAbwBpAGwAagBmACAAKgAgAEUARgBpAE4AMgBPACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAIABeAC0AMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAGEAbgBkACAAYQBsAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwAgAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxACwAIAAyADAAMgAzADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEEAXwA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIAA9ACAATQBOAFMAbwBpAGwAagBmACAAKgAgAEUARgBpAE4AMgBPACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AUwBvAGkAbABqAGYAXAAiACwAIABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAaQBOADIATwBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAZwBOADIATwBcACIALABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgADoAIABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAE8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgADoAIAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAgACAALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcAB1AHIAYwBoAGEAcwBlAGQAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwBcAG4ATQBOAFMAbwBpAGwAagBmAFwAbgBrAGcAXABuAE0AbwByAGcAYQBuAGkAYwBqAGYAIAA6ACAAbQBhAHMAcwAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagAgADoAIABrAGcAXABuAEYATgBvAHIAZwBhAG4AaQBjAGYAIAA6ACAAbgBpAHQAcgBvAGcAZQBuACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgADoAIABrAGcAIABOAC8AawBnAFwAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBvAHIAZwBhAG4AaQBjAGoAZgAsACAARgBOAG8AcgBnAGEAbgBpAGMAZgAsAFwAbgAgACAAIAAgAE0AbwByAGcAYQBuAGkAYwBqAGYAIAAqACAARgBOAG8AcgBnAGEAbgBpAGMAZgBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAagBmACAAPQAgAE0AbwByAGcAYQBuAGkAYwBqAGYAIAAqACAARgBOAG8AcgBnAGEAbgBpAGMAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AcgBnAGEAbgBpAGMAagBmAFwAIgAsACAAXAAiAG0AYQBzAHMAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGkAbgAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAIAA6ACAAawBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAE4AbwByAGcAYQBuAGkAYwBmAFwAIgAsACAAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIAA6ACAAawBnACAATgAvAGsAZwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQA6ACAARgBlAHIAdABpAGwAaQBzAGUAcgAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUALgAzACAATABpAG0AZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAFQAaABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAYQBuAGQAIABkAG8AbABvAG0AaQB0AGUAIAB0AG8AIABzAG8AaQBsAHMAXABuAEUAbABpAG0AZQBcAG4AdAAgAEMATwAyAFwAbgBNAGwAaQBtAGUAIAA6ACAAdABoAGUAIAB0AG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbABpAG0AZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIAA6ACAAawBnAFwAbgBGAHIAYQBjAEwAaQBtAGUAIAA6ACAAdABoAGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAYQBzACAAbABpAG0AZQBzAHQAbwBuAGUAIAAoAEMAYQBDAE8AMwApACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAFAAbABpAG0AZQAgADoAIABmAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABsAGkAbQBlAHMAdABvAG4AZQAgADoAIABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBFAEYAbABpAG0AZQAgADoAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABpAG0AZQBzAHQAbwBuAGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAOgAgAGsAZwAgAEMALwBrAGcAXABuAEYAcgBhAGMARABvAGwAIAA6ACAAdABoAGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAYQBzACAAZABvAGwAbwBtAGkAdABlACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAFAAUABkAG8AbAAgADoAIABmAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABkAG8AbABvAG0AaQB0AGUAIAA6ACAAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4ARQBGAGQAbwBsACAAOgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAG8AbABvAG0AaQB0AGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAOgAgAGsAZwAgAEMALwBrAGcAXABuAFwAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBsAGkAbQBlACwAIABGAHIAYQBjAEwAaQBtAGUALAAgAFAAbABpAG0AZQAsACAARQBGAGwAaQBtAGUALAAgAEYAcgBhAGMARABvAGwALAAgAFAAZABvAGwALAAgAEUARgBkAG8AbAAsACAAQwBnAEMATwAyACwAXABuACAAIAAgACAAKAAoAE0AbABpAG0AZQAgACoAIAAgAEYAcgBhAGMATABpAG0AZQAgACoAIABQAGwAaQBtAGUAIAAqACAARQBGAGwAaQBtAGUAKQAgACsAIAAoAE0AbABpAG0AZQAgACoAIABGAHIAYQBjAEQAbwBsACAAKgAgAFAAZABvAGwAIAAqACAARQBGAGQAbwBsACkAKQAgACoAIABDAGcAQwBPADIAIAAqACAAMQAwAF4ALQAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABoAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAG4AZAAgAGQAbwBsAG8AbQBpAHQAZQAgAHQAbwAgAHMAbwBpAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAGwAaQBtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQAsACAAMgAwADIAMwA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwBHAF8AMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBsAGkAbQBlACAAPQAgACgAKABNAGwAaQBtAGUAIAAqACAAIABGAHIAYQBjAEwAaQBtAGUAIAAqACAAUABsAGkAbQBlACAAKgAgAEUARgBsAGkAbQBlACkAIAArACAAKABNAGwAaQBtAGUAIAAqACAARgByAGEAYwBEAG8AbAAgACoAIABQAGQAbwBsACAAKgAgAEUARgBkAG8AbAApACkAIAAqACAAQwBnAEMATwAyACAAKgAgADEAMABeAC0AMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGwAaQBtAGUAXAAiACwAIABcACIAVABoAGUAIAB0AG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbABpAG0AZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIAA6ACAAawBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwAaQBtAGUAXAAiACwAIABcACIAVABoAGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAYQBzACAAbABpAG0AZQBzAHQAbwBuAGUAIAAoAEMAYQBDAE8AMwApACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAbABpAG0AZQBcACIALAAgAFwAIgBGAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABsAGkAbQBlAHMAdABvAG4AZQAgADoAIABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABpAG0AZQBcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABpAG0AZQBzAHQAbwBuAGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAOgAgAGsAZwAgAEMALwBrAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARABvAGwAXAAiACwAIABcACIAVABoAGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAYQBzACAAZABvAGwAbwBtAGkAdABlACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAUABkAG8AbABcACIALAAgAFwAIgBGAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABkAG8AbABvAG0AaQB0AGUAIAA6ACAAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGQAbwBsAFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAG8AbABvAG0AaQB0AGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAOgAgAGsAZwAgAEMALwBrAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAZwBDAE8AMgBcACIALABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADQAIABBAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABmAHIAbwBtACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcAG4AIABFAGEAZABpAG4AbwByAGcAYQBuAGkAYwBcAG4AIAB0ACAATgAyAE8AXABuAE0AdgBvAGwAaQBuAG8AcgBnAGEAbgBpAGMAagBmACAALAAgAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBzAGUAZAAgAGYAcgBvAG0AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzADoAIABrAGcAIABOAFwAbgBFAEYAYQBkAGoAIAAsACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEcAVwBQAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUATgAyAE8AYQBkACwARwBXAFAATgAyAE8ALAAgAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEcAVwBQACgARQBOADIATwBhAGQALABHAFcAUABOADIATwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYALAAgAEUARgBhAGQAagAsACAAQwBnAE4AMgBPACwAXABuACAAIAAgACAAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuACgATQB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYALABFAEYAYQBkAGoALABDAGcATgAyAE8AKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABmAHIAbwBtACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAYQBkAGkAbgBvAHIAZwBhAG4AaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAKAApACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBhAGQAaQBuAG8AcgBnAGEAbgBpAGMAIAA9ACAATQB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAIAAqACAARQBGAGEAZABqACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcACIAIAAsACAAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBzAGUAZAAgAGYAcgBvAG0AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAYQBkAGoAXAAiACAALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGcATgAyAE8AXAAiACwAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAA6ACAAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAA6ACAAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIAAgAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ATQB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAXABuAGsAZwAgAE4AXABuAE0ATgBqAGYAIAAsACAATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAA6ACAAawBnACAATgBcAG4ARgByAGEAYwBHAEEAUwBGAGYAIAAsACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdABoAGEAdAAgAHYAbwBsAGEAdABpAGwAaQBzAGUAcwAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AIABcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAGoAZgAsACAARgByAGEAYwBHAEEAUwBGAGYALABcAG4AIAAgACAAIABDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAoAE0ATgBqAGYALAAgAEYAcgBhAGMARwBBAFMARgBmACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAoACkAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgAgAD0AIABNAE4AagBmACAAKgAgAEYAcgBhAGMARwBBAFMARgBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAGoAZgBcACIALABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAA6ACAAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBGAGYAXAAiACwAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAaABhAHQAIAB2AG8AbABhAHQAaQBsAGkAcwBlAHMAIAA6ACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwByAG8AcABzACAAYwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ARQBcAG4AdAAgAE4AMgBPAFwAbgBFAD0AXABcAHMAdQBtAF8AewBjAH0AewBNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBnACwATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQB9AFwAbgBNAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIABjACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOACkAXABuAEUARgBOAGkAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBnAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AYwAsACAARQBGAE4AaQAsACAAQwBnAE4AMgBPACwAXABuACAAIAAgACAATQBjACAAKgAgAEUARgBOAGkAIAAqACAAQwBnAE4AMgBPACAAKgAgADEAMABeACgALQAzACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwByAG8AcABzACAAYwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXwB7AGMAfQB7AE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AGcALABOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIABjACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBOAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAZwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ATQBjAFwAbgBrAGcAIABOAFwAbgBNAF8AewBjAH0APQAoAFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AGMAfQAtAEYARgBPAEQAXwB7AGMAfQApAFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBBAEcAYwB9ACkAKwAoAFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQgBHAGMAfQBcAFwAdABpAG0AZQBzACAARABNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQgBHAGMAfQApAFwAbgBQAGMAIAA9ACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwApAFwAbgBSAEEARwBjACAAPQAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBSAEIARwBjACAAPQAgAGIAZQBsAG8AdwAgAGcAcgBvAHUAbgBkAC0AcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAgAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARgBjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARgBGAE8ARABjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARABNAGMAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAYwAgACgAawBnACAAZAByAHkAIAB3AGUAaQBnAGgAdAAvAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACkAXABuAE4AQwBBAEcAYwAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAE4AQwBCAEcAYwAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAGMALAAgAFIAQQBHAGMALAAgAEYAYwAsACAARgBGAE8ARABjACwAIABEAE0AYwAsACAATgBDAEEARwBjACwAIABSAEIARwBjACwAIABOAEMAQgBHAGMALABcAG4AIAAgACAAIAAoAFAAYwAgACoAIABSAEEARwBjACAAKgAgACgAMQAgAC0AIABGAGMAIAAtACAARgBGAE8ARABjACkAIAAqACAARABNAGMAIAAqACAATgBDAEEARwBjACkAIAArACAAKABQAGMAIAAqACAAUgBBAEcAYwAgACoAIABSAEIARwBjACAAKgAgAEQATQBjACAAKgAgAE4AQwBCAEcAYwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAYwB9AD0AKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAF8AewBjAH0ALQBGAEYATwBEAF8AewBjAH0AKQBcAFwAdABpAG0AZQBzACAARABNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAGMAfQApACsAKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEIARwBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEIARwBjAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGMAXAAiACwAXAAiAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBBAEcAYwBcACIALABcACIAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAQgBHAGMAXAAiACwAXAAiAGIAZQBsAG8AdwAgAGcAcgBvAHUAbgBkAC0AcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAgAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAYwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0AYwBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAYwAgACgAawBnACAAZAByAHkAIAB3AGUAaQBnAGgAdAAvAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBBAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAQgBHAGMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALABcACIAUwB0AGEAdABlACAAbwByACAAdABlAHIAcgBpAHQAbwByAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAB3AGgAZQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABhAHIAZQAgAGIAYQBsAGUAZABcAG4ARgBGAE8ARABjAGIAYQBsAGUAZABcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4ARgBGAE8ARABfAHsAYwB9AD0AXABcAGYAcgBhAGMAewBCAFwAXAB0AGkAbQBlAHMAIABNAF8AewBCAH0AfQB7AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHACwAYwB9AH0AXABuAEIAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABiAGEAbABlAHMAIABnAGUAbgBlAHIAYQB0AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBNAEIAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAGUAYQBjAGgAIABiAGEAbABlACAAKABrAGcAKQBcAG4AUABjACAAPQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAKQBcAG4AUgBBAEcAYwAgAD0AIAByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABCACwAIABNAEIALAAgAFAAYwAsACAAUgBBAEcAYwAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKAAoAEIAIAAqACAATQBCACkAIAAvACAAKABQAGMAIAAqACAAUgBBAEcAYwApACwAIAAwACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjACwAIABjAGEAbABjAHUAbABhAHQAZQBkACAAdwBoAGUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAYQByAGUAIABiAGEAbABlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAGMAYgBhAGwAZQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADIALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AewBjACwAYgBhAGwAZQBkAH0APQBcAFwAZgByAGEAYwB7AEIAXABcAHQAaQBtAGUAcwAgAE0AXwB7AEIAfQB9AHsAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcALABjAH0AfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAXAAiACwAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAYgBhAGwAZQBzACAAZwBlAG4AZQByAGEAdABlAGQAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBCAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAZQBhAGMAaAAgAGIAYQBsAGUAIAAoAGsAZwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGMAXAAiACwAXAAiAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBBAEcAYwBcACIALABcACIAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AGIAYQBsAGUAZABcAHUAMAAwADIANwAgAHQAbwAgAHYAYQByAGkAYQBiAGwAZQAgAHMAdQBiAHMAYwByAGkAcAB0AFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMAXABuAEYARgBPAEQAYwBcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEYARgBPAEQAYwBiAGEAbABlAGQALAAgAEYARgBPAEQAYwBvAHQAaABlAHIALABcAG4AIAAgACAAIABGAEYATwBEAGMAYgBhAGwAZQBkACAAKwAgAEYARgBPAEQAYwBvAHQAaABlAHIAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AewBjAH0AIAA9ACAARgBGAE8ARABfAHsAYwAsAGIAYQBsAGUAZAB9ACAAKwAgAEYARgBPAEQAXwB7AGMALABvAHQAaABlAHIAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAGMAYgBhAGwAZQBkAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAHcAaABlAHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAcgBlACAAYgBhAGwAZQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAGMAbwB0AGgAZQByAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAHcAaABlAHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAgAGIAeQAgAG8AdABoAGUAcgAgAG0AZQBhAG4AcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAdABoAGkAcwAgAGUAcQB1AGEAdABpAG8AbgAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAHUAcwBlAHIALQBkAGUAZgBpAG4AZQBkACAAcgBlAHMAaQBkAHUAZQAgAHIAZQBtAG8AdgBhAGwAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAYgBhAGwAaQBuAGcALgBcACIAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQQBnAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADEAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4AMQA6ACAAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADAALAAgADkALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAUgBlAHMAaQBkAHUAZQA6ACAAQwByAG8AcAAgAHIAYQB0AGkAbwBcACIALAAgAFwAIgBCAGUAbABvAHcALQBnAHIAbwB1AG4AZAA6ACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0AFwAIgAsACAAXAAiAEMAYQByAGIAbwBuACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAZAByAHkAIABtAGEAdAB0AGUAcgBcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkAFwAIgAsACAAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAXAAiACwAIABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAdABpAG0AZQAgAG8AZgAgAGIAdQByAG4AaQBuAGcAXAAiACwAIABcACIAQgB1AHIAbgBpAG4AZwAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsACAAXAAiAFIAQQBHAGMAXAAiACwAIABcACIAUgBCAEcAYwBcACIALAAgAFwAIgBEAE0AYwBcACIALAAgAFwAIgBDAEMAYwBcACIALAAgAFwAIgBOAEMAQQBHAGMAXAAiACwAIABcACIATgBDAEIARwBjAFwAIgAsACAAXAAiAFMAYwBcACIALAAgAFwAIgBaAGMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAMQAuADUAMAAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOQAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIAAxAC4AMgA0ACwAIAAwAC4AMwAyACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADcALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AMwA5ACwAIAAwAC4AOAA1ACwAIAAwAC4ANAAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANwAsACAAMQAuADAALAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAMQAuADQAMgAsACAAMAAuADQAMwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgADEALgAzADEALAAgADAALgAxADYALAAgADAALgA4ADAALAAgADAALgA0ADIALAAgADAALgAwADAANwAsACAAMAAuADAAMQAwACwAIAAxAC4AMAAsACAAMAAuADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIAAxAC4ANQAwACwAIAAwAC4AMgAyACwAIAAwAC4AOAAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADgALAAgADAALgAwADAANwAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgADEALgA1ADAALAAgADAALgA0ADIALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIAAxAC4ANAA2ACwAIAAwAC4AMwA2ACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADYALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgADEALgAzADcALAAgADAALgA1ADEALAAgADAALgA4ADcALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIAAwAC4AMwA0ACwAIAAwAC4ANAAzACwAIAAwAC4AMgA1ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAyADAALAAgADAALgAwADEAMAAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIAAxAC4AMAA3ACwAIAAwAC4AMgAwACwAIAAwAC4AOAAwACwAIAAwAC4ANAAyACwAIAAwAC4AMAAxADYALAAgADAALgAwADEANAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADIANQAsACAAMAAuADQANQAsACAAMAAuADIAMAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADcALAAgADEALgAwACwAIAAwAC4AOAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIAAxAC4AOQAwACwAIAAwAC4AMwAwACwAIAAwAC4AOQAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAbgAvAGEAXAAiACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgADEALgA1ADAALAAgADAALgAyADkALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgADIALgAwADgALAAgADAALgAzADMALAAgADAALgA5ADYALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAMQAuADMANAAsACAAMAAuADMANwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgAFwAIgBuAC8AYQBcACIALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgADEALgAwADAALAAgADAALgAyADIALAAgADAALgA4ADUALAAgADAALgA0ADAALAAgADAALgAwADAAOAAsACAAMAAuADAAMAA5ACwAIABcACIAbgAvAGEAXAAiACwAIABcACIAbgAvAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIAAxAC4ANQAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAXAB1ADAAMAAyADcATgAvAEEAXAB1ADAAMAAyADcAIAB2AGEAbAB1AGUAcwAgAHAAYQBzAHMAZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVABhAGIAbABlACAAQQAuADIALgAxAC4AMgA6ACAAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAIAAtACAARgByAGEAYwB0AGkAbwBuACAAcgBlAG0AbwB2AGUAZAAgACgARgBGAE8ARABjACkAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADIAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMAAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIABGAEYATwBEAGMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBDAHUAcwB0AG8AbQBpAHMAZQBkAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ADQALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAARgBGAE8ARABjAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIATgAvAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABTAHAAbABpAHQAIABcAHUAMAAwADIANwBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAB1ADAAMAAyADcAIABpAG4AdABvACAAaQBuAGQAaQB2AGkAZAB1AGEAbAAgAGMAcgBvAHAAIAB0AHkAcABlAHMAIABmAG8AcgAgAGUAYQBjAGgAIABzAHQAYQB0AGUALgAgAEwAaQBzAHQAZQBkACAAYQBsAGwAIABzAHQAYQB0AGUAcwAgAGYAbwByACAAUwB1AGcAYQByACAAQwBhAG4AZQAsACAAdwBpAHQAaAAgAFwAdQAwADAAMgA3AE4ALwBBAFwAdQAwADAAMgA3ACAAZgBvAHIAIABzAHQAYQB0AGUAcwAgAHcAaABlAHIAZQAgAGkAdAAgAGkAcwAgAG4AbwB0ACAAZwByAG8AdwBuAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUABhAHMAdAB1AHIAZQAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAIABQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAOgAgAFAAYQBzAHQAdQByAGUAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAAWQBpAGUAbABkACAAKAB0ACAARABNACAAaABhACkAIABZAHAAXAAiACwAIABcACIAQgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAOgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAFIAQgBHAHAAXAAiACwAIABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABBAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAE4AQwBBAEcAcABcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAEIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAATgBDAEIARwBwAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAEYARgBPAEQAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AbgB1AGEAbAAgAGcAcgBhAHMAcwBcACIALAAgADQALgA0ADEALAAgADAALgA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAYQBzAHMAIABjAGwAbwB2AGUAcgAgAG0AaQB4AHQAdQByAGUAXAAiACwAIAA4AC4AMwA0ACwAIAAwAC4AOAAsACAAMAAuADAAMgA1ACwAIAAwAC4AMAAxADYALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATAB1AGMAZQByAG4AZQBcACIALAAgADgALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADEAOQAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABsAGUAZwB1AG0AZQBcACIALAAgADUALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADIAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgBlAG4AbgBpAGEAbAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAA4AC4AMwA1ACwAIAAwAC4AOAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADIALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAIgApACkAOwBcAG4AXABuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAdQByAG4AaQBuAGcAIABvAGYAIABhAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAHIAZQBzAGkAZAB1AGUAcwAgAC0AIABFAEYAcwBcACIAKQApADsAXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAdgBvAGwAdQBtAGUAIAAyADoAIABUAGEAYgBsAGUAIAA1AC4AMwAxADoAIABCAHUAcgBuAGkAbgBnACAAbwBmACAAYQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIAByAGUAcwBpAGQAdQBlAHMAIAAtACAARQBGAHMAXAAiACkAKQA7AFwAbgBcAG4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzACAAcwBwAGUAYwBpAGUAcwBcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAEUARgBnACAAKABHAGcAIABlAGwAZQBtAGUAbgB0ACAAaQBuACAAcwBwAGUAYwBpAGUAcwAvACAARwBnACAAZQBsAGUAbQBlAG4AdAAgAGkAbgAgAGYAdQBlAGwAIABiAHUAcgBuAHQAKQBcACIALAAgAFwAIgBFAGwAZQBtAGUAbgB0AGEAbAAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgACgAQwBnACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAwAC4AMAAwADMANQAsACAAXAAiADEANgAvADEAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADAALgAwADAANwA2ACwAIABcACIANAA0AC8AMgA4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4ATwB4AFwAIgAsACAAMAAuADIAMQAwADAALAAgAFwAIgA0ADYALwAxADQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAMAAuADAANwA4ADAALAAgAFwAIgAyADgALwAxADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAMAAuADAAMAA5ADEALAAgAFwAIgAxADQALwAxADIAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAARgBvAHIAIABEAGEAaQByAHkAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAyAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAxAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAxAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ATABpAHYAZQB3AGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgAgAC0AIABUAGEAYgBsAGUAIABBADUALgA1AC4AMgAuADEAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAxAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ADEALAAgADEANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFIAZQBnAGkAbwBuAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAgADEAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBDAG8AdwBzACAAMQAtADIAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBlACAAMgBcACIALAAgAFwAIgBDAG8AdwBzACAAMgAtADMAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBlACAAMwBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgAFwAdQAwADAAMwBlACAAMQBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgADEALQAyAFwAIgAsACAAXAAiAFMAdABlAGUAcgBzACAAMgAtADMAXAAiACwAIABcACIAUwB0AGUAZQByAHMAIABcAHUAMAAwADMAZQAgADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAOAAwACwAIAA0ADgAMAAsACAANwA1ACwAIAAzADAAMAAsACAANAA0ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADcANQAsACAAMwA4ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxADcAMAAsACAANQAyADAALAAgADEANgAwACwAIAAzADYAMAAsACAANAA3ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADEANgAwACwAIAA0ADIAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADIANAAwACwAIAA1ADUAMAAsACAAMgAyADAALAAgADMAOQAwACwAIAA0ADkAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMgAyADAALAAgADQANQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMgA4ADAALAAgADUANgAwACwAIAAyADYAMAAsACAANAAxADAALAAgADUAMAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAyADYAMAAsACAANAA2ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIABcACIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAA4ADAALAAgADQAOAAwACwAIAA3ADUALAAgADMAMAAwACwAIAA0ADQAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAANwA1ACwAIAAzADgAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEANwAwACwAIAA1ADIAMAAsACAAMQA2ADAALAAgADMANgAwACwAIAA0ADcAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMQA2ADAALAAgADQAMgAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMgA0ADAALAAgADUANQAwACwAIAAyADIAMAAsACAAMwA5ADAALAAgADQAOQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAyADIAMAAsACAANAA1ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAyADgAMAAsACAANQA2ADAALAAgADIANgAwACwAIAA0ADEAMAAsACAANQAwADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADIANgAwACwAIAA0ADYAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAyADUAMAAsACAAOAAwADAALAAgADIAMgAwACwAIAA0ADAAMAAsACAANQAwADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADIAMwAwACwAIAA0ADIAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAzADIAMAAsACAAOAAwADAALAAgADIAOAAwACwAIAA0ADIAMAAsACAANQAwADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADIAOQAwACwAIAA0ADIAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAA4ADAALAAgADcAMAAwACwAIAA3ADAALAAgADMAMAAwACwAIAA0ADUAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAANwA1ACwAIAA0ADAAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAxADYAMAAsACAANwAwADAALAAgADEANAAwACwAIAAzADUAMAAsACAANAA1ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADEANQAwACwAIAA0ADAAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADEAMAA1ACwAIAA3ADAAMAAsACAAOAA1ACwAIAAzADAAMAAsACAANAA5ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADkAMAAsACAANAA4ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAA0ADgAMAAsACAANwA1ADAALAAgADEANQAwACwAIAAzADUAMAAsACAANQAzADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADEANgAwACwAIAA0ADYAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADIANQAwACwAIAA3ADIANQAsACAAMgAwADAALAAgADMANgAwACwAIAA1ADAAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMgAxADUALAAgADQAOQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMgA2ADAALAAgADcAMAAwACwAIAAyADEAMAAsACAAMwA4ADAALAAgADQANgAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAyADMAMAAsACAANAA3ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBJAEMAXAAiACwAIABcACIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAyADUAMAAsACAAOAAyADAALAAgADIANAAwACwAIAA0ADEAMAAsACAANQA2ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADIANAAwACwAIAA1ADEAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADIAOAAwACwAIAA4ADUAMAAsACAAMgA2ADAALAAgADQANAAwACwAIAA1ADUAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMgA3ADAALAAgADUAMgAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQAwADAALAAgADcAMAAwACwAIAA5ADUALAAgADMAMAAwACwAIAA0ADUAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAOQA1ACwAIAA0ADEAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADEANQAwACwAIAA3ADIAMAAsACAAMQA0ADAALAAgADMAMgAwACwAIAA0ADcAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMQA0ADAALAAgADQANAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMwA0ADAALAAgADgAMAAwACwAIAAyADYAMAAsACAANAAyADAALAAgADUANQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAzADAAMAAsACAANAA4ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUwBvAHUAdABoACAAVwBlAHMAdABcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADMAOAAwACwAIAA3ADgAMAAsACAAMwAwADAALAAgADQANQAwACwAIAA1ADMAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMwA0ADAALAAgADQANwAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQAwADAALAAgADYAOAAwACwAIAA4ADAALAAgADMAMgAwACwAIAA0ADgAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMQAwADAALAAgADMANAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMQA5ADAALAAgADcAMAAwACwAIAAxADUAMAAsACAAMwAzADAALAAgADQAOQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAxADcAMAAsACAAMwA2ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFAAaQBsAGIAYQByAGEAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAA4ADAALAAgADQANQAwACwAIAA3ADAALAAgADIANgAwACwAIAAzADQAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAOAAwACwAIAAzADcAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUABpAGwAYgBhAHIAYQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEANQAwACwAIAA1ADAAMAAsACAAMQA0ADAALAAgADMAMQAwACwAIAAzADYAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMQA1ADAALAAgADQAMAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBQAGkAbABiAGEAcgBhAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMgAzADAALAAgADUANQAwACwAIAAyADIAMAAsACAAMwAzADAALAAgADMAOAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAyADMAMAAsACAANAAyADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFAAaQBsAGIAYQByAGEAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAyADUAMAAsACAANQAwADAALAAgADIANAAwACwAIAAzADQAMAAsACAAMwA2ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADIANQAwACwAIAAzADkAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAOgBcACIALAAgADIAMgAwACwAIAA1ADAAMAAsACAAMQA4ADAALAAgADMAMAAwACwAIAAzADIAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMgAxADAALAAgADMANAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBLAGkAbQBiAGUAcgBsAGUAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgA6AFwAIgAsACAAMQAxADAALAAgADUANQAwACwAIAA5ADAALAAgADIAMgAwACwAIAAzADgAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMQAwADAALAAgADMAOQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBLAGkAbQBiAGUAcgBsAGUAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgA6AFwAIgAsACAAMQA3ADAALAAgADYAMAAwACwAIAAxADQAMAAsACAAMgA3ADAALAAgADMAOQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAxADYAMAAsACAANAAzADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAEsAaQBtAGIAZQByAGwAZQB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByADoAXAAiACwAIAAyADAAMAAsACAANQA1ADAALAAgADEANQAwACwAIAAyADgAMAAsACAAMwA1ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADEAOQAwACwAIAA0ADAAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAQQBsAGkAYwBlACAAUwBwAHIAaQBuAGcAcwBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADIAMgAwACwAIAA3ADAANgAsACAAMgAwADgALAAgADMAMgAzACwAIABcACIAXAAiACwAIAA0ADEANQAsACAANAA2ADcALAAgADIAMgAzACwAIABcACIAXAAiACwAIAAzADcAMQAsACAANAA5ADMALAAgADUAOAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBBAGwAaQBjAGUAIABTAHAAcgBpAG4AZwBzAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMQAxADAALAAgADcAMAAzACwAIAAxADEAMgAsACAAMgA1ADYALAAgAFwAIgBcACIALAAgADMANgA4ACwAIAA0ADYANQAsACAAMQAwADgALAAgAFwAIgBcACIALAAgADIAOAAwACwAIAA0ADIAMQAsACAANQA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAEEAbABpAGMAZQAgAFMAcAByAGkAbgBnAHMAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAxADcAMAAsACAANwAyADEALAAgADEANgA5ACwAIAAzADAANgAsACAAXAAiAFwAIgAsACAAMwA5ADIALAAgADQANgA0ACwAIAAxADcANgAsACAAXAAiAFwAIgAsACAAMwAzADkALAAgADQANwAwACwAIAA1ADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAQQBsAGkAYwBlACAAUwBwAHIAaQBuAGcAcwBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADIAMAAwACwAIAA3ADIANwAsACAAMgAxADEALAAgADMAMwA4ACwAIABcACIAXAAiACwAIAA0ADMAMgAsACAANAA5ADIALAAgADIAMgAyACwAIABcACIAXAAiACwAIAAzADcANwAsACAANAA5ADgALAAgADUAOQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBCAGEAcgBrAGwAeQBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADIAMgAwACwAIAA2ADIAMAAsACAAMgAyADcALAAgADMAMQA5ACwAIABcACIAXAAiACwAIAAzADkAOAAsACAANAA1ADIALAAgADIAMQA2ACwAIABcACIAXAAiACwAIAAzADMANAAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAQgBhAHIAawBsAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxADEAMAAsACAANgA1ADAALAAgADEAMAA4ACwAIAAyADYAMgAsACAAXAAiAFwAIgAsACAAMwA0ADYALAAgADQAMwAwACwAIAAxADEAMQAsACAAXAAiAFwAIgAsACAAMgAzADYALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAEIAYQByAGsAbAB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQA3ADAALAAgADYANwAwACwAIAAxADcAMAAsACAAMgA2ADYALAAgAFwAIgBcACIALAAgADMANgAzACwAIAA0ADQANAAsACAAMQA2ADkALAAgAFwAIgBcACIALAAgADIAOAAyACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBCAGEAcgBrAGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADIAMAAwACwAIAA2ADYAMAAsACAAMgAyADUALAAgADMAMAA3ACwAIABcACIAXAAiACwAIAAzADkAOAAsACAANAA1ADIALAAgADIAMQA0ACwAIABcACIAXAAiACwAIAAzADIANgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMgAyADAALAAgADYAMgAwACwAIAAxADcANwAsACAAMgA2ADcALAAgAFwAIgBcACIALAAgADMANgA1ACwAIAA0ADAANgAsACAAMgAzADEALAAgAFwAIgBcACIALAAgADIANAA5ACwAIAAzADIANAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMQAxADAALAAgADYANQAwACwAIAAxADAAMgAsACAAMgAwADMALAAgAFwAIgBcACIALAAgADIAOQA5ACwAIAAzADgAMAAsACAAMQAwADIALAAgAFwAIgBcACIALAAgADIAMQA4ACwAIAAyADYAMwAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQA3ADAALAAgADYANwAwACwAIAAxADcAMwAsACAAMgA1ADAALAAgAFwAIgBcACIALAAgADMAMwA2ACwAIAA0ADEANAAsACAAMQA3ADUALAAgAFwAIgBcACIALAAgADIANAAzACwAIAAzADAANAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMgAwADAALAAgADYANgAwACwAIAAyADAAMgAsACAAMgA3ADIALAAgAFwAIgBcACIALAAgADMANgA1ACwAIAAzADkAMAAsACAAMgAwADgALAAgAFwAIgBcACIALAAgADIANgAwACwAIAAzADMANwAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBIAGkAZwBoAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMgA2ADAALAAgADcAMAA1ACwAIAAyADEANQAsACAAMwAwADIALAAgAFwAIgBcACIALAAgADQAMQA2ACwAIAA1ADEAOQAsACAAMgAzADQALAAgAFwAIgBcACIALAAgADQANQA1ACwAIAA1ADUAMQAsACAANgA2ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIASABpAGcAaABcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEANQAzACwAIAA3ADAAMwAsACAAMQAxADgALAAgADIANwA3ACwAIABcACIAXAAiACwAIAAzADkANwAsACAANAA4ADMALAAgADEAMQAxACwAIABcACIAXAAiACwAIAAzADAANAAsACAANQAyADEALAAgADUANAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAEgAaQBnAGgAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAxADYAOAAsACAANwAxADgALAAgADEAOQAxACwAIAAzADEAOQAsACAAXAAiAFwAIgAsACAANAA0ADAALAAgADUAMAA2ACwAIAAxADgAOAAsACAAXAAiAFwAIgAsACAAMwAyADYALAAgADUAMgAwACwAIAA1ADgAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBIAGkAZwBoAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMgAzADUALAAgADcAMgAyACwAIAAyADAANwAsACAAMwA1ADIALAAgAFwAIgBcACIALAAgADQANwAwACwAIAA1ADEANAAsACAAMgAwADkALAAgAFwAIgBcACIALAAgADQAMgAxACwAIAA1ADEAMgAsACAANgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATQBvAGQAZQByAGEAdABlAC8ASABpAGcAaABcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADIAMwAwACwAIAA2ADcANAAsACAAMgAxADcALAAgAFwAIgBcACIALAAgADMANAA0ACwAIAAzADUANwAsACAANAA2ADcALAAgADIANAAyACwAIABcACIAXAAiACwAIAAzADcAMAAsACAANQA1ADAALAAgADYAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEgAaQBnAGgAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxADEAMwAsACAANgA2ADkALAAgADEAMQAzACwAIABcACIAXAAiACwAIAAyADgAMwAsACAAMwA2ADEALAAgADQANwA3ACwAIAAxADIAMAAsACAAXAAiAFwAIgAsACAAMgA3ADMALAAgADUANAA1ACwAIAA1ADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBNAG8AZABlAHIAYQB0AGUALwBIAGkAZwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQA3ADIALAAgADYAOAA1ACwAIAAxADcAMgAsACAAXAAiAFwAIgAsACAAMwAwADkALAAgADMANwA2ACwAIAA0ADcAMQAsACAAMgAzADgALAAgAFwAIgBcACIALAAgADMAMgA5ACwAIAA1ADcAMwAsACAANgAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATQBvAGQAZQByAGEAdABlAC8ASABpAGcAaABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADIANAAxACwAIAA2ADkAMgAsACAAMgAwADgALAAgAFwAIgBcACIALAAgADMANAA0ACwAIAAzADYANAAsACAANAA4ADQALAAgADIANgAwACwAIABcACIAXAAiACwAIAAzADUAMAAsACAANQA2ADcALAAgADYAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEwAbwB3AFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMgAzADYALAAgADYANwA0ACwAIAAxADcAOAAsACAAXAAiAFwAIgAsACAAMwAxADAALAAgADQAMgA4ACwAIAA0ADYANgAsACAAMQA5ADMALAAgAFwAIgBcACIALAAgADMANwAwACwAIAA1ADEAOQAsACAANQA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATQBvAGQAZQByAGEAdABlAC8ATABvAHcAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxADIAMAAsACAANgA2ADkALAAgADEAMQAyACwAIABcACIAXAAiACwAIAAyADUAMAAsACAAMwA5ADAALAAgADQANAA4ACwAIAAxADEANQAsACAAXAAiAFwAIgAsACAAMgA3ADMALAAgADQAMwAzACwAIAA1ADUANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBNAG8AZABlAHIAYQB0AGUALwBMAG8AdwBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADEAMgA1ACwAIAA2ADgANQAsACAAMQA0ADAALAAgAFwAIgBcACIALAAgADIANwA3ACwAIAA0ADAANwAsACAANAA1ADUALAAgADEANAAxACwAIABcACIAXAAiACwAIAAyADkANgAsACAANAA0ADUALAAgADUAOQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEwAbwB3AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMQA4ADAALAAgADYAOQAyACwAIAAxADgAMwAsACAAXAAiAFwAIgAsACAAMwAxADYALAAgADQAMwA4ACwAIAA0ADYAOAAsACAAMQA4ADkALAAgAFwAIgBcACIALAAgADMANQA0ACwAIAA1ADAAMAAsACAANQA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATABvAHcAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAxADkAMAAsACAANgAxADcALAAgADEANwA0ACwAIABcACIAXAAiACwAIAAyADYANQAsACAAMwA3ADEALAAgADQAMQA1ACwAIAAxADcAMAAsACAAXAAiAFwAIgAsACAAMgA3ADIALAAgADMAOQAyACwAIAA1ADMAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBMAG8AdwBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEAMQA5ACwAIAA1ADkAMQAsACAAMQA0ADAALAAgAFwAIgBcACIALAAgADIAMAA1ACwAIAAzADEAMAAsACAANAAwADUALAAgADEAMwAzACwAIABcACIAXAAiACwAIAAyADEAOAAsACAAMwAxADUALAAgADQANAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAEwAbwB3AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQA3ADUALAAgADYAMQAwACwAIAAxADYAMwAsACAAXAAiAFwAIgAsACAAMgAzADIALAAgADMANQAxACwAIAA0ADIANwAsACAAMQA0ADYALAAgAFwAIgBcACIALAAgADIANAAyACwAIAAzADIAMAAsACAANAA3ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATABvAHcAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAxADkAMgAsACAANgAxADUALAAgADEANgAyACwAIABcACIAXAAiACwAIAAyADUANQAsACAAMwA2ADQALAAgADQAMgAwACwAIAAxADUANwAsACAAXAAiAFwAIgAsACAAMgA2ADEALAAgADMANAAyACwAIAA0ADgANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMgBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBcAG4AawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADIAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMgBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMgBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgAgAC0AIABUAGEAYgBsAGUAIABBADUALgA1AC4AMgAuADIAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADIAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAQwBUACAAYQBuAGQAIABOAFMAVwAgAHMAcABsAGkAdAAuACAAXAB1ADAAMAAyADcATgBPAFwAdQAwADAAMgA3ACAAcgBlAHAAbABhAGMAZQBkACAAdwBpAHQAaAAgADAALgBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMgBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ADEALAAgADEANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFIAZQBnAGkAbwBuAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAgADEAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBDAG8AdwBzACAAMQAtADIAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBlACAAMgBcACIALAAgAFwAIgBDAG8AdwBzACAAMgAtADMAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBlACAAMwBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgAFwAdQAwADAAMwBlACAAMQBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgADEALQAyAFwAIgAsACAAXAAiAFMAdABlAGUAcgBzACAAMgAtADMAXAAiACwAIABcACIAUwB0AGUAZQByAHMAIABcAHUAMAAwADMAZQAgADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAuADUALAAgADAALgAyACwAIAAwAC4ANQAsACAAMAAuADQALAAgADAALgAzACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4ANQAsACAAMAAuADQALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxACwAIAAwAC4ANAAsACAAMAAuADkALAAgADAALgA3ACwAIAAwAC4AMwAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADkALAAgADAALgA0ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAuADgALAAgADAALgAzACwAIAAwAC4ANwAsACAAMAAuADMALAAgADAALgAyACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4ANwAsACAAMAAuADMALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwAC4ANAAsACAAMAAuADEALAAgADAALgA0ACwAIAAwAC4AMgAsACAAMAAuADEALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgA0ACwAIAAwAC4AMQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADAALgA1ACwAIAAwAC4AMgAsACAAMAAuADUALAAgADAALgA0ACwAIAAwAC4AMwAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADUALAAgADAALgA0ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMQAsACAAMAAuADQALAAgADAALgA5ACwAIAAwAC4ANwAsACAAMAAuADMALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgA5ACwAIAAwAC4ANAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADAALgA4ACwAIAAwAC4AMwAsACAAMAAuADcALAAgADAALgAzACwAIAAwAC4AMgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADcALAAgADAALgAzACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADQALAAgADAALgAxACwAIAAwAC4ANAAsACAAMAAuADIALAAgADAALgAxACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4ANAAsACAAMAAuADEALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAuADkAOQAsACAAMQAuADEALAAgADAALgA4ADgALAAgADAALgA1ADUALAAgADAALgA1ADUALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgA4ADgALAAgADAALgAyADIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAuADcANwAsACAAMAAsACAAMAAuADYANgAsACAAMAAuADIAMgAsACAAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADYANgAsACAAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAwAC4AOQAsACAALQAxAC4AMQAsACAAMAAuADcALAAgADAALgAyADIALAAgAC0AMAAuADUANQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADgALAAgAC0AMAAuADIAMgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwAC4AOAA4ACwAIAAwACwAIAAwAC4ANwA3ACwAIAAwAC4ANQA1ACwAIAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4AOAAyACwAIAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMQAsACAAMAAuADUALAAgADEALAAgADEALAAgAC0AMAAuADQANAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMQAsACAAMAAuADUALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAwAC4AOAAyACwAIAAwAC4ANQA1ACwAIAAwAC4ANwAxACwAIAAwAC4ANQA1ACwAIAAwAC4AOQA5ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4ANwA3ACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADAALgA3ADcALAAgADAALgA1ACwAIAAwAC4ANQA1ACwAIAAwAC4AMQAxACwAIAAtADAALgAzADMALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgA2ACwAIAAwAC4AMwAzACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADEAMQAsACAALQAwAC4AMgA3ACwAIAAwAC4AMQAxACwAIAAwAC4AMgAyACwAIAAtADAALgA0ADQALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgAxADYALAAgAC0AMAAuADIAMgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADEALgAxACwAIAAxAC4AMQAsACAAMQAuADEALAAgADAALgA5ADkALAAgADAALgA5ADkALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADEALgAxACwAIAAwAC4ANwA3ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAuADMAMwAsACAAMAAuADMAMwAsACAAMAAuADIAMgAsACAAMAAuADMAMwAsACAALQAwAC4AMQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADMAMwAsACAAMAAuADEAMQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADAALgA1ACwAIAAwAC4AMgAsACAAMAAuADUANQAsACAAMAAuADQANAAsACAAMAAuADIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgA1ADUALAAgADAALgAyACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADUANQAsACAAMAAuADIAMgAsACAAMAAuADQAOQAsACAAMAAuADIAMgAsACAAMAAuADIAMgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADQAOQAsACAAMAAuADMAMwAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUwBvAHUAdABoACAAVwBlAHMAdABcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADEALgA2ADQALAAgADEALgAxACwAIAAxAC4AMgAxACwAIAAwAC4AOQA5ACwAIAAwAC4ANgA2ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAxAC4ANAAyACwAIAAxAC4AMQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUwBvAHUAdABoACAAVwBlAHMAdABcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADAALgA0ADQALAAgAC0AMAAuADIAMgAsACAAMAAuADQANAAsACAAMAAuADMAMwAsACAALQAwAC4AMgAyACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4ANAA0ACwAIAAtADAALgAxADEALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAwAC4ANgAsACAAMAAsACAAMAAuADYALAAgADAALgAyADIALAAgAC0AMAAuADUANQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADYALAAgADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwAC4AOQA5ACwAIAAwAC4AMgAyACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAxACwAIAAwAC4AMQAxACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4ANwA3ACwAIAAwAC4ANAA0ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBQAGkAbABiAGEAcgBhAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAuADcALAAgAC0AMAAuADUANQAsACAAMAAuADcALAAgADAALgAyADIALAAgAC0AMAAuADIAMgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADcALAAgAC0AMAAuADIAMgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUABpAGwAYgBhAHIAYQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADAALgA3ADcALAAgADAALgA1ADUALAAgADAALgA3ADcALAAgADAALgA2ADYALAAgADAALgA1ADUALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgA3ADcALAAgADAALgAzADMALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFAAaQBsAGIAYQByAGEAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAwAC4AOAA4ACwAIAAwAC4ANQA1ACwAIAAwAC4AOAA4ACwAIAAwAC4AMgAyACwAIAAwAC4AMgAyACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4AOAA4ACwAIAAwAC4AMgAyACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBQAGkAbABiAGEAcgBhAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADIAMgAsACAALQAwAC4ANQA1ACwAIAAwAC4AMgAyACwAIAAwAC4AMQAxACwAIAAtADAALgAyADIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgAyADIALAAgAC0AMAAuADMAMwAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAwAC4AMgAyACwAIAAtADAALgA1ADUALAAgADAALgAzADMALAAgADAALgAyADIALAAgAC0AMAAuADMAMwAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADIAMgAsACAALQAwAC4ANQA1ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBLAGkAbQBiAGUAcgBsAGUAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADAALgA4ACwAIAAwAC4ANQA1ACwAIAAwAC4ANwAsACAAMAAuADQANAAsACAAMAAuADYANgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADgALAAgADAALgA1ADUALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAEsAaQBtAGIAZQByAGwAZQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAuADYANgAsACAAMAAuADUANQAsACAAMAAuADUANQAsACAAMAAuADUANQAsACAAMAAuADEAMQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADYANgAsACAAMAAuADUANQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwAC4AMwAzACwAIAAtADAALgA1ADUALAAgADAALgAxADEALAAgADAALgAxADEALAAgAC0AMAAuADQANAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADMAMwAsACAALQAwAC4ANQA1ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBBAGwAaQBjAGUAIABTAHAAcgBpAG4AZwBzAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAuADIAMgAsACAALQAwAC4AMgAzACwAIAAwAC4AMgA1ACwAIAAwAC4AMQA3ACwAIABcACIAXAAiACwAIAAwAC4AMQA4ACwAIAAtADAALgAyADgALAAgADAALgAzADIALAAgAFwAIgBcACIALAAgADAALgAyADQALAAgADAALgAyADUALAAgAC0AMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAQQBsAGkAYwBlACAAUwBwAHIAaQBuAGcAcwBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADAALgA2ADYALAAgADAALgAyACwAIAAwAC4ANgAyACwAIAAwAC4ANQA0ACwAIABcACIAXAAiACwAIAAwAC4AMwA4ACwAIAAwAC4AMgA3ACwAIAAwAC4ANwA1ACwAIABcACIAXAAiACwAIAAwAC4ANgA0ACwAIAAwAC4ANQA1ACwAIAAwAC4ANAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBBAGwAaQBjAGUAIABTAHAAcgBpAG4AZwBzAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAuADQAOQAsACAAMAAuADEAMwAsACAAMAAuADUANAAsACAAMAAuADQANQAsACAAXAAiAFwAIgAsACAAMAAuADMANQAsACAAMAAuADEANQAsACAAMAAuADYAMwAsACAAXAAiAFwAIgAsACAAMAAuADUANAAsACAAMAAuADQAMgAsACAAMAAuADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAQQBsAGkAYwBlACAAUwBwAHIAaQBuAGcAcwBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADAALgAyADcALAAgAC0AMAAuADgALAAgADAALgAyADIALAAgADAALgAwADkALAAgAFwAIgBcACIALAAgADAALgAxADIALAAgADAALgAwADIALAAgADAALgAyADUALAAgAFwAIgBcACIALAAgADAALgAxADgALAAgADAALgAxADIALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAEIAYQByAGsAbAB5AFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAuADIAMgAsACAALQAwAC4ANAA0ACwAIAAwAC4AMgAsACAAMAAuADIAMQAsACAAXAAiAFwAIgAsACAAMAAuADEAOAAsACAAMAAuADAAMQAsACAAMAAuADEAMgAsACAAXAAiAFwAIgAsACAAMAAuADAAOQAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAQgBhAHIAawBsAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMgAyACwAIAAwAC4ANgA4ACwAIAAwAC4AMgAyACwAIABcACIAXAAiACwAIAAwAC4AMgA0ACwAIAAwAC4AMgA1ACwAIAAwAC4ANgA0ACwAIABcACIAXAAiACwAIAAwAC4AMwA3ACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBCAGEAcgBrAGwAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADAALgA0ADkALAAgADAALgAwADUALAAgADAALgA2ADQALAAgADAALgAyADUALAAgAFwAIgBcACIALAAgADAALgAyADkALAAgADAALgAxADIALAAgADAALgA1ADcALAAgAFwAIgBcACIALAAgADAALgA0ADkALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAEIAYQByAGsAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADIANwAsACAALQAwAC4AMgA3ACwAIAAwAC4AMwAxACwAIAAwAC4AMgA5ACwAIABcACIAXAAiACwAIAAwAC4AMQA5ACwAIAAwAC4AMAA0ACwAIAAwAC4AMgA2ACwAIABcACIAXAAiACwAIAAwAC4AMgA4ACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAwAC4AMgAyACwAIAAtADAALgA0ADQALAAgADAALAAgADAALgAxADUALAAgAFwAIgBcACIALAAgADAALgAwADgALAAgADAALgAxADcALAAgADAALgAwADYALAAgAFwAIgBcACIALAAgADAALgAwADIALAAgAC0AMAAuADEANAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAuADYANgAsACAAMAAuADIAMgAsACAAMAAuADcAOQAsACAAMAAuADQALAAgAFwAIgBcACIALAAgADAALgAzADgALAAgADAALgAyADcALAAgADAALgA4ACwAIABcACIAXAAiACwAIAAwAC4AMQA2ACwAIAAwAC4AMwAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAuADQAOQAsACAAMAAuADAANQAsACAAMAAuADUANQAsACAAMAAuADMAOAAsACAAXAAiAFwAIgAsACAAMAAuADMANgAsACAAMAAuADAANgAsACAAMAAuADUAOAAsACAAXAAiAFwAIgAsACAAMAAuADIAMwAsACAAMAAuADQALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADAALgAyADcALAAgAC0AMAAuADIANwAsACAAMAAuADAAMgAsACAAMAAuADAAOQAsACAAXAAiAFwAIgAsACAAMAAuADEANgAsACAALQAwAC4AMAA0ACwAIAAwAC4AMgAxACwAIABcACIAXAAiACwAIAAwAC4AMAAzACwAIAAwAC4AMQAxACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAEgAaQBnAGgAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAwAC4AMgA3ACwAIAAtADAALgAxADkALAAgADAALgAzADgALAAgADAALgAyADUALAAgAFwAIgBcACIALAAgADAALgAwADcALAAgADAALgAwADUALAAgADAALgA1ADIALAAgAFwAIgBcACIALAAgADAALgA1ADUALAAgADAALgAxADkALAAgADAALgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAEgAaQBnAGgAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAwAC4AMQA2ACwAIAAwAC4AMQA2ACwAIAAwAC4AOAAsACAAMAAuADUANwAsACAAXAAiAFwAIgAsACAAMAAuADcANgAsACAAMAAuADQAOQAsACAAMAAuADgANAAsACAAXAAiAFwAIgAsACAAMAAuADUAMQAsACAAMAAuADMANgAsACAAMAAuADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBIAGkAZwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAuADQANQAsACAAMAAuADEALAAgADAALgA0ADkALAAgADAALgA0ADEALAAgAFwAIgBcACIALAAgADAALgA0ACwAIAAwAC4AMQA3ACwAIAAwAC4ANQA0ACwAIABcACIAXAAiACwAIAAwAC4ANgA0ACwAIAAtADAALgAwADUALAAgADAALgAzADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIASABpAGcAaABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADAALgA1ADEALAAgAC0AMAAuADAANwAsACAAMAAuADEAMwAsACAALQAwAC4AMAA5ACwAIABcACIAXAAiACwAIAAtADAALgAxADMALAAgADAALgAwADcALAAgADAALgAyADUALAAgAFwAIgBcACIALAAgADAALgA3ADEALAAgADAALgAxADcALAAgADAALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATQBvAGQAZQByAGEAdABlAC8ASABpAGcAaABcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgAC0AMAAuADEAMgAsACAALQAwAC4AMQA5ACwAIAAwAC4ANAAxACwAIAAwAC4AMAA5ACwAIABcACIAXAAiACwAIAAwAC4ANAAxACwAIAAtADAALgAxADkALAAgADAALgAwADcALAAgAFwAIgBcACIALAAgADEALgAwADcALAAgAC0AMAAuADAAOAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBNAG8AZABlAHIAYQB0AGUALwBIAGkAZwBoAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAuADYANQAsACAAMAAuADEAOQAsACAAMAAuADYANQAsACAAMAAuADUAMQAsACAAXAAiAFwAIgAsACAAMAAuADEAOAAsACAAMAAuADYAMwAsACAAMQAuADMALAAgAFwAIgBcACIALAAgADAALgA0ADgALAAgADEALgAxADIALAAgADAALgAzADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATQBvAGQAZQByAGEAdABlAC8ASABpAGcAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADAALgA3ACwAIAAwAC4AMQAzACwAIAAwAC4ANQAyACwAIAAwAC4AMwA0ACwAIABcACIAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAA0ACwAIAAwAC4ANwA3ACwAIABcACIAXAAiACwAIAAwAC4ANAAyACwAIAAwAC4AMQAyACwAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEgAaQBnAGgAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwAC4AMwAyACwAIAAtADAALgAwADYALAAgADAALgAyADUALAAgADAALgAxADkALAAgAFwAIgBcACIALAAgAC0AMAAuADEALAAgAC0AMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAFwAIgAsACAAMAAuADIAMwAsACAALQAwAC4AMQAzACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEwAbwB3AFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAuADYAMgAsACAALQAwAC4AMQA5ACwAIAAwAC4AMwA3ACwAIAAwAC4ANAAxACwAIABcACIAXAAiACwAIAAwAC4AMAA2ACwAIAAtADAALgAwADIALAAgADAALgA0ADcALAAgAFwAIgBcACIALAAgADAALgA0ADQALAAgADAALgAzACwAIAAwAC4AMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEwAbwB3AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAuADAANQAsACAAMAAuADEAOQAsACAAMAAuADMAMQAsACAAMAAuADUANAAsACAAXAAiAFwAIgAsACAAMAAuADUAMwAsACAAMAAuADEANQAsACAAMAAuADIAOAAsACAAXAAiAFwAIgAsACAAMAAuADUANwAsACAAMAAuADQAMgAsACAAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATQBvAGQAZQByAGEAdABlAC8ATABvAHcAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAwAC4AMwAzACwAIAAwAC4AMQAzACwAIAAwAC4AMwA5ACwAIAAwAC4AMwA2ACwAIABcACIAXAAiACwAIAAwAC4AMgA2ACwAIAAwAC4AMQAxACwAIAAwAC4ANAAsACAAXAAiAFwAIgAsACAAMAAuADQANAAsACAAMAAuADMANwAsACAALQAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEwAbwB3AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADYAMQAsACAALQAwAC4AMAA2ACwAIAAwAC4AMgAxACwAIAAwAC4AMQA4ACwAIABcACIAXAAiACwAIAAwAC4AMQAyACwAIAAwAC4AMAA2ACwAIAAwAC4AMgA5ACwAIABcACIAXAAiACwAIAAwAC4ANAAxACwAIAAwAC4ANAAxACwAIAAtADAALgAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATABvAHcAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAtADAALgAyADAALAAgADAALgAwADIALAAgADAALgAyADQALAAgADAALgAzADAALAAgAFwAIgBcACIALAAgADAALgAyADMALAAgAC0AMAAuADAANQAsACAAMAAuADMANAAsACAAXAAiAFwAIgAsACAAMAAuADMAMAAsACAAMAAuADUANwAsACAAMAAuADUAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBMAG8AdwBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADAALgA2ADIALAAgADAALgAyADEALAAgADAALgAyADUALAAgADAALgAzADIALAAgAFwAIgBcACIALAAgADAALgA0ADcALAAgADAALgAzADEALAAgADAALgAxADQALAAgAFwAIgBcACIALAAgADAALgA0ADAALAAgADAALgAyADYALAAgADAALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATABvAHcAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAwAC4ANAAwACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyACwAIAAwAC4AMgA3ACwAIABcACIAXAAiACwAIAAwAC4AMwAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMQAzACwAIABcACIAXAAiACwAIAAwAC4AMgA0ACwAIAAwAC4AMQA1ACwAIAAwAC4AMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAEwAbwB3AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADAAOAAsACAAMAAuADAANAAsACAAMAAuADAANgAsACAAMAAuADEAOAAsACAAXAAiAFwAIgAsACAAMAAuADEAMQAsACAALQAwAC4AMAA3ACwAIAAwAC4AMQAzACwAIABcACIAXAAiACwAIAAwAC4AMQA2ACwAIAAwAC4ANAAwACwAIAAwAC4AMwAzAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMwBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXABuAHAAZQByACAAYwBlAG4AdABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAzAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAALQAgAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAbwBmACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMwBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADMAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAyACAALQAgAFQAYQBiAGwAZQAgAEEANQAuADUALgAyAC4AMwBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMwBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAQwBUACAAYQBuAGQAIABOAFMAVwAgAHMAcABsAGkAdAAuAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAzAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBSAGUAZwBpAG8AbgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIABcACIAXAAiACwAIAA1ADUALAAgADYANQAsACAANgAwACwAIAA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIABcACIAXAAiACwAIAA1ADUALAAgADYANQAsACAANgAwACwAIAA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAFwAIgAsACAANQA1ACwAIAA2ADEALAAgADUANwAsACAANQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAFwAIgAsACAANQAzACwAIAA1ADcALAAgADUANQAsACAANQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQBcACIALAAgAFwAIgBcACIALAAgADcAMAAsACAANQA1ACwAIAA1ADUALAAgADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBcACIALAAgADcANQAsACAANgAwACwAIAA3ADAALAAgADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBcACIALAAgADgAMAAsACAANQA1ACwAIAA2ADAALAAgADcANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUwBvAHUAdABoACAAVwBlAHMAdABcACIALAAgADgAMAAsACAANQA4ACwAIAA1ADAALAAgADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUABpAGwAYgBhAHIAYQBcACIALAAgADQAMAAsACAANgA1ACwAIAA1ADUALAAgADQANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIAA0ADAALAAgADYANQAsACAANQA1ACwAIAA0ADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANABfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAC0AIABDAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQAgACgAZgByAGEAYwB0AGkAbwBuACkAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA0AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgAgAC0AIABUAGEAYgBsAGUAIABBADUALgA1AC4AMgAuADQAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAEMAVAAgAGEAbgBkACAATgBTAFcAIABzAHAAbABpAHQALgBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANABfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAIABcACIAUgBlAGcAaQBvAG4AXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADAANwAsACAAMAAuADEAMwAsACAAMAAuADEALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIABcACIAXAAiACwAIAAwAC4AMAA3ACwAIAAwAC4AMQAzACwAIAAwAC4AMQAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAXAAiACwAIAAwAC4AMAA1ADgALAAgADAALgAwADkAMgAsACAAMAAuADAANwA1ACwAIAAwAC4AMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIAXAAiACwAIAAwAC4AMAA3ADIALAAgADAALgAwADkAOQAsACAAMAAuADAANwA4ACwAIAAwAC4AMAA1ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADEANgAsACAAMAAuADAANwAsACAAMAAuADAAOQAsACAAMAAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIABcACIAXAAiACwAIAAwAC4AMgAsACAAMAAuADEALAAgADAALgAxADYALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADIANQAsACAAMAAuADAANwAsACAAMAAuADEALAAgADAALgAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiACwAIAAwAC4AMgAsACAAMAAuADAAOQAsACAAMAAuADAANgAsACAAMAAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFAAaQBsAGIAYQByAGEAXAAiACwAIAAwAC4AMAA0ACwAIAAwAC4AMQAyACwAIAAwAC4AMAA5ACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBLAGkAbQBiAGUAcgBsAGUAeQBcACIALAAgADAALgAwADQALAAgADAALgAxADIALAAgADAALgAwADkALAAgADAALgAwADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA1AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA1AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAEMAYQB0AHQAbABlACAALQAgAEYAZQBlAGQAIABpAG4AdABhAGsAZQAgAGEAZABqAHUAcwB0AG0AZQBuAHQAIABhAG4AZAAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAYQBuAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA1AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA1AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgAgAC0AIABUAGEAYgBsAGUAIABBADUALgA1AC4AMgAuADUAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADUAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAEMAVAAgAGEAbgBkACAATgBTAFcAIABzAHAAbABpAHQALgAgAFMAdABhAHQAZQAgAG4AYQBtAGUAcwAgAHIAZQBwAGwAYQBjAGUAZAAgAGIAeQAgAGEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGQAYQB0AGEAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA1AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ADEALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBSAGUAZwBpAG8AbgBcACIALAAgAFwAIgBTAGUAYQBzAG8AbgBcACIALAAgAFwAIgBGAGUAZQBkACAAYQBkAGoAdQBzAHQAbQBlAG4AdABcACIALAAgAFwAIgBNAGkAbABrACAAaQBuAHQAYQBrAGUAIAAvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAawBnAC8AZABhAHkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAxAC4AMwAsACAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEALgAxACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIABcACIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAxAC4AMwAsACAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEALgAxACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxAC4AMwAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAxAC4AMQAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEALgAzACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQAuADEALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAxAC4AMwAsACAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAxAC4AMQAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADEALgAzACwAIAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMQAuADEALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIABcACIAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALABcACIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsAFwAIgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBJAEMAXAAiACwAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQAuADMALAAgADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBJAEMAXAAiACwAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMQAuADEALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUwBvAHUAdABoACAAVwBlAHMAdABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADEALgAzACwAIAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMQAuADEALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFAAaQBsAGIAYQByAGEAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAxAC4AMwAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUABpAGwAYgBhAHIAYQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEALgAxACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBQAGkAbABiAGEAcgBhAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUABpAGwAYgBhAHIAYQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAEsAaQBtAGIAZQByAGwAZQB5AFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxAC4AMwAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAxAC4AMQAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA2AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXABuAGsAZwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA2AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAC0AIABTAHQAYQBuAGQAYQByAGQAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA2AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADYAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgAgAC0AIABUAGEAYgBsAGUAIABBADUALgA1AC4AMgAuADYAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADYAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAIABhAG4AZAAgAE4AUwBXACAAcwBwAGwAaQB0AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG4AYQBtAGUAcwAgAHIAZQBwAGwAYQBjAGUAZAAgAGIAeQAgAGEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGQAYQB0AGEAIABsAG8AbwBrAHUAcAAuAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAbAB1AHIAYQBsAGkAcwBlAGQAIABcAHUAMAAwADIANwBTAHQAZQBlAHIAXAB1ADAAMAAyADcAIAB0AG8AIABcAHUAMAAwADIANwBTAHQAZQBlAHIAcwBcAHUAMAAwADIANwAgAGYAbwByACAAYwBvAG4AcwBpAHMAdABlAG4AYwB5AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA2AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAOAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAgADEAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBDAG8AdwBzACAAMQAtADIAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBlACAAMgBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgAFwAdQAwADAAMwBlACAAMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIAA3ADAAMAAsACAANwAwADAALAAgADYAMAAwACwAIAA1ADAAMAAsACAANQAwADAALAAgADUAMAAwACwAIAA2ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgADcAMAAwACwAIAA3ADAAMAAsACAANgAwADAALAAgADUAMAAwACwAIAA1ADAAMAAsACAANQAwADAALAAgADYAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAANwA3ADAALAAgADcANwAwACwAIAA2ADYAMAAsACAANQA1ADAALAAgADUANQAwACwAIAA1ADUAMAAsACAANgA2ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgADcANwAwACwAIAA3ADcAMAAsACAANgA2ADAALAAgADUANQAwACwAIAA1ADUAMAAsACAANQA1ADAALAAgADYANgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAANwA3ADAALAAgADcANwAwACwAIAA2ADYAMAAsACAANQA1ADAALAAgADUANQAwACwAIAA1ADUAMAAsACAANgA2ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAANwA3ADAALAAgADcANwAwACwAIAA2ADYAMAAsACAANQA1ADAALAAgADUANQAwACwAIAA1ADUAMAAsACAANgA2ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAANwA3ADAALAAgADcANwAwACwAIAA2ADYAMAAsACAANQA1ADAALAAgADUANQAwACwAIAA1ADUAMAAsACAANgA2ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAANwA3ADAALAAgADcANwAwACwAIAA2ADYAMAAsACAANQA1ADAALAAgADUANQAwACwAIAA1ADUAMAAsACAANgA2ADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAZQB0AHUAcgBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGYAcgBvAG0AIABhAGwAbAAgAHAAYQBzAHQAdQByAGUAIAB0AHkAcABlAHMAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXABuAEUATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAcAB9AFwAXABsAGUAZgB0ACgATQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgBpAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwB7ADEAMAB9AF4AewAtADMAfQBcAFwAcgBpAGcAaAB0ACkAXABuAE0AcAAgAD0AIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcABhAHMAdAB1AHIAZQAgAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAE4AaQAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbAAgAGkAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlACAAaQAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAbgBDAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AcAAgAD0AIABQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcAG4AaQAgAD0AIABDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AcAAsACAARQBGAE4AaQAsACAAQwBOADIATwAsAFwAbgAgACAAIAAgAE0AcAAgACoAIABFAEYATgBpACAAKgAgAEMATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAZQB0AHUAcgBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGYAcgBvAG0AIABhAGwAbAAgAHAAYQBzAHQAdQByAGUAIAB0AHkAcABlAHMAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAF8AewBwAH0AXABcAGwAZQBmAHQAKABNAF8AcABcAFwAdABpAG0AZQBzACAARQBGAF8AewBOAGkAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzAHsAMQAwAH0AXgB7AC0AMwB9AFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBwAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcABhAHMAdAB1AHIAZQAgAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIAAoAGsAZwAgAE4AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAE4AaQBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIABpAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBnAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAbgBNAHAAXABuAGsAZwAgAE4AXABuAE0AXwBwACAAPQAgACgAQQBfAHAAIADXACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACAARgBGAE8ARABfAHAAKQAgAFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBwAH0AKQAgACsAIAAoAEEAXwBwACAAXABcAHQAaQBtAGUAcwAgACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAcAB9ACAAXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQgBHAHAAfQApAFwAbgBBAHAAIAA9ACAAYQByAGUAYQAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAByAGUAbgBlAHcAZQBkACAAbwByACAAcgBlAG0AbwB2AGUAZAAgACgAaABhACkAXABuAFkAcAAgAD0AIABhAHYAZQByAGEAZwBlACAAeQBpAGUAbABkACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAIAAoAHQAIABEAE0ALwBoAGEAKQBcAG4ATgBDAEEARwBwACAAPQAgAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAbgBSAEIARwBwACAAPQAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ATgBDAEIARwBwACAAPQAgAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4ARgBGAE8ARABwACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBwACAAPQAgAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBwACwAIABZAHAALAAgAEYARgBPAEQAcAAsACAATgBDAEEARwBwACwAIABSAEIARwBwACwAIABOAEMAQgBHAHAALABcAG4AIAAgACAAIAAoAEEAcAAgACoAIAAoAFkAcAAgACoAIAAxADAAXgAoAC0AMwApACkAIAAqACAAKAAxACAALQAgAEYARgBPAEQAcAApACAAKgAgAE4AQwBBAEcAcAApACAAKwAgACgAQQBwACAAKgAgACgAWQBwACAAKgAgADEAMABeACgALQAzACkAKQAgACoAIABSAEIARwBwACAAKgAgAE4AQwBCAEcAcAApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AcABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AcAAgAD0AIAAoAEEAXwBwACAAXABcAHQAaQBtAGUAcwAgACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACAARgBGAE8ARABfAHAAKQAgAFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBwAH0AKQAgACsAIAAoAEEAXwBwACAAXABcAHQAaQBtAGUAcwAgACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAcAB9ACAAXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQgBHAHAAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAXAAiACwAXAAiAGEAcgBlAGEAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAcgBlAG4AZQB3AGUAZAAgAG8AcgAgAHIAZQBtAG8AdgBlAGQAIAAoAGgAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAHAAXAAiACwAXAAiAGEAdgBlAHIAYQBnAGUAIAB5AGkAZQBsAGQAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcAAgACgAdAAgAEQATQAvAGgAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAQQBHAHAAXAAiACwAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAEIARwBwAFwAIgAsAFwAIgBiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAByAGEAdABpAG8AIABmAG8AcgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBCAEcAcABcACIALABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAHAAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIAAgAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuACAAIAAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAGsAZwAgAE4AMgBPAC0ATgAgAC8AIABrAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALAAwAC4AMAAxADEAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAFQAYQBiAGwAZQAgADUALgAyADEAIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAHMASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBOADIATwBFAEYAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBnACAATgAyAE8ALQBOAC8AIABHAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAHMASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADIAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA1ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAIAAwAC4AMAAwADQAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAYwBhAG4AZQBcACIALAAgADAALgAwADEAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgADAALgAwADAANQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAZQBcACIALAAgADAALgAwADAANgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVQByAGUAYQBDAE8AMgBFAEYAXABuAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ASABfADEAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFUAcgBlAGEAQwBPADIARQBGAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBhAHIAYgBvAG4AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHIAZQBhACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVQByAGUAYQBDAE8AMgBFAEYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0AG8AbgBuAGUAIABDAC8AdABvAG4AbgBlACAAdQByAGUAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFUAcgBlAGEAQwBPADIARQBGAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ASABfADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBVAHIAZQBhAEMATwAyAEUARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADQAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADQAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAAgAFQAYQBiAGwAZQAgADEAMQAuADEAIABbADEALAAgAHAALgAgADEAMQBdAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAXAAiACwAIABcACIARQBGACAAaQAgAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMARwBBAFMARgBmAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAFYARQBFAFIARwAgADIAMAAyADYAOgBUAGEAYgBsAGUAIAAxADIALgAyAC4AMgAuADkAXABuAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAAgAFQAYQBiAGwAZQAgADEAMQAuADMAIABbADEALAAgAHAALgAgADEAMQBdAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABmACAAdABoAGEAdAAgAHYAbwBsAGEAdABpAGwAaQBzAGUAcwAgAGEAcwAgAE4ASAAzACAAYQBuAGQAIABOAE8AeABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBHAEEAUwBGAGYASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABoAGUAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAIABmAHIAbwBtACAAdABoAGUAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHcAaABlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBHAEEAUwBGAGYASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMARwBBAFMARgBmAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6AFQAYQBiAGwAZQAgADEAMgAuADIALgAyAC4AOQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMARwBBAFMARgBmAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBQAEMAQwAgADIAMAAxADkAIABSAGUAZgBpAG4AZQBtAGUAbgB0ACAAVgBvAGwAdQBtAGUAIAA0ACAAVABhAGIAbABlACAAMQAxAC4AMwAgAFsAMQAsACAAcAAuACAAMQAxAF0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEcAQQBTAEYAZgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgBcACIALABcACIARgByAGEAYwBHAEEAUwBGAGYAXAAiACwAIABcACIAQgBhAHMAaQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBVAHIAZQBhAC0AYgBhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAMAAuADEANQAsACAAXAAiAFUAcgBlAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbQBtAG8AbgBpAHUAbQAtAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgADAALgAwADgALAAgAFwAIgBBAG0AbQBvAG4AaQB1AG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AaQB0AHIAYQB0AGUALQBiAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIAAwAC4AMAAxACwAIABcACIATgBpAHQAcgBhAHQAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBtAG0AbwBuAGkAdQBtAC0AbgBpAHQAcgBhAHQAZQAgAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgADAALgAwADUALAAgAFwAIgBBAG0AbQBvAG4AaQB1AG0ALQBuAGkAdAByAGEAdABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIAAwAC4AMQAxACwAIABcACIATwB0AGgAZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEcAQQBTAEYAZgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABcAHUAMAAwADIANwBCAGEAcwBpAHMAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGkAbQBwAGwAaQBmAGkAZQBkACAAbgBhAG0AaQBuAGcAIAB0AG8AIABhAHMAcwBpAHMAIAB3AGkAdABoACAAbABvAG8AawB1AHAAcwAgAGkAbgAgAGUAcQB1AGEAdABpAG8AbgBzAFwAIgApACkAOwBcAG4AXABuAFwAbgAgACAALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBcAG4AVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcAG4ASQBQAEMAQwA6ACAATgAyAE8AIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABNAEEATgBBAEcARQBEACAAUwBPAEkATABTACwAIABBAE4ARAAgAEMATwAyACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATABJAE0ARQAgAEEATgBEACAAVQBSAEUAQQAgAEEAUABQAEwASQBDAEEAVABJAE8ATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFQAYQBiAGwAZQAgAGMAcgBlAGEAdABlAGQAIABiAGEAcwBlAGQAIABvAG4AIABWAEUARQBSAEcAIAB0AGUAeAB0ACAAXAB1ADAAMAAyADcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AXAB1ADAAMAAyADcAXAAiACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAEYAdQBlAGwAXwBHAGUAdABUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAFMAdAByAGkAbgBnAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsAFwAbgAgACAAIAAgAEwARQBGAFQAKABDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAIABcACIALABDAGUAbABsACkAIAAtADEAKQBcAG4AKQA7AFwAbgBcAG4ARgB1AGUAbABfAEcAZQB0AFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABTAHQAcgBpAG4AZwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALABcAG4AIAAgACAAIABSAEkARwBIAFQAKABDAGUAbABsACwATABFAE4AKABDAGUAbABsACkALQBGAEkATgBEACgAXAAiACwAIABcACIALABDAGUAbABsACkAKQBcAG4AKQA7AFwAbgBcAG4ARgB1AGUAbABfAFQAbwB0AGEAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AXABuAD0AIABMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEYAdQBlAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAEEAcgByAGEAeQAsACAARgB1AGUAbABVAHMAZQBBAHIAcgBhAHkALAAgAEYAdQBlAGwAVQBzAGUALAAgAEYAdQBlAGwAVAB5AHAAZQBBAHIAcgBhAHkALAAgAEYAdQBlAGwAVAB5AHAAZQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIABTAFUATQAoAFwAbgAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAARgB1AGUAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIAAoAEYAdQBlAGwAVAB5AHAAZQBBAHIAcgBhAHkAIAA9ACAARgB1AGUAbABUAHkAcABlACkAIAAqACAAXABuACAAIAAgACAAIAAgACAAIAAoAEYAdQBlAGwAVQBzAGUAQQByAHIAYQB5ACAAPQAgAEYAdQBlAGwAVQBzAGUAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAMABcAG4AIAAgACkAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAvACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ASABlAGEAZABMAG8AcwB0AEQAdQByAGkAbgBnAE0AbwBuAHQAaABcAG4ALwAvACAAPQAgAEwAQQBNAEIARABBACgATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALABcAG4ALwAvACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuAC8ALwAgACAAIAAgACAAUwBVAE0AKABcAG4ALwAvACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsASABlAGEAZABdACwAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARABhAHQAZQBdACAAXAB1ADAAMAAzAGUAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAtADEAKQArADEAKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARABhAHQAZQBdACAAXAB1ADAAMAAzAGMAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAwACkAKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARgByAG8AbQBdACAAPQAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApAFwAbgAvAC8AIAAgACAAIAAgACAAIAApAFwAbgAvAC8AIAAgACAAIAAgACkALABcAG4ALwAvACAAIAAgACAAIAAwAFwAbgAvAC8AIAAgACAAKQBcAG4ALwAvACAAKQA7AFwAbgBcAG4ALwAvACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ASABlAGEAZABBAGQAZABlAGQARAB1AHIAaQBuAGcATQBvAG4AdABoAFwAbgAvAC8AIAA9ACAATABBAE0AQgBEAEEAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsAFwAbgAvAC8AIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4ALwAvACAAIAAgACAAIABTAFUATQAoAFwAbgAvAC8AIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAASQBuAHAAdQB0AF8ASABlAHIAZABNAG8AdgBlAG0AZQBuAHQAWwBIAGUAYQBkAF0ALABcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACgASQBuAHAAdQB0AF8ASABlAHIAZABNAG8AdgBlAG0AZQBuAHQAWwBEAGEAdABlAF0AIABcAHUAMAAwADMAZQA9ACAARQBPAE0ATwBOAFQASAAoAE0AbwBuAHQAaAAsAC0AMQApACsAMQApACAAKgBcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACgASQBuAHAAdQB0AF8ASABlAHIAZABNAG8AdgBlAG0AZQBuAHQAWwBEAGEAdABlAF0AIABcAHUAMAAwADMAYwA9ACAARQBPAE0ATwBOAFQASAAoAE0AbwBuAHQAaAAsADAAKQApACAAKgBcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACgASQBuAHAAdQB0AF8ASABlAHIAZABNAG8AdgBlAG0AZQBuAHQAWwBUAG8AXQAgAD0AIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAKQBcAG4ALwAvACAAIAAgACAAIAAgACAAKQBcAG4ALwAvACAAIAAgACAAIAApACwAXABuAC8ALwAgACAAIAAgACAAMABcAG4ALwAvACAAIAAgACkAXABuAC8ALwAgACkAOwBcAG4AXABuAC8ALwAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEgAZQBhAGQAUgBlAG0AYQBpAG4AaQBuAGcAQQB0AE0AbwBuAHQAaABFAG4AZABcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAFwAbgAvAC8AIAAgACAAIAAgAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwASABlAGEAZABBAHQAUwB0AGEAcgB0AE8AZgBNAG8AbgB0AGgALABcAG4ALwAvACAAIAAgACAAIABNAEEAWAAoAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAASABlAGEAZABBAHQAUwB0AGEAcgB0AE8AZgBNAG8AbgB0AGgALQBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBIAGUAYQBkAEwAbwBzAHQARAB1AHIAaQBuAGcATQBvAG4AdABoACgATQBvAG4AdABoACwATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkALAAgAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAMABcAG4ALwAvACAAIAAgACAAIAApAFwAbgAvAC8AIAApADsAXABuAFwAbgBcAG4ALwAvACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQATQBvAHYAZQBtAGUAbgB0AEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUALABcAG4ALwAvACAAIAAgAEwARQBUACgAXABuAC8ALwAgACAAIAAgACAAeQBtACwAIABUAEUAWABUACgATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUALABcACIAeQB5AHkAeQBtAG0AXAAiACkALABcAG4ALwAvACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuAC8ALwAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACAAIABIAGUAcgBkAFsATABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AIABpAG4AIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXQAsAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIAAgACgAVABFAFgAVAAoAEgAZQByAGQAWwBNAG8AbgB0AGgAXQAsAFwAIgB5AHkAeQB5AG0AbQBcACIAKQAgAD0AIAB5AG0AKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAgACAAKABIAGUAcgBkAFsATABpAHYAZQBzAHQAbwBjAGsAIABjAGwAYQBzAHMAXQAgAD0AIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAKQBcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACkALABcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgADEAXABuAC8ALwAgACAAIAAgACAAIAAgACkALABcAG4ALwAvACAAIAAgACAAIAAgACAAXAAiAFwAIgBcAG4ALwAvACAAIAAgACAAIAApAFwAbgAvAC8AIAAgACAAKQBcAG4ALwAvACAAKQA7AFwAbgBcAG4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARABhAHkAcwBNAG8AdgBlAG0AZQBuAHQAVABvAE0AbwBuAHQAaABFAG4AZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUALABcAG4AIAAgAEQAQQBUAEUARABJAEYAKABNAG8AdgBlAG0AZQBuAHQARABhAHQAZQAsACAARQBPAE0ATwBOAFQASAAoAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlACwAIAAwACkALAAgAFwAIgBkAFwAIgApAFwAbgApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBEAHUAcgBpAG4AZwBNAG8AbgB0AGgAUABlAHIASABlAGEAZABcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUALABcAG4ALwAvACAAIAAgAEkARgBFAFIAUgBPAFIAKAAgAFwAbgAvAC8AIAAgACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AE0AbwB2AGUAbQBlAG4AdABMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AKABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlACkAKgBcAG4ALwAvACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBEAGEAeQBzAE0AbwB2AGUAbQBlAG4AdABUAG8ATQBvAG4AdABoAEUAbgBkACgATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAKQBcAG4ALwAvACAAIAAgACwAIAAwACkAXABuAC8ALwAgACkAOwBcAG4AXABuAC8ALwAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQBkAGQAZQBkAEQAdQByAGkAbgBnAE0AbwBuAHQAaABcAG4ALwAvACAAPQAgAEwAQQBNAEIARABBACgATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABNAG8AdgBlAG0AZQBuAHQARABhAHQAZQAsACAAVwBlAGkAZwBoAHQAQQB0AE0AbwB2AGUAbQBlAG4AdABEAGEAdABlACwAIABIAGUAYQBkACwAXABuAC8ALwAgAEkARgBFAFIAUgBPAFIAKABcAG4ALwAvACAAIAAgACAAIABIAGUAYQBkACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAVwBlAGkAZwBoAHQAQQB0AE0AbwB2AGUAbQBlAG4AdABEAGEAdABlACsAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBEAHUAcgBpAG4AZwBNAG8AbgB0AGgAUABlAHIASABlAGEAZAAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAKQBcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACkAXABuAC8ALwAgACwAIAAwACkAXABuAC8ALwAgACkAOwBcAG4AXABuAC8ALwAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwByAG8AdwBuAEYAcgBvAG0ATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAVABvAHQAYQBsAFwAbgAvAC8AIAA9AEwAQQBNAEIARABBACgAXABuAC8ALwAgACAAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlACwAIABIAGUAYQBkACwAXABuAC8ALwAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBEAHUAcgBpAG4AZwBNAG8AbgB0AGgAUABlAHIASABlAGEAZAAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAKQAgACoAXABuAC8ALwAgACAAIABIAGUAYQBkAFwAbgAvAC8AIAApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBGAHIAbwBtAE0AbwBuAHQAaABTAHQAYQByAHQAUABlAHIASABlAGEAZABcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAG4AdABoACwAXABuAC8ALwAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBEAHUAcgBpAG4AZwBNAG8AbgB0AGgAUABlAHIASABlAGEAZAAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAARQBPAE0ATwBOAFQASAAoAE0AbwBuAHQAaAAsAC0AMQApACsAMQApAFwAbgAvAC8AIAApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBGAHIAbwBtAE0AbwBuAHQAaABTAHQAYQByAHQAVABvAHQAYQBsAFwAbgAvAC8AIAA9AEwAQQBNAEIARABBACgATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABNAG8AbgB0AGgALAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdABPAGYATQBvAG4AdABoACwAXABuAC8ALwAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBIAGUAYQBkAFIAZQBtAGEAaQBuAGkAbgBnAEEAdABNAG8AbgB0AGgARQBuAGQAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0AE8AZgBNAG8AbgB0AGgAKQAgACoAXABuAC8ALwAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBGAHIAbwBtAE0AbwBuAHQAaABTAHQAYQByAHQAUABlAHIASABlAGEAZAAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAG4AdABoACkAXABuAC8ALwAgACkAOwBcAG4AXABuAC8ALwAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEgAZQBhAGQAQQB0AEUAbgBkAE8AZgBNAG8AbgB0AGgAXABuAC8ALwAgAD0AIABMAEEATQBCAEQAQQAoAEgAZQBhAGQAQQB0AFMAdABhAHIAdAAsACAATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALABcAG4ALwAvACAAIAAgACAAIABIAGUAYQBkAEEAdABTAHQAYQByAHQAXABuAC8ALwAgACAAIAAgACAAKwAgAFwAbgAvAC8AIAAgACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEgAZQBhAGQAQQBkAGQAZQBkAEQAdQByAGkAbgBnAE0AbwBuAHQAaAAoAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkAXABuAC8ALwAgACAAIAAgACAALQAgAFwAbgAvAC8AIAAgACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEgAZQBhAGQATABvAHMAdABEAHUAcgBpAG4AZwBNAG8AbgB0AGgAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApAFwAbgAvAC8AIAApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEYAcgBvAG0AUwB0AGEAcgB0AE8AZgBNAG8AbgB0AGgAXABuAD0AIABMAEEATQBCAEQAQQAoAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAFAAZQByAEQAYQB5ACwAIABNAG8AbgB0AGgALABcAG4AIAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAArAFwAbgAgACAAKABMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AUABlAHIARABhAHkAKgBEAEEAVABFAEQASQBGACgARQBEAEEAVABFACgATQBvAG4AdABoACwAIAAwACkALAAgAEUARABBAFQARQAoAE0AbwBuAHQAaAAsACAAMQApACwAIABcACIAZABcACIAKQApAFwAbgApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBUAG8AdABhAGwATABpAHYAZQB3AGUAaQBnAGgAdABBAGQAZABlAGQARAB1AHIAaQBuAGcATQBvAG4AdABoAFwAbgAvAC8AIAA9ACAATABBAE0AQgBEAEEAKABcAG4ALwAvACAAIAAgACAAIABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsAFwAbgAvAC8AIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4ALwAvACAAIAAgACAAIABTAFUATQAoAFwAbgAvAC8AIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAASQBuAHAAdQB0AF8ASABlAHIAZABNAG8AdgBlAG0AZQBuAHQAWwBUAG8AdABhAGwAIAB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AZQBkACAAcwBpAG4AYwBlACAAagBvAGkAbgBpAG4AZwBdACwAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARABhAHQAZQBdACAAXAB1ADAAMAAzAGUAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAtADEAKQArADEAKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARABhAHQAZQBdACAAXAB1ADAAMAAzAGMAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAwACkAKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsAVABvAF0AIAA9ACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkAXABuAC8ALwAgACAAIAAgACAAIAAgACkAXABuAC8ALwAgACAAIAAgACAAKQAsAFwAbgAvAC8AIAAgACAAIAAgADAAXABuAC8ALwAgACAAIAApAFwAbgAvAC8AIAApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBUAG8AdABhAGwATABpAHYAZQB3AGUAaQBnAGgAdABHAHIAbwB3AG4ARAB1AHIAaQBuAGcATQBvAG4AdABoAFwAbgAvAC8AIAA9ACAATABBAE0AQgBEAEEAKABcAG4ALwAvACAAIAAgACAAIABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsAFwAbgAvAC8AIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4ALwAvACAAIAAgACAAIABTAFUATQAoAFwAbgAvAC8AIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAASQBuAHAAdQB0AF8ASABlAHIAZABNAG8AdgBlAG0AZQBuAHQAWwBMAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwByAG8AdwBuACAAcwBpAG4AYwBlACAAagBvAGkAbgBpAG4AZwBdACwAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARABhAHQAZQBdACAAXAB1ADAAMAAzAGUAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAtADEAKQArADEAKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARABhAHQAZQBdACAAXAB1ADAAMAAzAGMAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAwACkAKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsAVABvAF0AIAA9ACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkAXABuAC8ALwAgACAAIAAgACAAIAAgACkAXABuAC8ALwAgACAAIAAgACAAKQAsAFwAbgAvAC8AIAAgACAAIAAgADAAXABuAC8ALwAgACAAIAApAFwAbgAvAC8AIAApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQBkAGQAZQBkAEQAdQByAGkAbgBnAE0AbwBuAHQAaABcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAFwAbgAvAC8AIAAgACAAIAAgAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAXABuAC8ALwAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAvAC8AIAAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBUAG8AdABhAGwATABpAHYAZQB3AGUAaQBnAGgAdABBAGQAZABlAGQARAB1AHIAaQBuAGcATQBvAG4AdABoACgATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAKQAvAFwAbgAvAC8AIAAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBIAGUAYQBkAEEAZABkAGUAZABEAHUAcgBpAG4AZwBNAG8AbgB0AGgAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApAFwAbgAvAC8AIAAgACAAIAAgACAAIAAsACAAMABcAG4ALwAvACAAIAAgACAAIAApAFwAbgAvAC8AIAApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAUgBlAG0AYQBpAG4AaQBuAGcASABlAGEAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBvAG4AdABoACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABTAHQAYQByAHQALAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgAsAFwAbgAgACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQAUwB0AGEAcgB0ACsAKABMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AKgBEAEEAVABFAEQASQBGACgARQBEAEEAVABFACgATQBvAG4AdABoACwAIAAwACkALAAgAEUARABBAFQARQAoAE0AbwBuAHQAaAAsACAAMQApACwAIABcACIAZABcACIAKQApAFwAbgApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBQAHIAbwBwAG8AcgB0AGkAbwBuAEgAZQBhAGQAUgBlAG0AYQBpAG4AaQBuAGcAQQB0AEUAbgBkAE8AZgBNAG8AbgB0AGgAXABuAC8ALwAgAD0ATABBAE0AQgBEAEEAKABcAG4ALwAvACAAIAAgACAAIABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0ACwAXABuAC8ALwAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAvAC8AIAAgACAAIAAgACAAIABNAEkATgAoADEALABcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEgAZQBhAGQAUgBlAG0AYQBpAG4AaQBuAGcAQQB0AE0AbwBuAHQAaABFAG4AZAAoAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABIAGUAYQBkAEEAdABTAHQAYQByAHQAKQAvACAAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBIAGUAYQBkAEEAdABFAG4AZABPAGYATQBvAG4AdABoACgASABlAGEAZABBAHQAUwB0AGEAcgB0ACwAIABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApAFwAbgAvAC8AIAAgACAAIAAgACAAIAApACwAIAAwAFwAbgAvAC8AIAAgACAAIAAgACkAXABuAC8ALwAgACkAOwBcAG4AXABuAC8ALwAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFAAcgBvAHAAbwByAHQAaQBvAG4ASABlAGEAZABBAGQAZABlAGQARAB1AHIAaQBuAGcATQBvAG4AdABoAFwAbgAvAC8AIAA9AEwAQQBNAEIARABBACgAXABuAC8ALwAgACAAIAAgACAATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdAAsAFwAbgAvAC8AIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4ALwAvACAAIAAgACAAIAAgACAATQBJAE4AKAAxACwAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBIAGUAYQBkAEEAZABkAGUAZABEAHUAcgBpAG4AZwBNAG8AbgB0AGgAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApAC8AIABcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEgAZQBhAGQAQQB0AEUAbgBkAE8AZgBNAG8AbgB0AGgAKABIAGUAYQBkAEEAdABTAHQAYQByAHQALAAgAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkAXABuAC8ALwAgACAAIAAgACAAIAAgACkALAAgADAAXABuAC8ALwAgACAAIAAgACAAKQBcAG4ALwAvACAAKQA7AFwAbgBcAG4ALwAvACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AUAByAG8AcABvAHIAdABpAG8AbgBhAGwAQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AEEAZABkAGUAZABEAHUAcgBpAG4AZwBNAG8AbgB0AGgAXABuAC8ALwAgAD0ATABBAE0AQgBEAEEAKABcAG4ALwAvACAAIAAgACAAIABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0ACwAXABuAC8ALwAgACAAIAAgACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AUAByAG8AcABvAHIAdABpAG8AbgBIAGUAYQBkAEEAZABkAGUAZABEAHUAcgBpAG4AZwBNAG8AbgB0AGgAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0ACkAKgBcAG4ALwAvACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQBkAGQAZQBkAEQAdQByAGkAbgBnAE0AbwBuAHQAaAAoAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkAXABuAC8ALwAgACkAOwBcAG4AXABuAC8ALwAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFAAcgBvAHAAbwByAHQAaQBvAG4AYQBsAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABSAGUAbQBhAGkAbgBpAG4AZwBBAHQARQBuAGQATwBmAE0AbwBuAHQAaABcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAFwAbgAvAC8AIAAgACAAIAAgAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABIAGUAYQBkAEEAdABTAHQAYQByAHQALAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuACwAXABuAC8ALwAgACAAIAAgACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AUAByAG8AcABvAHIAdABpAG8AbgBIAGUAYQBkAFIAZQBtAGEAaQBuAGkAbgBnAEEAdABFAG4AZABPAGYATQBvAG4AdABoACgATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdAApACoAXABuAC8ALwAgACAAIAAgACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AFIAZQBtAGEAaQBuAGkAbgBnAEgAZQBhAGQAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuACkAXABuAC8ALwAgACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAXABuACAAIABIAEwATwBPAEsAVQBQACgATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABSAGEAbgBnAGUAXwBMAGkAdgBlAHMAdABvAGMAawBTAHQAYQByAHQAaQBuAGcAVgBhAGwAdQBlAHMALAAgADMALAAgAEYAQQBMAFMARQApAFwAbgApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBHAGUAdABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABFAG4AZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAXABuACAAIABIAEwATwBPAEsAVQBQACgATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABSAGEAbgBnAGUAXwBMAGkAdgBlAHMAdABvAGMAawBTAHQAYQByAHQAaQBuAGcAVgBhAGwAdQBlAHMALAAgADQALAAgAEYAQQBMAFMARQApAFwAbgApADsAXABuAFwAbgAvAC8AIABBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQARQBuAGQATwBmAE0AbwBuAHQAaABcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAFwAbgAvAC8AIAAgACAATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQAUwB0AGEAcgB0ACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4ALABcAG4ALwAvACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFAAcgBvAHAAbwByAHQAaQBvAG4AYQBsAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABBAGQAZABlAGQARAB1AHIAaQBuAGcATQBvAG4AdABoACgATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdAApACsAXABuAC8ALwAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBQAHIAbwBwAG8AcgB0AGkAbwBuAGEAbABBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAUgBlAG0AYQBpAG4AaQBuAGcAQQB0AEUAbgBkAE8AZgBNAG8AbgB0AGgAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0ACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABTAHQAYQByAHQALAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgApAFwAbgAvAC8AIAApADsAXABuAFwAbgBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQATQBvAG4AdABoAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABNAG8AbgB0AGgAUwB0AGEAcgB0ACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABNAG8AbgB0AGgARQBuAGQALABcAG4AIAAgAEkARgBTACgAXABuACAAIAAgACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQATQBvAG4AdABoAFMAdABhAHIAdAAgAFwAdQAwADAAMwBjAD0AMAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQATQBvAG4AdABoAEUAbgBkACwAXABuACAAIAAgACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQATQBvAG4AdABoAEUAbgBkACAAXAB1ADAAMAAzAGMAPQAwACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABNAG8AbgB0AGgAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAVABSAFUARQAsACAAKABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABNAG8AbgB0AGgAUwB0AGEAcgB0ACsATABpAHYAZQB3AGUAaQBnAGgAdABBAHQATQBvAG4AdABoAEUAbgBkACkALwAyAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AVABvAHQAYQBsAEwAaQB2AGUAdwBlAGkAZwBoAHQARwByAG8AdwBuAEQAdQByAGkAbgBnAE0AbwBuAHQAaABBAGQAZABlAGQAQQBuAGQAUgBlAG0AYQBpAG4AaQBuAGcAXABuAC8ALwAgAD0ATABBAE0AQgBEAEEAKABcAG4ALwAvACAAIAAgAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABIAGUAYQBkAEEAdABTAHQAYQByAHQALABcAG4ALwAvACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwByAG8AdwBuAEYAcgBvAG0ATQBvAG4AdABoAFMAdABhAHIAdABUAG8AdABhAGwAKABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAE0AbwBuAHQAaAAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0ACkAKwBcAG4ALwAvACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFQAbwB0AGEAbABMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBEAHUAcgBpAG4AZwBNAG8AbgB0AGgAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApAFwAbgAvAC8AIAApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBDAGEAbABjAHUAbABhAHQAZQBTAHQAYQB5AEQAdQByAGEAdABpAG8AbgBUAG8ARQBuAGQAMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAXABuACAAIABSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABTAHQAYQByAHQARABhAHQAZQAsAFwAbgAgACAASABlAGEAZABBAHQAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAUwB0AGEAcgB0AEQAYQB0AGUALABcAG4AIAAgAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAEUAbgBkAEQAYQB0AGUALABcAG4AIAAgAEgAZQBhAGQAQQB0AFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAEUAbgBkAEQAYQB0AGUALABcAG4AIAAgAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlAEEAcgByAGEAeQAsAFwAbgAgACAATQBvAHYAZQBtAGUAbgB0AFQAbwBBAHIAcgBhAHkALABcAG4AIAAgAE0AbwB2AGUAbQBlAG4AdABGAHIAbwBtAEEAcgByAGEAeQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABkAHUAcgBhAHQAaQBvAG4AUwB0AGEAcgB0ACwAIABJAEYAKABIAGUAYQBkAEEAdABSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABTAHQAYQByAHQARABhAHQAZQBcAHUAMAAwADMAZQAwACwAIABSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABTAHQAYQByAHQARABhAHQAZQAsACAATQBJAE4ASQBGAFMAKABNAG8AdgBlAG0AZQBuAHQARABhAHQAZQBBAHIAcgBhAHkALAAgAE0AbwB2AGUAbQBlAG4AdABUAG8AQQByAHIAYQB5ACwATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkAKQAsAFwAbgAgACAAIAAgAGQAdQByAGEAdABpAG8AbgBFAG4AZAAsACAASQBGACgASABlAGEAZABBAHQAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQARQBuAGQARABhAHQAZQAgAFwAdQAwADAAMwBlACAAMAAsACAAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQARQBuAGQARABhAHQAZQAsACAATQBBAFgASQBGAFMAKABNAG8AdgBlAG0AZQBuAHQARABhAHQAZQBBAHIAcgBhAHkALAAgAE0AbwB2AGUAbQBlAG4AdABGAHIAbwBtAEEAcgByAGEAeQAsAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApACkALABcAG4AIAAgACAAIABEAEEAVABFAEQASQBGACgARAB1AHIAYQB0AGkAbwBuAFMAdABhAHIAdAAsACAAZAB1AHIAYQB0AGkAbwBuAEUAbgBkACwAIABcACIAZABcACIAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEEAdgBlAHIAYQBnAGUASABlAGEAZABNAG8AbgB0AGgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEgAZQBhAGQAQQB0AE0AbwBuAHQAaABTAHQAYQByAHQALAAgAEgAZQBhAGQAQQB0AE0AbwBuAHQAaABFAG4AZAAsAFwAbgAgACAASQBGAFMAKABcAG4AIAAgACAAIABIAGUAYQBkAEEAdABNAG8AbgB0AGgAUwB0AGEAcgB0ACAAXAB1ADAAMAAzAGMAPQAwACwAIABIAGUAYQBkAEEAdABNAG8AbgB0AGgARQBuAGQALABcAG4AIAAgACAAIABIAGUAYQBkAEEAdABNAG8AbgB0AGgARQBuAGQAIABcAHUAMAAwADMAYwA9ADAALAAgAEgAZQBhAGQAQQB0AE0AbwBuAHQAaABTAHQAYQByAHQALABcAG4AIAAgACAAIABUAFIAVQBFACwAIAAoAEgAZQBhAGQAQQB0AE0AbwBuAHQAaABTAHQAYQByAHQAKwBIAGUAYQBkAEEAdABNAG8AbgB0AGgARQBuAGQAKQAvADIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBUAG8AdABhAGwAQgBpAHIAdABoAHMARAB1AHIAaQBuAGcATQBvAG4AdABoAFwAbgA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAG8AbgB0AGgALAAgAE0AbwB2AGUAbQBlAG4AdABIAGUAYQBkAEEAcgByAGEAeQAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwAIABNAG8AdgBlAG0AZQBuAHQAVAB5AHAAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAUwBVAE0AKABcAG4AIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAE0AbwB2AGUAbQBlAG4AdABIAGUAYQBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAKABNAG8AdgBlAG0AZQBuAHQARABhAHQAZQBBAHIAcgBhAHkAIABcAHUAMAAwADMAZQA9ACAARQBPAE0ATwBOAFQASAAoAE0AbwBuAHQAaAAsAC0AMQApACsAMQApACAAKgBcAG4AIAAgACAAIAAgACAAIAAgACgATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACAAXAB1ADAAMAAzAGMAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAwACkAKQAgACoAXABuACAAIAAgACAAIAAgACAAIAAoAE0AbwB2AGUAbQBlAG4AdABUAHkAcABlAEEAcgByAGEAeQAgAD0AIABcACIAQgBpAHIAdABoAFwAIgApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIAAwAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AQwBhAGwAYwB1AGwAYQB0AGUAUAByAG8AcABvAHIAdABpAG8AbgBDAG8AdwBzAEMAYQBsAHYAaQBuAGcAXABuAD0AIABMAEEATQBCAEQAQQAoAFwAbgAgACAAQgBpAHIAdABoAHMALAAgAEgAZQBhAGQALABcAG4AIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIABCAGkAcgB0AGgAcwAgAC8AIABIAGUAYQBkACwAXABuACAAIAAgACAAMABcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFQAbwB0AGEAbABNAG8AdgBlAG0AZQBuAHQATABpAHYAZQB3AGUAaQBnAGgAdABTAG8AbABkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAG8AdgBlAG0AZQBuAHQAVAB5AHAAZQAsACAASABlAGEAZAAsACAATABpAHYAZQB3AGUAaQBnAGgAdAAsAFwAbgAgACAASQBGACgATQBvAHYAZQBtAGUAbgB0AFQAeQBwAGUAIAA9ACAAXAAiAFMAYQBsAGUAXAAiACwAIABIAGUAYQBkACoATABpAHYAZQB3AGUAaQBnAGgAdAAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBTAHUAbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHcAZQBpAGcAaAB0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAG8AdgBlAG0AZQBuAHQAVAB5AHAAZQAsACAATQBvAHYAZQBtAGUAbgB0AFQAeQBwAGUAQQByAHIAYQB5ACwAIABIAGUAYQBkACwATABpAHYAZQB3AGUAaQBnAGgAdAAsACAAWwBTAG8AdQByAGMAZQBdACwAWwBTAG8AdQByAGMAZQBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIAB0AG8AdABhAGwATABpAHYAZQB3AGUAaQBnAGgAdAAsACAASABlAGEAZAAqAEwAaQB2AGUAdwBlAGkAZwBoAHQALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAE0AbwB2AGUAbQBlAG4AdABUAHkAcABlAEEAcgByAGEAeQA9AE0AbwB2AGUAbQBlAG4AdABUAHkAcABlACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAUwBvAHUAcgBjAGUAKQAsADEALAAtAC0AKABTAG8AdQByAGMAZQBBAHIAcgBhAHkAPQBTAG8AdQByAGMAZQApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHQAbwB0AGEAbABMAGkAdgBlAHcAZQBpAGcAaAB0ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBHAGUAdABIAGUAYQBkAEEAdABFAG4AZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAARQBuAGQARABhAHQAZQAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABEAGEAdABlAEEAcgByAGEAeQAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAEEAcgByAGEAeQAsACAASABlAGEAZABBAHQARQBuAGQATwBmAE0AbwBuAHQAaABBAHIAcgBhAHkALABcAG4AIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgAFQARQBYAFQAKABFAEQAQQBUAEUAKABFAG4AZABEAGEAdABlACwAIAAwACkALABcACIAbQBtAG0AbQAgAHkAeQB5AHkAXAAiACkAXAB1ADAAMAAyADYATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAXABuACAAIAAgACAAIAAgAEQAYQB0AGUAQQByAHIAYQB5AFwAdQAwADAAMgA2AEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAASABlAGEAZABBAHQARQBuAGQATwBmAE0AbwBuAHQAaABBAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAFwAIgAtAFwAIgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEUAbgB0AHIAeQBEAGEAdABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABIAGUAYQBkAEEAdABTAHQAYQByAHQALAAgAEgAZQBhAGQAQQB0AEUAbgB0AHIAeQAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABNAG8AdgBlAG0AZQBuAHQARABhAHQAZQBBAHIAcgBhAHkALAAgAE0AbwB2AGUAbQBlAG4AdABUAG8AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdAA9ADAALABcAG4AIAAgACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgACAAIABNAEkATgBJAEYAUwAoAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlAEEAcgByAGEAeQAsAE0AbwB2AGUAbQBlAG4AdABUAG8AQQByAHIAYQB5ACwATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0ASQBOAEkARgBTACgATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwATQBvAHYAZQBtAGUAbgB0AFQAbwBBAHIAcgBhAHkALABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACAAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAXAAiAC0AXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEUAeABpAHQARABhAHQAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAASABlAGEAZABBAHQARQBuAGQALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwAIABNAG8AdgBlAG0AZQBuAHQARgByAG8AbQBBAHIAcgBhAHkALABcAG4AIAAgAEkARgAoAFwAbgAgACAAIAAgAEgAZQBhAGQAQQB0AEUAbgBkAD0AMAAsAFwAbgAgACAAIAAgAEkARgAoAFwAbgAgACAAIAAgACAAIABNAEEAWABJAEYAUwAoAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlAEEAcgByAGEAeQAsAE0AbwB2AGUAbQBlAG4AdABGAHIAbwBtAEEAcgByAGEAeQAsAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApACwAXABuACAAIAAgACAAIAAgAE0AQQBYAEkARgBTACgATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwATQBvAHYAZQBtAGUAbgB0AEYAcgBvAG0AQQByAHIAYQB5ACwATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkALABcAG4AIAAgACAAIAAgACAAXAAiAC0AXAAiAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABcACIALQBcACIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBHAGUAdABIAGUAYQBkAEEAdABFAHgAaQB0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABFAHgAaQB0AEQAYQB0AGUALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAARABhAHQAZQBBAHIAcgBhAHkALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBBAHIAcgBhAHkALAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdABPAGYATQBvAG4AdABoAEEAcgByAGEAeQAsAFwAbgAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAVABFAFgAVAAoAEUARABBAFQARQAoAEUAeABpAHQARABhAHQAZQAsACAAMAApACwAXAAiAG0AbQBtAG0AIAB5AHkAeQB5AFwAIgApAFwAdQAwADAAMgA2AEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsAFwAbgAgACAAIAAgACAAIABEAGEAdABlAEEAcgByAGEAeQBcAHUAMAAwADIANgBMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdABPAGYATQBvAG4AdABoAEEAcgByAGEAeQApACwAXABuACAAIAAgACAAXAAiAC0AXAAiAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQBuAHQAcgB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAAsACAARQBuAHQAcgB5AEQAYQB0AGUALAAgAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlAEEAcgByAGEAeQAsACAATQBvAHYAZQBtAGUAbgB0AFQAbwBBAHIAcgBhAHkALAAgAE0AbwB2AGUAbQBlAG4AdABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAcgByAGEAeQAsAFwAbgAgACAASQBGACgAXABuACAAIAAgACAASQBTAE4AVQBNAEIARQBSACgARQBuAHQAcgB5AEQAYQB0AGUAKQAsAFwAbgAgACAAIAAgAEkARgAoAFwAbgAgACAAIAAgACAAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABTAHQAYQByAHQAPQAwACwAXABuACAAIAAgACAAIAAgAEEAVgBFAFIAQQBHAEUASQBGAFMAKABcAG4AIAAgACAAIAAgACAAIAAgAE0AbwB2AGUAbQBlAG4AdABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwAIABFAG4AdAByAHkARABhAHQAZQAsACAAXABuACAAIAAgACAAIAAgACAAIABNAG8AdgBlAG0AZQBuAHQAVABvAEEAcgByAGEAeQAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIABcACIALQBcACIAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAFwAIgAtAFwAIgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AEUAeABpAHQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQBuAGQALAAgAEUAeABpAHQARABhAHQAZQAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwAIABNAG8AdgBlAG0AZQBuAHQARgByAG8AbQBBAHIAcgBhAHkALAAgAE0AbwB2AGUAbQBlAG4AdABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAcgByAGEAeQAsAFwAbgAgACAASQBGACgAXABuACAAIAAgACAASQBTAE4AVQBNAEIARQBSACgARQB4AGkAdABEAGEAdABlACkALABcAG4AIAAgACAAIABJAEYAKABcAG4AIAAgACAAIAAgACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQBuAGQAPQAwACwAXABuACAAIAAgACAAIAAgAEEAVgBFAFIAQQBHAEUASQBGAFMAKABcAG4AIAAgACAAIAAgACAAIAAgAE0AbwB2AGUAbQBlAG4AdABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwAIABFAHgAaQB0AEQAYQB0AGUALABcAG4AIAAgACAAIAAgACAAIAAgAE0AbwB2AGUAbQBlAG4AdABGAHIAbwBtAEEAcgByAGEAeQAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIABcACIALQBcACIAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAFwAIgAtAFwAIgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABFAG4AdAByAHkARABhAHQAZQAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0ACwAIABIAGUAYQBkAEEAdABFAG4AZAAsACAAUgBlAHAAbwByAHQAaQBuAGcAUwB0AGEAcgB0AEQAYQB0AGUALAAgAEUAeABpAHQARABhAHQAZQAsACAAUgBlAHAAbwByAHQAaQBuAGcARQBuAGQARABhAHQAZQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABkAGEAdABlAE8AZgBFAG4AdAByAHkALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAEUAbgB0AHIAeQBEAGEAdABlACkALAAgAEUAbgB0AHIAeQBEAGEAdABlACwAIABcACIALQBcACIAKQAsAFwAbgAgACAAIAAgAGQAYQB0AGUATwBmAFIAZQBwAG8AcgB0AGkAbgBnAFMAdABhAHIAdAAsACAASQBGACgASABlAGEAZABBAHQAUwB0AGEAcgB0AFwAdQAwADAAMwBlADAALAAgAFIAZQBwAG8AcgB0AGkAbgBnAFMAdABhAHIAdABEAGEAdABlACwAIABcACIALQBcACIAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAGQAYQB0AGUATwBmAEUAeABpAHQALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAEUAeABpAHQARABhAHQAZQApACwAIABFAHgAaQB0AEQAYQB0AGUALAAgAFwAIgAtAFwAIgApACwAXABuACAAIAAgACAAZABhAHQAZQBPAGYAUgBlAHAAbwByAHQAaQBuAGcARQBuAGQALAAgAEkARgAoAEgAZQBhAGQAQQB0AEUAbgBkAFwAdQAwADAAMwBlADAALAAgAFIAZQBwAG8AcgB0AGkAbgBnAEUAbgBkAEQAYQB0AGUALAAgAFwAIgAtAFwAIgApACwAXABuAFwAbgAgACAAIAAgAGQAdQByAGEAdABpAG8AbgBTAHQAYQByAHQALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAGQAYQB0AGUATwBmAEUAbgB0AHIAeQApACwAIABkAGEAdABlAE8AZgBFAG4AdAByAHkALAAgAGQAYQB0AGUATwBmAFIAZQBwAG8AcgB0AGkAbgBnAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAZAB1AHIAYQB0AGkAbwBuAEUAbgBkACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABkAGEAdABlAE8AZgBFAHgAaQB0ACkALAAgAGQAYQB0AGUATwBmAEUAeABpAHQALAAgAGQAYQB0AGUATwBmAFIAZQBwAG8AcgB0AGkAbgBnAEUAbgBkACkALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEQAQQBUAEUARABJAEYAKABkAHUAcgBhAHQAaQBvAG4AUwB0AGEAcgB0ACwAIABkAHUAcgBhAHQAaQBvAG4ARQBuAGQALAAgAFwAIgBkAFwAIgApACwAIABcACIALQBcACIAXABuACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBHAGUAdABEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAUABvAHMAdABXAGUAYQBuAGkAbgBnAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkALAAgAEQAYQB5AHMAVwBlAGEAbgBpAG4AZwAsAFwAbgAgACAARgBMAE8ATwBSAC4ATQBBAFQASAAoAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5ACAALQAgAEQAYQB5AHMAVwBlAGEAbgBpAG4AZwAsACAAMABcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQAQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQBuAHQAcgB5ACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABFAG4AZAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQB4AGkAdAAsACAARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5ACwAXABuACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAcwB0AGEAcgB0AEwAaQB2AGUAdwBlAGkAZwBoAHQALAAgAEkARgAoAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdABcAHUAMAAwADMAZQAwACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABTAHQAYQByAHQALAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AEUAbgB0AHIAeQApACwAXABuACAAIAAgACAAIAAgAGUAbgBkAEwAaQB2AGUAdwBlAGkAZwBoAHQALAAgAEkARgAoAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AEUAbgBkAFwAdQAwADAAMwBlADAALABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABFAG4AZAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQB4AGkAdAApACwAXABuACAAIAAgACAAIAAgACgAZQBuAGQATABpAHYAZQB3AGUAaQBnAGgAdAAtAHMAdABhAHIAdABMAGkAdgBlAHcAZQBpAGcAaAB0ACkALwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXABuACAAIAAgACAAKQAsACAAMABcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEEAZABqAHUAcwB0AGUAZABMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAEEAcgByAGEAeQAsACAATQBvAG4AdABoAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAATQBvAG4AdABoACwAIABNAG8AbgB0AGgAQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALABcAG4AIAAgACAAIAAgACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAIAAqACAAQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEMAYQBsAGMAdQBsAGEAdABlAEcAcgBvAHcAdABoAEYAYQBjAHQAbwByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAAXABuACAAIABDAFAATQBvAG4AdABoAEEAcgByAGEAeQAsACAAQwBQAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBBAHIAcgBhAHkALAAgAEMAUABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEMAUABUAGEAYgBsAGUATgBhAG0AZQAsAFwAbgAgACAARABNAEQATQBvAG4AdABoAEEAcgByAGEAeQAsACAARABNAEQATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAEEAcgByAGEAeQAsACAARABNAEQAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABEAE0ARABUAGEAYgBsAGUATgBhAG0AZQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAG8AbgB0AGgAQwBQACwAIABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgAE0AbwBuAHQAaAAsACAAQwBQAE0AbwBuAHQAaABBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAXABuACAAIAAgACAAIAAgACAAIABDAFAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAQwBQAFIAZQB0AHUAcgBuAEEAcgByAGEAeQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYQB2AGUAcgBhAGcAZQBDAFAALABcAG4AIAAgACAAIABBAFYARQBSAEEARwBFACgAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAEMAUABUAGEAYgBsAGUATgBhAG0AZQAsACwATQBBAFQAQwBIACgATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAQwBQAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBBAHIAcgBhAHkALAAwACkAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAbQBvAG4AdABoAEQATQBEACwAIABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgAE0AbwBuAHQAaAAsACAARABNAEQATQBvAG4AdABoAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALABcAG4AIAAgACAAIAAgACAAIAAgAEQATQBEAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAEQATQBEAFIAZQB0AHUAcgBuAEEAcgByAGEAeQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYQB2AGUAcgBhAGcAZQBEAE0ARAAsAFwAbgAgACAAIAAgAEEAVgBFAFIAQQBHAEUAKABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgARABNAEQAVABhAGIAbABlAE4AYQBtAGUALAAsAE0AQQBUAEMASAAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsAEQATQBEAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBBAHIAcgBhAHkALAAwACkAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAQQBWAEUAUgBBAEcARQAoAFwAbgAgACAAIAAgACAAIABtAG8AbgB0AGgAQwBQAC8AYQB2AGUAcgBhAGcAZQBDAFAALAAgAG0AbwBuAHQAaABEAE0ARAAvAGEAdgBlAHIAYQBnAGUARABNAEQAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAF8ATABvAG8AawB1AHAATQBDAEYAUwB0AGEAdABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUALAAgAFMAdABhAHQAZQBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwATQBNAFMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQAsACAAUwB0AGEAdABlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABUAGEAYgBsAGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAWwBNAGkAbgAgAHQAZQBtAHAAXQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAFQAYQBiAGwAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBbAE0AYQB4ACAAdABlAG0AcABdACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAVABhAGIAbABlAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAFsATQBpAG4AIAByAGEAaQBuAGYAYQBsAGwAXQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAFQAYQBiAGwAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBbAE0AYQB4ACAAcgBhAGkAbgBmAGEAbABsAF0AKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABUAGEAYgBsAGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAWwBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXQApAFwAdQAwADAAMwBjAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABUAGEAYgBsAGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAWwBNAGEAeAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXQApAFwAdQAwADAAMwBlAD0AZgByAG8AcwB0AEQAYQB5AHMAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABUAGEAYgBsAGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAWwBNAGkAbgAgAGUAbABlAHYAYQB0AGkAbwBuAF0AKQBcAHUAMAAwADMAYwA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABUAGEAYgBsAGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAWwBNAGEAeAAgAGUAbABlAHYAYQB0AGkAbwBuAF0AKQBcAHUAMAAwADMAZQA9AGUAbABlAHYAKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABUAGEAYgBsAGUAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAWwBNAGkAbgAgAE0AQQBQADoAUABFAFQAXQApAFwAdQAwADAAMwBjAD0AbQBhAHAAXwBwAGUAdAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAFQAYQBiAGwAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBbAE0AYQB4ACAATQBBAFAAOgBQAEUAVABdACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAC8AKgAgAEkAZgAgAHQAaABlACAAdABlAG0AcAAgAGkAcwAgAG8AdgBlAHIAIAAxADgAIABhAG4AZAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABhAHIAZQAgADcAIABvAHIAIABiAGUAbABvAHcAIAB3AGUAIABnAGUAdAAgAG0AdQBsAHQAaQBwAGwAZQAgAHIAZQBzAHUAbAB0AHMALgBcAG4AIAAgACAAIAAgACAAIAAgAEkAbgAgAHQAaABpAHMAIABjAGEAcwBlACAAXAB1ADAAMAAyADcAdAByAG8AcABpAGMAYQBsAFwAdQAwADAAMgA3ACAAcgBlAHMAdQBsAHQAcwAgAHMAaABvAHUAbABkACAAYgBlACAAdQBzAGUAZAAsACAAcwBvACAAdwBlACAAdABhAGsAZQAgAHQAaABlACAAZgBpAHIAcwB0ACAAcgBlAHMAdQBsAHQAXABuACAAIAAgACAAIAAgACAAIABiAGUAYwBhAHUAcwBlACAAdAByAG8AcABpAGMAYQBsACAAdgBhAGwAdQBlAHMAIABhAHIAZQAgAGYAaQByAHMAdAAgAGkAbgAgAHQAaABlACAAdABhAGIAbABlACAAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAVABBAEsARQAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAFQAYQBiAGwAZQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBbAEMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAF0ALABtAGEAcwBrACwAIABcACIATgBvACAAbQBhAHQAYwBoAFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEAXABuACAAIAAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABJAHQAZQBtAEYAcgBvAG0ATQBpAG4ATQBhAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAE0AaQBuAEEAcgByAGEAeQAsACAATQBhAHgAQQByAHIAYQB5ACwAIABJAHQAZQBtAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABtAGEAcwBrACwAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AaQBuAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgATQBhAHgAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBMAG8AbwBrAHUAcABWAGEAbAB1AGUAKQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABJAHQAZQBtAEEAcgByAGEAeQAsACAAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8AUwB1AG0AUQB1AGEAbgB0AGkAdAB5AEYAcgBvAG0AQwByAGkAdABlAHIAaQBhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAHIAaQB0AGUAcgBpAGEAMQAsACAAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFEAdQBhAG4AdABpAHQAeQAsACAAWwBNAHUAbAB0AGkAcABsAGkAZQByAF0ALAAgAFsAQwByAGkAdABlAHIAaQBhADIAXQAsAFsAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AF0ALABcAG4AIAAgAEwARQBUACgAXABuACAAIAAgACAAbQB1AGwAdABpAHAAbABpAGUAcgAsACAASQBGACgASQBTAE8ATQBJAFQAVABFAEQAKABNAHUAbAB0AGkAcABsAGkAZQByACkALAAxACwATQB1AGwAdABpAHAAbABpAGUAcgApACwAXABuACAAIAAgACAAcQB1AGEAbgB0AGkAdAB5ACwAIABRAHUAYQBuAHQAaQB0AHkAKgBNAHUAbAB0AGkAcABsAGkAZQByACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMQBUAHkAcABlAEEAcgByAGEAeQA9AEMAcgBpAHQAZQByAGkAYQAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwByAGkAdABlAHIAaQBhADIAKQAsADEALAAtAC0AKABDAHIAaQB0AGUAcgBpAGEAMgBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHEAdQBhAG4AdABpAHQAeQApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4AZwBlAHQATwB2AGUAcgBsAGEAcABwAGkAbgBnAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAEEALABTAC0AMwA2ADUALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYQAsAFkARQBBAFIAKABBACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAYgAsAFkARQBBAFIAKABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAIABTACkALABcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUAIABFACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0AQQBYACgAMAAsAGwAYQBzAHQAWQBlAGEAcgAtAGYAaQByAHMAdABZAGUAYQByACsAMQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAFMALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBTAHQAYQByAHQALABcAG4AIAAgACAAIAAgACAAIAAgAEUALABQAHIAbwBkAHUAYwB0AGkAbwBuAEMAeQBjAGwAZQBFAG4AZAAsAFwAbgAgACAAIAAgACAAIAAgACAAbQAsAE0ATwBOAFQASAAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAZAAsAEQAQQBZACgAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAApACwAIAAvACoAaABlAGwAcABlAHIAOgAgAGUAbgBkACAAZABhAHQAZQAgAGYAbwByACAAYQAgAHIAZQBwAG8AcgB0AGkAbgBnACAAcABlAHIAaQBvAGQAIABzAHQAYQByAHQAaQBuAGcAIABhAHQAIABhACAAZwBpAHYAZQBuACAAZABhAHQAZQAqAC8AXABuACAAIAAgACAAIAAgACAAIABQAGUAcgBpAG8AZABFAG4AZAAsAEwAQQBNAEIARABBACgAcwB0ACwARQBEAEEAVABFACgAcwB0ACwAMQAyACkALQAxACkALAAgAC8AKgBvAG4AbAB5ACAAbgBlAGUAZAAgAHQAbwAgAGwAbwBvAGsAIABiAGEAYwBrACAAMwA2ADUAIABkAGEAeQBzACgAbQBhAHgAIABvAHYAZQByAGwAYQBwACAAdwBpAG4AZABvAHcAKQAqAC8AXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBhACAAZQBuAGQAcwAgAGIAZQBmAG8AcgBlACAAUwAsAGkAdAAgAGMAYQBuAFwAdQAwADAAMgA3AHQAIABvAHYAZQByAGwAYQBwADsAIABtAG8AdgBlACAAdABvACAAbgBlAHgAdAAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAZgBpAHIAcwB0AFkAZQBhAHIALAB5AGEAKwAoAFAAZQByAGkAbwBkAEUAbgBkACgARABBAFQARQAoAHkAYQAsAG0ALABkACkAKQBcAHUAMAAwADMAYwBTACkALAAgAC8AKgBpAGYAIAB0AGgAZQAgAGEAbgBjAGgAbwByACAAZgBvAHIAIAB5AGIAIABzAHQAYQByAHQAcwAgAGEAZgB0AGUAcgAgAEUALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAHAAcgBlAHYAaQBvAHUAcwAgAHkAZQBhAHIAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAbABhAHMAdABZAGUAYQByACwAeQBiAC0AKABEAEEAVABFACgAeQBiACwAbQAsAGQAKQBcAHUAMAAwADMAZQBFACkALABcAG4AIAAgACAAIAAgACAAIAAgAG4ALABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQByAHMALABTAEUAUQBVAEUATgBDAEUAKABuACwAMQAsAGYAaQByAHMAdABZAGUAYQByACwAMQApACwAXABuACAAIAAgACAAIAAgACAAIABzAHQAYQByAHQAcwAsAEQAQQBUAEUAKAB5AHIAcwAsAG0ALABkACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMALABNAEEAUAAoAHMAdABhAHIAdABzACwAUABlAHIAaQBvAGQARQBuAGQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAdABhAGcALABJAEYAKABzAHQAYQByAHQAcwA9AFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQALABcACIAIAAoAFQAaABpAHMAIAByAGUAcABvAHIAdABpAG4AZwAgAGMAeQBjAGwAZQApAFwAIgAsAFwAIgBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMAVABlAHgAdAAsAFQARQBYAFQAKABzAHQAYQByAHQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAGUAbgBkAHMAVABlAHgAdAAsAFQARQBYAFQAKABlAG4AZABzACwAXAAiAGQAZAAgAG0AbQBtACAAeQB5AHkAeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgAbgA9ADAALABcACIAXAAiACwASABTAFQAQQBDAEsAKABzAHQAYQByAHQAcwBUAGUAeAB0ACAAXAB1ADAAMAAyADYAIABcACIAIAB0AG8AIABcACIAIABcAHUAMAAwADIANgAgAGUAbgBkAHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAdABhAGcAKQApAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgA9AEwAQQBNAEIARABBACgARgB1AG4AYwB0AGkAbwBuACwAIABGAE8AUgBNAFUATABBAFQARQBYAFQAKABGAHUAbgBjAHQAaQBvAG4AKQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUwBjAG8AcABlADMAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABjAGgAZQBtAGkAYwBhAGwAIABjAG8AbQBwAG8AdQBuAGQAIABzAGMAbwBwAGUAIAAzAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBTAGMAbwBwAGUAIAAzACAARwBIAEcAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5ACAAMgAwADIANgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIANgAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAdABlAGcAbwByAHkAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBcACIALAAgAFwAIgBFAG0AYgBlAGQAZABlAGQAIABFAG0AaQBzAHMAaQBvAG4AcwAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABJAG4AdABlAG4AcwBpAHQAeQAgAFUAbgBpAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIAQQBtAG0AbwBuAGkAYQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMAAxADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAEEAbQBtAG8AbgBpAGEAXAAiACwAIABcACIAQwBoAGkAbgBhAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMAAxADAAMgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAEEAbQBtAG8AbgBpAGEAXAAiACwAIABcACIAWQBlAG0AZQBuAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMAAxADAAMwAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAEEAbQBtAG8AbgBpAGEAXAAiACwAIABcACIAQwBhAG4AYQBkAGEAXAAiACwAIABcACIAdABcACIALAAgADAAMQAwADEAMAA0ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIAVQByAGUAYQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMAAyADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAFUAcgBlAGEAXAAiACwAIABcACIAQwBoAGkAbgBhAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMAAyADAAMgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAFUAcgBlAGEAXAAiACwAIABcACIAWQBlAG0AZQBuAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMAAyADAAMwAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAFUAcgBlAGEAXAAiACwAIABcACIAQwBhAG4AYQBkAGEAXAAiACwAIABcACIAdABcACIALAAgADAAMQAwADIAMAA0ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIATQBvAG4AbwBhAG0AbQBvAG4AaQB1AG0AIABwAGgAbwBzAHAAaABhAHQAZQAgACgATQBBAFAAKQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMAAzADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAEQAaQBhAG0AbQBvAG4AaQB1AG0AIABQAGgAbwBzAHAAaABhAHQAZQAgACgARABBAFAAKQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMAA0ADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAFUAcgBlAGEALQBBAG0AbQBvAG4AaQB1AG0AIABOAGkAdAByAGEAdABlACAAKABVAEEATgApAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMQAwADUAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIAQQBtAG0AbwBuAGkAdQBtACAATgBpAHQAcgBhAHQAZQAgACgAQQBOACkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADAANgAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBDAGEAbABjAGkAdQBtACAAQQBtAG0AbwBuAGkAdQBtACAATgBpAHQAcgBhAHQAZQAgACgAQwBBAE4AKQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMAA3ADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAFMAdQBsAHAAaABhAHQAZQAgAG8AZgAgAEEAbQBtAG8AbgBpAGEAIAAoAFMATwBBACkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADAAOAAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBOAGkAdAByAG8AZwBlAG4AIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMAA5ADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAC0AIABOAGkAdAByAGEAdABlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMQAxADAAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIATgBpAHQAcgBvAGcAZQBuACAALQAgAEEAbQBtAG8AbgBpAGEAYwBhAGwAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADEAMQAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBNAHUAcgBpAGEAdABlACAAbwBmACAAUABvAHQAYQBzAGgAIAAoAE0ATwBQACAALwAgAEsAQwBMACkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADEAMgAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBTAGkAbgBnAGwAZQAgAHMAdQBwAGUAcgBwAGgAbwBzAHAAaABhAHQAZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMQAzADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAEQAbwB1AGIAbABlACAAcwB1AHAAZQByAHAAaABvAHMAcABoAGEAdABlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMQAxADQAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIAUABoAG8AcwBwAGgAbwByAHUAcwAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMQAxADUAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIAUABvAHQAYQBzAHMAaQB1AG0AIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMQA2ADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAFMAdQBsAGYAdQByACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADEANwAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBaAGkAbgBjACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADEAOAAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBDAGEAbABjAGkAdQBtACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADEAOQAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ATwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBTAGMAbwBwAGUAMwBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABzAGMAbwBwAGUAIAAzAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAYwBvAHAAZQAgADMAIABHAEgARwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkAIAAyADAAMgA2AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAdABlAGcAbwByAHkAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBcACIALAAgAFwAIgBFAG0AYgBlAGQAZABlAGQAIABFAG0AaQBzAHMAaQBvAG4AcwAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABJAG4AdABlAG4AcwBpAHQAeQAgAFUAbgBpAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBEAGEAaQByAHkAIABNAGEAbgB1AHIAZQBcACIALAAgAFwAIgBQAHIAaQBtAGEAcgB5ACAATQBNAFMAXAAiACwAIABcACIAdABcACIALAAgADAAMgAwADEAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBEAGEAaQByAHkAIABNAGEAbgB1AHIAZQBcACIALAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQAgAE0ATQBTAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADIAMAAxADAAMgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIAUABvAHIAawAgAE0AYQBuAHUAcgBlAFwAIgAsACAAXAAiAFAAcgBpAG0AYQByAHkAIABNAE0AUwBcACIALAAgAFwAIgB0AFwAIgAsACAAMAAyADAAMgAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAFAAbwByAGsAIABNAGEAbgB1AHIAZQBcACIALAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQAgAE0ATQBTAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADIAMAAyADAAMgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIARgBlAGUAZABsAG8AdAAgAE0AYQBuAHUAcgBlAFwAIgAsACAAXAAiAFAAcgBpAG0AYQByAHkAIABNAE0AUwBcACIALAAgAFwAIgB0AFwAIgAsACAAMAAyADAAMwAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAEYAZQBlAGQAbABvAHQAIABNAGEAbgB1AHIAZQBcACIALAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQAgAE0ATQBTAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADIAMAAzADAAMgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIARgBlAGUAZABsAG8AdAAgAE0AYQBuAHUAcgBlAFwAIgAsACAAXAAiAFQAZQByAHQAaQBhAHIAeQAgAE0ATQBTAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADIAMAAzADAAMwAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIAUABvAHUAbAB0AHIAeQAgAE0AYQBuAHUAcgBlAFwAIgAsACAAXAAiAFAAcgBpAG0AYQByAHkAIABNAE0AUwBcACIALAAgAFwAIgB0AFwAIgAsACAAMAAyADAANAAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQBcACIALAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQAgAE0ATQBTAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADIAMAA0ADAAMgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIATwB0AGgAZQByAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMgAwADUAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwBpAGwAIABhAG0AZQBuAGQAbQBlAG4AdABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBTAGMAbwBwAGUAMwBfAFMAbwBpAGwAQQBtAGUAbgBkAG0AZQBuAHQAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAbwBpAGwAIABhAG0AZQBuAGQAbQBlAG4AdABzACAAcwBjAG8AcABlACAAMwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAFMAbwBpAGwAQQBtAGUAbgBkAG0AZQBuAHQAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAUwBjAG8AcABlACAAMwAgAEcASABHACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAgADIAMAAyADYAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBTAG8AaQBsAEEAbQBlAG4AZABtAGUAbgB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA3ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AGUAZwBvAHIAeQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEUAbQBiAGUAZABkAGUAZAAgAEUAbQBpAHMAcwBpAG8AbgBzACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAEkAbgB0AGUAbgBzAGkAdAB5ACAAVQBuAGkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AaQBsACAAQQBtAGUAbgBkAG0AZQBuAHQAcwBcACIALAAgAFwAIgBMAGkAbQBlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMwAwADEAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAGkAbAAgAEEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIATABpAG0AZQBzAGEAbgBkAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMwAwADEAMAAyACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAGkAbAAgAEEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIARABvAGwAbwBtAGkAdABlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMwAwADEAMAAzACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAGkAbAAgAEEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIARwB5AHAAcwB1AG0AXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAzADAAMQAwADQALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AaQBsACAAQQBtAGUAbgBkAG0AZQBuAHQAcwBcACIALAAgAFwAIgBQAG8AdABhAHMAaABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADMAMAAxADAANQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBBAGcAcgBvAGMAaABlAG0AaQBjAGEAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBTAGMAbwBwAGUAMwBfAEEAZwByAG8AYwBoAGUAbQBpAGMAYQBsAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAGcAcgBvAGMAaABlAG0AaQBjAGEAbABzACAAcwBjAG8AcABlACAAMwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEEAZwByAG8AYwBoAGUAbQBpAGMAYQBsAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAYwBvAHAAZQAgADMAIABHAEgARwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkAIAAyADAAMgA2AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AQQBnAHIAbwBjAGgAZQBtAGkAYwBhAGwAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBBAGcAcgBvAGMAaABlAG0AaQBjAGEAbABzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA3ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AGUAZwBvAHIAeQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEUAbQBiAGUAZABkAGUAZAAgAEUAbQBpAHMAcwBpAG8AbgBzACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAEkAbgB0AGUAbgBzAGkAdAB5ACAAVQBuAGkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGcAcgBvAGMAaABlAG0AaQBjAGEAbABzAFwAIgAsACAAXAAiAEcAbAB5AHAAaABvAHMAYQB0AGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA0ADAAMQAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGcAcgBvAGMAaABlAG0AaQBjAGEAbABzAFwAIgAsACAAXAAiAFAAYQByAGEAcQB1AGEAdAAsACAAZABpAHEAdQBhAHQAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA0ADAAMQAwADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGcAcgBvAGMAaABlAG0AaQBjAGEAbABzAFwAIgAsACAAXAAiAEcAZQBuAGUAcgBpAGMAIABIAGUAcgBiAGkAYwBpAGQAZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADQAMAAxADAAMwAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAZwByAG8AYwBoAGUAbQBpAGMAYQBsAHMAXAAiACwAIABcACIARwBlAG4AZQByAGkAYwAgAEkAbgBzAGUAYwB0AGkAYwBpAGQAZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADQAMAAxADAANAAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAZwByAG8AYwBoAGUAbQBpAGMAYQBsAHMAXAAiACwAIABcACIARwBlAG4AZQByAGkAYwAgAEYAdQBuAGcAaQBjAGkAZABlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANAAwADEAMAA1ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEwAaQBjAGsAIABCAGwAbwBjAGsAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUwBjAG8AcABlADMAXwBMAGkAYwBrAEIAbABvAGMAawBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATABpAGMAawAgAEIAbABvAGMAawBzACAAcwBjAG8AcABlACAAMwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEwAaQBjAGsAQgBsAG8AYwBrAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAYwBvAHAAZQAgADMAIABHAEgARwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkAIAAyADAAMgA2AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ATABpAGMAawBCAGwAbwBjAGsAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBMAGkAYwBrAEIAbABvAGMAawBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAA3ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AGUAZwBvAHIAeQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEUAbQBiAGUAZABkAGUAZAAgAEUAbQBpAHMAcwBpAG8AbgBzACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAEkAbgB0AGUAbgBzAGkAdAB5ACAAVQBuAGkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAYwBrACAAQgBsAG8AYwBrAHMAXAAiACwAIABcACIATQBpAG4AZQByAGEAbAAgAGIAbABvAGMAawBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADUAMAAxADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBjAGsAIABCAGwAbwBjAGsAcwBcACIALAAgAFwAIgBXAGUAYQBuAGUAcgAgAGIAbABvAGMAawBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADUAMAAxADAAMgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBjAGsAIABCAGwAbwBjAGsAcwBcACIALAAgAFwAIgBEAHIAeQAgAHMAZQBhAHMAbwBuACAAbQBpAHgAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA1ADAAMQAwADMALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQQBuAGkAbQBhAGwAIABGAGUAZQBkAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBTAGMAbwBwAGUAMwBfAEEAbgBpAG0AYQBsAEYAZQBlAGQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAG4AaQBtAGEAbAAgAEYAZQBlAGQAIABzAGMAbwBwAGUAIAAzAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AQQBuAGkAbQBhAGwARgBlAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAUwBjAG8AcABlACAAMwAgAEcASABHACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAgADIAMAAyADYAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBBAG4AaQBtAGEAbABGAGUAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEEAbgBpAG0AYQBsAEYAZQBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANwAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAdABlAGcAbwByAHkAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBcACIALAAgAFwAIgBFAG0AYgBlAGQAZABlAGQAIABFAG0AaQBzAHMAaQBvAG4AcwAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABJAG4AdABlAG4AcwBpAHQAeQAgAFUAbgBpAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABGAGUAZQBkAFwAIgAsACAAXAAiAEcAcgBhAGkAbgBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADYAMAAxADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAARgBlAGUAZABcACIALAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA2ADAAMQAwADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEYAZQBlAGQAXAAiACwAIABcACIAVwBoAGUAYQB0ACAAQgByAGEAbgBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADYAMAAxADAAMwAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAARgBlAGUAZABcACIALAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADYAMAAxADAANAAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAARgBlAGUAZABcACIALAAgAFwAIgBTAG8AeQBiAGUAYQBuAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANgAwADEAMAA1ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABGAGUAZQBkAFwAIgAsACAAXAAiAFMAbwB5AGIAZQBhAG4AIABtAGUAYQBsAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANgAwADEAMAA2ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABGAGUAZQBkAFwAIgAsACAAXAAiAEMAYQBuAG8AbABhACAAbQBlAGEAbABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADYAMAAxADAANwAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAARgBlAGUAZABcACIALAAgAFwAIgBDAGEAbgBvAGwAYQAgAG8AaQBsAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANgAwADEAMAA4ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABGAGUAZQBkAFwAIgAsACAAXAAiAEIAZQBlAHQAIABwAHUAbABwAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANgAwADEAMAA5ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABGAGUAZQBkAFwAIgAsACAAXAAiAEMAbwB0AHQAbwBuACAAcwBlAGUAZABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADYAMAAxADEAMAAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAARgBlAGUAZABcACIALAAgAFwAIgBIAGEAeQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADYAMAAxADEAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAARgBlAGUAZABcACIALAAgAFwAIgBGAGUAZQBkACAAZgBvAHIAbQB1AGwAYQB0AGkAbwBuAHMAIAAoAGMAaABpAGMAawBlAG4ALAAgAHAAaQBnAHMALAAgAGMAYQB0AHQAbABlACwAIABkAGEAaQByAHkAKQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADYAMAAxADEAMgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAARgBlAGUAZABcACIALAAgAFwAIgBNAG8AbABhAHMAcwBlAHMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA2ADAAMQAxADMALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEYAZQBlAGQAXAAiACwAIABcACIAQgBlAG4AdABvAG4AaQB0AGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA2ADAAMQAxADQALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEYAZQBlAGQAXAAiACwAIABcACIATQBlAGEAdAAgAG0AZQBhAGwAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA2ADAAMQAxADUALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEYAZQBlAGQAXAAiACwAIABcACIAQgBlAG4AdABMAGkAbQBlACwAIABwAGgAbwBzAHAAaABvAHIAdQBzACwAIABwAG8AdABhAHMAaABvAG4AaQB0AGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA2ADAAMQAxADQALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQQBxAHUAYQBjAHUAbAB0AHUAcgBlACAARgBlAGUAZAAgAGEAbgBkACAAQgBhAGkAdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUwBjAG8AcABlADMAXwBBAHEAdQBhAGMAdQBsAHQAdQByAGUARgBlAGUAZABBAG4AZABCAGEAaQB0AF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlACAARgBlAGUAZAAgAGEAbgBkACAAQgBhAGkAdAAgAHMAYwBvAHAAZQAgADMAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBBAHEAdQBhAGMAdQBsAHQAdQByAGUARgBlAGUAZABBAG4AZABCAGEAaQB0AF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBTAGMAbwBwAGUAIAAzACAARwBIAEcAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5ACAAMgAwADIANgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBGAGUAZQBkAEEAbgBkAEIAYQBpAHQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AQQBxAHUAYQBjAHUAbAB0AHUAcgBlAEYAZQBlAGQAQQBuAGQAQgBhAGkAdABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAdABlAGcAbwByAHkAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBcACIALAAgAFwAIgBFAG0AYgBlAGQAZABlAGQAIABFAG0AaQBzAHMAaQBvAG4AcwAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABJAG4AdABlAG4AcwBpAHQAeQAgAFUAbgBpAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlACAARgBlAGUAZAAgAGEAbgBkACAAQgBhAGkAdABcACIALAAgAFwAIgBMAG8AdwAgAEEAbgBpAG0AYQBsACAAUAByAG8AdABlAGkAbgAgAEYAbwByAG0AdQBsAGEAdABlAGQAIABGAGUAZQBkAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANwAwADEAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlACAARgBlAGUAZAAgAGEAbgBkACAAQgBhAGkAdABcACIALAAgAFwAIgBIAGkAZwBoACAAQQBuAGkAbQBhAGwAIABQAHIAbwB0AGUAaQBuACAARgBvAHIAbQB1AGwAYQB0AGUAZAAgAEYAZQBlAGQAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA3ADAAMQAwADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAIABGAGUAZQBkACAAYQBuAGQAIABCAGEAaQB0AFwAIgAsACAAXAAiAEMAZQByAGUAYQBsACAAZwByAGEAaQBuAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANwAwADEAMAAzACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlACAARgBlAGUAZAAgAGEAbgBkACAAQgBhAGkAdABcACIALAAgAFwAIgBTAHEAdQBpAGQAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA3ADAAMQAwADQALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAIABGAGUAZQBkACAAYQBuAGQAIABCAGEAaQB0AFwAIgAsACAAXAAiAFcAaABvAGwAZQAgAEYAaQBzAGgAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA3ADAAMQAwADUALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAIABGAGUAZQBkACAAYQBuAGQAIABCAGEAaQB0AFwAIgAsACAAXAAiAFcAaABvAGwAZQAgAFMAYQByAGQAaQBuAGUAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADcAMAAxADAANgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAgAEYAZQBlAGQAIABhAG4AZAAgAEIAYQBpAHQAXAAiACwAIABcACIARgBpAHMAaAAgAEYAcgBhAG0AZQBzAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANwAwADEAMAA3ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlACAARgBlAGUAZAAgAGEAbgBkACAAQgBhAGkAdABcACIALAAgAFwAIgBGAGkAcwBoACAASABlAGEAZABzAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANwAwADEAMAA4ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEwAaQB2AGUAcwB0AG8AYwBrAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBTAGMAbwBwAGUAMwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATABpAHYAZQBzAHQAbwBjAGsAIABzAGMAbwBwAGUAIAAzAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAYwBvAHAAZQAgADMAIABHAEgARwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkAIAAyADAAMgA2AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAZQBnAG8AcgB5AFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdAAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAXAAiACwAIABcACIARQBtAGIAZQBkAGQAZQBkACAARQBtAGkAcwBzAGkAbwBuAHMAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAASQBuAHQAZQBuAHMAaQB0AHkAIABVAG4AaQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQB2AGUAcwB0AG8AYwBrAFwAIgAsACAAXAAiAEIAZQBlAGYAIABjAGEAdAB0AGwAZQBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgB0ACAATABXAFwAIgAsACAAMAA4ADAAMQAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEwAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAdgBlAHMAdABvAGMAawBcACIALAAgAFwAIgBCAGUAZQBmACAAYwBhAHQAdABsAGUAXAAiACwAIABcACIAUwBvAHUAdABoAGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAdAAgAEwAVwBcACIALAAgADAAOAAwADEAMAAyACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAIABMAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHYAZQBzAHQAbwBjAGsAXAAiACwAIABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlAFwAIgAsACAAXAAiAEQAYQBpAHIAeQAgAE8AcgBpAGcAaQBuAFwAIgAsACAAXAAiAHQAIABMAFcAXAAiACwAIAAwADgAMAAxADAAMgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATABXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQB2AGUAcwB0AG8AYwBrAFwAIgAsACAAXAAiAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdAAgAEwAVwBcACIALAAgADAAOAAwADEAMAAzACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAIABMAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHYAZQBzAHQAbwBjAGsAXAAiACwAIABcACIAUwBoAGUAZQBwAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdAAgAEwAVwBcACIALAAgADAAOAAwADEAMAA0ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAIABMAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHYAZQBzAHQAbwBjAGsAXAAiACwAIABcACIAUABpAGcAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAIABMAFcAXAAiACwAIAAwADgAMAAxADAANQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATABXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQB2AGUAcwB0AG8AYwBrAFwAIgAsACAAXAAiAEMAaABpAGMAawBlAG4AcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAIABMAFcAXAAiACwAIAAwADgAMAAxADAANgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATABXAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBQAGEAYwBrAGEAZwBpAG4AZwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUwBjAG8AcABlADMAXwBQAGEAYwBrAGEAZwBpAG4AZwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFAAYQBjAGsAYQBnAGkAbgBnACAAcwBjAG8AcABlACAAMwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAFAAYQBjAGsAYQBnAGkAbgBnAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBTAGMAbwBwAGUAIAAzACAARwBIAEcAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5ACAAMgAwADIANgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAFAAYQBjAGsAYQBnAGkAbgBnAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAFAAYQBjAGsAYQBnAGkAbgBnAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA3ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AGUAZwBvAHIAeQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEUAbQBiAGUAZABkAGUAZAAgAEUAbQBpAHMAcwBpAG8AbgBzACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAEkAbgB0AGUAbgBzAGkAdAB5ACAAVQBuAGkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAYwBrAGEAZwBpAG4AZwBcACIALAAgAFwAIgBXAGkAbgBlACAAYgBvAHQAdABsAGUAcwA6ACAARwBsAGEAcwBzACAALQAgAGMAbwBuAHYAZQBuAHQAaQBvAG4AYQBsAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAYgBvAHQAdABsAGUAXAAiACwAIAAwADkAMAAxADAAMQAsACAAXAAiAGIAbwB0AHQAbABlAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAC0AZQAgAC8AIABiAG8AdAB0AGwAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAYwBrAGEAZwBpAG4AZwBcACIALAAgAFwAIgBXAGkAbgBlACAAYgBvAHQAdABsAGUAcwA6ACAARwBsAGEAcwBzACAALQAgAGwAaQBnAGgAdABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGIAbwB0AHQAbABlAFwAIgAsACAAMAA5ADAAMQAwADIALAAgAFwAIgBiAG8AdAB0AGwAZQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgAtAGUAIAAvACAAYgBvAHQAdABsAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABhAGMAawBhAGcAaQBuAGcAXAAiACwAIABcACIAUABsAGEAcwB0AGkAYwAgAHAAYQBjAGsAYQBnAGkAbgBnAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBnAFwAIgAsACAAMAA5ADAAMgAwADEALAAgAFwAIgBrAGcAXAAiACwAIABcACIAawBnACAAQwBPADIALQBlACAALwAgAGsAZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAYwBrAGEAZwBpAG4AZwBcACIALAAgAFwAIgBQAG8AbAB5AGUAdABoAHkAbABlAG4AZQAgAHQAZQByAGUAcABoAHQAaABhAGwAYQB0AGUAIAAoAFAARQBUACkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGcAXAAiACwAIAAwADkAMAAyADAAMgAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgAtAGUAIAAvACAAawBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAYQBjAGsAYQBnAGkAbgBnAFwAIgAsACAAXAAiAFAAbwBsAHkAcAByAG8AcAB5AGwAZQBuAGUAIAAoAFAAUAApAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBnAFwAIgAsACAAMAA5ADAAMgAwADMALAAgAFwAIgBrAGcAXAAiACwAIABcACIAawBnACAAQwBPADIALQBlACAALwAgAGsAZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAYwBrAGEAZwBpAG4AZwBcACIALAAgAFwAIgBDAGEAcgBkAGIAbwBhAHIAZABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAZwBcACIALAAgADAAOQAwADIAMAA0ACwAIABcACIAawBnAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAC0AZQAgAC8AIABrAGcAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAZQBlAGQAcwAgAGEAbgBkACAAUwBlAGUAZABsAGkAbgBnAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AUwBlAGUAZABzAEEAbgBkAFMAZQBlAGQAbABpAG4AZwBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAUwBlAGUAZABzACAAYQBuAGQAIABTAGUAZQBkAGwAaQBuAGcAcwAgAHMAYwBvAHAAZQAgADMAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBTAGUAZQBkAHMAQQBuAGQAUwBlAGUAZABsAGkAbgBnAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAYwBvAHAAZQAgADMAIABHAEgARwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkAIAAyADAAMgA2AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AUwBlAGUAZABzAEEAbgBkAFMAZQBlAGQAbABpAG4AZwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAFMAZQBlAGQAcwBBAG4AZABTAGUAZQBkAGwAaQBuAGcAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAdABlAGcAbwByAHkAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBcACIALAAgAFwAIgBFAG0AYgBlAGQAZABlAGQAIABFAG0AaQBzAHMAaQBvAG4AcwAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABJAG4AdABlAG4AcwBpAHQAeQAgAFUAbgBpAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBlAGUAZABzACAAYQBuAGQAIABTAGUAZQBkAGwAaQBuAGcAcwBcACIAIAAsAFwAIgBTAGUAZQBkACAAKABnAGUAbgBlAHIAYQBsACAAYwByAG8AcAAgAGEAbgBkACAAcABhAHMAdAB1AHIAZQApAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADEAMAAwADEAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBlAGUAZABzACAAYQBuAGQAIABTAGUAZQBkAGwAaQBuAGcAcwBcACIAIAAsAFwAIgBTAGUAZQBkAGwAaQBuAGcAcwAgACgAZgBvAHIAZQBzAHQAcgB5ACwAIABoAG8AcgB0AGkAYwB1AGwAdAB1AHIAZQAsACAAZQBuAHYAaQByAG8AbgBtAGUAbgB0AGEAbAApAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAUwBlAGUAZABsAGkAbgBnAFwAIgAsACAAMQAwADAAMQAwADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAUwBlAGUAZABsAGkAbgBnAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBDAGwAZQBhAG4AaQBuAGcAIABjAGgAZQBtAGkAYwBhAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUwBjAG8AcABlADMAXwBDAGwAZQBhAG4AaQBuAGcAQwBoAGUAbQBpAGMAYQBsAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAGwAZQBhAG4AaQBuAGcAIABjAGgAZQBtAGkAYwBhAGwAcwAgAHMAYwBvAHAAZQAgADMAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBDAGwAZQBhAG4AaQBuAGcAQwBoAGUAbQBpAGMAYQBsAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAYwBvAHAAZQAgADMAIABHAEgARwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkAIAAyADAAMgA2AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AQwBsAGUAYQBuAGkAbgBnAEMAaABlAG0AaQBjAGEAbABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEMAbABlAGEAbgBpAG4AZwBDAGgAZQBtAGkAYwBhAGwAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAdABlAGcAbwByAHkAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBcACIALAAgAFwAIgBFAG0AYgBlAGQAZABlAGQAIABFAG0AaQBzAHMAaQBvAG4AcwAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABJAG4AdABlAG4AcwBpAHQAeQAgAFUAbgBpAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBsAGUAYQBuAGkAbgBnACAAYwBoAGUAbQBpAGMAYQBsAHMAXAAiACwAIABcACIARABlAHQAZQByAGcAZQBuAHQAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMQAxADAAMQAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAZQBhAG4AaQBuAGcAIABjAGgAZQBtAGkAYwBhAGwAcwBcACIALAAgAFwAIgBBAGMAaQBkAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADEAMQAwADEAMAAyACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBsAGUAYQBuAGkAbgBnACAAYwBoAGUAbQBpAGMAYQBsAHMAXAAiACwAIABcACIAQgBsAGUAYQBjAGgAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBMAFwAIgAsACAAMQAxADAAMQAwADMALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAATABcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBPAHQAaABlAHIAIABhAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAGkAbgBwAHUAdABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBTAGMAbwBwAGUAMwBfAE8AdABoAGUAcgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABJAG4AcAB1AHQAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE8AdABoAGUAcgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAaQBuAHAAdQB0AHMAIABzAGMAbwBwAGUAIAAzAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ATwB0AGgAZQByAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAEkAbgBwAHUAdABzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBTAGMAbwBwAGUAIAAzACAARwBIAEcAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5ACAAMgAwADIANgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAE8AdABoAGUAcgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABJAG4AcAB1AHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBPAHQAaABlAHIAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwASQBuAHAAdQB0AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAZQBnAG8AcgB5AFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdAAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAXAAiACwAIABcACIARQBtAGIAZQBkAGQAZQBkACAARQBtAGkAcwBzAGkAbwBuAHMAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAASQBuAHQAZQBuAHMAaQB0AHkAIABVAG4AaQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAASQBuAHAAdQB0AHMAXAAiACwAIABcACIAQwBPADIAIABmAG8AcgAgAGMAYQByAGIAbwBuAGEAdABpAG8AbgBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAxADIAMAAxADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAASQBuAHAAdQB0AHMAXAAiACwAIABcACIATABpAHYAZQBzAHQAbwBjAGsAIABhAG4AdABpAGIAaQBvAHQAaQBjAHMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMQAxADAAMQAwADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABBAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAEkAbgBwAHUAdABzAFwAIgAsACAAXAAiAE4AeQBsAG8AbgAgAG4AZQB0AHQAaQBuAGcAIABmAG8AcgAgAGgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADEAMQAwADEAMAAzACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIABJAG4AcAB1AHQAcwBcACIALAAgAFwAIgBQAGEAbABsAGUAdABzACAALQAgAFcAbwBvAGQAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMQAxADAAMQAwADQALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABBAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAEkAbgBwAHUAdABzAFwAIgAsACAAXAAiAFAAYQBsAGwAZQB0AHMAIAAtACAAUABsAGEAcwB0AGkAYwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAxADEAMAAxADAANQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAASQBuAHAAdQB0AHMAXAAiACwAIABcACIATABpAHYAZQBzAHQAbwBjAGsAIAB0AGEAZwBzAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADEAMQAwADEAMAA2ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ARgB1AGUAbABUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAIABzAGMAbwBwAGUAIAAzAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ARgB1AGUAbABUAHIAYQBuAHMAcABvAHIAdABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAUwBjAG8AcABlACAAMwAgAEcASABHACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAgADIAMAAyADYAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHYAYQBsAHUAZQBzACAAcwBvAHUAcgBjAGUAZAAgAGYAcgBvAG0AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgAC0AIABTAGUAZQAgAHIAZQBsAGUAdgBhAG4AdAAgAHQAYQBiAGwAZQAgAGkAbgAgAFwAdQAwADAAMgA3AEYAdQBlAGwAIABTAG8AdQByAGMAZQAgAEQAYQB0AGEAXAB1ADAAMAAyADcAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADIALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAZQBnAG8AcgB5AFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdAAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAXAAiACwAIABcACIARQBtAGIAZQBkAGQAZQBkACAARQBtAGkAcwBzAGkAbwBuAHMAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAASQBuAHQAZQBuAHMAaQB0AHkAIABVAG4AaQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAIAAtACAAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAawBsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAIAAtACAAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAHAAZQB0AHIAbwBsAGUAdQBtACAAZwBhAHMAIAAoAEwAUABHACkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEUAdABoAGEAbgBvAGwAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQgBpAG8AZABpAGUAcwBlAGwAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAawBsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAIAAtACAAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBPAHQAaABlAHIAIABiAGkAbwBmAHUAZQBsAHMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAbQAzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAIAAtACAATABpAGcAaAB0ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAawBsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAIAAtACAASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBDAG8AbQBwAHIAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAbQAzAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABtADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAIAAtACAARQB1AHIAbwAgAGkAdgAgAG8AcgAgAGgAaQBnAGgAZQByAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAIAAtACAARQB1AHIAbwAgAGkAaQBpAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAIAAtACAARQB1AHIAbwAgAGkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgAC0AIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgAC0AIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgAC0AIABFAHUAcgBvACAAaQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAawBsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAIAAtACAAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEcAYQBzAG8AbABpAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIASwBlAHIAbwBzAGUAbgBlACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGYAdQBlAGwAIABpAG4AIABhAG4AIABhAGkAcgBjAHIAYQBmAHQAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAawBsAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ARgB1AGUAbABTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkACAAcwBjAG8AcABlACAAMwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAUwBjAG8AcABlACAAMwAgAEcASABHACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAgADIAMAAyADYAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAdgBhAGwAdQBlAHMAIABzAG8AdQByAGMAZQBkACAAZgByAG8AbQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAALQAgAFMAZQBlACAAcgBlAGwAZQB2AGEAbgB0ACAAdABhAGIAbABlACAAaQBuACAAXAB1ADAAMAAyADcARgB1AGUAbAAgAFMAbwB1AHIAYwBlACAARABhAHQAYQBcAHUAMAAwADIANwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgA1ACwAIAA3ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AGUAZwBvAHIAeQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEUAbQBiAGUAZABkAGUAZAAgAEUAbQBpAHMAcwBpAG8AbgBzACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAEkAbgB0AGUAbgBzAGkAdAB5ACAAVQBuAGkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbABzACAAKABvAHQAaABlAHIAIAB0AGgAYQBuACAAcABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABvAGkAbAAgAHUAcwBlAGQAIABhAHMAIABmAHUAZQBsACkALAAgAGUALgBnAC4AIABsAHUAYgByAGkAYwBhAG4AdABzAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiACAAdAAgAFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAGcAcgBlAGEAcwBlAHMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIAQwByAHUAZABlACAAbwBpAGwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAcgB1AGQAZQAgAG8AaQBsACAAYwBvAG4AZABlAG4AcwBhAHQAZQBzAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAHQAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIATwB0AGgAZQByACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAbABpAHEAdQBpAGQAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIAB0ACAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAIgAsACAAXAAiAEEAdQB0AG8AbQBvAHQAaQB2AGUAIABnAGEAcwBvAGwAaQBuAGUAIAAvACAAcABlAHQAcgBvAGwAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAawBsACAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAIgAsACAAXAAiAEEAdgBpAGEAdABpAG8AbgAgAGcAYQBzAG8AbABpAG4AZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBLAGUAcgBvAHMAZQBuAGUAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdAApAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAawBsACAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAIgAsACAAXAAiAEEAdgBpAGEAdABpAG8AbgAgAHQAdQByAGIAaQBuAGUAIABmAHUAZQBsACAALwAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBIAGUAYQB0AGkAbgBnACAAbwBpAGwAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBGAHUAZQBsACAAbwBpAGwAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABhAHIAbwBtAGEAdABpAGMAIABoAHkAZAByAG8AYwBhAHIAYgBvAG4AcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBTAG8AbAB2AGUAbgB0AHMAOgAgAG0AaQBuAGUAcgBhAGwAIAB0AHUAcgBwAGUAbgB0AGkAbgBlACAAbwByACAAdwBoAGkAdABlACAAcwBwAGkAcgBpAHQAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAHAAZQB0AHIAbwBsAGUAdQBtACAAZwBhAHMAIAAoAEwAUABHACkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIATgBhAHAAaAB0AGgAYQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGMAbwBrAGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAdAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBSAGUAZgBpAG4AZQByAHkAIABnAGEAcwAgAGEAbgBkACAAbABpAHEAdQBpAGQAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIAB0ACAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAIgAsACAAXAAiAFIAZQBmAGkAbgBlAHIAeQAgAGMAbwBrAGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAdAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAHAAcgBvAGQAdQBjAHQAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAawBsACAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAIgAsACAAXAAiAEIAaQBvAGQAaQBlAHMAZQBsAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAawBsACAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAIgAsACAAXAAiAEUAdABoAGEAbgBvAGwAIABmAG8AcgAgAHUAcwBlACAAYQBzACAAYQAgAGYAdQBlAGwAIABpAG4AIABhAG4AIABpAG4AdABlAHIAbgBhAGwAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZQBuAGcAaQBuAGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIAQgBpAG8AZgB1AGUAbABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAIABhAG4AZAAgAGIAZQBsAG8AdwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAawBsACAAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzACAAcwBjAG8AcABlACAAMwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAUwBjAG8AcABlACAAMwAgAEcASABHACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAgADIAMAAyADYAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAdgBhAGwAdQBlAHMAIABzAG8AdQByAGMAZQBkACAAZgByAG8AbQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAALQAgAFMAZQBlACAAcgBlAGwAZQB2AGEAbgB0ACAAdABhAGIAbABlACAAaQBuACAAXAB1ADAAMAAyADcARgB1AGUAbAAgAFMAbwB1AHIAYwBlACAARABhAHQAYQBcAHUAMAAwADIANwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA3ACwAIAA3ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AGUAZwBvAHIAeQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEUAbQBiAGUAZABkAGUAZAAgAEUAbQBpAHMAcwBpAG8AbgBzACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAEkAbgB0AGUAbgBzAGkAdAB5ACAAVQBuAGkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAARwBhAHMAZQBvAHUAcwBcACIALAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAIgAsACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBHAGoAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEcAYQBzAGUAbwB1AHMAXAAiACwAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBHAGoAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEcAYQBzAGUAbwB1AHMAXAAiACwAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAIgAsACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBHAGoAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEcAYQBzAGUAbwB1AHMAXAAiACwAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBHAGoAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEcAYQBzAGUAbwB1AHMAXAAiACwAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBHAGoAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEcAYQBzAGUAbwB1AHMAXAAiACwAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEcAagBcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAARwBhAHMAZQBvAHUAcwBcACIALAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBHAGoAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEcAYQBzAGUAbwB1AHMAXAAiACwAIABcACIAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAIgAsACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBHAGoAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEcAYQBzAGUAbwB1AHMAXAAiACwAIABcACIAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBHAGoAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEcAYQBzAGUAbwB1AHMAXAAiACwAIABcACIAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAIgAsACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBHAGoAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEcAYQBzAGUAbwB1AHMAXAAiACwAIABcACIAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAEcAagBcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAARwBhAHMAZQBvAHUAcwBcACIALAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBHAGoAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQAgAC0AIABTAHQAYQB0AGUAIABHAHIAaQBkAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBTAGMAbwBwAGUAMwBfAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQAgAC0AIABTAHQAYQB0AGUAIABHAHIAaQBkACAAcwBjAG8AcABlACAAMwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAUwBjAG8AcABlACAAMwAgAEcASABHACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAgADIAMAAyADYAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAdgBhAGwAdQBlAHMAIABzAG8AdQByAGMAZQBkACAAZgByAG8AbQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAALQAgAFMAZQBlACAAcgBlAGwAZQB2AGEAbgB0ACAAdABhAGIAbABlACAAaQBuACAAXAB1ADAAMAAyADcARQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAUwBvAHUAcgBjAGUAIABEAGEAdABhAFwAdQAwADAAMgA3AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAZQBnAG8AcgB5AFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdAAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAXAAiACwAIABcACIARQBtAGIAZQBkAGQAZQBkACAARQBtAGkAcwBzAGkAbwBuAHMAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAASQBuAHQAZQBuAHMAaQB0AHkAIABVAG4AaQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBTAHQAYQB0AGUAIABHAHIAaQBkAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBTAHQAYQB0AGUAIABHAHIAaQBkAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBTAHQAYQB0AGUAIABHAHIAaQBkAFwAIgAsACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAUwB0AGEAdABlACAARwByAGkAZABcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBTAHQAYQB0AGUAIABHAHIAaQBkAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBTAHQAYQB0AGUAIABHAHIAaQBkAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0ACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAFMAVwBJAFMAKQBcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAUwB0AGEAdABlACAARwByAGkAZABcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABlAHIAbgAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABOAFcASQBTACkAXAAiACwAIABcACIAawBXAGgAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAFMAdABhAHQAZQAgAEcAcgBpAGQAXAAiACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBTAHQAYQB0AGUAIABHAHIAaQBkAFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5ACAALQAgAEQAYQByAHcAaQBuACAASwBhAHQAaABlAHIAaQBuAGUAIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgARABLAEkAUwApAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBTAHQAYQB0AGUAIABHAHIAaQBkAFwAIgAsACAAXAAiAE4AYQB0AGkAbwBuAGEAbABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAGUAcgB0AGkAbABpAHMAZQByACAAYwBoAGUAbQBpAGMAYQBsACAAYwBvAG0AcABvAHUAbgBkAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEUAbABlAG0AZQBuAHQAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAIABjAGgAZQBtAGkAYwBhAGwAIABjAG8AbQBwAG8AdQBuAGQAcwBcACIAKQApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8AQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAGgAZQBtAGkAYwBhAGwAIABjAG8AbQBwAG8AdQBuAGQAcwAgAHUAcwBlAGQAIABpAG4AIABmAGUAcgB0AGkAbABpAHMAZQByAHMALAAgAGEAbABvAG4AZwAgAHcAaQB0AGgAIAB0AGgAZQBpAHIAIABlAGwAZQBtAGUAbgB0AGEAbAAgAGMAbwBtAHAAbwBzAGkAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8AQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQARQBsAGUAbQBlAG4AdABzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADAALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBoAGUAbQBpAGMAYQBsACAAYwBvAG0AcABvAHUAbgBkAFwAIgAsACAAXAAiAE4AXAAiACwAIABcACIAUABcACIALAAgAFwAIgBLAFwAIgAsACAAXAAiAFMAXAAiACwAIABcACIAVQByAGUAYQBcACIALAAgAFwAIgBCAGEAcwBpAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBtAG0AbwBuAGkAYQBcACIALAAgADgAMgAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEEAbQBtAG8AbgBpAHUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAHIAZQBhAFwAIgAsACAAMAAuADQANgAsACAAMAAsACAAMAAsACAAMAAsACAAMQAsACAAXAAiAFUAcgBlAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AbwBhAG0AbQBvAG4AaQB1AG0AIABwAGgAbwBzAHAAaABhAHQAZQAgACgATQBBAFAAKQBcACIALAAgADAALgAxADEALAAgADAALgAyADEAOQAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEEAbQBtAG8AbgBpAHUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAYQBtAG0AbwBuAGkAdQBtACAAUABoAG8AcwBwAGgAYQB0AGUAIAAoAEQAQQBQACkAXAAiACwAIAAwAC4AMQA4ACwAIAAwAC4AMgAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEEAbQBtAG8AbgBpAHUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBVAHIAZQBhAC0AQQBtAG0AbwBuAGkAdQBtACAATgBpAHQAcgBhAHQAZQAgACgAVQBBAE4AKQBcACIALAAgADAALgAzADIALAAgADAALAAgADAALAAgADAALAAgADAALgAzADUALAAgAFwAIgBBAG0AbQBvAG4AaQB1AG0ALQBuAGkAdAByAGEAdABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbQBtAG8AbgBpAHUAbQAgAE4AaQB0AHIAYQB0AGUAIAAoAEEATgApAFwAIgAsACAAMAAuADMANQAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEEAbQBtAG8AbgBpAHUAbQAtAG4AaQB0AHIAYQB0AGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAGwAYwBpAHUAbQAgAEEAbQBtAG8AbgBpAHUAbQAgAE4AaQB0AHIAYQB0AGUAIAAoAEMAQQBOACkAXAAiACwAIAAwAC4AMgA2ADUALAAgADAALAAgADAALAAgADAALAAgADAALAAgAFwAIgBBAG0AbQBvAG4AaQB1AG0ALQBuAGkAdAByAGEAdABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAaQBuAGcAbABlACAAUwB1AHAAZQByAHAAaABvAHMAcABoAGEAdABlACAAKABTAFMAUAApAFwAIgAsACAAMAAsACAAMAAuADAAOAA4ACwAIAAwACwAIAAwAC4AMQAxACwAIAAwACwAIABcACIATwB0AGgAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwB1AGIAbABlACAAUwB1AHAAZQByAHAAaABvAHMAcABoAGEAdABlAFwAIgAsACAAMAAsACAAMAAuADAAOAA4ACwAIAAwACwAIAAwAC4AMQAxACwAIAAwACwAIABcACIATwB0AGgAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBsAHAAaABhAHQAZQAgAG8AZgAgAEEAbQBtAG8AbgBpAGEAIAAoAFMATwBBACkAXAAiACwAIAAwAC4AMgAxACwAIAAwACwAIAAwACwAIAAwAC4AMgA0ACwAIAAwACwAIABcACIAQQBtAG0AbwBuAGkAdQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AdQByAGkAYQB0AGUAIABvAGYAIABQAG8AdABhAHMAaAAgACgATQBPAFAAIAAvACAASwBDAEwAKQBcACIALAAgADAALAAgADAALAAgADAALgA2ACwAIAAwACwAIAAwACwAIABcACIATwB0AGgAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAMQAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAE4AaQB0AHIAYQB0AGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBpAHQAcgBvAGcAZQBuACAALQAgAE4AaQB0AHIAYQB0AGUAXAAiACwAIAAwAC4AMgAyADYALAAgADAALAAgADAALAAgADAALAAgADAALAAgAFwAIgBOAGkAdAByAGEAdABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAC0AIABBAG0AbQBvAG4AaQBhAGMAYQBsAFwAIgAsACAAMAAuADgAMgAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEEAbQBtAG8AbgBpAHUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGgAbwBzAHAAaABvAHIAdQBzACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwACwAIAAxACwAIAAwACwAIAAwACwAIAAwACwAIABcACIATwB0AGgAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAbwB0AGEAcwBzAGkAdQBtACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwACwAIAAwACwAIAAxACwAIAAwACwAIAAwACwAIABcACIATwB0AGgAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBsAGYAdQByACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAxACwAIAAwACwAIABcACIATwB0AGgAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFoAaQBuAGMAIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgAFwAIgBPAHQAaABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAGwAYwBpAHUAbQAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAE8AdABoAGUAcgBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgAgAHAAcgBvAGQAdQBjAHQAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFAAcgBvAGQAdQBjAHQAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAIABwAHIAbwBkAHUAYwB0AHMAXAAiACkAKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFAAcgBvAGQAdQBjAHQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFAAbwBwAHUAbABhAHIAIABmAGUAcgB0AGkAbABpAHMAZQByACAAcAByAG8AZAB1AGMAdABzACAAdQBzAGUAZAAgAGkAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACwAIABhAGwAbwBuAGcAIAB3AGkAdABoACAAdABoAGUAaQByACAAYwBoAGUAbQBpAGMAYQBsACAAYwBvAG0AcABvAHUAbgBkACAAYwBvAG0AcABvAHMAaQB0AGkAbwBuAFwAIgApACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBQAHIAbwBkAHUAYwB0AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFAAcgBvAGQAdQBjAHQAcwBfAEQAYQB0AGEAMQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzADEALAAgADIAMAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAxAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAxACAAcABlAHIAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAyAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAyACAAcABlAHIAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMgAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAzAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAzACAAcABlAHIAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMwAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA0ACAAcABlAHIAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANAAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA1AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA1ACAAcABlAHIAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA2AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA2ACAAcABlAHIAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANgAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAIABpAG4AZgBvACAAbABpAG4AawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgA3ADUAJQAgAE0AQQBQACAAMgA1ACUAIABNAE8AUABcACIALAAgAFwAIgBNAG8AbgBvAGEAbQBtAG8AbgBpAHUAbQAgAHAAaABvAHMAcABoAGEAdABlACAAKABNAEEAUAApAFwAIgAsACAAMAAuADcANQAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIATQB1AHIAaQBhAHQAZQAgAG8AZgAgAFAAbwB0AGEAcwBoACAAKABNAE8AUAAgAC8AIABLAEMATAApAFwAIgAsACAAMAAuADIANQAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIANwA1ACUAIABVAHIAZQBhACAAMgA1ACUAIABNAE8AUABcACIALAAgAFwAIgBVAHIAZQBhAFwAIgAsACAAMAAuADcANQAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIATQB1AHIAaQBhAHQAZQAgAG8AZgAgAFAAbwB0AGEAcwBoACAAKABNAE8AUAAgAC8AIABLAEMATAApAFwAIgAsACAAMAAuADIANQAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAOAAwACUAIABVAHIAZQBhACAAMgAwACUAIABNAEEAUABcACIALAAgAFwAIgBVAHIAZQBhAC0AQQBtAG0AbwBuAGkAdQBtACAATgBpAHQAcgBhAHQAZQAgACgAVQBBAE4AKQBcACIALAAgADAALgA4ACwAIABcACIAQwBoAGkAbgBhAFwAIgAsACAAXAAiAE0AbwBuAG8AYQBtAG0AbwBuAGkAdQBtACAAcABoAG8AcwBwAGgAYQB0AGUAIAAoAE0AQQBQACkAXAAiACwAIAAwAC4AMgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBjAHQAaQB2AGEAdABlACAATgBcACIALAAgAFwAIgBOAGkAdAByAG8AZwBlAG4AIAAtACAAQQBtAG0AbwBuAGkAYQBjAGEAbABcACIALAAgADAALgAwADcAMQAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIATgBpAHQAcgBvAGcAZQBuACAALQAgAE4AaQB0AHIAYQB0AGUAXAAiACwAIAAwAC4AMAAwADYALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAC0AIABVAHIAZQBpAGMAXAAiACwAIAAwAC4AMAA5ADMALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFAAaABvAHMAcABoAG8AcgB1AHMAIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADAALgAwADEALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFAAbwB0AGEAcwBzAGkAdQBtACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwAC4AMAA0ACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBTAHUAbABmAHUAcgAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAMAAuADgAMgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAQQBjAHQAaQB2AGUAIABOACAAKABMAGEAdwBuAHAAcgBpAGQAZQAuAGMAbwBtAC4AYQB1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBjAHQAaQB2AGkAcwB0ACAATQBhAHgAIABaAGkAbgBjAFwAIgAsACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAMAAuADAANwAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAWgBpAG4AYwAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAMAAuADcALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAQwBUAEkAVgBJAFMAVAAtAE0AQQBYAC4AcABkAGYAIAAoAGEAZwByAGkAYwBoAGUAbQAuAGMAbwBtAC4AYQB1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBnAGYAbABvAHcAXAAiACwAIABcACIATgBpAHQAcgBvAGcAZQBuACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwAC4AMQAyADkALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFAAaABvAHMAcABoAG8AcgB1AHMAIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADAALgAxADcANwAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAUwB1AGwAZgB1AHIAIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADAALgAwADYALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAUwBCAFAAIABIAGkAZwBoACAALwAgAE0AYQBpAG4AdABlAG4AYQBuAGMAZQAgAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBnAGYAbABvAHcAIABCAG8AbwBzAHQAXAAiACwAIABcACIATgBpAHQAcgBvAGcAZQBuACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwAC4AMQAyADEALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFAAaABvAHMAcABoAG8AcgB1AHMAIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADAALgAxADkAOAAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAUwB1AGwAZgB1AHIAIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADAALgAwADQAMQAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBTAEIAUAAgAEgAaQBnAGgAIAAvACAATQBhAGkAbgB0AGUAbgBhAG4AYwBlACAAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGcAZgBsAG8AdwAgAEIAbwBvAHMAdAAgAEUAeAB0AHIAYQBcACIALAAgAFwAIgBOAGkAdAByAG8AZwBlAG4AIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADAALgAxADIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFAAaABvAHMAcABoAG8AcgB1AHMAIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADAALgAxADkANwAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAUwB1AGwAZgB1AHIAIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADAALgAwADQALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAUwBCAFAAIABIAGkAZwBoACAALwAgAE0AYQBpAG4AdABlAG4AYQBuAGMAZQAgAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBnAE4AUABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAFMAQgBQACAASABpAGcAaAAgAC8AIABNAGEAaQBuAHQAZQBuAGEAbgBjAGUAIABTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsAFMAdABhAHIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBpAHQAIABGAGUAcgB0AGkAbABpAHoAZQByAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBtAG0AbwAgADMANgBcACIALAAgAFwAIgBVAHIAZQBhAFwAIgAsACAAMAAuADQALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFMAdQBsAHAAaABhAHQAZQAgAG8AZgAgAEEAbQBtAG8AbgBpAGEAIAAoAFMATwBBACkAXAAiACwAIAAwAC4ANgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUgBhAHYAZQBuAHMAZABvAHcAbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAZQB4ACAARwBhAEkAWABlACAATABvAHcAIABQACAAMgAxAC0AMQAtADYAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQgBhAGkAbABlAHkAcwAgAGMAbwBuAHQAcgBvAGwAbABlAGQAIAByAGUAbABlAGEAcwBlACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBnACAATgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBCAGkAZwAgAE4AIABBAG4AaAB5AGQAcgBvAHUAcwAgAGEAbQBtAG8AbgBpAGEAIABOAEgAMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAZwAgAFAAaABvAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBTAEIAUAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAFAAdQBsAHMAZQAgAGEAbgBkACAATAB1AHAAaQBuAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAG0AcABiAGUAbABsAHMAIABRAHUAaQBjAGsALQBOAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFEAdQBpAGMAawAgAC0AIABOACAAfAAgAEMAYQBtAHAAYgBlAGwAbABzACAARgBlAHIAdABpAGwAaQBzAGUAcgBzACAAQQB1AHMAdAByAGEAbABpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBLACAANQA1ACAAQQBtAGUAbABpAG8AcgBhAG4AdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBQAGEAYwBpAGYAaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzACAAQwByAG8AcAAgAEsAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAEIAbwBvAHMAdABlAHIAIABQAGwAdQBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMATAAgAFQARQBDACAARgBlAHIAdABpAGwAaQBzAGUAcgBzACAAQwByAG8AcAAgAEIAbwBvAHMAdABlAHIAIABQAGwAdQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAQQBQAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAE0AbwB1AG4AdABDAG8AbQBwAGEAcwBzACAARgBlAHIAdABpAGwAaQBzAGUAcgBzACAAQgBsAGUAbgBkAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABBAFAAUwBaAEMAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBpAHQAIABGAGUAcgB0AGkAbABpAHoAZQByAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQBhAHMAeQAgAE4AIABCAHUAbABrAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBjAGkAdABlAGMAIABQAGkAdgBvAHQAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQBuAHQAZQBjACAAVQByAGUAYQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBOAHUAdAB1AHIAZgAgAFUAcgBlAGEAIABHAHIAYQBuAHUAbABhAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB6AHkAZgBsAG8AdwAgAE4AYQBuAG8AIABDAGEAbABiAHUAZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBFAHoAeQBGAGwAbwB3ACAATgBhAG4AbwAgAEMAYQBsAGIAdQBkACAAfAAgAEwAbwB2AGUAbABhAG4AZAAgACgAbABvAHYAZQBsAGEAbgBkAGEAZwByAGkAcAByAG8AZAB1AGMAdABzAC4AYwBvAG0ALgBhAHUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAGwAZQB4AGkALQBOACAATgBJACAAbwBuAGwAeQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBSAGEAdgBlAG4AcwBkAG8AdwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAbAB5AHQAcgBlAGwAIABaAG4AUAAgADAALQA3AC0AMABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBZAGEAcgBhAFYAaQB0AGEAIABHAGwAeQB0AHIAZQBsACAAWgBuAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARwByAGEAbgAtAEEAbQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AYwBpAHQAZQBjACAAUABpAHYAbwB0ACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAcgBhAG4AdQBsAG8AYwBrACAAUwBTAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBjAGkAdABlAGMAIABQAGkAdgBvAHQAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARwByAGEAbgB1AGwAbwBjAGsAIABaAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBjAGkAdABlAGMAIABQAGkAdgBvAHQAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARwByAGUAZQBuACAAVQByAGUAYQAgAE4AVgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AYwBpAHQAZQBjACAAUABpAHYAbwB0ACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAeQBwAHMAdQBtACAAUwB1AGwAcABoAHUAcgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBHAHkAcABzAHUAbQAgAEkAbgBjAGkAdABlAGMAIABQAGkAdgBvAHQAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAHYAaQBnAG8AcgA4ACAAMAAtADMANwAtADMANwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBHAGUAbgBlAHMAaQBzACAAQQBHAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFAAcgBvAGQAdQBjAHQAcwBfAEQAYQB0AGEAMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzADEALAAgADIAMAAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAxAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAxACAAcABlAHIAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAyAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAyACAAcABlAHIAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMgAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAzAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAzACAAcABlAHIAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMwAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA0ACAAcABlAHIAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANAAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA1AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA1ACAAcABlAHIAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA2AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA2ACAAcABlAHIAYwBlAG4AdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANgAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAIABpAG4AZgBvACAAbABpAG4AawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBnAGEAbgBlAHMAZQAgAFMAdQBsAHAAaABhAHQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AYwBpAHQAZQBjACAAUABpAHYAbwB0ACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBQAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBjAGkAdABlAGMAIABQAGkAdgBvAHQAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIABJAG0AcABhAGMAdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG0AcABhAGMAdAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUABTAFoAQwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHUAbQBtAGkAdAAgAEYAZQByAHQAaQBsAGkAegBlAHIAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAeABpAG0AdQBtACAATgAtAFAAYQBjAHQAIAAyADkALQAwAC0AMABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBNAGEAeABpAG0AdQBtACAATgAtAFAAYQBjAHQAIAB8ACAATABvAHYAZQBsAGEAbgBkACAAKABsAG8AdgBlAGwAYQBuAGQAYQBnAHIAaQBwAHIAbwBkAHUAYwB0AHMALgBjAG8AbQAuAGEAdQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBjAHIAbwBzAG8AbAAgADEAMgAtADYALQA0ADQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUgBpAGcAYgB5AHQAYQB5AGwAbwByACAATQBpAGMAcgBvAHMAbwBsACAAUgBhAG4AZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBjAHIAbwBzAG8AbAAgADEANgAtADMAMgAtADEANgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBSAGkAZwBiAHkAdABhAHkAbABvAHIAIABNAGkAYwByAG8AcwBvAGwAIABSAGEAbgBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBpAGMAcgBvAHMAbwBsACAAMgA1AC0ANQAtADEAMABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBSAGkAZwBiAHkAdABhAHkAbABvAHIAIABNAGkAYwByAG8AcwBvAGwAIABSAGEAbgBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBpAGMAcgBvAHMAbwBsACAAMgA4AC0AMAAtADEANABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBSAGkAZwBiAHkAdABhAHkAbABvAHIAIABNAGkAYwByAG8AcwBvAGwAIABSAGEAbgBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBvAG4AbwAgAFAAbwB0AGEAcwBzAGkAdQBtACAAUABoAG8AcwBwAGgAYQB0AGUAIABNAEsAUABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHcAYQBuAGMAcgBvAHAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQB1AHIAaQBhAHQAZQAgAE8AZgAgAFAAbwB0AGEAcwBoACAATQBPAFAAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIATQBvAHUAbgB0AEMAbwBtAHAAYQBzAHMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAIABCAGwAZQBuAGQAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGkAdAByAG8AUABsAHUAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAGcAcgBvAFMAdABvAGMAawAgAEcAcgBvAHUAcAAgAE4AaQB0AHIAbwAgAFAAbAB1AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgB1AHQAcgBhAEcAbwBsAGQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB3AGEAbgBjAHIAbwBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvACAAUABlAHIAZgBvAHIAbQBhAG4AYwBlACAAMQA4AC0AMwAtADYAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUAByAG8AIABUAHUAcgBmACAARgBvAHIAbQB1AGwAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAE8AQQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBNAG8AdQBuAHQAQwBvAG0AcABhAHMAcwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAEIAbABlAG4AZABzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAUwBQAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbQBwAGEAYwB0ACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBwAGUAcgAgAFAAaABvAHMAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBTAEIAUAAgAFMAdQBwAGUAcgAgAFAASABPAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AHAAZQByACAAUwBSACAARQB4AHQAcgBhAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAUwBCAFAAIABTAHUAcABlAHIAIABQAG8AdABhAHMAaABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAUABlAHIAZgBlAGMAdABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AYwBpAHQAZQBjACAAUABpAHYAbwB0ACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBwAGUAcgBQAGEAcwB0AHUAcgBlACAAUABvAHQAYQBzAGgAIAA1ADoAMQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAFMAQgBQACAAUwB1AHAAZQByACAAUABvAHQAYQBzAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAYwBlAC0AaQB0ACAATQBuAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAYQBtAHAAYgBlAGwAbABzACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzACAAQQB1AHMAdAByAGEAbABpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQBuAGkAUwBaAG8AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBXAGUAbgBnAGYAdQBBAHUAcwB0AHIAYQBsAGkAYQAgAHUAbgBpAFMAWgBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQByAGUAYQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AEMAYQByAGQAXwBBAGQAZQBsAGEAaQBkAGUAXwB3AGUAYgAuAHAAZABmACAAKABpAG4AYwBpAHQAZQBjAHAAaQB2AG8AdABmAGUAcgB0AGkAbABpAHMAZQByAHMALgBjAG8AbQAuAGEAdQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBuAGcAZgB1ACAAUwBsAGEAbQAgAEcAcgBhAG4AdQBsAGEAcgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHQAcgBhAGkAZwBoAHQAcwAgACgAdwBlAG4AZwBmAHUALgBjAG8AbQAuAGEAdQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABGAGwAbwB3AFAAaABvAHMAIAAxADAAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABGAGwAbwB3AFAAaABvAHMAIAAxADMAWgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEYAbABvAHcAUABoAG8AcwAgADEANQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEYAbABvAHcAUABoAG8AcwAgAEsAWgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEsAZQB5AFAAcgBvACAAVAByAGEAYwBlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAASwBlAHkAUAByAG8AIABaAGkAbgBjAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBQAHIAbwBkAHUAYwB0AHMAXwBEAGEAdABhADMAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAxACwAIAAyADAALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMQAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMgBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMgAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADIAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMwBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMwAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADMAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANAAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADQAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANQAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADUAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANgBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANgAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADYAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAaQBuAGYAbwAgAGwAaQBuAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEsALQBGAGwAbwB3ACAAMAAtADAALQAxADUAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABLAC0ARgBsAG8AdwAgADAALQAxADQALQAzADAAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABLAC0ARgBsAG8AdwAgADAALQA3AC0AMwA2AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAASwAtAEYAbABvAHcAIAAxADMALQAwAC0ANwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEsALQBGAGwAbwB3ACAANAAtADAALQAxADIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAATQBJAEMAUgBPAC0AUwBVAEwAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAATgAyADQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAATgAyADUAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAATgAyADYAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAATgA0ADIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAATgAtAEMAQQBMACAAMQA1ACsAMQA4AEMAYQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEwAaQBxAHUAaQBkAHMAIABOAC0AQwBBAEwAIAAyADAAKwAxADAAQwBhACsAQgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEwAaQBxAHUAaQBkAHMAIABOAC0AQwBBAEwAIAAzADUAKwA2AEMAYQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEwAaQBxAHUAaQBkAHMAIABOAC0ARgBPAEwAIAAyADQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAATgAtAEYATwBMACAAMgA0ACsAVABFAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAATABpAHEAdQBpAGQAcwAgAFAALQBGAE8ATAAgAFoAaQBuAGMAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAAUwBVAEwAUwBBACAAMQAxAC0AMAAtADAAKwAxADIAUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEwAaQBxAHUAaQBkAHMAIABTAFUATABTAEEAIAAyADQALQAzAC0AMAArADYAUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEwAaQBxAHUAaQBkAHMAIABTAFUATABTAEEAIAAyADcALQAwAC0AMAArADcAUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEwAaQBxAHUAaQBkAHMAIABTAFUATABTAEEAIAAzADYALQAwAC0AMAArADMAUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQBMAGkAdgBhACAAQwBBAEwAQwBJAE4ASQBUACAAQgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQBMAGkAdgBhACAATgBJAFQAUgBBAEIATwBSAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFkAYQByAGEATABpAHYAYQAgAE4ASQBUAFIAQQBCAE8AUgAgAHwAIABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQBMAGkAdgBhACAAVABSAE8AUABJAEMATwBUAEUAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEATQBpAGwAYQAgAEMAbwBtAHAAbABlAHgAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEATQBpAGwAYQAgAEMAbwBtAHAAbABlAHgAIAAxADcALQA1AC0AMQAwACgANAApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAE0AaQBsAGEAIABDAG8AbQBwAGwAZQB4ACAAMgAxAC0ANwAtADMAKAA0ACkAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEATQBpAGwAYQAgAFUATgBJAFYARQBSAFMAQQBMAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAFIAZQBnAGEAIAAxADMALQAyAC0AMgAxAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAFYAaQB0AGEAIABCAE8AUgBUAFIAQQBDAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAFYAaQB0AGEAIABCAFIAQQBTAFMASQBUAFIARQBMACAARABGAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBQAHIAbwBkAHUAYwB0AHMAXwBEAGEAdABhADQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA2ACwAIAAyADAALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMQAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMgBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMgAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADIAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMwBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMwAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADMAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANAAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADQAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANQAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADUAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANgBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANgAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADYAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAaQBuAGYAbwAgAGwAaQBuAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQBWAGkAdABhACAAQgBSAEEAUwBTAEkAVABSAEUATAAgAFAAUgBPAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAFYAaQB0AGEAIABCAFUARAAgAEIAVQBJAEwARABFAFIAIABGAEwAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAVgBpAHQAYQAgAEYAUgBVAFQAUgBFAEwAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAVgBpAHQAYQAgAEcATABZAFQAUgBFAEwAIABaAG4AUABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQBWAGkAdABhACAARwBSAEEATQBJAFQAUgBFAEwAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAVgBpAHQAYQAgAEsATwBNAEIASQBQAEgATwBTAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAFYAaQB0AGEAIABNAEEATgBHAFoASQBOAEMAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAVgBpAHQAYQAgAE0ATwBMAFkAVABSAEEAQwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQBWAGkAdABhACAAUwBFAE4ASQBQAEgATwBTAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAFYAaQB0AGEAIABaAEkATgBUAFIAQQBDAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBaAGkAbgBjACAAUwB1AGwAcABoAGEAdABlACAATQBvAG4AbwBoAHkAZAByAGEAdABlAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbgBjAGkAdABlAGMAIABQAGkAdgBvAHQAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWgBpAG4AYwBzAG8AbABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHUAbABmAGEAdABlACAAWgBpAG4AYwBzAG8AbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBaAGkAbgBjAFMAdABhAHIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIASQBtAHAAYQBjAHQAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWgBNAEMALQAxAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEsAZQBtAGcAcgBvACAAWgBNAEMALQAxAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFoAbgAgADcAMAAwADAAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUgB1AHQAZQBjACAAWgBuACAANwAwADAAMABcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEwAaQBtAGUALAAgAGQAbwBsAG8AbQBpAHQAZQAgAGEAbgBkACAAZwB5AHAAcwB1AG0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGkAbQBlAEQAbwBsAG8AbQBpAHQAZQBHAHkAcABzAHUAbQBDAG8AbgBzAHQAYQBuAHQAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAbwBuAHMAdABhAG4AdABzACAAZgBvAHIAIABsAGkAbQBlACwAIABkAG8AbABvAG0AaQB0AGUAIABhAG4AZAAgAGcAeQBwAHMAdQBtAFwAIgApACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGkAbQBlAEQAbwBsAG8AbQBpAHQAZQBHAHkAcABzAHUAbQBDAG8AbgBzAHQAYQBuAHQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAbwBuAHMAdABhAG4AdABzACAAZgBvAHIAIABsAGkAbQBlACwAIABkAG8AbABvAG0AaQB0AGUAIABhAG4AZAAgAGcAeQBwAHMAdQBtAFwAIgApACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGkAbQBlAEQAbwBsAG8AbQBpAHQAZQBHAHkAcABzAHUAbQBDAG8AbgBzAHQAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgADUALgA4AC4AMgAgAE0AZQB0AGgAbwBkAG8AbABvAGcAaQBjAGEAbAAgAGkAcwBzAHUAZQBzACwAIABlAHEAdQBhAHQAaQBvAG4AIAAzAEcAXwAxAFwAIgApACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGkAbQBlAEQAbwBsAG8AbQBpAHQAZQBHAHkAcABzAHUAbQBDAG8AbgBzAHQAYQBuAHQAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAGwAZQBtAGUAbgB0AFwAIgAsACAAXAAiAFAAXAAiACwAIABcACIARQBGAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBtAGUAIAAoAEMAYQBsAGMAaQB1AG0AIABjAGEAcgBiAG8AbgBhAHQAZQApAFwAIgAsACAAMAAuADkALAAgADAALgAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbABvAG0AaQB0AGUAIAAoAE0AYQBnAG4AZQBzAGkAdQBtACAAYwBhAHIAYgBvAG4AYQB0AGUAKQBcACIALAAgADAALgA5ADUALAAgADAALgAxADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAHkAcABzAHUAbQBcACIALAAgADAALAAgADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGkAbQBlAEQAbwBsAG8AbQBpAHQAZQBHAHkAcABzAHUAbQBDAG8AbgBzAHQAYQBuAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABHAHkAcABzAHUAbQAgAGgAYQBzACAAYgBlAGUAbgAgAGEAZABkAGUAZAAgAHcAaQB0AGgAIABwAGwAYQBjAGUAaABvAGwAZABlAHIAIAB2AGEAbAB1AGUAcwAgAG8AZgAgADAAIABmAG8AcgAgAFAAIABhAG4AZAAgAEUARgAuAFwAIgApACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABjAHIAbwBwACAAYQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACwAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAGMAIABhAG4AZAAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABwAFwAbgBFAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGMAfQBcAFwAcwB1AG0AXwB7AHAAfQAoAE0AXwB7AGwAZQBhAGMAaAAsAGMAcAB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AGwAZQBhAGMAaAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AbABlAGEAYwBoAGMAcAAgAD0AIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABjACAAbwByACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIABwACAAKABrAGcAIABOACkAXABuAEUARgBsAGUAYQBjAGgAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAbgBwACAAPQAgAFAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBsAGUAYQBjAGgAYwBwACwAIABFAEYAbABlAGEAYwBoACwAIABDAGcATgAyAE8ALABcAG4AIAAgACAAIABNAGwAZQBhAGMAaABjAHAAIAAqACAARQBGAGwAZQBhAGMAaAAgACoAIABDAGcATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYwByAG8AcAAgAGEAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMwAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAF8AewBjAH0AXABcAHMAdQBtAF8AewBwAH0AKABNAF8AewBsAGUAYQBjAGgALABjAHAAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBnAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBsAGUAYQBjAGgAYwBwAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABjACAAbwByACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAIABwACAAKABrAGcAIABOACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAZwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgBNAGwAZQBhAGMAaABjAHAAXABuAGsAZwAgAE4AXABuAE0AXwB7AGwAZQBhAGMAaAAsAGMAcAB9AD0ATQBfAHsAYwBwAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAVwBFAFQAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBMAEUAQQBDAEgAXABuAE0AYwBwACAAPQAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABwACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgACgAawBnACAATgApAFwAbgBGAHIAYQBjAFcARQBUAGoAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAEYAcgBhAGMATABFAEEAQwBIACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAbgBwACAAPQAgAFAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcAG4AaQByACAAPQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AYwBwACwAIABGAHIAYQBjAFcARQBUAHoAaQByACwAIABGAHIAYQBjAEwARQBBAEMASAAsAFwAbgAgACAAIAAgAE0AYwBwACAAKgAgAEYAcgBhAGMAVwBFAFQAegBpAHIAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGwAZQBhAGMAaABjAHAAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGwAZQBhAGMAaAAsAGMAcAB9AD0ATQBfAHsAYwBwAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMAVwBFAFQAXwB7AHoALABpAHIAfQBcAFwAdABpAG0AZQBzACAARgByAGEAYwBMAEUAQQBDAEgAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGMAcABcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABjACAAbwByACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHAAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAKABrAGcAIABOACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAegBpAHIAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAdABoAGUAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACAAegAgAGEAbgBkACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAIABpAHIAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHoAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAaQBuACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQByAFwAIgAsACAAXAAiAEkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABjAHIAaQB0AGUAcgBpAGEAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAIAB6ACAAYQBuAGQAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgAuACAAUgBlAG0AbwB2AGUAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGMAcgBpAHQAZQByAGkAYQAgAGoALgBcACIAKQA7AFwAbgBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIAByAGUAZgBlAHIAZQBuAGMAZQA6AFwAbgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAHMAbwBpAGwAcwA6ACAAQQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgACgAMwAuAEQALgBiAC4AMQApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXABuAEEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAGIAeQAgAGcAcgBhAHoAaQBuAGcAIABhAG4AaQBtAGEAbABzACAAbwBuACAAcABhAHMAdAB1AHIAZQAsAFwAbgByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXABuAEUATgAyAE8AYQBkAFwAbgB0ACAATgAyAE8AXABuAEUATgAyAE8AYQBkACAAPQAgAE0AdgBvAGwAbQAgACoAIABFAEYAYQBkACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAXgAtADMAXABuAE0AdgBvAGwAbQAgADoATQBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAIAA6ACAAawBnACAATgBcAG4ARQBGAGEAZAAgADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBDAGcATgAyAE8AIAA6ACAARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBHAFcAUABcAG4AIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBOADIATwBhAGQALABHAFcAUABOADIATwAsAFwAbgAgACAAIAAgACAAKABFAE4AMgBPAGEAZAAgACoAIABHAFcAUABOADIATwApAFwAbgAgACAAIAApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQB2AG8AbABtACwARQBmAGEAZAAsAEMAZwBOADIATwAsAFwAbgAgACAAIAAgACgATQB2AG8AbABtACAAKgAgAEUAZgBhAGQAIAAqACAAQwBnAE4AMgBPACAAKgAgADEAMABeAC0AMwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAYgB5ACAAZwByAGEAegBpAG4AZwAgAGEAbgBpAG0AYQBsAHMAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwBhAGQAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEALAAgADIAMAAyADMAOgAgADMALgBEAC4AQgBfADQAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AYQBkACAAPQAgAE0AdgBvAGwAbQAgACoAIABFAEYAYQBkACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQB2AG8AbABtAFwAIgAsAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAXAAiACwAXAAiAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBhAGQAXAAiACwAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABhAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuAFwAIgAsAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGcATgAyAE8AXAAiACwAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsAFwAIgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABBAG4AaQBtAGEAbABXAGEAcwB0AGUAXABuAFQAaABlACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAsACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcwBvAGkAbABzAFwAbgBNAHYAbwBsAG0AXABuAGsAZwAgAE4AXABuAE0AdgBvAGwAbQAgAD0AIAAoAE0ATgBqAG0AIAArACAAVQBOAGoAbQAgACsAIABGAE4AagBtACkAIAAqACAARgByAGEAYwBHAEEAUwBNAHMAbwBpAGwAXABuAE0ATgBqAG0AIAA6ACAATQBhAHMAcwAgAG8AZgAgAG0AYQBuAHUAcgBlACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgADoAIABrAGcAIABOAFwAbgBVAE4AagBtACAAOgAgAE0AYQBzAHMAIABvAGYAIAB1AHIAaQBuAGUAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIABmAG8AcgAgAGUAYQBjAGgAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGMAbABhAHMAcwAgADoAIABrAGcAIABOAFwAbgBGAE4AagBtACAAOgAgAE0AYQBzAHMAIABvAGYAIABmAGEAZQBjAGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawAgAGYAbwByACAAZQBhAGMAaAAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAYwBsAGEAcwBzACAAOgAgAGsAZwAgAE4AXABuAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsACAAOgAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABBAG4AaQBtAGEAbABXAGEAcwB0AGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAGoAbQAsACAAVQBOAGoAbQAsACAARgBOAGoAbQAsACAARgByAGEAYwBHAEEAUwBNAHMAbwBpAGwALABcAG4AIAAgACAAIAAoAE0ATgBqAG0AIAArACAAVQBOAGoAbQAgACsAIABGAE4AagBtACkAIAAqACAARgByAGEAYwBHAEEAUwBNAHMAbwBpAGwAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAsACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcwBvAGkAbABzAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQAQQBuAGkAbQBhAGwAVwBhAHMAdABlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAHYAbwBsAG0AXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABBAG4AaQBtAGEAbABXAGEAcwB0AGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQAQQBuAGkAbQBhAGwAVwBhAHMAdABlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEALAAgADIAMAAyADMAOgAgADMALgBEAC4AQgBfADIAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABBAG4AaQBtAGEAbABXAGEAcwB0AGUAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAHYAbwBsAG0AIAA9ACAAKABNAE4AagBtACAAKwAgAFUATgBqAG0AIAArACAARgBOAGoAbQApACAAKgAgAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQAQQBuAGkAbQBhAGwAVwBhAHMAdABlAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AagBtAFwAIgAsAFwAIgBNAGEAcwBzACAAbwBmACAAbQBhAG4AdQByAGUAIABuAGkAdAByAG8AZwBlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgAsAFwAIgBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBVAE4AagBtAFwAIgAsAFwAIgBNAGEAcwBzACAAbwBmACAAdQByAGkAbgBlACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrACAAZgBvAHIAIABlAGEAYwBoACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABjAGwAYQBzAHMAXAAiACwAXAAiAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYATgBqAG0AXAAiACwAXAAiAE0AYQBzAHMAIABvAGYAIABmAGEAZQBjAGEAbAAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawAgAGYAbwByACAAZQBhAGMAaAAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAYwBsAGEAcwBzAFwAIgAsAFwAIgBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbABcACIALABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAXAAiACwAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBcAG4AVABoAGUAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAXABuAE0AdgBvAGwAaQBuAG8AcgBnAGEAbgBpAGMAXABuAGsAZwAgAE4AXABuAE0AdgBvAGwAaQBuAG8AcgBnAGEAbgBpAGMAIAA9ACAATQBOAGYAIAAqACAARgByAGEAYwBHAEEAUwBGAGYAXABuAE0ATgBmACAAOgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgADoAIABrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAEYAZgAgADoAIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AGgAYQB0ACAAdgBvAGwAYQB0AGkAbABpAHMAZQBzACAAOgAgACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAGYALAAgAEYAcgBhAGMARwBBAFMARgBmACwAXABuACAAIAAgACAATQBOAGYAIAAqACAARgByAGEAYwBHAEEAUwBGAGYAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABzAG8AaQBsAHMAXAAiACkAOwBcAG4AXABuAEEAZwBzAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAFwAIgApADsAXABuAFwAbgBBAGcAcwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEEAZwBzAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEALAAgADIAMAAyADMAOgAgADMALgBEAC4AQgBfADEAXAAiACkAOwBcAG4AXABuAEEAZwBzAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwAgAD0AIABNAE4AZgAgACoAIABGAHIAYQBjAEcAQQBTAEYAZgBcACIAKQA7AFwAbgBcAG4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBmAFwAIgAsAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZABcACIALABcACIAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBGAGYAXAAiACwAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAaABhAHQAIAB2AG8AbABhAHQAaQBsAGkAcwBlAHMAXAAiACwAXAAiACgAawBnACAATgBIADMAEyBOACAAKwAgAE4ATwB4ABMgTgApAC8AawBnACAATgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAcgBlAGYAZQByAGUAbgBjAGUAOgBcAG4AQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIABzAG8AaQBsAHMAOgAgAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAUgB1AG4AbwBmAGYAIAAoADMALgBEAC4AYgAuADIAKQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQQBnAFMAbwBpAGwAcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACwAXABuAGkAbgBvAHIAZwBhAG4AaQBjACAAYQBuAGQAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACwAXABuAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQBcAG4ARQBOADIATwBsAGUAYQBjAGgAIAA9ACAATQBsAGUAYQBjAGgAIAAqACAARQBGAGwAZQBhAGMAaAAgACoAIABDAGcATgAyAE8AIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgBNAGwAZQBhAGMAaAAgADoAIABNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABlAGQAIABhAG4AZAAgAHIAdQBuACAAbwBmAGYAIAA6ACAAawBnACAATgBcAG4ARQBGAGwAZQBhAGMAaAAgADoAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBDAGcATgAyAE8AIAA6ACAARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBBAGcAUwBvAGkAbABzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ARwBXAFAAXABuACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUATgAyAE8AbABlAGEAYwBoACwARwBXAFAATgAyAE8ALABcAG4AIAAgACAAIAAgACgARQBOADIATwBsAGUAYQBjAGgAIAAqACAARwBXAFAATgAyAE8AKQBcAG4AIAAgACAAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAGwAZQBhAGMAaAAsAEUARgBsAGUAYQBjAGgALABDAGcATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AbABlAGEAYwBoACAAKgAgAEUARgBsAGUAYQBjAGgAIAAqACAAQwBnAE4AMgBPACAAKgAgADEAMABeAC0AMwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAsAGkAbgBvAHIAZwBhAG4AaQBjACAAYQBuAGQAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsACwAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AbABlAGEAYwBoAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEALAAgADIAMAAyADMAOgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AbABlAGEAYwBoACAAPQAgAE0AbABlAGEAYwBoACAAKgAgAEUARgBsAGUAYQBjAGgAIAAqACAAQwBnAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtACAAMwBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBsAGUAYQBjAGgAXAAiACwAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAdABvACAAbABlAGEAYwBoAGUAZAAgAGEAbgBkACAAcgB1AG4AIABvAGYAZgBcACIALABcACIAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGwAZQBhAGMAaABcACIALABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAXAAiAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAZwBOADIATwBcACIALABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACwAXAAiAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQQBuAGkAbQBhAGwAVwBhAHMAdABlAE4ATABvAHMAdABcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIABmAHIAbwBtACAAbQBhAG4AdQByAGUALAAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXABuAE0AbABlAGEAYwBoAGEAbgBpAG0AYQBsAHcAYQBzAHQAZQA9ACgATQBOAGoAbQArAFUATgBqAG0AKwBGAE4AagBtACkAKgBGAHIAYQBjAFcARQBUACoARgByAGEAYwBMAEUAQQBDAEgAXABuAE0AbABlAGEAYwBoAGEAbgBpAG0AYQBsAHcAYQBzAHQAZQBcAG4AawBnACAATgBcAG4ATQBOAGoAbQAgADoAIABNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAOgAgAGsAZwAgAE4AXABuAFUATgBqAG0AIAA6ACAATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHUAcgBpAG4AZQAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrACAAOgAgAGsAZwAgAE4AXABuAEYATgBqAG0AIAA6ACAATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAA6ACAAawBnACAATgBcAG4ARgByAGEAYwBXAEUAVAAgADoAIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABpAG4AIAB0AGgAZQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlACAAbwBmACAAdABoAGUAIABlAG4AdABpAHQAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAEYAcgBhAGMATABFAEEAQwBIACAAOgAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBBAG4AaQBtAGEAbABXAGEAcwB0AGUATgBMAG8AcwB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBqAG0ALABVAE4AagBtACwARgBOAGoAbQAsAEYAcgBhAGMAVwBFAFQALABGAHIAYQBjAEwARQBBAEMASAAsAFwAbgAgACAAIAAgACgATQBOAGoAbQArAFUATgBqAG0AKwBGAE4AagBtACkAKgBGAHIAYQBjAFcARQBUACoARgByAGEAYwBMAEUAQQBDAEgAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQQBuAGkAbQBhAGwAVwBhAHMAdABlAE4ATABvAHMAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIABmAHIAbwBtACAAbQBhAG4AdQByAGUALAAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBOAEwAbwBzAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbABlAGEAYwBoAGEAbgBpAG0AYQBsAHcAYQBzAHQAZQBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQQBuAGkAbQBhAGwAVwBhAHMAdABlAE4ATABvAHMAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBOAEwAbwBzAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQAsACAAMgAwADIAMwA6ACAAMwAuAEQALgBCAF8ANgBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQQBuAGkAbQBhAGwAVwBhAHMAdABlAE4ATABvAHMAdABfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbABlAGEAYwBoAGEAbgBpAG0AYQBsAHcAYQBzAHQAZQA9ACgATQBOAGoAbQArAFUATgBqAG0AKwBGAE4AagBtACkAKgBGAHIAYQBjAFcARQBUACoARgByAGEAYwBMAEUAQQBDAEgAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBOAEwAbwBzAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATgBqAG0AXAAiACwAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABtAGEAbgB1AHIAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAXAAiACwAXAAiAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFUATgBqAG0AXAAiACwAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIAB1AHIAaQBuAGUAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALABcACIAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBOAGoAbQBcACIALABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAXAAiAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAXAAiACwAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAaQBuACAAdABoAGUAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAG8AZgAgAHQAaABlACAAZQBuAHQAaQB0AHkAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIATgBMAG8AcwB0AFwAbgBNAGwAZQBhAGMAaABpAG4AbwByAGcAYQBuAGkAYwBcAG4ATQBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAIAA9ACAATQAgACoAIABGAHIAYQBjAFcARQBUACAAKgAgAEYAcgBhAGMATABFAEEAQwBIAFwAbgBNACAAOgAgAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAOgAgAGsAZwAgAE4AXABuAEYAcgBhAGMAVwBFAFQAIAA6ACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABpAG4AIAB0AGgAZQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlACAAbwBmACAAdABoAGUAIABlAG4AdABpAHQAeQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAEYAcgBhAGMATABFAEEAQwBIACAAOgAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIATgBMAG8AcwB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ALAAgAEYAcgBhAGMAVwBFAFQALAAgAEYAcgBhAGMATABFAEEAQwBIACwAXABuACAAIAAgACAATQAgACoAIABGAHIAYQBjAFcARQBUACAAKgAgAEYAcgBhAGMATABFAEEAQwBIAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIATgBMAG8AcwB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAGYAcgBvAG0AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIATgBMAG8AcwB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBOAEwAbwBzAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQAsACAAMgAwADIAMwA6ACAAMwAuAEQALgBCAF8ANQBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBOAEwAbwBzAHQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGwAZQBhAGMAaABpAG4AbwByAGcAYQBuAGkAYwAgAD0AIABNACAAKgAgAEYAcgBhAGMAVwBFAFQAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIATgBMAG8AcwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFwAIgAsAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwBcACIALABcACIAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBXAEUAVABcACIALABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABpAG4AIAB0AGgAZQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlACAAbwBmACAAdABoAGUAIABlAG4AdABpAHQAeQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQwByAG8AcABSAGUAcwBpAGQAdQBlAE4ATABvAHMAdABcAG4ATQBsAGUAYQBjAGgAcgBlAHMAaQBkAHUAZQBcAG4ATQBsAGUAYQBjAGgAcgBlAHMAaQBkAHUAZQAgAD0AIABNACAAKgAgAEYAcgBhAGMAVwBFAFQAIAAqACAARgByAGEAYwBMAEUAQQBDAEgAXABuAE0AIAA6ACAATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgADoAIABrAGcAIABOAFwAbgBGAHIAYQBjAFcARQBUACAAOgAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAaQBuACAAdABoAGUAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAG8AZgAgAHQAaABlACAAZQBuAHQAaQB0AHkAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBGAHIAYQBjAEwARQBBAEMASAAgADoAIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUATgBMAG8AcwB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ALAAgAEYAcgBhAGMAVwBFAFQALAAgAEYAcgBhAGMATABFAEEAQwBIACwAXABuACAAIAAgACAATQAgACoAIABGAHIAYQBjAFcARQBUACAAKgAgAEYAcgBhAGMATABFAEEAQwBIAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBOAEwAbwBzAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAZgByAG8AbQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQwByAG8AcABSAGUAcwBpAGQAdQBlAE4ATABvAHMAdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBsAGUAYQBjAGgAcgBlAHMAaQBkAHUAZQBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQwByAG8AcABSAGUAcwBpAGQAdQBlAE4ATABvAHMAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBOAEwAbwBzAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQAsACAAMgAwADIAMwA6ACAAMwAuAEQALgBCAF8AOABcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQwByAG8AcABSAGUAcwBpAGQAdQBlAE4ATABvAHMAdABfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbABlAGEAYwBoAHIAZQBzAGkAZAB1AGUAIAA9ACAATQAgACoAIABGAHIAYQBjAFcARQBUACAAKgAgAEYAcgBhAGMATABFAEEAQwBIAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUATgBMAG8AcwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFwAIgAsAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgAsAFwAIgBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAFcARQBUAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGkAbgAgAHQAaABlACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAIABvAGYAIAB0AGgAZQAgAGUAbgB0AGkAdAB5AFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAHIAZQBmAGUAcgBlAG4AYwBlADoAXABuAFUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAYgB5ACAAZwByAGEAegBpAG4AZwAgAGEAbgBpAG0AYQBsAHMAIAAoADMALgBEAC4AYQAuADMAKQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFUAcgBpAG4AZQBBAG4AZABEAHUAbgBnAEQAZQBwAG8AcwBpAHQAZQBkAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAGIAeQAgAGcAcgBhAHoAaQBuAGcAIABhAG4AaQBtAGEAbABzACAAbwBuACAAcABhAHMAdAB1AHIAZQAsAFwAbgByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXABuAEUATgAyAE8AZABpAHIAXABuAHQAIABOADIATwBcAG4ARQBOADIATwBkAGkAcgAgAD0AIAAoACgAQQBGAGoAbQA9ADEANAAgACoAIABFAEYAUABSAFAAIAAqACAAQwBnAE4AMgBPACkAIAArACAAKABBAFUAagBtAD0AMQA0ACAAKgAgAEUARgBQAFIAUAAgACoAIABDAGcATgAyAE8AKQApACAAKgAgADEAMABeAC0AMwBcAG4AQQBGAGoAbQAgADoAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrACAAOgAgAGsAZwAgAE4AXABuAEEAVQBqAG0AIAA6ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHUAcgBpAG4AZQAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrACAAOgAgAGsAZwAgAE4AXABuAEUARgBQAFIAUAAgADoAIABkAGkAcgBlAGMAdAAgAE4AMgBPACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBDAGcATgAyAE8AIAA6ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAFUAcgBpAG4AZQBBAG4AZABEAHUAbgBnAEQAZQBwAG8AcwBpAHQAZQBkAF8ARwBXAFAAXABuACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUATgAyAE8AZABpAHIALABHAFcAUABOADIATwAsAFwAbgAgACAAIAAgACAAKABFAE4AMgBPAGQAaQByACAAKgAgAEcAVwBQAE4AMgBPACkAXABuACAAIAAgACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBVAHIAaQBuAGUAQQBuAGQARAB1AG4AZwBEAGUAcABvAHMAaQB0AGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABBAEYAagBtACwAIABBAFUAagBtACwAIABFAEYAUABSAFAALAAgAEMAZwBOADIATwAsAFwAbgAgACAAIAAgACgAKABBAEYAagBtACAAKgAgAEUARgBQAFIAUAAgACoAIABDAGcATgAyAE8AKQAgACsAIAAoAEEAVQBqAG0AIAAqACAARQBGAFAAUgBQACAAKgAgAEMAZwBOADIATwApACkAIAAqACAAMQAwAF4ALQAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBVAHIAaQBuAGUAQQBuAGQARAB1AG4AZwBEAGUAcABvAHMAaQB0AGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABiAHkAIABnAHIAYQB6AGkAbgBnACAAYQBuAGkAbQBhAGwAcwAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAFUAcgBpAG4AZQBBAG4AZABEAHUAbgBnAEQAZQBwAG8AcwBpAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPAGQAaQByAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8AVQByAGkAbgBlAEEAbgBkAEQAdQBuAGcARABlAHAAbwBzAGkAdABlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBVAHIAaQBuAGUAQQBuAGQARAB1AG4AZwBEAGUAcABvAHMAaQB0AGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxACwAIAAyADAAMgAzADoAIAAzAC4ARAAuAGEALgAzAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8AVQByAGkAbgBlAEEAbgBkAEQAdQBuAGcARABlAHAAbwBzAGkAdABlAGQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPAGQAaQByACAAPQAgACgAKABBAEYAagBtAD0AMQA0ACAAKgAgAEUARgBQAFIAUAAgACoAIABDAGcATgAyAE8AKQAgACsAIAAoAEEAVQBqAG0APQAxADQAIAAqACAARQBGAFAAUgBQACAAKgAgAEMAZwBOADIATwApACkAIAAqACAAMQAwAF4ALQAzAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8AVQByAGkAbgBlAEEAbgBkAEQAdQBuAGcARABlAHAAbwBzAGkAdABlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEARgBqAG0AXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABOACAAaQBuACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsAFwAIgBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAFUAagBtAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAHUAcgBpAG4AZQAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsAFwAIgBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAUABSAFAAXAAiACwAXAAiAGQAaQByAGUAYwB0ACAATgAyAE8AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGcATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsAFwAIgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAbgBFAEMASAA0AFwAbgB0ACAAQwBIADQAXABuAEUAXwB7AEMASAA0AH0APQBcAG4AXABcAHMAdQBtAF8AewBjAH0AKABNAF8AewBiAHUAcgBuACwAYwB9AFwAXAB0AGkAbQBlAHMAIABDAEMAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AYgB1AHIAbgBjACAAPQAgAG0AYQBzAHMAIABvAGYAIAByAGUAcwBpAGQAdQBlACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGsAZwApAFwAbgBDAEMAYwAgAD0AIABjAGEAcgBiAG8AbgAgAG0AYQBzAHMAIABmAHIAYQBjAHQAaQBvAG4AIABpAG4AIAB0AGgAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBFAEYAQwBIADQAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAAoAGsAZwAgAEMASAA0AC8AawBnACAAQwBIADQAIABiAHUAcgBuAHQAKQBcAG4AQwBDAEgANAAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABtAGUAdABoAGEAbgBlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AYgB1AHIAbgBjACwAIABDAEMAYwAsACAARQBGAEMASAA0ACwAIABDAF8AQwBIADQALABcAG4AIAAgACAAIABNAGIAdQByAG4AYwAgACoAIABDAEMAYwAgACoAIABFAEYAQwBIADQAIAAqACAAQwBfAEMASAA0ACAAKgAgADEAMABeACgALQAzACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXwB7AGMAfQAoAE0AXwB7AGIAdQByAG4ALABjAH0AXABcAHQAaQBtAGUAcwAgAEMAQwBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABFAEYAXwB7AEMASAA0AH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AEMASAA0AH0AXABcAHQAaQBtAGUAcwAgADEAMABeAHsALQAzAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYgB1AHIAbgBjAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBDAGMAXAAiACwAXAAiAGMAYQByAGIAbwBuACAAbQBhAHMAcwAgAGYAcgBhAGMAdABpAG8AbgAgAGkAbgAgAHQAaABlACAAcgBlAHMAaQBkAHUAZQBzACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBDAEgANABcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG0AZQB0AGgAYQBuAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAAoAGsAZwAgAEMASAA0AC8AawBnACAAQwBIADQAIABiAHUAcgBuAHQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBDAEgANABcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzAFwAbgBFAE4AMgBPAFwAbgB0ACAATgAyAE8AXABuAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGMAfQAoAE0AXwB7AGIAdQByAG4ALABjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXABuAE0AYgB1AHIAbgBjACAAPQAgAG0AYQBzAHMAIABvAGYAIAByAGUAcwBpAGQAdQBlACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGsAZwApAFwAbgBOAEMAQQBHAGMAIAA9ACAAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAGkAbgAgAHQAaABlACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAEUARgBOADIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGYAcgBvAG0AIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgACgAawBnACAATgAyAE8ALwBrAGcAIABOADIATwAgAGIAdQByAG4AdAApAFwAbgBDAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AYgB1AHIAbgBjACwAIABOAEMAQQBHAGMALAAgAEUARgBOADIATwAsACAAQwBOADIATwAsAFwAbgAgACAAIAAgAE0AYgB1AHIAbgBjACAAKgAgAE4AQwBBAEcAYwAgACoAIABFAEYATgAyAE8AIAAqACAAQwBOADIATwAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AE4AMgBPAH0APQBcAFwAcwB1AG0AXwB7AGMAfQAoAE0AXwB7AGIAdQByAG4ALABjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBiAHUAcgBuAGMAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIAByAGUAcwBpAGQAdQBlACAAYgB1AHIAbgB0ACAAZgBvAHIAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGsAZwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAQQBHAGMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIAB0AGgAZQAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYATgAyAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgByAG8AbQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAKABrAGcAIABOADIATwAvAGsAZwAgAE4AMgBPACAAYgB1AHIAbgB0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AFwAbgBNAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjACAAYgB1AHIAbgB0AFwAbgBNAGIAdQByAG4AYwBcAG4AawBnAFwAbgBNAF8AewBiAHUAcgBuACwAYwB9AD0AUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcAYwB9AFwAXAB0AGkAbQBlAHMAIABTAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABaAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEYAXwB7AGMAfQBcAG4AUABjACAAPQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACkAXABuAFIAQQBHAGMAIAA9ACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAC8AawBnACAAYwByAG8AcAApAFwAbgBTAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAcgBlAHMAaQBkAHUAZQBzACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAcgBlAG0AYQBpAG4AaQBuAGcAIABhAHQAIABiAHUAcgBuAGkAbgBnACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAEQATQBjACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAIABkAHIAeQAgAHcAZQBpAGcAaAB0AC8AawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAKQBcAG4AWgBjACAAPQAgAGIAdQByAG4AaQBuAGcAIABlAGYAZgBpAGMAaQBlAG4AYwB5ACAAKAByAGEAdABpAG8AIABvAGYAIABmAHUAZQBsACAAYgB1AHIAbgB0ACAAdABvACAAZgB1AGUAbAAgAGwAbwBhAGQAKQAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBGAGMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAGMALAAgAFIAQQBHAGMALAAgAFMAYwAsACAARABNAGMALAAgAFoAYwAsACAARgBjACwAXABuACAAIAAgACAAUABjACAAKgAgAFIAQQBHAGMAIAAqACAAUwBjACAAKgAgAEQATQBjACAAKgAgAFoAYwAgACoAIABGAGMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIABiAHUAcgBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYgB1AHIAbgBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgA0AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMwApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAYgB1AHIAbgAsAGMAfQA9AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAAUwBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAWgBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABGAF8AewBjAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABjAFwAIgAsAFwAIgBhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGsAZwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAEEARwBjAFwAIgAsAFwAIgByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUALwBrAGcAIABjAHIAbwBwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAYwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAcgBlAHMAaQBkAHUAZQBzACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAcgBlAG0AYQBpAG4AaQBuAGcAIABhAHQAIABiAHUAcgBuAGkAbgBnACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQATQBjAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACAAZAByAHkAIAB3AGUAaQBnAGgAdAAvAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFoAYwBcACIALABcACIAYgB1AHIAbgBpAG4AZwAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAIAAoAHIAYQB0AGkAbwAgAG8AZgAgAGYAdQBlAGwAIABiAHUAcgBuAHQAIAB0AG8AIABmAHUAZQBsACAAbABvAGEAZAApACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAYwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAB0AGgAYQB0ACAAaQBzACAAYgB1AHIAbgB0ACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEcAZQB0AEYAcgBhAGMAVwBFAFQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBMAG8AbwBrAHUAcAAsAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQALAAgAFwAbgAgACAAIAAgACAAIAAgACAAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ATABvAG8AawB1AHAALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQATABvAG8AawB1AHAAXABuACAAIAAgACAAIAAgACAAIAApACwAXABuACAAIAAgACAAIAAgACAAIABJAEYAKABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACAAKwAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABcAHUAMAAwADMAZQAwACwAIAAxACwAIAAwACkAXABuACAAIAAgACAAKQApADsAXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAHIAbwBwAFQAeQBwAGUALAAgAEMAcgBvAHAAVAB5AHAAZQBBAHIAcgBhAHkALAAgAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AQQByAHIAYQB5ACwAXABuACAAIAAgACAAMQAvACgAMQArAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQApACkAXABuACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAAsAFwAbgAgACAAIAAgACgAMQAtAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACkALwBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeABcAG4AKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEYAcgBhAGMAdABpAG8AbgBSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAG8AdABhAGwAUgBlAHMAaQBkAHUAZQAsACAAQQBtAG8AdQBuAHQAUgBlAG0AbwB2AGUAZAAsAFwAbgAgACAAIAAgACgAQQBtAG8AdQBuAHQAUgBlAG0AbwB2AGUAZAAqADEAMABeADMAKQAvACgAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUAKgAxADAAXgAzACkAXABuACkAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIABGAG8AcgAgAFMAdwBpAG4AZQBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBcAG4AVgBTAGoAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAHcAaQBuAGUAIAAtACAAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAAoAFYAUwBqACkAIAAtACAAMgAwADIAMAAgAHQAbwAgADIAMAAyADQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA2AC4AMQA6ACAAUwB3AGkAbgBlACAALQAgAEkAbgB0AGEAawBlACAAYQBuAGQAIABtAGEAbgB1AHIAZQAgAGMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzACAAZABlAHIAaQB2AGUAZAAgAGYAcgBvAG0AIABQAGkAZwBCAGEAbABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAATwBuAGwAeQAgAHUAcwBlAHMAIABkAGEAdABhACAAZgBvAHIAIAAyADAAMgAwAC0AMgAwADIANAAuACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcAUwB1AGMAawBlAHIAcwBcAHUAMAAwADIANwAsACAAXAB1ADAAMAAyADcAVwBlAGEAbgBlAHIAcwBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcARwByAG8AdwBlAHIAcwBcAHUAMAAwADIANwAgAGMAbABhAHMAcwBlAHMAIAB3AGgAaQBjAGgAIABoAGEAdgBlACAAdABoAGUAIABzAGEAbQBlACAAdgBhAGwAdQBlAHMAIABhAHMAIABcAHUAMAAwADIANwBTAGwAYQB1AGcAaAB0AGUAcgAgAHAAaQBnAHMAXAB1ADAAMAAyADcALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAYQBzAHMAXAAiACwAIABcACIAVgBTAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAbwBhAHIAcwBcACIALAAgADAALgA0ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAHcAcwBcACIALAAgADAALgA0ADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBpAGwAdABzAFwAIgAsACAAMAAuADUANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAYQB1AGcAaAB0AGUAcgAgAHAAaQBnAHMAXAAiACwAIAAwAC4AMwA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBjAGsAZQByAHMAXAAiACwAIAAwAC4AMwA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAZQBhAG4AZQByAHMAXAAiACwAIAAwAC4AMwA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAcgBvAHcAZQByAHMAXAAiACwAIAAwAC4AMwA5AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBCADAAXABuAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABwAGUAcgAgAGsAaQBsAG8AZwByAGEAbQAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAMABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAbQAzACAAQwBIADQAIAAvACAAawBnACAAVgBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBQAEMAQwAgACgAMgAwADEAOQApACwAIABDAGgAYQBwAHQAZQByACAAMQAwACAAWwA0AF0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMQA5ACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBNAFMAXwBNAEMARgBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADYALgA0ADoAIABTAHcAaQBuAGUAIAAtACAATQBDAEYAcwAgACgATQBDAEYAaQBtACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgAGEAbgBkACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0ALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBNAFMAXwBNAEMARgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADQAOgAgAFMAdwBpAG4AZQAgABMgIABNAEMARgBzACAAKABNAEMARgBpAG0AKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAYwBvAGwAdQBtAG4AcwAgAGYAbwByACAAQQBDAFQALAAgAHMAcABsAGkAdAAgAFEATABEACAAYQBuAGQAIABOAFQALgAgAEEAZABkAGUAZAAgAGUAeAB0AHIAYQAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBNAFMAXwBNAEMARgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADEAMAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIABcACIATgBUAFwAIgAsACAAXAAiAFMAQQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBXAEEAXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHUAdABkAG8AbwByACAAKABEAHIAeQAgAGwAbwB0ACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgBcACIALAAgADAALgAwADQALAAgADAALgAwADQALAAgADAALgAwADQALAAgADAALgAwADQALAAgADAALgAwADQALAAgADAALgAwADQALAAgADAALgAwADQALAAgADAALgAwADQALAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABvAGMAawBwAGkAbABlACAAKABTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACkAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBmAGYAbAB1AGUAbgB0ACAAcABvAG4AZAAgACgAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACkAXAAiACwAIAAwAC4ANwA1ACwAIAAwAC4ANwA1ACwAIAAwAC4ANwA4ACwAIAAwAC4ANwA4ACwAIAAwAC4ANwA1ACwAIAAwAC4ANwAwACwAIAAwAC4ANwA0ACwAIAAwAC4ANwA2ACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABlAHIAIAAvACAAQwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAFwAIgAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAaABvAHIAdAAgAEgAUgBUACAAdABhAG4AawAgAHMAdABvAHIAYQBnAGUAIABcAHUAMAAwADMAYwAgADEAIABtAG8AbgB0AGgAIAAoAHAAaQB0ACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBcAG4ANAAuADUAIABTAHcAaQBuAGUAIABGAGkAZwB1AHIAZQAgADQALgA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFMAdwBpAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUAIABTAHcAaQBuAGUAIABGAGkAZwB1AHIAZQAgADQALgA4AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG4AdgBlAG4AdABpAG8AbgBhAGwAIABoAG8AdQBzAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAIABoAG8AdQBzAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHUAdABkAG8AbwByAC8AZgByAGUAZQAgAHIAYQBuAGcAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUAOgAgAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADUALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgABQgIABNAGEAbgB1AHIAZQAgAE0AZQB0AGgAYQBuAGUAIABTAHcAaQBuAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcAG4ARQBDAEgANABcAG4AdAAgAEMASAA0AFwAbgB7AEUAfQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBfAHsAagB9ACgARABfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBtAGoAfQBcAFwAdABpAG0AZQBzACAATgBfAHsAagB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAbgBEAGoAIAA9ACAAbABlAG4AZwB0AGgAIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAG8AZgAgAHMAdwBpAG4AZQAgADoAIABkAGEAeQBzAFwAbgBNAG0AagAgAD0AIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIAA6ACAAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE4AagAgAD0AIABuAHUAbQBiAGUAcgBzACAAbwBmACAAcwB3AGkAbgBlACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgADoAIABoAGUAYQBkAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABEAGoALAAgAE0AbQBqACwAIABOAGoALABcAG4AIAAgACAAIABEAGoAIAAqACAATQBtAGoAIAAqACAATgBqACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB7AEUAfQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBfAHsAagB9ACgARABfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBtAGoAfQBcAFwAdABpAG0AZQBzACAATgBfAHsAagB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABqAFwAIgAsAFwAIgBsAGUAbgBnAHQAaAAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAbwBmACAAcwB3AGkAbgBlACAAOgAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbQBqAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAHcAaQBuAGUAIABjAGwAYQBzAHMAIAA6ACAAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AagBcACIALABcACIAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAA6ACAAaABlAGEAZABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBcAG4ATQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAdABoAGUAIABtAGEAbgB1AHIAZQAgAG8AZgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABvAGYAIABzAHcAaQBuAGUAXABuAE0AbQBqAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAbQBqAH0APQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQBNAF8AewBqAG0AVAB9AFwAbgBNAGoAbQBUACAAPQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAcABlAHIAIABjAGwAYQBzAHMALAAgAE0ATQBTACwAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAOgAgAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AagBtAFQALABcAG4AIAAgACAAIABTAFUATQAoAE0AagBtAFQAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AagBtAFQAMQAsACAATQBqAG0AVAAyACwAXABuACAAIAAgACAAIABTAFUATQAoAE0AagBtAFQAMQAsACAATQBqAG0AVAAyACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAdABoAGUAIABtAGEAbgB1AHIAZQAgAG8AZgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABvAGYAIABzAHcAaQBuAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG0AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AG0AagB9AD0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0ATQBfAHsAagBtAFQAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBqAG0AVABcACIALABcACIAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABwAGUAcgAgAGMAbABhAHMAcwAsACAATQBNAFMALAAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAA6ACAAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABTAHAAbABpAHQAIAB2AGEAcgBpAGEAYgBsAGUAIABNAGoAbQAgAGkAbgB0AG8AIABNAGoAbQBUADEAIABhAG4AZAAgAE0AagBtAFQAMgAgAGYAbwByACAAcwB0AGEAZwBlACAAMQAgAGEAbgBkACAAMgAgAE0ATQBTAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAbgBNAGkAagBtAFQAMQBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGkAagBtACwAVAA9ADEAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABGAFYAUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcAG4AVgBTAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABzAHcAaQBuAGUAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ARgBWAFMAagBtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBNAEMARgBpAG0AIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AGUAIAB6AG8AbgBlACAAYQBuAGQAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAEIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAagAsACAARgBWAFMAagBtAFQAMQAsACAATQBDAEYAaQBtACwAIABCAE8ALAAgAHIAaABvACwAXABuACAAIAAgACAAVgBTAGoAIAAqACAARgBWAFMAagBtAFQAMQAgACoAIABNAEMARgBpAG0AIAAqACAAQgBPACAAKgAgAHIAaABvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBpAGoAbQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGkAagBtACwAVAA9ADEAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABGAFYAUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABzAHcAaQBuAGUAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBWAFMAagBtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAaQBtAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAHoAbwBuAGUAIABhAG4AZAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAbgBGAFYAUwBqAG0AVAAxAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAEYAVgBTAF8AewBqAG0ALABUAD0AMQB9AD0ATQBNAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBTAFMAXwB7AG0AfQApAFwAbgBNAE0AUwBqAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAdABvACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwAgAGYAbwByACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAHAAcgBpAG8AcgAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAZQBwAGEAcgBhAHQAaQBvAG4AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBTAFMAbQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAGoAbQBUADEALAAgAFMAUwBtACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAcwBzAG0ALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFMAUwBtACkALAAgAFMAUwBtACwAIAAwACkALABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtAFQAMQAgACoAIAAoADEAIAAtACAAcwBzAG0AKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAVgBTAGoAbQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFYAUwBfAHsAagBtACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0AUwBTAF8AewBtAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBqAG0AVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAIABmAG8AcgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABwAHIAaQBvAHIAIAB0AG8AIABzAG8AbABpAGQAIABzAGUAcABhAHIAYQB0AGkAbwBuACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBTAG0AXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcwBlAHAAYQByAGEAdABlAGQAIAB0AG8AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABBAGQAZABlAGQAIABjAGgAZQBjAGsAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAXAB1ADAAMAAyADcATgAvAEEAXAB1ADAAMAAyADcAIAB2AGEAbAB1AGUAIAB0AG8AIAB6AGUAcgBvAC4AXAAiACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABpAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAbgBGAFYAUwBqAG0ANABUADEAXABuAGYAcgBhAGMAdABpAG8AbgBcAG4ARgBWAFMAXwB7AGoALABtAD0ANAAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagAsAG0APQA0ACwAVAA9ADEAfQArACgATQBNAFMAXwB7AGoALABtAD0AMQAsADcALAA5ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAAUwBTAF8AewBtAH0AKQBcAG4ATQBNAFMAagBtADQAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0ATQBTAGoAbQAxADcAOQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABNAE0AUwAgADEALAAgADcALAAgAGEAbgBkACAAOQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAFMAUwBtACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcwBlAHAAYQByAGEAdABlAGQAIAB0AG8AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAGoAbQA0AFQAMQAsACAATQBNAFMAagBtADEANwA5AFQAMQAsACAAUwBTAG0ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIABNAE0AUwBqAG0ANABUADEALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAE0ATQBTAGoAbQA0AFQAMQApACwAIABNAE0AUwBqAG0ANABUADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABNAE0AUwBqAG0AMQA3ADkAVAAxACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABNAE0AUwBqAG0AMQA3ADkAVAAxACkALAAgAE0ATQBTAGoAbQAxADcAOQBUADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABTAFMAbQAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAUwBTAG0AKQAsACAAUwBTAG0ALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABNAE0AUwBqAG0ANABUADEAIAArACAAKABNAE0AUwBqAG0AMQA3ADkAVAAxACAAKgAgAFMAUwBtACkAXABuACAAIAAgACAAKQBcAG4AIAAgACAAIABcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATQBTAGoAbQA0AFQAMQAsAFwAbgAgACAAIAAgAE0ATQBTAGoAbQBUADEAXwAxACwAIABNAE0AUwBqAG0AVAAxAF8AMgAsACAATQBNAFMAagBtAFQAMQBfADMALAAgAE0ATQBTAGoAbQBUADEAXwA0ACwAIABNAE0AUwBqAG0AVAAxAF8ANQAsAFwAbgAgACAAIAAgAFMAUwBqAG0AVAAxAF8AMQAsACAAUwBTAGoAbQBUADEAXwAyACwAIABTAFMAagBtAFQAMQBfADMALAAgAFMAUwBqAG0AVAAxAF8ANAAsACAAUwBTAGoAbQBUADEAXwA1ACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtADQAVAAxACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABNAE0AUwBqAG0ANABUADEAKQAsACAATQBNAFMAagBtADQAVAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtAFQAMQBfADEALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAE0ATQBTAGoAbQBUADEAXwAxACkALAAgAE0ATQBTAGoAbQBUADEAXwAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtAFQAMQBfADIALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAE0ATQBTAGoAbQBUADEAXwAyACkALAAgAE0ATQBTAGoAbQBUADEAXwAyACwAIAAwACkALABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtAFQAMQBfADMALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAE0ATQBTAGoAbQBUADEAXwAzACkALAAgAE0ATQBTAGoAbQBUADEAXwAzACwAIAAwACkALABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtAFQAMQBfADQALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAE0ATQBTAGoAbQBUADEAXwA0ACkALAAgAE0ATQBTAGoAbQBUADEAXwA0ACwAIAAwACkALABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtAFQAMQBfADUALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAE0ATQBTAGoAbQBUADEAXwA1ACkALAAgAE0ATQBTAGoAbQBUADEAXwA1ACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAUwBTAGoAbQBUADEAXwAxACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABTAFMAagBtAFQAMQBfADEAKQAsACAAUwBTAGoAbQBUADEAXwAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAUwBTAGoAbQBUADEAXwAyACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABTAFMAagBtAFQAMQBfADIAKQAsACAAUwBTAGoAbQBUADEAXwAyACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAUwBTAGoAbQBUADEAXwAzACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABTAFMAagBtAFQAMQBfADMAKQAsACAAUwBTAGoAbQBUADEAXwAzACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAUwBTAGoAbQBUADEAXwA0ACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABTAFMAagBtAFQAMQBfADQAKQAsACAAUwBTAGoAbQBUADEAXwA0ACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAUwBTAGoAbQBUADEAXwA1ACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABTAFMAagBtAFQAMQBfADUAKQAsACAAUwBTAGoAbQBUADEAXwA1ACwAIAAwACkALABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtADQAVAAxACAAKwAgAFwAbgAgACAAIAAgACAAIAAoAE0ATQBTAGoAbQBUADEAXwAxACAAKgAgAFMAUwBqAG0AVAAxAF8AMQApACAAKwAgAFwAbgAgACAAIAAgACAAIAAoAE0ATQBTAGoAbQBUADEAXwAyACAAKgAgAFMAUwBqAG0AVAAxAF8AMgApACAAKwAgAFwAbgAgACAAIAAgACAAIAAoAE0ATQBTAGoAbQBUADEAXwAzACAAKgAgAFMAUwBqAG0AVAAxAF8AMwApACAAKwBcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8ANAAgACoAIABTAFMAagBtAFQAMQBfADQAKQAgACsAXABuACAAIAAgACAAIAAgACgATQBNAFMAagBtAFQAMQBfADUAIAAqACAAUwBTAGoAbQBUADEAXwA1ACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFYAUwBqAG0ANABUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBWAFMAXwB7AGoALABtAD0ANAAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagAsAG0APQA0ACwAVAA9ADEAfQArACgATQBNAFMAXwB7AGoALABtAD0AMQAsADcALAA5ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAAUwBTAF8AewBtAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFYAUwBfAHsAagAsAG0APQA0ACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9ACsAKABNAE0AUwBfAHsAagAsAG0APQAxACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAAUwBTAF8AewBtAD0AMQAsAFQAPQAxAH0AKQArACgATQBNAFMAXwB7AGoALABtAD0ANwAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQA9ADcALABUAD0AMQB9ACkAKwAoAE0ATQBTAF8AewBqACwAbQA9ADkALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0APQA5ACwAVAA9ADEAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBqAG0ANABUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAGoAbQAxADcAOQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAATQBNAFMAIAAxACwAIAA3ACwAIABhAG4AZAAgADkAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAFMAbQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABTAHAAbABpAHQAIABlAHEAdQBhAHQAaQBvAG4AIABmAG8AcgAgAE0ATQBTAG0APQAxACwANwAsADkAIABpAG4AdABvACAAcwBlAHAAYQByAGEAdABlACAAaQB0AGUAbQBzACAAdABvACAAYQBsAGwAbwB3ACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AXAAiACkAOwBcAG4AIAAgAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAZQBhAGMAaAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAbgBNAGkAagBtAFQAMgBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGkAagBtACwAVAA9ADIAfQA9AFYAUwBUAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcAG4AVgBTAFQAagBtAFQAMgAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAE0ATQBTAGoAbQBUADIAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAGkAbQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAHoAbwBuAGUAIABhAG4AZAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgBpACAAPQAgAHMAdABhAHQAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFYAUwBUAGoAbQBUADIALAAgAEIATwAsACAATQBNAFMAagBtAFQAMgAsACAATQBDAEYAaQBtACwAIAByAGgAbwAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgAFYAUwBUAGoAbQBUADIALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFYAUwBUAGoAbQBUADIAKQAsACAAVgBTAFQAagBtAFQAMgAsACAAMAApACwAXABuACAAIAAgACAAIAAgAE0ATQBTAGoAbQBUADIALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAE0ATQBTAGoAbQBUADIAKQAsACAATQBNAFMAagBtAFQAMgAsACAAMAApACwAXABuACAAIAAgACAAIAAgAFYAUwBUAGoAbQBUADIAIAAqACAAQgBPACAAKgAgAE0ATQBTAGoAbQBUADIAIAAqACAATQBDAEYAaQBtACAAKgAgAHIAaABvAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAGUAYQBjAGgAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBpAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADYAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGkAagBtACwAVAA9ADIAfQA9AFYAUwBUAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAVABqAG0AVAAyAFwAIgAsAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBqAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAaQBtAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAHoAbwBuAGUAIABhAG4AZAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAcwB0AGEAdABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAFwAbgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAbgBWAFMAVABpAGoAbQBUADIAXABuAGsAZwAgAFYAUwBcAG4AVgBTAFQAXwB7AGkAagBtACwAVAA9ADIAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABGAFYAUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAFYAUwBMAF8AewBtACwAVAA9ADEAfQApAFwAbgBWAFMAagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBGAFYAUwBqAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAFYAUwBMAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAagAsACAARgBWAFMAagBtAFQAMQAsACAAVgBTAEwAbQBUADEALABcAG4AIAAgACAAIABWAFMAagAgACoAIABGAFYAUwBqAG0AVAAxACAAKgAgACgAMQAgAC0AIABWAFMATABtAFQAMQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAVABpAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAVgBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADcAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAFQAXwB7AGkAagBtACwAVAA9ADIAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABGAFYAUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAFYAUwBMAF8AewBtACwAVAA9ADEAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABzAHcAaQBuAGUAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBWAFMAagBtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAEwAbQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5ACIALAAiAHQAZQB4AHQAIgA6ACIALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANwAuADEAOgAgAFAAbwB1AGwAdAByAHkAIAAtACAARABpAGUAdAAgAHAAcgBvAHAAZQByAHQAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAbwB1AGwAdAByAHkAIAAtACAARABpAGUAdAAgAHAAcgBvAHAAZQByAHQAaQBlAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANwAuADEAOgAgAFAAbwB1AGwAdAByAHkAIAAtACAARABpAGUAdAAgAHAAcgBvAHAAZQByAHQAaQBlAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA1ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAHUAdAByAGkAZQBuAHQAIABhAG4AYQBsAHkAcwBpAHMAXAAiACwAIABcACIATABhAHkAZQByAHMAXAAiACwAIABcACIATQBlAGEAdAAgAGMAaABpAGMAawBlAG4AIABnAHIAbwB3AGUAcgBzAFwAIgAsACAAXAAiAE0AZQBhAHQAIABjAGgAaQBjAGsAZQBuACAAYgByAGUAZQBkAGUAcgBcACIALAAgAFwAIgBNAGUAYQB0ACAAbwB0AGgAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIAAoAGsAZwAvAGgAZQBhAGQALwBkAGEAeQApAFwAIgAsACAAMAAuADAAOAA2ACwAIAAwAC4AMAA5ADMALAAgADAALgAxADAAMwAsACAAMAAuADAAOQAzADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIAAwAC4AOAAwACwAIAAwAC4AOAAwACwAIAAwAC4AOAAwACwAIAAwAC4AOAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAcgB1AGQAZQAgAHAAcgBvAHQAZQBpAG4AXAAiACwAIAAwAC4AMQA5ACwAIAAwAC4AMgAzACwAIAAwAC4AMQA5ACwAIAAwAC4AMgAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAHIAZQB0AGUAbgB0AGkAbwBuACAAcgBhAHQAZQBcACIALAAgADAALgAzADUALAAgADAALgA0ADcALAAgADAALgAzADIALAAgADAALgA0ADcAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AdQByAGUAIABhAHMAaABcACIALAAgADAALgAxADgALAAgADAALgAxADUALAAgADAALgAxADgALAAgADAALgAxADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBDAEYAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANwAuADQAOgAgAFAAbwB1AGwAdAByAHkAIAAtACAATQBDAEYAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAE0AQwBGAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAG8AdQBsAHQAcgB5ACAALQAgAE0AQwBGAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBDAEYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBNAEMARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADcALgA0ADoAIABQAG8AdQBsAHQAcgB5ACAALQAgAE0AQwBGAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBwAGwAaQB0ACAATgBTAFcAIABhAG4AZAAgAEEAQwBUACAAaQBuAHQAbwAgAHMAZQBwAGEAcgBhAHQAZQAgAHMAdABhAHQAZQBzAC4AIABTAHAAbABpAHQAIABRAEwARAAgAGEAbgBkACAATgBUACAAaQBuAHQAbwAgAHMAZQBwAGEAcgBhAHQAZQAgAHMAdABhAHQAZQBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBjAGwAdQBkAGUAZAAgAHYAYQBsAHUAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAcwB0AGEAdABlACAAdwBoAGUAbgAgAFwAdQAwADAAMgA3AEEAbABsACAAcwB0AGEAdABlAHMAXAB1ADAAMAAyADcAIAB2AGEAbAB1AGUAIABpAHMAIABnAGkAdgBlAG4ALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAFwAdQAwADAAMgA3AFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgBcAHUAMAAwADIANwAgAHIAbwB3ACAAZgBvAHIAIABOAEkAUgAgAE0ATQBTACAAXAB1ADAAMAAyADcAQgBlAGwAdAAgAG0AYQBuAHUAcgBlACAAcgBlAG0AbwB2AGEAbABcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcAHUAMAAwADIANwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBDAEYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAAxADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGwAaQB0AHQAZQByAFwAIgAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgBcACIALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAAiACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALAAgAFwAIgBuAC8AYQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAbgAvAGEAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAwADUALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGQAaQBnAGUAcwB0AGUAcgAgAC8AIABDAG8AdgBlAHIAZQBkACAAcABvAG4AZABcACIALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgAFwAIgBEAGkAZwBlAHMAdABlAHIAIAAvACAAYwBvAHYAZQByAGUAZAAgAGwAYQBnAG8AbwBuAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAaQByAGUAYwB0ACAAcAByAG8AYwBlAHMAcwBpAG4AZwBcACIALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBDAEYAXwBOAG8AdABlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAdQAwADAAMgA3AFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAB1ADAAMAAyADcAIABhAHAAcABsAGkAZQBzACAATQBDAEYAIABmAG8AcgAgAGQAcgB5AGwAbwB0AC4AXAAiACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXABuAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAcABlAHIAIABwAG8AdQBsAHQAcgB5ACAAYwBsAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUABvAHUAbAB0AHIAeQAgAC0AIABNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgAHAAZQByACAAYwBsAGEAcwBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA2AC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAOgAgAFAAbwB1AGwAdAByAHkAIAAtACAATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIABwAGUAcgAgAGMAbABhAHMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABvAHUAbAB0AHIAeQAgAGMAbABhAHMAcwBcACIALAAgAFwAIgBCADAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAYQB5AGUAcgBzAFwAIgAsACAAMAAuADMAOQA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AZQBhAHQAIABjAGgAaQBjAGsAZQBuAHMAXAAiACwAIAAwAC4AMwA2AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBcAG4AUABvAHUAbAB0AHIAeQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAG8AdQBsAHQAcgB5ACAALQAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANgAgAFAAbwB1AGwAdAByAHkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBlAGUAIAByAGEAbgBnAGUAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBhAGcAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFYAUwBMAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFYAUwBMAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAG8AdQBsAHQAcgB5ACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFYAUwBMAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8AVgBTAEwAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADYALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAIABUAGEAYgBsAGUAIABnAGUAbgBlAHIAYQB0AGUAZAAgAGYAcgBvAG0AIABsAGkAbgBlACAAaQB0AGUAbQBzAC4AIABBAGQAZABlAGQAIABcAHUAMAAwADIANwBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AIABjAG8AbAB1AG0AbgBcAHUAMAAwADIANwAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFYAUwBMAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAFwAIgAsACAAXAAiAFYAUwBMAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaAAgAGwAaQB0AHQAZQByAFwAIgAsACAAMAAuADgANQAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABiAGUAZABkAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAIAAtACAAcwB0AG8AcgBlAGQAIABpAG4AIABoAG8AdQBzAGUAXAAiACwAIAAwAC4AOAAsACAAXAAiAE0AYQBuAHUAcgBlACAAcwB0AG8AcgBlAGQAIABpAG4AIABoAG8AdQBzAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABsAGkAdAB0AGUAcgAgAC0AIABiAGUAbAB0ACAAcgBlAG0AbwB2AGEAbABcACIALAAgADEALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4ANgA6ACAAUABvAHUAbAB0AHIAeQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADYALgAxAC4AMQAgAE0AZQB0AGgAbwBkACAAMQAgAC0AIABNAGEAbgB1AHIAZQAgAE0AZQB0AGgAYQBuAGUAIABQAG8AdQBsAHQAcgB5AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAEUAQwBIADQAXABuAHQAIABDAEgANABcAG4AewBFAH0AXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGsAfQAoAEQAXwB7AGoAawB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBtAGoAawB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAGsAfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcAG4ARABqAGsAIAA9ACAAZAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABhAG4AZAAgAHMAdQBiAGMAbABhAHMAcwAgAG8AZgAgAHAAbwB1AGwAdAByAHkAIAA6ACAAZABhAHkAcwBcAG4ATQBtAGoAawAgAD0AIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABhAG4AZAAgAHMAdQBiAGMAbABhAHMAcwAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBqAGsAIAA9ACAAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAHAAbwB1AGwAdAByAHkAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAYQBuAGQAIABzAHUAYgBjAGwAYQBzAHMAIAA6ACAAaABlAGEAZABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABqAGsALAAgAE0AbQBqAGsALAAgAE4AagBrACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAEQAagBrACwAIABNAG0AagBrACwAIABOAGoAawApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB7AEUAfQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAawB9ACgARABfAHsAagBrAH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AG0AagBrAH0AXABcAHQAaQBtAGUAcwAgAE4AXwB7AGoAawB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABqAGsAXAAiACwAXAAiAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAYQBuAGQAIABzAHUAYgBjAGwAYQBzAHMAIABvAGYAIABwAG8AdQBsAHQAcgB5ACAAOgAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbQBqAGsAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAGEAbgBkACAAcwB1AGIAYwBsAGEAcwBzACAAOgAgAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGoAawBcACIALABcACIAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAHAAbwB1AGwAdAByAHkAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAYQBuAGQAIABzAHUAYgBjAGwAYQBzAHMAIAA6ACAAaABlAGEAZABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBBAG4AZABTAHUAYgBjAGwAYQBzAHMAXABuAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHQAaABlACAAbQBhAG4AdQByAGUAIABvAGYAIABwAG8AdQBsAHQAcgB5AFwAbgBNAG0AagBrAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAbQBqAGsAfQA9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9AE0AXwB7AGoAawBtAFQAfQBcAG4ATQBqAGsAbQBUACAAPQAgAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAcABlAHIAIABjAGwAYQBzAHMALAAgAHMAdQBiAGMAbABhAHMAcwAsACAATQBNAFMALAAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAA6ACAAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAQQBuAGQAUwB1AGIAYwBsAGEAcwBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AagBrAG0AVAAsAFwAbgAgACAAIAAgAFMAVQBNACgATQBqAGsAbQBUACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBBAG4AZABTAHUAYgBjAGwAYQBzAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHQAaABlACAAbQBhAG4AdQByAGUAIABvAGYAIABwAG8AdQBsAHQAcgB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBBAG4AZABTAHUAYgBjAGwAYQBzAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbQBqAGsAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAEEAbgBkAFMAdQBiAGMAbABhAHMAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBBAG4AZABTAHUAYgBjAGwAYQBzAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADYALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAEEAbgBkAFMAdQBiAGMAbABhAHMAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAQQBuAGQAUwB1AGIAYwBsAGEAcwBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAbQBqAGsAfQA9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9AE0AXwB7AGoAawBtAFQAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAQQBuAGQAUwB1AGIAYwBsAGEAcwBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AagBrAG0AVABcACIALABcACIAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABwAGUAcgAgAGMAbABhAHMAcwAsACAAcwB1AGIAYwBsAGEAcwBzACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAbgBNAGoAawBtAFQAMQBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGoAawBtACwAVAA9ADEAfQA9AFYAUwBfAHsAagBrAH0AXABcAHQAaQBtAGUAcwAgAEIATwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBqAGsAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcABvAHUAbAB0AHIAeQAgAGMAbABhAHMAcwBlAHMAIABhAG4AZAAgAHMAdQBiAGMAbABhAHMAcwBlAHMAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBCAE8AagAgAD0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAcABlAHIAIABjAGwAYQBzAHMAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAE0ATQBTAGoAbQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAGoAawAsACAAQgBPAGoALAAgAE0ATQBTAGoAbQBUADEALAAgAE0AQwBGAGkAbQAsACAAcgBoAG8ALABcAG4AIAAgACAAIABWAFMAagBrACAAKgAgAEIATwBqACAAKgAgAE0ATQBTAGoAbQBUADEAIAAqACAATQBDAEYAaQBtACAAKgAgAHIAaABvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBqAGsAbQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAawBtACwAVAA9ADEAfQA9AFYAUwBfAHsAagBrAH0AXABcAHQAaQBtAGUAcwAgAEIATwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAGoAawBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcABvAHUAbAB0AHIAeQAgAGMAbABhAHMAcwBlAHMAIABhAG4AZAAgAHMAdQBiAGMAbABhAHMAcwBlAHMAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AagBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgAHAAZQByACAAYwBsAGEAcwBzACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBqAG0AVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBpAG0AXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBqAGsAbQBUADIAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBqAGsAbQAsAFQAPQAyAH0APQBWAFMAVABfAHsAagBrAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcAG4AVgBTAFQAagBrAG0AVAAyACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAIAA6ACAAawBnACAAVgBTAFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ATQBNAFMAagBtAFQAMgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAFQAagBrAG0AVAAyACwAIABCAE8ALAAgAE0ATQBTAGoAbQBUADIALAAgAE0AQwBGAGkAbQAsACAAcgBoAG8ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIABNAE0AUwBqAG0AVAAyACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKAAoAE0ATQBTAGoAbQBUADIAKQApACwAIABNAE0AUwBqAG0AVAAyACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAVgBTAFQAagBrAG0AVAAyACAAKgAgAEIATwAgACoAIABNAE0AUwBqAG0AVAAyACAAKgAgAE0AQwBGAGkAbQAgACoAIAByAGgAbwBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBqAGsAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAawBtACwAVAA9ADIAfQA9AFYAUwBUAF8AewBqAGsAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAyAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBUAGoAawBtAFQAMgBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwAgADoAIABrAGcAIABWAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAagBtAFQAMgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAGkAbQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgAGEAbgBkACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXABuAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXABuAFYAUwBUAGoAawBtAFQAMgBcAG4AawBnACAAVgBTAFwAbgBWAFMAVABfAHsAagBrAG0ALABUAD0AMgB9AD0AVgBTAF8AewBqAGsAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBWAFMATABfAHsAbQAsAFQAPQAxAH0AKQBcAG4AVgBTAGoAawAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgBvAHIAIABwAG8AdQBsAHQAcgB5ACAAYwBsAGEAcwBzAGUAcwAgAGEAbgBkACAAcwB1AGIAYwBsAGEAcwBzAGUAcwAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAE0ATQBTAGoAbQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AVgBTAEwAbQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAagBrACwAIABNAE0AUwBqAG0AVAAxACwAIABWAFMATABtAFQAMQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgAFYAUwBMAG0AVAAxACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKAAoAFYAUwBMAG0AVAAxACkAKQAsACAAVgBTAEwAbQBUADEALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABWAFMAagBrACAAKgAgAE0ATQBTAGoAbQBUADEAIAAqACAAKAAxACAALQAgAFYAUwBMAG0AVAAxACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAVABqAGsAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA2AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBUAF8AewBqAGsAbQAsAFQAPQAyAH0APQBWAFMAXwB7AGoAawB9AFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAFYAUwBMAF8AewBtACwAVAA9ADEAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAGoAawBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcABvAHUAbAB0AHIAeQAgAGMAbABhAHMAcwBlAHMAIABhAG4AZAAgAHMAdQBiAGMAbABhAHMAcwBlAHMAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBqAG0AVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMATABtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADYAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFYAUwBqAGsAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AVgBTAF8AewBqAGsAfQA9AEkAXwB7AGoAawB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARABNAEQAXwB7AGoAawB9ACkAXABcAHQAaQBtAGUAcwAoADEALQBBAF8AewBqAH0AKQBcAG4ASQBqAGsAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlACAAZgBvAHIAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAYQBuAGQAIABzAHUAYgBjAGwAYQBzAHMAIAA6ACAAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBEAE0ARABqAGsAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAIABmAG8AcgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABhAG4AZAAgAHMAdQBiAGMAbABhAHMAcwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAEEAagAgAD0AIABhAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAgAGYAbwByACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAGEAbgBkACAAcwB1AGIAYwBsAGEAcwBzACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA2AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEkAagBrACwAIABEAE0ARABqAGsALAAgAEEAagAsAFwAbgAgACAAIAAgAEkAagBrACAAKgAgACgAMQAgAC0AIABEAE0ARABqAGsAKQAgACoAIAAoADEAIAAtACAAQQBqACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA2AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA2AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAagBrAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA2AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA2AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA2AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA2AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA2AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAF8AewBqAGsAfQA9AEkAXwB7AGoAawB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARABNAEQAXwB7AGoAawB9ACkAXABcAHQAaQBtAGUAcwAoADEALQBBAF8AewBqAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANgBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAGoAawBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlACAAZgBvAHIAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAYQBuAGQAIABzAHUAYgBjAGwAYQBzAHMAIAA6ACAAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0ARABqAGsAXAAiACwAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAZgBvAHIAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAYQBuAGQAIABzAHUAYgBjAGwAYQBzAHMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGoAXAAiACwAXAAiAGEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlACAAZgBvAHIAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAYQBuAGQAIABzAHUAYgBjAGwAYQBzAHMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQA6ACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgAxAC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAATQBhAG4AdQByAGUAIABNAGUAdABoAGEAbgBlACAAQgBlAGUAZgAgAEYAZQBlAGQAbABvAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcAG4ARQBDAEgANABcAG4AdAAgAEMASAA0AFwAbgB7AEUAfQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgARABfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAEQAagAgAD0AIABsAGUAbgBnAHQAaAAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAZABhAHkAcwBcAG4ATQBqAG0AVAAgAD0AIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAHAAZQByACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAALAAgAE0ATQBTACwAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAOgAgAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBOAGoAIAA9ACAAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAaABlAGEAZABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABqACwAIABNAGoAbQBUACwAIABOAGoALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgARABqACwAIABNAGoAbQBUACwAIABOAGoAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAewBFAH0AXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQAoAEQAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAagBtAFQAfQBcAFwAdABpAG0AZQBzACAATgBfAHsAagB9ACkAXABcAHQAaQBtAGUAcwAxADAAXgB7AC0AMwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABqAFwAIgAsAFwAIgBsAGUAbgBnAHQAaAAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAZABhAHkAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBqAG0AVABcACIALABcACIAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBqAFwAIgAsAFwAIgBuAHUAbQBiAGUAcgBzACAAbwBmACAAYgBlAGUAZgAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABoAGUAYQBkAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXABuAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXABuAE0AagBtADUAVAAxAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAagBtAD0ANQAsAFQAPQAxAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAbQA9ADUALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAD0ANQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBqACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAEIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgBNAE0AUwBtADUAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAGkAbQA1ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAGQAcgB5AGwAbwB0ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAagAsACAAQgBPACwAIABNAE0AUwBtADUAVAAxACwAIABNAEMARgBpAG0ANQAsACAAcgBoAG8ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIABNAEMARgBpAG0ANQAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgATQBDAEYAaQBtADUAKQAsACAATQBDAEYAaQBtADUALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABWAFMAagAgACoAIABCAE8AIAAqACAATQBNAFMAbQA1AFQAMQAgACoAIABNAEMARgBpAG0ANQAgACoAIAByAGgAbwBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBqAG0ANQBUADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADIAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQA9ADUALABUAD0AMQB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQA1ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADUAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBqAFwAIgAsAFwAIgB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAG0ANQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAGkAbQA1AFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABkAHIAeQBsAG8AdAAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBqAG0AVAAyAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAagBtAFQAPQAyAH0APQAoADEALQBWAFMATAApAFwAXAB0AGkAbQBlAHMAIABWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAbQBUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcAG4AVgBTAEwAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBWAFMAagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ATQBNAFMAbQBUADIAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAGkAbQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAHIAaABvACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFYAUwBMACwAIABWAFMAagAsACAAQgBPACwAIABNAE0AUwBtAFQAMgAsACAATQBDAEYAaQBtACwAIAByAGgAbwAsAFwAbgAgACAAIAAgACgAMQAgAC0AIABWAFMATAApACAAKgAgAFYAUwBqACAAKgAgAEIATwAgACoAIABNAE0AUwBtAFQAMgAgACoAIABNAEMARgBpAG0AIAAqACAAcgBoAG8AXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQBUAD0AMgB9AD0AKAAxAC0AVgBTAEwAKQBcAFwAdABpAG0AZQBzACAAVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAEwAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAbQBUADIAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBpAG0AXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADMAIABNAE0AUwBcAG4ATQBqAG0AMQBUADMAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBqAG0APQAxACwAVAA9ADMAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAD0AMQAsAFQAPQAzAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0APQAxAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcAG4AVgBTAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAE0ATQBTAG0AMQBUADMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIAB0AGUAcgB0AGkAYQByAHkAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBNAEMARgBpAG0AMQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAagAsACAAQgBPACwAIABNAE0AUwBtADEAVAAzACwAIABNAEMARgBpAG0AMQAsACAAcgBoAG8ALABcAG4AIAAgACAAIABWAFMAagAgACoAIABCAE8AIAAqACAATQBNAFMAbQAxAFQAMwAgACoAIABNAEMARgBpAG0AMQAgACoAIAByAGgAbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAzACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AagBtADEAVAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBqAG0APQAxACwAVAA9ADMAfQA9AFYAUwBfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBtAD0AMQAsAFQAPQAzAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0APQAxAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAagAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAbQAxAFQAMwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIAB0AGUAcgB0AGkAYQByAHkAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBpAG0AMQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgAGEAbgBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgBcAG4AVgBTAGoAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AVgBTAF8AewBqAH0APQBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAoADEALQBEAE0ARABfAHsAagB9ACkAXABcAHQAaQBtAGUAcwAoADEALQBBACkAXABuAEkAagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBEAE0ARABqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAZgBvAHIAIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AQQAgAD0AIABhAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABJAGoALAAgAEQATQBEAGoALAAgAEEALABcAG4AIAAgACAAIABJAGoAIAAqACAAKAAxACAALQAgAEQATQBEAGoAKQAgACoAIAAoADEAIAAtACAAQQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAXwB7AGoAfQA9AEkAXwB7AGoAfQBcAFwAdABpAG0AZQBzACgAMQAtAEQATQBEAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzACgAMQAtAEEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAGoAXAAiACwAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgAGoAIAA6ACAAawBnACAARABNAC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0ARABqAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgAGoAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAFwAIgAsAFwAIgBhAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAZQBlAGQAbABvAHQAIAAtACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAZAB1AHIAaQBuAGcAIABzAHQAbwByAGEAZwBlACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBMAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADUAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAbwAgAGUAYQBjAGgAIAB0AGUAcgB0AGkAYQByAHkAIABzAHkAcwB0AGUAbQAgAGEAcwBzAHUAbQBlAGQAIAB0AGgAYQB0ACAAMgAgAHAAZQByACAAYwBlAG4AdAAgAGkAcwAgAHIAdQBuACAALQAgAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAZgBlAGUAZAAgAHAAYQBkAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBNAFMAbQAxAFQAMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADEALgAyAC4AMwAgAEMATwBOAFMAVABBAE4AVABTAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADAAMgApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXABuAEEAcwBoACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAG0AYQBuAHUAcgBlAC4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADYAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAxADkAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4ANwAuADQAOgAgAEYAZQBlAGQAbABvAHQAIAAtACAATQBDAEYAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkAGwAbwB0ACAALQAgAE0AQwBGAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADcALgA0ADoAIABGAGUAZQBkAGwAbwB0ACAALQAgAE0AQwBGAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAB1AHAAbABpAGMAYQB0AGUAZAAgAE4AUwBXACAAdgBhAGwAdQBlAHMAIABmAG8AcgAgAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABOAFQAIABhAG4AZAAgAFQAQQBTACAAYwBvAGwAdQBtAG4AcwAgAHcAaQB0AGgAIABcAHUAMAAwADIANwBuAG8AIABkAGEAdABhAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADEAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIABUAFwAIgAsACAAXAAiAE0ATQBTACAAbQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBOAFQAXAAiACwAIABcACIAUwBBAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFcAQQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBpAG0AYQByAHkAXAAiACwAIABcACIARAByAHkAIABsAG8AdAAgACgARgBlAGUAZABwAGEAZAApAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMwAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABQAGEAcwBzAGkAdgBlACAAVwBpAG4AZAByAG8AdwApAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgADAALAAgADAALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAcABvAG4AZAApAFwAIgAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcANwAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIAAwAC4ANwA1ACwAIAAwAC4ANwA1ACwAIAAwAC4ANwA3ACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMQBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAyAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AIABNAE0AUwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADMATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAKAA3ADAALQA4ADAAIABkAGEAeQBzACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQB4AHAAbwByAHQAIABtAGkAZAAgAGYAZQBkACAAKAA4ADAALQAyADAAMAAgAGQAYQB5AHMAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAHgAcABvAHIAdAAgAGwAbwBuAGcAIABmAGUAZAAgACgAMgAwADAAKwAgAGQAYQB5AHMAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAF8ARABhAGkAcgB5AF8AMwBfAEIAXwAxAF8AYQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAF8ARABhAGkAcgB5AF8AMwBfAEIAXwAxAF8AYQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXwBEAGEAaQByAHkAXwAzAF8AQgBfADEAXwBhAF8ARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADEAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AMQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBMAGkAdgBlAFcAZQBpAGcAaAB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AMQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBMAGkAdgBlAFcAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADEAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAyAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEwAaQB2AGUAVwBlAGkAZwBoAHQARwBhAGkAbgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AMwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADMAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AMwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AMwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA0AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEQATQBEAEEAbgBkAEMAUABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANABfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBEAE0ARABBAG4AZABDAFAAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA0AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEQATQBEAEEAbgBkAEMAUABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA0AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEQATQBEAEEAbgBkAEMAUABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADUAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUAByAGUAVwBlAGEAbgBlAGQARABhAHQAYQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBQAHIAZQBXAGUAYQBuAGUAZABEAGEAdABhAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBQAHIAZQBXAGUAYQBuAGUAZABEAGEAdABhAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADUAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUAByAGUAVwBlAGEAbgBlAGQARABhAHQAYQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADcAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATQBDAEYAcwBGAG8AcgBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBNAEMARgBzAEYAbwByAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBNAEMARgBzAEYAbwByAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADcAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATQBDAEYAcwBGAG8AcgBNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADkAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATgBPADIARQBGAEEAbgBkAEYAcgBhAGMATgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AOQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBOAE8AMgBFAEYAQQBuAGQARgByAGEAYwBOAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AOQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBOAE8AMgBFAEYAQQBuAGQARgByAGEAYwBOAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADkAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATgBPADIARQBGAEEAbgBkAEYAcgBhAGMATgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBTAHQAYQB0AGUAVABlAHIAcgBpAHQAbwByAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBTAHQAYQB0AGUAVABlAHIAcgBpAHQAbwByAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBTAHQAYQB0AGUAVABlAHIAcgBpAHQAbwByAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8AUwB0AGEAdABlAFQAZQByAHIAaQB0AG8AcgB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBTAHQAYQB0AGUAVABlAHIAcgBpAHQAbwByAHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEMAbABhAHMAcwBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAQwBsAGEAcwBzAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBDAGwAYQBzAHMAZQBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBDAGwAYQBzAHMAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAQwBsAGEAcwBzAGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAGwAbABvAGMAYQB0AGkAbwBuAE8AZgBXAGEAcwB0AGUAVABvAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBsAGwAbwBjAGEAdABpAG8AbgBPAGYAVwBhAHMAdABlAFQAbwBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAbABsAG8AYwBhAHQAaQBvAG4ATwBmAFcAYQBzAHQAZQBUAG8ATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBsAGwAbwBjAGEAdABpAG8AbgBPAGYAVwBhAHMAdABlAFQAbwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBsAGwAbwBjAGEAdABpAG8AbgBPAGYAVwBhAHMAdABlAFQAbwBNAE0AUwBfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBGAGUAcgB0AGkAbABpAHMAZQByAFAAcgBvAGQAdQBjAHQATABvAG8AawB1AHAAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABBAHAAcABsAGkAZQBkACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABvAHQAYQBsAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQQBwAHAAbABpAGUAZABBAGwAbABJAG4AZwByAGUAZABpAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAB0AEEAcABwAGwAaQBlAGQAQgB5AFMAbwB1AHIAYwBlAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABBAGMAdABpAHYAZQBJAG4AZwByAGUAZABpAGUAbgB0AEEAcABwAGwAaQBlAGQAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAUwBjAG8AcABlADMARQBGACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AEYAcgBhAGMAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ARABhAHQAYQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVABpAHQAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADAAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAyAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwA5AF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AOQBfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADMARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwA5AF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AOQBfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADMARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGEAdABhACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGEAdABhACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0ACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBHAFcAUAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAFUAcgBlAGEARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8AVQByAGUAYQBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8AVQByAGUAYQBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAFUAcgBlAGEARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAFUAcgBlAGEARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAFUAcgBlAGEARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAEcAVwBQACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBXAFAAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBEAGEAdABhACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBEAGEAdABhACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEMAdQBzAHQAbwBtAGkAcwBlAGQARABhAHQAYQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUABhAHMAdAB1AHIAZQBBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABhAHQAYQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAyAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAyAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMgBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAyAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADIAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAzAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMwBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAzAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAzAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAzAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA0AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADUAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA2AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADYAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADYAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA2AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANgBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAFMAdABhAG4AZABhAHIAZABSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8ARABhAHQAYQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBOADIATwBFAEYAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVQByAGUAYQBDAE8AMgBFAEYAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBVAHIAZQBhAEMATwAyAEUARgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBVAHIAZQBhAEMATwAyAEUARgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVQByAGUAYQBDAE8AMgBFAEYAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEcAQQBTAEYAZgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBHAEEAUwBGAGYASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEcAQQBTAEYAZgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEcAQQBTAEYAZgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEcAQQBTAEYAZgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMARwBBAFMARgBmAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAFMAdAByAGkAbgBnACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8ARwBlAHQAUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAFMAdAByAGkAbgBnACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8AVABvAHQAYQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEQAYQB5AHMATQBvAHYAZQBtAGUAbgB0AFQAbwBNAG8AbgB0AGgARQBuAGQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEYAcgBvAG0AUwB0AGEAcgB0AE8AZgBNAG8AbgB0AGgAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAUgBlAG0AYQBpAG4AaQBuAGcASABlAGEAZAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AEUAbgBkACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AE0AbwBuAHQAaAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEMAYQBsAGMAdQBsAGEAdABlAFMAdABhAHkARAB1AHIAYQB0AGkAbwBuAFQAbwBFAG4AZAAyACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AQQB2AGUAcgBhAGcAZQBIAGUAYQBkAE0AbwBuAHQAaAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFQAbwB0AGEAbABCAGkAcgB0AGgAcwBEAHUAcgBpAG4AZwBNAG8AbgB0AGgAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBDAGEAbABjAHUAbABhAHQAZQBQAHIAbwBwAG8AcgB0AGkAbwBuAEMAbwB3AHMAQwBhAGwAdgBpAG4AZwAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFQAbwB0AGEAbABNAG8AdgBlAG0AZQBuAHQATABpAHYAZQB3AGUAaQBnAGgAdABTAG8AbABkACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AUwB1AG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQB3AGUAaQBnAGgAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEgAZQBhAGQAQQB0AEUAbgBkACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQARQBuAHQAcgB5AEQAYQB0AGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBHAGUAdABFAHgAaQB0AEQAYQB0AGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBHAGUAdABIAGUAYQBkAEEAdABFAHgAaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQBuAHQAcgB5ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQB4AGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQAyACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AFAAbwBzAHQAVwBlAGEAbgBpAG4AZwAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQAQQBkAGoAdQBzAHQAZQBkAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEMAYQBsAGMAdQBsAGEAdABlAEcAcgBvAHcAdABoAEYAYQBjAHQAbwByACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsAXwBMAG8AbwBrAHUAcABNAEMARgBTAHQAYQB0AGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAHMAXwBEAGEAdABhACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBTAG8AaQBsAEEAbQBlAG4AZABtAGUAbgB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAFMAbwBpAGwAQQBtAGUAbgBkAG0AZQBuAHQAcwBfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBBAGcAcgBvAGMAaABlAG0AaQBjAGEAbABzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBnAHIAbwBjAGgAZQBtAGkAYwBhAGwAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBnAHIAbwBjAGgAZQBtAGkAYwBhAGwAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBnAHIAbwBjAGgAZQBtAGkAYwBhAGwAcwBfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBMAGkAYwBrAEIAbABvAGMAawBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ATABpAGMAawBCAGwAbwBjAGsAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ATABpAGMAawBCAGwAbwBjAGsAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ATABpAGMAawBCAGwAbwBjAGsAcwBfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBBAG4AaQBtAGEAbABGAGUAZQBkAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBuAGkAbQBhAGwARgBlAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBuAGkAbQBhAGwARgBlAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBuAGkAbQBhAGwARgBlAGUAZABfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBBAHEAdQBhAGMAdQBsAHQAdQByAGUARgBlAGUAZABBAG4AZABCAGEAaQB0AF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBxAHUAYQBjAHUAbAB0AHUAcgBlAEYAZQBlAGQAQQBuAGQAQgBhAGkAdABfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBxAHUAYQBjAHUAbAB0AHUAcgBlAEYAZQBlAGQAQQBuAGQAQgBhAGkAdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBxAHUAYQBjAHUAbAB0AHUAcgBlAEYAZQBlAGQAQQBuAGQAQgBhAGkAdABfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAdABhACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AUABhAGMAawBhAGcAaQBuAGcAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBQAGEAYwBrAGEAZwBpAG4AZwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AUABhAGMAawBhAGcAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAFAAYQBjAGsAYQBnAGkAbgBnAF8ARABhAHQAYQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAFMAZQBlAGQAcwBBAG4AZABTAGUAZQBkAGwAaQBuAGcAcwBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAFMAZQBlAGQAcwBBAG4AZABTAGUAZQBkAGwAaQBuAGcAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AUwBlAGUAZABzAEEAbgBkAFMAZQBlAGQAbABpAG4AZwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBTAGUAZQBkAHMAQQBuAGQAUwBlAGUAZABsAGkAbgBnAHMAXwBEAGEAdABhACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQwBsAGUAYQBuAGkAbgBnAEMAaABlAG0AaQBjAGEAbABzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQwBsAGUAYQBuAGkAbgBnAEMAaABlAG0AaQBjAGEAbABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBDAGwAZQBhAG4AaQBuAGcAQwBoAGUAbQBpAGMAYQBsAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEMAbABlAGEAbgBpAG4AZwBDAGgAZQBtAGkAYwBhAGwAcwBfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBPAHQAaABlAHIAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwASQBuAHAAdQB0AHMAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBPAHQAaABlAHIAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwASQBuAHAAdQB0AHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAE8AdABoAGUAcgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABJAG4AcAB1AHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ATwB0AGgAZQByAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAEkAbgBwAHUAdABzAF8ARABhAHQAYQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ARgB1AGUAbABTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGEAdABhACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ARgB1AGUAbABTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ARgB1AGUAbABTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARABhAHQAYQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEUAbABlAG0AZQBuAHQAcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEUAbABlAG0AZQBuAHQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEUAbABlAG0AZQBuAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQARQBsAGUAbQBlAG4AdABzAF8ARABhAHQAYQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBQAHIAbwBkAHUAYwB0AHMAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUAByAG8AZAB1AGMAdABzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFAAcgBvAGQAdQBjAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFAAcgBvAGQAdQBjAHQAcwBfAEQAYQB0AGEAMQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBQAHIAbwBkAHUAYwB0AHMAXwBEAGEAdABhADIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUAByAG8AZAB1AGMAdABzAF8ARABhAHQAYQAzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFAAcgBvAGQAdQBjAHQAcwBfAEQAYQB0AGEANAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGkAbQBlAEQAbwBsAG8AbQBpAHQAZQBHAHkAcABzAHUAbQBDAG8AbgBzAHQAYQBuAHQAcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGkAbQBlAEQAbwBsAG8AbQBpAHQAZQBHAHkAcABzAHUAbQBDAG8AbgBzAHQAYQBuAHQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGkAbQBlAEQAbwBsAG8AbQBpAHQAZQBHAHkAcABzAHUAbQBDAG8AbgBzAHQAYQBuAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAaQBtAGUARABvAGwAbwBtAGkAdABlAEcAeQBwAHMAdQBtAEMAbwBuAHMAdABhAG4AdABzAF8ARABhAHQAYQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGkAbQBlAEQAbwBsAG8AbQBpAHQAZQBHAHkAcABzAHUAbQBDAG8AbgBzAHQAYQBuAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARwBXAFAAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABBAG4AaQBtAGEAbABXAGEAcwB0AGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQAQQBuAGkAbQBhAGwAVwBhAHMAdABlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABBAG4AaQBtAGEAbABXAGEAcwB0AGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABBAG4AaQBtAGEAbABXAGEAcwB0AGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQAQQBuAGkAbQBhAGwAVwBhAHMAdABlAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQAQQBuAGkAbQBhAGwAVwBhAHMAdABlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBzAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBzAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEcAVwBQACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQQBuAGkAbQBhAGwAVwBhAHMAdABlAE4ATABvAHMAdAAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBBAG4AaQBtAGEAbABXAGEAcwB0AGUATgBMAG8AcwB0AF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBOAEwAbwBzAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQQBuAGkAbQBhAGwAVwBhAHMAdABlAE4ATABvAHMAdABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQQBuAGkAbQBhAGwAVwBhAHMAdABlAE4ATABvAHMAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBOAEwAbwBzAHQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBOAEwAbwBzAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdAAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBOAEwAbwBzAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBOAEwAbwBzAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUATgBMAG8AcwB0ACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBOAEwAbwBzAHQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQwByAG8AcABSAGUAcwBpAGQAdQBlAE4ATABvAHMAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUATgBMAG8AcwB0AF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUATgBMAG8AcwB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQwByAG8AcABSAGUAcwBpAGQAdQBlAE4ATABvAHMAdABfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQwByAG8AcABSAGUAcwBpAGQAdQBlAE4ATABvAHMAdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBVAHIAaQBuAGUAQQBuAGQARAB1AG4AZwBEAGUAcABvAHMAaQB0AGUAZABfAEcAVwBQACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBVAHIAaQBuAGUAQQBuAGQARAB1AG4AZwBEAGUAcABvAHMAaQB0AGUAZAAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8AVQByAGkAbgBlAEEAbgBkAEQAdQBuAGcARABlAHAAbwBzAGkAdABlAGQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAFUAcgBpAG4AZQBBAG4AZABEAHUAbgBnAEQAZQBwAG8AcwBpAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBVAHIAaQBuAGUAQQBuAGQARAB1AG4AZwBEAGUAcABvAHMAaQB0AGUAZABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAFUAcgBpAG4AZQBBAG4AZABEAHUAbgBnAEQAZQBwAG8AcwBpAHQAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAFUAcgBpAG4AZQBBAG4AZABEAHUAbgBnAEQAZQBwAG8AcwBpAHQAZQBkAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8AVQByAGkAbgBlAEEAbgBkAEQAdQBuAGcARABlAHAAbwBzAGkAdABlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4ACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAFIAZQBzAGkAZAB1AGUAQwByAG8AcABSAGEAdABpAG8AIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AQwBhAGwAYwB1AGwAYQB0AGUARgByAGEAYwB0AGkAbwBuAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBNAFMAXwBNAEMARgBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8ARABhAHQAYQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFQAaQB0AGwAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVABpAHQAbABlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFUAbgBpAHQAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFMAbwB1AHIAYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVABpAHQAbABlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBVAG4AaQB0ACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAFMAbwB1AHIAYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBUAGkAdABsAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVQBuAGkAdAAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AUwBvAHUAcgBjAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFQAaQB0AGwAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBVAG4AaQB0ACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBTAG8AdQByAGMAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBDAEYAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAE0AQwBGAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBDAEYAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBDAEYAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBNAEMARgBfAE4AbwB0AGUAcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFYAUwBMAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBWAFMATABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFYAUwBMAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFYAUwBMAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFYAUwBMAF8ARABhAHQAYQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAQQBuAGQAUwB1AGIAYwBsAGEAcwBzACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAEEAbgBkAFMAdQBiAGMAbABhAHMAcwBfAFQAaQB0AGwAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBBAG4AZABTAHUAYgBjAGwAYQBzAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAQQBuAGQAUwB1AGIAYwBsAGEAcwBzAF8AVQBuAGkAdAAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBBAG4AZABTAHUAYgBjAGwAYQBzAHMAXwBTAG8AdQByAGMAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBBAG4AZABTAHUAYgBjAGwAYQBzAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBBAG4AZABTAHUAYgBjAGwAYQBzAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAEEAbgBkAFMAdQBiAGMAbABhAHMAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0ACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBUAGkAdABsAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFUAbgBpAHQAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AUwBvAHUAcgBjAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA2AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADYAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANgBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA2AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA2AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANgBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADYAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADYAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBVAG4AaQB0ACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFMAbwB1AHIAYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdAAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AVABpAHQAbABlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFUAbgBpAHQAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFMAbwB1AHIAYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AVABpAHQAbABlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFUAbgBpAHQAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVABpAHQAbABlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAC4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlACIALAAiAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQAuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBNAGEAbgB1AHIAZQBNAGEAbgBhAGcAZQBtAGUAbgB0AF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUALgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADEATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADIATQBNAFMATwBwAHQAaQBvAG4AcwAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdAAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADMATQBNAFMATwBwAHQAaQBvAG4AcwAiAF0ALAAiAGwAbwBjAGEAbABlACIAOgB7ACIAbABpAHMAdABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHIAbwB3AFMAZQBwAGEAcgBhAHQAbwByACIAOgAiADsAIgAsACIAYwBvAGwAdQBtAG4AUwBlAHAAYQByAGEAdABvAHIAIgA6ACIALAAiACwAIgB0AGgAbwB1AHMAYQBuAGQAcwBTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAsACIALAAiAHQAaABvAHUAcwBhAG4AZABzAFAAbwBzAGkAdABpAG8AbgBzACIAOgBbADMAXQAsACIAZABlAGMAaQBtAGEAbABTAGUAcABhAHIAYQB0AG8AcgAiADoAIgAuACIALAAiAGQAYQB0AGUATwByAGQAZQByACIAOgAiAEQATQBZACIALAAiAGMAdQByAHIAZQBuAGMAeQBTAHkAbQBiAG8AbAAiADoAIgAkACIALAAiAGkAcwBDAHUAcgByAGUAbgBjAHkAUwB5AG0AYgBvAGwATABlAGEAZAAiADoAdAByAHUAZQAsACIAaQBzAEMAdQByAHIAZQBuAGMAeQBTAGUAcABCAHkAUwBwAGEAYwBlACIAOgBmAGEAbABzAGUALAAiAHIAbwB3AEwAZQB0AHQAZQByACIAOgAiAFIAIgAsACIAYwBvAGwAdQBtAG4ATABlAHQAdABlAHIAIgA6ACIAQwAiACwAIgByAGMATABlAGYAdABCAHIAYQBjAGsAZQB0ACIAOgAiAFsAIgAsACIAcgBjAFIAaQBnAGgAdABCAHIAYQBjAGsAZQB0ACIAOgAiAF0AIgAsACIAcwB0AGEAdABlAG0AZQBuAHQAUwBlAHAAYQByAGEAdABvAHIAIgA6ACIAOwAiACwAIgBsAG8AYwBhAGwAZQBOAGEAbQBlACIAOgAiAGUAbgAtAHUAcwAiAH0AfQA=</AFEJSONBlob>
+<AFEJSONBlob xmlns="http://schemas.advancedformulaenvironment.officeapps.live.com/afejsonblob/1.0">ewAiAHMAYwBoAGUAbQBhACIAOgAiAGgAdAB0AHAAOgAvAC8AcwBjAGgAZQBtAGEAcwAuAGEAZAB2AGEAbgBjAGUAZABmAG8AcgBtAHUAbABhAGUAbgB2AGkAcgBvAG4AbQBlAG4AdAAuAG8AZgBmAGkAYwBlAGEAcABwAHMALgBsAGkAdgBlAC4AYwBvAG0ALwBhAGYAZQBwAHIAbwBqAGUAYwB0AHMALwAwAC4AMgAiACwAIgBmAGkAbABlAHMAIgA6AFsAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBXAG8AcgBrAGIAbwBvAGsAIgAsACIAdABlAHgAdAAiADoAIgAvAC8AIAAtAC0ALQAgAFcAbwByAGsAYgBvAG8AawAgAG0AbwBkAHUAbABlACAALQAtAC0AXABuAC8ALwAgAEEAIABmAGkAbABlACAAbwBmACAAbgBhAG0AZQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwAgAG8AZgAgAHQAaABlACAAZgBvAHIAbQA6AFwAbgAvAC8AIAAgACAAIABuAGEAbQBlACAAPQAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5ACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIABGAG8AcgAgAEQAYQBpAHIAeQBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQA6ACAATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAF8ARABhAGkAcgB5AF8AMwBfAEIAXwAxAF8AYQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXABuAEEAIAA9ACAAYQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAZQB4AHAAcgBlAHMAcwBlAGQAIABhAHMAIABhACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXwBEAGEAaQByAHkAXwAzAF8AQgBfADEAXwBhAF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQAgAD0AIABhAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABlAHgAcAByAGUAcwBzAGUAZAAgAGEAcwAgAGEAIABmAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXwBEAGEAaQByAHkAXwAzAF8AQgBfADEAXwBhAF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAcQB1AGEAdABpAG8AbgAgADMALgBCAC4AMQBhAF8AMgBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AOAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAF8ARABhAGkAcgB5AF8AMwBfAEIAXwAxAF8AYQBfAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBCADAAIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAF8ARABhAGkAcgB5AF8AMwBfAEIAXwAxAF8AYQBfAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbABcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAF8ARABhAGkAcgB5AF8AMwBfAEIAXwAxAF8AYQBfAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAcQB1AGEAdABpAG8AbgAgADMALgBCAC4AMQBhAF8AMgBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIANAApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADEAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABcAG4AVABhAGIAbABlACAAQQA1AC4ANQAuADEALgAxACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAATICAATABpAHYAZQB3AGUAaQBnAGgAdAAgACgAawBnACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AMQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBMAGkAdgBlAFcAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADEAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgABMgIABMAGkAdgBlAHcAZQBpAGcAaAB0AFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAxAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEwAaQB2AGUAVwBlAGkAZwBoAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADEAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgA6ACAAVABhAGIAbABlACAAQQA1AC4ANQAuADEALgAxAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAxAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEwAaQB2AGUAVwBlAGkAZwBoAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAANgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABpAG0AZQAgAHAAZQByAGkAbwBkAFwAIgAsACAAXAAiAE0AaQBsAGsAaQBuAGcAIABDAG8AdwBzAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAYwAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBlADEAXAAiACwAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGMAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAMgAwADIAMAATIDIAMAAyADMAXAAiACwAIAA1ADUAMAAsACAAMwA3ADAALAAgADEANwA5ACwAIAA2ADAAMAAsACAAMgAyADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAFwAbgBUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADIAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgABMgIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgAgACgAawBnAC8AZABhAHkAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAyAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEwAaQB2AGUAVwBlAGkAZwBoAHQARwBhAGkAbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQA1AC4ANQAuADEALgAyACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAATICAATABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAyADoAIABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADIAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAaQBtAGUAIABwAGUAcgBpAG8AZABcACIALAAgAFwAIgBNAGkAbABrAGkAbgBnACAAQwBvAHcAcwBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGUAMQBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAMQAgACgAdwBlAGEAbgBlAGQAKQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAxAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAMAAyADAAEyAyADAAMgAzAFwAIgAsACAAMAAuADAAMQA2ACwAIAAwAC4ANgAsACAAMAAuADUANwAsACAAMAAuADEALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAzAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAFMAdABhAG4AZABhAHIAZABSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAFwAbgBUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADMAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgABMgIABTAHQAYQBuAGQAYQByAGQAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADMAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADMAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgABMgIABTAHQAYQBuAGQAYQByAGQAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADMAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAzAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAFMAdABhAG4AZABhAHIAZABSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgA6ACAAVABhAGIAbABlACAAQQA1AC4ANQAuADEALgAzAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAzAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAFMAdABhAG4AZABhAHIAZABSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGkAbQBlACAAcABlAHIAaQBvAGQAXAAiACwAIABcACIATQBpAGwAawBpAG4AZwAgAEMAbwB3AHMAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBlADEAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwAgAFwAdQAwADAAMwBjADEAIAAoAHcAZQBhAG4AZQBkACkAXAAiACwAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGUAMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAYwAxACAAKAB3AGUAYQBuAGUAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAyADAAMgAwABMgMgAwADIAMwBcACIALAAgADUAOQAwACwAIAA1ADkAMAAsACAANQA5ADAALAAgADcANwAwACwAIAA3ADcAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANABfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBEAE0ARABBAG4AZABDAFAAXABuAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4ANAAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAEyAgAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAYQBuAGQAIABjAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANABfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBEAE0ARABBAG4AZABDAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4ANAAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAEyAgAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAYQBuAGQAIABjAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANABfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBEAE0ARABBAG4AZABDAFAAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADQAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUARABNAEQAQQBuAGQAQwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAyADoAIABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADQAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADQAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUARABNAEQAQQBuAGQAQwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBEAE0ARABcACIALAAgAFwAIgBDAFAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsAFwAIgAsACAANwA1ACwAIAAyADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADUAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUAByAGUAVwBlAGEAbgBlAGQARABhAHQAYQBcAG4AVABhAGIAbABlACAAQQA1AC4ANQAuADEALgA1ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAATICAARABhAHQAYQAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGMAYQBsAHYAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADUAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUAByAGUAVwBlAGEAbgBlAGQARABhAHQAYQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQA1AC4ANQAuADEALgA1ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAATICAARABhAHQAYQAgAGYAbwByACAAcAByAGUALQB3AGUAYQBuAGUAZAAgAGMAYQBsAHYAZQBzAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA1AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAFAAcgBlAFcAZQBhAG4AZQBkAEQAYQB0AGEAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBQAHIAZQBXAGUAYQBuAGUAZABEAGEAdABhAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAyADoAIABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADUAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADUAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUAByAGUAVwBlAGEAbgBlAGQARABhAHQAYQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAdABlACAAcgBhAG4AZwBlAFwAIgAsACAAXAAiAEMAbABhAHMAcwBcACIALAAgAFwAIgBDAEgANAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXAAiACwAIABcACIAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAXAAiACwAIABcACIARgBhAGUAYwBhAGwAIABOAFwAIgAsACAAXAAiAFUAcgBpAG4AYQByAHkAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAyADAAMAA1ACsAXAAiACwAIABcACIASABlAGkAZgBlAHIAcwBcAHUAMAAwADMAYwAxAFwAIgAsACAAMAAuADAAMQA3ADYALAAgADAALgAyADYAOAA1ACwAIAAwAC4AMAAwADUANQAsACAAMAAuADAAMAA4ADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIAB5AGUAYQByAHMAXAAiACwAIABcACIAQgB1AGwAbABzAFwAdQAwADAAMwBjADEAXAAiACwAIAAwAC4AMAAyADAANAAsACAAMAAuADMAMAAwADMALAAgADAALgAwADAANQAwACwAIAAwAC4AMAAwADQAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBNAEMARgBzAEYAbwByAE0ATQBTAFwAbgBUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADcAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgABMgIABNAEMARgBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADcAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATQBDAEYAcwBGAG8AcgBNAE0AUwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAAQQA1AC4ANQAuADEALgA3ACAARABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIAATICAATQBDAEYAcwBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBNAEMARgBzAEYAbwByAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADcAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATQBDAEYAcwBGAG8AcgBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgA6ACAAVABhAGIAbABlACAAQQA1AC4ANQAuADEALgA3AFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA3AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAE0AQwBGAHMARgBvAHIATQBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAOQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXAAiACwAXAAiAEEAQwBUAFwAIgAsAFwAIgBOAFMAVwBcACIALABcACIATgBUAFwAIgAsAFwAIgBRAEwARABcACIALABcACIAUwBBAFwAIgAsAFwAIgBUAEEAUwBcACIALABcACIAVgBJAEMAXAAiACwAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAxACwAMAAuADAAMQAsADAALgAwADIALAAwAC4AMAAxACwAMAAuADAAMQAsADAALgAwADEALAAwAC4AMAAxACwAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsADAALgA3ADIALAAwAC4ANwA2ACwAMAAuADgALAAwAC4ANwA4ACwAMAAuADcANAAsADAALgA2ADkALAAwAC4ANwAzACwAMAAuADcANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtAHMAIAAoAGIAKQBcACIALAAwAC4AMAAwADUALAAwAC4AMAAwADUALAAwAC4AMAAxACwAMAAuADAAMAA1ACwAMAAuADAAMAA1ACwAMAAuADAAMAAxACwAMAAuADAAMAA1ACwAMAAuADAAMAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawBzACAAKABjACkAXAAiACwAMAAuADEANQAsADAALgAxADgALAAwAC4ANQAwACwAMAAuADIANAAsADAALgAxADcALAAwAC4AMQAzACwAMAAuADEANwAsADAALgAxADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQBcACIALAAwAC4AMAAyACwAMAAuADAAMgAsADAALgAwADIALAAwAC4AMAAyACwAMAAuADAAMgAsADAALgAwADIALAAwAC4AMAAyACwAMAAuADAAMgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AOQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBOAE8AMgBFAEYAQQBuAGQARgByAGEAYwBOAFwAbgBUAGEAYgBsAGUAIABBADUALgA1AC4AMQAuADkAIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgABMgIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIABhAG4AZAAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAE4ATwAyAEUARgBBAG4AZABGAHIAYQBjAE4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4AOQAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAEyAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgAGEAbgBkACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGIAeQAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAE4ATwAyAEUARgBBAG4AZABGAHIAYQBjAE4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAZQB4AGMAcgBlAHQAZQBkAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAE4ATwAyAEUARgBBAG4AZABGAHIAYQBjAE4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADIAOgAgAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4AOQBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AOQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBOAE8AMgBFAEYAQQBuAGQARgByAGEAYwBOAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAFwAIgAsAFwAIgBFAEYAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAKQBcACIALABcACIARgByAGEAYwBHAEEAUwBNAG0AIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AIABlAHgAYwByAGUAdABlAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBvAGkAZAAgAGEAdAAgAFAAYQBzAHQAdQByAGUAXAAiACwAMAAsADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIALAAwACwAMAAuADMANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAAgABMgIABTAHUAbQBwACAAYQBuAGQAIABEAGkAcwBwAGUAcgBzAGEAbABcACIALAAwACwAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGEAaQBsAHkAIABTAHAAcgBlAGEAZAAgABMgIABEAHIAYQBpAG4AcwAgAHQAbwAgAFAAYQBkAGQAbwBjAGsAXAAiACwAMAAsADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAMAAuADAAMAA1ACwAMAAuADMAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIAAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8AUwB0AGEAdABlAFQAZQByAHIAaQB0AG8AcgB5AFwAbgBUAGEAYgBsAGUAIAA1AC4AMgAgAFMAeQBtAGIAbwBsAHMAIAB1AHMAZQBkACAAaQBuACAAYQBsAGcAbwByAGkAdABoAG0AcwAgAGYAbwByACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAFMAdABhAHQAZQBUAGUAcgByAGkAdABvAHIAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABhAGIAbABlACAANQAuADIAIABTAHkAbQBiAG8AbABzACAAdQBzAGUAZAAgAGkAbgAgAGEAbABnAG8AcgBpAHQAaABtAHMAIABmAG8AcgAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAALQAgAFMAdABhAHQAZQAvAFQAZQByAHIAaQB0AG8AcgB5ACAAKABpACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBTAHQAYQB0AGUAVABlAHIAcgBpAHQAbwByAHkAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBTAHQAYQB0AGUAVABlAHIAcgBpAHQAbwByAHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAFMAdABhAHQAZQBUAGUAcgByAGkAdABvAHIAeQBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAFMAdABhAHQAZQBUAGUAcgByAGkAdABvAHIAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHkAbQBiAG8AbABcACIALAAgAFwAIgBTAHQAYQB0AGUALwAgAHQAZQByAHIAaQB0AG8AcgB5ACAAKABpACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADEALAAgAFwAIgBBAEMAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAzACwAIABcACIATgBTAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADQALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAA1ACwAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAA2ACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADcALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADgALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEMAbABhAHMAcwBlAHMAXABuAFQAYQBiAGwAZQAgADUALgAyACAAUwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEMAbABhAHMAcwBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAyACAAUwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAC0AIABEAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGMAbABhAHMAcwBlAHMAIAAoAGoAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBDAGwAYQBzAHMAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBqAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEMAbABhAHMAcwBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBDAGwAYQBzAHMAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEMAbABhAHMAcwBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIAUwB0AGEAdABlAC8AIAB0AGUAcgByAGkAdABvAHIAeQAgACgAaQApAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxACwAIABcACIATQBpAGwAawBpAG4AZwAgAGMAbwB3AHMAXAAiACwAIABcACIATQBpAGwAawBpAG4AZwAgAGMAbwB3AHMAIAAoADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAMgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAZQAgADEAIAB5AGUAYQByAFwAIgAsACAAXAAiAEgAZQBpAGYAZQByAHMAIABcAHUAMAAwADMAZQAgADEAIAB5AGUAYQByACAAKAAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADMALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAIAAxACAAeQBlAGEAcgBcACIALAAgAFwAIgBIAGUAaQBmAGUAcgBzACAAXAB1ADAAMAAzAGMAIAAxACAAeQBlAGEAcgAgACgAMwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAA0ACwAIABcACIAQgB1AGwAbABzACAAXAB1ADAAMAAzAGUAIAAxACAAeQBlAGEAcgBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAgADEAIAB5AGUAYQByACAAKAA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgADUALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAYwAgADEAIAB5AGUAYQByAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjACAAMQAgAHkAZQBhAHIAIAAoADUAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAgACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAbABsAG8AYwBhAHQAaQBvAG4ATwBmAFcAYQBzAHQAZQBUAG8ATQBNAFMAXABuAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4AOAAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAEyAgAEEAbABsAG8AYwBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAIAB0AG8AIABNAE0AUwAgABMgIABNAGkAbABrAGkAbgBnACAAYwBvAHcAcwAgACgAcABlAHIAIABjAGUAbgB0ACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAbABsAG8AYwBhAHQAaQBvAG4ATwBmAFcAYQBzAHQAZQBUAG8ATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4AOAAgAEQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAEyAgAEEAbABsAG8AYwBhAHQAaQBvAG4AIABvAGYAIAB3AGEAcwB0AGUAIAB0AG8AIABNAE0AUwAgABMgIABNAGkAbABrAGkAbgBnACAAYwBvAHcAcwAgACgAcABlAHIAIABjAGUAbgB0ACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAGwAbABvAGMAYQB0AGkAbwBuAE8AZgBXAGEAcwB0AGUAVABvAE0ATQBTAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAbABsAG8AYwBhAHQAaQBvAG4ATwBmAFcAYQBzAHQAZQBUAG8ATQBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgBjAGUAbgB0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBsAGwAbwBjAGEAdABpAG8AbgBPAGYAVwBhAHMAdABlAFQAbwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgAgAFQAYQBiAGwAZQAgAEEANQAuADUALgAxAC4AOABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAbABsAG8AYwBhAHQAaQBvAG4ATwBmAFcAYQBzAHQAZQBUAG8ATQBNAFMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMQAwACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBTAHkAbQBiAG8AbABcACIALAAgAFwAIgBNAE0AUwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBOAFQAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIABcACIAUwBBAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFcAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAANwA4AC4ANgAsACAANwA4AC4ANgAsACAANwA4AC4ANwAsACAANwA4AC4ANwAsACAAOAAwAC4ANQAsACAAOAA2AC4ANQAsACAAOAAzAC4AOQAsACAANwA5AC4AOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQBcACIALAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgAsACAAOQAuADAALAAgADkALgAwACwAIAA3AC4AMwAsACAANwAuADMALAAgADEAMAAuADQALAAgADgALgA0ACwAIAAxADAALgA4ACwAIAAxADAALgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIARABhAGkAbAB5ACAAUwBwAHIAZQBhAGQAOgAgAFMAdQBtAHAAIABhAG4AZAAgAGQAaQBzAHAAZQByAHMAYQBsAFwAIgAsACAAMgAuADAALAAgADIALgAwACwAIAAzAC4AMwAsACAAMwAuADMALAAgADEALgA0ACwAIAAyAC4ANAAsACAAMAAuADkALAAgADEALgA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARABhAGkAbAB5ACAAUwBwAHIAZQBhAGQAOgAgAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawBzAFwAIgAsACAAMQAuADkALAAgADEALgA5ACwAIAAyAC4ANAAsACAAMgAuADQALAAgADAALgA4ACwAIAAwAC4AOAAsACAAMAAuADIALAAgADAALgA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA0AFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAFMAdABvAHIAYQBnAGUAXAAiACwAIAA4AC4ANAAsACAAOAAuADQALAAgADgALgA0ACwAIAA4AC4ANAAsACAANgAuADkALAAgADIALgAwACwAIAA0AC4AMgAsACAANwAuADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzACAAaQBuAGMAbAB1AGQAaQBuAGcAIABsAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgACAAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA1AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAAYwBvAG0AYgB1AHMAdABlAGQAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABDAG8AbgB0AGUAbgB0ACAARgBhAGMAdABvAHIAIAAoAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAKQBcACIALAAgAFwAIgBGAHUAZQBsACAAdQBuAGkAdABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAE8AMgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAEgANABcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABOADIATwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAIABDAG8AbQBiAGkAbgBlAGQAIABnAGEAcwBlAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQBcACIALAAgADAALgAwADMAOQAzACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAgAHQAaABhAHQAIABpAHMAIABjAGEAcAB0AHUAcgBlAGQAIABmAG8AcgAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIAAwAC4AMAAzADcANwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADAALgAyACwAIAAwAC4AMAAzACwAIAA1ADEALgA2ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AYQBsACAAbQBpAG4AZQAgAHcAYQBzAHQAZQAgAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAANQAxAC4AOQAsACAANAAuADYALAAgADAALgAzACwAIAA1ADYALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAoAHIAZQB2AGUAcgB0AGkAbgBnACAAdABvACAAcwB0AGEAbgBkAGEAcgBkACAAYwBvAG4AZABpAHQAaQBvAG4AcwApAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQBuAHAAcgBvAGMAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAA2ADIAOQAsACAAXAAiAG0AMwBcACIALAAgADUANgAuADUALAAgADAALgAwADMALAAgADAALgAwADMALAAgADUANgAuADUANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBrAGUAIABvAHYAZQBuACAAZwBhAHMAXAAiACwAIAAwAC4AMAAxADgAMQAsACAAXAAiAG0AMwBcACIALAAgADMANwAuADAALAAgADAALgAwADMALAAgADAALgAwADUALAAgADMANwAuADAAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAbABhAHMAdAAgAGYAdQByAG4AYQBjAGUAIABnAGEAcwBcACIALAAgADAALgAwADAANAAwACwAIABcACIAbQAzAFwAIgAsACAAMgAzADQALgAwACwAIAAwAC4AMAAzACwAIAAwAC4AMAAyACwAIAAyADMANAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwBcACIALAAgADAALgAwADMAOQAwACwAIABcACIAbQAzAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADAANAAsACAAMAAuADAAMwAsACAANgAwAC4AMgA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBMAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAGUAbwB1AHMAIABmAG8AcwBzAGkAbAAgAGYAdQBlAGwAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlAFwAIgAsACAAMAAuADAAMwA5ADAALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAANQAxAC4ANQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABhAG4AZABmAGkAbABsACAAYgBpAG8AZwBhAHMAIAB0AGgAYQB0ACAAaQBzACAAYwBhAHAAdAB1AHIAZQBkACAAZgBvAHIAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAKABtAGUAdABoAGEAbgBlACAAbwBuAGwAeQApAFwAIgAsACAAMAAuADAAMwA3ADcALAAgAFwAIgBtADMAXAAiACwAIAAwAC4AMAAsACAANgAuADQALAAgADAALgAwADMALAAgADYALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGwAdQBkAGcAZQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgACgAbQBlAHQAaABhAG4AZQAgAG8AbgBsAHkAKQBcACIALAAgADAALgAwADMANwA3ACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADYALgA0ACwAIAAwAC4AMAAzACwAIAA2AC4ANAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQAgAGIAaQBvAGcAYQBzACAAdABoAGEAdAAgAGkAcwAgAGMAYQBwAHQAdQByAGUAZAAgAGYAbwByACAAYwBvAG0AYgB1AHMAdABpAG8AbgAsACAAbwB0AGgAZQByACAAdABoAGEAbgAgAHQAaABvAHMAZQAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAwAC4AMAAzADcAMAAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAA2AC4ANAAsACAAMAAuADAAMwAsACAANgAuADQAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAG0AZQB0AGgAYQBuAGUAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADAALgAwACwAIAAwAC4AMQAsACAAMAAuADAAMwAsACAAMAAuADEAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAeQBkAHIAbwBnAGUAbgBcACIALAAgADAALgAwADEAMgAyACwAIABcACIAbQAzAFwAIgAsACAAMAAuADAALAAgADAALgAwACwAIAAwAC4ANQAsACAAMAAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIAAxACwAIABcACIARwBKAFwAIgAsACAANQAxAC4ANAAsACAAMAAuADEALAAgADAALgAwADMALAAgADUAMQAuADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAMQAsACAAXAAiAEcASgBcACIALAAgADYAMAAuADIALAAgADAALgAwADQALAAgADAALgAwADMALAAgADYAMAAuADIANwBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcAHUAMAAwADIANwAgAGEAbgBkACAAXAB1ADAAMAAyADcAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAB1ADAAMAAyADcAIAB3AGUAcgBlACAAYQBkAGQAZQBkACwAIABlAGEAYwBoACAAdwBpAHQAaAAgAGEAbgAgAGUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAbwBmACAAMQAgAEcASgAgAHAAZQByACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwALgAgAFQAaABpAHMAIABpAHMAIABmAG8AcgAgAHUAcwBlAHIAcwAgAHcAaABvACAAaABhAHYAZQAgAGYAdQBlAGwAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABkAGEAdABhACAAaQBuACAARwBKACAAcgBhAHQAaABlAHIAIAB0AGgAYQBuACAAbQAzAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIABnAGEAcwBlAG8AdQBzACAAZgB1AGUAbABzAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAC4AXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA2AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAdABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAE4AYQB0AHUAcgBhAGwAIABHAGEAcwAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE0AZQB0AHIAbwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAATgBhAHQAdQByAGEAbAAgAEcAYQBzACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgBvAG4AIAAtACAATQBlAHQAcgBvAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAMQAzAC4AMQAsACAAMQA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFYAaQBjAHQAbwByAGkAYQBcACIALAAgADQALgAwACwAIAA0AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIAA4AC4AOAAsACAANwAuADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADEAMAAuADcALAAgADEAMAAuADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIAA0AC4AMQAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIAA0AC4AMAAsACAANAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgADQALgAxACwAIAA0AC4AMABcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE4AUwBXACAAYQBuAGQAIABBAEMAVAAgAHMAcABsAGkAdAAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIAByAG8AdwBzAC4AIABcAHUAMAAwADIANwBDAFwAdQAwADAAMgA3ACAAVgBhAGwAdQBlAHMAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAGEAbgBkACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAByAGUAcABsAGEAYwBlAGQAIAB3AGkAdABoACAAdABoAG8AcwBlACAAZgBvAHIAIABWAGkAYwB0AG8AcgBpAGEAIABhAG4AZAAgAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAgAHIAZQBzAHAAZQBjAHQAaQB2AGUAbAB5AC4AIAAoAFMAZQBlACAAYQBwAHAAZQBuAGQAaQBjAGUAcwApAFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMgAsACAAMgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEEAcwAgAFMAYwBvAHAAZQAgADMAIABmAGEAYwB0AG8AcgBzACAAYQByAGUAIABjAGEAbABjAHUAbABhAHQAZQBkACAAYQB0ACAAdABoAGUAIABwAG8AaQBuAHQAIAB3AGgAZQByAGUAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAIABpAHMAIABkAGUAbABpAHYAZQByAGUAZAAgAHQAbwAgAGUAbgBkACAAdQBzAGUAcgBzACwAIABpAHQAIABpAHMAIABuAGUAYwBlAHMAcwBhAHIAeQAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAYQB0ACAAZQBhAGMAaAAgAG8AZgAgAHQAaABlACAAbABvAGEAZAAgAGMAZQBuAHQAcgBlAHMALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBHAGEAcwAgAHIAZQBhAGMAaABlAHMAIABlAG4AZAAgAHUAcwBlAHIAcwAgAGUAaQB0AGgAZQByACAAZgByAG8AbQAgAHQAaABlACAAbQBlAHQAcgBvACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABuAGUAdAB3AG8AcgBrAHMAIABvAHIAIABkAGkAcgBlAGMAdAAgAGYAcgBvAG0AIAB0AGgAZQAgAGgAaQBnAGgAIAAtACAAcAByAGUAcwBzAHUAcgBlACAAZABpAHMAdAByAGkAYgB1AHQAaQBvAG4AIABwAGkAcABlAGwAaQBuAGUAcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAEgAbwB1AHMAZQBoAG8AbABkAHMAIABhAG4AZAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB1AHMAZQByAHMAIAB0AGUAbgBkACAAdABvACAAYgBlACAAcwBlAHIAdgBlAGQAIABiAHkAIAB0AGgAZQAgAGYAbwByAG0AZQByACwAIABhAG4AZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAGcAZQBuAGUAcgBhAHQAbwByAHMAIABhAG4AZAAgAGwAYQByAGcAZQAgAGkAbgBkAHUAcwB0AHIAaQBhAGwAIABwAGwAYQBuAHQAcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGwAYQB0AHQAZQByAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIALQBcACIALAAgAFwAIgBNAGUAdAByAG8AIABpAHMAIABkAGUAZgBpAG4AZQBkACAAYQBzACAAbABvAGMAYQB0AGUAZAAgAG8AbgAgAG8AcgAgAGUAYQBzAHQAIABvAGYAIAB0AGgAZQAgAGQAaQB2AGkAZABpAG4AZwAgAHIAYQBuAGcAZQAgAGkAbgAgAE4AUwBXACwAIABpAG4AYwBsAHUAZABpAG4AZwAgAEMAYQBuAGIAZQByAHIAYQAgAGEAbgBkACAAUQB1AGUAYQBuAGIAZQB5AGEAbgAsACAATQBlAGwAYgBvAHUAcgBuAGUALAAgAEIAcgBpAHMAYgBhAG4AZQAsACAAQQBkAGUAbABhAGkAZABlACAAbwByACAAUABlAHIAdABoAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIATwB0AGgAZQByAHcAaQBzAGUALAAgAHQAaABlACAAbgBvAG4AIAAtACAAbQBlAHQAcgBvACAAZgBhAGMAdABvAHIAIABzAGgAbwB1AGwAZAAgAGIAZQAgAHUAcwBlAGQALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEYAYQBjAHQAbwByAHMAIABhAHIAZQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAG8AcgAgAGEAbABsACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAHcAaABpAGMAaAAgAG0AYQB5ACAAaQBuAGMAbAB1AGQAZQAgAGMAbwBhAGwAIABzAGUAYQBtACAAbQBlAHQAaABhAG4AZQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACwAIABcACIAVABhAGIAbABlACAANgAgAGkAcwAgAG4AbwB0ACAAYQBwAHAAbABpAGMAYQBiAGwAZQAgAHQAbwAgAGUAdABoAGEAbgBlAC4AIABTAGUAZQAgAFQAYQBiAGwAZQAgADcAIABJAG4AZABpAHIAZQBjAHQAIAAoAFMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAZQB0AGgAYQBuAGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAEMAIAA9ACAAQwBvAG4AZgBpAGQAZQBuAHQAaQBhAGwALgAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZgBvAHIAIABUAGEAcwBtAGEAbgBpAGEAIABhAG4AZAAgAHQAaABlACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIABhAHIAZQAgAG4AbwB0ACAAYQB2AGEAaQBsAGEAYgBsAGUAIABkAHUAZQAgAHQAbwAgAGMAbwBuAGYAaQBkAGUAbgB0AGkAYQBsAGkAdAB5ACAAYwBvAG4AcwB0AHIAYQBpAG4AdABzACAAdABoAGEAdAAgAGEAcgBpAHMAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcACIALAAgAFwAIgBmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGEAIABsAGkAbQBpAHQAZQBkACAAbgB1AG0AYgBlAHIAIABvAGYAIABOAEcARQBSACAAZABhAHQAYQAgAGkAbgBwAHUAdABzAC4AIABJAHQAIABpAHMAIABzAHUAZwBnAGUAcwB0AGUAZAAgAHQAaABhAHQAIABmAG8AcgAgAFQAYQBzAG0AYQBuAGkAYQAgAHQAaABlACAAdQBzAGUAIABvAGYAIAB0AGgAZQAgAFYAaQBjAHQAbwByAGkAYQBuACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGkAcwAgAGEAcABwAHIAbwBwAHIAaQBhAHQAZQAsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAIgAsACAAXAAiAHcAaABpAGwAZQAgAGYAbwByACAATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAdABoAGUAIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABpAHMAIABhAHAAcAByAG8AcAByAGkAYQB0AGUALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgAtAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAZABvACAAbgBvAHQAIABpAG4AYwBsAHUAZABlACAAZgB1AGcAaQB0AGkAdgBlACAAZQBtAGkAcwBzAGkAbwBuACAAbABlAGEAawBhAGcAZQAgAGYAcgBvAG0AIABsAG8AdwAgAHAAcgBlAHMAcwB1AHIAZQAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGkAbwBuACAAcABpAHAAZQBsAGkAbgBlACAAbgBlAHQAdwBvAHIAawBzACAAdwBoAGkAbABlACAAdABoAG8AcwBlACAAZgByAG8AbQAgAGgAaQBnAGgAIABwAHIAZQBzAHMAdQByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAXAAiACwAIABcACIAZwBhAHMAIABuAGUAdAB3AG8AcgBrAHMAIABhAHIAZQAgAGMAbwBuAHMAaQBkAGUAcgBlAGQAIABuAGUAZwBsAGkAZwBpAGIAbABlAC4AXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAAcwBjAG8AcABlACAAMQAgAGEAbgBkACAAMwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGwAaQBxAHUAaQBkACAAZgB1AGUAbABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAXAAiACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBEAGkAcgBlAGMAdAAgACgAUwBjAG8AcABlACAAMQApACAAYQBuAGQAIABpAG4AZABpAHIAZQBjAHQAIAAoAHMAYwBvAHAAZQAgADMAKQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAHQAaABlACAAYwBvAG4AcwB1AG0AcAB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMALAAgAGkAbgBjAGwAdQBkAGkAbgBnACAAYwBlAHIAdABhAGkAbgAgAHAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMALgBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAA4AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADUALAAgADgALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACAAKABHAEoAIABwAGUAcgAgAHUAbgBpAHQAIABvAGYAIABmAHUAZQBsACkAXAAiACwAIABcACIARgB1AGUAbAAgAHUAbgBpAHQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBPADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBIADQAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAATgAyAE8AXAAiACwAIABcACIAUwBjAG8AcABlACAAMQAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByACAAKABrAGcAIABDAE8AMgAgAC0AIABlACAALwAgAEcASgApACAAQwBvAG0AYgBpAG4AZQBkACAAZwBhAHMAZQBzAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADMAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsAHMAIAAoAG8AdABoAGUAcgAgAHQAaABhAG4AIABwAGUAdAByAG8AbABlAHUAbQAgAGIAYQBzAGUAZAAgAG8AaQBsACAAdQBzAGUAZAAgAGEAcwAgAGYAdQBlAGwAKQAsACAAZQAuAGcALgAgAGwAdQBiAHIAaQBjAGEAbgB0AHMAXAAiACwAIAAzADgALgA4ACwAIABcACIAawBsAFwAIgAsACAAMQAzAC4AOQAsACAAMAAuADAALAAgADAALgAwACwAIAAxADMALgA5ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABnAHIAZQBhAHMAZQBzAFwAIgAsACAAMwA4AC4AOAAsACAAXAAiAGsAbABcACIALAAgADMALgA1ACwAIAAwAC4AMAAsACAAMAAuADAALAAgADMALgA1ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAHUAZABlACAAbwBpAGwAIABpAG4AYwBsAHUAZABpAG4AZwAgAGMAcgB1AGQAZQAgAG8AaQBsACAAYwBvAG4AZABlAG4AcwBhAHQAZQBzAFwAIgAsACAANAA1AC4AMwAsACAAXAAiAHQAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAANgA5AC4AOAA4ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIAA0ADYALgA1ACwAIABcACIAdABcACIALAAgADYAMQAuADAALAAgADAALgAwADgALAAgADAALgAyACwAIAA2ADEALgAyADgALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB1AHQAbwBtAG8AdABpAHYAZQAgAGcAYQBzAG8AbABpAG4AZQAgAC8AIABwAGUAdAByAG8AbAAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADQALgAyACwAIABcACIAawBMAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADIALAAgADAALgAyACwAIAA2ADcALgA4ADAALAAgADEANwAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIABnAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADMALgAxACwAIABcACIAawBMAFwAIgAsACAANgA3ACwAIAAwAC4AMgAsACAAMAAuADIALAAgADYANwAuADQAMAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0ACkAXAAiACwAIAAzADcALgA1ACwAIABcACIAawBMAFwAIgAsACAANgA4AC4AOQAsACAAMAAuADAAMQAsACAAMAAuADIALAAgADYAOQAuADEAMQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgAgAHQAdQByAGIAaQBuAGUAIABmAHUAZQBsACAALwAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA2ACwAIAAwAC4AMAAyACwAIAAwAC4AMgAsACAANgA5AC4AOAAyACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdABpAG4AZwAgAG8AaQBsAFwAIgAsACAAMwA3AC4AMwAsACAAXAAiAGsATABcACIALAAgADYAOQAuADUALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA3ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsATABcACIALAAgADYAOQAuADkALAAgADAALgAxACwAIAAwAC4AMgAsACAANwAwAC4AMgAwACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAMwA5AC4ANwAsACAAXAAiAGsATABcACIALAAgADcAMwAuADYALAAgADAALgAwADQALAAgADAALgAyACwAIAA3ADMALgA4ADQALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAGEAcgBvAG0AYQB0AGkAYwAgAGgAeQBkAHIAbwBjAGEAcgBiAG8AbgBzAFwAIgAsACAAMwA0AC4ANAAsACAAXAAiAGsATABcACIALAAgADYAOQAuADcALAAgADAALgAwADMALAAgADAALgAyACwAIAA2ADkALgA5ADMALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AbAB2AGUAbgB0AHMAOgAgAG0AaQBuAGUAcgBhAGwAIAB0AHUAcgBwAGUAbgB0AGkAbgBlACAAbwByACAAdwBoAGkAdABlACAAcwBwAGkAcgBpAHQAcwBcACIALAAgADMANAAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA3ACwAIAAwAC4AMAAzACwAIAAwAC4AMgAsACAANgA5AC4AOQAzACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABwAGUAdAByAG8AbABlAHUAbQAgAGcAYQBzACAAKABMAFAARwApAFwAIgAsACAAMgA1AC4ANwAsACAAXAAiAGsATABcACIALAAgADYAMAAuADIALAAgADAALgAyACwAIAAwAC4AMgAsACAANgAwAC4ANgAwACwAIAAyADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBhAHAAaAB0AGgAYQBcACIALAAgADMAMQAuADQALAAgAFwAIgBrAEwAXAAiACwAIAA2ADkALgA4ACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAA2ADkALgA4ADIALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAdAByAG8AbABlAHUAbQAgAGMAbwBrAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAdABcACIALAAgADkAMgAuADYALAAgADAALgAwADgALAAgADAALgAyACwAIAA5ADIALgA4ADgALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAZgBpAG4AZQByAHkAIABnAGEAcwAgAGEAbgBkACAAbABpAHEAdQBpAGQAcwBcACIALAAgADQAMgAuADkALAAgAFwAIgB0AFwAIgAsACAANQA0AC4ANwAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAANQA0AC4ANwA2ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAYwBvAGsAZQBcACIALAAgADMANAAuADIALAAgAFwAIgB0AFwAIgAsACAAOQAyAC4ANgAsACAAMAAuADAAOAAsACAAMAAuADIALAAgADkAMgAuADgAOAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAcAByAG8AZAB1AGMAdABzACAAbwB0AGgAZQByACAAdABoAGEAbgAgAG0AZQBuAHQAaQBvAG4AZQBkACAAaQBuACAAdABoAGUAIABpAHQAZQBtAHMAIABhAGIAbwB2AGUAXAAiACwAIAAzADQALgA0ACwAIABcACIAawBMAFwAIgAsACAANgA5AC4AOAAsACAAMAAuADAAMgAsACAAMAAuADEALAAgADYAOQAuADkAMgAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAaQBvAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA0AC4ANgAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAHQAaABhAG4AbwBsACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGEAIABmAHUAZQBsACAAaQBuACAAYQBuACAAaQBuAHQAZQByAG4AYQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGUAbgBnAGkAbgBlAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAbwBmAHUAZQBsAHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAdABoAG8AcwBlACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQAgAGEAbgBkACAAYgBlAGwAbwB3AFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsATABcACIALAAgADAALgAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMgAsACAAMAAuADIAOAAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGEAdgBpAGEAdABpAG8AbgAgAGsAZQByAG8AcwBlAG4AZQBcACIALAAgADMANgAuADgALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADAALgAyADIALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAEwAXAAiACwAIAAwAC4AMAAsACAAMAAuADEALAAgADAALgAyACwAIAAwAC4AMwAwACwAIABcACIATgBFAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAXAB1ADAAMAAyADcATgBFAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIABhAHMAIAB6AGUAcgBvACAAZgBvAHIAIABjAGEAbABjAHUAbABhAHQAaQBvAG4AcwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAdQBlAGwAIABzAGMAbwBwAGUAIAAxACAAYQBuAGQAIAAzACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAC0AIABUAHIAYQBuAHMAcABvAHIAdABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARgB1AGUAbAAgAHMAYwBvAHAAZQAgADEAIABhAG4AZAAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0AFwAIgApACkAOwBcAG4AXABuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBUAHIAYQBuAHMAcABvAHIAdABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAxACkAIABhAG4AZAAgAGkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMwApACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABvAGYAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAcwAgAGkAbgAgAGQAaQBmAGYAZQByAGUAbgB0ACAAdAByAGEAbgBzAHAAbwByAHQAIABlAHEAdQBpAHAAbQBlAG4AdABcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAVABhAGIAbABlACAAOQBcACIAKQApADsAXABuAFwAbgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMgAsACAAOQAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAYQBuAHMAcABvAHIAdAAgAHQAeQBwAGUAXAAiACwAIABcACIARgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAZQBkAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAQwBvAG4AdABlAG4AdAAgAEYAYQBjAHQAbwByACgARwBKACAAcABlAHIAIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbAApAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB1AG4AaQB0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMATwAyAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMASAA0AFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAE4AMgBPAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgAgACgAawBnACAAQwBPADIAIAAtACAAZQAgAC8AIABHAEoAKQAgAEMAbwBtAGIAaQBuAGUAZAAgAGcAYQBzAGUAcwBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAIAAoAGsAZwAgAEMATwAyACAALQAgAGUAIAAvACAARwBKACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAXAAiACwAIAAzADQALgAyACwAIABcACIAawBsAFwAIgAsACAANgA3AC4ANAAsACAAMAAuADAAMgAsACAAMAAuADIALAAgADYANwAuADYAMgAsACAAMQA3AC4AMgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbABcACIALAAgADMAOAAuADYALAAgAFwAIgBrAGwAXAAiACwAIAA2ADkALgA5ACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAANwAwAC4ANAAxACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAHAAZQB0AHIAbwBsAGUAdQBtACAAZwBhAHMAIAAoAEwAUABHACkAXAAiACwAIAAyADYALgAyACwAIABcACIAawBsAFwAIgAsACAANgAwAC4AMgAsACAAMAAuADUALAAgADAALgAzACwAIAA2ADEALgAwADAALAAgADIAMAAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgADMAOQAuADcALAAgAFwAIgBrAGwAXAAiACwAIAA3ADMALgA2ACwAIAAwAC4AMAA4ACwAIAAwAC4ANQAsACAANwA0AC4AMQA4ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBFAHQAaABhAG4AbwBsAFwAIgAsACAAMgAzAC4ANAAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADIALAAgADAALgA0ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQgBpAG8AZABpAGUAcwBlAGwAXAAiACwAIAAzADQALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgA4ACwAIAAxAC4ANwAsACAAMgAuADUALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMAAxACwAIAAwAC4ANQAsACAAMAAuADUAMQAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAE8AdABoAGUAcgAgAGIAaQBvAGYAdQBlAGwAcwBcACIALAAgADIAMwAuADQALAAgAFwAIgBrAGwAXAAiACwAIAAwAC4AMAAsACAAMAAuADgALAAgADEALgA3ACwAIAAyAC4ANQAsACAAXAAiAE4ARQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAZwBoAHQAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAwAC4AMAAzADkAMwAsACAAXAAiAG0AMwBcACIALAAgADUAMQAuADQALAAgADcALgAzACwAIAAwAC4AMwAsACAANQA5AC4AMAAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIAAyADUALgAzACwAIABcACIAawBsAFwAIgAsACAANQAxAC4ANAAsACAANwAuADMALAAgADAALgAzACwAIAA1ADkALgAwACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBDAG8AbQBwAHIAZQBzAHMAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMAAuADAAMwA5ADMALAAgAFwAIgBtADMAXAAiACwAIAA1ADEALgA0ACwAIAAyAC4AOAAsACAAMAAuADMALAAgADUANAAuADUALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAbgBhAHQAdQByAGEAbAAgAGcAYQBzAFwAIgAsACAAMgA1AC4AMwAsACAAXAAiAGsAbABcACIALAAgADUAMQAuADQALAAgADIALgA4ACwAIAAwAC4AMwAsACAANQA0AC4ANQAsACAAMQA4AC4AMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADAANwAsACAAMAAuADQALAAgADcAMAAuADMANwAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARABpAGUAcwBlAGwAIABvAGkAbAAgAC0AIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAANgA5AC4AOQAsACAAMAAuADEALAAgADAALgA0ACwAIAA3ADAALgA0ACwAIAAxADcALgAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADkALAAgADAALgAyACwAIAAwAC4ANAAsACAANwAwAC4ANQAsACAAMQA3AC4AMwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQB2ACAAbwByACAAaABpAGcAaABlAHIAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADcALAAgADAALgA0ACwAIAAwAC4ANAA3ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbAAgABMgIABFAHUAcgBvACAAaQBpAGkAXAAiACwAIAAzADgALgA2ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAxACwAIAAwAC4ANAAsACAAMAAuADUALAAgAFwAIgBOAEUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBSAGUAbgBlAHcAYQBiAGwAZQAgAGQAaQBlAHMAZQBsACAAEyAgAEUAdQByAG8AIABpAFwAIgAsACAAMwA4AC4ANgAsACAAXAAiAGsAbABcACIALAAgADAALgAwACwAIAAwAC4AMgAsACAAMAAuADQALAAgADAALgA2ACwAIABcACIATgBFAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdABcACIALAAgADMAMwAuADEALAAgAFwAIgBrAGwAXAAiACwAIAA2ADcALgAwACwAIAAwAC4AMAA2ACwAIAAwAC4ANgAsACAANgA3AC4ANgA2ACwAIAAxADgALgAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAMwA2AC4AOAAsACAAXAAiAGsAbABcACIALAAgADYAOQAuADYALAAgADAALgAwADEALAAgADAALgA2ACwAIAA3ADAALgAyADEALAAgADEAOAAuADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIAAzADYALgA4ACwAIABcACIAawBsAFwAIgAsACAAMAAuADAALAAgADAALgAwADEALAAgADAALgA2ACwAIAAwAC4ANgAxACwAIABcACIATgBFAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFwAdQAwADAAMgA3AE4ARQBcAHUAMAAwADIANwAgAHYAYQBsAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQA7AFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADgAOgAgAEYAdQBlAGwAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA4AC4AMQAgAEYAdQBlAGwAIABVAHMAZQAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAGYAdQBlAGwAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQAsACAARQBDACwAIABFAEYALABcAG4AIAAgACAAIABRACAAKgAgAEUAQwAgACoAIABFAEYAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXABuAEUAbQBpAHMAcwBpAG8AbgBzACAAZgBvAHIAIABlAGEAYwBoACAARwBIAEcAIABmAHIAbwBtACAAdABoAGUAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAYwBvAG0AYgB1AHMAdABlAGQAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAAZQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEALAAgAEUAQwAsACAARQBGACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEALAAgAEUAQwAsACAARQBGACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZQBuAGUAcgBnAHkAIABwAHUAcgBwAG8AcwBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADgALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMgAuADMAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdAByAGEAbgBzAHAAbwByAHQAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFACAAPQAgAFEAIAAqACAARQBDACAAKgAgAEUARgAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEAcQBcACIALAAgAFwAIgBBAG0AbwB1AG4AdAAgAG8AZgAgAGYAdQBlAGwAIAB0AHkAcABlACAAcQAgAGMAbwBtAGIAdQBzAHQAZQBkACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAFYAYQByAGkAZQBzACAAYgBhAHMAZQBkACAAbwBuACAAZgB1AGUAbAAgAHQAeQBwAGUAOgAgAGsATAAsACAAbQAzACwAIABHAEoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAQwBUAHIAYQBuAHMALABxAFwAIgAsACAAXAAiAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AHIAYQBuAHMAcABvAHIAdAAgAGUAbgBlAHIAZwB5ACAAcAB1AHIAcABvAHMAZQBzAFwAIgAsACAAXAAiAEcASgAgAC8AIAB1AG4AaQB0ACAAbwBmACAAZgB1AGUAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAFQAcgBhAG4AcwAsADEALABxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdAByAGEAbgBzAHAAbwByAHQAIABlAG4AZQByAGcAeQAgAHAAdQByAHAAbwBzAGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgBlACAALwAgAEcASgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcQBcACIALAAgAFwAIgBGAHUAZQBsACAAdAB5AHAAZQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVAByAGEAbgBzAFwAIgAsACAAXAAiAFQAcgBhAG4AcwBwAG8AcgB0ACAAYwBvAG0AYgB1AHMAdABpAG8AbgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZwBcACIALAAgAFwAIgBHAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAXAAiACwAIABcACIAUwBjAG8AcABlACAAMQBcACIALAAgAFwAIgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBcAG4ARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzAFwAbgBRACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZgB1AGUAbAAgAHQAeQBwAGUAIABxACAAdQBzAGUAZAAgAGYAbwByACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAHAAZQByAGEAdABpAG8AbgBzACAAOgAgAGsATABcAG4ARQBDACAAOgAgAEUAbgBlAHIAZwB5ACAAYwBvAG4AdABlAG4AdAAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAA6ACAARwBKAC8AawBMAFwAbgBFAEYAIAA6ACAAUwBjAG8AcABlACAAMQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwAgADoAIABrAGcAIABDAE8AMgBlACAALwAgAEcASgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEALAAgAEUAQwAsACAARQBGACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEALAAgAEUAQwAsACAARQBGACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAHQAaABlACAAcwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AIABvAGYAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADgALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMgAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABzAG8AdQByAGMAZQBzACAALQAgAEMAYQBsAGMAdQBsAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAIAA9ACAAUQAgACoAIABFAEMAIAAqACAARQBGACAAKgAgADEAMAAgAF4AIAAtACAAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAFMAQwAsAHEAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBHAEoAIAAvACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBTAEMALAAxACwAcQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEMAXAAiACwAIABcACIAUwB0AGEAdABpAG8AbgBhAHIAeQAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMgBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAFwAbgBFAG0AaQBzAHMAaQBvAG4AcwAgAGYAbwByACAAZQBhAGMAaAAgAEcASABHACAAZgByAG8AbQAgAGcAZQBuAGUAcgBpAGMAIABmAHUAZQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAHcAaABlAHIAZQAgAHQAaABlACAAdQBzAGEAZwBlACAAaQBzACAAbgBvAHQAIABrAG4AbwB3AG4AXABuAFEAIAA6ACAAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABnAGUAbgBlAHIAaQBjACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAIAA6ACAAawBMAFwAbgBFAEMAIAA6ACAARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwAgADoAIABHAEoALwBrAEwAXABuAEUARgAgADoAIABTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFEALAAgAEUAQwAsACAARQBGACwAXABuACAAIAAgACAAVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAoAFEALAAgAEUAQwAsACAARQBGACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABmAG8AcgAgAGUAYQBjAGgAIABHAEgARwAgAGYAcgBvAG0AIAB0AGgAZQAgAGcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBVAHMAZQBzACAAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAOAAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkALAAgADgALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApACAAYQBuAGQAIABlAHYAZQByAGEAZwBlAHMAIAB0AGgAZQAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIABmAG8AcgAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAYQBuAGQAIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZgB1AGUAbAAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMgAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABnAGUAbgBlAHIAaQBjACAAZQBuAGUAcgBnAHkAIABzAG8AdQByAGMAZQBzACAALQAgAEMAYQBsAGMAdQBsAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBmACAAbABpAHEAdQBpAGQAIABmAHUAZQBsAHMAIABhAG4AZAAgADIALgAzACAARQBzAHQAaQBtAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAcgBhAG4AcwBwAG8AcgB0ACAAZgB1AGUAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQAgAD0AIABRACAAKgAgAEUAQwAgACoAIABFAEYAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIABmAHUAZQBsACAAdAB5AHAAZQAgAHEAIAB1AHMAZQBkACAAZgBvAHIAIABnAGUAbgBlAHIAaQBjACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAG8AcABlAHIAYQB0AGkAbwBuAHMAXAAiACwAIABcACIAVgBhAHIAaQBlAHMAIABiAGEAcwBlAGQAIABvAG4AIABmAHUAZQBsACAAdAB5AHAAZQA6ACAAawBMACwAIABtADMALAAgAEcASgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEcAQwAsAHEAXAAiACwAIABcACIARQBuAGUAcgBnAHkAIABjAG8AbgB0AGUAbgB0ACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAbwBwAGUAcgBhAHQAaQBvAG4AcwBcACIALAAgAFwAIgBHAEoAIAAvACAAdQBuAGkAdAAgAG8AZgAgAGYAdQBlAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBHAEMALAAxACwAcQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAxACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGcAZQBuAGUAcgBpAGMAIABjAG8AbQBiAHUAcwB0AGkAbwBuACAAZgBvAHIAIABlAGEAYwBoACAAZwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAARwBKAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBxAFwAIgAsACAAXAAiAEYAdQBlAGwAIAB0AHkAcABlAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAEMAXAAiACwAIABcACIARwBlAG4AZQByAGkAYwAgAGMAbwBtAGIAdQBzAHQAaQBvAG4AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGcAXAAiACwAIABcACIARwByAGUAZQBuAGgAbwB1AHMAZQAgAGcAYQBzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAFMAYwBvAHAAZQAgADEAXAAiACwAIABcACIAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEYAZQByAHQAaQBsAGkAcwBlAHIAUAByAG8AZAB1AGMAdABMAG8AbwBrAHUAcABcAG4APQBMAEEATQBCAEQAQQAoAFAAcgBvAGQAdQBjAHQALAAgAFAAcgBvAGQAdQBjAHQAQQB0AHQAcgBpAGIAdQB0AGUALAAgAFAAcgBvAGQAdQBjAHQAQQByAHIAYQB5ACwAIABQAHIAbwBkAHUAYwB0AEEAcgByAGEAeQBDAG8AbAB1AG0AbgAsACAAUAByAG8AZAB1AGMAdABBAHIAcgBhAHkASABlAGEAZABlAHIAcwAsAFwAbgAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIABQAHIAbwBkAHUAYwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIABYAE0AQQBUAEMASAAoAFQAUgBJAE0AKABQAHIAbwBkAHUAYwB0ACkALAAgAFAAcgBvAGQAdQBjAHQAQQByAHIAYQB5AEMAbwBsAHUAbQBuACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAWABNAEEAVABDAEgAKABUAFIASQBNACgAUAByAG8AZAB1AGMAdABBAHQAdAByAGkAYgB1AHQAZQApACwAIABQAHIAbwBkAHUAYwB0AEEAcgByAGEAeQBIAGUAYQBkAGUAcgBzACwAIAAwACkAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAFwAIgBcACIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATABvAG8AawB1AHAAVABhAHIAZwBlAHQAMQAsAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAxACwAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFsATABvAG8AawB1AHAAVABhAHIAZwBlAHQAMgBdACwAWwBMAG8AbwBrAHUAcABBAHIAcgBhAHkAMgBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgATABvAG8AawB1AHAAQQByAHIAYQB5ADEAPQBMAG8AbwBrAHUAcABUAGEAcgBnAGUAdAAxACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATABvAG8AawB1AHAAVABhAHIAZwBlAHQAMgApACwAMQAsAC0ALQAoAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAyAD0ATABvAG8AawB1AHAAVABhAHIAZwBlAHQAMgApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABBAHAAcABsAGkAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0ACwAXABuACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAgACoAIABBAG0AZQBuAGQAbQBlAG4AdABQAGUAcgBjAGUAbgB0ACkAXABuACkAOwBcAG4AXABuAFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEEAcABwAGwAaQBlAGQAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACwAXABuACAAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMQAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADIAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANABdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADYAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALAAgACgAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAqAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsACAAKABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACoAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAIAAoAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKgBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzACkALAAgAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANAAsACAAKABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACoAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANAApACwAIABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADUALAAgACgAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAqAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAKQAsACAAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAIAAoAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKgBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2ACkALAAgACAAXABuACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMQAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxAFwAbgAgACAAIAAgACkAKwBcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAyAFwAbgAgACAAIAAgACkALAAgADAAKQArAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAzACwAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADMAXABuACAAIAAgACAAKQAsACAAMAApACsAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANABcAG4AIAAgACAAIAApACwAIAAwACkAKwBcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA1AFwAbgAgACAAIAAgACkALAAgADAAKQArAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA2ACwAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADYAXABuACAAIAAgACAAKQAsACAAMAApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAHQAQQBwAHAAbABpAGUAZABCAHkAUwBvAHUAcgBjAGUAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAXABuACAAIABTAG8AdQByAGMAZQAsAFwAbgAgACAAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAsAFwAbgAgACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEALABcAG4AIAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAxAFMAbwB1AHIAYwBlACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAyAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAyAFMAbwB1AHIAYwBlAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADMAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADMAUwBvAHUAcgBjAGUAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANABdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADQAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANABTAG8AdQByAGMAZQBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA1AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANQBdACwAXABuACAAIABbAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA1AFMAbwB1AHIAYwBlAF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADYAXQAsAFwAbgAgACAAWwBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2AF0ALABcAG4AIAAgAFsAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADYAUwBvAHUAcgBjAGUAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADEALAAgACgAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAqAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADEAKQAsAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQAMgAsACAAKABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACoAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQAMgApACwAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAIAAoAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKgBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAAzACkALAAgAFwAbgAgACAAIAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANAAsACAAKABBAG0AbwB1AG4AdABBAHAAcABsAGkAZQBkACoAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0AFAAZQByAGMAZQBuAHQANAApACwAIABcAG4AIAAgACAAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADUALAAgACgAQQBtAG8AdQBuAHQAQQBwAHAAbABpAGUAZAAqAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdABQAGUAcgBjAGUAbgB0ADUAKQAsACAAXABuACAAIAAgACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAIAAoAEEAbQBvAHUAbgB0AEEAcABwAGwAaQBlAGQAKgBQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAUABlAHIAYwBlAG4AdAA2ACkALAAgACAAXABuACAAIAAgACAARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMQAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAxACwAIABTAG8AdQByAGMAZQAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADEAUwBvAHUAcgBjAGUAXABuACAAIAAgACAAKQArAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAAyACwAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADIALAAgAFMAbwB1AHIAYwBlACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMgBTAG8AdQByAGMAZQBcAG4AIAAgACAAIAApACwAIAAwACkAKwBcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQAMwAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAAzACwAIABTAG8AdQByAGMAZQAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADMAUwBvAHUAcgBjAGUAXABuACAAIAAgACAAKQAsACAAMAApACsAXABuACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAKABcAG4AIAAgACAAIAAgACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADQALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAQQBtAG8AdQBuAHQANAAsACAAUwBvAHUAcgBjAGUALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA0AFMAbwB1AHIAYwBlAFwAbgAgACAAIAAgACkALAAgADAAKQArAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABGAGUAcgB0AGkAbABpAHMAZQByAF8AUwB1AG0AUAByAG8AZAB1AGMAdABBAHAAcABsAGkAZQBkACgAXABuACAAIAAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFAAcgBvAGQAdQBjAHQASQBuAGcAcgBlAGQAaQBlAG4AdAA1ACwAIABjAGEAbABjAHUAbABhAHQAZQBkAEEAbQBvAHUAbgB0ADUALAAgAFMAbwB1AHIAYwBlACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANQBTAG8AdQByAGMAZQBcAG4AIAAgACAAIAApACwAIAAwACkAKwBcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAdQBtAFAAcgBvAGQAdQBjAHQAQQBwAHAAbABpAGUAZAAoAFwAbgAgACAAIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABQAHIAbwBkAHUAYwB0AEkAbgBnAHIAZQBkAGkAZQBuAHQANgAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZABBAG0AbwB1AG4AdAA2ACwAIABTAG8AdQByAGMAZQAsACAAUAByAG8AZAB1AGMAdABJAG4AZwByAGUAZABpAGUAbgB0ADYAUwBvAHUAcgBjAGUAXABuACAAIAAgACAAKQAsACAAMAApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEcAZQB0AFMAYwBvAHAAZQAzAEUARgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAFMAYwBvAHAAZQAzAEEAcgByAGEAeQAsACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsACAAUwBvAHUAcgBjAGUALAAgAFMAbwB1AHIAYwBlAFIAbwB3ACwAXABuACAAIAAgACAASQBOAEQARQBYACgAUwBjAG8AcABlADMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAATQBBAFQAQwBIACgAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAAsACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsACAAMAApACwAXABuACAAIAAgACAAIAAgACAATQBBAFQAQwBIACgAUwBvAHUAcgBjAGUALAAgAFMAbwB1AHIAYwBlAFIAbwB3ACwAIAAwACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEcAZQB0AEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQARQBsAGUAbQBlAG4AdABGAHIAYQBjAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkACwAIABFAGwAZQBtAGUAbgB0ACwAIABDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEEAcgByAGEAeQAsACAAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABDAG8AbAB1AG0AbgAsACAARQBsAGUAbQBlAG4AdABSAG8AdwAsAFwAbgAgACAAIAAgAEkATgBEAEUAWAAoAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgAE0AQQBUAEMASAAoAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQALAAgAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQwBvAGwAdQBtAG4ALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABNAEEAVABDAEgAKABFAGwAZQBtAGUAbgB0ACwAIABFAGwAZQBtAGUAbgB0AFIAbwB3ACwAIAAwACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ASQBuAGQAaQByAGUAYwB0ACAAKABzAGMAbwBwAGUAIAAyACAAYQBuAGQAIABzAGMAbwBwAGUAIAAzACkAIABsAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBzACAAYQBzAHMAbwBjAGkAYQB0AGUAZAAgAHcAaQB0AGgAIAB0AGgAZQAgAGMAbwBuAHMAdQBtAHAAdABpAG8AbgAgAGEAbgBkACAAbABvAHMAcwBlAHMAIABvAGYAIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgAgAGEAYwBxAHUAaQByAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQAgAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwAgAGwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEkAbgBkAGkAcgBlAGMAdAAgACgAcwBjAG8AcABlACAAMgAgAGEAbgBkACAAcwBjAG8AcABlACAAMwApACAAbABvAGMAYQB0AGkAbwBuAC0AYgBhAHMAZQBkACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGEAcwBzAG8AYwBpAGEAdABlAGQAIAB3AGkAdABoACAAdABoAGUAIABjAG8AbgBzAHUAbQBwAHQAaQBvAG4AIABhAG4AZAAgAGwAbwBzAHMAZQBzACAAbwBmACAAcAB1AHIAYwBoAGEAcwBlAGQAIABvAHIAIABhAGMAcQB1AGkAcgBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAKQA7AFwAbgBcAG4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAAxAFwAIgApACkAOwBcAG4AXABuAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAYwBvAHAAZQAyAFMAYwBvAHAAZQAzAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMQAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALAAgAFQAZQByAHIAaQB0AG8AcgB5ACAAbwByACAAZwByAGkAZAAgAGQAZQBzAGMAcgBpAHAAdABpAG8AbgBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAyACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIALAAgAFwAIgBTAGMAbwBwAGUAIAAzACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgACgAawBnACAAQwBPADIALQBlAC8AawBXAGgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgADAALgA2ADQALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIAAwAC4ANwA4ACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgADAALgA2ADcALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgADAALgAyADIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdAAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABTAFcASQBTACkAXAAiACwAIAAwAC4ANQAwACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAZQByAG4AIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgATgBXAEkAUwApAFwAIgAsACAAMAAuADUANgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgADAALgAyADAALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQAgAC0AIABEAGEAcgB3AGkAbgAgAEsAYQB0AGgAZQByAGkAbgBlACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAEQASwBJAFMAKQBcACIALAAgADAALgA1ADYALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGEAdABpAG8AbgBhAGwAXAAiACwAIAAwAC4ANgAyACwAIAAwAC4AMAA3AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAATgBTAFcAIABhAG4AZAAgAEEAQwBUACAAcwBwAGwAaQB0ACAAaQBuAHQAbwAgAHMAZQBwAGEAcgBhAHQAZQAgAHIAbwB3AHMALgBcACIAKQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAxADAAOgAgAFMAYwBvAHAAZQAgADIAOgAgAEUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAFAAdQByAGMAaABhAHMAZQBkACAARQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwAxADAAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAyAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXABuAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4AUQBlAGwAZQBjACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkACAAOgAgAGsAVwBoAFwAbgBFAEYAMgAsAGUAbABlAGMAIAA6ACAATABvAGMAYQB0AGkAbwBuACAALQAgAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAAawBXAGgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABRAGUAbABlAGMALAAgAEUARgAyAGUAbABlAGMALABcAG4AIAAgACAAIABRAGUAbABlAGMAIAAqACAARQBGADIAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAG8AYwBhAHQAaQBvAG4ALQBiAGEAcwBlAGQAIABTAGMAbwBwAGUAIAAyACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAcAB1AHIAYwBoAGEAcwBlAGQAIABlAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQAyAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAAxADAALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgADIALgAyACAARQBzAHQAaQBtAGEAdABpAG4AZwAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHMAdABhAHQAaQBvAG4AYQByAHkAIABlAG4AZQByAGcAeQAgAHMAbwB1AHIAYwBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAMgAsAGUAbABlAGMAIAA9ACAAUQBlAGwAZQBjACAAKgAgAEUARgAyACwAZQBsAGUAYwAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBlAGwAZQBjAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAMgAsAGUAbABlAGMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAALQAgAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADIAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAAawBXAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIAUwBjAG8AcABlACAAMgBcACIALAAgAFwAIgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAyAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXABuAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcAG4AUQBlAGwAZQBjACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkACAAOgAgAGsAVwBoAFwAbgBFAEYAMwAsAGUAbABlAGMAIAA6ACAATABvAGMAYQB0AGkAbwBuACAALQAgAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAOgAgAGsAZwAgAEMATwAyAGUAIAAvACAAawBXAGgAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUQBlAGwAZQBjACwAIABFAEYAMwBlAGwAZQBjACwAXABuACAAIAAgACAAUQBlAGwAZQBjACAAKgAgAEUARgAzAGUAbABlAGMAIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEwAbwBjAGEAdABpAG8AbgAtAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABwAHUAcgBjAGgAYQBzAGUAZAAgAGUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AOQBfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADMARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQAzAGUAbABlAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIALQBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwA5AF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADEAMQAuADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIAAyAC4AMgAgAEUAcwB0AGkAbQBhAHQAaQBuAGcAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABzAHQAYQB0AGkAbwBuAGEAcgB5ACAAZQBuAGUAcgBnAHkAIABzAG8AdQByAGMAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwAxADEAXwA5AF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQAzACwAZQBsAGUAYwAgAD0AIABRAGUAbABlAGMAIAAqACAARQBGADMALABlAGwAZQBjACAAKgAgADEAMAAgAF4AIAAtACAAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AMQAxAF8AOQBfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADMARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBlAGwAZQBjAFwAIgAsACAAXAAiAEEAbQBvAHUAbgB0ACAAbwBmACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5ACAAcAB1AHIAYwBoAGEAcwBlAGQAIABmAHIAbwBtACAAdABoAGUAIABnAHIAaQBkAFwAIgAsACAAXAAiAGsAVwBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAMwAsAGUAbABlAGMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAALQAgAGIAYQBzAGUAZAAgAFMAYwBvAHAAZQAgADMAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAGUAIAAvACAAawBXAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIAUwBjAG8AcABlACAAMwBcACIALAAgAFwAIgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQQBwAHAAZQBuAGQAaQB4ACAAMgAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsAHMAOgAgAFQAYQBiAGwAZQAgADIAMwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAcwBcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAyADAAMgA1ACAALQAgAEEAcABwAGUAbgBkAGkAeAAgADIAIAAtACAAVABhAGIAbABlACAAMgAzAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzADkALAAgADUALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARwBhAHMAXAAiACwAIABcACIAQwBoAGUAbQBpAGMAYQBsACAAZgBvAHIAbQB1AGwAYQBcACIALAAgAFwAIgBHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgACgAQQBSADUAKQBcACIALAAgAFwAIgBHAGEAcwAgAC0AIABGAEMAIABuAGEAbQBlAFwAIgAsACAAXAAiAEEAZABpAHQAaQBvAG4AYQBsACAAZABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQBcACIALAAgAFwAIgBDAE8AMgBcACIALAAgADEALAAgAFwAIgBDAE8AMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGUAdABoAGEAbgBlAFwAIgAsACAAXAAiAEMASAA0AFwAIgAsACAAMgA4ACwAIABcACIAQwBIADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQBcACIALAAgAFwAIgBOADIATwBcACIALAAgADIANgA1ACwAIABcACIATgAyAE8AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGwAcABoAHUAcgAgAGgAZQB4AGEAZgBsAHUAbwByAGkAZABlAFwAIgAsACAAXAAiAFMARgA2AFwAIgAsACAAMgAzADUAMAAwACwAIABcACIAUwBGADYAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADMAIAAoAFIALQAyADMAKQBcACIALAAgAFwAIgBDAEgARgAzAFwAIgAsACAAIAAxADIANAAwADAALAAgAFwAIgBIAEYAQwAtADIAMwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADMAMgAgACgAUgAtADMAMgApAFwAIgAsACAAXAAiAEMASAAyAEYAMgBcACIALAAgADYANwA3ACwAIABcACIASABGAEMALQAzADIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQA0ADEAIAAoAFIALQA0ADEAKQBcACIALAAgAFwAIgBDAEgAMwBGAFwAIgAsACAAIAAxADEANgAsACAAXAAiAEgARgBDAC0ANAAxAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0ANAAzAC0AMQAwAG0AZQBlACAAKABSAC0ANAAzADEAMABtAGUAZQApAFwAIgAsACAAXAAiAEMANQBIADIARgAxADAAXAAiACwAIAAxADYANQAwACwAIABcACIASABGAEMALQA0ADMALQAxADAAbQBlAGUAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADIANQAgACgAUgAtADEAMgA1ACkAXAAiACwAIABcACIAQwAyAEgARgA1AFwAIgAsACAAIAAzADEANwAwACwAIABcACIASABGAEMALQAxADIANQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEAMwA0ACAAKABSAC0AMQAzADQAKQBcACIALAAgAFwAIgBDADIASAAyAEYANAAgACgAQwBIAEYAMgBDAEgARgAyACkAXAAiACwAIAAgADEAMQAyADAALAAgAFwAIgBIAEYAQwAtADEAMwA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMQAzADQAYQAgACgAUgAtADEAMwA0AGEAKQBcACIALAAgAFwAIgBDADIASAAyAEYANAAgACgAQwBIADIARgBDAEYAMwApAFwAIgAsACAAMQAzADAAMAAsACAAXAAiAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEANAAzACAAKABSAC0AMQA0ADMAKQBcACIALAAgAFwAIgBDADIASAAzAEYAMwAgACgAQwBIAEYAMgBDAEgAMgBGACkAXAAiACwAIAAzADIAOAAsACAAXAAiAEgARgBDAC0AMQA0ADMAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAxADQAMwBhACAAKABSAC0AMQA0ADMAYQApAFwAIgAsACAAXAAiAEMAMgBIADMARgAzACAAKABDAEYAMwBDAEgAMwApAFwAIgAsACAANAA4ADAAMAAsACAAXAAiAEgARgBDAC0AMQA0ADMAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADEANQAyAGEAIAAoAFIALQAxADUAMgBhACkAXAAiACwAIABcACIAQwAyAEgANABGADIAIAAoAEMASAAzAEMASABGADIAKQBcACIALAAgADEAMwA4ACwAIABcACIASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgAyADcAZQBhACAAKABSAC0AMgAyADcAZQBhACkAXAAiACwAIABcACIAQwAzAEgARgA3AFwAIgAsACAAMwAzADUAMAAsACAAXAAiAEgARgBDAC0AMgAyADcAZQBhAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgARgBDAC0AMgAzADYAZgBhACAAKABSAC0AMgAzADYAZgBhACkAXAAiACwAIABcACIAQwAzAEgAMgBGADYAXAAiACwAIAA4ADAANgAwACwAIABcACIASABGAEMALQAyADMANgBmAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADQANQBjAGEAIAAoAFIALQAyADQANQBjAGEAKQBcACIALAAgAFwAIgBDADMASAAzAEYANQBcACIALAAgADcAMQA2ACwAIABcACIASABGAEMALQAyADQANQBjAGEAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABGAEMALQAyADQANQBmAGEAIAAoAFIALQAyADQANQBmAGEAKQBcACIALAAgAFwAIgBDAEgARgAyAEMASAAyAEMARgAzAFwAIgAsACAAOAA1ADgALAAgAFwAIgBIAEYAQwAtADIANAA1AGYAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEYAQwAtADMANgA1AG0AZgBjACAAKABSAC0AMwA2ADUAbQBmAGMAKQBcACIALAAgAFwAIgBDAEgAMwBDAEYAMgBDAEgAMgBDAEYAMwBcACIALAAgADgAMAA0ACwAIABcACIASABGAEMALQAzADYANQBtAGYAYwBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMgAyACAAKABSAC0AMgAyACkAXAAiACwAIABcACIAQwBIAEMAbABGADIAXAAiACwAIAAxADcANgAwACwAIABcACIASABDAEYAQwAtADIAMgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQAyADMAIAAoAFIALQAxADIAMwApAFwAIgAsACAAXAAiAEMASABDAGwAMgAyAEMARgAzAFwAIgAsACAANwA5ACwAIABcACIASABDAEYAQwAtADEAMgAzAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAQwBGAEMALQAxADIANAAgACgAUgAtADEAMgA0ACkAXAAiACwAIABcACIAQwBIAEMAbABGAEMARgAzAFwAIgAsACAANQAyADcALAAgAFwAIgBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADEANAAxAGIAIAAoAFIALQAxADQAMQBiACkAXAAiACwAIABcACIAQwBIADMAQwBDAGwAMgBGAFwAIgAsACAANwA4ADIALAAgAFwAIgBIAEMARgBDAC0AMQA0ADEAYgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMQA0ADIAYgAgACgAUgAtADEANAAyAGIAKQBcACIALAAgAFwAIgBDAEgAMgBDAEMAbABGADIAXAAiACwAIAAxADkAOAAwACwAIABcACIASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABDAEYAQwAtADIAMgA1AGMAYQAgACgAUgAtADIAMgA1AGMAYQApAFwAIgAsACAAXAAiAEMASABDAGwAMgBDAEYAMgBDAEYAMwBcACIALAAgADEAMgA3ACwAIABcACIASABDAEYAQwAtADIAMgA1AGMAYQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAEMARgBDAC0AMgAyADUAYwBiACAAKABSAC0AMgAyADUAYwBiACkAXAAiACwAIABcACIAQwBIAEMAbABGAEMARgAyAEMAQwBJAEYAMgBcACIALAAgADUAMgA1ACwAIABcACIASABDAEYAQwAtADIAMgA1AGMAYgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADEANAAgAFAAZQByAGYAbAB1AG8AcgBvAG0AZQB0AGgAYQBuAGUAIAAoAHQAZQB0AHIAYQBmAGwAdQBvAHIAbwBtAGUAdABoAGEAbgBlACkAXAAiACwAIABcACIAQwBGADQAXAAiACwAIAA2ADYAMwAwACwAIABcACIAUABGAEMALQAxADQAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAxADEANgAgAFAAZQByAGYAbAB1AG8AcgBvAGUAdABoAGEAbgBlACAAKABoAGUAeABhAGYAbAB1AG8AcgBvAGUAdABoAGEAbgBlACkAXAAiACwAIABcACIAQwAyAEYANgBcACIALAAgADEAMQAxADAAMAAsACAAXAAiAFAARgBDAC0AMQAxADYAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABGAEMALQAyADEAOAAgAFAAZQByAGYAbAB1AG8AcgBvAHAAcgBvAHAAYQBuAGUAXAAiACwAIABcACIAQwAzAEYAOABcACIALAAgADgAOQAwADAALAAgAFwAIgBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMwAxAC0AMQAwACAAUABlAHIAZgBsAHUAbwByAG8AYgB1AHQAYQBuAGUAXAAiACwAIABcACIAQwA0AEYAMQAwAFwAIgAsACAAOQAyADAAMAAsACAAXAAiAFAARgBDAC0AMwAxAC0AMQAwAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AMwAxADgAIABQAGUAcgBmAGwAdQBvAHIAbwBjAHkAYwBsAG8AYgB1AHQAYQBuAGUAXAAiACwAIABcACIAYwAtAEMANABGADgAXAAiACwAIAA5ADUANAAwACwAIABcACIAUABGAEMALQAzADEAOABcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAEYAQwAtADQAMQAtADEAMgAgAFAAZQByAGYAbAB1AG8AcgBvAHAAZQBuAHQAYQBuAGUAXAAiACwAIABcACIAQwA1AEYAMQAyAFwAIgAsACAAOAA1ADUAMAAsACAAXAAiAFAARgBDAC0ANAAxAC0AMQAyAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0ANQAxAC0AMQA0ACAAUABlAHIAZgBsAHUAbwByAG8AaABlAHgAYQBuAGUAXAAiACwAIABcACIAQwA2AEYAMQA0AFwAIgAsACAANwA5ADEAMAAsACAAXAAiAFAARgBDAC0ANQAxAC0AMQA0AFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAARgBDAC0AOQAxAC0AMQA4ACAAUABlAHIAZgBsAHUAbgBhAGYAZQBuAGUAXAAiACwAIABcACIAQwAxADAARgAxADgAXAAiACwAIAA3ADEAOQAwACwAIABcACIAUABGAEMALQA5ADEALQAxADgAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADIAXAAiACwAIABcACIAQwBDAGwAMgBGADIAXAAiACwAIAAxADAAMgAwADAALAAgAFwAIgBDAEYAQwAtADEAMgBcACIALAAgAFwAIgBJAFAAQwBDACAARwBsAG8AYgBhAGwAIABXAGEAcgBtAGkAbgBnACAAUABvAHQAZQBuAHQAaQBhAGwAIABWAGEAbAB1AGUAcwAgAHYAMgAuADAAIAAtACAAKABBAFIANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMARgBDAC0AMQAzAFwAIgAsACAAXAAiAEMAQwBsAEYAMwBcACIALAAgADEAMwA5ADAAMAAsACAAXAAiAEMARgBDAC0AMQAzAFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBGAEMALQAxADEANABcACIALAAgAFwAIgBDAEMAbABGADIAQwBDAGwARgAyAFwAIgAsACAAOAA1ADkAMAAsACAAXAAiAEMARgBDAC0AMQAxADQAXAAiACwAIABcACIASQBQAEMAQwAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsACAAVgBhAGwAdQBlAHMAIAB2ADIALgAwACAALQAgACgAQQBSADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAEYAQwAtADEAMQA1AFwAIgAsACAAXAAiAEMAQwBsAEYAMgBDAEYAMwBcACIALAAgADcANgA3ADAALAAgAFwAIgBDAEYAQwAtADEAMQA1AFwAIgAsACAAXAAiAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABHAFcAUABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AEcAQQBTACAALQAgAEYAQwAgAG4AYQBtAGUAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIAB0AHIAdQBuAGMAYQB0AGUAZAAgAGcAYQBzACAAbgBhAG0AZQAgAHQAbwAgAGEAbABsAG8AdwAgAG0AYQB0AGMAaABpAG4AZwAgAHcAaQB0AGgAIABvAHQAaABlAHIAIAB0AGEAYgBsAGUAcwAuACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAZwBhAHMAZQBzACAAZgByAG8AbQAgAEkAUABDAEMAIABHAGwAbwBiAGEAbAAgAFcAYQByAG0AaQBuAGcAIABQAG8AdABlAG4AdABpAGEAbAAgAFYAYQBsAHUAZQBzACAAdgAyAC4AMAAgAC0AIAAoAEEAUgA1ACkALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AEEAZABkAGkAdABpAG8AbgBhAGwAIABkAGEAdABhACAAcwBvAHUAcgBjAGUAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAuAFwAIgApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQQBwAHAAZQBuAGQAaQB4ACAAMgAgAEcAbABvAGIAYQBsACAAVwBhAHIAbQBpAG4AZwAgAFAAbwB0AGUAbgB0AGkAYQBsAHMAOgAgAEIAbABlAG4AZABlAGQAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBCAGwAZQBuAGQAZQBkACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAIAAoAG0AYQBuAHkAIABjAG8AbgB0AGEAaQBuAGkAbgBnACAASABGAEMAUwAgAGEAbgBkAC8AbwByACAAUABGAEMAUwApAFwAIgApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEIAbABlAG4AZABzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAQQBwAHAAZQBuAGQAaQB4ACAAMgAgAC0AIABUAGEAYgBsAGUAIAAyADQAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUAMQAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGwAZQBuAGQAXAAiACwAIABcACIAQwBvAG4AcwB0AGkAdAB1AGUAbgB0AHMAXAAiACwAIABcACIAQwBvAG0AcABvAHMAaQB0AGkAbwBuACAAKAAlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAwAFwAIgAsACAAXAAiAEMARgBDAC0AMQAyAC8AQwBGAEMALQAxADEANABcACIALAAgAFwAIgBSAC0ANAAwADAAIABjAGEAbgAgAGgAYQB2AGUAIAB2AGEAcgBpAG8AdQBzACAAcAByAG8AcABvAHIAdABpAG8AbgBzACAAbwBmACAAQwBGAEMALQAxADIAIABhAG4AZAAgAEMARgBDAC0AMQAxADQALgAgAFQAaABlACAAZQB4AGEAYwB0ACAAYwBvAG0AcABvAHMAaQB0AGkAbwBuACAAbgBlAGUAZABzACAAdABvACAAYgBlACAAcwBwAGUAYwBpAGYAaQBlAGQALAAgAGUALgBnAC4ALAAgAFIALQA0ADAAMAAgACgANgAwAC8ANAAwACkALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADEAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEAMgA0AFwAIgAsACAAXAAiACgANQAzAC4AMAAvADEAMwAuADAALwAzADQALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAxAEIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQAvAEgAQwBGAEMALQAxADIANABcACIALAAgAFwAIgAoADYAMQAuADAALwAxADEALgAwAC8AMgA4AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMQBDAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEALwBIAEMARgBDAC0AMQAyADQAXAAiACwAIABcACIAKAAzADMALgAwAC8AMQA1AC4AMAAvADUAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADIAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiACgANgAwAC4AMAAvADIALgAwAC8AMwA4AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAMgBCAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIAXAAiACwAIABcACIAKAAzADgALgAwAC8AMgAuADAALwA2ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAAzAEEAXAAiACwAIABcACIASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAC8AUABGAEMALQAyADEAOABcACIALAAgAFwAIgAoADUALgAwAC8ANwA1AC4AMAAvADIAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAwADMAQgBcACIALAAgAFwAIgBIAEMALQAyADkAMAAvAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AFwAIgAsACAAXAAiACgANQAuADAALwA1ADYALgAwAC8AMwA5AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANABBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEANAAzAGEALwBIAEYAQwAtADEAMwA0AGEAXAAiACwAIABcACIAKAA0ADQALgAwAC8ANQAyAC4AMAAvADQALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA1AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvACAASABGAEMALQAxADUAMgBhAC8ASABDAEYAQwAtADEANAAyAGIALwBQAEYAQwAtADMAMQA4AFwAIgAsACAAXAAiACgANAA1AC4AMAAvADcALgAwAC8ANQAuADUALwA0ADIALgA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMAA2AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEgAQwAtADYAMAAwAGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADUANQAuADAALwAxADQALgAwAC8ANAAxAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANwBBAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADIAMAAuADAALwA0ADAALgAwAC8ANAAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANwBCAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADEAMAAuADAALwA3ADAALgAwAC8AMgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANwBDAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADIAMwAuADAALwAyADUALgAwAC8ANQAyAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANwBEAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADEANQAuADAALwAxADUALgAwAC8ANwAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAANwBFAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADIANQAuADAALwAxADUALgAwAC8ANgAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAOABBAFwAIgAsACAAXAAiAEgARgBDAC0AMQAyADUALwBIAEYAQwAtADEANAAzAGEALwBIAEMARgBDAC0AMgAyAFwAIgAsACAAXAAiACgANwAuADAALwA0ADYALgAwAC8ANAA3AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAOQBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEMARgBDAC0AMQAyADQALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADYAMAAuADAALwAyADUALgAwAC8AMQA1AC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADAAOQBCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEMARgBDAC0AMQAyADQALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADYANQAuADAALwAyADUALgAwAC8AMQAwAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMABBAFwAIgAsACAAXAAiAEgARgBDAC0AMwAyAC8ASABGAEMALQAxADIANQBcACIALAAgAFwAIgAoADUAMAAuADAALwA1ADAALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAwAEIAXAAiACwAIABcACIASABGAEMALQAzADIALwBIAEYAQwAtADEAMgA1AFwAIgAsACAAXAAiACgANAA1AC4AMAAvADUANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADEAQQBcACIALAAgAFwAIgBIAEMALQAxADIANwAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADEALgA1AC8AOAA3AC4ANQAvADEAMQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADEAQgBcACIALAAgAFwAIgBIAEMALQAxADIANwAwAC8ASABDAEYAQwAtADIAMgAvAEgARgBDAC0AMQA1ADIAYQBcACIALAAgAFwAIgAoADMALgAwAC8AOQA0AC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAxAEMAXAAiACwAIABcACIASABDAC0AMQAyADcAMAAvAEgAQwBGAEMALQAyADIALwBIAEYAQwAtADEANQAyAGEAXAAiACwAIABcACIAKAAzAC4AMAAvADkANQAuADUALwAxAC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEAMgBBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBQAEYAQwAtADIAMQA4AC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA3ADAALgAwAC8ANQAuADAALwAyADUALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQAzAEEAXAAiACwAIABcACIAUABGAEMALQAyADEAOAAvAEgARgBDAC0AMQAzADQAYQAvAEgAQwAtADYAMAAwAGEAXAAiACwAIABcACIAKAA5AC4AMAAvADgAOAAuADAALwAzAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANABBAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEMARgBDAC0AMQAyADQALwBIAEMALQA2ADAAMABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA1ADEALgAwAC8AMgA4AC4ANQAvADQALgAwAC8AMQA2AC4ANQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA0ADEANABCAFwAIgAsACAAXAAiAEgAQwBGAEMALQAyADIALwBIAEMARgBDAC0AMQAyADQALwBIAEMALQA2ADAAMABhAC8ASABDAEYAQwAtADEANAAyAGIAXAAiACwAIABcACIAKAA1ADAALgAwAC8AMwA5AC4AMAAvADEALgA1AC8AOQAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADUAQQBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAOAAyAC4AMAAvADEAOAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADUAQgBcACIALAAgAFwAIgBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMgA1AC4AMAAvADcANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADYAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMwA0AGEALwBIAEMARgBDAC0AMQAyADQALwBIAEMALQA2ADAAMABcACIALAAgAFwAIgAoADUAOQAuADAALwAzADkALgA1AC8AMQAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADcAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABDAC0ANgAwADAAXAAiACwAIABcACIAKAA0ADYALgA2AC8ANQAwAC4AMAAvADMALgA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMQA4AEEAXAAiACwAIABcACIASABDAC0AMgA5ADAALwBIAEMARgBDAC0AMgAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgAMQAuADUALwA5ADYALgAwAC8AMgAuADUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAxADkAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADMANABhAC8ASABFAC0ARQAxADcAMABcACIALAAgAFwAIgAoADcANwAuADAALwAxADkALgAwAC8ANAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANAAyADAAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMwA0AGEALwBIAEMARgBDAC0AMQA0ADIAYgBcACIALAAgAFwAIgAoADgAOAAuADAALwAxADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMgAxAEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQBcACIALAAgAFwAIgAoADUAOAAuADAALwA0ADIALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMgAyAEEAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgAQwAtADYAMAAwAGEAXAAiACwAIABcACIAKAA4ADUALgAxAC8AMQAxAC4ANQAvADMALgA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMgAyAEIAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgAQwAtADYAMAAwAGEAXAAiACwAIABcACIAKAA1ADUALgAwAC8ANAAyAC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADQAMgAyAEMAXAAiACwAIABcACIASABGAEMALQAxADIANQAvAEgARgBDAC0AMQAzADQAYQAvAEgAQwAtADYAMAAwAGEAXAAiACwAIABcACIAKAA4ADIALgAwAC8AMQA1AC4AMAAvADMALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAAwAFwAIgAsACAAXAAiAEMARgBDAC0AMQAyAC8ASABGAEMALQAxADUAMgBhAFwAIgAsACAAXAAiACgANwAzAC4AOAAvADIANgAuADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEMARgBDAC0AMQAyAFwAIgAsACAAXAAiACgANwA1AC4AMAAvADIANQAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADIAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAEMARgBDAC0AMQAxADUAXAAiACwAIABcACIAKAA0ADgALgA4AC8ANQAxAC4AMgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAMwBcACIALAAgAFwAIgBIAEYAQwAtADIAMwAvAEMARgBDAC0AMQAzAFwAIgAsACAAXAAiACgANAAwAC4AMQAvADUAOQAuADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADQAXAAiACwAIABcACIASABGAEMALQAzADIALwBDAEYAQwAtADEAMQA1AFwAIgAsACAAXAAiACgANAA4AC4AMgAvADUAMQAuADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADUAXAAiACwAIABcACIAQwBGAEMALQAxADIALwBIAEMARgBDAC0AMwAxAFwAIgAsACAAXAAiACgANwA4AC4AMAAvADIAMgAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADYAXAAiACwAIABcACIAQwBGAEMALQAzADEALwBDAEYAQwAtADEAMQA0AFwAIgAsACAAXAAiACgANQA1AC4AMQAvADQANAAuADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADcAQQBcACIALAAgAFwAIgBIAEYAQwAtADEAMgA1AC8ASABGAEMALQAxADQAMwBhAFwAIgAsACAAXAAiACgANQAwAC4AMAAvADUAMAAuADAAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAC0ANQAwADgAQQBcACIALAAgAFwAIgBIAEYAQwAtADIAMwAvAFAARgBDAC0AMQAxADYAXAAiACwAIABcACIAKAAzADkALgAwAC8ANgAxAC4AMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIALQA1ADAAOABCAFwAIgAsACAAXAAiAEgARgBDAC0AMgAzAC8AUABGAEMALQAxADEANgBcACIALAAgAFwAIgAoADQANgAuADAALwA1ADQALgAwACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgAtADUAMAA5AEEAXAAiACwAIABcACIASABDAEYAQwAtADIAMgAvAFAARgBDAC0AMgAxADgAXAAiACwAIABcACIAKAA0ADQALgAwAC8ANQA2AC4AMAApAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAGMAaABhAG4AZwBlAGQAIABIAEMANgAwADAAYQAgAHQAbwAgAEgAQwAtADYAMAAwAGEAIABmAG8AcgAgAGIAbABlAG4AZAAgAFIALQA0ADEANABCAC4AIABGAGkAeABlAGQAIAB0AHkAcABvACAAZgBvAHIAIABiAGwAZQBuAGQAIABSAC0ANAAwADUAQQAgAC0AIABDAGgAYQBuAGcAZQBkACAASABDAEYAQwAxADQAMgBiACAAdABvACAASABDAEYAQwAtADEANAAyAGIALgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBMAGUAYQBrAGEAZwBlACAAcgBhAHQAZQBzACAAZgBvAHIAIABjAG8AbQBtAG8AbgAgAHIAZQBmAHIAaQBnAGUAcgBhAHQAaQBvAG4AIABhAG4AZAAgAGEAaQByAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAGQAaQBjAGEAdABpAHYAZQAgAGwAZQBhAGsAYQBnAGUAIAByAGEAdABlAHMAIABmAG8AcgAgAGMAbwBtAG0AbwBuACAAcgBlAGYAcgBpAGcAZQByAGEAdABpAG8AbgAgAGEAbgBkACAAYQBpAHIAIAAtACAAYwBvAG4AZABpAHQAaQBvAG4AaQBuAGcAIABlAHEAdQBpAHAAbQBlAG4AdABcACIAKQApADsAXABuAFwAbgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABBAGMAYwBvAHUAbgB0AHMAIABGAGEAYwB0AG8AcgBzACAAMgAwADIANQAgAC0AIABUAGEAYgBsAGUAIAAxADAAXAAiACkAKQA7AFwAbgBcAG4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAxACwAIAAyACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIABsAGUAYQBrAGEAZwBlACAAcgBhAHQAZQAgACgAJQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAHIAZQBmAHIAaQBnAGUAcgBhAHQAbwByAHMAXAAiACwAIAAxAC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAG4AcwBwAG8AcgB0ACAAcgBlAGYAcgBpAGcAZQByAGEAdABpAG8AbgBcACIALAAgADEANQAuADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAIABBAC8AQwAgAHAAbwByAHQAYQBiAGwAZQBcACIALAAgADIALgA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAG0AZQBzAHQAaQBjACAAQQAvAEMAIABzAHAAbABpAHQAXAAiACwAIAAzAC4ANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwAgAEEALwBDACAAcABhAGMAawBhAGcAZQBkAFwAIgAsACAAMgAuADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAZwBoAHQAIAB2AGUAaABpAGMAbABlACAAQQAvAEMAXAAiACwAIAA2AC4ANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAZQBhAHYAeQAgAHYAZQBoAGkAYwBsAGUAIABBAC8AQwBcACIALAAgADEAMAAuADgAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AOQA6ACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AOQAuADEAIABSAGUAZgByAGkAZwBlAHIAYQBuAHQAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBcAG4AVABoAGUAIAB0AG8AdABhAGwAIABlAG0AaQBzAHMAaQBvAG4AcwAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAGwAZQBhAGsAaQBuAGcAIABkAHUAcgBpAG4AZwAgAG8AcABlAHIAYQB0AGkAbwBuACAAKABuAG8AdAAgAGQAdQByAGkAbgBnACAAaQBuAHMAdABhAGwAbABhAHQAaQBvAG4AIABvAHIAIABkAGkAcwBwAG8AcwBhAGwAKQBcAG4ARwBXAFAAUgAgADoAIABHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAG8AZgAgAHIAZQBmAHIAaQBnAGUAcgBhAG4AdAAgAFIAIAA6ACAARABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AYwBoAGEAcgBnAGUAUgBhACAAOgAgAEEAbQBvAHUAbgB0ACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgAgAGMAbwBuAHQAYQBpAG4AZQBkACAAaQBuACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAOgAgAGsAZwBcAG4AbABlAGEAawBhAGcAZQByAGEAdABlAGEAIAA6ACAAUAByAGMAZQBuAHQAYQBnAGUAIABvAGYAIAB0AG8AdABhAGwAIABjAGgAYQByAGcAZQAgAGwAZQBhAGsAZQBkACAAZgByAG8AbQAgAGEAcABwAGwAaQBhAG4AYwBlACAAYQAgAGUAYQBjAGgAIAB5AGUAYQByACAAOgAgAFAAZQByAGMAZQBuAHQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEcAVwBQAFIALAAgAGMAaABhAHIAZwBlAFIAYQAsACAAbABlAGEAawBhAGcAZQByAGEAdABlAGEALABcAG4AIAAgACAAIABHAFcAUABSACAAKgAgAGMAaABhAHIAZwBlAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBhAC8AMQAwADAAKQAgACoAIAAxADAAIABeACAALQAgADMAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAaABlACAAdABvAHQAYQBsACAAZQBtAGkAcwBzAGkAbwBuAHMAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABsAGUAYQBrAGkAbgBnACAAZAB1AHIAaQBuAGcAIABvAHAAZQByAGEAdABpAG8AbgAgACgAbgBvAHQAIABkAHUAcgBpAG4AZwAgAGkAbgBzAHQAYQBsAGwAYQB0AGkAbwBuACAAbwByACAAZABpAHMAcABvAHMAYQBsACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADkALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgADIAMAAyADUAIAAtACAAMwAuADEAIABFAHMAdABpAG0AYQB0AGkAbgBnACAAaQBuAGQAdQBzAHQAcgBpAGEAbAAgAHAAcgBvAGMAZQBzAHMAZQBzACAAZQBtAGkAcwBzAGkAbwBuAHMAIAAtACAAUgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAbABlAGEAawBhAGcAZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBHAFcAUABSACAAKgAgAGMAaABhAHIAZwBlAFIAYQAgACoAIAAoAGwAZQBhAGsAYQBnAGUAcgBhAHQAZQBhAC8AMQAwADAAKQAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABSAFwAIgAsACAAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAbwBmACAAcgBlAGYAcgBpAGcAZQByAGEAbgB0ACAAUgBcACIALAAgAFwAIgBEAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAGgAYQByAGcAZQBSAGEAXAAiACwAIABcACIAQQBtAG8AdQBuAHQAIABvAGYAIAByAGUAZgByAGkAZwBlAHIAYQBuAHQAIABSACAAYwBvAG4AdABhAGkAbgBlAGQAIABpAG4AIABhAHAAcABsAGkAYQBuAGMAZQAgAGEAXAAiACwAIABcACIAawBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBsAGUAYQBrAGEAZwBlAHIAYQB0AGUAYQBcACIALAAgAFwAIgBQAHIAYwBlAG4AdABhAGcAZQAgAG8AZgAgAHQAbwB0AGEAbAAgAGMAaABhAHIAZwBlACAAbABlAGEAawBlAGQAIABmAHIAbwBtACAAYQBwAHAAbABpAGEAbgBjAGUAIABhACAAZQBhAGMAaAAgAHkAZQBhAHIAXAAiACwAIABcACIAUABlAHIAYwBlAG4AdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYQBcACIALAAgAFwAIgBBAHAAcABsAGkAYQBuAGMAZQBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBcACIALAAgAFwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAXAAiACwAIABcACIAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADEAIABJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABhAGwAbAAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAcwAgAGYAIAB0AG8AIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzAFwAbgBFAE4AMgBPAFwAbgB0ACAAQwBPADIALQBlAFwAbgBNAE4AagBmACAAOgAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABpAG4AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqACAAOgAgAGsAZwAgAE4AXABuAEUARgBqAE4AMgBPACAAOgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcAG4AQwBnAE4AMgBPACAAOgAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAGoAIAA6ACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAbgBmACAAOgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXABuAEcAVwBQAE4AMgBPACAAOgAgAGcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAOgAgAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPAFwAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBHAFcAUABcAG4AIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBOADIATwAsAEcAVwBQAE4AMgBPACwAXABuACAAIAAgACAAIAAoAEUATgAyAE8AIAAqACAARwBXAFAATgAyAE8AKQBcAG4AIAAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBqAGYALAAgAEUARgBqAE4AMgBPACwAIABDAGcATgAyAE8ALABcAG4AIAAgACAAIABNAE4AagBmACAAKgAgAEUARgBqAE4AMgBPACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAIABeAC0AMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGEAbABsACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAHQAbwAgAGEAbABsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAC0AZQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQAsACAAMgAwADIAMwA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBBAF8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwAgAD0AIABNAE4AagBmACAAKgAgAEUARgBqAE4AMgBPACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAGoAZgBcACIALABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGkAbgAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAIAA6ACAAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGoATgAyAE8AXAAiACwAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACAAYQBwAHAAbABpAGUAZABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBnAE4AMgBPAFwAIgAsAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAOgAgAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAE4AMgBPAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABcAG4ATQBOAGoAZgBcAG4AawBnACAATgBcAG4AVABNAGoAZgAgADoAIABUAG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagAgADoAIABrAGcAXABuAEYATgBpAG4AbwByAGcAYQBuAGkAYwBmACAAOgAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAOgAgAGsAZwAgAE4ALwBrAGcAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABNAGoAZgAsACAARgBOAGkAbgBvAHIAZwBhAG4AaQBjAGYALABcAG4AIAAgACAAIABUAE0AagBmACAAKgAgAEYATgBpAG4AbwByAGcAYQBuAGkAYwBmAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADEALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQAsACAAMgAwADIAMwA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwAuAEQALgBBAF8AMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBqAGYAIAA9ACAAVABNAGoAZgAgACoAIABGAE4AaQBuAG8AcgBnAGEAbgBpAGMAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABNAGoAZgBcACIALABcACIAVABvAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAIAA6ACAAawBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAE4AaQBuAG8AcgBnAGEAbgBpAGMAZgBcACIALABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIAA6ACAAawBnACAATgAvAGsAZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAG4AbwByAGcAYQBuAGkAYwBcACIALAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAFUAcgBlAGEARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAEMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcgBlAHMAdQBsAHQAaQBuAGcAIABmAHIAbwBtACAAdABoAGUAIAB1AHMAZQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACwAIAB1AHIAZQBhAC0AYgBhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAbgBFAGoAZgBDAE8AMgBcAG4AdAAgAEMATwAyAFwAbgBNAFUAagBmACAAOgAgAG0AYQBzAHMAIABvAGYAIAB1AHIAZQBhACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagAgADoAIABrAGcAIAB1AHIAZQBhAFwAbgBFAEYAdQByAGUAYQBDAE8AMgAgADoAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBhAHIAYgBvAG4AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHIAZQBhAC0AYgBhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzACAAOgAgAGsAZwAgAEMALwBrAGcAIAB1AHIAZQBhACAAXABuAEMAZwBDAE8AMgAgADoAIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABjAGEAcgBiAG8AbgAgAGQAaQBvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAA6ACAAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AVQBqAGYALAAgAEUARgB1AHIAZQBhAEMATwAyACwAIABDAGcAQwBPADIALABcAG4AIAAgACAAIABNAFUAagBmACAAKgAgAEUARgB1AHIAZQBhAEMATwAyACAAKgAgAEMAZwBDAE8AMgAgACoAIAAxADAAIABeAC0AMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8AVQByAGUAYQBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIAByAGUAcwB1AGwAdABpAG4AZwAgAGYAcgBvAG0AIAB0AGgAZQAgAHUAcwBlACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMALAAgAHUAcgBlAGEALQBiAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAGoAZgBDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAFUAcgBlAGEARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBPADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8AVQByAGUAYQBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxACwAIAAyADAAMgAzADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ASABfADEAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBqAGYAQwBPADIAIAA9ACAATQBVAGoAZgAgAHgAIABFAEYAdQByAGUAYQBDAE8AMgAgAHgAIABDAGcAQwBPADIAIAB4ACAAMQAwAF4ALQAzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8AVQByAGUAYQBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAXwB7AGoAZgAsAEMATwAyAH0APQB7AE0AVQB9AF8AewBqAGYAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewB1AHIAZQBhACwAQwBPADIAfQBcAFwAIABcAFwAdABpAG0AZQBzAFwAXAAgAEMAXwB7AGcALABDAE8AMgB9AFwAXAB0AGkAbQBlAHMAewAxADAAfQBeAHsALQAzAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAFUAagBmAFwAIgAsAFwAIgBNAGEAcwBzACAAbwBmACAAdQByAGUAYQAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAIAA6ACAAawBnACAAdQByAGUAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAHUAcgBlAGEAQwBPADIAXAAiACwAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAGEAcgBiAG8AbgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHUAcgBlAGEALQBiAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIAA6ACAAawBnACAAQwAvAGsAZwAgAHUAcgBlAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAZwBDAE8AMgBcACIALABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALABcACIARgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAFwAbgBNAGEAcwBzACAAbwBmACAAdQByAGUAYQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAXABuAE0AVQBqAGYAXABuAGsAZwAgAHUAcgBlAGEAXABuAFQATQBqAGYAIAA6ACAAdABoAGUAIAB0AG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagAgADoAIABrAGcAXABuAEYAVQBmACAAOgAgAHQAaABlACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdQByAGUAYQAgAGkAbgAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgADoAIABrAGcAIAB1AHIAZQBhAC8AawBnAFwAbgBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAE0AagBmACwAIABGAFUAZgAsAFwAbgAgACAAIAAgAFQATQBqAGYAIAAqACAARgBVAGYAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAdQByAGUAYQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBVAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAdQByAGUAYQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAxAC4AMQAuADMALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AVQBqAGYAIAA9ACAAVABNAGoAZgAgANcAIABGAFUAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAE0AagBmAFwAIgAsAFwAIgB0AGgAZQAgAHQAbwB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABqACAAOgAgAGsAZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBVAGYAXAAiACwAXAAiAHQAaABlACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdQByAGUAYQAgAGkAbgAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgADoAIABrAGcAIAB1AHIAZQBhAC8AawBnAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGoAXAAiACwAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAZgBcACIALABcACIARgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUAOgAgAEYAZQByAHQAaQBsAGkAcwBlAHIAIABVAHMAZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1AC4AMgAgAE8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIABmAG8AcgAgAGEAbABsACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcAG4ARQBOADIATwBcAG4AdAAgAEMATwAyAC0AZQBcAG4ATQBOAFMAbwBpAGwAagBmACAAOgAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGkAbgAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAIAA6ACAAawBnACAATgBcAG4ARQBGAGkATgAyAE8AIAA6ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGQAaQByAGUAYwB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAbgBDAGcATgAyAE8AIAA6ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwA6ACAAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AagAgADoAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXABuAGYAIAA6ACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAbgBpACAAOgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAbgBHAFcAUABOADIATwAgADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgADoAIAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBHAFcAUABcAG4AIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARQBOADIATwAsAEcAVwBQAE4AMgBPACwAXABuACAAIAAgACAAIAAoAEUATgAyAE8AIAAqACAARwBXAFAATgAyAE8AKQBcAG4AIAAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAFMAbwBpAGwAagBmACwAIABFAEYAaQBOADIATwAsACAAQwBnAE4AMgBPACwAXABuACAAIAAgACAATQBOAFMAbwBpAGwAagBmACAAKgAgAEUARgBpAE4AMgBPACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAIABeAC0AMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAZgBvAHIAIABhAGwAbAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBzACAAZgAgAGEAbgBkACAAYQBsAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwAgAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgAtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAyAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxACwAIAAyADAAMgAzADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ARAAuAEEAXwA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AIAA9ACAATQBOAFMAbwBpAGwAagBmACAAKgAgAEUARgBpAE4AMgBPACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AUwBvAGkAbABqAGYAXAAiACwAIABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagAgADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAaQBOADIATwBcACIALAAgAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAZABpAHIAZQBjAHQAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAOgAgAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAZwBOADIATwBcACIALABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgADoAIABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBqAFwAIgAsAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGYAXAAiACwAXAAiAE8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAVwBQAE4AMgBPAFwAIgAsAFwAIgBHAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgADoAIAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAgACAALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcAB1AHIAYwBoAGEAcwBlAGQAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwBcAG4ATQBOAFMAbwBpAGwAagBmAFwAbgBrAGcAXABuAE0AbwByAGcAYQBuAGkAYwBqAGYAIAA6ACAAbQBhAHMAcwAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzACAAaQBuACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagAgADoAIABrAGcAXABuAEYATgBvAHIAZwBhAG4AaQBjAGYAIAA6ACAAbgBpAHQAcgBvAGcAZQBuACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgAgADoAIABrAGcAIABOAC8AawBnAFwAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBvAHIAZwBhAG4AaQBjAGoAZgAsACAARgBOAG8AcgBnAGEAbgBpAGMAZgAsAFwAbgAgACAAIAAgAE0AbwByAGcAYQBuAGkAYwBqAGYAIAAqACAARgBOAG8AcgBnAGEAbgBpAGMAZgBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAHUAcgBjAGgAYQBzAGUAZAAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATgBTAG8AaQBsAGoAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBOAFMAbwBpAGwAagBmACAAPQAgAE0AbwByAGcAYQBuAGkAYwBqAGYAIAAqACAARgBOAG8AcgBnAGEAbgBpAGMAZgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG8AcgBnAGEAbgBpAGMAagBmAFwAIgAsACAAXAAiAG0AYQBzAHMAIABvAGYAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAeQBwAGUAIABmACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgAGkAbgAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAGoAIAA6ACAAawBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAE4AbwByAGcAYQBuAGkAYwBmAFwAIgAsACAAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdAB5AHAAZQAgAGYAIAA6ACAAawBnACAATgAvAGsAZwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQA6ACAARgBlAHIAdABpAGwAaQBzAGUAcgAgAFUAcwBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADUALgAzACAATABpAG0AZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAFQAaABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAYQBuAGQAIABkAG8AbABvAG0AaQB0AGUAIAB0AG8AIABzAG8AaQBsAHMAXABuAEUAbABpAG0AZQBcAG4AdAAgAEMATwAyAFwAbgBNAGwAaQBtAGUAIAA6ACAAdABoAGUAIAB0AG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbABpAG0AZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIAA6ACAAawBnAFwAbgBGAHIAYQBjAEwAaQBtAGUAIAA6ACAAdABoAGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAYQBzACAAbABpAG0AZQBzAHQAbwBuAGUAIAAoAEMAYQBDAE8AMwApACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAFAAbABpAG0AZQAgADoAIABmAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABsAGkAbQBlAHMAdABvAG4AZQAgADoAIABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAbgBFAEYAbABpAG0AZQAgADoAIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABpAG0AZQBzAHQAbwBuAGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAOgAgAGsAZwAgAEMALwBrAGcAXABuAEYAcgBhAGMARABvAGwAIAA6ACAAdABoAGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAYQBzACAAZABvAGwAbwBtAGkAdABlACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXABuAFAAUABkAG8AbAAgADoAIABmAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABkAG8AbABvAG0AaQB0AGUAIAA6ACAAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4ARQBGAGQAbwBsACAAOgAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAG8AbABvAG0AaQB0AGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAOgAgAGsAZwAgAEMALwBrAGcAXABuAFwAbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBsAGkAbQBlACwAIABGAHIAYQBjAEwAaQBtAGUALAAgAFAAbABpAG0AZQAsACAARQBGAGwAaQBtAGUALAAgAEYAcgBhAGMARABvAGwALAAgAFAAZABvAGwALAAgAEUARgBkAG8AbAAsACAAQwBnAEMATwAyACwAXABuACAAIAAgACAAKAAoAE0AbABpAG0AZQAgACoAIAAgAEYAcgBhAGMATABpAG0AZQAgACoAIABQAGwAaQBtAGUAIAAqACAARQBGAGwAaQBtAGUAKQAgACsAIAAoAE0AbABpAG0AZQAgACoAIABGAHIAYQBjAEQAbwBsACAAKgAgAFAAZABvAGwAIAAqACAARQBGAGQAbwBsACkAKQAgACoAIABDAGcAQwBPADIAIAAqACAAMQAwAF4ALQAzAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABoAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAG8AZgAgAGwAaQBtAGUAIABhAG4AZAAgAGQAbwBsAG8AbQBpAHQAZQAgAHQAbwAgAHMAbwBpAGwAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAGwAaQBtAGUAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAE8AMgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADUALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQAsACAAMgAwADIAMwA6ACAARQBxAHUAYQB0AGkAbwBuACAAMwBHAF8AMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBsAGkAbQBlACAAPQAgACgAKABNAGwAaQBtAGUAIAAqACAAIABGAHIAYQBjAEwAaQBtAGUAIAAqACAAUABsAGkAbQBlACAAKgAgAEUARgBsAGkAbQBlACkAIAArACAAKABNAGwAaQBtAGUAIAAqACAARgByAGEAYwBEAG8AbAAgACoAIABQAGQAbwBsACAAKgAgAEUARgBkAG8AbAApACkAIAAqACAAQwBnAEMATwAyACAAKgAgADEAMABeAC0AMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGwAaQBtAGUAXAAiACwAIABcACIAVABoAGUAIAB0AG8AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbABpAG0AZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIAA6ACAAawBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwAaQBtAGUAXAAiACwAIABcACIAVABoAGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAYQBzACAAbABpAG0AZQBzAHQAbwBuAGUAIAAoAEMAYQBDAE8AMwApACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAbABpAG0AZQBcACIALAAgAFwAIgBGAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABsAGkAbQBlAHMAdABvAG4AZQAgADoAIABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABpAG0AZQBcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABpAG0AZQBzAHQAbwBuAGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAOgAgAGsAZwAgAEMALwBrAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARABvAGwAXAAiACwAIABcACIAVABoAGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAYQBzACAAZABvAGwAbwBtAGkAdABlACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAUABkAG8AbABcACIALAAgAFwAIgBGAHIAYQBjAHQAaQBvAG4AYQBsACAAcAB1AHIAaQB0AHkAIABvAGYAIABkAG8AbABvAG0AaQB0AGUAIAA6ACAAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAGQAbwBsAFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABkAG8AbABvAG0AaQB0AGUAIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABsAGkAbQBlACAAOgAgAGsAZwAgAEMALwBrAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAZwBDAE8AMgBcACIALABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAOgAgAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA1ADoAIABGAGUAcgB0AGkAbABpAHMAZQByACAAVQBzAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANQAuADQAIABBAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABmAHIAbwBtACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcAG4AIABFAGEAZABpAG4AbwByAGcAYQBuAGkAYwBcAG4AIAB0ACAATgAyAE8AXABuAE0AdgBvAGwAaQBuAG8AcgBnAGEAbgBpAGMAagBmACAALAAgAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBzAGUAZAAgAGYAcgBvAG0AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzADoAIABrAGcAIABOAFwAbgBFAEYAYQBkAGoAIAAsACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEcAVwBQAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUATgAyAE8AYQBkACwARwBXAFAATgAyAE8ALAAgAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEcAVwBQACgARQBOADIATwBhAGQALABHAFcAUABOADIATwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYALAAgAEUARgBhAGQAagAsACAAQwBnAE4AMgBPACwAXABuACAAIAAgACAAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuACgATQB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYALABFAEYAYQBkAGoALABDAGcATgAyAE8AKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABmAHIAbwBtACAAYQBsAGwAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAHMAIABmACAAYQBuAGQAIABhAGwAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQBzACAAagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAYQBkAGkAbgBvAHIAZwBhAG4AaQBjAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAKAApACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBhAGQAaQBuAG8AcgBnAGEAbgBpAGMAIAA9ACAATQB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAIAAqACAARQBGAGEAZABqACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgBcACIAIAAsACAAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBzAGUAZAAgAGYAcgBvAG0AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzADoAIABrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAYQBkAGoAXAAiACAALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgAgADoAIABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGcATgAyAE8AXAAiACwAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAA6ACAAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAagBcACIALABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBmAFwAIgAsAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAFcAUABOADIATwBcACIALABcACIARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAA6ACAAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIAAgAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ATQB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAXABuAGsAZwAgAE4AXABuAE0ATgBqAGYAIAAsACAATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAA6ACAAawBnACAATgBcAG4ARgByAGEAYwBHAEEAUwBGAGYAIAAsACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdABoAGEAdAAgAHYAbwBsAGEAdABpAGwAaQBzAGUAcwAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AIABcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBOAGoAZgAsACAARgByAGEAYwBHAEEAUwBGAGYALABcAG4AIAAgACAAIABDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAoAE0ATgBqAGYALAAgAEYAcgBhAGMARwBBAFMARgBmACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBqAGYAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANQAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAoACkAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAGoAZgAgAD0AIABNAE4AagBmACAAKgAgAEYAcgBhAGMARwBBAFMARgBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAGoAZgBcACIALABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAA6ACAAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBGAGYAXAAiACwAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHQAaABhAHQAIAB2AG8AbABhAHQAaQBsAGkAcwBlAHMAIAA6ACAAKABrAGcAIABOAEgAMwAtAE4AIAArACAATgBPAHgALQBOACkALwBrAGcAIABOAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwByAG8AcABzACAAYwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ARQBcAG4AdAAgAE4AMgBPAFwAbgBFAD0AXABcAHMAdQBtAF8AewBjAH0AewBNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBnACwATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQB9AFwAbgBNAGMAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIABjACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOACkAXABuAEUARgBOAGkAIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcAG4AQwBnAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AYwAsACAARQBGAE4AaQAsACAAQwBnAE4AMgBPACwAXABuACAAIAAgACAATQBjACAAKgAgAEUARgBOAGkAIAAqACAAQwBnAE4AMgBPACAAKgAgADEAMABeACgALQAzACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIAByAGUAdAB1AHIAbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABhAGMAcgBvAHMAcwAgAGEAbABsACAAYwByAG8AcABzACAAYwAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAPQBcAFwAcwB1AG0AXwB7AGMAfQB7AE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBOAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AGcALABOADIATwB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9AH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIABjACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBOAGkAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAZwBOADIATwBcACIALABcACIAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALABcACIAQwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcAG4ATQBjAFwAbgBrAGcAIABOAFwAbgBNAF8AewBjAH0APQAoAFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACgAMQAtAEYAXwB7AGMAfQAtAEYARgBPAEQAXwB7AGMAfQApAFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAATgBDAF8AewBBAEcAYwB9ACkAKwAoAFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQgBHAGMAfQBcAFwAdABpAG0AZQBzACAARABNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQgBHAGMAfQApAFwAbgBQAGMAIAA9ACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwApAFwAbgBSAEEARwBjACAAPQAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBSAEIARwBjACAAPQAgAGIAZQBsAG8AdwAgAGcAcgBvAHUAbgBkAC0AcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAgAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARgBjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARgBGAE8ARABjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARABNAGMAIAA9ACAAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAYwAgACgAawBnACAAZAByAHkAIAB3AGUAaQBnAGgAdAAvAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACkAXABuAE4AQwBBAEcAYwAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAE4AQwBCAEcAYwAgAD0AIABuAGkAdAByAG8AZwBlAG4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAIABOAC8AawBnACAARABNACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABQAGMALAAgAFIAQQBHAGMALAAgAEYAYwAsACAARgBGAE8ARABjACwAIABEAE0AYwAsACAATgBDAEEARwBjACwAIABSAEIARwBjACwAIABOAEMAQgBHAGMALABcAG4AIAAgACAAIAAoAFAAYwAgACoAIABSAEEARwBjACAAKgAgACgAMQAgAC0AIABGAGMAIAAtACAARgBGAE8ARABjACkAIAAqACAARABNAGMAIAAqACAATgBDAEEARwBjACkAIAArACAAKABQAGMAIAAqACAAUgBBAEcAYwAgACoAIABSAEIARwBjACAAKgAgAEQATQBjACAAKgAgAE4AQwBCAEcAYwApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAYwB9AD0AKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAoADEALQBGAF8AewBjAH0ALQBGAEYATwBEAF8AewBjAH0AKQBcAFwAdABpAG0AZQBzACAARABNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQQBHAGMAfQApACsAKABQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEIARwBjAH0AXABcAHQAaQBtAGUAcwAgAEQATQBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEIARwBjAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAwACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGMAXAAiACwAXAAiAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBBAEcAYwBcACIALABcACIAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAQgBHAGMAXAAiACwAXAAiAGIAZQBsAG8AdwAgAGcAcgBvAHUAbgBkAC0AcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAgAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBjAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYARgBPAEQAYwBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdABoAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0AYwBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAYwAgACgAawBnACAAZAByAHkAIAB3AGUAaQBnAGgAdAAvAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBBAEcAYwBcACIALABcACIAbgBpAHQAcgBvAGcAZQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAQgBHAGMAXAAiACwAXAAiAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAbwBmACAAYwByAG8AcAAgAGMAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALABcACIAUwB0AGEAdABlACAAbwByACAAdABlAHIAcgBpAHQAbwByAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMALAAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIAB3AGgAZQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABhAHIAZQAgAGIAYQBsAGUAZABcAG4ARgBGAE8ARABjAGIAYQBsAGUAZABcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4ARgBGAE8ARABfAHsAYwB9AD0AXABcAGYAcgBhAGMAewBCAFwAXAB0AGkAbQBlAHMAIABNAF8AewBCAH0AfQB7AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHACwAYwB9AH0AXABuAEIAIAA9ACAAbgB1AG0AYgBlAHIAIABvAGYAIABiAGEAbABlAHMAIABnAGUAbgBlAHIAYQB0AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBNAEIAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAGUAYQBjAGgAIABiAGEAbABlACAAKABrAGcAKQBcAG4AUABjACAAPQAgAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAKQBcAG4AUgBBAEcAYwAgAD0AIAByAGUAcwBpAGQAdQBlACAAdABvACAAYwByAG8AcAAgAHIAYQB0AGkAbwAgAGYAbwByACAAYwByAG8AcAAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AYwAgAD0AIABDAHIAbwBwACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABCACwAIABNAEIALAAgAFAAYwAsACAAUgBBAEcAYwAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKAAoAEIAIAAqACAATQBCACkAIAAvACAAKABQAGMAIAAqACAAUgBBAEcAYwApACwAIAAwACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdABoAGEAdAAgAGkAcwAgAHIAZQBtAG8AdgBlAGQAIABmAG8AcgAgAGMAcgBvAHAAIABjACwAIABjAGEAbABjAHUAbABhAHQAZQBkACAAdwBoAGUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAYQByAGUAIABiAGEAbABlAGQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAGMAYgBhAGwAZQBkAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAxAC4AMQAuADIALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AewBjACwAYgBhAGwAZQBkAH0APQBcAFwAZgByAGEAYwB7AEIAXABcAHQAaQBtAGUAcwAgAE0AXwB7AEIAfQB9AHsAUABfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABSAF8AewBBAEcALABjAH0AfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAXAAiACwAXAAiAG4AdQBtAGIAZQByACAAbwBmACAAYgBhAGwAZQBzACAAZwBlAG4AZQByAGEAdABlAGQAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBCAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAZQBhAGMAaAAgAGIAYQBsAGUAIAAoAGsAZwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGMAXAAiACwAXAAiAGEAbgBuAHUAYQBsACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAGMAcgBvAHAAIABjACAAKABrAGcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBBAEcAYwBcACIALABcACIAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABmAG8AcgAgAGMAcgBvAHAAIABjACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAOgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AGIAYQBsAGUAZABcAHUAMAAwADIANwAgAHQAbwAgAHYAYQByAGkAYQBiAGwAZQAgAHMAdQBiAHMAYwByAGkAcAB0AFwAIgApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAGYAbwByACAAYwByAG8AcAAgAGMAXABuAEYARgBPAEQAYwBcAG4AZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEYARgBPAEQAYwBiAGEAbABlAGQALAAgAEYARgBPAEQAYwBvAHQAaABlAHIALABcAG4AIAAgACAAIABGAEYATwBEAGMAYgBhAGwAZQBkACAAKwAgAEYARgBPAEQAYwBvAHQAaABlAHIAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAGMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAEYATwBEAF8AewBjAH0AIAA9ACAARgBGAE8ARABfAHsAYwAsAGIAYQBsAGUAZAB9ACAAKwAgAEYARgBPAEQAXwB7AGMALABvAHQAaABlAHIAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAGMAYgBhAGwAZQBkAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAHcAaABlAHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAcgBlACAAYgBhAGwAZQBkAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAGMAbwB0AGgAZQByAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAaABhAHQAIABpAHMAIAByAGUAbQBvAHYAZQBkACAAZgBvAHIAIABjAHIAbwBwACAAYwAsACAAYwBhAGwAYwB1AGwAYQB0AGUAZAAgAHcAaABlAHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGEAcgBlACAAcgBlAG0AbwB2AGUAZAAgAGIAeQAgAG8AdABoAGUAcgAgAG0AZQBhAG4AcwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAdABoAGkAcwAgAGUAcQB1AGEAdABpAG8AbgAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAHUAcwBlAHIALQBkAGUAZgBpAG4AZQBkACAAcgBlAHMAaQBkAHUAZQAgAHIAZQBtAG8AdgBhAGwAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAYgBhAGwAaQBuAGcALgBcACIAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQQBnAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAIgAsACIAdABlAHgAdAAiADoAIgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADEAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADIALgAxAC4AMQA6ACAAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADAALAAgADkALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiACwAIABcACIAUgBlAHMAaQBkAHUAZQA6ACAAQwByAG8AcAAgAHIAYQB0AGkAbwBcACIALAAgAFwAIgBCAGUAbABvAHcALQBnAHIAbwB1AG4AZAA6ACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIAByAGUAcwBpAGQAdQBlACAAcgBhAHQAaQBvAFwAIgAsACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABjAG8AbgB0AGUAbgB0AFwAIgAsACAAXAAiAEMAYQByAGIAbwBuACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAZAByAHkAIABtAGEAdAB0AGUAcgBcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkAFwAIgAsACAAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAXAAiACwAIABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAdABpAG0AZQAgAG8AZgAgAGIAdQByAG4AaQBuAGcAXAAiACwAIABcACIAQgB1AHIAbgBpAG4AZwAgAGUAZgBmAGkAYwBpAGUAbgBjAHkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsACAAXAAiAFIAQQBHAGMAXAAiACwAIABcACIAUgBCAEcAYwBcACIALAAgAFwAIgBEAE0AYwBcACIALAAgAFwAIgBDAEMAYwBcACIALAAgAFwAIgBOAEMAQQBHAGMAXAAiACwAIABcACIATgBDAEIARwBjAFwAIgAsACAAXAAiAFMAYwBcACIALAAgAFwAIgBaAGMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAMQAuADUAMAAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOQAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIAAxAC4AMgA0ACwAIAAwAC4AMwAyACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADcALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AMwA5ACwAIAAwAC4AOAA1ACwAIAAwAC4ANAAyACwAIAAwAC4AMAAwADUALAAgADAALgAwADAANwAsACAAMQAuADAALAAgADAALgA4ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAMQAuADQAMgAsACAAMAAuADQAMwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgADAALgA1ACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgADEALgAzADEALAAgADAALgAxADYALAAgADAALgA4ADAALAAgADAALgA0ADIALAAgADAALgAwADAANwAsACAAMAAuADAAMQAwACwAIAAxAC4AMAAsACAAMAAuADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIAAxAC4ANQAwACwAIAAwAC4AMgAyACwAIAAwAC4AOAAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADgALAAgADAALgAwADAANwAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgADEALgA1ADAALAAgADAALgA0ADIALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIAAxAC4ANAA2ACwAIAAwAC4AMwA2ACwAIAAwAC4AOAA4ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAwADYALAAgADAALgAwADEAMAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgADEALgAzADcALAAgADAALgA1ADEALAAgADAALgA4ADcALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIAAwAC4AMwA0ACwAIAAwAC4ANAAzACwAIAAwAC4AMgA1ACwAIAAwAC4ANAAwACwAIAAwAC4AMAAyADAALAAgADAALgAwADEAMAAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIAAxAC4AMAA3ACwAIAAwAC4AMgAwACwAIAAwAC4AOAAwACwAIAAwAC4ANAAyACwAIAAwAC4AMAAxADYALAAgADAALgAwADEANAAsACAAMAAuADUALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADIANQAsACAAMAAuADQANQAsACAAMAAuADIAMAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA1ACwAIAAwAC4AMAAwADcALAAgADEALgAwACwAIAAwAC4AOAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIAAxAC4AOQAwACwAIAAwAC4AMwAwACwAIAAwAC4AOQAwACwAIAAwAC4ANAAwACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAbgAvAGEAXAAiACwAIAAwAC4AOAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgADEALgA1ADAALAAgADAALgAyADkALAAgADAALgA4ADgALAAgADAALgA0ADAALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgADIALgAwADgALAAgADAALgAzADMALAAgADAALgA5ADYALAAgADAALgA0ADAALAAgADAALgAwADAAOQAsACAAMAAuADAAMQAwACwAIAAwAC4ANQAsACAAMAAuADgANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAMQAuADMANAAsACAAMAAuADMANwAsACAAMAAuADgAOAAsACAAMAAuADQAMAAsACAAMAAuADAAMAA2ACwAIAAwAC4AMAAxADAALAAgAFwAIgBuAC8AYQBcACIALAAgADAALgA4ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgADEALgAwADAALAAgADAALgAyADIALAAgADAALgA4ADUALAAgADAALgA0ADAALAAgADAALgAwADAAOAAsACAAMAAuADAAMAA5ACwAIABcACIAbgAvAGEAXAAiACwAIABcACIAbgAvAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIAAxAC4ANQAsACAAMAAuADIAOQAsACAAMAAuADgAOAAsACAAMAAuADQALAAgADAALgAwADAANgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAXAAiAG4ALwBhAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAXAB1ADAAMAAyADcATgAvAEEAXAB1ADAAMAAyADcAIAB2AGEAbAB1AGUAcwAgAHAAYQBzAHMAZQBkACAAYQBzACAAegBlAHIAbwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAHMALgBcACIAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAVABhAGIAbABlACAAQQAuADIALgAxAC4AMgA6ACAAQwByAG8AcAAgAGEAdAB0AHIAaQBiAHUAdABlAHMAIAAtACAARgByAGEAYwB0AGkAbwBuACAAcgBlAG0AbwB2AGUAZAAgACgARgBGAE8ARABjACkAXAAiACkAKQA7AFwAbgBcAG4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADIAOgAgAEMAcgBvAHAAIABhAHQAdAByAGkAYgB1AHQAZQBzACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIAAoAEYARgBPAEQAYwApAFwAIgApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIAMAAsACAAMwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAHIAbwBwACAAdAB5AHAAZQAgAGMAXAAiACwAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAHIAZQBtAG8AdgBlAGQAIABGAEYATwBEAGMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAGwAbAAgAHMAdABhAHQAZQBzAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBsAGwAIABvAHQAaABlAHIAIABjAHIAbwBwACAAdAB5AHAAZQBzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbABsACAAbwB0AGgAZQByACAAYwByAG8AcAAgAHQAeQBwAGUAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBDAHUAcwB0AG8AbQBpAHMAZQBkAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQA0ADQALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwByAG8AcAAgAHQAeQBwAGUAIABjAFwAIgAsACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBGAHIAYQBjAHQAaQBvAG4AIAByAGUAbQBvAHYAZQBkACAARgBGAE8ARABjAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUgBpAGMAZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAB1AGIAZQByAHMAIABhAG4AZAAgAHIAbwBvAHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHUAYgBlAHIAcwAgAGEAbgBkACAAcgBvAG8AdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAdQBiAGUAcgBzACAAYQBuAGQAIAByAG8AbwB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEgAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIASABvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcABzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AOAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAbwByAGEAZwBlACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAYQBnAGUAIABjAHIAbwBwAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAG8AcgBhAGcAZQAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgAgAEMAYQBuAGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIATgAvAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAQwBhAG4AZQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBOAC8AQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABDAGEAbgBlAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAE4ALwBBAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFcAaABlAGEAdABcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGgAZQBhAHQAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAGwAZQB5AFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGEAcgBsAGUAeQBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAGkAegBlAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAaQB6AGUAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBpAHoAZQBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBhAHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGEAdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AYQB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwByAGcAaAB1AG0AXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAHIAZwBoAHUAbQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAG8AcgBnAGgAdQBtAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFYASQBDAFwAIgAsACAAMAAuADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAaQB0AGkAYwBhAGwAZQBcACIALAAgAFwAIgBXAEEAXAAiACwAIAAwAC4AMQAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVAByAGkAdABpAGMAYQBsAGUAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBpAHQAaQBjAGEAbABlAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAMAAuADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIATgBTAFcAXAAiACwAIAAwAC4AMAA1ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABjAGUAcgBlAGEAbABzAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAMAAuADAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAMAAuADAAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGMAZQByAGUAYQBsAHMAXAAiACwAIABcACIAVABBAFMAXAAiACwAIAAwAC4AMQA2ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBOAFQAXAAiACwAIAAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYwBlAHIAZQBhAGwAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAB1AGwAcwBlAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAdQBsAHMAZQBzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHUAbABzAGUAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIAAwAC4AMAA3ADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABlAGEAbgB1AHQAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFcAQQBcACIALAAgADAALgAxADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAYQBuAHUAdABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAZQBhAG4AdQB0AHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIAAwAC4AMAAwADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAUQBMAEQAXAAiACwAIAAwAC4AMAA0ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwBpAGwAcwBlAGUAZABzAFwAIgAsACAAXAAiAFMAQQBcACIALAAgADAALgAwADkAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgADAALgAxADYAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAGkAbABzAGUAZQBkAHMAXAAiACwAIABcACIATgBUAFwAIgAsACAAMAAuADAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AaQBsAHMAZQBlAGQAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAYQBuAG4AdQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGEAbgBuAHUAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABhAG4AbgB1AGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgADAALgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBWAEkAQwBcACIALAAgADAALgAwADcAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBRAEwARABcACIALAAgADAALgAwADQAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBTAEEAXAAiACwAIAAwAC4AMAA5ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAcABlAHIAZQBuAG4AaQBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAMAAuADEAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAMAAuADEANgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAHAAZQByAGUAbgBuAGkAYQBsACAAYwByAG8AcABzAFwAIgAsACAAXAAiAE4AVABcACIALAAgADAALgAwADEAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABwAGUAcgBlAG4AbgBpAGEAbAAgAGMAcgBvAHAAcwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgADAALgAwADAAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABTAHAAbABpAHQAIABcAHUAMAAwADIANwBBAGwAbAAgAG8AdABoAGUAcgAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXAB1ADAAMAAyADcAIABpAG4AdABvACAAaQBuAGQAaQB2AGkAZAB1AGEAbAAgAGMAcgBvAHAAIAB0AHkAcABlAHMAIABmAG8AcgAgAGUAYQBjAGgAIABzAHQAYQB0AGUALgAgAEwAaQBzAHQAZQBkACAAYQBsAGwAIABzAHQAYQB0AGUAcwAgAGYAbwByACAAUwB1AGcAYQByACAAQwBhAG4AZQAsACAAdwBpAHQAaAAgAFwAdQAwADAAMgA3AE4ALwBBAFwAdQAwADAAMgA3ACAAZgBvAHIAIABzAHQAYQB0AGUAcwAgAHcAaABlAHIAZQAgAGkAdAAgAGkAcwAgAG4AbwB0ACAAZwByAG8AdwBuAC4AXAAiACkAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUABhAHMAdAB1AHIAZQAgAGEAdAB0AHIAaQBiAHUAdABlAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAIABQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBQAGEAcwB0AHUAcgBlACAAYQB0AHQAcgBpAGIAdQB0AGUAcwBcACIAKQApADsAXABuAFwAbgBQAGEAcwB0AHUAcgBlAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADMAOgAgAFAAYQBzAHQAdQByAGUAIABhAHQAdAByAGkAYgB1AHQAZQBzAFwAIgApACkAOwBcAG4AXABuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANgAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIALAAgAFwAIgBBAHYAZQByAGEAZwBlACAAWQBpAGUAbABkACAAKAB0ACAARABNACAAaABhACkAIABZAHAAXAAiACwAIABcACIAQgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAOgAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAFIAQgBHAHAAXAAiACwAIABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABBAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAE4AQwBBAEcAcABcACIALAAgAFwAIgBOACAAYwBvAG4AdABlAG4AdAAgAEIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAATgBDAEIARwBwAFwAIgAsACAAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgAEYARgBPAEQAcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AbgB1AGEAbAAgAGcAcgBhAHMAcwBcACIALAAgADQALgA0ADEALAAgADAALgA0ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAYQBzAHMAIABjAGwAbwB2AGUAcgAgAG0AaQB4AHQAdQByAGUAXAAiACwAIAA4AC4AMwA0ACwAIAAwAC4AOAAsACAAMAAuADAAMgA1ACwAIAAwAC4AMAAxADYALAAgADAALgA4ADsAXABuACAAIAAgACAAIAAgACAAIABcACIATAB1AGMAZQByAG4AZQBcACIALAAgADgALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADEAOQAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABsAGUAZwB1AG0AZQBcACIALAAgADUALgA2ADIALAAgADAALgA0ACwAIAAwAC4AMAAyADcALAAgADAALgAwADIAMgAsACAAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgBlAG4AbgBpAGEAbAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAA4AC4AMwA1ACwAIAAwAC4AOAAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADIALAAgADAALgA4AFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBUAGEAYgBsAGUAIAA1AC4AMwAxACAAQgB1AHIAbgBpAG4AZwAgAG8AZgAgAGEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcgBlAHMAaQBkAHUAZQBzACAALQAgAEUARgBzAFwAIgApACkAOwBcAG4AXABuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEIAdQByAG4AaQBuAGcAIABvAGYAIABhAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAHIAZQBzAGkAZAB1AGUAcwAgAC0AIABFAEYAcwBcACIAKQApADsAXABuAFwAbgBCAHUAcgBuAGkAbgBnAE8AZgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABSAGUAcwBpAGQAdQBlAHMARQBGAHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAdgBvAGwAdQBtAGUAIAAyADoAIABUAGEAYgBsAGUAIAA1AC4AMwAxADoAIABCAHUAcgBuAGkAbgBnACAAbwBmACAAYQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIAByAGUAcwBpAGQAdQBlAHMAIAAtACAARQBGAHMAXAAiACkAKQA7AFwAbgBcAG4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAzACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzACAAcwBwAGUAYwBpAGUAcwBcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAEUARgBnACAAKABHAGcAIABlAGwAZQBtAGUAbgB0ACAAaQBuACAAcwBwAGUAYwBpAGUAcwAvACAARwBnACAAZQBsAGUAbQBlAG4AdAAgAGkAbgAgAGYAdQBlAGwAIABiAHUAcgBuAHQAKQBcACIALAAgAFwAIgBFAGwAZQBtAGUAbgB0AGEAbAAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgACgAQwBnACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAwAC4AMAAwADMANQAsACAAXAAiADEANgAvADEAMgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOADIATwBcACIALAAgADAALgAwADAANwA2ACwAIABcACIANAA0AC8AMgA4AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4ATwB4AFwAIgAsACAAMAAuADIAMQAwADAALAAgAFwAIgA0ADYALwAxADQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBPAFwAIgAsACAAMAAuADAANwA4ADAALAAgAFwAIgAyADgALwAxADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAMAAuADAAMAA5ADEALAAgAFwAIgAxADQALwAxADIAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAARgBvAHIAIABEAGEAaQByAHkAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAyAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAxAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ATABpAHYAZQB3AGUAaQBnAGgAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAALQAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAxAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ATABpAHYAZQB3AGUAaQBnAGgAdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgAgAC0AIABUAGEAYgBsAGUAIABBADUALgA1AC4AMgAuADEAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAxAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ATABpAHYAZQB3AGUAaQBnAGgAdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ADEALAAgADEANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFIAZQBnAGkAbwBuAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAgADEAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBDAG8AdwBzACAAMQAtADIAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBlACAAMgBcACIALAAgAFwAIgBDAG8AdwBzACAAMgAtADMAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBlACAAMwBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgAFwAdQAwADAAMwBlACAAMQBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgADEALQAyAFwAIgAsACAAXAAiAFMAdABlAGUAcgBzACAAMgAtADMAXAAiACwAIABcACIAUwB0AGUAZQByAHMAIABcAHUAMAAwADMAZQAgADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAOAAwACwAIAA0ADgAMAAsACAANwA1ACwAIAAzADAAMAAsACAANAA0ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADcANQAsACAAMwA4ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxADcAMAAsACAANQAyADAALAAgADEANgAwACwAIAAzADYAMAAsACAANAA3ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADEANgAwACwAIAA0ADIAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADIANAAwACwAIAA1ADUAMAAsACAAMgAyADAALAAgADMAOQAwACwAIAA0ADkAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMgAyADAALAAgADQANQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMgA4ADAALAAgADUANgAwACwAIAAyADYAMAAsACAANAAxADAALAAgADUAMAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAyADYAMAAsACAANAA2ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIABcACIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAA4ADAALAAgADQAOAAwACwAIAA3ADUALAAgADMAMAAwACwAIAA0ADQAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAANwA1ACwAIAAzADgAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEANwAwACwAIAA1ADIAMAAsACAAMQA2ADAALAAgADMANgAwACwAIAA0ADcAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMQA2ADAALAAgADQAMgAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMgA0ADAALAAgADUANQAwACwAIAAyADIAMAAsACAAMwA5ADAALAAgADQAOQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAyADIAMAAsACAANAA1ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAyADgAMAAsACAANQA2ADAALAAgADIANgAwACwAIAA0ADEAMAAsACAANQAwADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADIANgAwACwAIAA0ADYAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAyADUAMAAsACAAOAAwADAALAAgADIAMgAwACwAIAA0ADAAMAAsACAANQAwADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADIAMwAwACwAIAA0ADIAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAzADIAMAAsACAAOAAwADAALAAgADIAOAAwACwAIAA0ADIAMAAsACAANQAwADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADIAOQAwACwAIAA0ADIAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAA4ADAALAAgADcAMAAwACwAIAA3ADAALAAgADMAMAAwACwAIAA0ADUAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAANwA1ACwAIAA0ADAAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAxADYAMAAsACAANwAwADAALAAgADEANAAwACwAIAAzADUAMAAsACAANAA1ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADEANQAwACwAIAA0ADAAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADEAMAA1ACwAIAA3ADAAMAAsACAAOAA1ACwAIAAzADAAMAAsACAANAA5ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADkAMAAsACAANAA4ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAA0ADgAMAAsACAANwA1ADAALAAgADEANQAwACwAIAAzADUAMAAsACAANQAzADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADEANgAwACwAIAA0ADYAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADIANQAwACwAIAA3ADIANQAsACAAMgAwADAALAAgADMANgAwACwAIAA1ADAAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMgAxADUALAAgADQAOQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMgA2ADAALAAgADcAMAAwACwAIAAyADEAMAAsACAAMwA4ADAALAAgADQANgAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAyADMAMAAsACAANAA3ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBJAEMAXAAiACwAIABcACIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAyADUAMAAsACAAOAAyADAALAAgADIANAAwACwAIAA0ADEAMAAsACAANQA2ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADIANAAwACwAIAA1ADEAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADIAOAAwACwAIAA4ADUAMAAsACAAMgA2ADAALAAgADQANAAwACwAIAA1ADUAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMgA3ADAALAAgADUAMgAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQAwADAALAAgADcAMAAwACwAIAA5ADUALAAgADMAMAAwACwAIAA0ADUAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAOQA1ACwAIAA0ADEAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADEANQAwACwAIAA3ADIAMAAsACAAMQA0ADAALAAgADMAMgAwACwAIAA0ADcAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMQA0ADAALAAgADQANAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMwA0ADAALAAgADgAMAAwACwAIAAyADYAMAAsACAANAAyADAALAAgADUANQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAzADAAMAAsACAANAA4ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUwBvAHUAdABoACAAVwBlAHMAdABcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADMAOAAwACwAIAA3ADgAMAAsACAAMwAwADAALAAgADQANQAwACwAIAA1ADMAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMwA0ADAALAAgADQANwAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQAwADAALAAgADYAOAAwACwAIAA4ADAALAAgADMAMgAwACwAIAA0ADgAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMQAwADAALAAgADMANAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMQA5ADAALAAgADcAMAAwACwAIAAxADUAMAAsACAAMwAzADAALAAgADQAOQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAxADcAMAAsACAAMwA2ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFAAaQBsAGIAYQByAGEAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAA4ADAALAAgADQANQAwACwAIAA3ADAALAAgADIANgAwACwAIAAzADQAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAOAAwACwAIAAzADcAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUABpAGwAYgBhAHIAYQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEANQAwACwAIAA1ADAAMAAsACAAMQA0ADAALAAgADMAMQAwACwAIAAzADYAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMQA1ADAALAAgADQAMAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBQAGkAbABiAGEAcgBhAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMgAzADAALAAgADUANQAwACwAIAAyADIAMAAsACAAMwAzADAALAAgADMAOAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAyADMAMAAsACAANAAyADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFAAaQBsAGIAYQByAGEAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAyADUAMAAsACAANQAwADAALAAgADIANAAwACwAIAAzADQAMAAsACAAMwA2ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADIANQAwACwAIAAzADkAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAOgBcACIALAAgADIAMgAwACwAIAA1ADAAMAAsACAAMQA4ADAALAAgADMAMAAwACwAIAAzADIAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMgAxADAALAAgADMANAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBLAGkAbQBiAGUAcgBsAGUAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgA6AFwAIgAsACAAMQAxADAALAAgADUANQAwACwAIAA5ADAALAAgADIAMgAwACwAIAAzADgAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMQAwADAALAAgADMAOQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBLAGkAbQBiAGUAcgBsAGUAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgA6AFwAIgAsACAAMQA3ADAALAAgADYAMAAwACwAIAAxADQAMAAsACAAMgA3ADAALAAgADMAOQAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAxADYAMAAsACAANAAzADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAEsAaQBtAGIAZQByAGwAZQB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByADoAXAAiACwAIAAyADAAMAAsACAANQA1ADAALAAgADEANQAwACwAIAAyADgAMAAsACAAMwA1ADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADEAOQAwACwAIAA0ADAAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAQQBsAGkAYwBlACAAUwBwAHIAaQBuAGcAcwBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADIAMgAwACwAIAA3ADAANgAsACAAMgAwADgALAAgADMAMgAzACwAIABcACIAXAAiACwAIAA0ADEANQAsACAANAA2ADcALAAgADIAMgAzACwAIABcACIAXAAiACwAIAAzADcAMQAsACAANAA5ADMALAAgADUAOAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBBAGwAaQBjAGUAIABTAHAAcgBpAG4AZwBzAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMQAxADAALAAgADcAMAAzACwAIAAxADEAMgAsACAAMgA1ADYALAAgAFwAIgBcACIALAAgADMANgA4ACwAIAA0ADYANQAsACAAMQAwADgALAAgAFwAIgBcACIALAAgADIAOAAwACwAIAA0ADIAMQAsACAANQA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAEEAbABpAGMAZQAgAFMAcAByAGkAbgBnAHMAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAxADcAMAAsACAANwAyADEALAAgADEANgA5ACwAIAAzADAANgAsACAAXAAiAFwAIgAsACAAMwA5ADIALAAgADQANgA0ACwAIAAxADcANgAsACAAXAAiAFwAIgAsACAAMwAzADkALAAgADQANwAwACwAIAA1ADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAQQBsAGkAYwBlACAAUwBwAHIAaQBuAGcAcwBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADIAMAAwACwAIAA3ADIANwAsACAAMgAxADEALAAgADMAMwA4ACwAIABcACIAXAAiACwAIAA0ADMAMgAsACAANAA5ADIALAAgADIAMgAyACwAIABcACIAXAAiACwAIAAzADcANwAsACAANAA5ADgALAAgADUAOQAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBCAGEAcgBrAGwAeQBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADIAMgAwACwAIAA2ADIAMAAsACAAMgAyADcALAAgADMAMQA5ACwAIABcACIAXAAiACwAIAAzADkAOAAsACAANAA1ADIALAAgADIAMQA2ACwAIABcACIAXAAiACwAIAAzADMANAAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAQgBhAHIAawBsAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxADEAMAAsACAANgA1ADAALAAgADEAMAA4ACwAIAAyADYAMgAsACAAXAAiAFwAIgAsACAAMwA0ADYALAAgADQAMwAwACwAIAAxADEAMQAsACAAXAAiAFwAIgAsACAAMgAzADYALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAEIAYQByAGsAbAB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQA3ADAALAAgADYANwAwACwAIAAxADcAMAAsACAAMgA2ADYALAAgAFwAIgBcACIALAAgADMANgAzACwAIAA0ADQANAAsACAAMQA2ADkALAAgAFwAIgBcACIALAAgADIAOAAyACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBCAGEAcgBrAGwAeQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADIAMAAwACwAIAA2ADYAMAAsACAAMgAyADUALAAgADMAMAA3ACwAIABcACIAXAAiACwAIAAzADkAOAAsACAANAA1ADIALAAgADIAMQA0ACwAIABcACIAXAAiACwAIAAzADIANgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMgAyADAALAAgADYAMgAwACwAIAAxADcANwAsACAAMgA2ADcALAAgAFwAIgBcACIALAAgADMANgA1ACwAIAA0ADAANgAsACAAMgAzADEALAAgAFwAIgBcACIALAAgADIANAA5ACwAIAAzADIANAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMQAxADAALAAgADYANQAwACwAIAAxADAAMgAsACAAMgAwADMALAAgAFwAIgBcACIALAAgADIAOQA5ACwAIAAzADgAMAAsACAAMQAwADIALAAgAFwAIgBcACIALAAgADIAMQA4ACwAIAAyADYAMwAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQA3ADAALAAgADYANwAwACwAIAAxADcAMwAsACAAMgA1ADAALAAgAFwAIgBcACIALAAgADMAMwA2ACwAIAA0ADEANAAsACAAMQA3ADUALAAgAFwAIgBcACIALAAgADIANAAzACwAIAAzADAANAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMgAwADAALAAgADYANgAwACwAIAAyADAAMgAsACAAMgA3ADIALAAgAFwAIgBcACIALAAgADMANgA1ACwAIAAzADkAMAAsACAAMgAwADgALAAgAFwAIgBcACIALAAgADIANgAwACwAIAAzADMANwAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBIAGkAZwBoAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMgA2ADAALAAgADcAMAA1ACwAIAAyADEANQAsACAAMwAwADIALAAgAFwAIgBcACIALAAgADQAMQA2ACwAIAA1ADEAOQAsACAAMgAzADQALAAgAFwAIgBcACIALAAgADQANQA1ACwAIAA1ADUAMQAsACAANgA2ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIASABpAGcAaABcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEANQAzACwAIAA3ADAAMwAsACAAMQAxADgALAAgADIANwA3ACwAIABcACIAXAAiACwAIAAzADkANwAsACAANAA4ADMALAAgADEAMQAxACwAIABcACIAXAAiACwAIAAzADAANAAsACAANQAyADEALAAgADUANAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAEgAaQBnAGgAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAxADYAOAAsACAANwAxADgALAAgADEAOQAxACwAIAAzADEAOQAsACAAXAAiAFwAIgAsACAANAA0ADAALAAgADUAMAA2ACwAIAAxADgAOAAsACAAXAAiAFwAIgAsACAAMwAyADYALAAgADUAMgAwACwAIAA1ADgAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBIAGkAZwBoAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMgAzADUALAAgADcAMgAyACwAIAAyADAANwAsACAAMwA1ADIALAAgAFwAIgBcACIALAAgADQANwAwACwAIAA1ADEANAAsACAAMgAwADkALAAgAFwAIgBcACIALAAgADQAMgAxACwAIAA1ADEAMgAsACAANgAwADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATQBvAGQAZQByAGEAdABlAC8ASABpAGcAaABcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADIAMwAwACwAIAA2ADcANAAsACAAMgAxADcALAAgAFwAIgBcACIALAAgADMANAA0ACwAIAAzADUANwAsACAANAA2ADcALAAgADIANAAyACwAIABcACIAXAAiACwAIAAzADcAMAAsACAANQA1ADAALAAgADYAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEgAaQBnAGgAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxADEAMwAsACAANgA2ADkALAAgADEAMQAzACwAIABcACIAXAAiACwAIAAyADgAMwAsACAAMwA2ADEALAAgADQANwA3ACwAIAAxADIAMAAsACAAXAAiAFwAIgAsACAAMgA3ADMALAAgADUANAA1ACwAIAA1ADUAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBNAG8AZABlAHIAYQB0AGUALwBIAGkAZwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQA3ADIALAAgADYAOAA1ACwAIAAxADcAMgAsACAAXAAiAFwAIgAsACAAMwAwADkALAAgADMANwA2ACwAIAA0ADcAMQAsACAAMgAzADgALAAgAFwAIgBcACIALAAgADMAMgA5ACwAIAA1ADcAMwAsACAANgAyADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATQBvAGQAZQByAGEAdABlAC8ASABpAGcAaABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADIANAAxACwAIAA2ADkAMgAsACAAMgAwADgALAAgAFwAIgBcACIALAAgADMANAA0ACwAIAAzADYANAAsACAANAA4ADQALAAgADIANgAwACwAIABcACIAXAAiACwAIAAzADUAMAAsACAANQA2ADcALAAgADYAMgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEwAbwB3AFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMgAzADYALAAgADYANwA0ACwAIAAxADcAOAAsACAAXAAiAFwAIgAsACAAMwAxADAALAAgADQAMgA4ACwAIAA0ADYANgAsACAAMQA5ADMALAAgAFwAIgBcACIALAAgADMANwAwACwAIAA1ADEAOQAsACAANQA2ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATQBvAGQAZQByAGEAdABlAC8ATABvAHcAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxADIAMAAsACAANgA2ADkALAAgADEAMQAyACwAIABcACIAXAAiACwAIAAyADUAMAAsACAAMwA5ADAALAAgADQANAA4ACwAIAAxADEANQAsACAAXAAiAFwAIgAsACAAMgA3ADMALAAgADQAMwAzACwAIAA1ADUANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBNAG8AZABlAHIAYQB0AGUALwBMAG8AdwBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADEAMgA1ACwAIAA2ADgANQAsACAAMQA0ADAALAAgAFwAIgBcACIALAAgADIANwA3ACwAIAA0ADAANwAsACAANAA1ADUALAAgADEANAAxACwAIABcACIAXAAiACwAIAAyADkANgAsACAANAA0ADUALAAgADUAOQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEwAbwB3AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMQA4ADAALAAgADYAOQAyACwAIAAxADgAMwAsACAAXAAiAFwAIgAsACAAMwAxADYALAAgADQAMwA4ACwAIAA0ADYAOAAsACAAMQA4ADkALAAgAFwAIgBcACIALAAgADMANQA0ACwAIAA1ADAAMAAsACAANQA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATABvAHcAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAxADkAMAAsACAANgAxADcALAAgADEANwA0ACwAIABcACIAXAAiACwAIAAyADYANQAsACAAMwA3ADEALAAgADQAMQA1ACwAIAAxADcAMAAsACAAXAAiAFwAIgAsACAAMgA3ADIALAAgADMAOQAyACwAIAA1ADMAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBMAG8AdwBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEAMQA5ACwAIAA1ADkAMQAsACAAMQA0ADAALAAgAFwAIgBcACIALAAgADIAMAA1ACwAIAAzADEAMAAsACAANAAwADUALAAgADEAMwAzACwAIABcACIAXAAiACwAIAAyADEAOAAsACAAMwAxADUALAAgADQANAA1ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAEwAbwB3AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQA3ADUALAAgADYAMQAwACwAIAAxADYAMwAsACAAXAAiAFwAIgAsACAAMgAzADIALAAgADMANQAxACwAIAA0ADIANwAsACAAMQA0ADYALAAgAFwAIgBcACIALAAgADIANAAyACwAIAAzADIAMAAsACAANAA3ADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATABvAHcAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAxADkAMgAsACAANgAxADUALAAgADEANgAyACwAIABcACIAXAAiACwAIAAyADUANQAsACAAMwA2ADQALAAgADQAMgAwACwAIAAxADUANwAsACAAXAAiAFwAIgAsACAAMgA2ADEALAAgADMANAAyACwAIAA0ADgANABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMgBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBcAG4AawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADIAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAC0AIABMAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwBhAGkAbgBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMgBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMgBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgAgAC0AIABUAGEAYgBsAGUAIABBADUALgA1AC4AMgAuADIAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADIAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAQwBUACAAYQBuAGQAIABOAFMAVwAgAHMAcABsAGkAdAAuACAAXAB1ADAAMAAyADcATgBPAFwAdQAwADAAMgA3ACAAcgBlAHAAbABhAGMAZQBkACAAdwBpAHQAaAAgADAALgBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMgBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ADEALAAgADEANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAFIAZQBnAGkAbwBuAFwAIgAsACAAXAAiAFMAZQBhAHMAbwBuAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAgADEAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBDAG8AdwBzACAAMQAtADIAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBlACAAMgBcACIALAAgAFwAIgBDAG8AdwBzACAAMgAtADMAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBlACAAMwBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgAFwAdQAwADAAMwBlACAAMQBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgADEALQAyAFwAIgAsACAAXAAiAFMAdABlAGUAcgBzACAAMgAtADMAXAAiACwAIABcACIAUwB0AGUAZQByAHMAIABcAHUAMAAwADMAZQAgADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAuADUALAAgADAALgAyACwAIAAwAC4ANQAsACAAMAAuADQALAAgADAALgAzACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4ANQAsACAAMAAuADQALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxACwAIAAwAC4ANAAsACAAMAAuADkALAAgADAALgA3ACwAIAAwAC4AMwAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADkALAAgADAALgA0ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAuADgALAAgADAALgAzACwAIAAwAC4ANwAsACAAMAAuADMALAAgADAALgAyACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4ANwAsACAAMAAuADMALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwAC4ANAAsACAAMAAuADEALAAgADAALgA0ACwAIAAwAC4AMgAsACAAMAAuADEALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgA0ACwAIAAwAC4AMQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADAALgA1ACwAIAAwAC4AMgAsACAAMAAuADUALAAgADAALgA0ACwAIAAwAC4AMwAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADUALAAgADAALgA0ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMQAsACAAMAAuADQALAAgADAALgA5ACwAIAAwAC4ANwAsACAAMAAuADMALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgA5ACwAIAAwAC4ANAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADAALgA4ACwAIAAwAC4AMwAsACAAMAAuADcALAAgADAALgAzACwAIAAwAC4AMgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADcALAAgADAALgAzACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADQALAAgADAALgAxACwAIAAwAC4ANAAsACAAMAAuADIALAAgADAALgAxACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4ANAAsACAAMAAuADEALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAuADkAOQAsACAAMQAuADEALAAgADAALgA4ADgALAAgADAALgA1ADUALAAgADAALgA1ADUALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgA4ADgALAAgADAALgAyADIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAuADcANwAsACAAMAAsACAAMAAuADYANgAsACAAMAAuADIAMgAsACAAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADYANgAsACAAMAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAwAC4AOQAsACAALQAxAC4AMQAsACAAMAAuADcALAAgADAALgAyADIALAAgAC0AMAAuADUANQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADgALAAgAC0AMAAuADIAMgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwAC4AOAA4ACwAIAAwACwAIAAwAC4ANwA3ACwAIAAwAC4ANQA1ACwAIAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4AOAAyACwAIAAwACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMQAsACAAMAAuADUALAAgADEALAAgADEALAAgAC0AMAAuADQANAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMQAsACAAMAAuADUALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAwAC4AOAAyACwAIAAwAC4ANQA1ACwAIAAwAC4ANwAxACwAIAAwAC4ANQA1ACwAIAAwAC4AOQA5ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4ANwA3ACwAIAAwAC4ANQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADAALgA3ADcALAAgADAALgA1ACwAIAAwAC4ANQA1ACwAIAAwAC4AMQAxACwAIAAtADAALgAzADMALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgA2ACwAIAAwAC4AMwAzACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADEAMQAsACAALQAwAC4AMgA3ACwAIAAwAC4AMQAxACwAIAAwAC4AMgAyACwAIAAtADAALgA0ADQALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgAxADYALAAgAC0AMAAuADIAMgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADEALgAxACwAIAAxAC4AMQAsACAAMQAuADEALAAgADAALgA5ADkALAAgADAALgA5ADkALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADEALgAxACwAIAAwAC4ANwA3ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAuADMAMwAsACAAMAAuADMAMwAsACAAMAAuADIAMgAsACAAMAAuADMAMwAsACAALQAwAC4AMQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADMAMwAsACAAMAAuADEAMQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADAALgA1ACwAIAAwAC4AMgAsACAAMAAuADUANQAsACAAMAAuADQANAAsACAAMAAuADIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgA1ADUALAAgADAALgAyACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADUANQAsACAAMAAuADIAMgAsACAAMAAuADQAOQAsACAAMAAuADIAMgAsACAAMAAuADIAMgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADQAOQAsACAAMAAuADMAMwAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUwBvAHUAdABoACAAVwBlAHMAdABcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADEALgA2ADQALAAgADEALgAxACwAIAAxAC4AMgAxACwAIAAwAC4AOQA5ACwAIAAwAC4ANgA2ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAxAC4ANAAyACwAIAAxAC4AMQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUwBvAHUAdABoACAAVwBlAHMAdABcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADAALgA0ADQALAAgAC0AMAAuADIAMgAsACAAMAAuADQANAAsACAAMAAuADMAMwAsACAALQAwAC4AMgAyACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4ANAA0ACwAIAAtADAALgAxADEALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAwAC4ANgAsACAAMAAsACAAMAAuADYALAAgADAALgAyADIALAAgAC0AMAAuADUANQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADYALAAgADAALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwAC4AOQA5ACwAIAAwAC4AMgAyACwAIAAwAC4ANwA3ACwAIAAwAC4AMQAxACwAIAAwAC4AMQAxACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4ANwA3ACwAIAAwAC4ANAA0ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBQAGkAbABiAGEAcgBhAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAuADcALAAgAC0AMAAuADUANQAsACAAMAAuADcALAAgADAALgAyADIALAAgAC0AMAAuADIAMgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADcALAAgAC0AMAAuADIAMgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUABpAGwAYgBhAHIAYQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADAALgA3ADcALAAgADAALgA1ADUALAAgADAALgA3ADcALAAgADAALgA2ADYALAAgADAALgA1ADUALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgA3ADcALAAgADAALgAzADMALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFAAaQBsAGIAYQByAGEAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAwAC4AOAA4ACwAIAAwAC4ANQA1ACwAIAAwAC4AOAA4ACwAIAAwAC4AMgAyACwAIAAwAC4AMgAyACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIAAwAC4AOAA4ACwAIAAwAC4AMgAyACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBQAGkAbABiAGEAcgBhAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADIAMgAsACAALQAwAC4ANQA1ACwAIAAwAC4AMgAyACwAIAAwAC4AMQAxACwAIAAtADAALgAyADIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgADAALgAyADIALAAgAC0AMAAuADMAMwAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAwAC4AMgAyACwAIAAtADAALgA1ADUALAAgADAALgAzADMALAAgADAALgAyADIALAAgAC0AMAAuADMAMwAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADIAMgAsACAALQAwAC4ANQA1ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBLAGkAbQBiAGUAcgBsAGUAeQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADAALgA4ACwAIAAwAC4ANQA1ACwAIAAwAC4ANwAsACAAMAAuADQANAAsACAAMAAuADYANgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADgALAAgADAALgA1ADUALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAEsAaQBtAGIAZQByAGwAZQB5AFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAuADYANgAsACAAMAAuADUANQAsACAAMAAuADUANQAsACAAMAAuADUANQAsACAAMAAuADEAMQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADYANgAsACAAMAAuADUANQAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwAC4AMwAzACwAIAAtADAALgA1ADUALAAgADAALgAxADEALAAgADAALgAxADEALAAgAC0AMAAuADQANAAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADMAMwAsACAALQAwAC4ANQA1ACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBBAGwAaQBjAGUAIABTAHAAcgBpAG4AZwBzAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAuADIAMgAsACAALQAwAC4AMgAzACwAIAAwAC4AMgA1ACwAIAAwAC4AMQA3ACwAIABcACIAXAAiACwAIAAwAC4AMQA4ACwAIAAtADAALgAyADgALAAgADAALgAzADIALAAgAFwAIgBcACIALAAgADAALgAyADQALAAgADAALgAyADUALAAgAC0AMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAQQBsAGkAYwBlACAAUwBwAHIAaQBuAGcAcwBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADAALgA2ADYALAAgADAALgAyACwAIAAwAC4ANgAyACwAIAAwAC4ANQA0ACwAIABcACIAXAAiACwAIAAwAC4AMwA4ACwAIAAwAC4AMgA3ACwAIAAwAC4ANwA1ACwAIABcACIAXAAiACwAIAAwAC4ANgA0ACwAIAAwAC4ANQA1ACwAIAAwAC4ANAA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBBAGwAaQBjAGUAIABTAHAAcgBpAG4AZwBzAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAuADQAOQAsACAAMAAuADEAMwAsACAAMAAuADUANAAsACAAMAAuADQANQAsACAAXAAiAFwAIgAsACAAMAAuADMANQAsACAAMAAuADEANQAsACAAMAAuADYAMwAsACAAXAAiAFwAIgAsACAAMAAuADUANAAsACAAMAAuADQAMgAsACAAMAAuADIANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAQQBsAGkAYwBlACAAUwBwAHIAaQBuAGcAcwBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADAALgAyADcALAAgAC0AMAAuADgALAAgADAALgAyADIALAAgADAALgAwADkALAAgAFwAIgBcACIALAAgADAALgAxADIALAAgADAALgAwADIALAAgADAALgAyADUALAAgAFwAIgBcACIALAAgADAALgAxADgALAAgADAALgAxADIALAAgADAALgAwADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAEIAYQByAGsAbAB5AFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAuADIAMgAsACAALQAwAC4ANAA0ACwAIAAwAC4AMgAsACAAMAAuADIAMQAsACAAXAAiAFwAIgAsACAAMAAuADEAOAAsACAAMAAuADAAMQAsACAAMAAuADEAMgAsACAAXAAiAFwAIgAsACAAMAAuADAAOQAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAQgBhAHIAawBsAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAwAC4ANgA2ACwAIAAwAC4AMgAyACwAIAAwAC4ANgA4ACwAIAAwAC4AMgAyACwAIABcACIAXAAiACwAIAAwAC4AMgA0ACwAIAAwAC4AMgA1ACwAIAAwAC4ANgA0ACwAIABcACIAXAAiACwAIAAwAC4AMwA3ACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBCAGEAcgBrAGwAeQBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADAALgA0ADkALAAgADAALgAwADUALAAgADAALgA2ADQALAAgADAALgAyADUALAAgAFwAIgBcACIALAAgADAALgAyADkALAAgADAALgAxADIALAAgADAALgA1ADcALAAgAFwAIgBcACIALAAgADAALgA0ADkALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAEIAYQByAGsAbAB5AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADIANwAsACAALQAwAC4AMgA3ACwAIAAwAC4AMwAxACwAIAAwAC4AMgA5ACwAIABcACIAXAAiACwAIAAwAC4AMQA5ACwAIAAwAC4AMAA0ACwAIAAwAC4AMgA2ACwAIABcACIAXAAiACwAIAAwAC4AMgA4ACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AVABcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAwAC4AMgAyACwAIAAtADAALgA0ADQALAAgADAALAAgADAALgAxADUALAAgAFwAIgBcACIALAAgADAALgAwADgALAAgADAALgAxADcALAAgADAALgAwADYALAAgAFwAIgBcACIALAAgADAALgAwADIALAAgAC0AMAAuADEANAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAuADYANgAsACAAMAAuADIAMgAsACAAMAAuADcAOQAsACAAMAAuADQALAAgAFwAIgBcACIALAAgADAALgAzADgALAAgADAALgAyADcALAAgADAALgA4ACwAIABcACIAXAAiACwAIAAwAC4AMQA2ACwAIAAwAC4AMwAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAuADQAOQAsACAAMAAuADAANQAsACAAMAAuADUANQAsACAAMAAuADMAOAAsACAAXAAiAFwAIgAsACAAMAAuADMANgAsACAAMAAuADAANgAsACAAMAAuADUAOAAsACAAXAAiAFwAIgAsACAAMAAuADIAMwAsACAAMAAuADQALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADAALgAyADcALAAgAC0AMAAuADIANwAsACAAMAAuADAAMgAsACAAMAAuADAAOQAsACAAXAAiAFwAIgAsACAAMAAuADEANgAsACAALQAwAC4AMAA0ACwAIAAwAC4AMgAxACwAIABcACIAXAAiACwAIAAwAC4AMAAzACwAIAAwAC4AMQAxACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAEgAaQBnAGgAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAwAC4AMgA3ACwAIAAtADAALgAxADkALAAgADAALgAzADgALAAgADAALgAyADUALAAgAFwAIgBcACIALAAgADAALgAwADcALAAgADAALgAwADUALAAgADAALgA1ADIALAAgAFwAIgBcACIALAAgADAALgA1ADUALAAgADAALgAxADkALAAgADAALgA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAEgAaQBnAGgAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAwAC4AMQA2ACwAIAAwAC4AMQA2ACwAIAAwAC4AOAAsACAAMAAuADUANwAsACAAXAAiAFwAIgAsACAAMAAuADcANgAsACAAMAAuADQAOQAsACAAMAAuADgANAAsACAAXAAiAFwAIgAsACAAMAAuADUAMQAsACAAMAAuADMANgAsACAAMAAuADEANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBIAGkAZwBoAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAuADQANQAsACAAMAAuADEALAAgADAALgA0ADkALAAgADAALgA0ADEALAAgAFwAIgBcACIALAAgADAALgA0ACwAIAAwAC4AMQA3ACwAIAAwAC4ANQA0ACwAIABcACIAXAAiACwAIAAwAC4ANgA0ACwAIAAtADAALgAwADUALAAgADAALgAzADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIASABpAGcAaABcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADAALgA1ADEALAAgAC0AMAAuADAANwAsACAAMAAuADEAMwAsACAALQAwAC4AMAA5ACwAIABcACIAXAAiACwAIAAtADAALgAxADMALAAgADAALgAwADcALAAgADAALgAyADUALAAgAFwAIgBcACIALAAgADAALgA3ADEALAAgADAALgAxADcALAAgADAALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATQBvAGQAZQByAGEAdABlAC8ASABpAGcAaABcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgAC0AMAAuADEAMgAsACAALQAwAC4AMQA5ACwAIAAwAC4ANAAxACwAIAAwAC4AMAA5ACwAIABcACIAXAAiACwAIAAwAC4ANAAxACwAIAAtADAALgAxADkALAAgADAALgAwADcALAAgAFwAIgBcACIALAAgADEALgAwADcALAAgAC0AMAAuADAAOAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBNAG8AZABlAHIAYQB0AGUALwBIAGkAZwBoAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAuADYANQAsACAAMAAuADEAOQAsACAAMAAuADYANQAsACAAMAAuADUAMQAsACAAXAAiAFwAIgAsACAAMAAuADEAOAAsACAAMAAuADYAMwAsACAAMQAuADMALAAgAFwAIgBcACIALAAgADAALgA0ADgALAAgADEALgAxADIALAAgADAALgAzADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATQBvAGQAZQByAGEAdABlAC8ASABpAGcAaABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADAALgA3ACwAIAAwAC4AMQAzACwAIAAwAC4ANQAyACwAIAAwAC4AMwA0ACwAIABcACIAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAA0ACwAIAAwAC4ANwA3ACwAIABcACIAXAAiACwAIAAwAC4ANAAyACwAIAAwAC4AMQAyACwAIAAwAC4ANwA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEgAaQBnAGgAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwAC4AMwAyACwAIAAtADAALgAwADYALAAgADAALgAyADUALAAgADAALgAxADkALAAgAFwAIgBcACIALAAgAC0AMAAuADEALAAgAC0AMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAFwAIgAsACAAMAAuADIAMwAsACAALQAwAC4AMQAzACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEwAbwB3AFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAuADYAMgAsACAALQAwAC4AMQA5ACwAIAAwAC4AMwA3ACwAIAAwAC4ANAAxACwAIABcACIAXAAiACwAIAAwAC4AMAA2ACwAIAAtADAALgAwADIALAAgADAALgA0ADcALAAgAFwAIgBcACIALAAgADAALgA0ADQALAAgADAALgAzACwAIAAwAC4AMQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEwAbwB3AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAuADAANQAsACAAMAAuADEAOQAsACAAMAAuADMAMQAsACAAMAAuADUANAAsACAAXAAiAFwAIgAsACAAMAAuADUAMwAsACAAMAAuADEANQAsACAAMAAuADIAOAAsACAAXAAiAFwAIgAsACAAMAAuADUANwAsACAAMAAuADQAMgAsACAAMAAuADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATQBvAGQAZQByAGEAdABlAC8ATABvAHcAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAwAC4AMwAzACwAIAAwAC4AMQAzACwAIAAwAC4AMwA5ACwAIAAwAC4AMwA2ACwAIABcACIAXAAiACwAIAAwAC4AMgA2ACwAIAAwAC4AMQAxACwAIAAwAC4ANAAsACAAXAAiAFwAIgAsACAAMAAuADQANAAsACAAMAAuADMANwAsACAALQAwAC4AMAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE0AbwBkAGUAcgBhAHQAZQAvAEwAbwB3AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADYAMQAsACAALQAwAC4AMAA2ACwAIAAwAC4AMgAxACwAIAAwAC4AMQA4ACwAIABcACIAXAAiACwAIAAwAC4AMQAyACwAIAAwAC4AMAA2ACwAIAAwAC4AMgA5ACwAIABcACIAXAAiACwAIAAwAC4ANAAxACwAIAAwAC4ANAAxACwAIAAtADAALgAxADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATABvAHcAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAtADAALgAyADAALAAgADAALgAwADIALAAgADAALgAyADQALAAgADAALgAzADAALAAgAFwAIgBcACIALAAgADAALgAyADMALAAgAC0AMAAuADAANQAsACAAMAAuADMANAAsACAAXAAiAFwAIgAsACAAMAAuADMAMAAsACAAMAAuADUANwAsACAAMAAuADUAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBMAG8AdwBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADAALgA2ADIALAAgADAALgAyADEALAAgADAALgAyADUALAAgADAALgAzADIALAAgAFwAIgBcACIALAAgADAALgA0ADcALAAgADAALgAzADEALAAgADAALgAxADQALAAgAFwAIgBcACIALAAgADAALgA0ADAALAAgADAALgAyADYALAAgADAALgA0ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIATABvAHcAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAwAC4ANAAwACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyACwAIAAwAC4AMgA3ACwAIABcACIAXAAiACwAIAAwAC4AMwAwACwAIAAwAC4AMAA4ACwAIAAwAC4AMQAzACwAIABcACIAXAAiACwAIAAwAC4AMgA0ACwAIAAwAC4AMQA1ACwAIAAwAC4AMgAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAEwAbwB3AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAuADAAOAAsACAAMAAuADAANAAsACAAMAAuADAANgAsACAAMAAuADEAOAAsACAAXAAiAFwAIgAsACAAMAAuADEAMQAsACAALQAwAC4AMAA3ACwAIAAwAC4AMQAzACwAIABcACIAXAAiACwAIAAwAC4AMQA2ACwAIAAwAC4ANAAwACwAIAAwAC4AMwAzAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMwBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXABuAHAAZQByACAAYwBlAG4AdABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAzAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlACAALQAgAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAbwBmACAAZgBlAGUAZAAgAGkAbgB0AGEAawBlACAAKABwAGUAcgAgAGMAZQBuAHQAKQBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMwBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADMAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBEAHIAeQBNAGEAdAB0AGUAcgBEAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAyACAALQAgAFQAYQBiAGwAZQAgAEEANQAuADUALgAyAC4AMwBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMwBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAQwBUACAAYQBuAGQAIABOAFMAVwAgAHMAcABsAGkAdAAuAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAzAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADYALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBSAGUAZwBpAG8AbgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIABcACIAXAAiACwAIAA1ADUALAAgADYANQAsACAANgAwACwAIAA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIABcACIAXAAiACwAIAA1ADUALAAgADYANQAsACAANgAwACwAIAA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAFwAIgAsACAANQA1ACwAIAA2ADEALAAgADUANwAsACAANQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAFwAIgAsACAANQAzACwAIAA1ADcALAAgADUANQAsACAANQAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQBcACIALAAgAFwAIgBcACIALAAgADcAMAAsACAANQA1ACwAIAA1ADUALAAgADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBcACIALAAgADcANQAsACAANgAwACwAIAA3ADAALAAgADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALAAgAFwAIgBcACIALAAgADgAMAAsACAANQA1ACwAIAA2ADAALAAgADcANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUwBvAHUAdABoACAAVwBlAHMAdABcACIALAAgADgAMAAsACAANQA4ACwAIAA1ADAALAAgADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUABpAGwAYgBhAHIAYQBcACIALAAgADQAMAAsACAANgA1ACwAIAA1ADUALAAgADQANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIAA0ADAALAAgADYANQAsACAANQA1ACwAIAA0ADUAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANABfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAC0AIABDAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGYAZQBlAGQAIABpAG4AdABhAGsAZQAgACgAZgByAGEAYwB0AGkAbwBuACkAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA0AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgAgAC0AIABUAGEAYgBsAGUAIABBADUALgA1AC4AMgAuADQAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAEMAVAAgAGEAbgBkACAATgBTAFcAIABzAHAAbABpAHQALgBcACIAKQA7AFwAbgBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANABfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUAXAAiACwAIABcACIAUgBlAGcAaQBvAG4AXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADAANwAsACAAMAAuADEAMwAsACAAMAAuADEALAAgADAALgAwADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIABcACIAXAAiACwAIAAwAC4AMAA3ACwAIAAwAC4AMQAzACwAIAAwAC4AMQAsACAAMAAuADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAXAAiACwAIAAwAC4AMAA1ADgALAAgADAALgAwADkAMgAsACAAMAAuADAANwA1ACwAIAAwAC4AMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIAXAAiACwAIAAwAC4AMAA3ADIALAAgADAALgAwADkAOQAsACAAMAAuADAANwA4ACwAIAAwAC4AMAA1ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADEANgAsACAAMAAuADAANwAsACAAMAAuADAAOQAsACAAMAAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIABcACIAXAAiACwAIAAwAC4AMgAsACAAMAAuADEALAAgADAALgAxADYALAAgADAALgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsACAAXAAiAFwAIgAsACAAMAAuADIANQAsACAAMAAuADAANwAsACAAMAAuADEALAAgADAALgAyADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiACwAIAAwAC4AMgAsACAAMAAuADAAOQAsACAAMAAuADAANgAsACAAMAAuADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFAAaQBsAGIAYQByAGEAXAAiACwAIAAwAC4AMAA0ACwAIAAwAC4AMQAyACwAIAAwAC4AMAA5ACwAIAAwAC4AMAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBLAGkAbQBiAGUAcgBsAGUAeQBcACIALAAgADAALgAwADQALAAgADAALgAxADIALAAgADAALgAwADkALAAgADAALgAwADYAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA1AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA1AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAEMAYQB0AHQAbABlACAALQAgAEYAZQBlAGQAIABpAG4AdABhAGsAZQAgAGEAZABqAHUAcwB0AG0AZQBuAHQAIABhAG4AZAAgAG0AaQBsAGsAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAYQBuAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA1AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA1AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgAgAC0AIABUAGEAYgBsAGUAIABBADUALgA1AC4AMgAuADUAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADUAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAEMAVAAgAGEAbgBkACAATgBTAFcAIABzAHAAbABpAHQALgAgAFMAdABhAHQAZQAgAG4AYQBtAGUAcwAgAHIAZQBwAGwAYQBjAGUAZAAgAGIAeQAgAGEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGQAYQB0AGEAIABsAG8AbwBrAHUAcAAuAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA1AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ADEALAAgADUALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQBcACIALAAgAFwAIgBSAGUAZwBpAG8AbgBcACIALAAgAFwAIgBTAGUAYQBzAG8AbgBcACIALAAgAFwAIgBGAGUAZQBkACAAYQBkAGoAdQBzAHQAbQBlAG4AdABcACIALAAgAFwAIgBNAGkAbABrACAAaQBuAHQAYQBrAGUAIAAvACAAcAByAG8AZAB1AGMAdABpAG8AbgAgACgAawBnAC8AZABhAHkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAxAC4AMwAsACAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEALgAxACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBTAFcAXAAiACwAIABcACIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAxAC4AMwAsACAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEALgAxACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBUAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxAC4AMwAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAxAC4AMQAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFQAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEALgAzACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFEATABEAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQAuADEALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQBMAEQAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBBAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAxAC4AMwAsACAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAxAC4AMQAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAHAAcgBpAG4AZwBcACIALAAgADEALgAzACwAIAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMQAuADEALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABBAFMAXAAiACwAIABcACIAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEkAQwBcACIALABcACIAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYASQBDAFwAIgAsAFwAIgBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBJAEMAXAAiACwAXAAiAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMQAuADMALAAgADYAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBJAEMAXAAiACwAXAAiAFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMQAuADEALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAFcAZQBzAHQAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAwACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgAsACAAXAAiAFMAdQBtAG0AZQByAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUwBvAHUAdABoACAAVwBlAHMAdABcACIALAAgAFwAIgBBAHUAdAB1AG0AbgBcACIALAAgADEALgAzACwAIAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgAsACAAXAAiAFcAaQBuAHQAZQByAFwAIgAsACAAMQAuADEALAAgADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAFAAaQBsAGIAYQByAGEAXAAiACwAIABcACIAUwBwAHIAaQBuAGcAXAAiACwAIAAxAC4AMwAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUABpAGwAYgBhAHIAYQBcACIALAAgAFwAIgBTAHUAbQBtAGUAcgBcACIALAAgADEALgAxACwAIAAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAQQBcACIALAAgAFwAIgBQAGkAbABiAGEAcgBhAFwAIgAsACAAXAAiAEEAdQB0AHUAbQBuAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIAUABpAGwAYgBhAHIAYQBcACIALAAgAFwAIgBXAGkAbgB0AGUAcgBcACIALAAgADAALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBBAFwAIgAsACAAXAAiAEsAaQBtAGIAZQByAGwAZQB5AFwAIgAsACAAXAAiAFMAcAByAGkAbgBnAFwAIgAsACAAMAAsACAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIABcACIAUwB1AG0AbQBlAHIAXAAiACwAIAAxAC4AMwAsACAANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIABcACIAQQB1AHQAdQBtAG4AXAAiACwAIAAxAC4AMQAsACAAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAEEAXAAiACwAIABcACIASwBpAG0AYgBlAHIAbABlAHkAXAAiACwAIABcACIAVwBpAG4AdABlAHIAXAAiACwAIAAwACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA2AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXABuAGsAZwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA2AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAC0AIABTAHQAYQBuAGQAYQByAGQAIAByAGUAZgBlAHIAZQBuAGMAZQAgAHcAZQBpAGcAaAB0AHMAIAAoAGsAZwApAFwAIgApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA2AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADYAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMgAgAC0AIABUAGEAYgBsAGUAIABBADUALgA1AC4AMgAuADYAXAAiACkAOwBcAG4AXABuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADYAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAIABhAG4AZAAgAE4AUwBXACAAcwBwAGwAaQB0AC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdABhAHQAZQAgAG4AYQBtAGUAcwAgAHIAZQBwAGwAYQBjAGUAZAAgAGIAeQAgAGEAYgBiAHIAZQB2AGkAYQB0AGkAbwBuAHMAIAB0AG8AIABhAGkAZAAgAGQAYQB0AGEAIABsAG8AbwBrAHUAcAAuAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAbAB1AHIAYQBsAGkAcwBlAGQAIABcAHUAMAAwADIANwBTAHQAZQBlAHIAXAB1ADAAMAAyADcAIAB0AG8AIABcAHUAMAAwADIANwBTAHQAZQBlAHIAcwBcAHUAMAAwADIANwAgAGYAbwByACAAYwBvAG4AcwBpAHMAdABlAG4AYwB5AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA2AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAOAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlAFwAIgAsACAAXAAiAEIAdQBsAGwAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBCAHUAbABsAHMAIABcAHUAMAAwADMAZQAgADEAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBDAG8AdwBzACAAMQAtADIAXAAiACwAIABcACIAQwBvAHcAcwAgAFwAdQAwADAAMwBlACAAMgBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgAFwAdQAwADAAMwBjACAAMQBcACIALAAgAFwAIgBTAHQAZQBlAHIAcwAgAFwAdQAwADAAMwBlACAAMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBDAFQAXAAiACwAIAA3ADAAMAAsACAANwAwADAALAAgADYAMAAwACwAIAA1ADAAMAAsACAANQAwADAALAAgADUAMAAwACwAIAA2ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAFMAVwBcACIALAAgADcAMAAwACwAIAA3ADAAMAAsACAANgAwADAALAAgADUAMAAwACwAIAA1ADAAMAAsACAANQAwADAALAAgADYAMAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAANwA3ADAALAAgADcANwAwACwAIAA2ADYAMAAsACAANQA1ADAALAAgADUANQAwACwAIAA1ADUAMAAsACAANgA2ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgADcANwAwACwAIAA3ADcAMAAsACAANgA2ADAALAAgADUANQAwACwAIAA1ADUAMAAsACAANQA1ADAALAAgADYANgAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAANwA3ADAALAAgADcANwAwACwAIAA2ADYAMAAsACAANQA1ADAALAAgADUANQAwACwAIAA1ADUAMAAsACAANgA2ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABhAHMAbQBhAG4AaQBhAFwAIgAsACAANwA3ADAALAAgADcANwAwACwAIAA2ADYAMAAsACAANQA1ADAALAAgADUANQAwACwAIAA1ADUAMAAsACAANgA2ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAANwA3ADAALAAgADcANwAwACwAIAA2ADYAMAAsACAANQA1ADAALAAgADUANQAwACwAIAA1ADUAMAAsACAANgA2ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAANwA3ADAALAAgADcANwAwACwAIAA2ADYAMAAsACAANQA1ADAALAAgADUANQAwACwAIAA1ADUAMAAsACAANgA2ADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAZQB0AHUAcgBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGYAcgBvAG0AIABhAGwAbAAgAHAAYQBzAHQAdQByAGUAIAB0AHkAcABlAHMAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXABuAEUATgAyAE8AXABuAHQAIABOADIATwBcAG4ARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAcAB9AFwAXABsAGUAZgB0ACgATQBfAHAAXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgBpAH0AXABcAHQAaQBtAGUAcwAgAEMAXwB7AE4AMgBPAH0AXABcAHQAaQBtAGUAcwB7ADEAMAB9AF4AewAtADMAfQBcAFwAcgBpAGcAaAB0ACkAXABuAE0AcAAgAD0AIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcABhAHMAdAB1AHIAZQAgAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIAAoAGsAZwAgAE4AKQBcAG4ARQBGAE4AaQAgAD0AIABlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbAAgAGkAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlACAAaQAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAbgBDAE4AMgBPACAAPQAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4AcAAgAD0AIABQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcAG4AaQAgAD0AIABDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AcAAsACAARQBGAE4AaQAsACAAQwBOADIATwAsAFwAbgAgACAAIAAgAE0AcAAgACoAIABFAEYATgBpACAAKgAgAEMATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB0AGgAZQAgAHIAZQB0AHUAcgBuACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAGYAcgBvAG0AIABhAGwAbAAgAHAAYQBzAHQAdQByAGUAIAB0AHkAcABlAHMAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAF8AewBwAH0AXABcAGwAZQBmAHQAKABNAF8AcABcAFwAdABpAG0AZQBzACAARQBGAF8AewBOAGkAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzAHsAMQAwAH0AXgB7AC0AMwB9AFwAXAByAGkAZwBoAHQAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBwAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAcABhAHMAdAB1AHIAZQAgAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIAAoAGsAZwAgAE4AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAE4AaQBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAIABpAG4AIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAIAAoAGsAZwAgAE4AMgBPAC0ATgAvAGsAZwAgAE4AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBnAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHAAXAAiACwAXAAiAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcgBlAHQAdQByAG4AZQBkACAAdABvACAAdABoAGUAIABzAG8AaQBsAFwAbgBNAHAAXABuAGsAZwAgAE4AXABuAE0AXwBwACAAPQAgACgAQQBfAHAAIADXACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACAARgBGAE8ARABfAHAAKQAgAFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBwAH0AKQAgACsAIAAoAEEAXwBwACAAXABcAHQAaQBtAGUAcwAgACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAcAB9ACAAXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQgBHAHAAfQApAFwAbgBBAHAAIAA9ACAAYQByAGUAYQAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAByAGUAbgBlAHcAZQBkACAAbwByACAAcgBlAG0AbwB2AGUAZAAgACgAaABhACkAXABuAFkAcAAgAD0AIABhAHYAZQByAGEAZwBlACAAeQBpAGUAbABkACAAbwBmACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAIAAoAHQAIABEAE0ALwBoAGEAKQBcAG4ATgBDAEEARwBwACAAPQAgAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAbgBSAEIARwBwACAAPQAgAGIAZQBsAG8AdwAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAHIAYQB0AGkAbwAgAGYAbwByACAAcABhAHMAdAB1AHIAZQAgAGMAcgBvAHAAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ATgBDAEIARwBwACAAPQAgAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYgBlAGwAbwB3AC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcAG4ARgBGAE8ARABwACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBwACAAPQAgAFAAYQBzAHQAdQByAGUAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBwACwAIABZAHAALAAgAEYARgBPAEQAcAAsACAATgBDAEEARwBwACwAIABSAEIARwBwACwAIABOAEMAQgBHAHAALABcAG4AIAAgACAAIAAoAEEAcAAgACoAIAAoAFkAcAAgACoAIAAxADAAXgAoAC0AMwApACkAIAAqACAAKAAxACAALQAgAEYARgBPAEQAcAApACAAKgAgAE4AQwBBAEcAcAApACAAKwAgACgAQQBwACAAKgAgACgAWQBwACAAKgAgADEAMABeACgALQAzACkAKQAgACoAIABSAEIARwBwACAAKgAgAE4AQwBCAEcAcAApAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AcABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADIALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AcAAgAD0AIAAoAEEAXwBwACAAXABcAHQAaQBtAGUAcwAgACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApACAAXABcAHQAaQBtAGUAcwAgACgAMQAtACAARgBGAE8ARABfAHAAKQAgAFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBwAH0AKQAgACsAIAAoAEEAXwBwACAAXABcAHQAaQBtAGUAcwAgACgAWQBfAHAAIABcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAXAB0AGkAbQBlAHMAIABSAF8AewBCAEcAcAB9ACAAXABcAHQAaQBtAGUAcwAgAE4AQwBfAHsAQgBHAHAAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHAAXAAiACwAXAAiAGEAcgBlAGEAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAcgBlAG4AZQB3AGUAZAAgAG8AcgAgAHIAZQBtAG8AdgBlAGQAIAAoAGgAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBZAHAAXAAiACwAXAAiAGEAdgBlAHIAYQBnAGUAIAB5AGkAZQBsAGQAIABvAGYAIABwAGEAcwB0AHUAcgBlACAAYwByAG8AcAAgACgAdAAgAEQATQAvAGgAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEMAQQBHAHAAXAAiACwAXAAiAE4AIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAYQBiAG8AdgBlAC0AZwByAG8AdQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBSAEIARwBwAFwAIgAsAFwAIgBiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIAByAGEAdABpAG8AIABmAG8AcgAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AQwBCAEcAcABcACIALABcACIATgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABiAGUAbABvAHcALQBnAHIAbwB1AG4AZAAgAHAAYQBzAHQAdQByAGUAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAEYATwBEAHAAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHAAYQBzAHQAdQByAGUAIAB5AGkAZQBsAGQAIAB0AGgAYQB0ACAAaQBzACAAcgBlAG0AbwB2AGUAZAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAdAB5AHAAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAZQBuAHQAZQByAHAAcgBpAHMAZQAgAHQAeQBwAGUAcwBcAG4ARQB4AGMAZQBsACAAbQBvAGQAdQBsAGUAIABuAGEAbQBlADoAIABDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXABuAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAAoADAALgA2ADcAOAA0ACAAawBnAC8AbQAzACkAXABuAFQAYQBrAGUAbgAgAGYAcgBvAG0AIAB0AGgAZQAgAE4AYQB0AGkAbwBuAGEAbAAgAEcAcgBlAGUAbgBoAG8AdQBzAGUAIABhAG4AZAAgAEUAbgBlAHIAZwB5ACAAUgBlAHAAbwByAHQAaQBuAGcAIABcAG4AKABNAGUAYQBzAHUAcgBlAG0AZQBuAHQAKQAgAEQAZQB0AGUAcgBtAGkAbgBhAHQAaQBvAG4AIAAyADAAMAA4AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHAAIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcALwBtADMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgAxAGEAXwAyACwAIAAzAC4AQgAuADEAYwBfADIALAAgADMALgBCAC4AMwBfADEALAAgADMALgBCAC4ANABnAF8AMgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADYANwA4ADQAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAFwAbgBDAGcAIAA9ACAANAA0AC8AMgA4ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAATgAyAE8AIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAYQBjAHQAbwByAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgANAA0AC8AMgA4ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAFwAbgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABnAGEAcwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAZwBhAHMAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBDAGcAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgBcACIALAAgAFwAIgBDAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAAxAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgADIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwAyAFwAIgAsACAAXAAiADQANAAvADEAMgBcACIALAAgADQANAAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMASAA0AFwAIgAsACAAXAAiADEANgAvADEAMgBcACIALAAgADEANgAsACAAMQAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AMgBPAFwAIgAsACAAXAAiADQANAAvADIAOABcACIALAAgADQANAAsACAAMgA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwB4AFwAIgAsACAAXAAiADQANgAvADEANABcACIALAAgADQANgAsACAAMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMATwBcACIALAAgAFwAIgAyADgALwAxADIAXAAiACwAIAAyADgALAAgADEAMgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgAgAEwAaQBtAGUAXAAiACwAIABcACIANAA0AC8AMQAyAFwAIgAsACAANAA0ACwAIAAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBNAFYATwBDAFwAIgAsACAAXAAiADEANAAvADEAMgBcACIALAAgADEANAAsACAAMQAyAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABOADIATwBcAG4ARwBsAG8AYgBhAGwAIAB3AGEAcgBtAGkAbgBnACAAcABvAHQAZQBuAHQAaQBhAGwAIABmAG8AcgAgAGcAcgBlAGUAbgBoAG8AdQBzAGUAIABnAGEAcwBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABnAHIAZQBlAG4AaABvAHUAcwBlACAAZwBhAHMAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBXAFAATgAyAE8AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgBhAGMAdABvAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEcAVwBQAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADgALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAYQBzAFwAIgAsACAAXAAiAEMATwAyAC0AZQAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE8AMgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBIADQAXAAiACwAIAAyADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgAyAE8AXAAiACwAIAAyADYANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAEYANABcACIALAAgADYANgAzADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwAyAEYANgBcACIALAAgADEAMgAyADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAEYANgBcACIALAAgADIAMgA4ADAAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAEYAMwBcACIALAAgADEANwAyADAAMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwB0AGEAdABlAHMAIABhAG4AZAAgAHQAZQByAHIAaQB0AG8AcgBpAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBBAHUAcwB0AHIAYQBsAGkAYQBuAFMAdABhAHQAZQBzAFQAZQByAHIAaQB0AG8AcgBpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA5ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAYQB0AGUALwBUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBDAG8AbQBtAG8AbgAgAE4AYQBtAGUAXAAiACwAIABcACIAQQBiAGIAcgBlAHYAaQBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAE4AUwBXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAQwBhAHAAaQB0AGEAbAAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEEAQwBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAVgBpAGMAdABvAHIAaQBhAFwAIgAsACAAXAAiAFYASQBDAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIAUQBMAEQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFMAQQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAFcAZQBzAHQAZQByAG4AIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBXAEEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIAVABBAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AbwByAHQAaABlAHIAbgAgAFQAZQByAHIAaQB0AG8AcgB5AFwAIgAsACAAXAAiAE4AVABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBCAFMAIABTAHQAYQB0AGkAcwB0AGMAYQBsACAAQQByAGUAYQBzACAATABlAHYAZQBsACAANAAgAC0AIABXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAEIAdQByAGUAYQB1ACAAbwBmACAAUwB0AGEAdABpAHMAdABpAGMAcwAgACgAQQBCAFMAKQAgAC0AIABTAHQAYQB0AGkAcwB0AGkAYwBhAGwAIABBAHIAZQBhAHMAIABMAGUAdgBlAGwAIAAyACAALQAgADIAMAAyADEAIAAtACAAUwBoAGEAcABlAGYAaQBsAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAQQAgADQAIABOAGEAbQBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAHUAbgBiAHUAcgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGEAbgBkAHUAcgBhAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABJAG4AbgBlAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABOAG8AcgB0AGgAIABFAGEAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAGUAcgB0AGgAIAAtACAATgBvAHIAdABoACAAVwBlAHMAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABlAHIAdABoACAALQAgAFMAbwB1AHQAaAAgAEUAYQBzAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAZQByAHQAaAAgAC0AIABTAG8AdQB0AGgAIABXAGUAcwB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAVwBoAGUAYQB0ACAAQgBlAGwAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE8AdQB0AGIAYQBjAGsAIAAoAE4AbwByAHQAaAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAATwB1AHQAYgBhAGMAawAgACgAUwBvAHUAdABoACkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAyADoAIABUAHIAYQBuAHMAbABhAHQAaQBuAGcAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBzACAAdABvACAAdwBlAHQAIABhAG4AZAAgAGQAcgB5ACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAdwBhAHIAbQAgAC8AIABjAG8AbwBsACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAvACAAZAByAHkAIAAtACAAbABvAHcAIABmAHIAbwBzAHQAIABhAG4AZAAgAGgAaQBnAGgAIAB0AGUAbQBwACAAYwBsAGEAcwBzAGUAcwAgAHQAbwAgAGEAYwBjAG8AbQBtAG8AZABhAHQAZQAgAGMAbABpAG0AYQB0AGUAIABzAGMAZQBuAGEAcgBpAG8AcwAgAGUAeABjAGwAdQBkAGUAZAAgAGIAeQAgAFYARQBFAFIARwAgAGMAcgBpAHQAZQByAGkAYQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGkAeABlAGQAIAB0AHkAcABvACAALQAgAEMAaABhAG4AZwBlAGQAIABcAHUAMAAwADIANwBGAHIAeQBcAHUAMAAwADIANwAgAHQAbwAgAFwAdQAwADAAMgA3AEQAcgB5AFwAdQAwADAAMgA3AC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbABpAG0AYQB0AGUAIABaAG8AbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAbwByACAARAByAHkAIABaAG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABkAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFcAYQByAG0AIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBXAGUAdAAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdABcACIALAAgAFwAIgBEAHIAeQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGEAcgBtACAAdABlAG0AcABlAHIAYQB0AGUAIABtAG8AaQBzAHQAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAaABpAGcAaAAgAHQAZQBtAHAAXAAiACwAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAFcAZQB0ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5ACAALQAgAGwAbwB3ACAAZgByAG8AcwB0AFwAIgAsACAAXAAiAEQAcgB5ACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIAB3AGEAcgBtACAALwAgAGMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAG0AbwBpAHMAdAAgAC8AIABkAHIAeQAgAC0AIABsAG8AdwAgAGYAcgBvAHMAdAAgAGEAbgBkACAAaABpAGcAaAAgAHQAZQBtAHAAIABjAGwAYQBzAHMAZQBzACAAdABvACAAYQBjAGMAbwBtAG0AbwBkAGEAdABlACAAYwBsAGkAbQBhAHQAZQAgAHMAYwBlAG4AYQByAGkAbwBzACAAZQB4AGMAbAB1AGQAZQBkACAAYgB5ACAAVgBFAEUAUgBHACAAYwByAGkAdABlAHIAaQBhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAaQB4AGUAZAAgAHQAeQBwAG8AIABpAG4AIABNAEEAVAAgAHYAYQBsAHUAZQAgAGYAbwByACAAdwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAIAAtACAAYwBoAGEAbgBnAGUAZAAgADEAMAAgAHQAbwAgADEAMQAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABtAGkAbgAgAGEAbgBkACAAbQBhAHgAIABjAG8AbAB1AG0AbgBzACAAZgBvAHIAIABNAEEAVAAsACAATQBBAFAALAAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAIABwAGUAcgAgAHkAZQBhAHIALAAgAGUAbABlAHYAYQB0AGkAbwBuACwAIABNAEEAUAA6AFAARQBUACAAdABvACAAYwBhAGwAYwB1AGwAYQB0AGUAIAB6AG8AbgBlAHMAIABmAHIAbwBtACAAcgBlAGEAbAAgAGMAbABpAG0AYQB0AGUAIABkAGEAdABhAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAQQBGACAAYQBjAGMAZQBwAHQAcwAgAHIAYQBpAG4AZgBhAGwAbAAgAGEAcwAgAGEAIABwAHIAbwB4AHkAIABmAG8AcgAgAHAAcgBlAGMAaQBwAGkAdABhAHQAaQBvAG4ALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOQAsACAAMQA2ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAEEAVABcACIALAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBGAHIAbwBzAHQAIABkAGEAeQBzACAAcABlAHIAIAB5AGUAYQByAFwAIgAsACAAXAAiAEUAbABlAHYAYQB0AGkAbwBuAFwAIgAsACAAXAAiAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIAB0AGUAbQBwAFwAIgAsACAAXAAiAE0AYQB4ACAAdABlAG0AcABcACIALAAgAFwAIgBNAGkAbgAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGEAeAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBNAGkAbgAgAGYAcgBvAHMAdAAgAGQAYQB5AHMAXAAiACwAIABcACIATQBhAHgAIABmAHIAbwBzAHQAIABkAGEAeQBzAFwAIgAsACAAXAAiAE0AaQBuACAAZQBsAGUAdgBhAHQAaQBvAG4AXAAiACwAIABcACIATQBhAHgAIABlAGwAZQB2AGEAdABpAG8AbgBcACIALAAgAFwAIgBNAGkAbgAgAE0AQQBQADoAUABFAFQAXAAiACwAIABcACIATQBpAG4AIABNAEEAUAA6AFAARQBUAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAbwBwAGkAYwBhAGwAIABtAG8AbgB0AGEAbgBlAFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAANwAsACAAMQAwADAAMAAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAHcAZQB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADIAMAAwADAAIABtAG0AXAAiACwAIABcACIAZCIgADcAXAAiACwAIABcACIAZCIgADEAMAAwADAAIABtAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAMQA4AC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAyADAAMAAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAG0AbwBpAHMAdABcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAOAAgAEMAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAMAAwACAAbQBtACAALQAgAGQiIAAyADAAMAAwACAAbQBtAFwAIgAsACAAXAAiAGQiIAA3AFwAIgAsACAAXAAiAGQiIAAxADAAMAAwACAAbQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgADEAOAAuADAAMAAxACwAIAA5ADkAOQA5ADkAOQAsACAAMQAwADAAMAAuADAAMAAxACwAIAAyADAAMAAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA3ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQAuADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBvAHAAaQBjAGEAbAAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQA4ACAAQwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AbQBcACIALAAgAFwAIgBkIiAANwBcACIALAAgAFwAIgBkIiAAMQAwADAAMAAgAG0AXAAiACwAIABcACIAQQBuAHkAXAAiACwAIAAxADgALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADEAMAAwADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADcALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5AC4AOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMQAwACAAQwBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBcAHUAMAAwADMAZQAgADEAXAAiACwAIAAxADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgADEALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQAgAHQAZQBtAHAAZQByAGEAdABlACAAZAByAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxADAAIABDAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAGQiIAAxAFwAIgAsACAAMQAwAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAgAC0AOQA5ADkAOQA5ADkALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG8AbAAgAHQAZQBtAHAAZQByAGEAdABlACAAbQBvAGkAcwB0AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAXAB1ADAAMAAzAGUAIAAxAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAAMQAwACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAxAC4AMAAwADEALAAgADkAOQA5ADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAIAB0AGUAbQBwAGUAcgBhAHQAZQAgAGQAcgB5AFwAIgAsACAAXAAiAFwAdQAwADAAMwBlACAAMAAgAEMAIAAtACAAZCIgADEAMAAgAEMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAZCIgADEAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADAALAAgAC0AOQA5ADkAOQA5ADkALAAgADkAOQA5ADkAOQA5ACwAIAAtADkAOQA5ADkAOQA5ACwAIAA5ADkAOQA5ADkAOQAsACAALQA5ADkAOQA5ADkAOQAsACAAOQA5ADkAOQA5ADkALAAgACAALQA5ADkAOQA5ADkAOQAsACAAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AdABlADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBUACAAPQAgAG0AZQBhAG4AIABhAG4AbgB1AGEAbAAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAIAA9ACAAbQBlAGEAbgAgAGEAbgBuAHUAYQBsACAAcAByAGUAYwBpAHAAaQB0AGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABFAFQAIAA9ACAAcABvAHQAZQBuAHQAaQBhAGwAIABlAHYAYQBwAG8AdAByAGEAbgBzAHAAaQByAGEAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAMQAuADMAOgAgAEMAbABpAG0AYQB0AGUAIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAIABjAGwAYQBzAHMAaQBmAGkAYwBhAHQAaQBvAG4AcwAgAGEAbgBkACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBGACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABNAEEAVAAgAG0AaQBuACAAYQBuAGQAIABNAEEAVAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAWgBvAG4AZQBcACIALAAgAFwAIgBNAGUAZABpAGEAbgAgAEEAbgBuAHUAYQBsACAAVABlAG0AcABlAHIAYQB0AHUAcgBlACAAKABNAEEAVAApAFwAIgAsACAAXAAiAE0AaQBuACAATQBBAFQAXAAiACwAIABcACIATQBhAHgAIABNAEEAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBhAHIAbQBcACIALAAgAFwAIgBlIiAAMgA2ACAAQwBcACIALAAgADIANgAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAG0AcABlAHIAYQB0AGUAXAAiACwAIABcACIAMQA1ACAALQAgADIANQAgAEMAXAAiACwAIAAxADUALAAgADIANQAuADkAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBvAGwAXAAiACwAIABcACIAZCIgADEANAAgAEMAXAAiACwAIAAtADkAOQA5ADkAOQA5ACwAIAAxADQALgA5ADkAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgADEALgAzADoAIABDAGwAaQBtAGEAdABlACAAYQBuAGQAIABSAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlACAAYwBsAGEAcwBzAGkAZgBpAGMAYQB0AGkAbwBuAHMAIABhAG4AZAAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ARgAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAAQQBkAGQAZQBkACAAZQB4AHQAcgBhACAAUgBhAGkAbgBmAGEAbABsACAAbQBpAG4AIABhAG4AZAAgAFIAYQBpAG4AZgBhAGwAbAAgAG0AYQB4ACAAYwBvAGwAdQBtAG4AcwAgAHQAbwAgAGMAYQBsAGMAdQBsAGEAdABlACAAegBvAG4AZQAgAGYAcgBvAG0AIAByAGUAYQBsACAAcgBhAGkAbgBmAGEAbABsACAAZABhAHQAYQAuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAANAAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBhAGkAbgBmAGEAbABsACAAWgBvAG4AZQBcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGkAbgBcACIALAAgAFwAIgBSAGEAaQBuAGYAYQBsAGwAIABtAGEAeABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIALAAgAFwAIgBBAG4AbgB1AGEAbAAgAHIAYQBpAG4AZgBhAGwAbAAgAFwAdQAwADAAMwBlACAANgAwADAAbQBtAFwAIgAsACAANgAwADAALgAwADAAMQAsACAAOQA5ADkAOQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiACwAIABcACIAQQBuAG4AdQBhAGwAIAByAGEAaQBuAGYAYQBsAGwAIABkIiAANgAwADAAbQBtAFwAIgAsACAALQA5ADkAOQA5ADkAOQAsACAANgAwADAAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIAAxAC4AMwA6ACAAQwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAUgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQAgAGMAbABhAHMAcwBpAGYAaQBjAGEAdABpAG8AbgBzACAAYQBuAGQAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhAFwAbgAgACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABaAG8AbgBlAFwAIgAsACAAXAAiAEwAZQBhAGMAaABpAG4AZwAgAGMAcgBpAHQAZQByAGkAYQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAbwBjAGMAdQByAHMAXAAiACwAIABcACIAowMoADXYX9w12E7cNdhW3DXYW9wpAFwAdQAwADAAMwBlAKMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABlAGEAYwBoAGkAbgBnACAAZABvAGUAcwAgAG4AbwB0ACAAbwBjAGMAdQByAFwAIgAsACAAXAAiAKMDKAA12F/cNdhO3DXYVtw12FvcKQBkIqMDKAA12DjcNdhH3DAAKQArADXYYNw12FzcNdhW3DXYWdwgADXYZNw12E7cNdhh3DXYUtw12F/cIAAOITXYXNw12FncNdhR3DXYVtw12FvcNdhU3CAANdhQ3DXYTtw12F3cNdhO3DXYUNw12FbcNdhh3DXYZtxcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcwAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAXAAiAEYAcgBhAGMAVwBFAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFkAZQBzACAALQAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAC0AIABuAG8AdAAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAXAAiACwAIAAwAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQB1AHMAdAByAGEAbABpAGEAbgAgAGQAYQB0AGEAIABzAGMAbwByAGUAcwAgAGYAbwByACAAcwBjAG8AcABlACAAMwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABYAFgAWABYAFgAWABYAFgAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8ARABhAHQAYQBcAG4AIAAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABhAHQAYQAgAHMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAEQAYQB0AGEAIABzAGMAbwByAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB0AGUAcgBuAGEAdABpAG8AbgBhAGwAIABzAGMAbwBwAGUAIAAzACAAZABhAHQAYQBiAGEAcwBlAFwAIgAsACAAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAHUAcwB0AHIAYQBsAGkAYQBuACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB0AGEAdABlACAAbwByACAAcgBlAGcAaQBvAG4AYQBsACAAcwBjAG8AcABlACAAMwAgAGQAYQB0AGEAYgBhAHMAZQBcACIALAAgADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABpAG4AdABlAG4AcwBpAHQAeQAgAGMAYQBsAGMAdQBsAGEAdABlAGQAIABmAHIAbwBtACAAYQBwAHAAcgBvAHYAZQBkACAAbQBlAHQAaABvAGQAXAAiACwAIAA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAZQByAGkAZgBpAGUAZAAgAGMAcgBlAGQAZQBuAHQAaQBhAGwAIABtAGEAdABjAGgAaQBuAGcAIABJAFMATwAxADQAMAA2ADcAXAAiACwAIAA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AIAAgAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAFwAbgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAHQAaABhAHQAIABpAHMAIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgAoAEQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgA1AC4ANQAuADIALgAzACAAQwBvAG4AcwB0AGEAbgB0ACAAUABhAHIAYQBtAGUAdABlAHIAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQA6ACAATABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAMwAuAEQALgBiAC4AMgApAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALAAwAC4AMgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXABuADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAbgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAGcAZQBuACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgAyAE8ALQBOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ADUALgA1AC4AMgAuADMAIABDAG8AbgBzAHQAYQBuAHQAIABQAGEAcgBhAG0AZQB0AGUAcgBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgAgADMALgBEAC4AQgBfADEAMABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsADAALgAwADEAMQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAFwAbgBUAGEAYgBsAGUAIABBAC4AMgAuADIALgAxAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAcwAgAGYAbwByACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAIAAoAEUARgBOADIATwApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAKABrAGcAIABOADIATwAtAE4AIAAvACAAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMgAuADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAE4AMgBPAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANQAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagBcACIALABcACIARQBGAE4AMgBPAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABzAHkAcwB0AGUAbQAgAG8AbgBsAHkAXAAiACwAIABcACIASQByAHIAaQBnAGEAdABpAG8AbgAgAG0AZQB0AGgAbwBkAFwAIgAsACAAXAAiAFIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADUAOQAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAwAC4AMAAwADcALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAwAC4AMAAwADEAOAAsACAAXAAiAFAAYQBzAHQAdQByAGUAXAAiACwAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgAFwAIgBMAG8AdwAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAMAAuADAAMAAxADgALAAgAFwAIgBQAGEAcwB0AHUAcgBlAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIASABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAIAAoAGwAbwB3ACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAAyADkALAAgAFwAIgBDAHIAbwBwAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIATABvAHcAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwBuAC0AaQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwACAAKABoAGkAZwBoACAAcgBhAGkAbgBmAGEAbABsACkAXAAiACwAMAAuADAAMAA4ACwAIABcACIAQwByAG8AcABcACIALAAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAEgAaQBnAGgAIAByAGEAaQBuAGYAYQBsAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBnAGEAcgBcACIALAAwAC4AMAAxADkAOQAsACAAXAAiAFMAdQBnAGEAcgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAHQAdABvAG4AXAAiACwAMAAuADAAMAA1ADMALAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASABvAHIAdABpAGMAdQBsAHQAdQByAGEAbAAgAGMAcgBvAHAAcwBcACIALAAwAC4AMAAwADYANAAsACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBhAGwAIABjAHIAbwBwAHMAXAAiACwAIABcACIAQQBuAHkAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAGMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAKQBcACIALAAwAC4AMAAwADMALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAEMAbwBuAHQAaQBuAHUAbwB1AHMAIABmAGwAbwBvAGQAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFIAaQBjAGUAIAAoAHMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAKQBcACIALAAwAC4AMAAwADUALAAgAFwAIgBSAGkAYwBlAFwAIgAsACAAXAAiAFMAaQBuAGcAbABlACAAYQBuAGQAIABtAHUAbAB0AGkAcABsAGUAIABkAHIAYQBpAG4AYQBnAGUALAAgAG8AcgAgAGEAbAB0AGUAcgBuAGEAdABlACAAdwBlAHQAdABpAG4AZwAgAGEAbgBkACAAZAByAHkAaQBuAGcAXAAiACwAIABcACIAQQBuAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAwAC4AMAAwADIANgAsACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBBAG4AeQBcACIALAAgAFwAIgBBAG4AeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsADAALgAwADAAMQA4ACwAIABcACIARgBvAHIAZQBzAHQAcgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgAsACAAXAAiAEEAbgB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBOADIATwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAEYAIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGQAdQBwAGwAaQBjAGEAdABlACAAXAB1ADAAMAAyADcAQQBxAHUAYQBjAHUAbAB0AHUAcgBlAFwAdQAwADAAMgA3ACAAcgBvAHcALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBlAG0AbwB2AGUAZAAgAGEAcwB0AGUAcgBpAHMAawBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAGQAZABlAGQAIABcAHUAMAAwADIANwBwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABvAG4AbAB5AFwAdQAwADAAMgA3ACwAIABcAHUAMAAwADIANwByAGEAaQBuAGYAYQBsAGwAIAB6AG8AbgBlAFwAdQAwADAAMgA3ACAAYQBuAGQAIABcAHUAMAAwADIANwBpAHIAcgBpAGcAYQB0AGkAbwBuACAAbQBlAHQAaABvAGQAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgBzACAAdABvACAAYQBpAGQAIABsAG8AbwBrAHUAcAAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAAXAB1ADAAMAAyADcAbgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAB1ADAAMAAyADcAIAByAG8AdwAgAHcAaQB0AGgAIABzAGEAbQBlACAARQBGACAAZgBvAHIAIABsAG8AdwAgAGEAbgBkACAAaABpAGcAaAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAE4AMgBPACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUATgAyAE8AOgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAE4AMgBPACkAXABuAEcAVwBQAE4AMgBPADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATgAyAE8AKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBOADIATwAsACAARwBXAFAAXwBOADIATwAsAFwAbgAgACAAIAAgAEUAXwBOADIATwAgACoAIABHAFcAUABfAE4AMgBPAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AE4AMgBPAH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AE4AMgBPAH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBOADIATwBcACIALABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAATgAyAE8AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAATgAyAE8AXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABOADIATwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgBDAG8AbgB2AGUAcgB0ACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAdABvACAAYwBhAHIAYgBvAG4AIABkAGkAbwB4AGkAZABlACAAZQBxAHUAaQB2AGEAbABlAG4AdAAgAGUAbQBpAHMAcwBpAG8AbgBzAFwAbgBFAEMASAA0ACAAQwBPADIAZQBcAG4AdAAgAEMATwAyAGUAXABuAEUAQwBIADQAOgAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgACgAdAAgAEMASAA0ACkAXABuAEcAVwBQAEMASAA0ADoAIABnAGwAbwBiAGEAbAAgAHcAYQByAG0AaQBuAGcAIABwAG8AdABlAG4AdABpAGEAbAAgAGYAbwByACAAbQBlAHQAaABhAG4AZQAgACgAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAAQwBIADQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUAXwBDAEgANAAsACAARwBXAFAAXwBDAEgANAAsAFwAbgAgACAAIAAgAEUAXwBDAEgANAAgACoAIABHAFcAUABfAEMASAA0AFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBvAG4AdgBlAHIAdAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHQAbwAgAGMAYQByAGIAbwBuACAAZABpAG8AeABpAGQAZQAgAGUAcQB1AGkAdgBhAGwAZQBuAHQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0ACAAQwBPADIAZQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMATwAyAGUAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQwBPADIAXwBlACAAPQAgAEUAXwB7AEMASAA0AH0AIABcAFwAdABpAG0AZQBzACAARwBXAFAAXwB7AEMASAA0AH0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBDAEgANABcACIALABcACIATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAKAB0ACAAQwBIADQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARwBXAFAAQwBIADQAXAAiACwAXAAiAEcAbABvAGIAYQBsACAAdwBhAHIAbQBpAG4AZwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAKAB0ACAAQwBPADIALQBlACAALwAgAHQAIABDAEgANAApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAAdABoAGEAdAAgAGkAcwAgAGMAbwBtAG0AbwBuACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGMAcgBvAHAAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAOgAgAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxAFwAbgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAFQAYQBiAGwAZQAgADUALgAyADEAIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAIABmAG8AcgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAHMASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAZgBvAHIAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBOADIATwBFAEYAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARwBnACAATgAyAE8ALQBOAC8AIABHAGcAIABOAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAHMASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADIAMQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABwAGEAcwB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA1ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADEAOAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAG4ALQBpAHIAcgBpAGcAYQB0AGUAZAAgAGMAcgBvAHAAXAAiACwAIAAwAC4AMAAwADQAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AGcAYQByACAAYwBhAG4AZQBcACIALAAgADAALgAwADEAOQA5ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AdAB0AG8AbgBcACIALAAgADAALgAwADAANQAzADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBIAG8AcgB0AGkAYwB1AGwAdAB1AHIAZQBcACIALAAgADAALgAwADAANgA0AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVQByAGUAYQBDAE8AMgBFAEYAXABuAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ASABfADEAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFUAcgBlAGEAQwBPADIARQBGAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYwBhAHIAYgBvAG4AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHIAZQBhACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVQByAGUAYQBDAE8AMgBFAEYAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0AG8AbgBuAGUAIABDAC8AdABvAG4AbgBlACAAdQByAGUAYQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFUAcgBlAGEAQwBPADIARQBGAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIABFAHEAdQBhAHQAaQBvAG4AIAAzAC4ASABfADEAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBVAHIAZQBhAEMATwAyAEUARgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADIAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADQAIABFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAG4AZAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAbgBkACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOADIATwAgAC0AIABOACAALwAgAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAyAC4AMQAuADQAXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBOADIATwBFAEYATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAAgAFQAYQBiAGwAZQAgADEAMQAuADEAIABbADEALAAgAHAALgAgADEAMQBdAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAGkAXAAiACwAIABcACIARQBGACAAaQAgAE4AMgBPAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAVwBlAHQAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQBcACIALAAgADAALgAwADAANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMARwBBAFMARgBmAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAFYARQBFAFIARwAgADIAMAAyADYAOgBUAGEAYgBsAGUAIAAxADIALgAyAC4AMgAuADkAXABuAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAAgAFQAYQBiAGwAZQAgADEAMQAuADMAIABbADEALAAgAHAALgAgADEAMQBdAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABmACAAdABoAGEAdAAgAHYAbwBsAGEAdABpAGwAaQBzAGUAcwAgAGEAcwAgAE4ASAAzACAAYQBuAGQAIABOAE8AeABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBHAEEAUwBGAGYASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVABoAGUAIABkAGkAcgBlAGMAdAAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAIABmAHIAbwBtACAAdABoAGUAIABvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHcAaABlAG4AIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBHAEEAUwBGAGYASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiACgAawBnACAATgBIADMALQBOACAAKwAgAE4ATwB4AC0ATgApAC8AawBnACAATgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMARwBBAFMARgBmAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6AFQAYQBiAGwAZQAgADEAMgAuADIALgAyAC4AOQBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMARwBBAFMARgBmAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIASQBQAEMAQwAgADIAMAAxADkAIABSAGUAZgBpAG4AZQBtAGUAbgB0ACAAVgBvAGwAdQBtAGUAIAA0ACAAVABhAGIAbABlACAAMQAxAC4AMwAgAFsAMQAsACAAcAAuACAAMQAxAF0AXAAiACkAOwBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEcAQQBTAEYAZgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AHkAcABlACAAZgBcACIALABcACIARgByAGEAYwBHAEEAUwBGAGYAXAAiACwAIABcACIAQgBhAHMAaQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBVAHIAZQBhAC0AYgBhAHMAZQBkACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAMAAuADEANQAsACAAXAAiAFUAcgBlAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbQBtAG8AbgBpAHUAbQAtAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgADAALgAwADgALAAgAFwAIgBBAG0AbQBvAG4AaQB1AG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AaQB0AHIAYQB0AGUALQBiAGEAcwBlAGQAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIAAwAC4AMAAxACwAIABcACIATgBpAHQAcgBhAHQAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBtAG0AbwBuAGkAdQBtAC0AbgBpAHQAcgBhAHQAZQAgAGIAYQBzAGUAZAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgADAALgAwADUALAAgAFwAIgBBAG0AbQBvAG4AaQB1AG0ALQBuAGkAdAByAGEAdABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIAAwAC4AMQAxACwAIABcACIATwB0AGgAZQByAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AIAAgAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEcAQQBTAEYAZgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABGAFIATwBNACAAUwBPAFUAUgBDAEUAIABEAEEAVABBADoAIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABcAHUAMAAwADIANwBCAGEAcwBpAHMAXAB1ADAAMAAyADcAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABzAGkAbQBwAGwAaQBmAGkAZQBkACAAbgBhAG0AaQBuAGcAIAB0AG8AIABhAHMAcwBpAHMAIAB3AGkAdABoACAAbABvAG8AawB1AHAAcwAgAGkAbgAgAGUAcQB1AGEAdABpAG8AbgBzAFwAIgApACkAOwBcAG4AXABuAFwAbgAgACAALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBcAG4AVgBFAEUAUgBHACAAMgAwADIANgA6ACAAQwBoAGEAcAB0AGUAcgAgADEALAAgAHMAZQBjAHQAaQBvAG4AIAAxAC4AOAAuADIAIABMAGUAYQBjAGgAaQBuAGcALAAgAGMAbABpAG0AYQB0AGUAIABhAG4AZAAgAHIAYQBpAG4AZgBhAGwAbAAgAHoAbwBuAGUAcwBcAG4ASQBQAEMAQwA6ACAATgAyAE8AIABFAE0ASQBTAFMASQBPAE4AUwAgAEYAUgBPAE0AIABNAEEATgBBAEcARQBEACAAUwBPAEkATABTACwAIABBAE4ARAAgAEMATwAyACAARQBNAEkAUwBTAEkATwBOAFMAIABGAFIATwBNACAATABJAE0ARQAgAEEATgBEACAAVQBSAEUAQQAgAEEAUABQAEwASQBDAEEAVABJAE8ATgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAFcARQBUACAAZgBvAHIAIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABDAGgAYQBwAHQAZQByACAAMQAsACAAcwBlAGMAdABpAG8AbgAgADEALgA4AC4AMgAgAEwAZQBhAGMAaABpAG4AZwAsACAAYwBsAGkAbQBhAHQAZQAgAGEAbgBkACAAcgBhAGkAbgBmAGEAbABsACAAegBvAG4AZQBzAFwAIgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAyADAAMQA5ACAAUgBlAGYAaQBuAGUAbQBlAG4AdAAgAFYAbwBsAHUAbQBlACAANAA6ACAAQwBoAGEAcAB0AGUAcgAgADEAMQA6ACAATgAyAE8AIABFAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABNAGEAbgBhAGcAZQBkACAAUwBvAGkAbABzACwAIABhAG4AZAAgAEMATwAyACAARQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAATABpAG0AZQAgAGEAbgBkACAAVQByAGUAYQAgAEEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQAgAGkAcgBcACIALABcACIARgByAGEAYwBXAEUAVABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBvAHQAIABpAHIAcgBpAGcAYQB0AGUAZABcACIALAAgADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAGkAcAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcAByAGkAbgBrAGwAZQByACAAaQByAHIAaQBnAGEAdABpAG8AbgBcACIALAAgADEAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB1AHIAZgBhAGMAZQAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAGkAcgByAGkAZwBhAHQAaQBvAG4AXAAiACwAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAgACAAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAFQAYQBiAGwAZQAgAGMAcgBlAGEAdABlAGQAIABiAGEAcwBlAGQAIABvAG4AIABWAEUARQBSAEcAIAB0AGUAeAB0ACAAXAB1ADAAMAAyADcAQQByAGUAYQBzACAAYQByAGUAIABzAHUAYgBqAGUAYwB0ACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAKABpAC4AZQAuACwAIABpAG4AIAB0AGgAZQAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAKQAgAHcAaABlAG4ALgAuAC4AIAB0AGgAZQAgAGwAYQBuAGQAIABpAHMAIABpAHIAcgBpAGcAYQB0AGUAZAAgACgAZQB4AGMAZQBwAHQAIABkAHIAaQBwACAAaQByAHIAaQBnAGEAdABpAG8AbgApAC4AXAB1ADAAMAAyADcAXAAiACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AdQByAGMAZQAgAGQAYQB0AGEAIAB0AGgAYQB0ACAAaQBzACAAYwBvAG0AbQBvAG4AIABhAGMAcgBvAHMAcwAgAGEAbABsACAAbABpAHYAZQBzAHQAbwBjAGsAIAB0AHkAcABlAHMAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAFMAbwB1AHIAYwBlADoAIABOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQBcAG4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBcAG4ARgByAGEAYwBXAEUAVABNAE0AUwBpACAAPQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4AKABUAGEAYgBsAGUAIABBADUALgA1AC4AMQAwAC4AMgAgAGkAcwAgAHIAZQBmAGUAcgBlAG4AYwBlAGQAIABpAG4AIABOAEkAUgAgAGIAdQB0ACAAMQAgAGkAcwAgAHUAcwBlAGQAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAFcARQBUAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAxACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXABuAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTACAAPQAgADAALgAwADIAIAAoAEcAZwAgAE4ALwBHAGcAIABhAHAAcABsAGkAZQBkACkAIAAoAEMAUwAgAEUARgAsACAAcwBvAHUAcgBjAGUAIABJAFAAQwBDACAAKAAyADAAMQA5ACkAKQAgAFwAbgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBNAFMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIABWAG8AbAB1AG0AZQAgADEAOgAgAEUAcQB1AGEAdABpAG8AbgBzACAAMwAuAEIALgA1AGEAXwAzACwAIAAzAC4AQgAuADUAYwBfADMALAAgADMALgBCAC4ANQBkAF8AMwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAyACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAHIAcgBpAGcAYQB0AGUAZAAgAHAAYQBzAHQAdQByAGUAXAAiACwAIAAwAC4AMAAwADUAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIASQByAHIAaQBnAGEAdABlAGQAIABjAHIAbwBwAFwAIgAsACAAMAAuADAAMAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAcABhAHMAdAB1AHIAZQBcACIALAAgADAALgAwADAAMQA4ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAG8AbgAtAGkAcgByAGkAZwBhAHQAZQBkACAAYwByAG8AcABcACIALAAgADAALgAwADAANAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAZwBhAHIAIABjAGEAbgBlAFwAIgAsACAAMAAuADAAMQA5ADkAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwB0AHQAbwBuAFwAIgAsACAAMAAuADAAMAA1ADMAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEgAbwByAHQAaQBjAHUAbAB0AHUAcgBlAFwAIgAsACAAMAAuADAAMAA2ADQAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXABuAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAYQBiAGwAZQAgADUALgAxADIAIABBAGQAZABpAHQAaQBvAG4AYQBsACAAcwB5AG0AYgBvAGwAcwAgAHUAcwBlAGQAIABpAG4AIABhAGwAZwBvAHIAaQB0AGgAbQBzACAAZgBvAHIAIABtAGEAbgB1AHIAZQAgAHIAZQBsAGEAdABlAGQAIABlAG0AaQBzAHMAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVgBhAGkAcgBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAFYAbwBsAHUAbQBlACAAMQA6ACAAVABhAGIAbABlACAANQAuADEAMgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAOQAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwB5AG0AYgBvAGwAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0ACAAcwB5AHMAdABlAG0AXAAiACwAIABcACIAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgAbQA9ADEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADIAXAAiACwAIABcACIATABpAHEAdQBpAGQAIABzAHkAcwB0AGUAbQBzAFwAIgAsACAAXAAiAEwAaQBxAHUAaQBkACAAcwB5AHMAdABlAG0AcwAgACgAbQA9ADIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADMAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAXAAiACwAIABcACIARABhAGkAbAB5ACAAcwBwAHIAZQBhAGQAIAAoAG0APQAzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGEAXAAiACwAIABcACIAUwB1AG0AcAAgAGEAbgBkACAAZABpAHMAcABlAHIAcwBhAGwAIABzAHkAcwB0AGUAbQBcACIALAAgAFwAIgBTAHUAbQBwACAAYQBuAGQAIABkAGkAcwBwAGUAcgBzAGEAbAAgAHMAeQBzAHQAZQBtACAAKABtAD0AMwBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAzAGIAXAAiACwAIABcACIARAByAGEAaQBuAHMAIAB0AG8AIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAEQAcgBhAGkAbgBzACAAdABvACAAcABhAGQAZABvAGMAawAgACgAbQA9ADMAYgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIANABcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIAAoAG0APQA0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA1AFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIALAAgAFwAIgBEAHIAeQBsAG8AdAAgACgAZgBlAGUAZAAgAHAAYQBkACkAIAAoAG0APQA1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgA2AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQAgACgAbQA9ADYAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADcAXAAiACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwAgACgAbQA9ADcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADgAXAAiACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgAsACAAXAAiAEQAZQBlAHAAIABsAGkAdAB0AGUAcgAgACgAbQA9ADgAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADkAXAAiACwAIABcACIAUABpAHQAIABzAHQAbwByAGEAZwBlAFwAIgAsACAAXAAiAFAAaQB0ACAAcwB0AG8AcgBhAGcAZQAgACgAbQA9ADkAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMABcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwAgACgAbQA9ADEAMAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAbwB1AHQAIABiAGUAZABkAGkAbgBnACAAKABtAD0AMQAxACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADEAYQBcACIALAAgAFwAIgBCAGUAbAB0ACAAbQBhAG4AdQByAGUAIAByAGUAbQBvAHYAYQBsAFwAIgAsACAAXAAiAEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAIAAoAG0APQAxADEAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABcACIAMQAxAGIAXAAiACwAIABcACIATQBhAG4AdQByAGUAIABzAHQAbwByAGUAZAAgAGkAbgAgAGgAbwB1AHMAZQBcACIALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlACAAKABtAD0AMQAxAGIAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEAMgBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnACAAKABtAD0AMQAyACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFwAIgAxADMAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AIAAoAG0APQAxADMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAXAAiADEANABcACIALAAgAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAAoAG0APQAxADQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAEYAdQBlAGwAXwBHAGUAdABUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAFMAdAByAGkAbgBnAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwBlAGwAbAAsAFwAbgAgACAAIAAgAEwARQBGAFQAKABDAGUAbABsACwAIABGAEkATgBEACgAXAAiACwAIABcACIALABDAGUAbABsACkAIAAtADEAKQBcAG4AKQA7AFwAbgBcAG4ARgB1AGUAbABfAEcAZQB0AFMAdABhAHQAaQBvAG4AYQByAHkARgB1AGUAbABTAHQAcgBpAG4AZwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALABcAG4AIAAgACAAIABSAEkARwBIAFQAKABDAGUAbABsACwATABFAE4AKABDAGUAbABsACkALQBGAEkATgBEACgAXAAiACwAIABcACIALABDAGUAbABsACkAKQBcAG4AKQA7AFwAbgBcAG4ARgB1AGUAbABfAFQAbwB0AGEAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AXABuAD0AIABMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEYAdQBlAGwAQwBvAG4AcwB1AG0AcAB0AGkAbwBuAEEAcgByAGEAeQAsACAARgB1AGUAbABVAHMAZQBBAHIAcgBhAHkALAAgAEYAdQBlAGwAVQBzAGUALAAgAEYAdQBlAGwAVAB5AHAAZQBBAHIAcgBhAHkALAAgAEYAdQBlAGwAVAB5AHAAZQAsAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIABTAFUATQAoAFwAbgAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAFwAbgAgACAAIAAgACAAIAAgACAARgB1AGUAbABDAG8AbgBzAHUAbQBwAHQAaQBvAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgACAAIAAoAEYAdQBlAGwAVAB5AHAAZQBBAHIAcgBhAHkAIAA9ACAARgB1AGUAbABUAHkAcABlACkAIAAqACAAXABuACAAIAAgACAAIAAgACAAIAAoAEYAdQBlAGwAVQBzAGUAQQByAHIAYQB5ACAAPQAgAEYAdQBlAGwAVQBzAGUAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAMABcAG4AIAAgACkAXABuACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzACIALAAiAHQAZQB4AHQAIgA6ACIALwAvACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ASABlAGEAZABMAG8AcwB0AEQAdQByAGkAbgBnAE0AbwBuAHQAaABcAG4ALwAvACAAPQAgAEwAQQBNAEIARABBACgATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALABcAG4ALwAvACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuAC8ALwAgACAAIAAgACAAUwBVAE0AKABcAG4ALwAvACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsASABlAGEAZABdACwAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARABhAHQAZQBdACAAXAB1ADAAMAAzAGUAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAtADEAKQArADEAKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARABhAHQAZQBdACAAXAB1ADAAMAAzAGMAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAwACkAKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARgByAG8AbQBdACAAPQAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApAFwAbgAvAC8AIAAgACAAIAAgACAAIAApAFwAbgAvAC8AIAAgACAAIAAgACkALABcAG4ALwAvACAAIAAgACAAIAAwAFwAbgAvAC8AIAAgACAAKQBcAG4ALwAvACAAKQA7AFwAbgBcAG4ALwAvACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ASABlAGEAZABBAGQAZABlAGQARAB1AHIAaQBuAGcATQBvAG4AdABoAFwAbgAvAC8AIAA9ACAATABBAE0AQgBEAEEAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsAFwAbgAvAC8AIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4ALwAvACAAIAAgACAAIABTAFUATQAoAFwAbgAvAC8AIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAASQBuAHAAdQB0AF8ASABlAHIAZABNAG8AdgBlAG0AZQBuAHQAWwBIAGUAYQBkAF0ALABcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACgASQBuAHAAdQB0AF8ASABlAHIAZABNAG8AdgBlAG0AZQBuAHQAWwBEAGEAdABlAF0AIABcAHUAMAAwADMAZQA9ACAARQBPAE0ATwBOAFQASAAoAE0AbwBuAHQAaAAsAC0AMQApACsAMQApACAAKgBcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACgASQBuAHAAdQB0AF8ASABlAHIAZABNAG8AdgBlAG0AZQBuAHQAWwBEAGEAdABlAF0AIABcAHUAMAAwADMAYwA9ACAARQBPAE0ATwBOAFQASAAoAE0AbwBuAHQAaAAsADAAKQApACAAKgBcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACgASQBuAHAAdQB0AF8ASABlAHIAZABNAG8AdgBlAG0AZQBuAHQAWwBUAG8AXQAgAD0AIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAKQBcAG4ALwAvACAAIAAgACAAIAAgACAAKQBcAG4ALwAvACAAIAAgACAAIAApACwAXABuAC8ALwAgACAAIAAgACAAMABcAG4ALwAvACAAIAAgACkAXABuAC8ALwAgACkAOwBcAG4AXABuAC8ALwAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEgAZQBhAGQAUgBlAG0AYQBpAG4AaQBuAGcAQQB0AE0AbwBuAHQAaABFAG4AZABcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAFwAbgAvAC8AIAAgACAAIAAgAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwASABlAGEAZABBAHQAUwB0AGEAcgB0AE8AZgBNAG8AbgB0AGgALABcAG4ALwAvACAAIAAgACAAIABNAEEAWAAoAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAASABlAGEAZABBAHQAUwB0AGEAcgB0AE8AZgBNAG8AbgB0AGgALQBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBIAGUAYQBkAEwAbwBzAHQARAB1AHIAaQBuAGcATQBvAG4AdABoACgATQBvAG4AdABoACwATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkALAAgAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAMABcAG4ALwAvACAAIAAgACAAIAApAFwAbgAvAC8AIAApADsAXABuAFwAbgBcAG4ALwAvACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQATQBvAHYAZQBtAGUAbgB0AEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUALABcAG4ALwAvACAAIAAgAEwARQBUACgAXABuAC8ALwAgACAAIAAgACAAeQBtACwAIABUAEUAWABUACgATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUALABcACIAeQB5AHkAeQBtAG0AXAAiACkALABcAG4ALwAvACAAIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuAC8ALwAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACAAIABIAGUAcgBkAFsATABpAHYAZQB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AIABpAG4AIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXQAsAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAIAAgACgAVABFAFgAVAAoAEgAZQByAGQAWwBNAG8AbgB0AGgAXQAsAFwAIgB5AHkAeQB5AG0AbQBcACIAKQAgAD0AIAB5AG0AKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAgACAAKABIAGUAcgBkAFsATABpAHYAZQBzAHQAbwBjAGsAIABjAGwAYQBzAHMAXQAgAD0AIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAKQBcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACkALABcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgADEAXABuAC8ALwAgACAAIAAgACAAIAAgACkALABcAG4ALwAvACAAIAAgACAAIAAgACAAXAAiAFwAIgBcAG4ALwAvACAAIAAgACAAIAApAFwAbgAvAC8AIAAgACAAKQBcAG4ALwAvACAAKQA7AFwAbgBcAG4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARABhAHkAcwBNAG8AdgBlAG0AZQBuAHQAVABvAE0AbwBuAHQAaABFAG4AZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUALABcAG4AIAAgAEQAQQBUAEUARABJAEYAKABNAG8AdgBlAG0AZQBuAHQARABhAHQAZQAsACAARQBPAE0ATwBOAFQASAAoAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlACwAIAAwACkALAAgAFwAIgBkAFwAIgApAFwAbgApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBEAHUAcgBpAG4AZwBNAG8AbgB0AGgAUABlAHIASABlAGEAZABcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUALABcAG4ALwAvACAAIAAgAEkARgBFAFIAUgBPAFIAKAAgAFwAbgAvAC8AIAAgACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AE0AbwB2AGUAbQBlAG4AdABMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AKABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlACkAKgBcAG4ALwAvACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBEAGEAeQBzAE0AbwB2AGUAbQBlAG4AdABUAG8ATQBvAG4AdABoAEUAbgBkACgATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAKQBcAG4ALwAvACAAIAAgACwAIAAwACkAXABuAC8ALwAgACkAOwBcAG4AXABuAC8ALwAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQBkAGQAZQBkAEQAdQByAGkAbgBnAE0AbwBuAHQAaABcAG4ALwAvACAAPQAgAEwAQQBNAEIARABBACgATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABNAG8AdgBlAG0AZQBuAHQARABhAHQAZQAsACAAVwBlAGkAZwBoAHQAQQB0AE0AbwB2AGUAbQBlAG4AdABEAGEAdABlACwAIABIAGUAYQBkACwAXABuAC8ALwAgAEkARgBFAFIAUgBPAFIAKABcAG4ALwAvACAAIAAgACAAIABIAGUAYQBkACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAAVwBlAGkAZwBoAHQAQQB0AE0AbwB2AGUAbQBlAG4AdABEAGEAdABlACsAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBEAHUAcgBpAG4AZwBNAG8AbgB0AGgAUABlAHIASABlAGEAZAAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAKQBcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgACkAXABuAC8ALwAgACwAIAAwACkAXABuAC8ALwAgACkAOwBcAG4AXABuAC8ALwAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwByAG8AdwBuAEYAcgBvAG0ATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAVABvAHQAYQBsAFwAbgAvAC8AIAA9AEwAQQBNAEIARABBACgAXABuAC8ALwAgACAAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlACwAIABIAGUAYQBkACwAXABuAC8ALwAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBEAHUAcgBpAG4AZwBNAG8AbgB0AGgAUABlAHIASABlAGEAZAAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAKQAgACoAXABuAC8ALwAgACAAIABIAGUAYQBkAFwAbgAvAC8AIAApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBGAHIAbwBtAE0AbwBuAHQAaABTAHQAYQByAHQAUABlAHIASABlAGEAZABcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAG4AdABoACwAXABuAC8ALwAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBEAHUAcgBpAG4AZwBNAG8AbgB0AGgAUABlAHIASABlAGEAZAAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAARQBPAE0ATwBOAFQASAAoAE0AbwBuAHQAaAAsAC0AMQApACsAMQApAFwAbgAvAC8AIAApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBGAHIAbwBtAE0AbwBuAHQAaABTAHQAYQByAHQAVABvAHQAYQBsAFwAbgAvAC8AIAA9AEwAQQBNAEIARABBACgATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABNAG8AbgB0AGgALAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdABPAGYATQBvAG4AdABoACwAXABuAC8ALwAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBIAGUAYQBkAFIAZQBtAGEAaQBuAGkAbgBnAEEAdABNAG8AbgB0AGgARQBuAGQAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0AE8AZgBNAG8AbgB0AGgAKQAgACoAXABuAC8ALwAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBGAHIAbwBtAE0AbwBuAHQAaABTAHQAYQByAHQAUABlAHIASABlAGEAZAAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAG4AdABoACkAXABuAC8ALwAgACkAOwBcAG4AXABuAC8ALwAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEgAZQBhAGQAQQB0AEUAbgBkAE8AZgBNAG8AbgB0AGgAXABuAC8ALwAgAD0AIABMAEEATQBCAEQAQQAoAEgAZQBhAGQAQQB0AFMAdABhAHIAdAAsACAATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALABcAG4ALwAvACAAIAAgACAAIABIAGUAYQBkAEEAdABTAHQAYQByAHQAXABuAC8ALwAgACAAIAAgACAAKwAgAFwAbgAvAC8AIAAgACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEgAZQBhAGQAQQBkAGQAZQBkAEQAdQByAGkAbgBnAE0AbwBuAHQAaAAoAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkAXABuAC8ALwAgACAAIAAgACAALQAgAFwAbgAvAC8AIAAgACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEgAZQBhAGQATABvAHMAdABEAHUAcgBpAG4AZwBNAG8AbgB0AGgAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApAFwAbgAvAC8AIAApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEYAcgBvAG0AUwB0AGEAcgB0AE8AZgBNAG8AbgB0AGgAXABuAD0AIABMAEEATQBCAEQAQQAoAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAFAAZQByAEQAYQB5ACwAIABNAG8AbgB0AGgALABcAG4AIAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAArAFwAbgAgACAAKABMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AUABlAHIARABhAHkAKgBEAEEAVABFAEQASQBGACgARQBEAEEAVABFACgATQBvAG4AdABoACwAIAAwACkALAAgAEUARABBAFQARQAoAE0AbwBuAHQAaAAsACAAMQApACwAIABcACIAZABcACIAKQApAFwAbgApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBUAG8AdABhAGwATABpAHYAZQB3AGUAaQBnAGgAdABBAGQAZABlAGQARAB1AHIAaQBuAGcATQBvAG4AdABoAFwAbgAvAC8AIAA9ACAATABBAE0AQgBEAEEAKABcAG4ALwAvACAAIAAgACAAIABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsAFwAbgAvAC8AIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4ALwAvACAAIAAgACAAIABTAFUATQAoAFwAbgAvAC8AIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAASQBuAHAAdQB0AF8ASABlAHIAZABNAG8AdgBlAG0AZQBuAHQAWwBUAG8AdABhAGwAIAB3AGUAaQBnAGgAdAAgAGcAYQBpAG4AZQBkACAAcwBpAG4AYwBlACAAagBvAGkAbgBpAG4AZwBdACwAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARABhAHQAZQBdACAAXAB1ADAAMAAzAGUAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAtADEAKQArADEAKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARABhAHQAZQBdACAAXAB1ADAAMAAzAGMAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAwACkAKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsAVABvAF0AIAA9ACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkAXABuAC8ALwAgACAAIAAgACAAIAAgACkAXABuAC8ALwAgACAAIAAgACAAKQAsAFwAbgAvAC8AIAAgACAAIAAgADAAXABuAC8ALwAgACAAIAApAFwAbgAvAC8AIAApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBUAG8AdABhAGwATABpAHYAZQB3AGUAaQBnAGgAdABHAHIAbwB3AG4ARAB1AHIAaQBuAGcATQBvAG4AdABoAFwAbgAvAC8AIAA9ACAATABBAE0AQgBEAEEAKABcAG4ALwAvACAAIAAgACAAIABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsAFwAbgAvAC8AIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4ALwAvACAAIAAgACAAIABTAFUATQAoAFwAbgAvAC8AIAAgACAAIAAgACAAIABGAEkATABUAEUAUgAoAFwAbgAvAC8AIAAgACAAIAAgACAAIAAgACAASQBuAHAAdQB0AF8ASABlAHIAZABNAG8AdgBlAG0AZQBuAHQAWwBMAGkAdgBlAHcAZQBpAGcAaAB0ACAAZwByAG8AdwBuACAAcwBpAG4AYwBlACAAagBvAGkAbgBpAG4AZwBdACwAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARABhAHQAZQBdACAAXAB1ADAAMAAzAGUAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAtADEAKQArADEAKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsARABhAHQAZQBdACAAXAB1ADAAMAAzAGMAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAwACkAKQAgACoAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIAAoAEkAbgBwAHUAdABfAEgAZQByAGQATQBvAHYAZQBtAGUAbgB0AFsAVABvAF0AIAA9ACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkAXABuAC8ALwAgACAAIAAgACAAIAAgACkAXABuAC8ALwAgACAAIAAgACAAKQAsAFwAbgAvAC8AIAAgACAAIAAgADAAXABuAC8ALwAgACAAIAApAFwAbgAvAC8AIAApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQBkAGQAZQBkAEQAdQByAGkAbgBnAE0AbwBuAHQAaABcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAFwAbgAvAC8AIAAgACAAIAAgAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAXABuAC8ALwAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAvAC8AIAAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBUAG8AdABhAGwATABpAHYAZQB3AGUAaQBnAGgAdABBAGQAZABlAGQARAB1AHIAaQBuAGcATQBvAG4AdABoACgATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAKQAvAFwAbgAvAC8AIAAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBIAGUAYQBkAEEAZABkAGUAZABEAHUAcgBpAG4AZwBNAG8AbgB0AGgAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApAFwAbgAvAC8AIAAgACAAIAAgACAAIAAsACAAMABcAG4ALwAvACAAIAAgACAAIAApAFwAbgAvAC8AIAApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAUgBlAG0AYQBpAG4AaQBuAGcASABlAGEAZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBvAG4AdABoACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABTAHQAYQByAHQALAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgAsAFwAbgAgACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQAUwB0AGEAcgB0ACsAKABMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AKgBEAEEAVABFAEQASQBGACgARQBEAEEAVABFACgATQBvAG4AdABoACwAIAAwACkALAAgAEUARABBAFQARQAoAE0AbwBuAHQAaAAsACAAMQApACwAIABcACIAZABcACIAKQApAFwAbgApADsAXABuAFwAbgAvAC8AIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBQAHIAbwBwAG8AcgB0AGkAbwBuAEgAZQBhAGQAUgBlAG0AYQBpAG4AaQBuAGcAQQB0AEUAbgBkAE8AZgBNAG8AbgB0AGgAXABuAC8ALwAgAD0ATABBAE0AQgBEAEEAKABcAG4ALwAvACAAIAAgACAAIABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0ACwAXABuAC8ALwAgACAAIAAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAvAC8AIAAgACAAIAAgACAAIABNAEkATgAoADEALABcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEgAZQBhAGQAUgBlAG0AYQBpAG4AaQBuAGcAQQB0AE0AbwBuAHQAaABFAG4AZAAoAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABIAGUAYQBkAEEAdABTAHQAYQByAHQAKQAvACAAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBIAGUAYQBkAEEAdABFAG4AZABPAGYATQBvAG4AdABoACgASABlAGEAZABBAHQAUwB0AGEAcgB0ACwAIABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApAFwAbgAvAC8AIAAgACAAIAAgACAAIAApACwAIAAwAFwAbgAvAC8AIAAgACAAIAAgACkAXABuAC8ALwAgACkAOwBcAG4AXABuAC8ALwAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFAAcgBvAHAAbwByAHQAaQBvAG4ASABlAGEAZABBAGQAZABlAGQARAB1AHIAaQBuAGcATQBvAG4AdABoAFwAbgAvAC8AIAA9AEwAQQBNAEIARABBACgAXABuAC8ALwAgACAAIAAgACAATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdAAsAFwAbgAvAC8AIAAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4ALwAvACAAIAAgACAAIAAgACAATQBJAE4AKAAxACwAXABuAC8ALwAgACAAIAAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBIAGUAYQBkAEEAZABkAGUAZABEAHUAcgBpAG4AZwBNAG8AbgB0AGgAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApAC8AIABcAG4ALwAvACAAIAAgACAAIAAgACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEgAZQBhAGQAQQB0AEUAbgBkAE8AZgBNAG8AbgB0AGgAKABIAGUAYQBkAEEAdABTAHQAYQByAHQALAAgAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkAXABuAC8ALwAgACAAIAAgACAAIAAgACkALAAgADAAXABuAC8ALwAgACAAIAAgACAAKQBcAG4ALwAvACAAKQA7AFwAbgBcAG4ALwAvACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AUAByAG8AcABvAHIAdABpAG8AbgBhAGwAQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AEEAZABkAGUAZABEAHUAcgBpAG4AZwBNAG8AbgB0AGgAXABuAC8ALwAgAD0ATABBAE0AQgBEAEEAKABcAG4ALwAvACAAIAAgACAAIABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0ACwAXABuAC8ALwAgACAAIAAgACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AUAByAG8AcABvAHIAdABpAG8AbgBIAGUAYQBkAEEAZABkAGUAZABEAHUAcgBpAG4AZwBNAG8AbgB0AGgAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0ACkAKgBcAG4ALwAvACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQBkAGQAZQBkAEQAdQByAGkAbgBnAE0AbwBuAHQAaAAoAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkAXABuAC8ALwAgACkAOwBcAG4AXABuAC8ALwAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFAAcgBvAHAAbwByAHQAaQBvAG4AYQBsAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABSAGUAbQBhAGkAbgBpAG4AZwBBAHQARQBuAGQATwBmAE0AbwBuAHQAaABcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAFwAbgAvAC8AIAAgACAAIAAgAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABIAGUAYQBkAEEAdABTAHQAYQByAHQALAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuACwAXABuAC8ALwAgACAAIAAgACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AUAByAG8AcABvAHIAdABpAG8AbgBIAGUAYQBkAFIAZQBtAGEAaQBuAGkAbgBnAEEAdABFAG4AZABPAGYATQBvAG4AdABoACgATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdAApACoAXABuAC8ALwAgACAAIAAgACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AFIAZQBtAGEAaQBuAGkAbgBnAEgAZQBhAGQAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuACkAXABuAC8ALwAgACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAXABuACAAIABIAEwATwBPAEsAVQBQACgATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABSAGEAbgBnAGUAXwBMAGkAdgBlAHMAdABvAGMAawBTAHQAYQByAHQAaQBuAGcAVgBhAGwAdQBlAHMALAAgADMALAAgAEYAQQBMAFMARQApAFwAbgApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBHAGUAdABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABFAG4AZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAXABuACAAIABIAEwATwBPAEsAVQBQACgATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABSAGEAbgBnAGUAXwBMAGkAdgBlAHMAdABvAGMAawBTAHQAYQByAHQAaQBuAGcAVgBhAGwAdQBlAHMALAAgADQALAAgAEYAQQBMAFMARQApAFwAbgApADsAXABuAFwAbgAvAC8AIABBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQARQBuAGQATwBmAE0AbwBuAHQAaABcAG4ALwAvACAAPQBMAEEATQBCAEQAQQAoAFwAbgAvAC8AIAAgACAATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQAUwB0AGEAcgB0ACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4ALABcAG4ALwAvACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFAAcgBvAHAAbwByAHQAaQBvAG4AYQBsAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABBAGQAZABlAGQARAB1AHIAaQBuAGcATQBvAG4AdABoACgATQBvAG4AdABoACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdAApACsAXABuAC8ALwAgACAAIABMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBQAHIAbwBwAG8AcgB0AGkAbwBuAGEAbABBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAUgBlAG0AYQBpAG4AaQBuAGcAQQB0AEUAbgBkAE8AZgBNAG8AbgB0AGgAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0ACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABTAHQAYQByAHQALAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgApAFwAbgAvAC8AIAApADsAXABuAFwAbgBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQATQBvAG4AdABoAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABNAG8AbgB0AGgAUwB0AGEAcgB0ACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABNAG8AbgB0AGgARQBuAGQALABcAG4AIAAgAEkARgBTACgAXABuACAAIAAgACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQATQBvAG4AdABoAFMAdABhAHIAdAAgAFwAdQAwADAAMwBjAD0AMAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQATQBvAG4AdABoAEUAbgBkACwAXABuACAAIAAgACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQATQBvAG4AdABoAEUAbgBkACAAXAB1ADAAMAAzAGMAPQAwACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABNAG8AbgB0AGgAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAVABSAFUARQAsACAAKABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABNAG8AbgB0AGgAUwB0AGEAcgB0ACsATABpAHYAZQB3AGUAaQBnAGgAdABBAHQATQBvAG4AdABoAEUAbgBkACkALwAyAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ALwAvACAATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AVABvAHQAYQBsAEwAaQB2AGUAdwBlAGkAZwBoAHQARwByAG8AdwBuAEQAdQByAGkAbgBnAE0AbwBuAHQAaABBAGQAZABlAGQAQQBuAGQAUgBlAG0AYQBpAG4AaQBuAGcAXABuAC8ALwAgAD0ATABBAE0AQgBEAEEAKABcAG4ALwAvACAAIAAgAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABIAGUAYQBkAEEAdABTAHQAYQByAHQALABcAG4ALwAvACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwByAG8AdwBuAEYAcgBvAG0ATQBvAG4AdABoAFMAdABhAHIAdABUAG8AdABhAGwAKABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAE0AbwBuAHQAaAAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0ACkAKwBcAG4ALwAvACAAIAAgAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFQAbwB0AGEAbABMAGkAdgBlAHcAZQBpAGcAaAB0AEcAcgBvAHcAbgBEAHUAcgBpAG4AZwBNAG8AbgB0AGgAKABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApAFwAbgAvAC8AIAApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBDAGEAbABjAHUAbABhAHQAZQBTAHQAYQB5AEQAdQByAGEAdABpAG8AbgBUAG8ARQBuAGQAMgBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAXABuACAAIABSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABTAHQAYQByAHQARABhAHQAZQAsAFwAbgAgACAASABlAGEAZABBAHQAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAUwB0AGEAcgB0AEQAYQB0AGUALABcAG4AIAAgAFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAEUAbgBkAEQAYQB0AGUALABcAG4AIAAgAEgAZQBhAGQAQQB0AFIAZQBwAG8AcgB0AGkAbgBnAFAAZQByAGkAbwBkAEUAbgBkAEQAYQB0AGUALABcAG4AIAAgAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlAEEAcgByAGEAeQAsAFwAbgAgACAATQBvAHYAZQBtAGUAbgB0AFQAbwBBAHIAcgBhAHkALABcAG4AIAAgAE0AbwB2AGUAbQBlAG4AdABGAHIAbwBtAEEAcgByAGEAeQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABkAHUAcgBhAHQAaQBvAG4AUwB0AGEAcgB0ACwAIABJAEYAKABIAGUAYQBkAEEAdABSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABTAHQAYQByAHQARABhAHQAZQBcAHUAMAAwADMAZQAwACwAIABSAGUAcABvAHIAdABpAG4AZwBQAGUAcgBpAG8AZABTAHQAYQByAHQARABhAHQAZQAsACAATQBJAE4ASQBGAFMAKABNAG8AdgBlAG0AZQBuAHQARABhAHQAZQBBAHIAcgBhAHkALAAgAE0AbwB2AGUAbQBlAG4AdABUAG8AQQByAHIAYQB5ACwATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkAKQAsAFwAbgAgACAAIAAgAGQAdQByAGEAdABpAG8AbgBFAG4AZAAsACAASQBGACgASABlAGEAZABBAHQAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQARQBuAGQARABhAHQAZQAgAFwAdQAwADAAMwBlACAAMAAsACAAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQARQBuAGQARABhAHQAZQAsACAATQBBAFgASQBGAFMAKABNAG8AdgBlAG0AZQBuAHQARABhAHQAZQBBAHIAcgBhAHkALAAgAE0AbwB2AGUAbQBlAG4AdABGAHIAbwBtAEEAcgByAGEAeQAsAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApACkALABcAG4AIAAgACAAIABEAEEAVABFAEQASQBGACgARAB1AHIAYQB0AGkAbwBuAFMAdABhAHIAdAAsACAAZAB1AHIAYQB0AGkAbwBuAEUAbgBkACwAIABcACIAZABcACIAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEEAdgBlAHIAYQBnAGUASABlAGEAZABNAG8AbgB0AGgAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEgAZQBhAGQAQQB0AE0AbwBuAHQAaABTAHQAYQByAHQALAAgAEgAZQBhAGQAQQB0AE0AbwBuAHQAaABFAG4AZAAsAFwAbgAgACAASQBGAFMAKABcAG4AIAAgACAAIABIAGUAYQBkAEEAdABNAG8AbgB0AGgAUwB0AGEAcgB0ACAAXAB1ADAAMAAzAGMAPQAwACwAIABIAGUAYQBkAEEAdABNAG8AbgB0AGgARQBuAGQALABcAG4AIAAgACAAIABIAGUAYQBkAEEAdABNAG8AbgB0AGgARQBuAGQAIABcAHUAMAAwADMAYwA9ADAALAAgAEgAZQBhAGQAQQB0AE0AbwBuAHQAaABTAHQAYQByAHQALABcAG4AIAAgACAAIABUAFIAVQBFACwAIAAoAEgAZQBhAGQAQQB0AE0AbwBuAHQAaABTAHQAYQByAHQAKwBIAGUAYQBkAEEAdABNAG8AbgB0AGgARQBuAGQAKQAvADIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBUAG8AdABhAGwAQgBpAHIAdABoAHMARAB1AHIAaQBuAGcATQBvAG4AdABoAFwAbgA9ACAATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAG8AbgB0AGgALAAgAE0AbwB2AGUAbQBlAG4AdABIAGUAYQBkAEEAcgByAGEAeQAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwAIABNAG8AdgBlAG0AZQBuAHQAVAB5AHAAZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAUwBVAE0AKABcAG4AIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABcAG4AIAAgACAAIAAgACAAIAAgAE0AbwB2AGUAbQBlAG4AdABIAGUAYQBkAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAKABNAG8AdgBlAG0AZQBuAHQARABhAHQAZQBBAHIAcgBhAHkAIABcAHUAMAAwADMAZQA9ACAARQBPAE0ATwBOAFQASAAoAE0AbwBuAHQAaAAsAC0AMQApACsAMQApACAAKgBcAG4AIAAgACAAIAAgACAAIAAgACgATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACAAXAB1ADAAMAAzAGMAPQAgAEUATwBNAE8ATgBUAEgAKABNAG8AbgB0AGgALAAwACkAKQAgACoAXABuACAAIAAgACAAIAAgACAAIAAoAE0AbwB2AGUAbQBlAG4AdABUAHkAcABlAEEAcgByAGEAeQAgAD0AIABcACIAQgBpAHIAdABoAFwAIgApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIAAwAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AQwBhAGwAYwB1AGwAYQB0AGUAUAByAG8AcABvAHIAdABpAG8AbgBDAG8AdwBzAEMAYQBsAHYAaQBuAGcAXABuAD0AIABMAEEATQBCAEQAQQAoAFwAbgAgACAAQgBpAHIAdABoAHMALAAgAEgAZQBhAGQALABcAG4AIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIABCAGkAcgB0AGgAcwAgAC8AIABIAGUAYQBkACwAXABuACAAIAAgACAAMABcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFQAbwB0AGEAbABNAG8AdgBlAG0AZQBuAHQATABpAHYAZQB3AGUAaQBnAGgAdABTAG8AbABkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAG8AdgBlAG0AZQBuAHQAVAB5AHAAZQAsACAASABlAGEAZAAsACAATABpAHYAZQB3AGUAaQBnAGgAdAAsAFwAbgAgACAASQBGACgATQBvAHYAZQBtAGUAbgB0AFQAeQBwAGUAIAA9ACAAXAAiAFMAYQBsAGUAXAAiACwAIABIAGUAYQBkACoATABpAHYAZQB3AGUAaQBnAGgAdAAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBTAHUAbQBQAHUAcgBjAGgAYQBzAGUAZABMAGkAdgBlAHcAZQBpAGcAaAB0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAG8AdgBlAG0AZQBuAHQAVAB5AHAAZQAsACAATQBvAHYAZQBtAGUAbgB0AFQAeQBwAGUAQQByAHIAYQB5ACwAIABIAGUAYQBkACwATABpAHYAZQB3AGUAaQBnAGgAdAAsACAAWwBTAG8AdQByAGMAZQBdACwAWwBTAG8AdQByAGMAZQBBAHIAcgBhAHkAXQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIAB0AG8AdABhAGwATABpAHYAZQB3AGUAaQBnAGgAdAAsACAASABlAGEAZAAqAEwAaQB2AGUAdwBlAGkAZwBoAHQALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMQAsAC0ALQAoAE0AbwB2AGUAbQBlAG4AdABUAHkAcABlAEEAcgByAGEAeQA9AE0AbwB2AGUAbQBlAG4AdABUAHkAcABlACkALABcAG4AIAAgACAAIABjAHIAaQB0AGUAcgBpAGEAMgAsAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAUwBvAHUAcgBjAGUAKQAsADEALAAtAC0AKABTAG8AdQByAGMAZQBBAHIAcgBhAHkAPQBTAG8AdQByAGMAZQApACkALABcAG4AIAAgACAAIABTAFUATQBQAFIATwBEAFUAQwBUACgAYwByAGkAdABlAHIAaQBhADEAKgBjAHIAaQB0AGUAcgBpAGEAMgAqAHQAbwB0AGEAbABMAGkAdgBlAHcAZQBpAGcAaAB0ACkAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBHAGUAdABIAGUAYQBkAEEAdABFAG4AZABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAARQBuAGQARABhAHQAZQAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABEAGEAdABlAEEAcgByAGEAeQAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAEEAcgByAGEAeQAsACAASABlAGEAZABBAHQARQBuAGQATwBmAE0AbwBuAHQAaABBAHIAcgBhAHkALABcAG4AIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgAFQARQBYAFQAKABFAEQAQQBUAEUAKABFAG4AZABEAGEAdABlACwAIAAwACkALABcACIAbQBtAG0AbQAgAHkAeQB5AHkAXAAiACkAXAB1ADAAMAAyADYATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAXABuACAAIAAgACAAIAAgAEQAYQB0AGUAQQByAHIAYQB5AFwAdQAwADAAMgA2AEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAASABlAGEAZABBAHQARQBuAGQATwBmAE0AbwBuAHQAaABBAHIAcgBhAHkAKQAsAFwAbgAgACAAIAAgAFwAIgAtAFwAIgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEUAbgB0AHIAeQBEAGEAdABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABIAGUAYQBkAEEAdABTAHQAYQByAHQALAAgAEgAZQBhAGQAQQB0AEUAbgB0AHIAeQAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAIABNAG8AdgBlAG0AZQBuAHQARABhAHQAZQBBAHIAcgBhAHkALAAgAE0AbwB2AGUAbQBlAG4AdABUAG8AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdAA9ADAALABcAG4AIAAgACAAIAAgACAASQBGACgAXABuACAAIAAgACAAIAAgACAAIABNAEkATgBJAEYAUwAoAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlAEEAcgByAGEAeQAsAE0AbwB2AGUAbQBlAG4AdABUAG8AQQByAHIAYQB5ACwATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkALABcAG4AIAAgACAAIAAgACAAIAAgAE0ASQBOAEkARgBTACgATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwATQBvAHYAZQBtAGUAbgB0AFQAbwBBAHIAcgBhAHkALABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAXAAiAC0AXAAiACAAXABuACAAIAAgACAAIAAgACkALABcAG4AIAAgACAAIAAgACAAXAAiAC0AXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEUAeABpAHQARABhAHQAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAASABlAGEAZABBAHQARQBuAGQALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwAIABNAG8AdgBlAG0AZQBuAHQARgByAG8AbQBBAHIAcgBhAHkALABcAG4AIAAgAEkARgAoAFwAbgAgACAAIAAgAEgAZQBhAGQAQQB0AEUAbgBkAD0AMAAsAFwAbgAgACAAIAAgAEkARgAoAFwAbgAgACAAIAAgACAAIABNAEEAWABJAEYAUwAoAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlAEEAcgByAGEAeQAsAE0AbwB2AGUAbQBlAG4AdABGAHIAbwBtAEEAcgByAGEAeQAsAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwApACwAXABuACAAIAAgACAAIAAgAE0AQQBYAEkARgBTACgATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwATQBvAHYAZQBtAGUAbgB0AEYAcgBvAG0AQQByAHIAYQB5ACwATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACkALABcAG4AIAAgACAAIAAgACAAXAAiAC0AXAAiAFwAbgAgACAAIAAgACkALABcAG4AIAAgACAAIABcACIALQBcACIAXABuACAAIAApAFwAbgApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBHAGUAdABIAGUAYQBkAEEAdABFAHgAaQB0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABFAHgAaQB0AEQAYQB0AGUALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAARABhAHQAZQBBAHIAcgBhAHkALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBBAHIAcgBhAHkALAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdABPAGYATQBvAG4AdABoAEEAcgByAGEAeQAsAFwAbgAgACAASQBGAEUAUgBSAE8AUgAoAFwAbgAgACAAIAAgAFgATABPAE8ASwBVAFAAKABcAG4AIAAgACAAIAAgACAAVABFAFgAVAAoAEUARABBAFQARQAoAEUAeABpAHQARABhAHQAZQAsACAAMAApACwAXAAiAG0AbQBtAG0AIAB5AHkAeQB5AFwAIgApAFwAdQAwADAAMgA2AEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsAFwAbgAgACAAIAAgACAAIABEAGEAdABlAEEAcgByAGEAeQBcAHUAMAAwADIANgBMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAIAAgAEgAZQBhAGQAQQB0AFMAdABhAHIAdABPAGYATQBvAG4AdABoAEEAcgByAGEAeQApACwAXABuACAAIAAgACAAXAAiAC0AXAAiAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQBuAHQAcgB5AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAAsACAARQBuAHQAcgB5AEQAYQB0AGUALAAgAE0AbwB2AGUAbQBlAG4AdABEAGEAdABlAEEAcgByAGEAeQAsACAATQBvAHYAZQBtAGUAbgB0AFQAbwBBAHIAcgBhAHkALAAgAE0AbwB2AGUAbQBlAG4AdABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAcgByAGEAeQAsAFwAbgAgACAASQBGACgAXABuACAAIAAgACAASQBTAE4AVQBNAEIARQBSACgARQBuAHQAcgB5AEQAYQB0AGUAKQAsAFwAbgAgACAAIAAgAEkARgAoAFwAbgAgACAAIAAgACAAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABTAHQAYQByAHQAPQAwACwAXABuACAAIAAgACAAIAAgAEEAVgBFAFIAQQBHAEUASQBGAFMAKABcAG4AIAAgACAAIAAgACAAIAAgAE0AbwB2AGUAbQBlAG4AdABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwAIABFAG4AdAByAHkARABhAHQAZQAsACAAXABuACAAIAAgACAAIAAgACAAIABNAG8AdgBlAG0AZQBuAHQAVABvAEEAcgByAGEAeQAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIABcACIALQBcACIAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAFwAIgAtAFwAIgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AEUAeABpAHQAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQBuAGQALAAgAEUAeABpAHQARABhAHQAZQAsACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwAIABNAG8AdgBlAG0AZQBuAHQARgByAG8AbQBBAHIAcgBhAHkALAAgAE0AbwB2AGUAbQBlAG4AdABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAcgByAGEAeQAsAFwAbgAgACAASQBGACgAXABuACAAIAAgACAASQBTAE4AVQBNAEIARQBSACgARQB4AGkAdABEAGEAdABlACkALABcAG4AIAAgACAAIABJAEYAKABcAG4AIAAgACAAIAAgACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQBuAGQAPQAwACwAXABuACAAIAAgACAAIAAgAEEAVgBFAFIAQQBHAEUASQBGAFMAKABcAG4AIAAgACAAIAAgACAAIAAgAE0AbwB2AGUAbQBlAG4AdABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAATQBvAHYAZQBtAGUAbgB0AEQAYQB0AGUAQQByAHIAYQB5ACwAIABFAHgAaQB0AEQAYQB0AGUALABcAG4AIAAgACAAIAAgACAAIAAgAE0AbwB2AGUAbQBlAG4AdABGAHIAbwBtAEEAcgByAGEAeQAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIABcACIALQBcACIAXABuACAAIAAgACAAKQAsAFwAbgAgACAAIAAgAFwAIgAtAFwAIgBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQAyAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABFAG4AdAByAHkARABhAHQAZQAsACAASABlAGEAZABBAHQAUwB0AGEAcgB0ACwAIABIAGUAYQBkAEEAdABFAG4AZAAsACAAUgBlAHAAbwByAHQAaQBuAGcAUwB0AGEAcgB0AEQAYQB0AGUALAAgAEUAeABpAHQARABhAHQAZQAsACAAUgBlAHAAbwByAHQAaQBuAGcARQBuAGQARABhAHQAZQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABkAGEAdABlAE8AZgBFAG4AdAByAHkALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAEUAbgB0AHIAeQBEAGEAdABlACkALAAgAEUAbgB0AHIAeQBEAGEAdABlACwAIABcACIALQBcACIAKQAsAFwAbgAgACAAIAAgAGQAYQB0AGUATwBmAFIAZQBwAG8AcgB0AGkAbgBnAFMAdABhAHIAdAAsACAASQBGACgASABlAGEAZABBAHQAUwB0AGEAcgB0AFwAdQAwADAAMwBlADAALAAgAFIAZQBwAG8AcgB0AGkAbgBnAFMAdABhAHIAdABEAGEAdABlACwAIABcACIALQBcACIAKQAsAFwAbgAgACAAIAAgAFwAbgAgACAAIAAgAGQAYQB0AGUATwBmAEUAeABpAHQALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAEUAeABpAHQARABhAHQAZQApACwAIABFAHgAaQB0AEQAYQB0AGUALAAgAFwAIgAtAFwAIgApACwAXABuACAAIAAgACAAZABhAHQAZQBPAGYAUgBlAHAAbwByAHQAaQBuAGcARQBuAGQALAAgAEkARgAoAEgAZQBhAGQAQQB0AEUAbgBkAFwAdQAwADAAMwBlADAALAAgAFIAZQBwAG8AcgB0AGkAbgBnAEUAbgBkAEQAYQB0AGUALAAgAFwAIgAtAFwAIgApACwAXABuAFwAbgAgACAAIAAgAGQAdQByAGEAdABpAG8AbgBTAHQAYQByAHQALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAGQAYQB0AGUATwBmAEUAbgB0AHIAeQApACwAIABkAGEAdABlAE8AZgBFAG4AdAByAHkALAAgAGQAYQB0AGUATwBmAFIAZQBwAG8AcgB0AGkAbgBnAFMAdABhAHIAdAApACwAXABuACAAIAAgACAAZAB1AHIAYQB0AGkAbwBuAEUAbgBkACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABkAGEAdABlAE8AZgBFAHgAaQB0ACkALAAgAGQAYQB0AGUATwBmAEUAeABpAHQALAAgAGQAYQB0AGUATwBmAFIAZQBwAG8AcgB0AGkAbgBnAEUAbgBkACkALABcAG4AIAAgACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAAIAAgAEQAQQBUAEUARABJAEYAKABkAHUAcgBhAHQAaQBvAG4AUwB0AGEAcgB0ACwAIABkAHUAcgBhAHQAaQBvAG4ARQBuAGQALAAgAFwAIgBkAFwAIgApACwAIABcACIALQBcACIAXABuACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBHAGUAdABEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAUABvAHMAdABXAGUAYQBuAGkAbgBnAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkALAAgAEQAYQB5AHMAVwBlAGEAbgBpAG4AZwAsAFwAbgAgACAARgBMAE8ATwBSAC4ATQBBAFQASAAoAFwAbgAgACAAIAAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgACAARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5ACAALQAgAEQAYQB5AHMAVwBlAGEAbgBpAG4AZwAsACAAMABcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQA7AFwAbgBcAG4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQAQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQBuAHQAcgB5ACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABFAG4AZAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQB4AGkAdAAsACAARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5ACwAXABuACAAIABJAEYARQBSAFIATwBSACgAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAAcwB0AGEAcgB0AEwAaQB2AGUAdwBlAGkAZwBoAHQALAAgAEkARgAoAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdABcAHUAMAAwADMAZQAwACwAIABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABTAHQAYQByAHQALAAgAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AEUAbgB0AHIAeQApACwAXABuACAAIAAgACAAIAAgAGUAbgBkAEwAaQB2AGUAdwBlAGkAZwBoAHQALAAgAEkARgAoAEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AEUAbgBkAFwAdQAwADAAMwBlADAALABMAGkAdgBlAHcAZQBpAGcAaAB0AEEAdABFAG4AZAAsACAATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQB4AGkAdAApACwAXABuACAAIAAgACAAIAAgACgAZQBuAGQATABpAHYAZQB3AGUAaQBnAGgAdAAtAHMAdABhAHIAdABMAGkAdgBlAHcAZQBpAGcAaAB0ACkALwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXABuACAAIAAgACAAKQAsACAAMABcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEEAZABqAHUAcwB0AGUAZABMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuACwAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALAAgAE0AbwBuAHQAaAAsACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAEEAcgByAGEAeQAsACAATQBvAG4AdABoAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAATQBvAG4AdABoACwAIABNAG8AbgB0AGgAQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALABcAG4AIAAgACAAIAAgACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAIAAqACAAQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEMAYQBsAGMAdQBsAGEAdABlAEcAcgBvAHcAdABoAEYAYQBjAHQAbwByAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAG8AbgB0AGgALAAgAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsACAAXABuACAAIABDAFAATQBvAG4AdABoAEEAcgByAGEAeQAsACAAQwBQAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBBAHIAcgBhAHkALAAgAEMAUABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALAAgAEMAUABUAGEAYgBsAGUATgBhAG0AZQAsAFwAbgAgACAARABNAEQATQBvAG4AdABoAEEAcgByAGEAeQAsACAARABNAEQATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAEEAcgByAGEAeQAsACAARABNAEQAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABEAE0ARABUAGEAYgBsAGUATgBhAG0AZQAsAFwAbgAgACAATABFAFQAKABcAG4AIAAgACAAIABtAG8AbgB0AGgAQwBQACwAIABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgAE0AbwBuAHQAaAAsACAAQwBQAE0AbwBuAHQAaABBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFwAbgAgACAAIAAgACAAIAAgACAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAXABuACAAIAAgACAAIAAgACAAIABDAFAATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIAAgACAAQwBQAFIAZQB0AHUAcgBuAEEAcgByAGEAeQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYQB2AGUAcgBhAGcAZQBDAFAALABcAG4AIAAgACAAIABBAFYARQBSAEEARwBFACgAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAEMAUABUAGEAYgBsAGUATgBhAG0AZQAsACwATQBBAFQAQwBIACgATABpAHYAZQBzAHQAbwBjAGsAQwBsAGEAcwBzACwAQwBQAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBBAHIAcgBhAHkALAAwACkAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAbQBvAG4AdABoAEQATQBEACwAIABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgAE0AbwBuAHQAaAAsACAARABNAEQATQBvAG4AdABoAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgAXABuACAAIAAgACAAIAAgACAAIABMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMALABcAG4AIAAgACAAIAAgACAAIAAgAEQATQBEAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBBAHIAcgBhAHkALABcAG4AIAAgACAAIAAgACAAIAAgAEQATQBEAFIAZQB0AHUAcgBuAEEAcgByAGEAeQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAYQB2AGUAcgBhAGcAZQBEAE0ARAAsAFwAbgAgACAAIAAgAEEAVgBFAFIAQQBHAEUAKABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgARABNAEQAVABhAGIAbABlAE4AYQBtAGUALAAsAE0AQQBUAEMASAAoAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwAsAEQATQBEAEwAaQB2AGUAcwB0AG8AYwBrAEMAbABhAHMAcwBBAHIAcgBhAHkALAAwACkAKQBcAG4AIAAgACAAIAApACwAXABuACAAIAAgACAAQQBWAEUAUgBBAEcARQAoAFwAbgAgACAAIAAgACAAIABtAG8AbgB0AGgAQwBQAC8AYQB2AGUAcgBhAGcAZQBDAFAALAAgAG0AbwBuAHQAaABEAE0ARAAvAGEAdgBlAHIAYQBnAGUARABNAEQAXABuACAAIAAgACAAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAEwAaQB2AGUAcwB0AG8AYwBrAF8ATABvAG8AawB1AHAATQBDAEYAUwB0AGEAdABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAE0AUwAsACAATQBNAFMAQQByAHIAYQB5ACwAIABTAHQAYQB0AGUALAAgAFMAdABhAHQAZQBBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsAFwAbgAgACAAWABMAE8ATwBLAFUAUAAoAE0ATQBTACwATQBNAFMAQQByAHIAYQB5ACwAXABuACAAIAAgACAAWABMAE8ATwBLAFUAUAAoAFMAdABhAHQAZQAsACAAUwB0AGEAdABlAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsAFIAbwB3AHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBhAG4AZABBAHIAcgBhAHkALABcAG4AIAAgACAAIABSAE8AVwAoAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACkAIAArACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQAgAC0AIAAxAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACwAXABuACAAIABDAE8ATABVAE0ATgAoAFQAYQBiAGwAZQBIAGUAYQBkAGUAcgBDAGUAbABsACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEEAcgByAGEAeQBJAG4AVABhAGIAbABlAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAQQByAHIAYQB5AEQAYQB0AGEALAAgAFQAYQBiAGwAZQBoAGUAYQBkAGUAcgBDAGUAbABsACwAIABSAG8AdwBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAYQBuAGQAQQByAHIAYQB5ACwAIABbAEMAbwBsAHUAbQBuAHMAQgBlAHQAdwBlAGUAbgBIAGUAYQBkAGUAcgBBAG4AZABBAHIAcgBhAHkAXQAsAFwAbgAgAEkARgBFAFIAUgBPAFIAKABcAG4AIAAgACAAIAAgAEkATgBEAEUAWAAoAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABVAE4ASQBRAFUARQAoAEEAcgByAGEAeQBEAGEAdABhACkALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIABSAE8AVwAoACkALQBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAKABUAGEAYgBsAGUAaABlAGEAZABlAHIAQwBlAGwAbAAsACAAUgBvAHcAcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAGEAbgBkAEEAcgByAGEAeQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAQwBPAEwAVQBNAE4AKAApAC0AVQB0AGkAbABpAHQAeQBfAEcAZQB0AEEAcgByAGEAeQBUAGEAYgBsAGUAQwBvAGwAdQBtAG4AUwB0AGEAcgB0AE4AdQBtAGIAZQByACgAVABhAGIAbABlAGgAZQBhAGQAZQByAEMAZQBsAGwAKQAgACsAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgAQwBvAGwAdQBtAG4AcwBCAGUAdAB3AGUAZQBuAEgAZQBhAGQAZQByAEEAbgBkAEEAcgByAGEAeQApACwAIAAxACwAIABDAG8AbAB1AG0AbgBzAEIAZQB0AHcAZQBlAG4ASABlAGEAZABlAHIAQQBuAGQAQQByAHIAYQB5ACkAXABuACAAIAAgACAAIAAgACAAIAApACwAIABcACIAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQAsACAATABvAG8AawB1AHAAQQByAHIAYQB5ACwAIABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAAVgBhAGwAdQBlAEkAbgBUAGEAYgBsAGUATgB1AG0AYgBlAHIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAXABuACAAIAAgACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAXABuACAAIAAgACAAIAAgACAAIABYAEwATwBPAEsAVQBQACgATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABMAG8AbwBrAHUAcABBAHIAcgBhAHkALAAgAFIAZQB0AHUAcgBuAEEAcgByAGEAeQAsACAAXAAiAFwAIgApAFwAbgAgACAAIAAgACkALAAgAFgATABPAE8ASwBVAFAAKABMAG8AbwBrAHUAcABWAGEAbAB1AGUALAAgAEwAbwBvAGsAdQBwAEEAcgByAGEAeQAsACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACwAIABcACIAXAAiACkALAAgADAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAcABsAGkAdABTAHQAcgBpAG4AZwBJAG4AdABvAEEAcgByAGEAeQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEMAZQBsAGwALAAgAEQAZQBsAGkAbQBpAHQAZQByACwAIABbAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxAF0ALAAgAFsAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIAXQAsAFwAbgAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAWABNAEwAKABcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBcAHUAMAAwADMAYwB0AFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiACAAXAB1ADAAMAAyADYAXABuACAAIAAgACAAIAAgACAAIABTAFUAQgBTAFQASQBUAFUAVABFACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFMAVQBCAFMAVABJAFQAVQBUAEUAKABTAFUAQgBTAFQASQBUAFUAVABFACgAQwBlAGwAbAAsAEMAaABhAHIAYQBjAHQAZQByAFQAbwBSAGUAbQBvAHYAZQAxACwAXAAiAFwAIgApACwAQwBoAGEAcgBhAGMAdABlAHIAVABvAFIAZQBtAG8AdgBlADIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARABlAGwAaQBtAGkAdABlAHIALABcACIAXAB1ADAAMAAzAGMALwBzAFwAdQAwADAAMwBlAFwAdQAwADAAMwBjAHMAXAB1ADAAMAAzAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAKQAgAFwAdQAwADAAMgA2AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFwAdQAwADAAMwBjAC8AcwBcAHUAMAAwADMAZQBcAHUAMAAwADMAYwAvAHQAXAB1ADAAMAAzAGUAXAAiACwAXABuACAAIAAgACAAIAAgACAAIABcACIALwAvAHMAXAAiAFwAbgAgACAAIAAgACkAXABuACkAOwBcAG4AXABuAFUAdABpAGwAaQB0AHkAXwBHAGUAdABDAGwAaQBtAGEAdABlAFoAbwBuAGUAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABhAHYAZwBUAGUAbQBwACwAYQB2AGcAUgBhAGkAbgAsAGYAcgBvAHMAdABEAGEAeQBzACwAZQBsAGUAdgAsAG0AYQBwAF8AcABlAHQALABcAG4AIAAgACAAIABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQAsAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACwAXABuACAAIAAgACAAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQAsAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkALABcAG4AIAAgACAAIABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACwAbQBhAHgARgByAG8AcwB0AEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAG0AYQB4AEUAbABlAHYAYQB0AGkAbwBuAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAG0AaQBuAFAARQBUAEEAcgByAGEAeQAsAG0AYQB4AFAARQBUAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgAGMAbABpAG0AYQB0AGUAWgBvAG4AZQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBUAGUAbQBwAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAVABlAG0AcAApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFQAZQBtAHAAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBhAHYAZwBUAGUAbQBwACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUgBhAGkAbgBmAGEAbABsAEEAcgByAGEAeQApAFwAdQAwADAAMwBjAD0AYQB2AGcAUgBhAGkAbgApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AFIAYQBpAG4AZgBhAGwAbABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGEAdgBnAFIAYQBpAG4AKQAqAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABtAGkAbgBGAHIAbwBzAHQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBmAHIAbwBzAHQARABhAHkAcwApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAG0AYQB4AEYAcgBvAHMAdABBAHIAcgBhAHkAKQBcAHUAMAAwADMAZQA9AGYAcgBvAHMAdABEAGEAeQBzACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4ARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgARQBsAGUAdgBhAHQAaQBvAG4AQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBlAGwAZQB2ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBpAG4AUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGMAPQBtAGEAcABfAHAAZQB0ACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACgAVgBBAEwAVQBFACgAbQBhAHgAUABFAFQAQQByAHIAYQB5ACkAXAB1ADAAMAAzAGUAPQBtAGEAcABfAHAAZQB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAFQAQQBLAEUAKABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAARgBJAEwAVABFAFIAKABjAGwAaQBtAGEAdABlAFoAbwBuAGUAQQByAHIAYQB5ACwAbQBhAHMAawAsACAAXAAiAE4AbwAgAG0AYQB0AGMAaABcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAxAFwAbgAgACAAIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAASQB0AGUAbQBGAHIAbwBtAE0AaQBuAE0AYQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABvAG8AawB1AHAAVgBhAGwAdQBlACwAIABNAGkAbgBBAHIAcgBhAHkALAAgAE0AYQB4AEEAcgByAGEAeQAsACAASQB0AGUAbQBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAAbQBhAHMAawAsAFwAbgAgACAAIAAgACAAIAAgACAAKABWAEEATABVAEUAKABNAGkAbgBBAHIAcgBhAHkAKQBcAHUAMAAwADMAYwA9AEwAbwBvAGsAdQBwAFYAYQBsAHUAZQApACoAXABuACAAIAAgACAAIAAgACAAIAAoAFYAQQBMAFUARQAoAE0AYQB4AEEAcgByAGEAeQApAFwAdQAwADAAMwBlAD0ATABvAG8AawB1AHAAVgBhAGwAdQBlACkALABcAG4AIAAgACAAIAAgACAAIAAgAEYASQBMAFQARQBSACgASQB0AGUAbQBBAHIAcgBhAHkALAAgAG0AYQBzAGsALAAgAFwAIgBOAG8AIABtAGEAdABjAGgAXAAiACkAXABuACAAIAAgACAAKQBcAG4AKQA7AFwAbgBcAG4AVQB0AGkAbABpAHQAeQBfAFMAdQBtAFEAdQBhAG4AdABpAHQAeQBGAHIAbwBtAEMAcgBpAHQAZQByAGkAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAQwByAGkAdABlAHIAaQBhADEALAAgAEMAcgBpAHQAZQByAGkAYQAxAFQAeQBwAGUAQQByAHIAYQB5ACwAIABRAHUAYQBuAHQAaQB0AHkALAAgAFsATQB1AGwAdABpAHAAbABpAGUAcgBdACwAIABbAEMAcgBpAHQAZQByAGkAYQAyAF0ALABbAEMAcgBpAHQAZQByAGkAYQAyAEEAcgByAGEAeQBdACwAXABuACAAIABMAEUAVAAoAFwAbgAgACAAIAAgAG0AdQBsAHQAaQBwAGwAaQBlAHIALAAgAEkARgAoAEkAUwBPAE0ASQBUAFQARQBEACgATQB1AGwAdABpAHAAbABpAGUAcgApACwAMQAsAE0AdQBsAHQAaQBwAGwAaQBlAHIAKQAsAFwAbgAgACAAIAAgAHEAdQBhAG4AdABpAHQAeQAsACAAUQB1AGEAbgB0AGkAdAB5ACoATQB1AGwAdABpAHAAbABpAGUAcgAsAFwAbgAgACAAIAAgAGMAcgBpAHQAZQByAGkAYQAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADEAVAB5AHAAZQBBAHIAcgBhAHkAPQBDAHIAaQB0AGUAcgBpAGEAMQApACwAXABuACAAIAAgACAAYwByAGkAdABlAHIAaQBhADIALABJAEYAKABJAFMATwBNAEkAVABUAEUARAAoAEMAcgBpAHQAZQByAGkAYQAyACkALAAxACwALQAtACgAQwByAGkAdABlAHIAaQBhADIAQQByAHIAYQB5AD0AQwByAGkAdABlAHIAaQBhADIAKQApACwAXABuACAAIAAgACAAUwBVAE0AUABSAE8ARABVAEMAVAAoAGMAcgBpAHQAZQByAGkAYQAxACoAYwByAGkAdABlAHIAaQBhADIAKgBxAHUAYQBuAHQAaQB0AHkAKQBcAG4AIAAgACkAXABuACkAOwBcAG4AXABuAGcAZQB0AE8AdgBlAHIAbABhAHAAcABpAG4AZwBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAXABuACAAIAAgACAAIAAgACAAIABBACwAUwAtADMANgA1ACwAXABuACAAIAAgACAAIAAgACAAIAB5AGEALABZAEUAQQBSACgAQQApACwAXABuACAAIAAgACAAIAAgACAAIAB5AGIALABZAEUAQQBSACgARQApACwAXABuACAAIAAgACAAIAAgACAAIABmAGkAcgBzAHQAWQBlAGEAcgAsAHkAYQArACgAUABlAHIAaQBvAGQARQBuAGQAKABEAEEAVABFACgAeQBhACwAbQAsAGQAKQApAFwAdQAwADAAMwBjACAAUwApACwAXABuACAAIAAgACAAIAAgACAAIABsAGEAcwB0AFkAZQBhAHIALAB5AGIALQAoAEQAQQBUAEUAKAB5AGIALABtACwAZAApAFwAdQAwADAAMwBlACAARQApACwAXABuACAAIAAgACAAIAAgACAAIABNAEEAWAAoADAALABsAGEAcwB0AFkAZQBhAHIALQBmAGkAcgBzAHQAWQBlAGEAcgArADEAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAFMAdABhAHIAdAAsAFAAcgBvAGQAdQBjAHQAaQBvAG4AQwB5AGMAbABlAEUAbgBkACwAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAFMAdABhAHIAdAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABTACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXABuACAAIAAgACAAIAAgACAAIABFACwAUAByAG8AZAB1AGMAdABpAG8AbgBDAHkAYwBsAGUARQBuAGQALABcAG4AIAAgACAAIAAgACAAIAAgAG0ALABNAE8ATgBUAEgAKABSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACkALABcAG4AIAAgACAAIAAgACAAIAAgAGQALABEAEEAWQAoAFIAZQBwAG8AcgB0AGkAbgBnAEMAeQBjAGwAZQBTAHQAYQByAHQAKQAsACAALwAqAGgAZQBsAHAAZQByADoAIABlAG4AZAAgAGQAYQB0AGUAIABmAG8AcgAgAGEAIAByAGUAcABvAHIAdABpAG4AZwAgAHAAZQByAGkAbwBkACAAcwB0AGEAcgB0AGkAbgBnACAAYQB0ACAAYQAgAGcAaQB2AGUAbgAgAGQAYQB0AGUAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAUABlAHIAaQBvAGQARQBuAGQALABMAEEATQBCAEQAQQAoAHMAdAAsAEUARABBAFQARQAoAHMAdAAsADEAMgApAC0AMQApACwAIAAvACoAbwBuAGwAeQAgAG4AZQBlAGQAIAB0AG8AIABsAG8AbwBrACAAYgBhAGMAawAgADMANgA1ACAAZABhAHkAcwAoAG0AYQB4ACAAbwB2AGUAcgBsAGEAcAAgAHcAaQBuAGQAbwB3ACkAKgAvAFwAbgAgACAAIAAgACAAIAAgACAAQQAsAFMALQAzADYANQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBhACwAWQBFAEEAUgAoAEEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAeQBiACwAWQBFAEEAUgAoAEUAKQAsACAALwAqAGkAZgAgAHQAaABlACAAYQBuAGMAaABvAHIAIABmAG8AcgAgAHkAYQAgAGUAbgBkAHMAIABiAGUAZgBvAHIAZQAgAFMALABpAHQAIABjAGEAbgBcAHUAMAAwADIANwB0ACAAbwB2AGUAcgBsAGEAcAA7ACAAbQBvAHYAZQAgAHQAbwAgAG4AZQB4AHQAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGYAaQByAHMAdABZAGUAYQByACwAeQBhACsAKABQAGUAcgBpAG8AZABFAG4AZAAoAEQAQQBUAEUAKAB5AGEALABtACwAZAApACkAXAB1ADAAMAAzAGMAUwApACwAIAAvACoAaQBmACAAdABoAGUAIABhAG4AYwBoAG8AcgAgAGYAbwByACAAeQBiACAAcwB0AGEAcgB0AHMAIABhAGYAdABlAHIAIABFACwAaQB0ACAAYwBhAG4AXAB1ADAAMAAyADcAdAAgAG8AdgBlAHIAbABhAHAAOwAgAG0AbwB2AGUAIAB0AG8AIABwAHIAZQB2AGkAbwB1AHMAIAB5AGUAYQByACoALwBcAG4AIAAgACAAIAAgACAAIAAgAGwAYQBzAHQAWQBlAGEAcgAsAHkAYgAtACgARABBAFQARQAoAHkAYgAsAG0ALABkACkAXAB1ADAAMAAzAGUARQApACwAXABuACAAIAAgACAAIAAgACAAIABuACwATQBBAFgAKAAwACwAbABhAHMAdABZAGUAYQByAC0AZgBpAHIAcwB0AFkAZQBhAHIAKwAxACkALABcAG4AIAAgACAAIAAgACAAIAAgAHkAcgBzACwAUwBFAFEAVQBFAE4AQwBFACgAbgAsADEALABmAGkAcgBzAHQAWQBlAGEAcgAsADEAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAcwB0AGEAcgB0AHMALABEAEEAVABFACgAeQByAHMALABtACwAZAApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzACwATQBBAFAAKABzAHQAYQByAHQAcwAsAFAAZQByAGkAbwBkAEUAbgBkACkALABcAG4AIAAgACAAIAAgACAAIAAgAHQAYQBnACwASQBGACgAcwB0AGEAcgB0AHMAPQBSAGUAcABvAHIAdABpAG4AZwBDAHkAYwBsAGUAUwB0AGEAcgB0ACwAXAAiACAAKABUAGgAaQBzACAAcgBlAHAAbwByAHQAaQBuAGcAIABjAHkAYwBsAGUAKQBcACIALABcACIAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAHMAdABhAHIAdABzAFQAZQB4AHQALABUAEUAWABUACgAcwB0AGEAcgB0AHMALABcACIAZABkACAAbQBtAG0AIAB5AHkAeQB5AFwAIgApACwAXABuACAAIAAgACAAIAAgACAAIABlAG4AZABzAFQAZQB4AHQALABUAEUAWABUACgAZQBuAGQAcwAsAFwAIgBkAGQAIABtAG0AbQAgAHkAeQB5AHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAEkARgAoAG4APQAwACwAXAAiAFwAIgAsAEgAUwBUAEEAQwBLACgAcwB0AGEAcgB0AHMAVABlAHgAdAAgAFwAdQAwADAAMgA2ACAAXAAiACAAdABvACAAXAAiACAAXAB1ADAAMAAyADYAIABlAG4AZABzAFQAZQB4AHQAIABcAHUAMAAwADIANgAgAHQAYQBnACkAKQBcAG4AIAAgACAAIAApAFwAbgApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4APQBMAEEATQBCAEQAQQAoAEYAdQBuAGMAdABpAG8AbgAsACAAVABFAFgAVABCAEUARgBPAFIARQAoAEYATwBSAE0AVQBMAEEAVABFAFgAVAAoAEYAdQBuAGMAdABpAG8AbgApACwAIABcACIAKABcACIAKQApADsAXABuAFwAbgBVAHQAaQBsAGkAdAB5AF8ATABvAG8AawB1AHAATgAyAE8ARQBGAEYAcgBvAG0AUAByAG8AZABJAHIAcgBpAGcAYQB0AGkAbwBuAFIAYQBpAG4AZgBhAGwAbABcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQALAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBBAHIAcgBhAHkALAAgAEkAcgByAGkAZwBhAHQAaQBvAG4ATQBlAHQAaABvAGQAQQByAHIAYQB5ACwAIABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkALABSAGUAdAB1AHIAbgBBAHIAcgBhAHkALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIAAgACAASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAAsACAASQBGACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZAA9AFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAXAAiAE4AbwB0ACAAaQByAHIAaQBnAGEAdABlAGQAXAAiACwAIABcACIAQQBuAHkAXAAiACkALABcAG4AIAAgACAAIAAgACAAIAAgAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlACwAIABJAEYAKABJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACAAPQAgAFwAIgBOAG8AdAAgAGkAcgByAGkAZwBhAHQAZQBkAFwAIgAsACAAUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUALAAgAFwAIgBBAG4AeQBcACIAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAWABMAE8ATwBLAFUAUAAoADEALAAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgACAAIAAoAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AQQByAHIAYQB5AD0AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQApACoAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgACgASQByAHIAaQBnAGEAdABpAG8AbgBNAGUAdABoAG8AZABBAHIAcgBhAHkAPQBJAHIAcgBpAGcAYQB0AGkAbwBuAE0AZQB0AGgAbwBkACkAKgBcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAKABSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBBAHIAcgBhAHkAPQBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQApACwAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIAAgACAAUgBlAHQAdQByAG4AQQByAHIAYQB5ACkAXABuACAAIAAgACAAKQBcAG4AKQA7ACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhACIALAAiAHQAZQB4AHQAIgA6ACIAXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYwBoAGUAbQBpAGMAYQBsACAAYwBvAG0AcABvAHUAbgBkACAAcwBjAG8AcABlACAAMwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAUwBjAG8AcABlACAAMwAgAEcASABHACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAgADIAMAAyADYAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyADYALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAZQBnAG8AcgB5AFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdAAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAXAAiACwAIABcACIARQBtAGIAZQBkAGQAZQBkACAARQBtAGkAcwBzAGkAbwBuAHMAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAASQBuAHQAZQBuAHMAaQB0AHkAIABVAG4AaQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAEEAbQBtAG8AbgBpAGEAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADAAMQAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBBAG0AbQBvAG4AaQBhAFwAIgAsACAAXAAiAEMAaABpAG4AYQBcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADAAMQAwADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBBAG0AbQBvAG4AaQBhAFwAIgAsACAAXAAiAFkAZQBtAGUAbgBcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADAAMQAwADMALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBBAG0AbQBvAG4AaQBhAFwAIgAsACAAXAAiAEMAYQBuAGEAZABhAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMAAxADAANAAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAFUAcgBlAGEAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADAAMgAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBVAHIAZQBhAFwAIgAsACAAXAAiAEMAaABpAG4AYQBcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADAAMgAwADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBVAHIAZQBhAFwAIgAsACAAXAAiAFkAZQBtAGUAbgBcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADAAMgAwADMALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBVAHIAZQBhAFwAIgAsACAAXAAiAEMAYQBuAGEAZABhAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMAAyADAANAAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAE0AbwBuAG8AYQBtAG0AbwBuAGkAdQBtACAAcABoAG8AcwBwAGgAYQB0AGUAIAAoAE0AQQBQACkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADAAMwAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBEAGkAYQBtAG0AbwBuAGkAdQBtACAAUABoAG8AcwBwAGgAYQB0AGUAIAAoAEQAQQBQACkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADAANAAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBVAHIAZQBhAC0AQQBtAG0AbwBuAGkAdQBtACAATgBpAHQAcgBhAHQAZQAgACgAVQBBAE4AKQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMAA1ADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAEEAbQBtAG8AbgBpAHUAbQAgAE4AaQB0AHIAYQB0AGUAIAAoAEEATgApAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMQAwADYAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIAQwBhAGwAYwBpAHUAbQAgAEEAbQBtAG8AbgBpAHUAbQAgAE4AaQB0AHIAYQB0AGUAIAAoAEMAQQBOACkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADAANwAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBTAHUAbABwAGgAYQB0AGUAIABvAGYAIABBAG0AbQBvAG4AaQBhACAAKABTAE8AQQApAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMQAwADgAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIATgBpAHQAcgBvAGcAZQBuACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADAAOQAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBOAGkAdAByAG8AZwBlAG4AIAAtACAATgBpAHQAcgBhAHQAZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMQAwADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAC0AIABBAG0AbQBvAG4AaQBhAGMAYQBsAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMQAxADEAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIATQB1AHIAaQBhAHQAZQAgAG8AZgAgAFAAbwB0AGEAcwBoACAAKABNAE8AUAAgAC8AIABLAEMATAApAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMQAxADIAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIAUwBpAG4AZwBsAGUAIABzAHUAcABlAHIAcABoAG8AcwBwAGgAYQB0AGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADEAMwAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBEAG8AdQBiAGwAZQAgAHMAdQBwAGUAcgBwAGgAbwBzAHAAaABhAHQAZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMQA0ADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAFAAaABvAHMAcABoAG8AcgB1AHMAIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADEAMQA1ADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgBvAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAFAAbwB0AGEAcwBzAGkAdQBtACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAxADEANgAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AbwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBTAHUAbABmAHUAcgAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMQAxADcAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIAWgBpAG4AYwAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMQAxADgAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIASQBuAG8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIAQwBhAGwAYwBpAHUAbQAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMQAxADkAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAE8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAIABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUwBjAG8AcABlADMAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAcwBjAG8AcABlACAAMwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBTAGMAbwBwAGUAIAAzACAARwBIAEcAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5ACAAMgAwADIANgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADEALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAZQBnAG8AcgB5AFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdAAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAXAAiACwAIABcACIARQBtAGIAZQBkAGQAZQBkACAARQBtAGkAcwBzAGkAbwBuAHMAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAASQBuAHQAZQBuAHMAaQB0AHkAIABVAG4AaQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIARABhAGkAcgB5ACAATQBhAG4AdQByAGUAXAAiACwAIABcACIAUAByAGkAbQBhAHIAeQAgAE0ATQBTAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADIAMAAxADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AcgBnAGEAbgBpAGMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiACwAIABcACIARABhAGkAcgB5ACAATQBhAG4AdQByAGUAXAAiACwAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAIABNAE0AUwBcACIALAAgAFwAIgB0AFwAIgAsACAAMAAyADAAMQAwADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAFAAbwByAGsAIABNAGEAbgB1AHIAZQBcACIALAAgAFwAIgBQAHIAaQBtAGEAcgB5ACAATQBNAFMAXAAiACwAIABcACIAdABcACIALAAgADAAMgAwADIAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBQAG8AcgBrACAATQBhAG4AdQByAGUAXAAiACwAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAIABNAE0AUwBcACIALAAgAFwAIgB0AFwAIgAsACAAMAAyADAAMgAwADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAEYAZQBlAGQAbABvAHQAIABNAGEAbgB1AHIAZQBcACIALAAgAFwAIgBQAHIAaQBtAGEAcgB5ACAATQBNAFMAXAAiACwAIABcACIAdABcACIALAAgADAAMgAwADMAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBGAGUAZQBkAGwAbwB0ACAATQBhAG4AdQByAGUAXAAiACwAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAIABNAE0AUwBcACIALAAgAFwAIgB0AFwAIgAsACAAMAAyADAAMwAwADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAEYAZQBlAGQAbABvAHQAIABNAGEAbgB1AHIAZQBcACIALAAgAFwAIgBUAGUAcgB0AGkAYQByAHkAIABNAE0AUwBcACIALAAgAFwAIgB0AFwAIgAsACAAMAAyADAAMwAwADMALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAFAAbwB1AGwAdAByAHkAIABNAGEAbgB1AHIAZQBcACIALAAgAFwAIgBQAHIAaQBtAGEAcgB5ACAATQBNAFMAXAAiACwAIABcACIAdABcACIALAAgADAAMgAwADQAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwByAGcAYQBuAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAATQBhAG4AdQByAGUAXAAiACwAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAIABNAE0AUwBcACIALAAgAFwAIgB0AFwAIgAsACAAMAAyADAANAAwADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHIAZwBhAG4AaQBjACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgAsACAAXAAiAE8AdABoAGUAcgBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADIAMAA1ADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAG8AaQBsACAAYQBtAGUAbgBkAG0AZQBuAHQAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUwBjAG8AcABlADMAXwBTAG8AaQBsAEEAbQBlAG4AZABtAGUAbgB0AHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBTAG8AaQBsACAAYQBtAGUAbgBkAG0AZQBuAHQAcwAgAHMAYwBvAHAAZQAgADMAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBTAG8AaQBsAEEAbQBlAG4AZABtAGUAbgB0AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAYwBvAHAAZQAgADMAIABHAEgARwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkAIAAyADAAMgA2AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAFMAbwBpAGwAQQBtAGUAbgBkAG0AZQBuAHQAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAdABlAGcAbwByAHkAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBcACIALAAgAFwAIgBFAG0AYgBlAGQAZABlAGQAIABFAG0AaQBzAHMAaQBvAG4AcwAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABJAG4AdABlAG4AcwBpAHQAeQAgAFUAbgBpAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAGkAbAAgAEEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIATABpAG0AZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADMAMAAxADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwBpAGwAIABBAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAEwAaQBtAGUAcwBhAG4AZABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADMAMAAxADAAMgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwBpAGwAIABBAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAEQAbwBsAG8AbQBpAHQAZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADMAMAAxADAAMwAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAbwBpAGwAIABBAG0AZQBuAGQAbQBlAG4AdABzAFwAIgAsACAAXAAiAEcAeQBwAHMAdQBtAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAAMwAwADEAMAA0ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBvAGkAbAAgAEEAbQBlAG4AZABtAGUAbgB0AHMAXAAiACwAIABcACIAUABvAHQAYQBzAGgAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAAzADAAMQAwADUALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQQBnAHIAbwBjAGgAZQBtAGkAYwBhAGwAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUwBjAG8AcABlADMAXwBBAGcAcgBvAGMAaABlAG0AaQBjAGEAbABzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQBnAHIAbwBjAGgAZQBtAGkAYwBhAGwAcwAgAHMAYwBvAHAAZQAgADMAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBBAGcAcgBvAGMAaABlAG0AaQBjAGEAbABzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBTAGMAbwBwAGUAIAAzACAARwBIAEcAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5ACAAMgAwADIANgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEEAZwByAG8AYwBoAGUAbQBpAGMAYQBsAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AQQBnAHIAbwBjAGgAZQBtAGkAYwBhAGwAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAdABlAGcAbwByAHkAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBcACIALAAgAFwAIgBFAG0AYgBlAGQAZABlAGQAIABFAG0AaQBzAHMAaQBvAG4AcwAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABJAG4AdABlAG4AcwBpAHQAeQAgAFUAbgBpAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBnAHIAbwBjAGgAZQBtAGkAYwBhAGwAcwBcACIALAAgAFwAIgBHAGwAeQBwAGgAbwBzAGEAdABlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANAAwADEAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBnAHIAbwBjAGgAZQBtAGkAYwBhAGwAcwBcACIALAAgAFwAIgBQAGEAcgBhAHEAdQBhAHQALAAgAGQAaQBxAHUAYQB0AFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANAAwADEAMAAyACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBnAHIAbwBjAGgAZQBtAGkAYwBhAGwAcwBcACIALAAgAFwAIgBHAGUAbgBlAHIAaQBjACAASABlAHIAYgBpAGMAaQBkAGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA0ADAAMQAwADMALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGcAcgBvAGMAaABlAG0AaQBjAGEAbABzAFwAIgAsACAAXAAiAEcAZQBuAGUAcgBpAGMAIABJAG4AcwBlAGMAdABpAGMAaQBkAGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA0ADAAMQAwADQALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGcAcgBvAGMAaABlAG0AaQBjAGEAbABzAFwAIgAsACAAXAAiAEcAZQBuAGUAcgBpAGMAIABGAHUAbgBnAGkAYwBpAGQAZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADQAMAAxADAANQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBMAGkAYwBrACAAQgBsAG8AYwBrAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ATABpAGMAawBCAGwAbwBjAGsAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEwAaQBjAGsAIABCAGwAbwBjAGsAcwAgAHMAYwBvAHAAZQAgADMAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBMAGkAYwBrAEIAbABvAGMAawBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBTAGMAbwBwAGUAIAAzACAARwBIAEcAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5ACAAMgAwADIANgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEwAaQBjAGsAQgBsAG8AYwBrAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ATABpAGMAawBCAGwAbwBjAGsAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAdABlAGcAbwByAHkAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBcACIALAAgAFwAIgBFAG0AYgBlAGQAZABlAGQAIABFAG0AaQBzAHMAaQBvAG4AcwAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABJAG4AdABlAG4AcwBpAHQAeQAgAFUAbgBpAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAGMAawAgAEIAbABvAGMAawBzAFwAIgAsACAAXAAiAE0AaQBuAGUAcgBhAGwAIABiAGwAbwBjAGsAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA1ADAAMQAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAYwBrACAAQgBsAG8AYwBrAHMAXAAiACwAIABcACIAVwBlAGEAbgBlAHIAIABiAGwAbwBjAGsAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA1ADAAMQAwADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAYwBrACAAQgBsAG8AYwBrAHMAXAAiACwAIABcACIARAByAHkAIABzAGUAYQBzAG8AbgAgAG0AaQB4AFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANQAwADEAMAAzACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEEAbgBpAG0AYQBsACAARgBlAGUAZABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUwBjAG8AcABlADMAXwBBAG4AaQBtAGEAbABGAGUAZQBkAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQQBuAGkAbQBhAGwAIABGAGUAZQBkACAAcwBjAG8AcABlACAAMwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEEAbgBpAG0AYQBsAEYAZQBlAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAYwBvAHAAZQAgADMAIABHAEgARwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkAIAAyADAAMgA2AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AQQBuAGkAbQBhAGwARgBlAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBBAG4AaQBtAGEAbABGAGUAZQBkAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADcALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAZQBnAG8AcgB5AFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdAAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAXAAiACwAIABcACIARQBtAGIAZQBkAGQAZQBkACAARQBtAGkAcwBzAGkAbwBuAHMAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAASQBuAHQAZQBuAHMAaQB0AHkAIABVAG4AaQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAARgBlAGUAZABcACIALAAgAFwAIgBHAHIAYQBpAG4AXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA2ADAAMQAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEYAZQBlAGQAXAAiACwAIABcACIAVwBoAGUAYQB0AFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANgAwADEAMAAyACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABGAGUAZQBkAFwAIgAsACAAXAAiAFcAaABlAGEAdAAgAEIAcgBhAG4AXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA2ADAAMQAwADMALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEYAZQBlAGQAXAAiACwAIABcACIAQgBhAHIAbABlAHkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA2ADAAMQAwADQALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEYAZQBlAGQAXAAiACwAIABcACIAUwBvAHkAYgBlAGEAbgBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADYAMAAxADAANQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAARgBlAGUAZABcACIALAAgAFwAIgBTAG8AeQBiAGUAYQBuACAAbQBlAGEAbABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADYAMAAxADAANgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAARgBlAGUAZABcACIALAAgAFwAIgBDAGEAbgBvAGwAYQAgAG0AZQBhAGwAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA2ADAAMQAwADcALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEYAZQBlAGQAXAAiACwAIABcACIAQwBhAG4AbwBsAGEAIABvAGkAbABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADYAMAAxADAAOAAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAARgBlAGUAZABcACIALAAgAFwAIgBCAGUAZQB0ACAAcAB1AGwAcABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADYAMAAxADAAOQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBpAG0AYQBsACAARgBlAGUAZABcACIALAAgAFwAIgBDAG8AdAB0AG8AbgAgAHMAZQBlAGQAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA2ADAAMQAxADAALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEYAZQBlAGQAXAAiACwAIABcACIASABhAHkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA2ADAAMQAxADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEYAZQBlAGQAXAAiACwAIABcACIARgBlAGUAZAAgAGYAbwByAG0AdQBsAGEAdABpAG8AbgBzACAAKABjAGgAaQBjAGsAZQBuACwAIABwAGkAZwBzACwAIABjAGEAdAB0AGwAZQAsACAAZABhAGkAcgB5ACkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA2ADAAMQAxADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AaQBtAGEAbAAgAEYAZQBlAGQAXAAiACwAIABcACIATQBvAGwAYQBzAHMAZQBzAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANgAwADEAMQAzACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABGAGUAZQBkAFwAIgAsACAAXAAiAEIAZQBuAHQAbwBuAGkAdABlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANgAwADEAMQA0ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABGAGUAZQBkAFwAIgAsACAAXAAiAE0AZQBhAHQAIABtAGUAYQBsAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANgAwADEAMQA1ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBuAGkAbQBhAGwAIABGAGUAZQBkAFwAIgAsACAAXAAiAEIAZQBuAHQATABpAG0AZQAsACAAcABoAG8AcwBwAGgAbwByAHUAcwAsACAAcABvAHQAYQBzAGgAbwBuAGkAdABlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANgAwADEAMQA0ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAgAEYAZQBlAGQAIABhAG4AZAAgAEIAYQBpAHQAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AQQBxAHUAYQBjAHUAbAB0AHUAcgBlAEYAZQBlAGQAQQBuAGQAQgBhAGkAdABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAgAEYAZQBlAGQAIABhAG4AZAAgAEIAYQBpAHQAIABzAGMAbwBwAGUAIAAzAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AQQBxAHUAYQBjAHUAbAB0AHUAcgBlAEYAZQBlAGQAQQBuAGQAQgBhAGkAdABfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAUwBjAG8AcABlACAAMwAgAEcASABHACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAgADIAMAAyADYAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBBAHEAdQBhAGMAdQBsAHQAdQByAGUARgBlAGUAZABBAG4AZABCAGEAaQB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQBGAGUAZQBkAEEAbgBkAEIAYQBpAHQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADkALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAZQBnAG8AcgB5AFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdAAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAXAAiACwAIABcACIARQBtAGIAZQBkAGQAZQBkACAARQBtAGkAcwBzAGkAbwBuAHMAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAASQBuAHQAZQBuAHMAaQB0AHkAIABVAG4AaQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAgAEYAZQBlAGQAIABhAG4AZAAgAEIAYQBpAHQAXAAiACwAIABcACIATABvAHcAIABBAG4AaQBtAGEAbAAgAFAAcgBvAHQAZQBpAG4AIABGAG8AcgBtAHUAbABhAHQAZQBkACAARgBlAGUAZABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADcAMAAxADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAgAEYAZQBlAGQAIABhAG4AZAAgAEIAYQBpAHQAXAAiACwAIABcACIASABpAGcAaAAgAEEAbgBpAG0AYQBsACAAUAByAG8AdABlAGkAbgAgAEYAbwByAG0AdQBsAGEAdABlAGQAIABGAGUAZQBkAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANwAwADEAMAAyACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlACAARgBlAGUAZAAgAGEAbgBkACAAQgBhAGkAdABcACIALAAgAFwAIgBDAGUAcgBlAGEAbAAgAGcAcgBhAGkAbgBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADcAMAAxADAAMwAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAgAEYAZQBlAGQAIABhAG4AZAAgAEIAYQBpAHQAXAAiACwAIABcACIAUwBxAHUAaQBkAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANwAwADEAMAA0ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlACAARgBlAGUAZAAgAGEAbgBkACAAQgBhAGkAdABcACIALAAgAFwAIgBXAGgAbwBsAGUAIABGAGkAcwBoAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADAANwAwADEAMAA1ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBxAHUAYQBjAHUAbAB0AHUAcgBlACAARgBlAGUAZAAgAGEAbgBkACAAQgBhAGkAdABcACIALAAgAFwAIgBXAGgAbwBsAGUAIABTAGEAcgBkAGkAbgBlAHMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMAA3ADAAMQAwADYALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAHEAdQBhAGMAdQBsAHQAdQByAGUAIABGAGUAZQBkACAAYQBuAGQAIABCAGEAaQB0AFwAIgAsACAAXAAiAEYAaQBzAGgAIABGAHIAYQBtAGUAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADcAMAAxADAANwAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAcQB1AGEAYwB1AGwAdAB1AHIAZQAgAEYAZQBlAGQAIABhAG4AZAAgAEIAYQBpAHQAXAAiACwAIABcACIARgBpAHMAaAAgAEgAZQBhAGQAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAwADcAMAAxADAAOAAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBMAGkAdgBlAHMAdABvAGMAawBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUwBjAG8AcABlADMAXwBMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEwAaQB2AGUAcwB0AG8AYwBrACAAcwBjAG8AcABlACAAMwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBTAGMAbwBwAGUAIAAzACAARwBIAEcAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5ACAAMgAwADIANgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAA3ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AGUAZwBvAHIAeQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEUAbQBiAGUAZABkAGUAZAAgAEUAbQBpAHMAcwBpAG8AbgBzACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAEkAbgB0AGUAbgBzAGkAdAB5ACAAVQBuAGkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAdgBlAHMAdABvAGMAawBcACIALAAgAFwAIgBCAGUAZQBmACAAYwBhAHQAdABsAGUAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIAdAAgAEwAVwBcACIALAAgADAAOAAwADEAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAIABMAFcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATABpAHYAZQBzAHQAbwBjAGsAXAAiACwAIABcACIAQgBlAGUAZgAgAGMAYQB0AHQAbABlAFwAIgAsACAAXAAiAFMAbwB1AHQAaABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAHQAIABMAFcAXAAiACwAIAAwADgAMAAxADAAMgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATABXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQB2AGUAcwB0AG8AYwBrAFwAIgAsACAAXAAiAEIAZQBlAGYAIABjAGEAdAB0AGwAZQBcACIALAAgAFwAIgBEAGEAaQByAHkAIABPAHIAaQBnAGkAbgBcACIALAAgAFwAIgB0ACAATABXAFwAIgAsACAAMAA4ADAAMQAwADIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEwAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAdgBlAHMAdABvAGMAawBcACIALAAgAFwAIgBEAGEAaQByAHkAIABjAGEAdAB0AGwAZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAIABMAFcAXAAiACwAIAAwADgAMAAxADAAMwAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATABXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQB2AGUAcwB0AG8AYwBrAFwAIgAsACAAXAAiAFMAaABlAGUAcABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAIABMAFcAXAAiACwAIAAwADgAMAAxADAANAAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0ACAATABXAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEwAaQB2AGUAcwB0AG8AYwBrAFwAIgAsACAAXAAiAFAAaQBnAHMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0ACAATABXAFwAIgAsACAAMAA4ADAAMQAwADUALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEwAVwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAdgBlAHMAdABvAGMAawBcACIALAAgAFwAIgBDAGgAaQBjAGsAZQBuAHMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0ACAATABXAFwAIgAsACAAMAA4ADAAMQAwADYALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdAAgAEwAVwBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUABhAGMAawBhAGcAaQBuAGcAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AUABhAGMAawBhAGcAaQBuAGcAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBQAGEAYwBrAGEAZwBpAG4AZwAgAHMAYwBvAHAAZQAgADMAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBQAGEAYwBrAGEAZwBpAG4AZwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAUwBjAG8AcABlACAAMwAgAEcASABHACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAgADIAMAAyADYAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBQAGEAYwBrAGEAZwBpAG4AZwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBQAGEAYwBrAGEAZwBpAG4AZwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAdABlAGcAbwByAHkAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBcACIALAAgAFwAIgBFAG0AYgBlAGQAZABlAGQAIABFAG0AaQBzAHMAaQBvAG4AcwAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABJAG4AdABlAG4AcwBpAHQAeQAgAFUAbgBpAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABhAGMAawBhAGcAaQBuAGcAXAAiACwAIABcACIAVwBpAG4AZQAgAGIAbwB0AHQAbABlAHMAOgAgAEcAbABhAHMAcwAgAC0AIABjAG8AbgB2AGUAbgB0AGkAbwBuAGEAbABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGIAbwB0AHQAbABlAFwAIgAsACAAMAA5ADAAMQAwADEALAAgAFwAIgBiAG8AdAB0AGwAZQBcACIALAAgAFwAIgBrAGcAIABDAE8AMgAtAGUAIAAvACAAYgBvAHQAdABsAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABhAGMAawBhAGcAaQBuAGcAXAAiACwAIABcACIAVwBpAG4AZQAgAGIAbwB0AHQAbABlAHMAOgAgAEcAbABhAHMAcwAgAC0AIABsAGkAZwBoAHQAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBiAG8AdAB0AGwAZQBcACIALAAgADAAOQAwADEAMAAyACwAIABcACIAYgBvAHQAdABsAGUAXAAiACwAIABcACIAawBnACAAQwBPADIALQBlACAALwAgAGIAbwB0AHQAbABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAYQBjAGsAYQBnAGkAbgBnAFwAIgAsACAAXAAiAFAAbABhAHMAdABpAGMAIABwAGEAYwBrAGEAZwBpAG4AZwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAZwBcACIALAAgADAAOQAwADIAMAAxACwAIABcACIAawBnAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAC0AZQAgAC8AIABrAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABhAGMAawBhAGcAaQBuAGcAXAAiACwAIABcACIAUABvAGwAeQBlAHQAaAB5AGwAZQBuAGUAIAB0AGUAcgBlAHAAaAB0AGgAYQBsAGEAdABlACAAKABQAEUAVAApAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBnAFwAIgAsACAAMAA5ADAAMgAwADIALAAgAFwAIgBrAGcAXAAiACwAIABcACIAawBnACAAQwBPADIALQBlACAALwAgAGsAZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAGEAYwBrAGEAZwBpAG4AZwBcACIALAAgAFwAIgBQAG8AbAB5AHAAcgBvAHAAeQBsAGUAbgBlACAAKABQAFAAKQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAZwBcACIALAAgADAAOQAwADIAMAAzACwAIABcACIAawBnAFwAIgAsACAAXAAiAGsAZwAgAEMATwAyAC0AZQAgAC8AIABrAGcAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABhAGMAawBhAGcAaQBuAGcAXAAiACwAIABcACIAQwBhAHIAZABiAG8AYQByAGQAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGcAXAAiACwAIAAwADkAMAAyADAANAAsACAAXAAiAGsAZwBcACIALAAgAFwAIgBrAGcAIABDAE8AMgAtAGUAIAAvACAAawBnAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBTAGUAZQBkAHMAIABhAG4AZAAgAFMAZQBlAGQAbABpAG4AZwBzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBTAGMAbwBwAGUAMwBfAFMAZQBlAGQAcwBBAG4AZABTAGUAZQBkAGwAaQBuAGcAcwBfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAZQBlAGQAcwAgAGEAbgBkACAAUwBlAGUAZABsAGkAbgBnAHMAIABzAGMAbwBwAGUAIAAzAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AUwBlAGUAZABzAEEAbgBkAFMAZQBlAGQAbABpAG4AZwBzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBTAGMAbwBwAGUAIAAzACAARwBIAEcAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5ACAAMgAwADIANgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAFMAZQBlAGQAcwBBAG4AZABTAGUAZQBkAGwAaQBuAGcAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBTAGUAZQBkAHMAQQBuAGQAUwBlAGUAZABsAGkAbgBnAHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAZQBnAG8AcgB5AFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdAAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAXAAiACwAIABcACIARQBtAGIAZQBkAGQAZQBkACAARQBtAGkAcwBzAGkAbwBuAHMAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAASQBuAHQAZQBuAHMAaQB0AHkAIABVAG4AaQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBlAGQAcwAgAGEAbgBkACAAUwBlAGUAZABsAGkAbgBnAHMAXAAiACAALABcACIAUwBlAGUAZAAgACgAZwBlAG4AZQByAGEAbAAgAGMAcgBvAHAAIABhAG4AZAAgAHAAYQBzAHQAdQByAGUAKQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAxADAAMAAxADAAMQAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBlAGQAcwAgAGEAbgBkACAAUwBlAGUAZABsAGkAbgBnAHMAXAAiACAALABcACIAUwBlAGUAZABsAGkAbgBnAHMAIAAoAGYAbwByAGUAcwB0AHIAeQAsACAAaABvAHIAdABpAGMAdQBsAHQAdQByAGUALAAgAGUAbgB2AGkAcgBvAG4AbQBlAG4AdABhAGwAKQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFMAZQBlAGQAbABpAG4AZwBcACIALAAgADEAMAAwADEAMAAyACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAFMAZQBlAGQAbABpAG4AZwBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AQwBsAGUAYQBuAGkAbgBnACAAYwBoAGUAbQBpAGMAYQBsAHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AQwBsAGUAYQBuAGkAbgBnAEMAaABlAG0AaQBjAGEAbABzAF8AVABpAHQAbABlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQwBsAGUAYQBuAGkAbgBnACAAYwBoAGUAbQBpAGMAYQBsAHMAIABzAGMAbwBwAGUAIAAzAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8AQwBsAGUAYQBuAGkAbgBnAEMAaABlAG0AaQBjAGEAbABzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBTAGMAbwBwAGUAIAAzACAARwBIAEcAIABFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBzACAAZgBvAHIAIABBAHUAcwB0AHIAYQBsAGkAYQBuACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBlACwAIABGAGkAcwBoAGUAcgBpAGUAcwAgAGEAbgBkACAARgBvAHIAZQBzAHQAcgB5ACAAMgAwADIANgBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEMAbABlAGEAbgBpAG4AZwBDAGgAZQBtAGkAYwBhAGwAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBDAGwAZQBhAG4AaQBuAGcAQwBoAGUAbQBpAGMAYQBsAHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADcALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBhAHQAZQBnAG8AcgB5AFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIAUwBvAHUAcgBjAGUAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdAAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAXAAiACwAIABcACIARQBtAGIAZQBkAGQAZQBkACAARQBtAGkAcwBzAGkAbwBuAHMAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAASQBuAHQAZQBuAHMAaQB0AHkAIABVAG4AaQB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbABlAGEAbgBpAG4AZwAgAGMAaABlAG0AaQBjAGEAbABzAFwAIgAsACAAXAAiAEQAZQB0AGUAcgBnAGUAbgB0AFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADEAMQAwADEAMAAxACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQwBsAGUAYQBuAGkAbgBnACAAYwBoAGUAbQBpAGMAYQBsAHMAXAAiACwAIABcACIAQQBjAGkAZABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAxADEAMAAxADAAMgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAbABlAGEAbgBpAG4AZwAgAGMAaABlAG0AaQBjAGEAbABzAFwAIgAsACAAXAAiAEIAbABlAGEAYwBoAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIATABcACIALAAgADEAMQAwADEAMAAzACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAEwAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ATwB0AGgAZQByACAAYQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIABpAG4AcAB1AHQAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUwBjAG8AcABlADMAXwBPAHQAaABlAHIAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwASQBuAHAAdQB0AHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBPAHQAaABlAHIAIABhAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAGkAbgBwAHUAdABzACAAcwBjAG8AcABlACAAMwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAE8AdABoAGUAcgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABJAG4AcAB1AHQAcwBfAFMAbwB1AHIAYwBlAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAUwBjAG8AcABlACAAMwAgAEcASABHACAARQBtAGkAcwBzAGkAbwBuACAARgBhAGMAdABvAHIAcwAgAGYAbwByACAAQQB1AHMAdAByAGEAbABpAGEAbgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAZQAsACAARgBpAHMAaABlAHIAaQBlAHMAIABhAG4AZAAgAEYAbwByAGUAcwB0AHIAeQAgADIAMAAyADYAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBPAHQAaABlAHIAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwASQBuAHAAdQB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ATwB0AGgAZQByAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAEkAbgBwAHUAdABzAF8ARABhAHQAYQBcAG4APQBMAEEATQBCAEQAQQAoAFwAbgAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAA3ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AGUAZwBvAHIAeQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEUAbQBiAGUAZABkAGUAZAAgAEUAbQBpAHMAcwBpAG8AbgBzACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAEkAbgB0AGUAbgBzAGkAdAB5ACAAVQBuAGkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABBAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAEkAbgBwAHUAdABzAFwAIgAsACAAXAAiAEMATwAyACAAZgBvAHIAIABjAGEAcgBiAG8AbgBhAHQAaQBvAG4AXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMQAyADAAMQAwADEALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABBAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAEkAbgBwAHUAdABzAFwAIgAsACAAXAAiAEwAaQB2AGUAcwB0AG8AYwBrACAAYQBuAHQAaQBiAGkAbwB0AGkAYwBzAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADEAMQAwADEAMAAyACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIABJAG4AcAB1AHQAcwBcACIALAAgAFwAIgBOAHkAbABvAG4AIABuAGUAdAB0AGkAbgBnACAAZgBvAHIAIABoAG8AcgB0AGkAYwB1AGwAdAB1AHIAZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAxADEAMAAxADAAMwAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE8AdABoAGUAcgAgAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAASQBuAHAAdQB0AHMAXAAiACwAIABcACIAUABhAGwAbABlAHQAcwAgAC0AIABXAG8AbwBkAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgADEAMQAwADEAMAA0ACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATwB0AGgAZQByACAAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIABJAG4AcAB1AHQAcwBcACIALAAgAFwAIgBQAGEAbABsAGUAdABzACAALQAgAFAAbABhAHMAdABpAGMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAMQAxADAAMQAwADUALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBPAHQAaABlAHIAIABBAGcAcgBpAGMAdQBsAHQAdQByAGEAbAAgAEkAbgBwAHUAdABzAFwAIgAsACAAXAAiAEwAaQB2AGUAcwB0AG8AYwBrACAAdABhAGcAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIAAxADEAMAAxADAANgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIAB0AFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAAcwBjAG8AcABlACAAMwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAVAByAGEAbgBzAHAAbwByAHQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAYwBvAHAAZQAgADMAIABHAEgARwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkAIAAyADAAMgA2AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ARgB1AGUAbABUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIAB2AGEAbAB1AGUAcwAgAHMAbwB1AHIAYwBlAGQAIABmAHIAbwBtACAATgBhAHQAaQBvAG4AYQBsACAARwByAGUAZQBuAGgAbwB1AHMAZQAgAEEAYwBjAG8AdQBuAHQAcwAgAEYAYQBjAHQAbwByAHMAIAAtACAAUwBlAGUAIAByAGUAbABlAHYAYQBuAHQAIAB0AGEAYgBsAGUAIABpAG4AIABcAHUAMAAwADIANwBGAHUAZQBsACAAUwBvAHUAcgBjAGUAIABEAGEAdABhAFwAdQAwADAAMgA3AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ARgB1AGUAbABUAHIAYQBuAHMAcABvAHIAdABfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAyACwAIAA3ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AGUAZwBvAHIAeQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEUAbQBiAGUAZABkAGUAZAAgAEUAbQBpAHMAcwBpAG8AbgBzACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAEkAbgB0AGUAbgBzAGkAdAB5ACAAVQBuAGkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIARwBhAHMAbwBsAGkAbgBlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABwAGUAdAByAG8AbABlAHUAbQAgAGcAYQBzACAAKABMAFAARwApAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEYAdQBlAGwAIABvAGkAbABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAawBsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAIAAtACAAQwBhAHIAcwAgAGEAbgBkACAAbABpAGcAaAB0ACAAYwBvAG0AbQBlAHIAYwBpAGEAbAAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBFAHQAaABhAG4AbwBsAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEIAaQBvAGQAaQBlAHMAZQBsAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABDAGEAcgBzACAAYQBuAGQAIABsAGkAZwBoAHQAIABjAG8AbQBtAGUAcgBjAGkAYQBsACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEMAYQByAHMAIABhAG4AZAAgAGwAaQBnAGgAdAAgAGMAbwBtAG0AZQByAGMAaQBhAGwAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATwB0AGgAZQByACAAYgBpAG8AZgB1AGUAbABzAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABMAGkAZwBoAHQAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAEMAbwBtAHAAcgBlAHMAcwBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBtADMAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAG0AMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEwAaQBnAGgAdAAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABuAGEAdAB1AHIAYQBsACAAZwBhAHMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEgAZQBhAHYAeQAgAGQAdQB0AHkAIAB2AGUAaABpAGMAbABlAHMAXAAiACwAIABcACIAQwBvAG0AcAByAGUAcwBzAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAG0AMwBcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAbQAzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAIAAtACAASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBMAGkAcQB1AGUAZgBpAGUAZAAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAawBsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAIAAtACAASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAHYAIABvAHIAIABoAGkAZwBoAGUAcgBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAawBsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAIAAtACAASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAGkAaQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAawBsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAIAAtACAASABlAGEAdgB5ACAAZAB1AHQAeQAgAHYAZQBoAGkAYwBsAGUAcwBcACIALAAgAFwAIgBEAGkAZQBzAGUAbAAgAG8AaQBsACAALQAgAEUAdQByAG8AIABpAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAIAAtACAARQB1AHIAbwAgAGkAdgAgAG8AcgAgAGgAaQBnAGgAZQByAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAIAAtACAARQB1AHIAbwAgAGkAaQBpAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABIAGUAYQB2AHkAIABkAHUAdAB5ACAAdgBlAGgAaQBjAGwAZQBzAFwAIgAsACAAXAAiAFIAZQBuAGUAdwBhAGIAbABlACAAZABpAGUAcwBlAGwAIAAtACAARQB1AHIAbwAgAGkAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFQAcgBhAG4AcwBwAG8AcgB0ACAALQAgAEEAdgBpAGEAdABpAG8AbgBcACIALAAgAFwAIgBHAGEAcwBvAGwAaQBuAGUAIABmAG8AcgAgAHUAcwBlACAAYQBzACAAZgB1AGUAbAAgAGkAbgAgAGEAbgAgAGEAaQByAGMAcgBhAGYAdABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAtAGUAIAAvACAAawBsAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAVAByAGEAbgBzAHAAbwByAHQAIAAtACAAQQB2AGkAYQB0AGkAbwBuAFwAIgAsACAAXAAiAEsAZQByAG8AcwBlAG4AZQAgAGYAbwByACAAdQBzAGUAIABhAHMAIABmAHUAZQBsACAAaQBuACAAYQBuACAAYQBpAHIAYwByAGEAZgB0AFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyAC0AZQAgAC8AIABrAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABUAHIAYQBuAHMAcABvAHIAdAAgAC0AIABBAHYAaQBhAHQAaQBvAG4AXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIALQBlACAALwAgAGsAbABcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZAAgAHMAYwBvAHAAZQAgADMAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAYwBvAHAAZQAgADMAIABHAEgARwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkAIAAyADAAMgA2AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ARgB1AGUAbABTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHYAYQBsAHUAZQBzACAAcwBvAHUAcgBjAGUAZAAgAGYAcgBvAG0AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgAC0AIABTAGUAZQAgAHIAZQBsAGUAdgBhAG4AdAAgAHQAYQBiAGwAZQAgAGkAbgAgAFwAdQAwADAAMgA3AEYAdQBlAGwAIABTAG8AdQByAGMAZQAgAEQAYQB0AGEAXAB1ADAAMAAyADcAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIANQAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAdABlAGcAbwByAHkAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBcACIALAAgAFwAIgBFAG0AYgBlAGQAZABlAGQAIABFAG0AaQBzAHMAaQBvAG4AcwAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABJAG4AdABlAG4AcwBpAHQAeQAgAFUAbgBpAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAIgAsACAAXAAiAFAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAbwBpAGwAcwAgACgAbwB0AGgAZQByACAAdABoAGEAbgAgAHAAZQB0AHIAbwBsAGUAdQBtACAAYgBhAHMAZQBkACAAbwBpAGwAIAB1AHMAZQBkACAAYQBzACAAZgB1AGUAbAApACwAIABlAC4AZwAuACAAbAB1AGIAcgBpAGMAYQBuAHQAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgAgAHQAIABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABnAHIAZQBhAHMAZQBzAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAawBsACAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAIgAsACAAXAAiAEMAcgB1AGQAZQAgAG8AaQBsACAAaQBuAGMAbAB1AGQAaQBuAGcAIABjAHIAdQBkAGUAIABvAGkAbAAgAGMAbwBuAGQAZQBuAHMAYQB0AGUAcwBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIAB0ACAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAIgAsACAAXAAiAE8AdABoAGUAcgAgAG4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAdAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBBAHUAdABvAG0AbwB0AGkAdgBlACAAZwBhAHMAbwBsAGkAbgBlACAALwAgAHAAZQB0AHIAbwBsACAAKABvAHQAaABlAHIAIAB0AGgAYQBuACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGYAdQBlAGwAIABpAG4AIABhAG4AIABhAGkAcgBjAHIAYQBmAHQAKQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIABnAGEAcwBvAGwAaQBuAGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIASwBlAHIAbwBzAGUAbgBlACAAKABvAHQAaABlAHIAIAB0AGgAYQBuACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGYAdQBlAGwAIABpAG4AIABhAG4AIABhAGkAcgBjAHIAYQBmAHQAKQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBBAHYAaQBhAHQAaQBvAG4AIAB0AHUAcgBiAGkAbgBlACAAZgB1AGUAbAAgAC8AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIASABlAGEAdABpAG4AZwAgAG8AaQBsAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAawBsACAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAIgAsACAAXAAiAEQAaQBlAHMAZQBsACAAbwBpAGwAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIARgB1AGUAbAAgAG8AaQBsAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAawBsACAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAIgAsACAAXAAiAEwAaQBxAHUAZQBmAGkAZQBkACAAYQByAG8AbQBhAHQAaQBjACAAaAB5AGQAcgBvAGMAYQByAGIAbwBuAHMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIAUwBvAGwAdgBlAG4AdABzADoAIABtAGkAbgBlAHIAYQBsACAAdAB1AHIAcABlAG4AdABpAG4AZQAgAG8AcgAgAHcAaABpAHQAZQAgAHMAcABpAHIAaQB0AHMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIATABpAHEAdQBlAGYAaQBlAGQAIABwAGUAdAByAG8AbABlAHUAbQAgAGcAYQBzACAAKABMAFAARwApAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAawBsACAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAIgAsACAAXAAiAE4AYQBwAGgAdABoAGEAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABjAG8AawBlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAHQAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIAUgBlAGYAaQBuAGUAcgB5ACAAZwBhAHMAIABhAG4AZAAgAGwAaQBxAHUAaQBkAHMAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAdAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBSAGUAZgBpAG4AZQByAHkAIABjAG8AawBlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAdABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAHQAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIAUABlAHQAcgBvAGwAZQB1AG0AIABiAGEAcwBlAGQAIABwAHIAbwBkAHUAYwB0AHMAIABvAHQAaABlAHIAIAB0AGgAYQBuACAAbQBlAG4AdABpAG8AbgBlAGQAIABpAG4AIAB0AGgAZQAgAGkAdABlAG0AcwAgAGEAYgBvAHYAZQBcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBCAGkAbwBkAGkAZQBzAGUAbABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABMAGkAcQB1AGkAZABcACIALAAgAFwAIgBFAHQAaABhAG4AbwBsACAAZgBvAHIAIAB1AHMAZQAgAGEAcwAgAGEAIABmAHUAZQBsACAAaQBuACAAYQBuACAAaQBuAHQAZQByAG4AYQBsACAAYwBvAG0AYgB1AHMAdABpAG8AbgAgAGUAbgBnAGkAbgBlAFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAawBsAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAAawBsACAAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEwAaQBxAHUAaQBkAFwAIgAsACAAXAAiAEIAaQBvAGYAdQBlAGwAcwAgAG8AdABoAGUAcgAgAHQAaABhAG4AIAB0AGgAbwBzAGUAIABtAGUAbgB0AGkAbwBuAGUAZAAgAGkAbgAgAHQAaABlACAAaQB0AGUAbQBzACAAYQBiAG8AdgBlACAAYQBuAGQAIABiAGUAbABvAHcAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABhAHYAaQBhAHQAaQBvAG4AIABrAGUAcgBvAHMAZQBuAGUAXAAiACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBrAGwAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABrAGwAIABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAATABpAHEAdQBpAGQAXAAiACwAIABcACIAUgBlAG4AZQB3AGEAYgBsAGUAIABkAGkAZQBzAGUAbABcACIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAGsAbABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAGsAbAAgAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAARwBhAHMAZQBvAHUAcwBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAARwBhAHMAZQBvAHUAcwAgAHMAYwBvAHAAZQAgADMAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAYwBvAHAAZQAgADMAIABHAEgARwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkAIAAyADAAMgA2AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ARgB1AGUAbABTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHYAYQBsAHUAZQBzACAAcwBvAHUAcgBjAGUAZAAgAGYAcgBvAG0AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgAC0AIABTAGUAZQAgAHIAZQBsAGUAdgBhAG4AdAAgAHQAYQBiAGwAZQAgAGkAbgAgAFwAdQAwADAAMgA3AEYAdQBlAGwAIABTAG8AdQByAGMAZQAgAEQAYQB0AGEAXAB1ADAAMAAyADcAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANwAsACAANwAsAFwAbgAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBDAGEAdABlAGcAbwByAHkAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBTAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABGAGEAYwB0AG8AcgBcACIALAAgAFwAIgBFAG0AYgBlAGQAZABlAGQAIABFAG0AaQBzAHMAaQBvAG4AcwAgAFUAbgBpAHQAXAAiACwAIABcACIARQBtAGkAcwBzAGkAbwBuAHMAIABJAG4AdABlAG4AcwBpAHQAeQAgAFUAbgBpAHQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEcAYQBzAGUAbwB1AHMAXAAiACwAIABcACIATgBhAHQAdQByAGEAbAAgAGcAYQBzACAAZABpAHMAdAByAGkAYgB1AHQAZQBkACAAaQBuACAAYQAgAHAAaQBwAGUAbABpAG4AZQAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAXAAiAE4AZQB3ACAAUwBvAHUAdABoACAAVwBhAGwAZQBzAFwAIgAsACAAXAAiAEcAagBcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAARwBhAHMAZQBvAHUAcwBcACIALAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIABcACIAQQBDAFQAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAIgAsACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAIgAsACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgAFwAIgBRAHUAZQBlAG4AcwBsAGEAbgBkAFwAIgAsACAAXAAiAEcAagBcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAARwBhAHMAZQBvAHUAcwBcACIALAAgAFwAIgBOAGEAdAB1AHIAYQBsACAAZwBhAHMAIABkAGkAcwB0AHIAaQBiAHUAdABlAGQAIABpAG4AIABhACAAcABpAHAAZQBsAGkAbgBlACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIABcACIAUwBvAHUAdABoACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAIgAsACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAIgAsACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgAFwAIgBUAGEAcwBtAGEAbgBpAGEAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAIgAsACAAXAAiAE4AYQB0AHUAcgBhAGwAIABnAGEAcwAgAGQAaQBzAHQAcgBpAGIAdQB0AGUAZAAgAGkAbgAgAGEAIABwAGkAcABlAGwAaQBuAGUAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQBcACIALAAgAFwAIgBHAGoAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEcAYQBzAGUAbwB1AHMAXAAiACwAIABcACIAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIABcACIATgBlAHcAIABTAG8AdQB0AGgAIABXAGEAbABlAHMAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAIgAsACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAEcAagBcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAARwBhAHMAZQBvAHUAcwBcACIALAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAIgAsACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAXAAiAFEAdQBlAGUAbgBzAGwAYQBuAGQAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAIgAsACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAXAAiAFMAbwB1AHQAaAAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgAsACAAXAAiAEcAagBcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBGAHUAZQBsACAALQAgAFMAdABhAHQAaQBvAG4AYQByAHkAIAAtACAARwBhAHMAZQBvAHUAcwBcACIALAAgAFwAIgBUAG8AdwBuACAAZwBhAHMAIAAtACAARwBpAGcAYQBqAG8AdQBsAGUAcwBcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEYAdQBlAGwAIAAtACAAUwB0AGEAdABpAG8AbgBhAHIAeQAgAC0AIABHAGEAcwBlAG8AdQBzAFwAIgAsACAAXAAiAFQAbwB3AG4AIABnAGEAcwAgAC0AIABHAGkAZwBhAGoAbwB1AGwAZQBzAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBHAGoAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgB1AGUAbAAgAC0AIABTAHQAYQB0AGkAbwBuAGEAcgB5ACAALQAgAEcAYQBzAGUAbwB1AHMAXAAiACwAIABcACIAVABvAHcAbgAgAGcAYQBzACAALQAgAEcAaQBnAGEAagBvAHUAbABlAHMAXAAiACwAIABcACIATgBvAHIAdABoAGUAcgBuACAAVABlAHIAcgBpAHQAbwByAHkAXAAiACwAIABcACIARwBqAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgBcAG4AIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgApACkAKQA7AFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAtACAAUwB0AGEAdABlACAARwByAGkAZABcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AUwBjAG8AcABlADMAXwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAIAAtACAAUwB0AGEAdABlACAARwByAGkAZAAgAHMAYwBvAHAAZQAgADMAXAAiACkAKQA7AFwAbgBcAG4AUwBjAG8AcABlADMAXwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFMAYwBvAHAAZQAgADMAIABHAEgARwAgAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAHMAIABmAG8AcgAgAEEAdQBzAHQAcgBhAGwAaQBhAG4AIABBAGcAcgBpAGMAdQBsAHQAdQByAGUALAAgAEYAaQBzAGgAZQByAGkAZQBzACAAYQBuAGQAIABGAG8AcgBlAHMAdAByAHkAIAAyADAAMgA2AFwAIgApACkAOwBcAG4AXABuAFMAYwBvAHAAZQAzAF8ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAHYAYQBsAHUAZQBzACAAcwBvAHUAcgBjAGUAZAAgAGYAcgBvAG0AIABOAGEAdABpAG8AbgBhAGwAIABHAHIAZQBlAG4AaABvAHUAcwBlACAAQQBjAGMAbwB1AG4AdABzACAARgBhAGMAdABvAHIAcwAgAC0AIABTAGUAZQAgAHIAZQBsAGUAdgBhAG4AdAAgAHQAYQBiAGwAZQAgAGkAbgAgAFwAdQAwADAAMgA3AEUAbABlAGMAdAByAGkAYwBpAHQAeQAgAFMAbwB1AHIAYwBlACAARABhAHQAYQBcAHUAMAAwADIANwBcACIAKQApADsAXABuAFwAbgBTAGMAbwBwAGUAMwBfAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAxACwAIAA3ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQB0AGUAZwBvAHIAeQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0AFwAIgAsACAAXAAiAFMAbwB1AHIAYwBlAFwAIgAsACAAXAAiAFAAcgBvAGQAdQBjAHQAIABVAG4AaQB0AFwAIgAsACAAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAEYAYQBjAHQAbwByAFwAIgAsACAAXAAiAEUAbQBiAGUAZABkAGUAZAAgAEUAbQBpAHMAcwBpAG8AbgBzACAAVQBuAGkAdABcACIALAAgAFwAIgBFAG0AaQBzAHMAaQBvAG4AcwAgAEkAbgB0AGUAbgBzAGkAdAB5ACAAVQBuAGkAdABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAUwB0AGEAdABlACAARwByAGkAZABcACIALAAgAFwAIgBOAGUAdwAgAFMAbwB1AHQAaAAgAFcAYQBsAGUAcwBcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAUwB0AGEAdABlACAARwByAGkAZABcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAUwB0AGEAdABlACAARwByAGkAZABcACIALAAgAFwAIgBWAGkAYwB0AG8AcgBpAGEAXAAiACwAIABcACIAawBXAGgAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAFMAdABhAHQAZQAgAEcAcgBpAGQAXAAiACwAIABcACIAUQB1AGUAZQBuAHMAbABhAG4AZABcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAUwB0AGEAdABlACAARwByAGkAZABcACIALAAgAFwAIgBTAG8AdQB0AGgAIABBAHUAcwB0AHIAYQBsAGkAYQBcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAUwB0AGEAdABlACAARwByAGkAZABcACIALAAgAFwAIgBXAGUAcwB0AGUAcgBuACAAQQB1AHMAdAByAGEAbABpAGEAIAAtACAAUwBvAHUAdABoACAAVwBlAHMAdAAgAEkAbgB0AGUAcgBjAG8AbgBuAGUAYwB0AGUAZAAgAFMAeQBzAHQAZQBtACAAKABTAFcASQBTACkAXAAiACwAIABcACIAawBXAGgAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AFwAIgAsACAAXAAiAFMAdABhAHQAZQAgAEcAcgBpAGQAXAAiACwAIABcACIAVwBlAHMAdABlAHIAbgAgAEEAdQBzAHQAcgBhAGwAaQBhACAALQAgAE4AbwByAHQAaAAgAFcAZQBzAHQAZQByAG4AIABJAG4AdABlAHIAYwBvAG4AbgBlAGMAdABlAGQAIABTAHkAcwB0AGUAbQAgACgATgBXAEkAUwApAFwAIgAsACAAXAAiAGsAVwBoAFwAIgAsACAAXAAiAFgAWABYAFgAWABYAFwAIgAsACAAXAAiAHQAXAAiACwAIABcACIAdAAgAEMATwAyACAALQAgAGUAIAAvACAARwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBcACIALAAgAFwAIgBTAHQAYQB0AGUAIABHAHIAaQBkAFwAIgAsACAAXAAiAFQAYQBzAG0AYQBuAGkAYQBcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAUwB0AGEAdABlACAARwByAGkAZABcACIALAAgAFwAIgBOAG8AcgB0AGgAZQByAG4AIABUAGUAcgByAGkAdABvAHIAeQAgAC0AIABEAGEAcgB3AGkAbgAgAEsAYQB0AGgAZQByAGkAbgBlACAASQBuAHQAZQByAGMAbwBuAG4AZQBjAHQAZQBkACAAUwB5AHMAdABlAG0AIAAoAEQASwBJAFMAKQBcACIALAAgAFwAIgBrAFcAaABcACIALAAgAFwAIgBYAFgAWABYAFgAWABcACIALAAgAFwAIgB0AFwAIgAsACAAXAAiAHQAIABDAE8AMgAgAC0AIABlACAALwAgAEcAagBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXAAiACwAIABcACIAUwB0AGEAdABlACAARwByAGkAZABcACIALAAgAFwAIgBOAGEAdABpAG8AbgBhAGwAXAAiACwAIABcACIAawBXAGgAXAAiACwAIABcACIAWABYAFgAWABYAFgAXAAiACwAIABcACIAdABcACIALAAgAFwAIgB0ACAAQwBPADIAIAAtACAAZQAgAC8AIABHAGoAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgAgAGMAaABlAG0AaQBjAGEAbAAgAGMAbwBtAHAAbwB1AG4AZABzAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8AQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAGUAcgB0AGkAbABpAHMAZQByACAAYwBoAGUAbQBpAGMAYQBsACAAYwBvAG0AcABvAHUAbgBkAHMAXAAiACkAKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQARQBsAGUAbQBlAG4AdABzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuAFwAbgA9AEwAQQBNAEIARABBACgAKABcACIAQwBoAGUAbQBpAGMAYQBsACAAYwBvAG0AcABvAHUAbgBkAHMAIAB1AHMAZQBkACAAaQBuACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzACwAIABhAGwAbwBuAGcAIAB3AGkAdABoACAAdABoAGUAaQByACAAZQBsAGUAbQBlAG4AdABhAGwAIABjAG8AbQBwAG8AcwBpAHQAaQBvAG4AXAAiACkAKQA7AFwAbgBcAG4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQARQBsAGUAbQBlAG4AdABzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEUAbABlAG0AZQBuAHQAcwBfAEQAYQB0AGEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMgAwACwAIAA3ACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAaABlAG0AaQBjAGEAbAAgAGMAbwBtAHAAbwB1AG4AZABcACIALAAgAFwAIgBOAFwAIgAsACAAXAAiAFAAXAAiACwAIABcACIASwBcACIALAAgAFwAIgBTAFwAIgAsACAAXAAiAFUAcgBlAGEAXAAiACwAIABcACIAQgBhAHMAaQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbQBtAG8AbgBpAGEAXAAiACwAIAA4ADIALAAgADAALAAgADAALAAgADAALAAgADAALAAgAFwAIgBBAG0AbQBvAG4AaQB1AG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQByAGUAYQBcACIALAAgADAALgA0ADYALAAgADAALAAgADAALAAgADAALAAgADEALAAgAFwAIgBVAHIAZQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AbwBuAG8AYQBtAG0AbwBuAGkAdQBtACAAcABoAG8AcwBwAGgAYQB0AGUAIAAoAE0AQQBQACkAXAAiACwAIAAwAC4AMQAxACwAIAAwAC4AMgAxADkALAAgADAALAAgADAALAAgADAALAAgAFwAIgBBAG0AbQBvAG4AaQB1AG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABpAGEAbQBtAG8AbgBpAHUAbQAgAFAAaABvAHMAcABoAGEAdABlACAAKABEAEEAUAApAFwAIgAsACAAMAAuADEAOAAsACAAMAAuADIALAAgADAALAAgADAALAAgADAALAAgAFwAIgBBAG0AbQBvAG4AaQB1AG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAVQByAGUAYQAtAEEAbQBtAG8AbgBpAHUAbQAgAE4AaQB0AHIAYQB0AGUAIAAoAFUAQQBOACkAXAAiACwAIAAwAC4AMwAyACwAIAAwACwAIAAwACwAIAAwACwAIAAwAC4AMwA1ACwAIABcACIAQQBtAG0AbwBuAGkAdQBtAC0AbgBpAHQAcgBhAHQAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAG0AbQBvAG4AaQB1AG0AIABOAGkAdAByAGEAdABlACAAKABBAE4AKQBcACIALAAgADAALgAzADUALAAgADAALAAgADAALAAgADAALAAgADAALAAgAFwAIgBBAG0AbQBvAG4AaQB1AG0ALQBuAGkAdAByAGEAdABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBsAGMAaQB1AG0AIABBAG0AbQBvAG4AaQB1AG0AIABOAGkAdAByAGEAdABlACAAKABDAEEATgApAFwAIgAsACAAMAAuADIANgA1ACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIAQQBtAG0AbwBuAGkAdQBtAC0AbgBpAHQAcgBhAHQAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAGkAbgBnAGwAZQAgAFMAdQBwAGUAcgBwAGgAbwBzAHAAaABhAHQAZQAgACgAUwBTAFAAKQBcACIALAAgADAALAAgADAALgAwADgAOAAsACAAMAAsACAAMAAuADEAMQAsACAAMAAsACAAXAAiAE8AdABoAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AdQBiAGwAZQAgAFMAdQBwAGUAcgBwAGgAbwBzAHAAaABhAHQAZQBcACIALAAgADAALAAgADAALgAwADgAOAAsACAAMAAsACAAMAAuADEAMQAsACAAMAAsACAAXAAiAE8AdABoAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAbABwAGgAYQB0AGUAIABvAGYAIABBAG0AbQBvAG4AaQBhACAAKABTAE8AQQApAFwAIgAsACAAMAAuADIAMQAsACAAMAAsACAAMAAsACAAMAAuADIANAAsACAAMAAsACAAXAAiAEEAbQBtAG8AbgBpAHUAbQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAHUAcgBpAGEAdABlACAAbwBmACAAUABvAHQAYQBzAGgAIAAoAE0ATwBQACAALwAgAEsAQwBMACkAXAAiACwAIAAwACwAIAAwACwAIAAwAC4ANgAsACAAMAAsACAAMAAsACAAXAAiAE8AdABoAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGkAdAByAG8AZwBlAG4AIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADEALAAgADAALAAgADAALAAgADAALAAgADAALAAgAFwAIgBOAGkAdAByAGEAdABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAC0AIABOAGkAdAByAGEAdABlAFwAIgAsACAAMAAuADIAMgA2ACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIATgBpAHQAcgBhAHQAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBOAGkAdAByAG8AZwBlAG4AIAAtACAAQQBtAG0AbwBuAGkAYQBjAGEAbABcACIALAAgADAALgA4ADIALAAgADAALAAgADAALAAgADAALAAgADAALAAgAFwAIgBBAG0AbQBvAG4AaQB1AG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUABoAG8AcwBwAGgAbwByAHUAcwAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAMAAsACAAMQAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAE8AdABoAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAG8AdABhAHMAcwBpAHUAbQAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAMAAsACAAMAAsACAAMQAsACAAMAAsACAAMAAsACAAXAAiAE8AdABoAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAbABmAHUAcgAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAMQAsACAAMAAsACAAXAAiAE8AdABoAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBaAGkAbgBjACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIATwB0AGgAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBsAGMAaQB1AG0AIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADAALAAgADAALAAgADAALAAgADAALAAgADAALAAgAFwAIgBPAHQAaABlAHIAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAIABwAHIAbwBkAHUAYwB0AHMAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBQAHIAbwBkAHUAYwB0AHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBGAGUAcgB0AGkAbABpAHMAZQByACAAcAByAG8AZAB1AGMAdABzAFwAIgApACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBQAHIAbwBkAHUAYwB0AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBQAG8AcAB1AGwAYQByACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAHAAcgBvAGQAdQBjAHQAcwAgAHUAcwBlAGQAIABpAG4AIABBAHUAcwB0AHIAYQBsAGkAYQAsACAAYQBsAG8AbgBnACAAdwBpAHQAaAAgAHQAaABlAGkAcgAgAGMAaABlAG0AaQBjAGEAbAAgAGMAbwBtAHAAbwB1AG4AZAAgAGMAbwBtAHAAbwBzAGkAdABpAG8AbgBcACIAKQApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUAByAG8AZAB1AGMAdABzAF8AUwBvAHUAcgBjAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBYAFgAWABYAFgAWABYAFwAIgApACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBQAHIAbwBkAHUAYwB0AHMAXwBEAGEAdABhADEAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAxACwAIAAyADAALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMQAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMgBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMgAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADIAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMwBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMwAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADMAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANAAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADQAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANQAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADUAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANgBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANgAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADYAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAaQBuAGYAbwAgAGwAaQBuAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIANwA1ACUAIABNAEEAUAAgADIANQAlACAATQBPAFAAXAAiACwAIABcACIATQBvAG4AbwBhAG0AbQBvAG4AaQB1AG0AIABwAGgAbwBzAHAAaABhAHQAZQAgACgATQBBAFAAKQBcACIALAAgADAALgA3ADUALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAE0AdQByAGkAYQB0AGUAIABvAGYAIABQAG8AdABhAHMAaAAgACgATQBPAFAAIAAvACAASwBDAEwAKQBcACIALAAgADAALgAyADUALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiADcANQAlACAAVQByAGUAYQAgADIANQAlACAATQBPAFAAXAAiACwAIABcACIAVQByAGUAYQBcACIALAAgADAALgA3ADUALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAE0AdQByAGkAYQB0AGUAIABvAGYAIABQAG8AdABhAHMAaAAgACgATQBPAFAAIAAvACAASwBDAEwAKQBcACIALAAgADAALgAyADUALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiADgAMAAlACAAVQByAGUAYQAgADIAMAAlACAATQBBAFAAXAAiACwAIABcACIAVQByAGUAYQAtAEEAbQBtAG8AbgBpAHUAbQAgAE4AaQB0AHIAYQB0AGUAIAAoAFUAQQBOACkAXAAiACwAIAAwAC4AOAAsACAAXAAiAEMAaABpAG4AYQBcACIALAAgAFwAIgBNAG8AbgBvAGEAbQBtAG8AbgBpAHUAbQAgAHAAaABvAHMAcABoAGEAdABlACAAKABNAEEAUAApAFwAIgAsACAAMAAuADIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAYwB0AGkAdgBhAHQAZQAgAE4AXAAiACwAIABcACIATgBpAHQAcgBvAGcAZQBuACAALQAgAEEAbQBtAG8AbgBpAGEAYwBhAGwAXAAiACwAIAAwAC4AMAA3ADEALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAC0AIABOAGkAdAByAGEAdABlAFwAIgAsACAAMAAuADAAMAA2ACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBOAGkAdAByAG8AZwBlAG4AIAAtACAAVQByAGUAaQBjAFwAIgAsACAAMAAuADAAOQAzACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBQAGgAbwBzAHAAaABvAHIAdQBzACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwAC4AMAAxACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBQAG8AdABhAHMAcwBpAHUAbQAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAMAAuADAANAAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAG4AbwB0ACAAcwBwAGUAYwBpAGYAaQBlAGQAXAAiACwAIABcACIAUwB1AGwAZgB1AHIAIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADAALgA4ADIALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAEEAYwB0AGkAdgBlACAATgAgACgATABhAHcAbgBwAHIAaQBkAGUALgBjAG8AbQAuAGEAdQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAYwB0AGkAdgBpAHMAdAAgAE0AYQB4ACAAWgBpAG4AYwBcACIALAAgAFwAIgBOAGkAdAByAG8AZwBlAG4AIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADAALgAwADcALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFoAaQBuAGMAIAAtACAARwBlAG4AZQByAGkAYwBcACIALAAgADAALgA3ACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBBAEMAVABJAFYASQBTAFQALQBNAEEAWAAuAHAAZABmACAAKABhAGcAcgBpAGMAaABlAG0ALgBjAG8AbQAuAGEAdQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAZwBmAGwAbwB3AFwAIgAsACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAMAAuADEAMgA5ACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBQAGgAbwBzAHAAaABvAHIAdQBzACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwAC4AMQA3ADcALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFMAdQBsAGYAdQByACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwAC4AMAA2ACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAFMAQgBQACAASABpAGcAaAAgAC8AIABNAGEAaQBuAHQAZQBuAGEAbgBjAGUAIABTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAZwBmAGwAbwB3ACAAQgBvAG8AcwB0AFwAIgAsACAAXAAiAE4AaQB0AHIAbwBnAGUAbgAgAC0AIABHAGUAbgBlAHIAaQBjAFwAIgAsACAAMAAuADEAMgAxACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBQAGgAbwBzAHAAaABvAHIAdQBzACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwAC4AMQA5ADgALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFMAdQBsAGYAdQByACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwAC4AMAA0ADEALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAUwBCAFAAIABIAGkAZwBoACAALwAgAE0AYQBpAG4AdABlAG4AYQBuAGMAZQAgAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBnAGYAbABvAHcAIABCAG8AbwBzAHQAIABFAHgAdAByAGEAXAAiACwAIABcACIATgBpAHQAcgBvAGcAZQBuACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwAC4AMQAyACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBQAGgAbwBzAHAAaABvAHIAdQBzACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwAC4AMQA5ADcALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFMAdQBsAGYAdQByACAALQAgAEcAZQBuAGUAcgBpAGMAXAAiACwAIAAwAC4AMAA0ACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAFMAQgBQACAASABpAGcAaAAgAC8AIABNAGEAaQBuAHQAZQBuAGEAbgBjAGUAIABTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAZwBOAFAAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBTAEIAUAAgAEgAaQBnAGgAIAAvACAATQBhAGkAbgB0AGUAbgBhAG4AYwBlACAAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBBAGwAbABTAHQAYQByAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAdQBtAG0AaQB0ACAARgBlAHIAdABpAGwAaQB6AGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEEAbQBtAG8AIAAzADYAXAAiACwAIABcACIAVQByAGUAYQBcACIALAAgADAALgA0ACwAIABcACIATABvAGMAYQB0AGkAbwBuACAAbgBvAHQAIABzAHAAZQBjAGkAZgBpAGUAZABcACIALAAgAFwAIgBTAHUAbABwAGgAYQB0AGUAIABvAGYAIABBAG0AbQBvAG4AaQBhACAAKABTAE8AQQApAFwAIgAsACAAMAAuADYALAAgAFwAIgBMAG8AYwBhAHQAaQBvAG4AIABuAG8AdAAgAHMAcABlAGMAaQBmAGkAZQBkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFIAYQB2AGUAbgBzAGQAbwB3AG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQQBwAGUAeAAgAEcAYQBJAFgAZQAgAEwAbwB3ACAAUAAgADIAMQAtADEALQA2AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEIAYQBpAGwAZQB5AHMAIABjAG8AbgB0AHIAbwBsAGwAZQBkACAAcgBlAGwAZQBhAHMAZQAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBCAGkAZwAgAE4AXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQgBpAGcAIABOACAAQQBuAGgAeQBkAHIAbwB1AHMAIABhAG0AbQBvAG4AaQBhACAATgBIADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAQgBpAGcAIABQAGgAbwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAUwBCAFAAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAIABQAHUAbABzAGUAIABhAG4AZAAgAEwAdQBwAGkAbgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBtAHAAYgBlAGwAbABzACAAUQB1AGkAYwBrAC0ATgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBRAHUAaQBjAGsAIAAtACAATgAgAHwAIABDAGEAbQBwAGIAZQBsAGwAcwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMASwAgADUANQAgAEEAbQBlAGwAaQBvAHIAYQBuAHQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUABhAGMAaQBmAGkAYwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAEMAcgBvAHAAIABLAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEMAcgBvAHAAIABCAG8AbwBzAHQAZQByACAAUABsAHUAcwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBTAEwAIABUAEUAQwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAEMAcgBvAHAAIABCAG8AbwBzAHQAZQByACAAUABsAHUAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBEAEEAUABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBNAG8AdQBuAHQAQwBvAG0AcABhAHMAcwAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAEIAbABlAG4AZABzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEQAQQBQAFMAWgBDAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAdQBtAG0AaQB0ACAARgBlAHIAdABpAGwAaQB6AGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAYQBzAHkAIABOACAAQgB1AGwAawBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AYwBpAHQAZQBjACAAUABpAHYAbwB0ACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAbgB0AGUAYwAgAFUAcgBlAGEAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIATgB1AHQAdQByAGYAIABVAHIAZQBhACAARwByAGEAbgB1AGwAYQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEUAegB5AGYAbABvAHcAIABOAGEAbgBvACAAQwBhAGwAYgB1AGQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIARQB6AHkARgBsAG8AdwAgAE4AYQBuAG8AIABDAGEAbABiAHUAZAAgAHwAIABMAG8AdgBlAGwAYQBuAGQAIAAoAGwAbwB2AGUAbABhAG4AZABhAGcAcgBpAHAAcgBvAGQAdQBjAHQAcwAuAGMAbwBtAC4AYQB1ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIARgBsAGUAeABpAC0ATgAgAE4ASQAgAG8AbgBsAHkAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUgBhAHYAZQBuAHMAZABvAHcAbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAGwAeQB0AHIAZQBsACAAWgBuAFAAIAAwAC0ANwAtADAAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAWQBhAHIAYQBWAGkAdABhACAARwBsAHkAdAByAGUAbAAgAFoAbgBQAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAcgBhAG4ALQBBAG0AXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAGMAaQB0AGUAYwAgAFAAaQB2AG8AdAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAYQBuAHUAbABvAGMAawAgAFMAUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AYwBpAHQAZQBjACAAUABpAHYAbwB0ACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAcgBhAG4AdQBsAG8AYwBrACAAWgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AYwBpAHQAZQBjACAAUABpAHYAbwB0ACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEcAcgBlAGUAbgAgAFUAcgBlAGEAIABOAFYAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAGMAaQB0AGUAYwAgAFAAaQB2AG8AdAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBHAHkAcABzAHUAbQAgAFMAdQBsAHAAaAB1AHIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIARwB5AHAAcwB1AG0AIABJAG4AYwBpAHQAZQBjACAAUABpAHYAbwB0ACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAEkAbgB2AGkAZwBvAHIAOAAgADAALQAzADcALQAzADcAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIARwBlAG4AZQBzAGkAcwAgAEEARwBcACIAXABuACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AKQApACkAOwBcAG4AXABuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBQAHIAbwBkAHUAYwB0AHMAXwBEAGEAdABhADIAXABuAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAxACwAIAAyADAALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMQAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADEAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMgBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMgAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADIAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMwBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAAMwAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADMAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANABcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANAAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADQAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANQAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADUAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANgBcACIALAAgAFwAIgBJAG4AZwByAGUAZABpAGUAbgB0ACAANgAgAHAAZQByAGMAZQBuAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADYAIABzAG8AdQByAGMAZQBcACIALAAgAFwAIgBQAHIAbwBkAHUAYwB0ACAAaQBuAGYAbwAgAGwAaQBuAGsAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAG4AZwBhAG4AZQBzAGUAIABTAHUAbABwAGgAYQB0AGUAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAGMAaQB0AGUAYwAgAFAAaQB2AG8AdAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAEEAUABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AYwBpAHQAZQBjACAAUABpAHYAbwB0ACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AQQBQACAASQBtAHAAYQBjAHQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIASQBtAHAAYQBjAHQAIABmAGUAcgB0AGkAbABpAHMAZQByAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBBAFAAUwBaAEMAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AG0AbQBpAHQAIABGAGUAcgB0AGkAbABpAHoAZQByAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATQBhAHgAaQBtAHUAbQAgAE4ALQBQAGEAYwB0ACAAMgA5AC0AMAAtADAAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIATQBhAHgAaQBtAHUAbQAgAE4ALQBQAGEAYwB0ACAAfAAgAEwAbwB2AGUAbABhAG4AZAAgACgAbABvAHYAZQBsAGEAbgBkAGEAZwByAGkAcAByAG8AZAB1AGMAdABzAC4AYwBvAG0ALgBhAHUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAYwByAG8AcwBvAGwAIAAxADIALQA2AC0ANAA0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFIAaQBnAGIAeQB0AGEAeQBsAG8AcgAgAE0AaQBjAHIAbwBzAG8AbAAgAFIAYQBuAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAYwByAG8AcwBvAGwAIAAxADYALQAzADIALQAxADYAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUgBpAGcAYgB5AHQAYQB5AGwAbwByACAATQBpAGMAcgBvAHMAbwBsACAAUgBhAG4AZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBjAHIAbwBzAG8AbAAgADIANQAtADUALQAxADAAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUgBpAGcAYgB5AHQAYQB5AGwAbwByACAATQBpAGMAcgBvAHMAbwBsACAAUgBhAG4AZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBjAHIAbwBzAG8AbAAgADIAOAAtADAALQAxADQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUgBpAGcAYgB5AHQAYQB5AGwAbwByACAATQBpAGMAcgBvAHMAbwBsACAAUgBhAG4AZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AbwBuAG8AIABQAG8AdABhAHMAcwBpAHUAbQAgAFAAaABvAHMAcABoAGEAdABlACAATQBLAFAAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB3AGEAbgBjAHIAbwBwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE0AdQByAGkAYQB0AGUAIABPAGYAIABQAG8AdABhAHMAaAAgAE0ATwBQAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAE0AbwB1AG4AdABDAG8AbQBwAGEAcwBzACAARgBlAHIAdABpAGwAaQBzAGUAcgBzACAAQgBsAGUAbgBkAHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIATgBpAHQAcgBvAFAAbAB1AHMAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQQBnAHIAbwBTAHQAbwBjAGsAIABHAHIAbwB1AHAAIABOAGkAdAByAG8AIABQAGwAdQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAE4AdQB0AHIAYQBHAG8AbABkAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFMAdwBhAG4AYwByAG8AcABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwAgAFAAZQByAGYAbwByAG0AYQBuAGMAZQAgADEAOAAtADMALQA2AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFAAcgBvACAAVAB1AHIAZgAgAEYAbwByAG0AdQBsAGEAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwBPAEEAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIATQBvAHUAbgB0AEMAbwBtAHAAYQBzAHMAIABGAGUAcgB0AGkAbABpAHMAZQByAHMAIABCAGwAZQBuAGQAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAFMAUABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG0AcABhAGMAdAAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcABlAHIAIABQAGgAbwBzAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAUwBCAFAAIABTAHUAcABlAHIAIABQAEgATwBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFMAdQBwAGUAcgAgAFMAUgAgAEUAeAB0AHIAYQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAFMAQgBQACAAUwB1AHAAZQByACAAUABvAHQAYQBzAGgAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAUwB1AFAAZQByAGYAZQBjAHQAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIASQBuAGMAaQB0AGUAYwAgAFAAaQB2AG8AdAAgAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAcABlAHIAUABhAHMAdAB1AHIAZQAgAFAAbwB0AGEAcwBoACAANQA6ADEAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwBTAEIAUAAgAFMAdQBwAGUAcgAgAFAAbwB0AGEAcwBoAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBhAGMAZQAtAGkAdAAgAE0AbgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAGEAbQBwAGIAZQBsAGwAcwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAcwAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAbgBpAFMAWgBvAG4AXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAVwBlAG4AZwBmAHUAQQB1AHMAdAByAGEAbABpAGEAIAB1AG4AaQBTAFoAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFUAcgBlAGEAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdABDAGEAcgBkAF8AQQBkAGUAbABhAGkAZABlAF8AdwBlAGIALgBwAGQAZgAgACgAaQBuAGMAaQB0AGUAYwBwAGkAdgBvAHQAZgBlAHIAdABpAGwAaQBzAGUAcgBzAC4AYwBvAG0ALgBhAHUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAbgBnAGYAdQAgAFMAbABhAG0AIABHAHIAYQBuAHUAbABhAHIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB0AHIAYQBpAGcAaAB0AHMAIAAoAHcAZQBuAGcAZgB1AC4AYwBvAG0ALgBhAHUAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAARgBsAG8AdwBQAGgAbwBzACAAMQAwAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAARgBsAG8AdwBQAGgAbwBzACAAMQAzAFoAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABGAGwAbwB3AFAAaABvAHMAIAAxADUAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABGAGwAbwB3AFAAaABvAHMAIABLAFoAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABLAGUAeQBQAHIAbwAgAFQAcgBhAGMAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEsAZQB5AFAAcgBvACAAWgBpAG4AYwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUAByAG8AZAB1AGMAdABzAF8ARABhAHQAYQAzAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMAMQAsACAAMgAwACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADEAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADEAIABwAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAxACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADIAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADIAIABwAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAyACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADMAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADMAIABwAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAzACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADQAIABwAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA0ACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADUAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADUAIABwAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA1ACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADYAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADYAIABwAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA2ACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdAAgAGkAbgBmAG8AIABsAGkAbgBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABLAC0ARgBsAG8AdwAgADAALQAwAC0AMQA1AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAASwAtAEYAbABvAHcAIAAwAC0AMQA0AC0AMwAwAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAASwAtAEYAbABvAHcAIAAwAC0ANwAtADMANgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEsALQBGAGwAbwB3ACAAMQAzAC0AMAAtADcAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABLAC0ARgBsAG8AdwAgADQALQAwAC0AMQAyAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAATABpAHEAdQBpAGQAcwAgAE0ASQBDAFIATwAtAFMAVQBMAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAATABpAHEAdQBpAGQAcwAgAE4AMgA0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAATABpAHEAdQBpAGQAcwAgAE4AMgA1AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAATABpAHEAdQBpAGQAcwAgAE4AMgA2AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAATABpAHEAdQBpAGQAcwAgAE4ANAAyAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAATABpAHEAdQBpAGQAcwAgAE4ALQBDAEEATAAgADEANQArADEAOABDAGEAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAATgAtAEMAQQBMACAAMgAwACsAMQAwAEMAYQArAEIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAATgAtAEMAQQBMACAAMwA1ACsANgBDAGEAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAATgAtAEYATwBMACAAMgA0AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAATABpAHEAdQBpAGQAcwAgAE4ALQBGAE8ATAAgADIANAArAFQARQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQAgAEwAaQBxAHUAaQBkAHMAIABQAC0ARgBPAEwAIABaAGkAbgBjAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhACAATABpAHEAdQBpAGQAcwAgAFMAVQBMAFMAQQAgADEAMQAtADAALQAwACsAMQAyAFMAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAAUwBVAEwAUwBBACAAMgA0AC0AMwAtADAAKwA2AFMAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAAUwBVAEwAUwBBACAAMgA3AC0AMAAtADAAKwA3AFMAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAIABMAGkAcQB1AGkAZABzACAAUwBVAEwAUwBBACAAMwA2AC0AMAAtADAAKwAzAFMAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEATABpAHYAYQAgAEMAQQBMAEMASQBOAEkAVAAgAEIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEATABpAHYAYQAgAE4ASQBUAFIAQQBCAE8AUgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBZAGEAcgBhAEwAaQB2AGEAIABOAEkAVABSAEEAQgBPAFIAIAB8ACAAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEATABpAHYAYQAgAFQAUgBPAFAASQBDAE8AVABFAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAE0AaQBsAGEAIABDAG8AbQBwAGwAZQB4AFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAE0AaQBsAGEAIABDAG8AbQBwAGwAZQB4ACAAMQA3AC0ANQAtADEAMAAoADQAKQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQBNAGkAbABhACAAQwBvAG0AcABsAGUAeAAgADIAMQAtADcALQAzACgANAApAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAE0AaQBsAGEAIABVAE4ASQBWAEUAUgBTAEEATABcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQBSAGUAZwBhACAAMQAzAC0AMgAtADIAMQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQBWAGkAdABhACAAQgBPAFIAVABSAEEAQwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQBWAGkAdABhACAAQgBSAEEAUwBTAEkAVABSAEUATAAgAEQARgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUAByAG8AZAB1AGMAdABzAF8ARABhAHQAYQA0AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEANgAsACAAMgAwACwAXABuACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFAAcgBvAGQAdQBjAHQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADEAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADEAIABwAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAxACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADIAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADIAIABwAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAyACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADMAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADMAIABwAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAAzACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADQAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADQAIABwAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA0ACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADUAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADUAIABwAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA1ACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADYAXAAiACwAIABcACIASQBuAGcAcgBlAGQAaQBlAG4AdAAgADYAIABwAGUAcgBjAGUAbgB0AFwAIgAsACAAXAAiAEkAbgBnAHIAZQBkAGkAZQBuAHQAIAA2ACAAcwBvAHUAcgBjAGUAXAAiACwAIABcACIAUAByAG8AZAB1AGMAdAAgAGkAbgBmAG8AIABsAGkAbgBrAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAVgBpAHQAYQAgAEIAUgBBAFMAUwBJAFQAUgBFAEwAIABQAFIATwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQBWAGkAdABhACAAQgBVAEQAIABCAFUASQBMAEQARQBSACAARgBMAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAFYAaQB0AGEAIABGAFIAVQBUAFIARQBMAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAFYAaQB0AGEAIABHAEwAWQBUAFIARQBMACAAWgBuAFAAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAVgBpAHQAYQAgAEcAUgBBAE0ASQBUAFIARQBMAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAFYAaQB0AGEAIABLAE8ATQBCAEkAUABIAE8AUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQBWAGkAdABhACAATQBBAE4ARwBaAEkATgBDAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEMAcgBvAHAAIABOAHUAdAByAGkAdABpAG8AbgAgAFMAbwBsAHUAdABpAG8AbgBzACAAKABZAGEAcgBhACAAQQB1AHMAdAByAGEAbABpAGEAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBZAGEAcgBhAFYAaQB0AGEAIABNAE8ATABZAFQAUgBBAEMAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAQwByAG8AcAAgAE4AdQB0AHIAaQB0AGkAbwBuACAAUwBvAGwAdQB0AGkAbwBuAHMAIAAoAFkAYQByAGEAIABBAHUAcwB0AHIAYQBsAGkAYQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFkAYQByAGEAVgBpAHQAYQAgAFMARQBOAEkAUABIAE8AUwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWQBhAHIAYQBWAGkAdABhACAAWgBJAE4AVABSAEEAQwBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBDAHIAbwBwACAATgB1AHQAcgBpAHQAaQBvAG4AIABTAG8AbAB1AHQAaQBvAG4AcwAgACgAWQBhAHIAYQAgAEEAdQBzAHQAcgBhAGwAaQBhACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWgBpAG4AYwAgAFMAdQBsAHAAaABhAHQAZQAgAE0AbwBuAG8AaAB5AGQAcgBhAHQAZQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBJAG4AYwBpAHQAZQBjACAAUABpAHYAbwB0ACAARgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFoAaQBuAGMAcwBvAGwAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAXAAiACwAIABcACIAUwB1AGwAZgBhAHQAZQAgAFoAaQBuAGMAcwBvAGwAXAAiADsAXABuACAAIAAgACAAIAAgACAAIABcACIAWgBpAG4AYwBTAHQAYQByAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAEkAbQBwAGEAYwB0ACAAZgBlAHIAdABpAGwAaQBzAGUAcgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAXAAiAFoATQBDAC0AMQBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBcACIALAAgAFwAIgBLAGUAbQBnAHIAbwAgAFoATQBDAC0AMQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBaAG4AIAA3ADAAMAAwAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFwAIgAsACAAXAAiAFIAdQB0AGUAYwAgAFoAbgAgADcAMAAwADAAXAAiAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBMAGkAbQBlACwAIABkAG8AbABvAG0AaQB0AGUAIABhAG4AZAAgAGcAeQBwAHMAdQBtAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABpAG0AZQBEAG8AbABvAG0AaQB0AGUARwB5AHAAcwB1AG0AQwBvAG4AcwB0AGEAbgB0AHMAXwBUAGkAdABsAGUAXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAG8AbgBzAHQAYQBuAHQAcwAgAGYAbwByACAAbABpAG0AZQAsACAAZABvAGwAbwBtAGkAdABlACAAYQBuAGQAIABnAHkAcABzAHUAbQBcACIAKQApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABpAG0AZQBEAG8AbABvAG0AaQB0AGUARwB5AHAAcwB1AG0AQwBvAG4AcwB0AGEAbgB0AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AXABuAD0ATABBAE0AQgBEAEEAKAAoAFwAIgBDAG8AbgBzAHQAYQBuAHQAcwAgAGYAbwByACAAbABpAG0AZQAsACAAZABvAGwAbwBtAGkAdABlACAAYQBuAGQAIABnAHkAcABzAHUAbQBcACIAKQApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABpAG0AZQBEAG8AbABvAG0AaQB0AGUARwB5AHAAcwB1AG0AQwBvAG4AcwB0AGEAbgB0AHMAXwBTAG8AdQByAGMAZQBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAVgBvAGwAdQBtAGUAIAAxADoAIAA1AC4AOAAuADIAIABNAGUAdABoAG8AZABvAGwAbwBnAGkAYwBhAGwAIABpAHMAcwB1AGUAcwAsACAAZQBxAHUAYQB0AGkAbwBuACAAMwBHAF8AMQBcACIAKQApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABpAG0AZQBEAG8AbABvAG0AaQB0AGUARwB5AHAAcwB1AG0AQwBvAG4AcwB0AGEAbgB0AHMAXwBEAGEAdABhAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADMALABcAG4AIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIABcACIARQBsAGUAbQBlAG4AdABcACIALAAgAFwAIgBQAFwAIgAsACAAXAAiAEUARgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgAFwAIgBMAGkAbQBlACAAKABDAGEAbABjAGkAdQBtACAAYwBhAHIAYgBvAG4AYQB0AGUAKQBcACIALAAgADAALgA5ACwAIAAwAC4AMQAyADsAXABuACAAIAAgACAAIAAgACAAIABcACIARABvAGwAbwBtAGkAdABlACAAKABNAGEAZwBuAGUAcwBpAHUAbQAgAGMAYQByAGIAbwBuAGEAdABlACkAXAAiACwAIAAwAC4AOQA1ACwAIAAwAC4AMQAzADsAXABuACAAIAAgACAAIAAgACAAIABcACIARwB5AHAAcwB1AG0AXAAiACwAIAAwACwAIAAwAFwAbgAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACkAKQApADsAXABuAFwAbgBGAGUAcgB0AGkAbABpAHMAZQByAF8ATABpAG0AZQBEAG8AbABvAG0AaQB0AGUARwB5AHAAcwB1AG0AQwBvAG4AcwB0AGEAbgB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4APQBMAEEATQBCAEQAQQAoACgAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAARgBSAE8ATQAgAFMATwBVAFIAQwBFACAARABBAFQAQQA6ACAARwB5AHAAcwB1AG0AIABoAGEAcwAgAGIAZQBlAG4AIABhAGQAZABlAGQAIAB3AGkAdABoACAAcABsAGEAYwBlAGgAbwBsAGQAZQByACAAdgBhAGwAdQBlAHMAIABvAGYAIAAwACAAZgBvAHIAIABQACAAYQBuAGQAIABFAEYALgBcACIAKQApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXABuAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYwByAG8AcAAgAGEAbgBkACAAcABhAHMAdAB1AHIAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAHIAZQB0AHUAcgBuAGUAZAAgAHQAbwAgAHQAaABlACAAcwBvAGkAbAAsACAAYQBjAHIAbwBzAHMAIABhAGwAbAAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIABjACAAYQBuAGQAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcABcAG4ARQBOADIATwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAF8AewBjAH0AXABcAHMAdQBtAF8AewBwAH0AKABNAF8AewBsAGUAYQBjAGgALABjAHAAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBsAGUAYQBjAGgAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAGwAZQBhAGMAaABjAHAAIAA9ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAcAAgACgAawBnACAATgApAFwAbgBFAEYAbABlAGEAYwBoACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAKABrAGcAIABOADIATwAtAE4ALwBrAGcAIABOACkAXABuAEMATgAyAE8AIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBjACAAPQAgAEMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcAG4AcAAgAD0AIABQAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AbABlAGEAYwBoAGMAcAAsACAARQBGAGwAZQBhAGMAaAAsACAAQwBnAE4AMgBPACwAXABuACAAIAAgACAATQBsAGUAYQBjAGgAYwBwACAAKgAgAEUARgBsAGUAYQBjAGgAIAAqACAAQwBnAE4AMgBPACAAKgAgADEAMABeACgALQAzACkAXABuACAAIAApAFwAbgA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAGMAcgBvAHAAIABhAG4AZAAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIAByAGUAdAB1AHIAbgBlAGQAIAB0AG8AIAB0AGgAZQAgAHMAbwBpAGwAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADMALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBfAHsATgAyAE8AfQA9AFwAXABzAHUAbQBfAHsAYwB9AFwAXABzAHUAbQBfAHsAcAB9ACgATQBfAHsAbABlAGEAYwBoACwAYwBwAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAbABlAGEAYwBoAH0AXABcAHQAaQBtAGUAcwAgAEMAZwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbABlAGEAYwBoAGMAcABcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlACAAcAAgACgAawBnACAATgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAbABlAGEAYwBoAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGcATgAyAE8AXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4ATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcAG4ATQBsAGUAYQBjAGgAYwBwAFwAbgBrAGcAIABOAFwAbgBNAF8AewBsAGUAYQBjAGgALABjAHAAfQA9AE0AXwB7AGMAcAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAFcARQBUAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAFwAbgBNAGMAcAAgAD0AIABtAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgAGMAIABvAHIAIABwAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQBzACAAcAAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIAAoAGsAZwAgAE4AKQBcAG4ARgByAGEAYwBXAEUAVABqACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB0AGgAYQB0ACAAaQBzACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABmAHIAbwBtACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtACAAagAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBGAHIAYQBjAEwARQBBAEMASAAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBjACAAPQAgAEMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAdAB5AHAAZQBcAG4AcAAgAD0AIABQAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXABuAGkAcgAgAD0AIABpAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAGMAcAAsACAARgByAGEAYwBXAEUAVAB6AGkAcgAsACAARgByAGEAYwBMAEUAQQBDAEgALABcAG4AIAAgACAAIABNAGMAcAAgACoAIABGAHIAYQBjAFcARQBUAHoAaQByACAAKgAgAEYAcgBhAGMATABFAEEAQwBIAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBsAGUAYQBjAGgAYwBwAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADYALgAzAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBsAGUAYQBjAGgALABjAHAAfQA9AE0AXwB7AGMAcAB9AFwAXAB0AGkAbQBlAHMAIABGAHIAYQBjAFcARQBUAF8AewB6ACwAaQByAH0AXABcAHQAaQBtAGUAcwAgAEYAcgBhAGMATABFAEEAQwBIAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANwAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBjAHAAXAAiACwAXAAiAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAYwAgAG8AcgAgAHAAYQBzAHQAdQByAGUAIAByAGUAcwBpAGQAdQBlAHMAIABwACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgACgAawBnACAATgApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAFcARQBUAHoAaQByAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZgByAG8AbQAgAHQAaABlACAAbABlAGEAYwBoAGkAbgBnACAAegBvAG4AZQAgAHoAIABhAG4AZAAgAGkAcgByAGkAZwBhAHQAaQBvAG4AIAB0AHkAcABlACAAaQByACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgB6AFwAIgAsACAAXAAiAEwAbwBjAGEAdABpAG8AbgAgAGkAbgAgAGwAZQBhAGMAaABpAG4AZwAgAHoAbwBuAGUAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAIAB0AHkAcABlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBwAFwAIgAsAFwAIgBQAGEAcwB0AHUAcgBlACAAcgBlAHMAaQBkAHUAZQAgAHQAeQBwAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAcgBcACIALAAgAFwAIgBJAHIAcgBpAGcAYQB0AGkAbwBuACAAdAB5AHAAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuACAAIABWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAEYAUgBPAE0AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAYwByAGkAdABlAHIAaQBhACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIAB6AG8AbgBlACAAegAgAGEAbgBkACAAaQByAHIAaQBnAGEAdABpAG8AbgAgAHQAeQBwAGUAIABpAHIALgAgAFIAZQBtAG8AdgBlAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AIABjAHIAaQB0AGUAcgBpAGEAIABqAC4AXAAiACkAOwBcAG4AXABuAFwAbgBcAG4AIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIAAyADAAMgAzACAAcgBlAGYAZQByAGUAbgBjAGUAOgBcAG4AQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAIABzAG8AaQBsAHMAOgAgAEEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIAAoADMALgBEAC4AYgAuADEAKQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAFwAbgBBAHQAbQBvAHMAcABoAGUAcgBpAGMAIABkAGUAcABvAHMAaQB0AGkAbwBuACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABiAHkAIABnAHIAYQB6AGkAbgBnACAAYQBuAGkAbQBhAGwAcwAgAG8AbgAgAHAAYQBzAHQAdQByAGUALABcAG4AcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAbgBFAE4AMgBPAGEAZABcAG4AdAAgAE4AMgBPAFwAbgBFAE4AMgBPAGEAZAAgAD0AIABNAHYAbwBsAG0AIAAqACAARQBGAGEAZAAgACoAIABDAGcATgAyAE8AIAAqACAAMQAwAF4ALQAzAFwAbgBNAHYAbwBsAG0AIAA6AE0AbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACAAOgAgAGsAZwAgAE4AXABuAEUARgBhAGQAIAA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4AQwBnAE4AMgBPACAAOgAgAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARwBXAFAAXABuACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEUATgAyAE8AYQBkACwARwBXAFAATgAyAE8ALABcAG4AIAAgACAAIAAgACgARQBOADIATwBhAGQAIAAqACAARwBXAFAATgAyAE8AKQBcAG4AIAAgACAAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AdgBvAGwAbQAsAEUAZgBhAGQALABDAGcATgAyAE8ALABcAG4AIAAgACAAIAAoAE0AdgBvAGwAbQAgACoAIABFAGYAYQBkACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAXgAtADMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEEAdABtAG8AcwBwAGgAZQByAGkAYwAgAGQAZQBwAG8AcwBpAHQAaQBvAG4AIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAGIAeQAgAGcAcgBhAHoAaQBuAGcAIABhAG4AaQBtAGEAbABzACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AYQBkAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxACwAIAAyADAAMgAzADoAIAAzAC4ARAAuAEIAXwA0AFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPAGEAZAAgAD0AIABNAHYAbwBsAG0AIAAqACAARQBGAGEAZAAgACoAIABDAGcATgAyAE8AIAAqACAAMQAwACAAXgAgAC0AIAAzAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AdgBvAGwAbQBcACIALABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgAsAFwAIgBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAYQBkAFwAIgAsAFwAIgBFAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAYQB0AG0AbwBzAHAAaABlAHIAaQBjACAAZABlAHAAbwBzAGkAdABpAG8AbgBcACIALABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBnAE4AMgBPAFwAIgAsAFwAIgBGAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALABcACIAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQAQQBuAGkAbQBhAGwAVwBhAHMAdABlAFwAbgBUAGgAZQAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAbQBhAG4AdQByAGUALAAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHMAbwBpAGwAcwBcAG4ATQB2AG8AbABtAFwAbgBrAGcAIABOAFwAbgBNAHYAbwBsAG0AIAA9ACAAKABNAE4AagBtACAAKwAgAFUATgBqAG0AIAArACAARgBOAGoAbQApACAAKgAgAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAbgBNAE4AagBtACAAOgAgAE0AYQBzAHMAIABvAGYAIABtAGEAbgB1AHIAZQAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIAA6ACAAawBnACAATgBcAG4AVQBOAGoAbQAgADoAIABNAGEAcwBzACAAbwBmACAAdQByAGkAbgBlACAAbgBpAHQAcgBvAGcAZQBuACAAZQB4AGMAcgBlAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAsACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrACAAZgBvAHIAIABlAGEAYwBoACAAZABhAGkAcgB5ACAAYwBhAHQAdABsAGUAIABjAGwAYQBzAHMAIAA6ACAAawBnACAATgBcAG4ARgBOAGoAbQAgADoAIABNAGEAcwBzACAAbwBmACAAZgBhAGUAYwBhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIABmAG8AcgAgAGUAYQBjAGgAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGMAbABhAHMAcwAgADoAIABrAGcAIABOAFwAbgBGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbAAgADoAIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABmAGEAZQBjAGUAcwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcABhAHMAdAB1AHIAZQAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQAQQBuAGkAbQBhAGwAVwBhAHMAdABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBqAG0ALAAgAFUATgBqAG0ALAAgAEYATgBqAG0ALAAgAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsACwAXABuACAAIAAgACAAKABNAE4AagBtACAAKwAgAFUATgBqAG0AIAArACAARgBOAGoAbQApACAAKgAgAEYAcgBhAGMARwBBAFMATQBzAG8AaQBsAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABBAG4AaQBtAGEAbABXAGEAcwB0AGUAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABmAHIAbwBtACAAbQBhAG4AdQByAGUALAAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZgBhAGUAYwBlAHMAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHMAbwBpAGwAcwBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQB2AG8AbABtAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQAQQBuAGkAbQBhAGwAVwBhAHMAdABlAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAATgBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxACwAIAAyADAAMgAzADoAIAAzAC4ARAAuAEIAXwAyAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQAQQBuAGkAbQBhAGwAVwBhAHMAdABlAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQB2AG8AbABtACAAPQAgACgATQBOAGoAbQAgACsAIABVAE4AagBtACAAKwAgAEYATgBqAG0AKQAgACoAIABGAHIAYQBjAEcAQQBTAE0AcwBvAGkAbABcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBOAGoAbQBcACIALABcACIATQBhAHMAcwAgAG8AZgAgAG0AYQBuAHUAcgBlACAAbgBpAHQAcgBvAGcAZQBuACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwBcACIALABcACIAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVQBOAGoAbQBcACIALABcACIATQBhAHMAcwAgAG8AZgAgAHUAcgBpAG4AZQAgAG4AaQB0AHIAbwBnAGUAbgAgAGUAeABjAHIAZQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawAgAGYAbwByACAAZQBhAGMAaAAgAGQAYQBpAHIAeQAgAGMAYQB0AHQAbABlACAAYwBsAGEAcwBzAFwAIgAsAFwAIgBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAE4AagBtAFwAIgAsAFwAIgBNAGEAcwBzACAAbwBmACAAZgBhAGUAYwBhAGwAIABuAGkAdAByAG8AZwBlAG4AIABlAHgAYwByAGUAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIABmAG8AcgAgAGUAYQBjAGgAIABkAGEAaQByAHkAIABjAGEAdAB0AGwAZQAgAGMAbABhAHMAcwBcACIALABcACIAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBHAEEAUwBNAHMAbwBpAGwAXAAiACwAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIAB1AHIAaQBuAGUAIABhAG4AZAAgAGYAYQBlAGMAZQBzACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgAsAFwAIgAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXABuAFQAaABlACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHYAbwBsAGEAdABpAGwAaQBzAGUAZAAgAGYAcgBvAG0AIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAbgBNAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjAFwAbgBrAGcAIABOAFwAbgBNAHYAbwBsAGkAbgBvAHIAZwBhAG4AaQBjACAAPQAgAE0ATgBmACAAKgAgAEYAcgBhAGMARwBBAFMARgBmAFwAbgBNAE4AZgAgADoATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAA6ACAAawBnACAATgBcAG4ARgByAGEAYwBHAEEAUwBGAGYAIAA6ACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdABoAGEAdAAgAHYAbwBsAGEAdABpAGwAaQBzAGUAcwAgADoAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AXABuAEEAZwBzAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0ATgBmACwAIABGAHIAYQBjAEcAQQBTAEYAZgAsAFwAbgAgACAAIAAgAE0ATgBmACAAKgAgAEYAcgBhAGMARwBBAFMARgBmAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEEAZwBzAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAZgByAG8AbQAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGQAZQBwAG8AcwBpAHQAZQBkACAAbwBuACAAcwBvAGkAbABzAFwAIgApADsAXABuAFwAbgBBAGcAcwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQB2AG8AbABpAG4AbwByAGcAYQBuAGkAYwBcACIAKQA7AFwAbgBcAG4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBBAGcAcwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxACwAIAAyADAAMgAzADoAIAAzAC4ARAAuAEIAXwAxAFwAIgApADsAXABuAFwAbgBBAGcAcwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AdgBvAGwAaQBuAG8AcgBnAGEAbgBpAGMAIAA9ACAATQBOAGYAIAAqACAARgByAGEAYwBHAEEAUwBGAGYAXAAiACkAOwBcAG4AXABuAEEAZwBzAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AZgBcACIALABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAXAAiACwAXAAiAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMARwBBAFMARgBmAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABpAG4AbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIAB0AGgAYQB0ACAAdgBvAGwAYQB0AGkAbABpAHMAZQBzAFwAIgAsAFwAIgAoAGsAZwAgAE4ASAAzABMgTgAgACsAIABOAE8AeAATIE4AKQAvAGsAZwAgAE4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAMgAwADIAMwAgAHIAZQBmAGUAcgBlAG4AYwBlADoAXABuAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsACAAcwBvAGkAbABzADoAIABMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAFIAdQBuAG8AZgBmACAAKAAzAC4ARAAuAGIALgAyACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEEAZwBTAG8AaQBsAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXABuAEwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAsAFwAbgBpAG4AbwByAGcAYQBuAGkAYwAgAGEAbgBkACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAsAFwAbgB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUAXABuAEUATgAyAE8AbABlAGEAYwBoACAAPQAgAE0AbABlAGEAYwBoACAAKgAgAEUARgBsAGUAYQBjAGgAIAAqACAAQwBnAE4AMgBPACAAKgAgADEAMAAgAF4AIAAtACAAMwBcAG4ATQBsAGUAYQBjAGgAIAA6ACAATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIAB0AG8AIABsAGUAYQBjAGgAZQBkACAAYQBuAGQAIAByAHUAbgAgAG8AZgBmACAAOgAgAGsAZwAgAE4AXABuAEUARgBsAGUAYQBjAGgAIAA6ACAARQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4AQwBnAE4AMgBPACAAOgAgAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AQQBnAFMAbwBpAGwAcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEcAVwBQAFwAbgAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAE4AMgBPAGwAZQBhAGMAaAAsAEcAVwBQAE4AMgBPACwAXABuACAAIAAgACAAIAAoAEUATgAyAE8AbABlAGEAYwBoACAAKgAgAEcAVwBQAE4AMgBPACkAXABuACAAIAAgACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBsAGUAYQBjAGgALABFAEYAbABlAGEAYwBoACwAQwBnAE4AMgBPACwAXABuACAAIAAgACAAKABNAGwAZQBhAGMAaAAgACoAIABFAEYAbABlAGEAYwBoACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAXgAtADMAKQBcAG4AIAAgACkAXABuADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBMAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUALABpAG4AbwByAGcAYQBuAGkAYwAgAGEAbgBkACAAbwByAGcAYQBuAGkAYwAgAGYAZQByAHQAaQBsAGkAcwBlAHIAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbAAsACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPAGwAZQBhAGMAaABcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABOADIATwBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBOAGEAdABpAG8AbgBhAGwAIABJAG4AdgBlAG4AdABvAHIAeQAgAFIAZQBwAG8AcgB0ACAAVgBvAGwAdQBtAGUAIAAxACwAIAAyADAAMgAzADoAIAAzAC4ARAAuAEIAXwAxADAAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAE4AMgBPAGwAZQBhAGMAaAAgAD0AIABNAGwAZQBhAGMAaAAgACoAIABFAEYAbABlAGEAYwBoACAAKgAgAEMAZwBOADIATwAgACoAIAAxADAAIABeACAALQAgADMAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADMALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbABlAGEAYwBoAFwAIgAsAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAHQAbwAgAGwAZQBhAGMAaABlAGQAIABhAG4AZAAgAHIAdQBuACAAbwBmAGYAXAAiACwAXAAiAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUARgBsAGUAYQBjAGgAXAAiACwAXAAiAEUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsAFwAIgBrAGcAIABOADIATwAtAE4ALwBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAGcATgAyAE8AXAAiACwAXAAiAEYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAIgAsAFwAIgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBOAEwAbwBzAHQAXABuAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACwAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAbgBNAGwAZQBhAGMAaABhAG4AaQBtAGEAbAB3AGEAcwB0AGUAPQAoAE0ATgBqAG0AKwBVAE4AagBtACsARgBOAGoAbQApACoARgByAGEAYwBXAEUAVAAqAEYAcgBhAGMATABFAEEAQwBIAFwAbgBNAGwAZQBhAGMAaABhAG4AaQBtAGEAbAB3AGEAcwB0AGUAXABuAGsAZwAgAE4AXABuAE0ATgBqAG0AIAA6ACAATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAG0AYQBuAHUAcgBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgADoAIABrAGcAIABOAFwAbgBVAE4AagBtACAAOgAgAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIAB1AHIAaQBuAGUAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawAgADoAIABrAGcAIABOAFwAbgBGAE4AagBtACAAOgAgAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrACAAOgAgAGsAZwAgAE4AXABuAEYAcgBhAGMAVwBFAFQAIAA6ACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAATgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAaQBuACAAdABoAGUAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAG8AZgAgAHQAaABlACAAZQBuAHQAaQB0AHkAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBGAHIAYQBjAEwARQBBAEMASAAgADoAIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQQBuAGkAbQBhAGwAVwBhAHMAdABlAE4ATABvAHMAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE4AagBtACwAVQBOAGoAbQAsAEYATgBqAG0ALABGAHIAYQBjAFcARQBUACwARgByAGEAYwBMAEUAQQBDAEgALABcAG4AIAAgACAAIAAoAE0ATgBqAG0AKwBVAE4AagBtACsARgBOAGoAbQApACoARgByAGEAYwBXAEUAVAAqAEYAcgBhAGMATABFAEEAQwBIAFwAbgAgACAAKQBcAG4AOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBOAEwAbwBzAHQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABsAG8AcwB0ACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACwAIAB1AHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIAB0AG8AIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBBAG4AaQBtAGEAbABXAGEAcwB0AGUATgBMAG8AcwB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGwAZQBhAGMAaABhAG4AaQBtAGEAbAB3AGEAcwB0AGUAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBOAEwAbwBzAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBBAG4AaQBtAGEAbABXAGEAcwB0AGUATgBMAG8AcwB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEALAAgADIAMAAyADMAOgAgADMALgBEAC4AQgBfADYAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBOAEwAbwBzAHQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGwAZQBhAGMAaABhAG4AaQBtAGEAbAB3AGEAcwB0AGUAPQAoAE0ATgBqAG0AKwBVAE4AagBtACsARgBOAGoAbQApACoARgByAGEAYwBXAEUAVAAqAEYAcgBhAGMATABFAEEAQwBIAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBBAG4AaQBtAGEAbABXAGEAcwB0AGUATgBMAG8AcwB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE4AagBtAFwAIgAsAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAbQBhAG4AdQByAGUAIABhAHAAcABsAGkAZQBkACAAdABvACAAcwBvAGkAbABzAFwAIgAsAFwAIgBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBVAE4AagBtAFwAIgAsAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAdQByAGkAbgBlACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAXAAiAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYATgBqAG0AXAAiACwAXAAiAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAIgAsAFwAIgBrAGcAIABOAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAFcARQBUAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGkAbgAgAHQAaABlACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAIABvAGYAIAB0AGgAZQAgAGUAbgB0AGkAdAB5AFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMATABFAEEAQwBIAFwAIgAsAFwAIgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABcAG4ATQBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAXABuAE0AbABlAGEAYwBoAGkAbgBvAHIAZwBhAG4AaQBjACAAPQAgAE0AIAAqACAARgByAGEAYwBXAEUAVAAgACoAIABGAHIAYQBjAEwARQBBAEMASABcAG4ATQAgADoAIABNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAaQBuACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwAgADoAIABrAGcAIABOAFwAbgBGAHIAYQBjAFcARQBUACAAOgAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAaQBuACAAdABoAGUAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAG8AZgAgAHQAaABlACAAZQBuAHQAaQB0AHkAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBGAHIAYQBjAEwARQBBAEMASAAgADoAIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIAB0AGgAYQB0ACAAaQBzACAAbABvAHMAdAAgAHQAaAByAG8AdQBnAGgAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNACwAIABGAHIAYQBjAFcARQBUACwAIABGAHIAYQBjAEwARQBBAEMASAAsAFwAbgAgACAAIAAgAE0AIAAqACAARgByAGEAYwBXAEUAVAAgACoAIABGAHIAYQBjAEwARQBBAEMASABcAG4AIAAgACkAXABuADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGwAbwBzAHQAIABmAHIAbwBtACAAaQBuAG8AcgBnAGEAbgBpAGMAIABmAGUAcgB0AGkAbABpAHMAZQByACAAdABvACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBOAEwAbwBzAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbABlAGEAYwBoAGkAbgBvAHIAZwBhAG4AaQBjAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAE4AXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIATgBMAG8AcwB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEALAAgADIAMAAyADMAOgAgADMALgBEAC4AQgBfADUAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIATgBMAG8AcwB0AF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBsAGUAYQBjAGgAaQBuAG8AcgBnAGEAbgBpAGMAIAA9ACAATQAgACoAIABGAHIAYQBjAFcARQBUACAAKgAgAEYAcgBhAGMATABFAEEAQwBIAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBcACIALABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGkAbgBvAHIAZwBhAG4AaQBjACAAZgBlAHIAdABpAGwAaQBzAGUAcgAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAXAAiACwAXAAiAGsAZwAgAE4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAcgBhAGMAVwBFAFQAXAAiACwAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGEAdgBhAGkAbABhAGIAbABlACAAZgBvAHIAIABsAGUAYQBjAGgAaQBuAGcAIABhAG4AZAAgAHIAdQBuAG8AZgBmACAAaQBuACAAdABoAGUAIABjAGwAaQBtAGEAdABlACAAegBvAG4AZQAgAG8AZgAgAHQAaABlACAAZQBuAHQAaQB0AHkAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBMAEUAQQBDAEgAXAAiACwAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAHQAaABhAHQAIABpAHMAIABsAG8AcwB0ACAAdABoAHIAbwB1AGcAaAAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBOAEwAbwBzAHQAXABuAE0AbABlAGEAYwBoAHIAZQBzAGkAZAB1AGUAXABuAE0AbABlAGEAYwBoAHIAZQBzAGkAZAB1AGUAIAA9ACAATQAgACoAIABGAHIAYQBjAFcARQBUACAAKgAgAEYAcgBhAGMATABFAEEAQwBIAFwAbgBNACAAOgAgAE0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAGEAcABwAGwAaQBlAGQAIAB0AG8AIABzAG8AaQBsAHMAIAA6ACAAawBnACAATgBcAG4ARgByAGEAYwBXAEUAVAAgADoAIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABhAHYAYQBpAGwAYQBiAGwAZQAgAGYAbwByACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgAGkAbgAgAHQAaABlACAAYwBsAGkAbQBhAHQAZQAgAHoAbwBuAGUAIABvAGYAIAB0AGgAZQAgAGUAbgB0AGkAdAB5ACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ARgByAGEAYwBMAEUAQQBDAEgAIAA6ACAARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQwByAG8AcABSAGUAcwBpAGQAdQBlAE4ATABvAHMAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNACwAIABGAHIAYQBjAFcARQBUACwAIABGAHIAYQBjAEwARQBBAEMASAAsAFwAbgAgACAAIAAgAE0AIAAqACAARgByAGEAYwBXAEUAVAAgACoAIABGAHIAYQBjAEwARQBBAEMASABcAG4AIAAgACkAXABuADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUATgBMAG8AcwB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAbABvAHMAdAAgAGYAcgBvAG0AIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBOAEwAbwBzAHQAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AbABlAGEAYwBoAHIAZQBzAGkAZAB1AGUAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBOAEwAbwBzAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABOAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUATgBMAG8AcwB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AYQB0AGkAbwBuAGEAbAAgAEkAbgB2AGUAbgB0AG8AcgB5ACAAUgBlAHAAbwByAHQAIABWAG8AbAB1AG0AZQAgADEALAAgADIAMAAyADMAOgAgADMALgBEAC4AQgBfADgAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBOAEwAbwBzAHQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGwAZQBhAGMAaAByAGUAcwBpAGQAdQBlACAAPQAgAE0AIAAqACAARgByAGEAYwBXAEUAVAAgACoAIABGAHIAYQBjAEwARQBBAEMASABcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQwByAG8AcABSAGUAcwBpAGQAdQBlAE4ATABvAHMAdABfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMwAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBcACIALABcACIATQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACAAYQBwAHAAbABpAGUAZAAgAHQAbwAgAHMAbwBpAGwAcwBcACIALABcACIAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgByAGEAYwBXAEUAVABcACIALABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAYQB2AGEAaQBsAGEAYgBsAGUAIABmAG8AcgAgAGwAZQBhAGMAaABpAG4AZwAgAGEAbgBkACAAcgB1AG4AbwBmAGYAIABpAG4AIAB0AGgAZQAgAGMAbABpAG0AYQB0AGUAIAB6AG8AbgBlACAAbwBmACAAdABoAGUAIABlAG4AdABpAHQAeQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAYQBjAEwARQBBAEMASABcACIALABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAbgBpAHQAcgBvAGcAZQBuACAAdABoAGEAdAAgAGkAcwAgAGwAbwBzAHQAIAB0AGgAcgBvAHUAZwBoACAAbABlAGEAYwBoAGkAbgBnACAAYQBuAGQAIAByAHUAbgBvAGYAZgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgADIAMAAyADMAIAByAGUAZgBlAHIAZQBuAGMAZQA6AFwAbgBVAHIAaQBuAGUAIABhAG4AZAAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAGIAeQAgAGcAcgBhAHoAaQBuAGcAIABhAG4AaQBtAGEAbABzACAAKAAzAC4ARAAuAGEALgAzACkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuACoALwBcAG4AXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBVAHIAaQBuAGUAQQBuAGQARAB1AG4AZwBEAGUAcABvAHMAaQB0AGUAZABcAG4ATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAdQByAGkAbgBlACAAYQBuAGQAIABkAHUAbgBnACAAZABlAHAAbwBzAGkAdABlAGQAIABiAHkAIABnAHIAYQB6AGkAbgBnACAAYQBuAGkAbQBhAGwAcwAgAG8AbgAgAHAAYQBzAHQAdQByAGUALABcAG4AcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAbgBFAE4AMgBPAGQAaQByAFwAbgB0ACAATgAyAE8AXABuAEUATgAyAE8AZABpAHIAIAA9ACAAKAAoAEEARgBqAG0APQAxADQAIAAqACAARQBGAFAAUgBQACAAKgAgAEMAZwBOADIATwApACAAKwAgACgAQQBVAGoAbQA9ADEANAAgACoAIABFAEYAUABSAFAAIAAqACAAQwBnAE4AMgBPACkAKQAgACoAIAAxADAAXgAtADMAXABuAEEARgBqAG0AIAA6ACAAbQBhAHMAcwAgAG8AZgAgAG4AaQB0AHIAbwBnAGUAbgAgAGkAbgAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawAgADoAIABrAGcAIABOAFwAbgBBAFUAagBtACAAOgAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AZwBlAG4AIABpAG4AIAB1AHIAaQBuAGUAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawAgADoAIABrAGcAIABOAFwAbgBFAEYAUABSAFAAIAA6ACAAZABpAHIAZQBjAHQAIABOADIATwAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAIAA6ACAAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcAG4AQwBnAE4AMgBPACAAOgAgAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAE4AMgBPACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBVAHIAaQBuAGUAQQBuAGQARAB1AG4AZwBEAGUAcABvAHMAaQB0AGUAZABfAEcAVwBQAFwAbgAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABFAE4AMgBPAGQAaQByACwARwBXAFAATgAyAE8ALABcAG4AIAAgACAAIAAgACgARQBOADIATwBkAGkAcgAgACoAIABHAFcAUABOADIATwApAFwAbgAgACAAIAApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8AVQByAGkAbgBlAEEAbgBkAEQAdQBuAGcARABlAHAAbwBzAGkAdABlAGQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQQBGAGoAbQAsACAAQQBVAGoAbQAsACAARQBGAFAAUgBQACwAIABDAGcATgAyAE8ALABcAG4AIAAgACAAIAAoACgAQQBGAGoAbQAgACoAIABFAEYAUABSAFAAIAAqACAAQwBnAE4AMgBPACkAIAArACAAKABBAFUAagBtACAAKgAgAEUARgBQAFIAUAAgACoAIABDAGcATgAyAE8AKQApACAAKgAgADEAMABeAC0AMwBcAG4AIAAgACkAXABuADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8AVQByAGkAbgBlAEEAbgBkAEQAdQBuAGcARABlAHAAbwBzAGkAdABlAGQAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHUAcgBpAG4AZQAgAGEAbgBkACAAZAB1AG4AZwAgAGQAZQBwAG8AcwBpAHQAZQBkACAAYgB5ACAAZwByAGEAegBpAG4AZwAgAGEAbgBpAG0AYQBsAHMAIABvAG4AIABwAGEAcwB0AHUAcgBlACwAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACkAOwBcAG4AXABuAEEAZwBTAG8AaQBsAHMAXwBVAHIAaQBuAGUAQQBuAGQARAB1AG4AZwBEAGUAcABvAHMAaQB0AGUAZABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwBkAGkAcgBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAFUAcgBpAG4AZQBBAG4AZABEAHUAbgBnAEQAZQBwAG8AcwBpAHQAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAE4AMgBPAFwAIgApADsAXABuAFwAbgBBAGcAUwBvAGkAbABzAF8AVQByAGkAbgBlAEEAbgBkAEQAdQBuAGcARABlAHAAbwBzAGkAdABlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBhAHQAaQBvAG4AYQBsACAASQBuAHYAZQBuAHQAbwByAHkAIABSAGUAcABvAHIAdAAgAFYAbwBsAHUAbQBlACAAMQAsACAAMgAwADIAMwA6ACAAMwAuAEQALgBhAC4AMwBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAFUAcgBpAG4AZQBBAG4AZABEAHUAbgBnAEQAZQBwAG8AcwBpAHQAZQBkAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBOADIATwBkAGkAcgAgAD0AIAAoACgAQQBGAGoAbQA9ADEANAAgACoAIABFAEYAUABSAFAAIAAqACAAQwBnAE4AMgBPACkAIAArACAAKABBAFUAagBtAD0AMQA0ACAAKgAgAEUARgBQAFIAUAAgACoAIABDAGcATgAyAE8AKQApACAAKgAgADEAMABeAC0AMwBcACIAKQA7AFwAbgBcAG4AQQBnAFMAbwBpAGwAcwBfAFUAcgBpAG4AZQBBAG4AZABEAHUAbgBnAEQAZQBwAG8AcwBpAHQAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAEYAagBtAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAATgAgAGkAbgAgAGQAdQBuAGcAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALABcACIAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBVAGoAbQBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAE4AIABpAG4AIAB1AHIAaQBuAGUAIABkAGUAcABvAHMAaQB0AGUAZAAgAG8AbgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALABcACIAawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAFAAUgBQAFwAIgAsAFwAIgBkAGkAcgBlAGMAdAAgAE4AMgBPACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHAAYQBzAHQAdQByAGUALAAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIALABcACIAawBnACAATgAyAE8ALQBOAC8AawBnACAATgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBnAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABOADIATwAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwBcACIALABcACIAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnACIALAAiAHQAZQB4AHQAIgA6ACIALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcAG4ARQBDAEgANABcAG4AdAAgAEMASAA0AFwAbgBFAF8AewBDAEgANAB9AD0AXABuAFwAXABzAHUAbQBfAHsAYwB9ACgATQBfAHsAYgB1AHIAbgAsAGMAfQBcAFwAdABpAG0AZQBzACAAQwBDAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsAQwBIADQAfQBcAFwAdABpAG0AZQBzACAAQwBfAHsAQwBIADQAfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAGIAdQByAG4AYwAgAD0AIABtAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAKQBcAG4AQwBDAGMAIAA9ACAAYwBhAHIAYgBvAG4AIABtAGEAcwBzACAAZgByAGEAYwB0AGkAbwBuACAAaQBuACAAdABoAGUAIAByAGUAcwBpAGQAdQBlAHMAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARQBGAEMASAA0ACAAPQAgAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAZgByAG8AbQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAKABrAGcAIABDAEgANAAvAGsAZwAgAEMASAA0ACAAYgB1AHIAbgB0ACkAXABuAEMAQwBIADQAIAA9ACAAZgBhAGMAdABvAHIAIAB0AG8AIABjAG8AbgB2AGUAcgB0ACAAZQBsAGUAbQBlAG4AdABhAGwAIABtAGEAcwBzACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAHQAbwAgAG0AbwBsAGUAYwB1AGwAYQByACAAbQBhAHMAcwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBjACAAPQAgAEMAcgBvAHAAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAGIAdQByAG4AYwAsACAAQwBDAGMALAAgAEUARgBDAEgANAAsACAAQwBfAEMASAA0ACwAXABuACAAIAAgACAATQBiAHUAcgBuAGMAIAAqACAAQwBDAGMAIAAqACAARQBGAEMASAA0ACAAKgAgAEMAXwBDAEgANAAgACoAIAAxADAAXgAoAC0AMwApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAAQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADEAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBDAEgANAB9AD0AXABcAHMAdQBtAF8AewBjAH0AKABNAF8AewBiAHUAcgBuACwAYwB9AFwAXAB0AGkAbQBlAHMAIABDAEMAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARQBGAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIABDAF8AewBDAEgANAB9AFwAXAB0AGkAbQBlAHMAIAAxADAAXgB7AC0AMwB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANQAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGIAdQByAG4AYwBcACIALABcACIAbQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABiAHUAcgBuAHQAIABmAG8AcgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAQwBjAFwAIgAsAFwAIgBjAGEAcgBiAG8AbgAgAG0AYQBzAHMAIABmAHIAYQBjAHQAaQBvAG4AIABpAG4AIAB0AGgAZQAgAHIAZQBzAGkAZAB1AGUAcwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBFAEYAQwBIADQAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIABtAGUAdABoAGEAbgBlACAAZgByAG8AbQAgAGIAdQByAG4AaQBuAGcAIABvAGYAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQBzACAAKABrAGcAIABDAEgANAAvAGsAZwAgAEMASAA0ACAAYgB1AHIAbgB0ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAQwBIADQAXAAiACwAXAAiAGYAYQBjAHQAbwByACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAGUAbABlAG0AZQBuAHQAYQBsACAAbQBhAHMAcwAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAB0AG8AIABtAG8AbABlAGMAdQBsAGEAcgAgAG0AYQBzAHMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAYwBcACIALABcACIAQwByAG8AcAAgAHQAeQBwAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAFwAbgBOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAdABoAGUAIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwBcAG4ARQBOADIATwBcAG4AdAAgAE4AMgBPAFwAbgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAF8AewBjAH0AKABNAF8AewBiAHUAcgBuACwAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAbgBNAGIAdQByAG4AYwAgAD0AIABtAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAKQBcAG4ATgBDAEEARwBjACAAPQAgAG4AaQB0AHIAbwBnAGUAbgAgAGMAbwBuAHQAZQBuAHQAIABpAG4AIAB0AGgAZQAgAGEAYgBvAHYAZQAtAGcAcgBvAHUAbgBkACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACAATgAvAGsAZwAgAEQATQApAFwAbgBFAEYATgAyAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAG4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABmAHIAbwBtACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAIAAoAGsAZwAgAE4AMgBPAC8AawBnACAATgAyAE8AIABiAHUAcgBuAHQAKQBcAG4AQwBOADIATwAgAD0AIABmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXABuAGMAIAA9ACAAQwByAG8AcAAgAHQAeQBwAGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAGIAdQByAG4AYwAsACAATgBDAEEARwBjACwAIABFAEYATgAyAE8ALAAgAEMATgAyAE8ALABcAG4AIAAgACAAIABNAGIAdQByAG4AYwAgACoAIABOAEMAQQBHAGMAIAAqACAARQBGAE4AMgBPACAAKgAgAEMATgAyAE8AIAAqACAAMQAwAF4AKAAtADMAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBGAHUAbgBjAHQAaQBvAG4ATgBhAG0AZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAHQAaABlACAAYgB1AHIAbgBpAG4AZwAgAG8AZgAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAHMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgB0ACAATgAyAE8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANgAuADQALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAyACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AewBOADIATwB9AD0AXABcAHMAdQBtAF8AewBjAH0AKABNAF8AewBiAHUAcgBuACwAYwB9AFwAXAB0AGkAbQBlAHMAIABOAEMAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAgAEUARgBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAQwBfAHsATgAyAE8AfQBcAFwAdABpAG0AZQBzACAAMQAwAF4AewAtADMAfQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYgB1AHIAbgBjAFwAIgAsAFwAIgBtAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAGIAdQByAG4AdAAgAGYAbwByACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBDAEEARwBjAFwAIgAsAFwAIgBuAGkAdAByAG8AZwBlAG4AIABjAG8AbgB0AGUAbgB0ACAAaQBuACAAdABoAGUAIABhAGIAbwB2AGUALQBnAHIAbwB1AG4AZAAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGsAZwAgAE4ALwBrAGcAIABEAE0AKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQBGAE4AMgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAbgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAGYAcgBvAG0AIABiAHUAcgBuAGkAbgBnACAAbwBmACAAYwByAG8AcAAgAHIAZQBzAGkAZAB1AGUAcwAgACgAawBnACAATgAyAE8ALwBrAGcAIABOADIATwAgAGIAdQByAG4AdAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAE4AMgBPAFwAIgAsAFwAIgBmAGEAYwB0AG8AcgAgAHQAbwAgAGMAbwBuAHYAZQByAHQAIABlAGwAZQBtAGUAbgB0AGEAbAAgAG0AYQBzAHMAIABvAGYAIABuAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAAdABvACAAbQBvAGwAZQBjAHUAbABhAHIAIABtAGEAcwBzACAAKABkAGkAbQBlAG4AcwBpAG8AbgBsAGUAcwBzACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGMAXAAiACwAXAAiAEMAcgBvAHAAIAB0AHkAcABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABcAG4ATQBhAHMAcwAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAIABvAGYAIABjAHIAbwBwACAAYwAgAGIAdQByAG4AdABcAG4ATQBiAHUAcgBuAGMAXABuAGsAZwBcAG4ATQBfAHsAYgB1AHIAbgAsAGMAfQA9AFAAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAUgBfAHsAQQBHAGMAfQBcAFwAdABpAG0AZQBzACAAUwBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABEAE0AXwB7AGMAfQBcAFwAdABpAG0AZQBzACAAWgBfAHsAYwB9AFwAXAB0AGkAbQBlAHMAIABGAF8AewBjAH0AXABuAFAAYwAgAD0AIABhAG4AbgB1AGEAbAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGsAZwApAFwAbgBSAEEARwBjACAAPQAgAHIAZQBzAGkAZAB1AGUAIAB0AG8AIABjAHIAbwBwACAAcgBhAHQAaQBvACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQAvAGsAZwAgAGMAcgBvAHAAKQBcAG4AUwBjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAcwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAYgB1AHIAbgBpAG4AZwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBEAE0AYwAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAYwBvAG4AdABlAG4AdAAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAawBnACAAZAByAHkAIAB3AGUAaQBnAGgAdAAvAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlACkAXABuAFoAYwAgAD0AIABiAHUAcgBuAGkAbgBnACAAZQBmAGYAaQBjAGkAZQBuAGMAeQAgACgAcgBhAHQAaQBvACAAbwBmACAAZgB1AGUAbAAgAGIAdQByAG4AdAAgAHQAbwAgAGYAdQBlAGwAIABsAG8AYQBkACkAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGQAaQBtAGUAbgBzAGkAbwBuAGwAZQBzAHMAKQBcAG4ARgBjACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAbgBjACAAPQAgAEMAcgBvAHAAIAB0AHkAcABlAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADMAXwBfAE0AYQBzAHMATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBCAHUAcgBuAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAUABjACwAIABSAEEARwBjACwAIABTAGMALAAgAEQATQBjACwAIABaAGMALAAgAEYAYwAsAFwAbgAgACAAIAAgAFAAYwAgACoAIABSAEEARwBjACAAKgAgAFMAYwAgACoAIABEAE0AYwAgACoAIABaAGMAIAAqACAARgBjAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGEAcwBzACAAbwBmACAAcgBlAHMAaQBkAHUAZQAgAG8AZgAgAGMAcgBvAHAAIABjACAAYgB1AHIAbgB0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGIAdQByAG4AYwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA2AC4ANAAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMwBfAF8ATQBhAHMAcwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAEIAdQByAG4AdABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGIAdQByAG4ALABjAH0APQBQAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFIAXwB7AEEARwBjAH0AXABcAHQAaQBtAGUAcwAgAFMAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARABNAF8AewBjAH0AXABcAHQAaQBtAGUAcwAgAFoAXwB7AGMAfQBcAFwAdABpAG0AZQBzACAARgBfAHsAYwB9AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAzAF8AXwBNAGEAcwBzAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAQgB1AHIAbgB0AF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA3ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAYwBcACIALABcACIAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAKABrAGcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUgBBAEcAYwBcACIALABcACIAcgBlAHMAaQBkAHUAZQAgAHQAbwAgAGMAcgBvAHAAIAByAGEAdABpAG8AIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGsAZwAgAGMAcgBvAHAAIAByAGUAcwBpAGQAdQBlAC8AawBnACAAYwByAG8AcAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHIAZQBzAGkAZAB1AGUAcwAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgAHIAZQBtAGEAaQBuAGkAbgBnACAAYQB0ACAAYgB1AHIAbgBpAG4AZwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAE0AYwBcACIALABcACIAZAByAHkAIABtAGEAdAB0AGUAcgAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABjAHIAbwBwACAAdAB5AHAAZQAgAGMAIAAoAGsAZwAgAGQAcgB5ACAAdwBlAGkAZwBoAHQALwBrAGcAIABjAHIAbwBwACAAcgBlAHMAaQBkAHUAZQApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBaAGMAXAAiACwAXAAiAGIAdQByAG4AaQBuAGcAIABlAGYAZgBpAGMAaQBlAG4AYwB5ACAAKAByAGEAdABpAG8AIABvAGYAIABmAHUAZQBsACAAYgB1AHIAbgB0ACAAdABvACAAZgB1AGUAbAAgAGwAbwBhAGQAKQAgAG8AZgAgAGMAcgBvAHAAIAB0AHkAcABlACAAYwAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAGMAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHQAaABlACAAYQBuAG4AdQBhAGwAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAYwByAG8AcAAgAHQAeQBwAGUAIABjACAAdABoAGEAdAAgAGkAcwAgAGIAdQByAG4AdAAgACgAZABpAG0AZQBuAHMAaQBvAG4AbABlAHMAcwApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBjAFwAIgAsAFwAIgBDAHIAbwBwACAAdAB5AHAAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAiACwAIgB0AGUAeAB0ACIAOgAiAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBHAGUAdABGAHIAYQBjAFcARQBUAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUALABcAG4AIAAgACAAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtACwAXABuACAAIAAgACAATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABcAG4AIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwACwAXABuACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ARgByAGEAYwBXAEUAVABMAG8AbwBrAHUAcAAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgACAAIABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlACwATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUATABvAG8AawB1AHAALABMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAFYAYQBsAHUAZQBJAG4AVABhAGIAbABlAE4AdQBtAGIAZQByACgAXABuACAAIAAgACAAIAAgACAAIAAgACAAIAAgAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0ALABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEwAbwBvAGsAdQBwACwAUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBGAHIAYQBjAFcARQBUAEwAbwBvAGsAdQBwAFwAbgAgACAAIAAgACAAIAAgACAAKQAsAFwAbgAgACAAIAAgACAAIAAgACAASQBGACgATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUARgByAGEAYwBXAEUAVAAgACsAIABQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAEYAcgBhAGMAVwBFAFQAXAB1ADAAMAAzAGUAMAAsACAAMQAsACAAMAApAFwAbgAgACAAIAAgACkAKQA7AFwAbgBcAG4AXABuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAEMAYQBsAGMAdQBsAGEAdABlAEgAYQByAHYAZQBzAHQASQBuAGQAZQB4AFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAQwByAG8AcABUAHkAcABlACwAIABDAHIAbwBwAFQAeQBwAGUAQQByAHIAYQB5ACwAIABSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAEEAcgByAGEAeQAsAFwAbgAgACAAIAAgADEALwAoADEAKwBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAoAEMAcgBvAHAAVAB5AHAAZQAsACAAQwByAG8AcABUAHkAcABlAEEAcgByAGEAeQAsACAAUgBlAHMAaQBkAHUAZQBDAHIAbwBwAFIAYQB0AGkAbwBBAHIAcgBhAHkAKQApAFwAbgApADsAXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBSAGUAcwBpAGQAdQBlAEMAcgBvAHAAUgBhAHQAaQBvAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASABhAHIAdgBlAHMAdABJAG4AZABlAHgALABcAG4AIAAgACAAIAAoADEALQBIAGEAcgB2AGUAcwB0AEkAbgBkAGUAeAApAC8ASABhAHIAdgBlAHMAdABJAG4AZABlAHgAXABuACkAOwBcAG4AXABuAFwAbgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBDAGEAbABjAHUAbABhAHQAZQBGAHIAYQBjAHQAaQBvAG4AUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAFwAbgA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVABvAHQAYQBsAFIAZQBzAGkAZAB1AGUALAAgAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQALABcAG4AIAAgACAAIAAoAEEAbQBvAHUAbgB0AFIAZQBtAG8AdgBlAGQAKgAxADAAXgAzACkALwAoAFQAbwB0AGEAbABSAGUAcwBpAGQAdQBlACoAMQAwAF4AMwApAFwAbgApACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AUwBvAHUAcgBjAGUAIABkAGEAdABhACAARgBvAHIAIABTAHcAaQBuAGUAXABuAEUAeABjAGUAbAAgAG0AbwBkAHUAbABlACAAbgBhAG0AZQA6ACAAUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXABuAFYAUwBqAFwAbgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUwB3AGkAbgBlACAALQAgAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAKABWAFMAagApACAALQAgADIAMAAyADAAIAB0AG8AIAAyADAAMgA0AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4ANgAuADEAOgAgAFMAdwBpAG4AZQAgAC0AIABJAG4AdABhAGsAZQAgAGEAbgBkACAAbQBhAG4AdQByAGUAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwAgAGQAZQByAGkAdgBlAGQAIABmAHIAbwBtACAAUABpAGcAQgBhAGwAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAE8AbgBsAHkAIAB1AHMAZQBzACAAZABhAHQAYQAgAGYAbwByACAAMgAwADIAMAAtADIAMAAyADQALgAgAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AFMAdQBjAGsAZQByAHMAXAB1ADAAMAAyADcALAAgAFwAdQAwADAAMgA3AFcAZQBhAG4AZQByAHMAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AEcAcgBvAHcAZQByAHMAXAB1ADAAMAAyADcAIABjAGwAYQBzAHMAZQBzACAAdwBoAGkAYwBoACAAaABhAHYAZQAgAHQAaABlACAAcwBhAG0AZQAgAHYAYQBsAHUAZQBzACAAYQBzACAAXAB1ADAAMAAyADcAUwBsAGEAdQBnAGgAdABlAHIAIABwAGkAZwBzAFwAdQAwADAAMgA3AC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAOAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBsAGEAcwBzAFwAIgAsACAAXAAiAFYAUwBqAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAG8AYQByAHMAXAAiACwAIAAwAC4ANAAwADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAbwB3AHMAXAAiACwAIAAwAC4ANAA2ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEcAaQBsAHQAcwBcACIALAAgADAALgA1ADUAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBsAGEAdQBnAGgAdABlAHIAIABwAGkAZwBzAFwAIgAsACAAMAAuADMAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHUAYwBrAGUAcgBzAFwAIgAsACAAMAAuADMAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBXAGUAYQBuAGUAcgBzAFwAIgAsACAAMAAuADMAOQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBHAHIAbwB3AGUAcgBzAFwAIgAsACAAMAAuADMAOQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4AQgAwAFwAbgBtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIABvAGYAIABtAGUAdABoAGEAbgBlACAAcABlAHIAIABrAGkAbABvAGcAcgBhAG0AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCADAAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAG0AMwAgAEMASAA0ACAALwAgAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEkAUABDAEMAIAAoADIAMAAxADkAKQAsACAAQwBoAGEAcAB0AGUAcgAgADEAMAAgAFsANABdAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8ATQBlAHQAaABhAG4AZQBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAGUAdABoAGEAbgBlAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAMAAuADEAOQApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBcAG4AVABhAGIAbABlACAAQQAuADEALgA2AC4ANAA6ACAAUwB3AGkAbgBlACAALQAgAE0AQwBGAHMAIAAoAE0AQwBGAGkAbQApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdAAgAHMAeQBzAHQAZQBtAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADYALgA0ADoAIABTAHcAaQBuAGUAIAATICAATQBDAEYAcwAgACgATQBDAEYAaQBtACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBNAE0AUwBfAE0AQwBGAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQAgAEQAQQBUAEEAOgAgAEEAZABkAGUAZAAgAGMAbwBsAHUAbQBuAHMAIABmAG8AcgAgAEEAQwBUACwAIABzAHAAbABpAHQAIABRAEwARAAgAGEAbgBkACAATgBUAC4AIABBAGQAZABlAGQAIABlAHgAdAByAGEAIABjAG8AbAB1AG0AbgAgAHcAaQB0AGgAIABNAE0AUwAgAG4AYQBtAGUAcwAgAHQAaABhAHQAIABtAGEAdABjAGgAIABOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAE0ATQBTAF8ATQBDAEYAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA4ACwAIAAxADAALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVABBAFMAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB1AHQAZABvAG8AcgAgACgARAByAHkAIABsAG8AdAApAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMwAsACAAMAAuADAAMwAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGUAZQBwACAAbABpAHQAdABlAHIAXAAiACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIAAwAC4AMAA0ACwAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAHQAbwBjAGsAcABpAGwAZQAgACgAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQApAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAZgBmAGwAdQBlAG4AdAAgAHAAbwBuAGQAIAAoAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgApAFwAIgAsACAAMAAuADcANQAsACAAMAAuADcANQAsACAAMAAuADcAOAAsACAAMAAuADcAOAAsACAAMAAuADcANQAsACAAMAAuADcAMAAsACAAMAAuADcANAAsACAAMAAuADcANgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAZABpAGcAZQBzAHQAZQByACAALwAgAEMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBcACIALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAXAAiAEQAaQBnAGUAcwB0AGUAcgAgAC8AIABjAG8AdgBlAHIAZQBkACAAbABhAGcAbwBvAG4AcwBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGgAbwByAHQAIABIAFIAVAAgAHQAYQBuAGsAIABzAHQAbwByAGEAZwBlACAAXAB1ADAAMAAzAGMAIAAxACAAbQBvAG4AdABoACAAKABwAGkAdAAgAHMAdABvAHIAYQBnAGUAKQBcACIALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADMALAAgADAALgAwADMALAAgAFwAIgBQAGkAdAAgAHMAdABvAHIAYQBnAGUAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBTAHcAaQBuAGUAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXABuADQALgA1ACAAUwB3AGkAbgBlACAARgBpAGcAdQByAGUAIAA0AC4AOABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBTAHcAaQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUwB3AGkAbgBlAF8AUAByAG8AZAB1AGMAdABpAG8AbgBTAHkAcwB0AGUAbQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1ACAAUwB3AGkAbgBlACAARgBpAGcAdQByAGUAIAA0AC4AOABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFMAdwBpAG4AZQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAbwBuAHYAZQBuAHQAaQBvAG4AYQBsACAAaABvAHUAcwBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABlAGUAcAAgAGwAaQB0AHQAZQByACAAaABvAHUAcwBpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATwB1AHQAZABvAG8AcgAvAGYAcgBlAGUAIAByAGEAbgBnAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8ATQBhAG4AdQByAGUATQBhAG4AYQBnAGUAbQBlAG4AdABfAFMAdwBpAG4AZQBfAE0AZQB0AGgAYQBuAGUAIgAsACIAdABlAHgAdAAiADoAIgAvACoAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA1ADoAIABTAHcAaQBuAGUAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA1AC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAUICAATQBhAG4AdQByAGUAIABNAGUAdABoAGEAbgBlACAAUwB3AGkAbgBlAFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAEUAQwBIADQAXABuAHQAIABDAEgANABcAG4AewBFAH0AXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXwB7AGoAfQAoAEQAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAbQBqAH0AXABcAHQAaQBtAGUAcwAgAE4AXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcAG4ARABqACAAPQAgAGwAZQBuAGcAdABoACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABvAGYAIABzAHcAaQBuAGUAIAA6ACAAZABhAHkAcwBcAG4ATQBtAGoAIAA9ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzACAAOgAgAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBOAGoAIAA9ACAAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAHMAdwBpAG4AZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIAA6ACAAaABlAGEAZABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABqACwAIABNAG0AagAsACAATgBqACwAXABuACAAIAAgACAARABqACAAKgAgAE0AbQBqACAAKgAgAE4AagAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAewBFAH0AXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXwB7AGoAfQAoAEQAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAbQBqAH0AXABcAHQAaQBtAGUAcwAgAE4AXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAagBcACIALABcACIAbABlAG4AZwB0AGgAIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAG8AZgAgAHMAdwBpAG4AZQAgADoAIABkAGEAeQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG0AagBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwB3AGkAbgBlACAAYwBsAGEAcwBzACAAOgAgAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGoAXAAiACwAXAAiAG4AdQBtAGIAZQByAHMAIABvAGYAIABzAHcAaQBuAGUAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAOgAgAGgAZQBhAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXABuAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHQAaABlACAAbQBhAG4AdQByAGUAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAbwBmACAAcwB3AGkAbgBlAFwAbgBNAG0AagBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AG0AagB9AD0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0ATQBfAHsAagBtAFQAfQBcAG4ATQBqAG0AVAAgAD0AIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAHAAZQByACAAYwBsAGEAcwBzACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAGoAbQBUACwAXABuACAAIAAgACAAUwBVAE0AKABNAGoAbQBUACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAGoAbQBUADEALAAgAE0AagBtAFQAMgAsAFwAbgAgACAAIAAgACAAUwBVAE0AKABNAGoAbQBUADEALAAgAE0AagBtAFQAMgApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAHQAaABlACAAbQBhAG4AdQByAGUAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAbwBmACAAcwB3AGkAbgBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBtAGoAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBtAGoAfQA9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9AE0AXwB7AGoAbQBUAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AagBtAFQAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAcABlAHIAIABjAGwAYQBzAHMALAAgAE0ATQBTACwAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAOgAgAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAUwBwAGwAaQB0ACAAdgBhAHIAaQBhAGIAbABlACAATQBqAG0AIABpAG4AdABvACAATQBqAG0AVAAxACAAYQBuAGQAIABNAGoAbQBUADIAIABmAG8AcgAgAHMAdABhAGcAZQAgADEAIABhAG4AZAAgADIAIABNAE0AUwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcAG4ATQBpAGoAbQBUADEAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBpAGoAbQAsAFQAPQAxAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBqACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAcwB3AGkAbgBlACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAEYAVgBTAGoAbQBUADEAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAaQBtACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdABlACAAegBvAG4AZQAgAGEAbgBkACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4AcgBoAG8AIAA9ACAAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAGoALAAgAEYAVgBTAGoAbQBUADEALAAgAE0AQwBGAGkAbQAsACAAQgBPACwAIAByAGgAbwAsAFwAbgAgACAAIAAgAFYAUwBqACAAKgAgAEYAVgBTAGoAbQBUADEAIAAqACAATQBDAEYAaQBtACAAKgAgAEIATwAgACoAIAByAGgAbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AaQBqAG0AVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBpAGoAbQAsAFQAPQAxAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADUALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAcwB3AGkAbgBlACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAVgBTAGoAbQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAGkAbQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AGUAIAB6AG8AbgBlACAAYQBuAGQAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIABvAHQAaABlAHIAIAB0AGgAYQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcAG4ARgBWAFMAagBtAFQAMQBcAG4AZgByAGEAYwB0AGkAbwBuAFwAbgBGAFYAUwBfAHsAagBtACwAVAA9ADEAfQA9AE0ATQBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0AUwBTAF8AewBtAH0AKQBcAG4ATQBNAFMAagBtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAIABmAG8AcgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABwAHIAaQBvAHIAIAB0AG8AIABzAG8AbABpAGQAIABzAGUAcABhAHIAYQB0AGkAbwBuACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AUwBTAG0AIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABzAGUAcABhAHIAYQB0AGUAZAAgAHQAbwAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABmAG8AcgAgAGUAYQBjAGgAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANABfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUAByAGkAbQBhAHIAeQBTAHkAcwB0AGUAbQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE0AUwBqAG0AVAAxACwAIABTAFMAbQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgAHMAcwBtACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABTAFMAbQApACwAIABTAFMAbQAsACAAMAApACwAXABuACAAIAAgACAAIAAgAE0ATQBTAGoAbQBUADEAIAAqACAAKAAxACAALQAgAHMAcwBtACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAG8AdABoAGUAcgAgAHQAaABhAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAFYAUwBqAG0AVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA1AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA0AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBQAHIAaQBtAGEAcgB5AFMAeQBzAHQAZQBtAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagBtACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACgAMQAtAFMAUwBfAHsAbQB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAagBtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAE0ATQBTACAAZgBvAHIAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAcAByAGkAbwByACAAdABvACAAcwBvAGwAaQBkACAAcwBlAHAAYQByAGEAdABpAG8AbgAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAUwBtAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADQAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFAAcgBpAG0AYQByAHkAUwB5AHMAdABlAG0AXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAQQBkAGQAZQBkACAAYwBoAGUAYwBrACAAdABvACAAYwBvAG4AdgBlAHIAdAAgAFwAdQAwADAAMgA3AE4ALwBBAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlACAAdABvACAAegBlAHIAbwAuAFwAIgApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXABuAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcAG4ARgBWAFMAagBtADQAVAAxAFwAbgBmAHIAYQBjAHQAaQBvAG4AXABuAEYAVgBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9AD0ATQBNAFMAXwB7AGoALABtAD0ANAAsAFQAPQAxAH0AKwAoAE0ATQBTAF8AewBqACwAbQA9ADEALAA3ACwAOQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQB9ACkAXABuAE0ATQBTAGoAbQA0AFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBNAE0AUwBqAG0AMQA3ADkAVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAATQBNAFMAIAAxACwAIAA3ACwAIABhAG4AZAAgADkAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBTAFMAbQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHMAZQBwAGEAcgBhAHQAZQBkACAAdABvACAAcwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQAgAGYAbwByACAAZQBhAGMAaAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE0AUwBqAG0ANABUADEALAAgAE0ATQBTAGoAbQAxADcAOQBUADEALAAgAFMAUwBtACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtADQAVAAxACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABNAE0AUwBqAG0ANABUADEAKQAsACAATQBNAFMAagBtADQAVAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtADEANwA5AFQAMQAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgATQBNAFMAagBtADEANwA5AFQAMQApACwAIABNAE0AUwBqAG0AMQA3ADkAVAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAUwBTAG0ALAAgAEkARgAoAEkAUwBOAFUATQBCAEUAUgAoAFMAUwBtACkALAAgAFMAUwBtACwAIAAwACkALABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtADQAVAAxACAAKwAgACgATQBNAFMAagBtADEANwA5AFQAMQAgACoAIABTAFMAbQApAFwAbgAgACAAIAAgACkAXABuACAAIAAgACAAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAE0AUwBqAG0ANABUADEALABcAG4AIAAgACAAIABNAE0AUwBqAG0AVAAxAF8AMQAsACAATQBNAFMAagBtAFQAMQBfADIALAAgAE0ATQBTAGoAbQBUADEAXwAzACwAIABNAE0AUwBqAG0AVAAxAF8ANAAsACAATQBNAFMAagBtAFQAMQBfADUALABcAG4AIAAgACAAIABTAFMAagBtAFQAMQBfADEALAAgAFMAUwBqAG0AVAAxAF8AMgAsACAAUwBTAGoAbQBUADEAXwAzACwAIABTAFMAagBtAFQAMQBfADQALAAgAFMAUwBqAG0AVAAxAF8ANQAsAFwAbgAgACAAIAAgAEwARQBUACgAXABuACAAIAAgACAAIAAgAE0ATQBTAGoAbQA0AFQAMQAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgATQBNAFMAagBtADQAVAAxACkALAAgAE0ATQBTAGoAbQA0AFQAMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgAE0ATQBTAGoAbQBUADEAXwAxACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABNAE0AUwBqAG0AVAAxAF8AMQApACwAIABNAE0AUwBqAG0AVAAxAF8AMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgAE0ATQBTAGoAbQBUADEAXwAyACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABNAE0AUwBqAG0AVAAxAF8AMgApACwAIABNAE0AUwBqAG0AVAAxAF8AMgAsACAAMAApACwAXABuACAAIAAgACAAIAAgAE0ATQBTAGoAbQBUADEAXwAzACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABNAE0AUwBqAG0AVAAxAF8AMwApACwAIABNAE0AUwBqAG0AVAAxAF8AMwAsACAAMAApACwAXABuACAAIAAgACAAIAAgAE0ATQBTAGoAbQBUADEAXwA0ACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABNAE0AUwBqAG0AVAAxAF8ANAApACwAIABNAE0AUwBqAG0AVAAxAF8ANAAsACAAMAApACwAXABuACAAIAAgACAAIAAgAE0ATQBTAGoAbQBUADEAXwA1ACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABNAE0AUwBqAG0AVAAxAF8ANQApACwAIABNAE0AUwBqAG0AVAAxAF8ANQAsACAAMAApACwAXABuACAAIAAgACAAIAAgAFMAUwBqAG0AVAAxAF8AMQAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAUwBTAGoAbQBUADEAXwAxACkALAAgAFMAUwBqAG0AVAAxAF8AMQAsACAAMAApACwAXABuACAAIAAgACAAIAAgAFMAUwBqAG0AVAAxAF8AMgAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAUwBTAGoAbQBUADEAXwAyACkALAAgAFMAUwBqAG0AVAAxAF8AMgAsACAAMAApACwAXABuACAAIAAgACAAIAAgAFMAUwBqAG0AVAAxAF8AMwAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAUwBTAGoAbQBUADEAXwAzACkALAAgAFMAUwBqAG0AVAAxAF8AMwAsACAAMAApACwAXABuACAAIAAgACAAIAAgAFMAUwBqAG0AVAAxAF8ANAAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAUwBTAGoAbQBUADEAXwA0ACkALAAgAFMAUwBqAG0AVAAxAF8ANAAsACAAMAApACwAXABuACAAIAAgACAAIAAgAFMAUwBqAG0AVAAxAF8ANQAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAUwBTAGoAbQBUADEAXwA1ACkALAAgAFMAUwBqAG0AVAAxAF8ANQAsACAAMAApACwAXABuACAAIAAgACAAIAAgAE0ATQBTAGoAbQA0AFQAMQAgACsAIABcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8AMQAgACoAIABTAFMAagBtAFQAMQBfADEAKQAgACsAIABcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8AMgAgACoAIABTAFMAagBtAFQAMQBfADIAKQAgACsAIABcAG4AIAAgACAAIAAgACAAKABNAE0AUwBqAG0AVAAxAF8AMwAgACoAIABTAFMAagBtAFQAMQBfADMAKQAgACsAXABuACAAIAAgACAAIAAgACgATQBNAFMAagBtAFQAMQBfADQAIAAqACAAUwBTAGoAbQBUADEAXwA0ACkAIAArAFwAbgAgACAAIAAgACAAIAAoAE0ATQBTAGoAbQBUADEAXwA1ACAAKgAgAFMAUwBqAG0AVAAxAF8ANQApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABpAG4AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBWAFMAagBtADQAVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA1ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA1AF8ARgByAGEAYwB0AGkAbwBuAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBTAG8AbABpAGQAUwB0AG8AcgBhAGcAZQBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAVgBTAF8AewBqACwAbQA9ADQALABUAD0AMQB9AD0ATQBNAFMAXwB7AGoALABtAD0ANAAsAFQAPQAxAH0AKwAoAE0ATQBTAF8AewBqACwAbQA9ADEALAA3ACwAOQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADUAXwBGAHIAYQBjAHQAaQBvAG4AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFMAbwBsAGkAZABTAHQAbwByAGEAZwBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBWAFMAXwB7AGoALABtAD0ANAAsAFQAPQAxAH0APQBNAE0AUwBfAHsAagAsAG0APQA0ACwAVAA9ADEAfQArACgATQBNAFMAXwB7AGoALABtAD0AMQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAFMAUwBfAHsAbQA9ADEALABUAD0AMQB9ACkAKwAoAE0ATQBTAF8AewBqACwAbQA9ADcALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABTAFMAXwB7AG0APQA3ACwAVAA9ADEAfQApACsAKABNAE0AUwBfAHsAagAsAG0APQA5ACwAVAA9ADEAfQBcAFwAdABpAG0AZQBzACAAUwBTAF8AewBtAD0AOQAsAFQAPQAxAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAagBtADQAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBqAG0AMQA3ADkAVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAE0ATQBTACAAMQAsACAANwAsACAAYQBuAGQAIAA5ACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBTAG0AXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAcwBlAHAAYQByAGEAdABlAGQAIAB0AG8AIABzAG8AbABpAGQAIABzAHQAbwByAGEAZwBlACAAZgBvAHIAIABlAGEAYwBoACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANQBfAEYAcgBhAGMAdABpAG8AbgBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAUwBvAGwAaQBkAFMAdABvAHIAYQBnAGUAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAUwBwAGwAaQB0ACAAZQBxAHUAYQB0AGkAbwBuACAAZgBvAHIAIABNAE0AUwBtAD0AMQAsADcALAA5ACAAaQBuAHQAbwAgAHMAZQBwAGEAcgBhAHQAZQAgAGkAdABlAG0AcwAgAHQAbwAgAGEAbABsAG8AdwAgAGYAbwByACAAYwBhAGwAYwB1AGwAYQB0AGkAbwBuAFwAIgApADsAXABuACAAIABcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAGUAYQBjAGgAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4ATQBpAGoAbQBUADIAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBpAGoAbQAsAFQAPQAyAH0APQBWAFMAVABfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBUAGoAbQBUADIAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAEIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgBNAE0AUwBqAG0AVAAyACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBNAEMARgBpAG0AIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AGUAIAB6AG8AbgBlACAAYQBuAGQAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAHIAaABvACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcAG4AaQAgAD0AIABzAHQAYQB0AGUAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAVABqAG0AVAAyACwAIABCAE8ALAAgAE0ATQBTAGoAbQBUADIALAAgAE0AQwBGAGkAbQAsACAAcgBoAG8ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIABWAFMAVABqAG0AVAAyACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABWAFMAVABqAG0AVAAyACkALAAgAFYAUwBUAGoAbQBUADIALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABNAE0AUwBqAG0AVAAyACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABNAE0AUwBqAG0AVAAyACkALAAgAE0ATQBTAGoAbQBUADIALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABWAFMAVABqAG0AVAAyACAAKgAgAEIATwAgACoAIABNAE0AUwBqAG0AVAAyACAAKgAgAE0AQwBGAGkAbQAgACoAIAByAGgAbwBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANgBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIABlAGEAYwBoACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AaQBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA2AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA2ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBpAGoAbQAsAFQAPQAyAH0APQBWAFMAVABfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADYAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAFQAagBtAFQAMgBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAagBtAFQAMgBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAGkAbQBcACIALABcACIAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AGUAIAB6AG8AbgBlACAAYQBuAGQAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAXAAiAHMAdABhAHQAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBcAG4AVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AHIAYQBuAHMAZgBlAHIAcgBlAGQAIAB0AG8AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcAG4AVgBTAFQAaQBqAG0AVAAyAFwAbgBrAGcAIABWAFMAXABuAFYAUwBUAF8AewBpAGoAbQAsAFQAPQAyAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBWAFMATABfAHsAbQAsAFQAPQAxAH0AKQBcAG4AVgBTAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABzAHcAaQBuAGUAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4ARgBWAFMAagBtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGkAbgAgAGUAYQBjAGgAIABwAHIAaQBtAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBWAFMATABtAFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAGoALAAgAEYAVgBTAGoAbQBUADEALAAgAFYAUwBMAG0AVAAxACwAXABuACAAIAAgACAAVgBTAGoAIAAqACAARgBWAFMAagBtAFQAMQAgACoAIAAoADEAIAAtACAAVgBTAEwAbQBUADEAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAFQAaQBqAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAFYAUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADUALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA3ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA1AF8AMQBfADEAXwBfADcAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFMAdABhAGcAZQAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANQBfADEAXwAxAF8AXwA3AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABTAHQAYQBnAGUAMgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBUAF8AewBpAGoAbQAsAFQAPQAyAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAARgBWAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBWAFMATABfAHsAbQAsAFQAPQAxAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADUAXwAxAF8AMQBfAF8ANwBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAUwB0AGEAZwBlADIAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAGoAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAcwB3AGkAbgBlACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAVgBTAGoAbQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBMAG0AVAAxAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABkAHUAcgBpAG4AZwAgAHMAdABvAHIAYQBnAGUAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAIgB9ACwAewAiAHAAYQB0AGgAIgA6ACIALwBwAHIAbwBqAGUAYwB0AHMALwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADcALgAxADoAIABQAG8AdQBsAHQAcgB5ACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBQAG8AdQBsAHQAcgB5ACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADcALgAxADoAIABQAG8AdQBsAHQAcgB5ACAALQAgAEQAaQBlAHQAIABwAHIAbwBwAGUAcgB0AGkAZQBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAANQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgB1AHQAcgBpAGUAbgB0ACAAYQBuAGEAbAB5AHMAaQBzAFwAIgAsACAAXAAiAEwAYQB5AGUAcgBzAFwAIgAsACAAXAAiAE0AZQBhAHQAIABjAGgAaQBjAGsAZQBuACAAZwByAG8AdwBlAHIAcwBcACIALAAgAFwAIgBNAGUAYQB0ACAAYwBoAGkAYwBrAGUAbgAgAGIAcgBlAGUAZABlAHIAXAAiACwAIABcACIATQBlAGEAdAAgAG8AdABoAGUAcgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGkAbgB0AGEAawBlACAAKABrAGcALwBoAGUAYQBkAC8AZABhAHkAKQBcACIALAAgADAALgAwADgANgAsACAAMAAuADAAOQAzACwAIAAwAC4AMQAwADMALAAgADAALgAwADkAMwA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5AFwAIgAsACAAMAAuADgAMAAsACAAMAAuADgAMAAsACAAMAAuADgAMAAsACAAMAAuADgAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAHIAdQBkAGUAIABwAHIAbwB0AGUAaQBuAFwAIgAsACAAMAAuADEAOQAsACAAMAAuADIAMwAsACAAMAAuADEAOQAsACAAMAAuADIAMwA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAGkAdAByAG8AZwBlAG4AIAByAGUAdABlAG4AdABpAG8AbgAgAHIAYQB0AGUAXAAiACwAIAAwAC4AMwA1ACwAIAAwAC4ANAA3ACwAIAAwAC4AMwAyACwAIAAwAC4ANAA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AYQBuAHUAcgBlACAAYQBzAGgAXAAiACwAIAAwAC4AMQA4ACwAIAAwAC4AMQA1ACwAIAAwAC4AMQA4ACwAIAAwAC4AMQA1AFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAE0AQwBGAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADcALgA0ADoAIABQAG8AdQBsAHQAcgB5ACAALQAgAE0AQwBGAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBNAEMARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUABvAHUAbAB0AHIAeQAgAC0AIABNAEMARgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAE0AQwBGAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBDAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgA3AC4ANAA6ACAAUABvAHUAbAB0AHIAeQAgAC0AIABNAEMARgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAE0AQwBGAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA1ACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAcABsAGkAdAAgAE4AUwBXACAAYQBuAGQAIABBAEMAVAAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIABzAHQAYQB0AGUAcwAuACAAUwBwAGwAaQB0ACAAUQBMAEQAIABhAG4AZAAgAE4AVAAgAGkAbgB0AG8AIABzAGUAcABhAHIAYQB0AGUAIABzAHQAYQB0AGUAcwAuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBJAG4AYwBsAHUAZABlAGQAIAB2AGEAbAB1AGUAcwAgAGYAbwByACAAZQBhAGMAaAAgAHMAdABhAHQAZQAgAHcAaABlAG4AIABcAHUAMAAwADIANwBBAGwAbAAgAHMAdABhAHQAZQBzAFwAdQAwADAAMgA3ACAAdgBhAGwAdQBlACAAaQBzACAAZwBpAHYAZQBuAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAdQBwAGwAaQBjAGEAdABlAGQAIABcAHUAMAAwADIANwBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAB1ADAAMAAyADcAIAByAG8AdwAgAGYAbwByACAATgBJAFIAIABNAE0AUwAgAFwAdQAwADAAMgA3AEIAZQBsAHQAIABtAGEAbgB1AHIAZQAgAHIAZQBtAG8AdgBhAGwAXAB1ADAAMAAyADcAIABhAG4AZAAgAFwAdQAwADAAMgA3AE0AYQBuAHUAcgBlACAAcwB0AG8AcgBlAGQAIABpAG4AIABoAG8AdQBzAGUAXAB1ADAAMAAyADcAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAE0AQwBGAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADEAMAAsACAAMQAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIAQQBsAGwAIABzAHQAYQB0AGUAcwBcACIALAAgAFwAIgBOAFMAVwBcACIALAAgAFwAIgBBAEMAVABcACIALAAgAFwAIgBRAEwARABcACIALAAgAFwAIgBOAFQAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAUwBBAFwAIgAsACAAXAAiAFcAQQBcACIALAAgAFwAIgBUAEEAUwBcACIALAAgAFwAIgBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABsAGkAdAB0AGUAcgBcACIALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAXAAiACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIABcACIAQgBlAGwAdAAgAG0AYQBuAHUAcgBlACAAcgBlAG0AbwB2AGEAbABcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByAFwAIgAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAMAAuADAAMQA1ACwAIAAwAC4AMAAxADUALAAgADAALgAwADEANQAsACAAXAAiAE0AYQBuAHUAcgBlACAAcwB0AG8AcgBlAGQAIABpAG4AIABoAG8AdQBzAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAYQBzAHQAdQByAGUAIAByAGEAbgBnAGUAIABhAG4AZAAgAHAAYQBkAGQAbwBjAGsAXAAiACwAIABcACIAbgAvAGEAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAzACwAIAAwAC4AMAAzACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIAUABhAHMAdAB1AHIAZQAgAHIAYQBuAGcAZQAgAGEAbgBkACAAcABhAGQAZABvAGMAawBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgADAALgAwADIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBDAG8AbQBwAG8AcwB0AGkAbgBnACAAKABwAGEAcwBzAGkAdgBlACAAdwBpAG4AZAByAG8AdwApAFwAIgAsACAAXAAiAG4ALwBhAFwAIgAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMQAsACAAMAAuADAAMAA1ACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABkAGkAZwBlAHMAdABlAHIAIAAvACAAQwBvAHYAZQByAGUAZAAgAHAAbwBuAGQAXAAiACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIAAwAC4AMQAsACAAMAAuADEALAAgADAALgAxACwAIABcACIARABpAGcAZQBzAHQAZQByACAALwAgAGMAbwB2AGUAcgBlAGQAIABsAGEAZwBvAG8AbgBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAHAAcgBvAGMAZQBzAHMAaQBuAGcAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABwAHIAbwBjAGUAcwBzAGkAbgBnAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgAgAHQAbwAgAHMAbwBpAGwAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIAAwACwAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAE0AQwBGAF8ATgBvAHQAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcAHUAMAAwADIANwBQAGEAcwB0AHUAcgBlACAAcgBhAG4AZwBlACAAYQBuAGQAIABwAGEAZABkAG8AYwBrAFwAdQAwADAAMgA3ACAAYQBwAHAAbABpAGUAcwAgAE0AQwBGACAAZgBvAHIAIABkAHIAeQBsAG8AdAAuAFwAIgApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAFwAbgBNAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgAHAAZQByACAAcABvAHUAbAB0AHIAeQAgAGMAbABhAHMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAbwB1AGwAdAByAHkAIAAtACAATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIABwAGUAcgAgAGMAbABhAHMAcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANgAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUADoAIABQAG8AdQBsAHQAcgB5ACAALQAgAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAcABlAHIAIABjAGwAYQBzAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAbwB1AGwAdAByAHkAIABjAGwAYQBzAHMAXAAiACwAIABcACIAQgAwAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAGEAeQBlAHIAcwBcACIALAAgADAALgAzADkAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGUAYQB0ACAAYwBoAGkAYwBrAGUAbgBzAFwAIgAsACAAMAAuADMANgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXABuAFAAbwB1AGwAdAByAHkAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUABvAHUAbAB0AHIAeQAgAC0AIABQAHIAbwBkAHUAYwB0AGkAbwBuACAAcwB5AHMAdABlAG0AcwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADYAIABQAG8AdQBsAHQAcgB5AFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFAAcgBvAGQAdQBjAHQAaQBvAG4AUwB5AHMAdABlAG0AcwBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBQAHIAbwBkAHUAYwB0AGkAbwBuAFMAeQBzAHQAZQBtAHMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAHMAeQBzAHQAZQBtAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBGAHIAZQBlACAAcgBhAG4AZwBlAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIAYQByAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEMAYQBnAGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBWAFMATABcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIABsAG8AcwB0ACAAaQBuACAAdABoAGUAIABwAHIAaQBtAGEAcgB5ACAATQBNAFMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBWAFMATABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUABvAHUAbAB0AHIAeQAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBWAFMATABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABvAHUAbAB0AHIAeQBfAFYAUwBMAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA2AC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAG8AdQBsAHQAcgB5AF8AVgBTAEwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6ACAAVABhAGIAbABlACAAZwBlAG4AZQByAGEAdABlAGQAIABmAHIAbwBtACAAbABpAG4AZQAgAGkAdABlAG0AcwAuACAAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuACAAYwBvAGwAdQBtAG4AXAB1ADAAMAAyADcALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAbwB1AGwAdAByAHkAXwBWAFMATABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA0ACwAIAAzACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBcACIALAAgAFwAIgBWAFMATABcACIALAAgAFwAIgBOAEkAUgAgAGQAZQBmAGkAbgBpAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFAAbwB1AGwAdAByAHkAIABtAGEAbgB1AHIAZQAgAHcAaQB0AGgAIABsAGkAdAB0AGUAcgBcACIALAAgADAALgA4ADUALAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoACAAYgBlAGQAZABpAG4AZwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUABvAHUAbAB0AHIAeQAgAG0AYQBuAHUAcgBlACAAdwBpAHQAaABvAHUAdAAgAGwAaQB0AHQAZQByACAALQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlAFwAIgAsACAAMAAuADgALAAgAFwAIgBNAGEAbgB1AHIAZQAgAHMAdABvAHIAZQBkACAAaQBuACAAaABvAHUAcwBlAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAG8AdQBsAHQAcgB5ACAAbQBhAG4AdQByAGUAIAB3AGkAdABoAG8AdQB0ACAAbABpAHQAdABlAHIAIAAtACAAYgBlAGwAdAAgAHIAZQBtAG8AdgBhAGwAXAAiACwAIAAxACwAIABcACIAQgBlAGwAdAAgAG0AYQBuAHUAcgBlACAAcgBlAG0AbwB2AGEAbABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBQAG8AdQBsAHQAcgB5AF8ATQBlAHQAaABhAG4AZQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADYAOgAgAFAAbwB1AGwAdAByAHkAXABuAD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0AXABuADQALgA2AC4AMQAuADEAIABNAGUAdABoAG8AZAAgADEAIAAtACAATQBhAG4AdQByAGUAIABNAGUAdABoAGEAbgBlACAAUABvAHUAbAB0AHIAeQBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4AKgAvAFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBcAG4AVABvAHQAYQBsACAAYQBuAG4AdQBhAGwAIABtAGUAdABoAGEAbgBlACAAZQBtAGkAcwBzAGkAbwBuAHMAIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABtAGEAbgBhAGcAZQBtAGUAbgB0AFwAbgBFAEMASAA0AFwAbgB0ACAAQwBIADQAXABuAHsARQB9AF8AewBDAEgANAB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBrAH0AKABEAF8AewBqAGsAfQBcAFwAdABpAG0AZQBzACAATQBfAHsAbQBqAGsAfQBcAFwAdABpAG0AZQBzACAATgBfAHsAagBrAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAEQAagBrACAAPQAgAGQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAYQBuAGQAIABzAHUAYgBjAGwAYQBzAHMAIABvAGYAIABwAG8AdQBsAHQAcgB5ACAAOgAgAGQAYQB5AHMAXABuAE0AbQBqAGsAIAA9ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAYwBsAGEAcwBzACAAYQBuAGQAIABzAHUAYgBjAGwAYQBzAHMAIAA6ACAAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE4AagBrACAAPQAgAG4AdQBtAGIAZQByAHMAIABvAGYAIABwAG8AdQBsAHQAcgB5ACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAGEAbgBkACAAcwB1AGIAYwBsAGEAcwBzACAAOgAgAGgAZQBhAGQAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAEQAagBrACwAIABNAG0AagBrACwAIABOAGoAawAsAFwAbgAgACAAIAAgAFMAVQBNAFAAUgBPAEQAVQBDAFQAKABEAGoAawAsACAATQBtAGoAawAsACAATgBqAGsAKQAgACoAIAAxADAAIABeACAALQAzAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARQBDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAdAAgAEMASAA0AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADYALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAxACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAewBFAH0AXwB7AEMASAA0AH0APQBcAFwAcwB1AG0AXwB7AGoAfQBcAFwAcwB1AG0AXwB7AGsAfQAoAEQAXwB7AGoAawB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBtAGoAawB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAGsAfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAagBrAFwAIgAsAFwAIgBkAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAbwBmACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAGEAbgBkACAAcwB1AGIAYwBsAGEAcwBzACAAbwBmACAAcABvAHUAbAB0AHIAeQAgADoAIABkAGEAeQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAG0AagBrAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABhAG4AZAAgAHMAdQBiAGMAbABhAHMAcwAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBqAGsAXAAiACwAXAAiAG4AdQBtAGIAZQByAHMAIABvAGYAIABwAG8AdQBsAHQAcgB5ACAAaQBuACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAGEAbgBkACAAcwB1AGIAYwBsAGEAcwBzACAAOgAgAGgAZQBhAGQAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAQQBuAGQAUwB1AGIAYwBsAGEAcwBzAFwAbgBNAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIAB0AGgAZQAgAG0AYQBuAHUAcgBlACAAbwBmACAAcABvAHUAbAB0AHIAeQBcAG4ATQBtAGoAawBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AG0AagBrAH0APQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQBNAF8AewBqAGsAbQBUAH0AXABuAE0AagBrAG0AVAAgAD0AIABtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAHAAZQByACAAYwBsAGEAcwBzACwAIABzAHUAYgBjAGwAYQBzAHMALAAgAE0ATQBTACwAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAOgAgAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAEEAbgBkAFMAdQBiAGMAbABhAHMAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAGoAawBtAFQALABcAG4AIAAgACAAIABTAFUATQAoAE0AagBrAG0AVAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAQQBuAGQAUwB1AGIAYwBsAGEAcwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIAB0AGgAZQAgAG0AYQBuAHUAcgBlACAAbwBmACAAcABvAHUAbAB0AHIAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAQQBuAGQAUwB1AGIAYwBsAGEAcwBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAG0AagBrAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBBAG4AZABTAHUAYgBjAGwAYQBzAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMgBfAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBQAGUAcgBDAGwAYQBzAHMAQQBuAGQAUwB1AGIAYwBsAGEAcwBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgA2AC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAyAF8ATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFAAZQByAEMAbABhAHMAcwBBAG4AZABTAHUAYgBjAGwAYQBzAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAEEAbgBkAFMAdQBiAGMAbABhAHMAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AG0AagBrAH0APQBcAFwAcwB1AG0AXwB7AG0AfQBcAFwAcwB1AG0AXwB7AFQAfQBNAF8AewBqAGsAbQBUAH0AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADIAXwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AUABlAHIAQwBsAGEAcwBzAEEAbgBkAFMAdQBiAGMAbABhAHMAcwBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGoAawBtAFQAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAcABlAHIAIABjAGwAYQBzAHMALAAgAHMAdQBiAGMAbABhAHMAcwAsACAATQBNAFMALAAgAGEAbgBkACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAA6ACAAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcAG4ATQBqAGsAbQBUADEAXABuAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAF8AewBqAGsAbQAsAFQAPQAxAH0APQBWAFMAXwB7AGoAawB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAagBrACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAHAAbwB1AGwAdAByAHkAIABjAGwAYQBzAHMAZQBzACAAYQBuAGQAIABzAHUAYgBjAGwAYQBzAHMAZQBzACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AQgBPAGoAIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgAHAAZQByACAAYwBsAGEAcwBzACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgBNAE0AUwBqAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAGkAbQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAHIAaABvACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFYAUwBqAGsALAAgAEIATwBqACwAIABNAE0AUwBqAG0AVAAxACwAIABNAEMARgBpAG0ALAAgAHIAaABvACwAXABuACAAIAAgACAAVgBTAGoAawAgACoAIABCAE8AagAgACoAIABNAE0AUwBqAG0AVAAxACAAKgAgAE0AQwBGAGkAbQAgACoAIAByAGgAbwBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAxACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AagBrAG0AVAAxAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADYALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAAzACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBqAGsAbQAsAFQAPQAxAH0APQBWAFMAXwB7AGoAawB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXwB7AGoAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAgAE0AQwBGAF8AewBpAG0AfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBqAGsAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAHAAbwB1AGwAdAByAHkAIABjAGwAYQBzAHMAZQBzACAAYQBuAGQAIABzAHUAYgBjAGwAYQBzAHMAZQBzACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAGoAXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIABwAGUAcgAgAGMAbABhAHMAcwAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAagBtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAaQBtAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXABuAE0AagBrAG0AVAAyAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAagBrAG0ALABUAD0AMgB9AD0AVgBTAFQAXwB7AGoAawBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAagBtACwAVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBUAGoAawBtAFQAMgAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTACAAOgAgAGsAZwAgAFYAUwBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAE0ATQBTAGoAbQBUADIAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcwBlAGMAbwBuAGQAYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAE0AQwBGAGkAbQAgAD0AIABtAGUAdABoAGEAbgBlACAAYwBvAG4AdgBlAHIAcwBpAG8AbgAgAGYAYQBjAHQAbwByACAAZgBvAHIAIAB0AGUAbQBwAGUAcgBhAHQAdQByAGUAIAB6AG8AbgBlACAAYQBuAGQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAHIAaABvACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFYAUwBUAGoAawBtAFQAMgAsACAAQgBPACwAIABNAE0AUwBqAG0AVAAyACwAIABNAEMARgBpAG0ALAAgAHIAaABvACwAXABuACAAIAAgACAATABFAFQAKABcAG4AIAAgACAAIAAgACAATQBNAFMAagBtAFQAMgAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAKABNAE0AUwBqAG0AVAAyACkAKQAsACAATQBNAFMAagBtAFQAMgAsACAAMAApACwAXABuACAAIAAgACAAIAAgAFYAUwBUAGoAawBtAFQAMgAgACoAIABCAE8AIAAqACAATQBNAFMAagBtAFQAMgAgACoAIABNAEMARgBpAG0AIAAqACAAcgBoAG8AXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFAAcgBvAGQAdQBjAHQAaQBvAG4AIABvAGYAIABtAGUAdABoAGEAbgBlACAAaQBuACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AagBrAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAANAAuADYALgAxAC4AMQAsACAARQBxAHUAYQB0AGkAbwBuACAAKAA0ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBNAF8AewBqAGsAbQAsAFQAPQAyAH0APQBWAFMAVABfAHsAagBrAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABCAE8AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0ALABUAD0AMgB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAH0AXABcAHQAaQBtAGUAcwAgAFwAXAByAGgAbwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMgAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAFMAVABqAGsAbQBUADIAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAIAA6ACAAawBnACAAVgBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBCAE8AXAAiACwAXAAiAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0ATQBTAGoAbQBUADIAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHMAZQBjAG8AbgBkAGEAcgB5ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAEMARgBpAG0AXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAFwAbgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAHQAcgBhAG4AcwBmAGUAcgByAGUAZAAgAHQAbwAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAbgBWAFMAVABqAGsAbQBUADIAXABuAGsAZwAgAFYAUwBcAG4AVgBTAFQAXwB7AGoAawBtACwAVAA9ADIAfQA9AFYAUwBfAHsAagBrAH0AXABcAHQAaQBtAGUAcwAgAE0ATQBTAF8AewBqAG0ALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAKAAxAC0AVgBTAEwAXwB7AG0ALABUAD0AMQB9ACkAXABuAFYAUwBqAGsAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAbwByACAAcABvAHUAbAB0AHIAeQAgAGMAbABhAHMAcwBlAHMAIABhAG4AZAAgAHMAdQBiAGMAbABhAHMAcwBlAHMAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBNAE0AUwBqAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAZQBhAGMAaAAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAFYAUwBMAG0AVAAxACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAAVgBTAGoAawAsACAATQBNAFMAagBtAFQAMQAsACAAVgBTAEwAbQBUADEALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIABWAFMATABtAFQAMQAsACAASQBGACgASQBTAE4AVQBNAEIARQBSACgAKABWAFMATABtAFQAMQApACkALAAgAFYAUwBMAG0AVAAxACwAIAAwACkALABcAG4AIAAgACAAIAAgACAAVgBTAGoAawAgACoAIABNAE0AUwBqAG0AVAAxACAAKgAgACgAMQAgAC0AIABWAFMATABtAFQAMQApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAdAByAGEAbgBzAGYAZQByAHIAZQBkACAAdABvACAAdAByAGUAYQB0AG0AZQBuAHQAIABzAHQAYQBnAGUAIAAyACAATQBNAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAFQAagBrAG0AVAAyAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAHMAVAByAGEAbgBzAGYAZQByAHIAZQBkAFQAbwBTAHQAYQBnAGUAMgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABzAFQAcgBhAG4AcwBmAGUAcgByAGUAZABUAG8AUwB0AGEAZwBlADIAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMAVABfAHsAagBrAG0ALABUAD0AMgB9AD0AVgBTAF8AewBqAGsAfQBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AGoAbQAsAFQAPQAxAH0AXABcAHQAaQBtAGUAcwAoADEALQBWAFMATABfAHsAbQAsAFQAPQAxAH0AKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAcwBUAHIAYQBuAHMAZgBlAHIAcgBlAGQAVABvAFMAdABhAGcAZQAyAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAUwBqAGsAXAAiACwAXAAiAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAG8AcgAgAHAAbwB1AGwAdAByAHkAIABjAGwAYQBzAHMAZQBzACAAYQBuAGQAIABzAHUAYgBjAGwAYQBzAHMAZQBzACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAagBtAFQAMQBcACIALABcACIAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIABpAG4AIABlAGEAYwBoACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAEwAbQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8ANgBfADEAXwAxAF8AXwA2AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBWAG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBWAFMAagBrAFwAbgBrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAFYAUwBfAHsAagBrAH0APQBJAF8AewBqAGsAfQBcAFwAdABpAG0AZQBzACgAMQAtAEQATQBEAF8AewBqAGsAfQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AQQBfAHsAagB9ACkAXABuAEkAagBrACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgAGYAbwByACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAGEAbgBkACAAcwB1AGIAYwBsAGEAcwBzACAAOgAgAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcAG4ARABNAEQAagBrACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABkAGkAZwBlAHMAdABpAGIAaQBsAGkAdAB5ACAAZgBvAHIAIABlAGEAYwBoACAAYwBsAGEAcwBzACAAYQBuAGQAIABzAHUAYgBjAGwAYQBzAHMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBBAGoAIAA9ACAAYQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAIABmAG8AcgAgAGUAYQBjAGgAIABjAGwAYQBzAHMAIABhAG4AZAAgAHMAdQBiAGMAbABhAHMAcwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANgBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABJAGoAawAsACAARABNAEQAagBrACwAIABBAGoALABcAG4AIAAgACAAIABJAGoAawAgACoAIAAoADEAIAAtACAARABNAEQAagBrACkAIAAqACAAKAAxACAALQAgAEEAagApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANgBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANgBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAGoAawBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANgBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANgBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4ANgAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADYAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANgBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADYAXwAxAF8AMQBfAF8ANgBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBfAHsAagBrAH0APQBJAF8AewBqAGsAfQBcAFwAdABpAG0AZQBzACgAMQAtAEQATQBEAF8AewBqAGsAfQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AQQBfAHsAagB9ACkAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwA2AF8AMQBfADEAXwBfADYAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIASQBqAGsAXAAiACwAXAAiAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgAGYAbwByACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAGEAbgBkACAAcwB1AGIAYwBsAGEAcwBzACAAOgAgAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABNAEQAagBrAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGYAbwByACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAGEAbgBkACAAcwB1AGIAYwBsAGEAcwBzACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBqAFwAIgAsAFwAIgBhAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAgAGYAbwByACAAZQBhAGMAaAAgAGMAbABhAHMAcwAgAGEAbgBkACAAcwB1AGIAYwBsAGEAcwBzACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgAiAH0ALAB7ACIAcABhAHQAaAAiADoAIgAvAHAAcgBvAGoAZQBjAHQAcwAvAE0AYQBuAHUAcgBlAE0AYQBuAGEAZwBlAG0AZQBuAHQAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQAiACwAIgB0AGUAeAB0ACIAOgAiAC8AKgBcAG4APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQBcAG4ANAAuADEAOgAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgA0AC4AMQAuADEALgAxACAATQBlAHQAaABvAGQAIAAxACAALQAgAE0AYQBuAHUAcgBlACAATQBlAHQAaABhAG4AZQAgAEIAZQBlAGYAIABGAGUAZQBkAGwAbwB0AFwAbgA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AD0APQA9AFwAbgAqAC8AXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFwAbgBUAG8AdABhAGwAIABhAG4AbgB1AGEAbAAgAG0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAG0AYQBuAGEAZwBlAG0AZQBuAHQAXABuAEUAXwBDAEgANABcAG4AdAAgAEMASAA0AFwAbgB7AEUAfQBfAHsAQwBIADQAfQA9AFwAXABzAHUAbQBfAHsAagB9AFwAXABzAHUAbQBfAHsAbQB9AFwAXABzAHUAbQBfAHsAVAB9ACgARABfAHsAagB9AFwAXAB0AGkAbQBlAHMAIABNAF8AewBqAG0AVAB9AFwAXAB0AGkAbQBlAHMAIABOAF8AewBqAH0AKQBcAFwAdABpAG0AZQBzADEAMABeAHsALQAzAH0AXABuAEQAXwBqACAAPQAgAGwAZQBuAGcAdABoACAAbwBmACAAcwB0AGEAeQAgAG8AZgAgAGUAYQBjAGgAIABjAGEAdAB0AGwAZQAgAGcAcgBvAHUAcAAgADoAIABkAGEAeQBzAFwAbgBNAF8AagBtAFQAIAA9ACAAbQBlAHQAaABhAG4AZQAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAbQBhAG4AdQByAGUAIABwAGUAcgAgAGMAYQB0AHQAbABlACAAZwByAG8AdQBwACwAIABNAE0AUwAsACAAYQBuAGQAIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADoAIABrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATgBfAGoAIAA9ACAAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAaABlAGEAZABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAARABfAGoALAAgAE0AXwBqAG0AVAAsACAATgBfAGoALABcAG4AIAAgACAAIAAoAEQAXwBqACAAKgAgAE0AXwBqAG0AVAAgACoAIABOAF8AagApACAAKgAgADEAMAAgAF4AIAAtADMAXABuACAAIAApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFQAbwB0AGEAbAAgAGEAbgBuAHUAYQBsACAAbQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAZgByAG8AbQAgAG0AYQBuAHUAcgBlACAAbQBhAG4AYQBnAGUAbQBlAG4AdABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBFAF8AQwBIADQAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHQAIABDAEgANABcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAxAF8AVABvAHQAYQBsAEEAbgBuAHUAYQBsAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADEAXwBUAG8AdABhAGwAQQBuAG4AdQBhAGwATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAHsARQB9AF8AewBDAEgANAB9AD0AXABcAHMAdQBtAF8AewBqAH0AXABcAHMAdQBtAF8AewBtAH0AXABcAHMAdQBtAF8AewBUAH0AKABEAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAE0AXwB7AGoAbQBUAH0AXABcAHQAaQBtAGUAcwAgAE4AXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAMQAwAF4AewAtADMAfQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMQBfAFQAbwB0AGEAbABBAG4AbgB1AGEAbABNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAXwBqAFwAIgAsAFwAIgBsAGUAbgBnAHQAaAAgAG8AZgAgAHMAdABhAHkAIABvAGYAIABlAGEAYwBoACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAAIAA6ACAAZABhAHkAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBfAGoAbQBUAFwAIgAsAFwAIgBtAGUAdABoAGEAbgBlACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABtAGEAbgB1AHIAZQAgAHAAZQByACAAYwBhAHQAdABsAGUAIABnAHIAbwB1AHAALAAgAE0ATQBTACwAIABhAG4AZAAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAOgAgAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBOAF8AagBcACIALABcACIAbgB1AG0AYgBlAHIAcwAgAG8AZgAgAGIAZQBlAGYAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAaABlAGEAZABcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AFwAbgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMQAgAE0ATQBTAFwAbgBNAF8AagBtADUAVAAxAFwAbgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcAG4ATQBfAHsAagBtAD0ANQAsAFQAPQAxAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAbQA9ADUALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAD0ANQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBfAGoAIAA9ACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AQgBPACAAPQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwAIAA6ACAAbQAzACAAQwBIADQALwBrAGcAIABWAFMAXABuAE0ATQBTAF8AbQA1AFQAMQAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAHAAcgBpAG0AYQByAHkAIABzAHkAcwB0AGUAbQAgAGQAcgB5AGwAbwB0ACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBNAEMARgBfAGkAbQA1ACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAGQAcgB5AGwAbwB0ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMAXwBqACwAIABCAE8ALAAgAE0ATQBTAF8AbQA1AFQAMQAsACAATQBDAEYAXwBpAG0ANQAsACAAcgBoAG8ALABcAG4AIAAgACAAIABMAEUAVAAoAFwAbgAgACAAIAAgACAAIABNAEMARgBfAGkAbQA1ACwAIABJAEYAKABJAFMATgBVAE0AQgBFAFIAKABNAEMARgBfAGkAbQA1ACkALAAgAE0AQwBGAF8AaQBtADUALAAgADAAKQAsAFwAbgAgACAAIAAgACAAIABWAFMAXwBqACAAKgAgAEIATwAgACoAIABNAE0AUwBfAG0ANQBUADEAIAAqACAATQBDAEYAXwBpAG0ANQAgACoAIAByAGgAbwBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADEAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAbQA1AFQAMQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMgBfAFMAdABhAGcAZQAxAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBEAHIAeQBsAG8AdABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgAMgApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAyAF8AUwB0AGEAZwBlADEATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEQAcgB5AGwAbwB0AF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAagBtAD0ANQAsAFQAPQAxAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAbQA9ADUALABUAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAD0ANQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADIAXwBTAHQAYQBnAGUAMQBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4ARAByAHkAbABvAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAG0ANQBUADEAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAG0AYQBuAHUAcgBlACAAaQBuACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAZAByAHkAbABvAHQAIABNAE0AUwAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtADUAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAGQAcgB5AGwAbwB0ACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgByAGgAbwBcACIALABcACIAZABlAG4AcwBpAHQAeQAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIAA6ACAAawBnAC8AbQAzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBpAFwAIgAsACAAXAAiAHMAdABhAHQAZQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAC8AKgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwAzAF8AUwB0AGEAZwBlADIATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAFwAbgBQAHIAbwBkAHUAYwB0AGkAbwBuACAAbwBmACAAbQBlAHQAaABhAG4AZQAgAGkAbgAgAHQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAMgAgAE0ATQBTAFwAbgBNAF8AagBtAFQAMgBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGoAbQBUAD0AMgB9AD0AKAAxAC0AVgBTAEwAKQBcAFwAdABpAG0AZQBzACAAVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXABuAFYAUwBMACAAPQAgAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4AVgBTAF8AagAgAD0AIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAIABwAHIAbwBkAHUAYwB0AGkAbwBuACAAZgByAG8AbQAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAGkAbgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIAA6ACAAawBnAC8AaABlAGEAZAAvAGQAYQB5AFwAbgBCAE8AIAA9ACAAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcAG4ATQBNAFMAXwBtAFQAMgAgAD0AIABmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcAG4ATQBDAEYAXwBpAG0AIAA9ACAAbQBlAHQAaABhAG4AZQAgAGMAbwBuAHYAZQByAHMAaQBvAG4AIABmAGEAYwB0AG8AcgAgAGYAbwByACAAdABlAG0AcABlAHIAYQB0AHUAcgBlACAAegBvAG4AZQAgAGEAbgBkACAATQBNAFMAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgByAGgAbwAgAD0AIABkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABWAFMATAAsACAAVgBTAF8AagAsACAAQgBPACwAIABNAE0AUwBfAG0AVAAyACwAIABNAEMARgBfAGkAbQAsACAAcgBoAG8ALABcAG4AIAAgACAAIAAoADEAIAAtACAAVgBTAEwAKQAgACoAIABWAFMAXwBqACAAKgAgAEIATwAgACoAIABNAE0AUwBfAG0AVAAyACAAKgAgAE0AQwBGAF8AaQBtACAAKgAgAHIAaABvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADIAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAbQBUADIAXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBrAGcAIABDAEgANAAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADMAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8AMwBfAFMAdABhAGcAZQAyAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AXwB7AGoAbQBUAD0AMgB9AD0AKAAxAC0AVgBTAEwAKQBcAFwAdABpAG0AZQBzACAAVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0AVAA9ADIAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADMAXwBTAHQAYQBnAGUAMgBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADcALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAEwAXAAiACwAXAAiAGYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAOgAgAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQgBPAFwAIgAsAFwAIgBlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAE0AUwBfAG0AVAAyAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAGkAbgAgAGUAYQBjAGgAIABzAGUAYwBvAG4AZABhAHIAeQAgAHMAeQBzAHQAZQBtACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBDAEYAXwBpAG0AXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAE0ATQBTACAAOgAgAGYAcgBhAGMAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAcgBoAG8AXAAiACwAXAAiAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAaQBcACIALAAgAFwAIgBzAHQAYQB0AGUAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAvACoAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBcAG4AUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADMAIABNAE0AUwBcAG4ATQBfAGoAbQAxAFQAMwBcAG4AawBnACAAQwBIADQALwBoAGUAYQBkAC8AZABhAHkAXABuAE0AXwB7AGoAbQA9ADEALABUAD0AMwB9AD0AVgBTAF8AewBqAH0AXABcAHQAaQBtAGUAcwAgAEIATwBcAFwAdABpAG0AZQBzACAATQBNAFMAXwB7AG0APQAxACwAVAA9ADMAfQBcAFwAdABpAG0AZQBzACAATQBDAEYAXwB7AGkAbQA9ADEAfQBcAFwAdABpAG0AZQBzACAAXABcAHIAaABvAFwAbgBWAFMAXwBqACAAPQAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AIABmAHIAbwBtACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAAaQBuACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXABuAEIATwAgAD0AIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsACAAOgAgAG0AMwAgAEMASAA0AC8AawBnACAAVgBTAFwAbgBNAE0AUwBfAG0AMQBUADMAIAA9ACAAZgByAGEAYwB0AGkAbwBuACAAbwBmACAAbQBhAG4AdQByAGUAIAB0AG8AIAB0AGUAcgB0AGkAYQByAHkAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAcwB5AHMAdABlAG0AIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgBNAEMARgBfAGkAbQAxACAAPQAgAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAHIAaABvACAAPQAgAGQAZQBuAHMAaQB0AHkAIABvAGYAIABtAGUAdABoAGEAbgBlACAAOgAgAGsAZwAvAG0AMwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAFYAUwBfAGoALAAgAEIATwAsACAATQBNAFMAXwBtADEAVAAzACwAIABNAEMARgBfAGkAbQAxACwAIAByAGgAbwAsAFwAbgAgACAAIAAgAFYAUwBfAGoAIAAqACAAQgBPACAAKgAgAE0ATQBTAF8AbQAxAFQAMwAgACoAIABNAEMARgBfAGkAbQAxACAAKgAgAHIAaABvAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAUAByAG8AZAB1AGMAdABpAG8AbgAgAG8AZgAgAG0AZQB0AGgAYQBuAGUAIABpAG4AIAB0AHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgADMAIABNAE0AUwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAGoAbQAxAFQAMwBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANABfAFMAdABhAGcAZQAzAE0AZQB0AGgAYQBuAGUAUAByAG8AZAB1AGMAdABpAG8AbgBBAG4AYQBlAHIAbwBiAGkAYwBMAGEAZwBvAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAgAEMASAA0AC8AaABlAGEAZAAvAGQAYQB5AFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMQAuADEALAAgAEUAcQB1AGEAdABpAG8AbgAgACgANAApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA0AF8AUwB0AGEAZwBlADMATQBlAHQAaABhAG4AZQBQAHIAbwBkAHUAYwB0AGkAbwBuAEEAbgBhAGUAcgBvAGIAaQBjAEwAYQBnAG8AbwBuAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIATQBfAHsAagBtAD0AMQAsAFQAPQAzAH0APQBWAFMAXwB7AGoAfQBcAFwAdABpAG0AZQBzACAAQgBPAFwAXAB0AGkAbQBlAHMAIABNAE0AUwBfAHsAbQA9ADEALABUAD0AMwB9AFwAXAB0AGkAbQBlAHMAIABNAEMARgBfAHsAaQBtAD0AMQB9AFwAXAB0AGkAbQBlAHMAIABcAFwAcgBoAG8AXAAiACkAOwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADQAXwBTAHQAYQBnAGUAMwBNAGUAdABoAGEAbgBlAFAAcgBvAGQAdQBjAHQAaQBvAG4AQQBuAGEAZQByAG8AYgBpAGMATABhAGcAbwBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADIALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBTAF8AagBcACIALABcACIAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgAgAGYAcgBvAG0AIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIABpAG4AIABlAGEAYwBoACAAZwByAG8AdQBwACAAagAgADoAIABrAGcALwBoAGUAYQBkAC8AZABhAHkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEIATwBcACIALABcACIAZQBtAGkAcwBzAGkAbwBuAHMAIABwAG8AdABlAG4AdABpAGEAbAAgADoAIABtADMAIABDAEgANAAvAGsAZwAgAFYAUwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBNAFMAXwBtADEAVAAzAFwAIgAsAFwAIgBmAHIAYQBjAHQAaQBvAG4AIABvAGYAIABtAGEAbgB1AHIAZQAgAHQAbwAgAHQAZQByAHQAaQBhAHIAeQAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AQwBGAF8AaQBtADEAXAAiACwAXAAiAG0AZQB0AGgAYQBuAGUAIABjAG8AbgB2AGUAcgBzAGkAbwBuACAAZgBhAGMAdABvAHIAIABmAG8AcgAgAHQAZQBtAHAAZQByAGEAdAB1AHIAZQAgAHoAbwBuAGUAIABhAG4AZAAgAGEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AIABzAHkAcwB0AGUAbQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAHIAaABvAFwAIgAsAFwAIgBkAGUAbgBzAGkAdAB5ACAAbwBmACAAbQBlAHQAaABhAG4AZQAgADoAIABrAGcALwBtADMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAGkAXAAiACwAIABcACIAcwB0AGEAdABlAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4ALwAqAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZAAgAHAAcgBvAGQAdQBjAHQAaQBvAG4AXABuAFYAUwBfAGoAXABuAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcAG4AVgBTAF8AewBqAH0APQBJAF8AewBqAH0AXABcAHQAaQBtAGUAcwAoADEALQBEAE0ARABfAHsAagB9ACkAXABcAHQAaQBtAGUAcwAoADEALQBBACkAXABuAEkAXwBqACAAPQAgAGQAcgB5ACAAbQBhAHQAdABlAHIAIABpAG4AdABhAGsAZQAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABrAGcAIABEAE0ALwBoAGUAYQBkAC8AZABhAHkAXABuAEQATQBEAF8AagAgAD0AIABkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgADoAIABmAHIAYQBjAHQAaQBvAG4AXABuAEEAIAA9ACAAYQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFYARQBFAFIARwBfADQAXwAxAF8AMQBfADEAXwBfADUAXwBWAG8AbABhAHQAaQBsAGUAUwBvAGwAaQBkAFAAcgBvAGQAdQBjAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAASQBfAGoALAAgAEQATQBEAF8AagAsACAAQQAsAFwAbgAgACAAIAAgAEkAXwBqACAAKgAgACgAMQAgAC0AIABEAE0ARABfAGoAKQAgACoAIAAoADEAIAAtACAAQQApAFwAbgAgACAAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkACAAcAByAG8AZAB1AGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBTAF8AagBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAGsAZwAvAGgAZQBhAGQALwBkAGEAeQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADEALgAxACwAIABFAHEAdQBhAHQAaQBvAG4AIAAoADUAKQBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AVgBFAEUAUgBHAF8ANABfADEAXwAxAF8AMQBfAF8ANQBfAFYAbwBsAGEAdABpAGwAZQBTAG8AbABpAGQAUAByAG8AZAB1AGMAdABpAG8AbgBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYAUwBfAHsAagB9AD0ASQBfAHsAagB9AFwAXAB0AGkAbQBlAHMAKAAxAC0ARABNAEQAXwB7AGoAfQApAFwAXAB0AGkAbQBlAHMAKAAxAC0AQQApAFwAIgApADsAXABuAFwAbgBWAEUARQBSAEcAXwA0AF8AMQBfADEAXwAxAF8AXwA1AF8AVgBvAGwAYQB0AGkAbABlAFMAbwBsAGkAZABQAHIAbwBkAHUAYwB0AGkAbwBuAF8AQQByAGcAdQBtAGUAbgB0AHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAyACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEkAXwBqAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAaQBuAHQAYQBrAGUAIABmAG8AcgAgAGUAYQBjAGgAIABnAHIAbwB1AHAAIABqACAAOgAgAGsAZwAgAEQATQAvAGgAZQBhAGQALwBkAGEAeQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABNAEQAXwBqAFwAIgAsAFwAIgBkAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQAgAGYAbwByACAAZQBhAGMAaAAgAGcAcgBvAHUAcAAgAGoAIAA6ACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAFwAIgAsAFwAIgBhAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAgADoAIABmAHIAYQBjAHQAaQBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAFwAbgBcAG4AXABuACIAfQAsAHsAIgBwAGEAdABoACIAOgAiAC8AcAByAG8AagBlAGMAdABzAC8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAIgAsACIAdABlAHgAdAAiADoAIgAvACoAIABcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAFwAbgBGAHIAYQBjAHQAaQBvAG4AIABvAGYAIAB2AG8AbABhAHQAaQBsAGUAIABzAG8AbABpAGQAcwAgAGwAbwBzAHQAIABpAG4AIAB0AGgAZQAgAHAAcgBpAG0AYQByAHkAIABNAE0AUwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAGUAZQBkAGwAbwB0ACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAHYAbwBsAGEAdABpAGwAZQAgAHMAbwBsAGkAZABzACAAbABvAHMAdAAgAGQAdQByAGkAbgBnACAAcwB0AG8AcgBhAGcAZQAgAGkAbgAgAHQAaABlACAAcAByAGkAbQBhAHIAeQAgAHMAeQBzAHQAZQBtAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFYAUwBMAF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAFMATABcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBWAFMATABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AVgBTAEwAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgA1ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBcAG4ARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AG8AIABlAGEAYwBoACAAdABlAHIAdABpAGEAcgB5ACAAcwB5AHMAdABlAG0AIABhAHMAcwB1AG0AZQBkACAAdABoAGEAdAAgADIAIABwAGUAcgAgAGMAZQBuAHQAIABpAHMAIAByAHUAbgAgAC0AIABvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAZQBlAGQAIABwAGEAZAAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgByAGEAYwB0AGkAbwBuACAAbwBmACAAdgBvAGwAYQB0AGkAbABlACAAcwBvAGwAaQBkAHMAIAB0AG8AIABlAGEAYwBoACAAdABlAHIAdABpAGEAcgB5ACAAcwB5AHMAdABlAG0AIABhAHMAcwB1AG0AZQBkACAAdABoAGEAdAAgADIAIABwAGUAcgAgAGMAZQBuAHQAIABpAHMAIAByAHUAbgAgAC0AIABvAGYAZgAgAGYAcgBvAG0AIAB0AGgAZQAgAGYAZQBlAGQAIABwAGEAZAAuAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBWAGEAcgBpAGEAYgBsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0ATQBTAG0AMQBUADMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBNAFMAbQAxAFQAMwBfAFUAbgBpAHQAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEYAcgBhAGMAdABpAG8AbgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgADQALgAxAC4AMgAuADMAIABDAE8ATgBTAFQAQQBOAFQAUwBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAE0AUwBtADEAVAAzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0ATQBTAG0AMQBUADMAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoADAALgAwADIAKQA7AFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AFwAbgBBAHMAaAAgAGMAbwBuAHQAZQBuAHQAIABvAGYAIABtAGEAbgB1AHIAZQAuAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQQBzAGgAIABjAG8AbgB0AGUAbgB0ACAAbwBmACAAbQBhAG4AdQByAGUALgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAGIAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBBAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBGAHIAYQBjAHQAaQBvAG4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBzAGgAQwBvAG4AdABlAG4AdABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMQA2ACkAOwBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABcAG4ATQBlAHQAaABhAG4AZQAgAGUAbQBpAHMAcwBpAG8AbgBzACAAcABvAHQAZQBuAHQAaQBhAGwALgBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAE0AZQB0AGgAYQBuAGUAIABlAG0AaQBzAHMAaQBvAG4AcwAgAHAAbwB0AGUAbgB0AGkAYQBsAC4AXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQBiAGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgAwAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBtADMAIABDAEgANAAgAC8AIABrAGcAIABWAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIAA0AC4AMQAuADIALgAzACAAQwBPAE4AUwBUAEEATgBUAFMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAFAAbwB0AGUAbgB0AGkAYQBsAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKAAwAC4AMQA5ACkAOwBcAG4AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAFMAdABhAGcAZQAxAE0ATQBTAE8AcAB0AGkAbwBuAHMAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxACwAIAAxACwAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AUwB0AGEAZwBlADIATQBNAFMATwBwAHQAaQBvAG4AcwBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADQALAAgADEALABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBvAGwAaQBkACAAcwB0AG8AcgBhAGcAZQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARABpAHIAZQBjAHQAIABhAHAAcABsAGkAYwBhAHQAaQBvAG4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE4AbwAgAE0ATQBTAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBTAHQAYQBnAGUAMwBNAE0AUwBPAHAAdABpAG8AbgBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMQAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBBAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBMAGkAdgBlAHMAdABvAGMAawBDAGwAYQBzAHMAZQBzAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgAMwAsACAAMQAsAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARQB4AHAAbwByAHQAIABtAGkAZAAgAGYAZQBkAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEUAeABwAG8AcgB0ACAAbABvAG4AZwAgAGYAZQBkAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgAxADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEQAdQByAGEAdABpAG8AbgAgAG8AZgAgAHMAdABhAHkAIAAoAGQAYQB5AHMAKQBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABEAHUAcgBhAHQAaQBvAG4AIABvAGYAIABzAHQAYQB5ACAAKABkAGEAeQBzACkAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADEAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARAB1AHIAYQB0AGkAbwBuACAAbwBmACAAcwB0AGEAeQAgACgAZABhAHkAcwApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAHUAcgBhAHQAaQBvAG4ATwBmAFMAdABhAHkAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMgAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIARgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAXAAiACwAIABcACIATABlAG4AZwB0AGgAIABvAGYAIABTAHQAYQB5AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIAMQAtADgAMAAgAGQAYQB5AHMAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIAOAAxAC0AMgAwADAAIABkAGEAeQBzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0AZgBlAGQAXAAiACwAIABcACIAMgAwADEAKwAgAGQAYQB5AHMAXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADIAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAAQQBuAGkAbQBhAGwAIABjAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBcAG4ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAFwAbgAqAC8AXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEEAbgBpAG0AYQBsAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBzAF8AVABpAHQAbABlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEEAbgBpAG0AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgAyADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEEAbgBpAG0AYQBsACAAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8AQQBuAGkAbQBhAGwAQwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAHMAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADMALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBvAHYAZQBkACAAZgBlAGUAZABsAG8AdAAgAHQAeQBwAGUAcwAgAHQAbwAgAGEAIABzAGUAcABhAHIAYQB0AGUAIABjAG8AbAB1AG0AbgAgAHQAbwAgAGEAaQBkACAAbABvAG8AawB1AHAALgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATgBhAG0AZQBkACAAXAB1ADAAMAAyADcAYwBoAGEAcgBhAGMAdABlAHIAaQBzAHQAaQBjAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAAtACAAbwByAGkAZwBpAG4AYQBsACAAaABhAHMAIABoAGUAYQBkAGUAcgAgAFwAdQAwADAAMgA3AFUAbgBpAHQAXAB1ADAAMAAyADcAIAB3AGgAaQBjAGgAIABjAG8AdgBlAHIAcwAgAHQAdwBvACAAYwBvAGwAdQBtAG4AcwApAFwAIgBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBBAG4AaQBtAGEAbABDAGgAYQByAGEAYwB0AGUAcgBpAHMAdABpAGMAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADAALAAgADcALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBlAGQAbABvAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAEMAaABhAHIAYQBjAHQAZQByAGkAcwB0AGkAYwBcACIALAAgAFwAIgBVAG4AaQB0AFwAIgAsACAAXAAiADIAMAAwADUALQAyADAAMAA5AFwAIgAsACAAXAAiADIAMAAxADAALQAyADAAMQA0AFwAIgAsACAAXAAiADIAMAAxADUALQAyADAAMQA5AFwAIgAsACAAXAAiADIAMAAyADAALQAyADAAMgAzAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARABhAHkAcwAgAG8AbgAgAGYAZQBlAGQAXAAiACwAIABcACIAZABhAHkAcwBcACIALAAgADcAMAAsACAANwAwACwAIAA3ADAALAAgADcANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARgBlAGUAZAAgAGkAbgB0AGEAawBlAFwAIgAsACAAXAAiAGsAZwAgAEQATQAvAGQAYQB5AFwAIgAsACAAMQAwAC4AMAAsACAAMQAwAC4AMAAsACAAMQAwAC4ANAAsACAAMQAwAC4ANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIATgAgAHIAZQB0AGUAbgB0AGkAbwBuAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdAAgAG8AZgAgAGkAbgB0AGEAawBlAFwAIgAsACAAMgAxAC4AMQAsACAAMgAwAC4ANAAsACAAMgAwAC4ANAAsACAAMgAwAC4ANAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEQAYQB5AHMAIABvAG4AIABmAGUAZQBkAFwAIgAsACAAXAAiAGQAYQB5AHMAXAAiACwAIAAxADEANQAsACAAMQAxADUALAAgADEAMgAwACwAIAAxADUAMAA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBNAGkAZAAtAGYAZQBkAFwAIgAsACAAXAAiAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBkAGEAeQBcACIALAAgADEAMQAuADIALAAgADEAMAAuADgALAAgADEAMAAuADgALAAgADEAMAAuADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBOACAAcgBlAHQAZQBuAHQAaQBvAG4AXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0ACAAbwBmACAAaQBuAHQAYQBrAGUAXAAiACwAIAAxADIALgA1ACwAIAAxADIALgA3ACwAIAAxADIALgA3ACwAIAAxADIALgA3ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgBEAGEAeQBzACAAbwBuACAAZgBlAGUAZABcACIALAAgAFwAIgBkAGEAeQBzAFwAIgAsACAAMgA1ADAALAAgADIANQAwACwAIAAyADUAMAAsACAAMgA1ADAAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAGYAZQBkAFwAIgAsACAAXAAiAEYAZQBlAGQAIABpAG4AdABhAGsAZQBcACIALAAgAFwAIgBrAGcAIABEAE0ALwBkAGEAeQBcACIALAAgADkALgAwACwAIAA4AC4ANQAsACAAOAAuADIALAAgADgALgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEwAbwBuAGcALQBmAGUAZABcACIALAAgAFwAIgBOACAAcgBlAHQAZQBuAHQAaQBvAG4AXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0ACAAbwBmACAAaQBuAHQAYQBrAGUAXAAiACwAIAA2AC4ANgAsACAANwAuADAALAAgADcALgAwACwAIAA3AC4AMABcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAFwAbgBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADMAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARABpAGUAdAAgAHAAcgBvAHAAZQByAHQAaQBlAHMAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBEAGkAZQB0AFAAcgBvAHAAZQByAHQAaQBlAHMAXwBUAGkAdABsAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARABpAGUAdAAgAHAAcgBvAHAAZQByAHQAaQBlAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AUwBvAHUAcgBjAGUAXABuACAAIAA9AEwAQQBNAEIARABBACgAXAAiAFYARQBFAFIARwAgADIAMAAyADYAOgAgAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADMAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAARABpAGUAdAAgAHAAcgBvAHAAZQByAHQAaQBlAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARABpAGUAdABQAHIAbwBwAGUAcgB0AGkAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAzACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AEMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAZgByAGEAYwB0AGkAbwBuACAAYwBvAGwAdQBtAG4AIABhAG4AZAAgAGMAbwBuAHYAZQByAHQAZQBkACAATgBEAEYAIABhAG4AZAAgAEUAdABoAGUAcgAgAGUAeAB0AHIAYQBjAHQAIAB2AGEAbAB1AGUAcwAgAHQAbwAgAGYAcgBhAGMAdABpAG8AbgBzAC4AXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AbwB2AGUAZAAgAGYAZQBlAGQAbABvAHQAIAB0AHkAcABlAHMAIAB0AG8AIABhACAAcwBlAHAAYQByAGEAdABlACAAYwBvAGwAdQBtAG4AIAB0AG8AIABhAGkAZAAgAGwAbwBvAGsAdQBwAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEQAaQBlAHQAUAByAG8AcABlAHIAdABpAGUAcwBfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAxADMALAAgADgALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEYAZQBlAGQAbABvAHQAIAB0AHkAcABlAFwAIgAsACAAXAAiAE4AdQB0AHIAaQBlAG4AdAAgAGEAbgBhAGwAeQBzAGkAcwBcACIALAAgAFwAIgBVAG4AaQB0AFwAIgAsACAAXAAiADIAMAAwADUALQAyADAAMAA5AFwAIgAsACAAXAAiADIAMAAxADAALQAyADAAMQA0AFwAIgAsACAAXAAiADIAMAAxADUALQAyADAAMQA5AFwAIgAsACAAXAAiADIAMAAyADAALQAyADAAMgAzAFwAIgAsACAAXAAiAEMAbwBuAHYAZQByAHQAZQBkACAAdABvACAAZgByAGEAYwB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAG8AbQBlAHMAdABpAGMAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ACwAIAAwAC4AMQA0ADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADMALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAwAC4AMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEQAbwBtAGUAcwB0AGkAYwBcACIALAAgAFwAIgBFAHQAaABlAHIAIABFAHgAdAByAGEAYwB0AFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADQALgA1ACwAIAA0AC4ANQAsACAANAAuADgALAAgADQALgA4ACwAIAAwAC4AMAA0ADgAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBEAHIAeQAgAG0AYQB0AHQAZQByACAAZABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxACwAIAAwAC4AOAAxADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyADUALAAgADAALgAxADIALAAgADAALgAxADIALAAgADAALgAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATQBpAGQALQBmAGUAZABcACIALAAgAFwAIgBOAEQARgBcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAAyADQALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAyADIALgAwACwAIAAwAC4AMgAyADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAE0AaQBkAC0AZgBlAGQAXAAiACwAIABcACIARQB0AGgAZQByACAARQB4AHQAcgBhAGMAdABcACIALAAgAFwAIgBwAGUAcgAgAGMAZQBuAHQAXAAiACwAIAA1AC4AMAAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4AMAAsACAAMAAuADAANQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIARAByAHkAIABtAGEAdAB0AGUAcgAgAGQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXAAiACwAIABcACIAZgByAGEAYwB0AGkAbwBuAFwAIgAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQAsACAAMAAuADgAMQA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBMAG8AbgBnAC0ARgBlAGQAXAAiACwAIABcACIAQwByAHUAZABlACAAcAByAG8AdABlAGkAbgBcACIALAAgAFwAIgBmAHIAYQBjAHQAaQBvAG4AXAAiACwAIAAwAC4AMQAzACwAIAAwAC4AMQAyADUALAAgADAALgAxADIALAAgADAALgAxADIALAAgADAALgAxADIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAE4ARABGAFwAIgAsACAAXAAiAHAAZQByACAAYwBlAG4AdABcACIALAAgADIANAAuADAALAAgADIANAAuADAALAAgADIANAAuADAALAAgADIANAAuADAALAAgADAALgAyADQAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIATABvAG4AZwAtAEYAZQBkAFwAIgAsACAAXAAiAEUAdABoAGUAcgAgAEUAeAB0AHIAYQBjAHQAXAAiACwAIABcACIAcABlAHIAIABjAGUAbgB0AFwAIgAsACAANQAuADAALAAgADUALgAwACwAIAA1AC4ANQAsACAANQAuADUALAAgADAALgAwADUANQBcAG4AIAAgACAAIAAgACAAIAAgAH0ALAAgAHIALAAgAGMAKQBcAG4AIAAgACAAIAAgACAAKQBcAG4AIAAgACAAIAApAFwAbgAgACAAKQA7AFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADQAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATQBDAEYAcwAgACgAZgByAGEAYwB0AGkAbwBuACkAIAAoAE0AQwBGAGkAbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABNAEMARgBzAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE0AQwBGAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBTAG8AdQByAGMAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAVgBFAEUAUgBHACAAMgAwADIANgA6ACAAVABhAGIAbABlACAAQQAuADEALgAxAC4ANAA6ACAAQgBlAGUAZgAgAGYAZQBlAGQAbABvAHQAIABjAGEAdAB0AGwAZQAgAC0AIABNAEMARgBzACAAKABmAHIAYQBjAHQAaQBvAG4AKQAgACgATQBDAEYAaQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBNAEMARgBfAFYAYQByAGkAYQB0AGkAbwBuAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANAAsACAAMQAsACAAXABuACAAIAAgACAAIAAgAEwAQQBNAEIARABBACgAcgAsAGMALAAgAFwAbgAgACAAIAAgACAAIAAgACAASQBOAEQARQBYACgAewBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVgBBAFIASQBBAFQASQBPAE4AIABPAE4AIABTAE8AVQBSAEMARQA6AFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBEAHUAcABsAGkAYwBhAHQAZQBkACAATgBTAFcAIAB2AGEAbAB1AGUAcwAgAGYAbwByACAAQQBDAFQAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAE4AVAAgAGEAbgBkACAAVABBAFMAIABjAG8AbAB1AG0AbgBzACAAdwBpAHQAaAAgAFwAdQAwADAAMgA3AG4AbwAgAGQAYQB0AGEAXAB1ADAAMAAyADcAIAB2AGEAbAB1AGUAcwBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATQBDAEYAXwBEAGEAdABhAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAbgAgACAAIAAgAE0AQQBLAEUAQQBSAFIAQQBZACgANgAsACAAMQAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAE4AUwBXAFwAIgAsACAAXAAiAEEAQwBUAFwAIgAsACAAXAAiAFEATABEAFwAIgAsACAAXAAiAE4AVABcACIALAAgAFwAIgBTAEEAXAAiACwAIABcACIAVgBJAEMAXAAiACwAIABcACIAVwBBAFwAIgAsACAAXAAiAFQAQQBTAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAzACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlACAAKABTAHQAbwBjAGsAcABpAGwAZQApAFwAIgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAMAAuADAAMgAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIAAwAC4AMAAyACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABzAHQAbwByAGEAZwBlAFwAIgA7ACAAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIAAwAC4AMAAxACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgADAALgAwADEALAAgADAALgAwADEALAAgADAALgAwADEALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAIABcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAMAAsACAAMAAsACAAXAAiAE4AbwAgAGQAYQB0AGEAXAAiACwAIAAwACwAIAAwACwAIAAwACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwAgAFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAcgB0AGkAYQByAHkAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABFAGYAZgBsAHUAZQBuAHQAIABwAG8AbgBkACkAXAAiACwAIAAwAC4ANwA1ACwAIAAwAC4ANwA1ACwAIAAwAC4ANwA3ACwAIABcACIATgBvACAAZABhAHQAYQBcACIALAAgADAALgA3ADUALAAgADAALgA3ADUALAAgADAALgA3ADcALAAgAFwAIgBOAG8AIABkAGEAdABhAFwAIgAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBcAG4AXABuAC8AKgAgAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXABuAFQAYQBiAGwAZQAgAEEALgAxAC4AMQAuADUAOgAgAEIAZQBlAGYAIABmAGUAZQBkAGwAbwB0ACAAYwBhAHQAdABsAGUAIAAtACAATgBpAHQAcgBvAHUAcwAgAG8AeABpAGQAZQAgAEUARgBzACAAKABFAEYAbQBUACkAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AKgAvAFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABOAGkAdAByAG8AdQBzACAAbwB4AGkAZABlACAARQBGAHMAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBGAHMAXwBVAG4AaQB0AFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAEYAcwBfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA1ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAE4AaQB0AHIAbwB1AHMAIABvAHgAaQBkAGUAIABFAEYAcwAgACgARQBGAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAAyACwAIAAxACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBWAEEAUgBJAEEAVABJAE8ATgAgAE8ATgAgAFMATwBVAFIAQwBFADoAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAEEAZABkAGUAZAAgAFwAdQAwADAAMgA3AE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcAHUAMAAwADIANwAgAGMAbwBsAHUAbQBuACAAdwBpAHQAaAAgAE0ATQBTACAAbgBhAG0AZQBzACAAdABoAGEAdAAgAG0AYQB0AGMAaAAgAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBzAC4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUARgBzAF8ARABhAHQAYQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADYALAAgADQALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFQAcgBlAGEAdABtAGUAbgB0ACAAcwB0AGEAZwBlACAAVABcACIALAAgAFwAIgBNAE0AUwAgAG0AXAAiACwAIABcACIARQBGAG0AVAAgACgAawBnACAATgAyAE8ALQBOAC8AawBnACAATgApAFwAIgAsACAAXAAiAE4ASQBSACAAZABlAGYAaQBuAGkAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUAByAGkAbQBhAHIAeQBcACIALAAgAFwAIgBEAHIAeQAgAGwAbwB0ACAAKABGAGUAZQBkAHAAYQBkACkAXAAiACwAIAAwAC4AMAAwADUANAAsACAAXAAiAEQAcgB5AGwAbwB0ACAAKABmAGUAZQBkACAAcABhAGQAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIAUwBvAGwAaQBkACAAUwB0AG8AcgBhAGcAZQAgACgAUwB0AG8AYwBrAHAAaQBsAGUAKQBcACIALAAgADAALgAwADAANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4AMAAxACwAIABcACIAQwBvAG0AcABvAHMAdABpAG4AZwAgACgAcABhAHMAcwBpAHYAZQAgAHcAaQBuAGQAcgBvAHcAKQBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAUwBlAGMAbwBuAGQAYQByAHkAXAAiACwAIABcACIARABpAHIAZQBjAHQAIABBAHAAcABsAGkAYwBhAHQAaQBvAG4AIAB0AG8AIABzAG8AaQBsAFwAIgAsACAAMAAsACAAXAAiAEQAaQByAGUAYwB0ACAAYQBwAHAAbABpAGMAYQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAGUAcgB0AGkAYQByAHkAXAAiACwAIABcACIAVQBuAGMAbwB2AGUAcgBlAGQAIABhAG4AYQBlAHIAbwBiAGkAYwAgAGwAYQBnAG8AbwBuACAAKABFAGYAZgBsAHUAZQBuAHQAIABQAG8AbgBkACkAXAAiACwAIAAwACwAIABcACIAQQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFwAbgBcAG4ALwAqACAAXABuAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAFwAbgBUAGEAYgBsAGUAIABBAC4AMQAuADEALgA2ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAbgAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0ALQAtAC0AXABuACoALwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFQAaQB0AGwAZQBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIARgBlAGUAZABsAG8AdAAgAC0AIABGAHIAYQBjAHQAaQBvAG4AIABvAGYAIABOACAAdgBvAGwAYQB0AGkAbABpAHMAZQBkACAAYgB5ACAATQBNAFMAIAAoAEYAcgBhAGMARwBBAFMATQBtAFQAKQBcACIAKQA7AFwAbgBcAG4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAZQBlAGQAbABvAHQAXwBGAHIAYQBjAE4AVgBvAGwAYQB0AGkAbABpAHMAZQBkAF8AVQBuAGkAdABcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcACIAXAAiACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAFMAbwB1AHIAYwBlAFwAbgAgACAAPQBMAEEATQBCAEQAQQAoAFwAIgBWAEUARQBSAEcAIAAyADAAMgA2ADoAIABUAGEAYgBsAGUAIABBAC4AMQAuADEALgA2ADoAIABCAGUAZQBmACAAZgBlAGUAZABsAG8AdAAgAGMAYQB0AHQAbABlACAALQAgAEYAcgBhAGMAdABpAG8AbgAgAG8AZgAgAE4AIAB2AG8AbABhAHQAaQBsAGkAcwBlAGQAIABiAHkAIABNAE0AUwAgACgARgByAGEAYwBHAEEAUwBNAG0AVAApAFwAIgApADsAXABuAFwAbgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgBlAGUAZABsAG8AdABfAEYAcgBhAGMATgBWAG8AbABhAHQAaQBsAGkAcwBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgBcAG4AIAAgAD0ATABBAE0AQgBEAEEAKABcAG4AIAAgACAAIABNAEEASwBFAEEAUgBSAEEAWQAoADIALAAgADEALAAgAFwAbgAgACAAIAAgACAAIABMAEEATQBCAEQAQQAoAHIALABjACwAIABcAG4AIAAgACAAIAAgACAAIAAgAEkATgBEAEUAWAAoAHsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFYAQQBSAEkAQQBUAEkATwBOACAATwBOACAAUwBPAFUAUgBDAEUAOgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAQQBkAGQAZQBkACAAXAB1ADAAMAAyADcATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAdQAwADAAMgA3ACAAYwBvAGwAdQBtAG4AIAB3AGkAdABoACAATQBNAFMAIABuAGEAbQBlAHMAIAB0AGgAYQB0ACAAbQBhAHQAYwBoACAATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAHMALgBcACIAXABuACAAIAAgACAAIAAgACAAIAB9ACwAIAByACwAIABjACkAXABuACAAIAAgACAAIAAgACkAXABuACAAIAAgACAAKQBcAG4AIAAgACkAOwBcAG4AXABuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAGUAZQBkAGwAbwB0AF8ARgByAGEAYwBOAFYAbwBsAGEAdABpAGwAaQBzAGUAZABfAEQAYQB0AGEAXABuACAAIAA9AEwAQQBNAEIARABBACgAXABuACAAIAAgACAATQBBAEsARQBBAFIAUgBBAFkAKAA2ACwAIAA0ACwAIABcAG4AIAAgACAAIAAgACAATABBAE0AQgBEAEEAKAByACwAYwAsACAAXABuACAAIAAgACAAIAAgACAAIABJAE4ARABFAFgAKAB7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBUAHIAZQBhAHQAbQBlAG4AdAAgAHMAdABhAGcAZQAgAFQAXAAiACwAIABcACIATQBNAFMAIABtAFwAIgAsACAAXAAiAEYAcgBhAGMARwBBAFMATQBtAFQAIAAoAGsAZwAgAE4ASAAzAC0ATgAgACsAIABOAE8AeAAtAE4AKQAvAGsAZwAgAE4AXAAiACwAIABcACIATgBJAFIAIABkAGUAZgBpAG4AaQB0AGkAbwBuAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBQAHIAaQBtAGEAcgB5AFwAIgAsACAAXAAiAEQAcgB5ACAAbABvAHQAIAAoAEYAZQBlAGQAcABhAGQAKQBcACIALAAgADAALgA2ACwAIABcACIARAByAHkAbABvAHQAIAAoAGYAZQBlAGQAIABwAGEAZAApAFwAIgA7AFwAbgAgACAAIAAgACAAIAAgACAAIAAgAFwAIgBTAGUAYwBvAG4AZABhAHIAeQBcACIALAAgAFwAIgBTAG8AbABpAGQAIABTAHQAbwByAGEAZwBlACAAKABTAHQAbwBjAGsAcABpAGwAZQApAFwAIgAsACAAMAAuADIANQAsACAAXAAiAFMAbwBsAGkAZAAgAHMAdABvAHIAYQBnAGUAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAFAAYQBzAHMAaQB2AGUAIABXAGkAbgBkAHIAbwB3ACkAXAAiACwAIAAwAC4ANAAsACAAXAAiAEMAbwBtAHAAbwBzAHQAaQBuAGcAIAAoAHAAYQBzAHMAaQB2AGUAIAB3AGkAbgBkAHIAbwB3ACkAXAAiADsAXABuACAAIAAgACAAIAAgACAAIAAgACAAXAAiAFMAZQBjAG8AbgBkAGEAcgB5AFwAIgAsACAAXAAiAEQAaQByAGUAYwB0ACAAQQBwAHAAbABpAGMAYQB0AGkAbwBuACAAdABvACAAcwBvAGkAbABcACIALAAgADAALAAgAFwAIgBEAGkAcgBlAGMAdAAgAGEAcABwAGwAaQBjAGEAdABpAG8AbgBcACIAOwBcAG4AIAAgACAAIAAgACAAIAAgACAAIABcACIAVABlAHIAdABpAGEAcgB5AFwAIgAsACAAXAAiAFUAbgBjAG8AdgBlAHIAZQBkACAAYQBuAGEAZQByAG8AYgBpAGMAIABsAGEAZwBvAG8AbgAgACgARQBmAGYAbAB1AGUAbgB0ACAAcABvAG4AZAApAFwAIgAsACAAMAAuADMANQAsACAAXAAiAEEAbgBhAGUAcgBvAGIAaQBjACAAbABhAGcAbwBvAG4AXAAiAFwAbgAgACAAIAAgACAAIAAgACAAfQAsACAAcgAsACAAYwApAFwAbgAgACAAIAAgACAAIAApAFwAbgAgACAAIAAgACkAXABuACAAIAApADsAXABuAFwAbgAiAH0AXQAsACIAcAByAG8AagBlAGMAdABOAGEAbQBlAHMAIgA6AFsAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAF8ARABhAGkAcgB5AF8AMwBfAEIAXwAxAF8AYQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAxAF8ARABhAGkAcgB5AF8AMwBfAEIAXwAxAF8AYQBfAEEAcwBoAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBBAHMAaABDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADEAXwBEAGEAaQByAHkAXwAzAF8AQgBfADEAXwBhAF8ARQBtAGkAcwBzAGkAbwBuAHMAUABvAHQAZQBuAHQAaQBhAGwAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMQBfAEQAYQBpAHIAeQBfADMAXwBCAF8AMQBfAGEAXwBFAG0AaQBzAHMAaQBvAG4AcwBQAG8AdABlAG4AdABpAGEAbABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADEAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AMQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBMAGkAdgBlAFcAZQBpAGcAaAB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AMQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBMAGkAdgBlAFcAZQBpAGcAaAB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADEAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwAyAF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEwAaQB2AGUAVwBlAGkAZwBoAHQARwBhAGkAbgBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADIAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATABpAHYAZQBXAGUAaQBnAGgAdABHAGEAaQBuAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AMwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADMAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AMwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AMwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA0AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEQATQBEAEEAbgBkAEMAUABfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANABfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBEAE0ARABBAG4AZABDAFAAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA0AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEQATQBEAEEAbgBkAEMAUABfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADEAXwA0AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEQATQBEAEEAbgBkAEMAUABfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADUAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUAByAGUAVwBlAGEAbgBlAGQARABhAHQAYQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBQAHIAZQBXAGUAYQBuAGUAZABEAGEAdABhAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBQAHIAZQBXAGUAYQBuAGUAZABEAGEAdABhAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADUAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAUAByAGUAVwBlAGEAbgBlAGQARABhAHQAYQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADcAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATQBDAEYAcwBGAG8AcgBNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBNAEMARgBzAEYAbwByAE0ATQBTAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8ANwBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBNAEMARgBzAEYAbwByAE0ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADcAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATQBDAEYAcwBGAG8AcgBNAE0AUwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADkAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATgBPADIARQBGAEEAbgBkAEYAcgBhAGMATgBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AOQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBOAE8AMgBFAEYAQQBuAGQARgByAGEAYwBOAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAxAF8AOQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBOAE8AMgBFAEYAQQBuAGQARgByAGEAYwBOAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMQBfADkAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUATgBPADIARQBGAEEAbgBkAEYAcgBhAGMATgBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBTAHQAYQB0AGUAVABlAHIAcgBpAHQAbwByAHkAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBTAHQAYQB0AGUAVABlAHIAcgBpAHQAbwByAHkAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBTAHQAYQB0AGUAVABlAHIAcgBpAHQAbwByAHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8AUwB0AGEAdABlAFQAZQByAHIAaQB0AG8AcgB5AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBTAHQAYQB0AGUAVABlAHIAcgBpAHQAbwByAHkAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AUwB5AG0AYgBvAGwAcwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8ARABhAGkAcgB5AF8ARABhAGkAcgB5AEMAYQB0AHQAbABlAEMAbABhAHMAcwBlAHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAQwBsAGEAcwBzAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBDAGwAYQBzAHMAZQBzAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAFMAeQBtAGIAbwBsAHMAXwBMAGkAdgBlAHMAdABvAGMAawBfAEQAYQBpAHIAeQBfAEQAYQBpAHIAeQBDAGEAdAB0AGwAZQBDAGwAYQBzAHMAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBTAHkAbQBiAG8AbABzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAaQByAHkAXwBEAGEAaQByAHkAQwBhAHQAdABsAGUAQwBsAGEAcwBzAGUAcwBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkAXwBBAGwAbABvAGMAYQB0AGkAbwBuAE8AZgBXAGEAcwB0AGUAVABvAE0ATQBTAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBsAGwAbwBjAGEAdABpAG8AbgBPAGYAVwBhAHMAdABlAFQAbwBNAE0AUwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQBpAHIAeQBfAEEAbABsAG8AYwBhAHQAaQBvAG4ATwBmAFcAYQBzAHQAZQBUAG8ATQBNAFMAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBsAGwAbwBjAGEAdABpAG8AbgBPAGYAVwBhAHMAdABlAFQAbwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAaQByAHkALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAGkAcgB5AF8AQQBsAGwAbwBjAGEAdABpAG8AbgBPAGYAVwBhAHMAdABlAFQAbwBNAE0AUwBfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBfAFQAaQB0AGwAZQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAF8ARABhAHQAYQAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAdQBlAGwAXwBTAGMAbwBwAGUAMQBTAGMAbwBwAGUAMwBFAG0AaQBzAHMAaQBvAG4ARgBhAGMAdABvAHIAcwBTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAHUAZQBsAF8AUwBjAG8AcABlADEAUwBjAG8AcABlADMARQBtAGkAcwBzAGkAbwBuAEYAYQBjAHQAbwByAHMAVAByAGEAbgBzAHAAbwByAHQAXwBEAGEAdABhACIALAAiAEYAdQBlAGwAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgB1AGUAbABfAFMAYwBvAHAAZQAxAFMAYwBvAHAAZQAzAEUAbQBpAHMAcwBpAG8AbgBGAGEAYwB0AG8AcgBzAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AVQBuAGkAdAAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMQBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADEAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBUAHIAYQBuAHMAcABvAHIAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAxAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AVAByAGEAbgBzAHAAbwByAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AMgBfADEAXwAxAF8AXwAxAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAFMAdABhAHQAaQBvAG4AYQByAHkAXwBVAG4AaQB0ACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwAyAF8AMQBfADEAXwBfADEAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4AUwB0AGEAdABpAG8AbgBhAHIAeQBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfADIAXwAxAF8AMQBfAF8AMQBfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBTAHQAYQB0AGkAbwBuAGEAcgB5AF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AVABpAHQAbABlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFUAbgBpAHQAIgAsACIARgB1AGUAbABfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOABfAFgAXwBGAHUAZQBsAEMAbwBtAGIAdQBzAHQAaQBvAG4ARwBlAG4AZQByAGkAYwBfAFMAbwB1AHIAYwBlACIALAAiAEYAdQBlAGwAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADgAXwBYAF8ARgB1AGUAbABDAG8AbQBiAHUAcwB0AGkAbwBuAEcAZQBuAGUAcgBpAGMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAHUAZQBsAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA4AF8AWABfAEYAdQBlAGwAQwBvAG0AYgB1AHMAdABpAG8AbgBHAGUAbgBlAHIAaQBjAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBGAGUAcgB0AGkAbABpAHMAZQByAFAAcgBvAGQAdQBjAHQATABvAG8AawB1AHAAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAHUAbQBQAHIAbwBkAHUAYwB0AEEAcABwAGwAaQBlAGQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABBAHAAcABsAGkAZQBkACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABvAHQAYQBsAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQAQQBwAHAAbABpAGUAZABBAGwAbABJAG4AZwByAGUAZABpAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAG8AdABhAGwAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZAB0AEEAcABwAGwAaQBlAGQAQgB5AFMAbwB1AHIAYwBlAEEAbABsAEkAbgBnAHIAZQBkAGkAZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAbwB0AGEAbABBAGMAdABpAHYAZQBJAG4AZwByAGUAZABpAGUAbgB0AEEAcABwAGwAaQBlAGQAQQBsAGwASQBuAGcAcgBlAGQAaQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAUwBjAG8AcABlADMARQBGACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBlAHQAQwBoAGUAbQBpAGMAYQBsAEMAbwBtAHAAbwB1AG4AZABFAGwAZQBtAGUAbgB0AEYAcgBhAGMAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAGMAbwBwAGUAMgBTAGMAbwBwAGUAMwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ARABhAHQAYQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8AUwBjAG8AcABlADIAUwBjAG8AcABlADMATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVABpAHQAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMABfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADAAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAyAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAwAF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwA5AF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AOQBfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADMARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAFQAaQB0AGwAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwAxADEAXwA5AF8AMQBfADEAXwBfADEAXwBTAGMAbwBwAGUAMwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBMAG8AYwBhAHQAaQBvAG4AQgBhAHMAZQBkAF8AVQBuAGkAdAAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADEAMQBfADkAXwAxAF8AMQBfAF8AMQBfAFMAYwBvAHAAZQAzAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEwAbwBjAGEAdABpAG8AbgBCAGEAcwBlAGQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AMQAxAF8AOQBfADEAXwAxAF8AXwAxAF8AUwBjAG8AcABlADMARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ATABvAGMAYQB0AGkAbwBuAEIAYQBzAGUAZABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AUwBvAHUAcgBjAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwARwBXAFAAXwBEAGEAdABhACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AQwBoAGUAbQBpAGMAYQBsAEcAVwBQAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBUAGkAdABsAGUAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBTAG8AdQByAGMAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEMAaABlAG0AaQBjAGEAbABCAGwAZQBuAGQAcwBfAEQAYQB0AGEAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBDAGgAZQBtAGkAYwBhAGwAQgBsAGUAbgBkAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEwAZQBhAGsAYQBnAGUAUgBhAHQAZQBzAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGUAcwBjAHIAaQBwAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBMAGUAYQBrAGEAZwBlAFIAYQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBEAGEAdABhACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ATABlAGEAawBhAGcAZQBSAGEAdABlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AVABpAHQAbABlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBSAGUAZgByAGkAZwBlAHIAYQBuAHQAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AVgBFAEUAUgBHAF8AOQBfADEAXwAxAF8AXwAxAF8AUgBlAGYAcgBpAGcAZQByAGEAbgB0AEwAZQBhAGsAaQBuAGcAXwBVAG4AaQB0ACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFMAbwB1AHIAYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBWAEUARQBSAEcAXwA5AF8AMQBfADEAXwBfADEAXwBSAGUAZgByAGkAZwBlAHIAYQBuAHQATABlAGEAawBpAG4AZwBfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AIgAsACIAUgBlAGYAcgBpAGcAZQByAGEAbgB0AHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAFYARQBFAFIARwBfADkAXwAxAF8AMQBfAF8AMQBfAFIAZQBmAHIAaQBnAGUAcgBhAG4AdABMAGUAYQBrAGkAbgBnAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBHAFcAUAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAxAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMQBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADEAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAFUAcgBlAGEARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8AVQByAGUAYQBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADEAXwBVAHIAZQBhAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAxAF8AVQByAGUAYQBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAFUAcgBlAGEARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAFUAcgBlAGEARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMQBfAFUAcgBlAGEARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ASQBuAG8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMQBfADEAXwAzAF8AXwAyAF8ATQBhAHMAcwBPAGYAVQByAGUAYQBBAHAAcABsAGkAZQBkAFQAbwBTAG8AaQBsAHMAXwBTAG8AdQByAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEkAbgBvAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADEAXwAxAF8AMwBfAF8AMgBfAE0AYQBzAHMATwBmAFUAcgBlAGEAQQBwAHAAbABpAGUAZABUAG8AUwBvAGkAbABzAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBJAG4AbwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAxAF8AMQBfADMAXwBfADIAXwBNAGEAcwBzAE8AZgBVAHIAZQBhAEEAcABwAGwAaQBlAGQAVABvAFMAbwBpAGwAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAEcAVwBQACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAxAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADEAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMQBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBPAHIAZwBhAG4AaQBjAC4AVgBFAEUAUgBHAF8ANQBfADIAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATwByAGcAYQBuAGkAYwAuAFYARQBFAFIARwBfADUAXwAyAF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAE8AcgBnAGEAbgBpAGMALgBWAEUARQBSAEcAXwA1AF8AMgBfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGkAbQBlAC4AVgBFAEUAUgBHAF8ANQBfADMAXwAxAF8AMQBfAF8AMQBfAEwAaQBtAGUAQQBwAHAAbABpAGMAYQB0AGkAbwBuAF8AUwBvAHUAcgBjAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABpAG0AZQAuAFYARQBFAFIARwBfADUAXwAzAF8AMQBfADEAXwBfADEAXwBMAGkAbQBlAEEAcABwAGwAaQBjAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAaQBtAGUALgBWAEUARQBSAEcAXwA1AF8AMwBfADEAXwAxAF8AXwAxAF8ATABpAG0AZQBBAHAAcABsAGkAYwBhAHQAaQBvAG4AXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARwBXAFAAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAxAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMQBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADEAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4ALgBWAEUARQBSAEcAXwA1AF8ANABfADEAXwAxAF8AXwAyAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAC4AVgBFAEUAUgBHAF8ANQBfADQAXwAxAF8AMQBfAF8AMgBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgAuAFYARQBFAFIARwBfADUAXwA0AF8AMQBfADEAXwBfADIAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAEIAYQBsAGUAZABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABCAGEAbABlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAQgBhAGwAZQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADEAXwAxAF8AMgBfAF8AMQBhAF8AXwBGAHIAYQBjAHQAaQBvAG4ATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBSAGUAbQBvAHYAZQBkAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AQwByAG8AcABSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMQBfADEAXwAyAF8AXwAxAGEAXwBfAEYAcgBhAGMAdABpAG8AbgBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAFIAZQBtAG8AdgBlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAxAF8AMQBfADIAXwBfADEAYQBfAF8ARgByAGEAYwB0AGkAbwBuAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAUgBlAG0AbwB2AGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEEAdAB0AHIAaQBiAHUAdABlAHMAXwBEAGEAdABhACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABBAHQAdAByAGkAYgB1AHQAZQBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAHIAbwBwAEYAcgBhAGMAdABpAG8AbgBSAGUAbQBvAHYAZQBkAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBEAGEAdABhACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwByAG8AcABGAHIAYQBjAHQAaQBvAG4AUgBlAG0AbwB2AGUAZABfAEMAdQBzAHQAbwBtAGkAcwBlAGQARABhAHQAYQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAcgBvAHAARgByAGEAYwB0AGkAbwBuAFIAZQBtAG8AdgBlAGQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFAAYQBzAHQAdQByAGUAQQB0AHQAcgBpAGIAdQB0AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUABhAHMAdAB1AHIAZQBBAHQAdAByAGkAYgB1AHQAZQBzAF8ARABhAHQAYQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEIAdQByAG4AaQBuAGcATwBmAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAFIAZQBzAGkAZAB1AGUAcwBFAEYAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQgB1AHIAbgBpAG4AZwBPAGYAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwAUgBlAHMAaQBkAHUAZQBzAEUARgBzAF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAyAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAyAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMgBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAyAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADIAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEcAYQBpAG4AXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAzAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFQAaQB0AGwAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8AMwBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEQAcgB5AE0AYQB0AHQAZQByAEQAaQBnAGUAcwB0AGkAYgBpAGwAaQB0AHkAXwBVAG4AaQB0ACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAzAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAzAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwAzAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8ARAByAHkATQBhAHQAdABlAHIARABpAGcAZQBzAHQAaQBiAGkAbABpAHQAeQBfAEQAYQB0AGEAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AVABpAHQAbABlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA0AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AQwByAHUAZABlAFAAcgBvAHQAZQBpAG4AQwBvAG4AdABlAG4AdABfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADQAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8ARABhAHQAYQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADUAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBDAHIAdQBkAGUAUAByAG8AdABlAGkAbgBDAG8AbgB0AGUAbgB0AF8AVQBuAGkAdAAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQAXwBTAG8AdQByAGMAZQAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAEMAcgB1AGQAZQBQAHIAbwB0AGUAaQBuAEMAbwBuAHQAZQBuAHQAXwBEAGEAdABhACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA2AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBUAGkAdABsAGUAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADYAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFUAbgBpAHQAIgAsACIAUwBvAHUAcgBjAGUARABhAHQAYQBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgAuAE4ASQBSAF8AMgAwADIAMwBfAFYAbwBsADIAXwBBADUAXwA1AF8AMgBfADYAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYAXwBTAHQAYQBuAGQAYQByAGQAUgBlAGYAZQByAGUAbgBjAGUAVwBlAGkAZwBoAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBQAGEAcwB0AHUAcgBlAEIAZQBlAGYALgBOAEkAUgBfADIAMAAyADMAXwBWAG8AbAAyAF8AQQA1AF8ANQBfADIAXwA2AF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAF8AUwB0AGEAbgBkAGEAcgBkAFIAZQBmAGUAcgBlAG4AYwBlAFcAZQBpAGcAaAB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAG8AdQByAGMAZQBEAGEAdABhAF8AUABhAHMAdAB1AHIAZQBCAGUAZQBmAC4ATgBJAFIAXwAyADAAMgAzAF8AVgBvAGwAMgBfAEEANQBfADUAXwAyAF8ANgBfAFAAYQBzAHQAdQByAGUAQgBlAGUAZgBfAFMAdABhAG4AZABhAHIAZABSAGUAZgBlAHIAZQBuAGMAZQBXAGUAaQBnAGgAdABzAF8ARABhAHQAYQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADEAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMQBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAxAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMALgBWAEUARQBSAEcAXwA2AF8AMgBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ASQBuAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAF8AVQBuAGkAdAAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwAuAFYARQBFAFIARwBfADYAXwAyAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBJAG4AUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAHMAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBzAC4AVgBFAEUAUgBHAF8ANgBfADIAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEkAbgBQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAcwBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABlAG4AcwBpAHQAeQBPAGYATQBlAHQAaABhAG4AZQBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAZQBuAHMAaQB0AHkATwBmAE0AZQB0AGgAYQBuAGUAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQATgAyAG8ARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAEMAZwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBvAG4AdgBlAHIAdABOADIAbwBFAGwAZQBtAGUAbgB0AGEAbABUAG8ATQBvAGwAZQBjAHUAbABhAHIAQwBnAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AE4AMgBvAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBDAGcAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAG8AbgB2AGUAcgB0AEcAYQBzAEUAbABlAG0AZQBuAHQAYQBsAFQAbwBNAG8AbABlAGMAdQBsAGEAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbwBuAHYAZQByAHQARwBhAHMARQBsAGUAbQBlAG4AdABhAGwAVABvAE0AbwBsAGUAYwB1AGwAYQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARwBXAFAAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBHAFcAUABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEEAdQBzAHQAcgBhAGwAaQBhAG4AUwB0AGEAdABlAHMAVABlAHIAcgBpAHQAbwByAGkAZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQQB1AHMAdAByAGEAbABpAGEAbgBTAHQAYQB0AGUAcwBUAGUAcgByAGkAdABvAHIAaQBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAQQBTAEEANABBAHIAZQBhAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAEEAUwBBADQAQQByAGUAYQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBBAFMAQQA0AEEAcgBlAGEAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVwBlAHQAQQBuAGQARAByAHkAWgBvAG4AZQBzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBXAGUAdABBAG4AZABEAHIAeQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFcAZQB0AEEAbgBkAEQAcgB5AFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEMAbABpAG0AYQB0AGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBDAGwAaQBtAGEAdABlAFoAbwBuAGUAcwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AQwBsAGkAbQBhAHQAZQBaAG8AbgBlAHMAXwBBAHAAcABlAG4AZABpAGMAZQBzACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBUAGUAbQBwAGUAcgBhAHQAdQByAGUAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVABlAG0AcABlAHIAYQB0AHUAcgBlAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFQAZQBtAHAAZQByAGEAdAB1AHIAZQBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBSAGEAaQBuAGYAYQBsAGwAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AUgBhAGkAbgBmAGEAbABsAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAFIAYQBpAG4AZgBhAGwAbABaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGUAYQBjAGgAaQBuAGcAWgBvAG4AZQBzAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABlAGEAYwBoAGkAbgBnAFoAbwBuAGUAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAZQBhAGMAaABpAG4AZwBaAG8AbgBlAHMAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARABhAHQAYQBTAGMAbwByAGUAcwBfAFMAYwBvAHAAZQAzAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBEAGEAdABhAFMAYwBvAHIAZQBzAF8AUwBjAG8AcABlADMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEQAYQB0AGEAUwBjAG8AcgBlAHMAXwBTAGMAbwBwAGUAMwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMATABFAEEAQwBIAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEwARQBBAEMASABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBMAEUAQQBDAEgAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEUARgBsAGUAYQBjAGgAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBFAEYAbABlAGEAYwBoAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARQBGAGwAZQBhAGMAaABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABOADIATwBUAG8AQwBPADIAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQATgAyAE8AVABvAEMATwAyAGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AE4AMgBPAFQAbwBDAE8AMgBlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQwBvAG0AbQBvAG4AXwBDAG8AbgB2AGUAcgB0AEMASAA0AFQAbwBDAE8AMgBlAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEMAbwBtAG0AbwBuAF8AQwBvAG4AdgBlAHIAdABDAEgANABUAG8AQwBPADIAZQBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBMAGEAdABlAHgARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBDAG8AbQBtAG8AbgBfAEMAbwBuAHYAZQByAHQAQwBIADQAVABvAEMATwAyAGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBOADIATwBFAEYAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBzAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVQByAGUAYQBDAE8AMgBFAEYAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBVAHIAZQBhAEMATwAyAEUARgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBVAHIAZQBhAEMATwAyAEUARgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8AVQByAGUAYQBDAE8AMgBFAEYAXwBEAGEAdABhACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAE4AMgBPAEUARgBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ATgAyAE8ARQBGAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEcAQQBTAEYAZgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBHAEEAUwBGAGYASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEcAQQBTAEYAZgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEcAQQBTAEYAZgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAEcAQQBTAEYAZgBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMARwBBAFMARgBmAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBGAHIAYQBjAFcARQBUAEkAcgByAGkAZwBhAHQAaQBvAG4AXwBTAG8AdQByAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAEMAcgBvAHAAcABpAG4AZwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAF8ARgByAGEAYwBXAEUAVABJAHIAcgBpAGcAYQB0AGkAbwBuAF8ARABhAHQAYQAiACwAIgBDAG8AbQBtAG8AbgBDAHIAbwBwAHAAaQBuAGcAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AQwBvAG0AbQBvAG4AQwByAG8AcABwAGkAbgBnAF8AUwBvAHUAcgBjAGUARABhAHQAYQBfAEYAcgBhAGMAVwBFAFQASQByAHIAaQBnAGEAdABpAG8AbgBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMAVwBFAFQATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8ARgByAGEAYwBXAEUAVABNAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAEYAcgBhAGMATABFAEEAQwBIAF8ATQBTAF8AUwBvAHUAcgBjAGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBGAHIAYQBjAEwARQBBAEMASABfAE0AUwBfAEQAYQB0AGEAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBvAHUAcgBjAGUARABhAHQAYQBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AQwBvAG0AbQBvAG4AXwBTAHkAbQBiAG8AbABzAE0ATQBTAF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFYAYQBpAHIAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAG8AdQByAGMAZQBEAGEAdABhAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBDAG8AbQBtAG8AbgBfAFMAeQBtAGIAbwBsAHMATQBNAFMAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAFMAbwB1AHIAYwBlACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAbwB1AHIAYwBlAEQAYQB0AGEAXwBMAGkAdgBlAHMAdABvAGMAawBfAEMAbwBtAG0AbwBuAF8AUwB5AG0AYgBvAGwAcwBNAE0AUwBfAEQAYQB0AGEAIgAsACIARgB1AGUAbABfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEYAdQBlAGwAXwBHAGUAdABUAHIAYQBuAHMAcABvAHIAdABGAHUAZQBsAFMAdAByAGkAbgBnACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8ARwBlAHQAUwB0AGEAdABpAG8AbgBhAHIAeQBGAHUAZQBsAFMAdAByAGkAbgBnACIALAAiAEYAdQBlAGwAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBGAHUAZQBsAF8AVABvAHQAYQBsAEMAbwBuAHMAdQBtAHAAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEQAYQB5AHMATQBvAHYAZQBtAGUAbgB0AFQAbwBNAG8AbgB0AGgARQBuAGQAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBMAGkAdgBlAHcAZQBpAGcAaAB0AEYAcgBvAG0AUwB0AGEAcgB0AE8AZgBNAG8AbgB0AGgAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBBAHYAZQByAGEAZwBlAEwAaQB2AGUAdwBlAGkAZwBoAHQAUgBlAG0AYQBpAG4AaQBuAGcASABlAGEAZAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AFMAdABhAHIAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEwAaQB2AGUAdwBlAGkAZwBoAHQAQQB0AEUAbgBkACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AQQB2AGUAcgBhAGcAZQBMAGkAdgBlAHcAZQBpAGcAaAB0AE0AbwBuAHQAaAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEMAYQBsAGMAdQBsAGEAdABlAFMAdABhAHkARAB1AHIAYQB0AGkAbwBuAFQAbwBFAG4AZAAyACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AQQB2AGUAcgBhAGcAZQBIAGUAYQBkAE0AbwBuAHQAaAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFQAbwB0AGEAbABCAGkAcgB0AGgAcwBEAHUAcgBpAG4AZwBNAG8AbgB0AGgAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBDAGEAbABjAHUAbABhAHQAZQBQAHIAbwBwAG8AcgB0AGkAbwBuAEMAbwB3AHMAQwBhAGwAdgBpAG4AZwAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAFQAbwB0AGEAbABNAG8AdgBlAG0AZQBuAHQATABpAHYAZQB3AGUAaQBnAGgAdABTAG8AbABkACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8AUwB1AG0AUAB1AHIAYwBoAGEAcwBlAGQATABpAHYAZQB3AGUAaQBnAGgAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEgAZQBhAGQAQQB0AEUAbgBkACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQARQBuAHQAcgB5AEQAYQB0AGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBHAGUAdABFAHgAaQB0AEQAYQB0AGUAIgAsACIAQwBvAG0AbQBvAG4ATABpAHYAZQBzAHQAbwBjAGsAXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBMAGkAdgBlAHMAdABvAGMAawBNAG8AdgBlAG0AZQBuAHQAXwBHAGUAdABIAGUAYQBkAEEAdABFAHgAaQB0ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQBuAHQAcgB5ACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQATABpAHYAZQB3AGUAaQBnAGgAdABBAHQARQB4AGkAdAAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEQAdQByAGEAdABpAG8AbgBPAGYAUwB0AGEAeQAyACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQARAB1AHIAYQB0AGkAbwBuAE8AZgBTAHQAYQB5AFAAbwBzAHQAVwBlAGEAbgBpAG4AZwAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEcAZQB0AEEAdgBlAHIAYQBnAGUATABpAHYAZQB3AGUAaQBnAGgAdABHAGEAaQBuACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsATQBvAHYAZQBtAGUAbgB0AF8ARwBlAHQAQQBkAGoAdQBzAHQAZQBkAEwAaQB2AGUAdwBlAGkAZwBoAHQARwBhAGkAbgAiACwAIgBDAG8AbQBtAG8AbgBMAGkAdgBlAHMAdABvAGMAawBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAEwAaQB2AGUAcwB0AG8AYwBrAE0AbwB2AGUAbQBlAG4AdABfAEMAYQBsAGMAdQBsAGEAdABlAEcAcgBvAHcAdABoAEYAYQBjAHQAbwByACIALAAiAEMAbwBtAG0AbwBuAEwAaQB2AGUAcwB0AG8AYwBrAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4ATABpAHYAZQBzAHQAbwBjAGsAXwBMAG8AbwBrAHUAcABNAEMARgBTAHQAYQB0AGUAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBSAG8AdwBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQQByAHIAYQB5AFQAYQBiAGwAZQBDAG8AbAB1AG0AbgBTAHQAYQByAHQATgB1AG0AYgBlAHIAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARABpAHMAcABsAGEAeQBBAHIAcgBhAHkASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBMAG8AbwBrAHUAcABWAGEAbAB1AGUASQBuAFQAYQBiAGwAZQBOAHUAbQBiAGUAcgAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHAAbABpAHQAUwB0AHIAaQBuAGcASQBuAHQAbwBBAHIAcgBhAHkAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBVAHQAaQBsAGkAdAB5AF8ARwBlAHQAQwBsAGkAbQBhAHQAZQBaAG8AbgBlACIALAAiAEMAbwBtAG0AbwBuAF8ASQBuAHAAdQB0AEYAdQBuAGMAdABpAG8AbgBzAC4AVQB0AGkAbABpAHQAeQBfAEwAbwBvAGsAdQBwAEkAdABlAG0ARgByAG8AbQBNAGkAbgBNAGEAeAAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBTAHUAbQBRAHUAYQBuAHQAaQB0AHkARgByAG8AbQBDAHIAaQB0AGUAcgBpAGEAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAQwB5AGMAbABlAHMAIgAsACIAQwBvAG0AbQBvAG4AXwBJAG4AcAB1AHQARgB1AG4AYwB0AGkAbwBuAHMALgBnAGUAdABPAHYAZQByAGwAYQBwAHAAaQBuAGcAUgBlAHAAbwByAHQAaQBuAGcAUABlAHIAaQBvAGQAcwAiACwAIgBDAG8AbQBtAG8AbgBfAEkAbgBwAHUAdABGAHUAbgBjAHQAaQBvAG4AcwAuAFUAdABpAGwAaQB0AHkAXwBEAGkAcwBwAGwAYQB5AEYAdQBuAGMAdABpAG8AbgBOAGEAbQBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAE8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBPAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ATwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAHMAXwBEAGEAdABhACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AUwBvAGkAbABBAG0AZQBuAGQAbQBlAG4AdABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBTAG8AaQBsAEEAbQBlAG4AZABtAGUAbgB0AHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAFMAbwBpAGwAQQBtAGUAbgBkAG0AZQBuAHQAcwBfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBBAGcAcgBvAGMAaABlAG0AaQBjAGEAbABzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBnAHIAbwBjAGgAZQBtAGkAYwBhAGwAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBnAHIAbwBjAGgAZQBtAGkAYwBhAGwAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBnAHIAbwBjAGgAZQBtAGkAYwBhAGwAcwBfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBMAGkAYwBrAEIAbABvAGMAawBzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ATABpAGMAawBCAGwAbwBjAGsAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ATABpAGMAawBCAGwAbwBjAGsAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ATABpAGMAawBCAGwAbwBjAGsAcwBfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBBAG4AaQBtAGEAbABGAGUAZQBkAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBuAGkAbQBhAGwARgBlAGUAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBuAGkAbQBhAGwARgBlAGUAZABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBuAGkAbQBhAGwARgBlAGUAZABfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBBAHEAdQBhAGMAdQBsAHQAdQByAGUARgBlAGUAZABBAG4AZABCAGEAaQB0AF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBxAHUAYQBjAHUAbAB0AHUAcgBlAEYAZQBlAGQAQQBuAGQAQgBhAGkAdABfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBxAHUAYQBjAHUAbAB0AHUAcgBlAEYAZQBlAGQAQQBuAGQAQgBhAGkAdABfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQQBxAHUAYQBjAHUAbAB0AHUAcgBlAEYAZQBlAGQAQQBuAGQAQgBhAGkAdABfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBMAGkAdgBlAHMAdABvAGMAawBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEwAaQB2AGUAcwB0AG8AYwBrAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBMAGkAdgBlAHMAdABvAGMAawBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ATABpAHYAZQBzAHQAbwBjAGsAXwBEAGEAdABhACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AUABhAGMAawBhAGcAaQBuAGcAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBQAGEAYwBrAGEAZwBpAG4AZwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AUABhAGMAawBhAGcAaQBuAGcAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAFAAYQBjAGsAYQBnAGkAbgBnAF8ARABhAHQAYQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAFMAZQBlAGQAcwBBAG4AZABTAGUAZQBkAGwAaQBuAGcAcwBfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAFMAZQBlAGQAcwBBAG4AZABTAGUAZQBkAGwAaQBuAGcAcwBfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AUwBlAGUAZABzAEEAbgBkAFMAZQBlAGQAbABpAG4AZwBzAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBTAGUAZQBkAHMAQQBuAGQAUwBlAGUAZABsAGkAbgBnAHMAXwBEAGEAdABhACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQwBsAGUAYQBuAGkAbgBnAEMAaABlAG0AaQBjAGEAbABzAF8AVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8AQwBsAGUAYQBuAGkAbgBnAEMAaABlAG0AaQBjAGEAbABzAF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBDAGwAZQBhAG4AaQBuAGcAQwBoAGUAbQBpAGMAYQBsAHMAXwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEMAbABlAGEAbgBpAG4AZwBDAGgAZQBtAGkAYwBhAGwAcwBfAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBPAHQAaABlAHIAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwASQBuAHAAdQB0AHMAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBPAHQAaABlAHIAQQBnAHIAaQBjAHUAbAB0AHUAcgBhAGwASQBuAHAAdQB0AHMAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAE8AdABoAGUAcgBBAGcAcgBpAGMAdQBsAHQAdQByAGEAbABJAG4AcAB1AHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ATwB0AGgAZQByAEEAZwByAGkAYwB1AGwAdAB1AHIAYQBsAEkAbgBwAHUAdABzAF8ARABhAHQAYQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAVAByAGEAbgBzAHAAbwByAHQAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFQAcgBhAG4AcwBwAG8AcgB0AF8AUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFQAcgBhAG4AcwBwAG8AcgB0AF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFQAcgBhAG4AcwBwAG8AcgB0AF8ARABhAHQAYQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFQAaQB0AGwAZQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAUwB0AGEAdABpAG8AbgBhAHIAeQBMAGkAcQB1AGkAZABfAFMAbwB1AHIAYwBlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ARgB1AGUAbABTAHQAYQB0AGkAbwBuAGEAcgB5AEwAaQBxAHUAaQBkAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFMAdABhAHQAaQBvAG4AYQByAHkATABpAHEAdQBpAGQAXwBEAGEAdABhACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ARgB1AGUAbABTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAVABpAHQAbABlACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ARgB1AGUAbABTAHQAYQB0AGkAbwBuAGEAcgB5AEcAYQBzAGUAbwB1AHMAUwBvAHUAcgBjAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBGAHUAZQBsAFMAdABhAHQAaQBvAG4AYQByAHkARwBhAHMAZQBvAHUAcwBWAGEAcgBpAGEAdABpAG8AbgAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEYAdQBlAGwAUwB0AGEAdABpAG8AbgBhAHIAeQBHAGEAcwBlAG8AdQBzAEQAYQB0AGEAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBUAGkAdABsAGUAIgAsACIAUwBjAG8AcABlADMAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4AUwBjAG8AcABlADMAXwBFAGwAZQBjAHQAcgBpAGMAaQB0AHkAXwBTAG8AdQByAGMAZQAiACwAIgBTAGMAbwBwAGUAMwBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBTAGMAbwBwAGUAMwBfAEUAbABlAGMAdAByAGkAYwBpAHQAeQBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAFMAYwBvAHAAZQAzAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAFMAYwBvAHAAZQAzAF8ARQBsAGUAYwB0AHIAaQBjAGkAdAB5AF8ARABhAHQAYQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEUAbABlAG0AZQBuAHQAcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEUAbABlAG0AZQBuAHQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBDAGgAZQBtAGkAYwBhAGwAQwBvAG0AcABvAHUAbgBkAEUAbABlAG0AZQBuAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEMAaABlAG0AaQBjAGEAbABDAG8AbQBwAG8AdQBuAGQARQBsAGUAbQBlAG4AdABzAF8ARABhAHQAYQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBQAHIAbwBkAHUAYwB0AHMAXwBUAGkAdABsAGUAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUAByAG8AZAB1AGMAdABzAF8ARABlAHMAYwByAGkAcAB0AGkAbwBuACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFAAcgBvAGQAdQBjAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFAAcgBvAGQAdQBjAHQAcwBfAEQAYQB0AGEAMQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBQAHIAbwBkAHUAYwB0AHMAXwBEAGEAdABhADIAIgAsACIARgBlAHIAdABpAGwAaQBzAGUAcgBfAFMAbwB1AHIAYwBlAEQAYQB0AGEALgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUAByAG8AZAB1AGMAdABzAF8ARABhAHQAYQAzACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAFAAcgBvAGQAdQBjAHQAcwBfAEQAYQB0AGEANAAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGkAbQBlAEQAbwBsAG8AbQBpAHQAZQBHAHkAcABzAHUAbQBDAG8AbgBzAHQAYQBuAHQAcwBfAFQAaQB0AGwAZQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGkAbQBlAEQAbwBsAG8AbQBpAHQAZQBHAHkAcABzAHUAbQBDAG8AbgBzAHQAYQBuAHQAcwBfAEQAZQBzAGMAcgBpAHAAdABpAG8AbgAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGkAbQBlAEQAbwBsAG8AbQBpAHQAZQBHAHkAcABzAHUAbQBDAG8AbgBzAHQAYQBuAHQAcwBfAFMAbwB1AHIAYwBlACIALAAiAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBTAG8AdQByAGMAZQBEAGEAdABhAC4ARgBlAHIAdABpAGwAaQBzAGUAcgBfAEwAaQBtAGUARABvAGwAbwBtAGkAdABlAEcAeQBwAHMAdQBtAEMAbwBuAHMAdABhAG4AdABzAF8ARABhAHQAYQAiACwAIgBGAGUAcgB0AGkAbABpAHMAZQByAF8AUwBvAHUAcgBjAGUARABhAHQAYQAuAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBMAGkAbQBlAEQAbwBsAG8AbQBpAHQAZQBHAHkAcABzAHUAbQBDAG8AbgBzAHQAYQBuAHQAcwBfAFYAYQByAGkAYQB0AGkAbwBuACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBUAGkAdABsAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADEAXwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBFAG0AaQBzAHMAaQBvAG4AcwBDAHIAbwBwAEEAbgBkAFAAYQBzAHQAdQByAGUAUgBlAHMAaQBkAHUAZQBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8AUwBvAHUAcgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMQBfAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAEUAbQBpAHMAcwBpAG8AbgBzAEMAcgBvAHAAQQBuAGQAUABhAHMAdAB1AHIAZQBSAGUAcwBpAGQAdQBlAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAxAF8AXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYARQBtAGkAcwBzAGkAbwBuAHMAQwByAG8AcABBAG4AZABQAGEAcwB0AHUAcgBlAFIAZQBzAGkAZAB1AGUAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFUAbgBpAHQAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAcwBfAEUAcQB1AGEAdABpAG8AbgBzAF8ATABlAGEAYwBoAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADMAXwAxAF8AMQBfAF8AMgBfAF8ATQBhAHMAcwBPAGYATgBpAHQAcgBvAGcAZQBuAEwAbwBzAHQAVABoAHIAbwB1AGcAaABMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBTAG8AdQByAGMAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8ATABhAHQAZQB4AEUAcQB1AGEAdABpAG8AbgAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBzAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBMAGUAYQBjAGgAaQBuAGcALgBWAEUARQBSAEcAXwA2AF8AMwBfADEAXwAxAF8AXwAyAF8AXwBNAGEAcwBzAE8AZgBOAGkAdAByAG8AZwBlAG4ATABvAHMAdABUAGgAcgBvAHUAZwBoAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEwAZQBhAGMAaABpAG4AZwAuAFYARQBFAFIARwBfADYAXwAzAF8AMQBfADEAXwBfADIAXwBfAE0AYQBzAHMATwBmAE4AaQB0AHIAbwBnAGUAbgBMAG8AcwB0AFQAaAByAG8AdQBnAGgATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8ARwBXAFAAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEEAdABtAG8AcwBwAGgAZQByAGkAYwBEAGUAcABvAHMAaQB0AGkAbwBuAF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8AQQB0AG0AbwBzAHAAaABlAHIAaQBjAEQAZQBwAG8AcwBpAHQAaQBvAG4AXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBBAHQAbQBvAHMAcABoAGUAcgBpAGMARABlAHAAbwBzAGkAdABpAG8AbgBfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABBAG4AaQBtAGEAbABXAGEAcwB0AGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQAQQBuAGkAbQBhAGwAVwBhAHMAdABlAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABBAG4AaQBtAGEAbABXAGEAcwB0AGUAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABBAG4AaQBtAGEAbABXAGEAcwB0AGUAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQAQQBuAGkAbQBhAGwAVwBhAHMAdABlAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBWAG8AbABhAHQAaQBsAGkAcwBlAGQAQQBuAGkAbQBhAGwAVwBhAHMAdABlAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBzAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAHMAbwBpAGwAcwBfAE0AYQBzAHMAVgBvAGwAYQB0AGkAbABpAHMAZQBkAEkAbgBvAHIAZwBhAG4AaQBjAEYAZQByAHQAaQBsAGkAcwBlAHIAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBzAG8AaQBsAHMAXwBNAGEAcwBzAFYAbwBsAGEAdABpAGwAaQBzAGUAZABJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAEcAVwBQACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAEwAZQBhAGMAaABpAG4AZwBBAG4AZABSAHUAbgBvAGYAZgBfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBVAG4AaQB0ACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBMAGUAYQBjAGgAaQBuAGcAQQBuAGQAUgB1AG4AbwBmAGYAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATABlAGEAYwBoAGkAbgBnAEEAbgBkAFIAdQBuAG8AZgBmAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQQBuAGkAbQBhAGwAVwBhAHMAdABlAE4ATABvAHMAdAAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBBAG4AaQBtAGEAbABXAGEAcwB0AGUATgBMAG8AcwB0AF8AVABpAHQAbABlACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBOAEwAbwBzAHQAXwBWAGEAcgBpAGEAYgBsAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQQBuAGkAbQBhAGwAVwBhAHMAdABlAE4ATABvAHMAdABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQQBuAGkAbQBhAGwAVwBhAHMAdABlAE4ATABvAHMAdABfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBOAEwAbwBzAHQAXwBSAGUAYQBkAGEAYgBsAGUARQBxAHUAYQB0AGkAbwBuACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEEAbgBpAG0AYQBsAFcAYQBzAHQAZQBOAEwAbwBzAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdAAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABfAFQAaQB0AGwAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBOAEwAbwBzAHQAXwBOAEkAUgBSAGUAZgBlAHIAZQBuAGMAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBJAG4AbwByAGcAYQBuAGkAYwBGAGUAcgB0AGkAbABpAHMAZQByAE4ATABvAHMAdABfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMASQBuAG8AcgBnAGEAbgBpAGMARgBlAHIAdABpAGwAaQBzAGUAcgBOAEwAbwBzAHQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUATgBMAG8AcwB0ACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBNAGEAcwBzAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBOAEwAbwBzAHQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQwByAG8AcABSAGUAcwBpAGQAdQBlAE4ATABvAHMAdABfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUATgBMAG8AcwB0AF8AVQBuAGkAdAAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8ATQBhAHMAcwBDAHIAbwBwAFIAZQBzAGkAZAB1AGUATgBMAG8AcwB0AF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQwByAG8AcABSAGUAcwBpAGQAdQBlAE4ATABvAHMAdABfAFIAZQBhAGQAYQBiAGwAZQBFAHEAdQBhAHQAaQBvAG4AIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAE0AYQBzAHMAQwByAG8AcABSAGUAcwBpAGQAdQBlAE4ATABvAHMAdABfAEEAcgBnAHUAbQBlAG4AdABzACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBVAHIAaQBuAGUAQQBuAGQARAB1AG4AZwBEAGUAcABvAHMAaQB0AGUAZABfAEcAVwBQACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBVAHIAaQBuAGUAQQBuAGQARAB1AG4AZwBEAGUAcABvAHMAaQB0AGUAZAAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8AVQByAGkAbgBlAEEAbgBkAEQAdQBuAGcARABlAHAAbwBzAGkAdABlAGQAXwBUAGkAdABsAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAFUAcgBpAG4AZQBBAG4AZABEAHUAbgBnAEQAZQBwAG8AcwBpAHQAZQBkAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEMAbwBtAG0AbwBuAEEAZwBTAG8AaQBsAHMAXwBFAHEAdQBhAHQAaQBvAG4AcwAuAEEAZwBTAG8AaQBsAHMAXwBVAHIAaQBuAGUAQQBuAGQARAB1AG4AZwBEAGUAcABvAHMAaQB0AGUAZABfAFUAbgBpAHQAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAFUAcgBpAG4AZQBBAG4AZABEAHUAbgBnAEQAZQBwAG8AcwBpAHQAZQBkAF8ATgBJAFIAUgBlAGYAZQByAGUAbgBjAGUAIgAsACIAQwBvAG0AbQBvAG4AQQBnAFMAbwBpAGwAcwBfAEUAcQB1AGEAdABpAG8AbgBzAC4AQQBnAFMAbwBpAGwAcwBfAFUAcgBpAG4AZQBBAG4AZABEAHUAbgBnAEQAZQBwAG8AcwBpAHQAZQBkAF8AUgBlAGEAZABhAGIAbABlAEUAcQB1AGEAdABpAG8AbgAiACwAIgBDAG8AbQBtAG8AbgBBAGcAUwBvAGkAbABzAF8ARQBxAHUAYQB0AGkAbwBuAHMALgBBAGcAUwBvAGkAbABzAF8AVQByAGkAbgBlAEEAbgBkAEQAdQBuAGcARABlAHAAbwBzAGkAdABlAGQAXwBBAHIAZwB1AG0AZQBuAHQAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVABpAHQAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFYAYQByAGkAYQBiAGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAxAF8AXwBNAGUAdABoAGEAbgBlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFMAbwB1AHIAYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAE4ASQBSAFIAZQBmAGUAcgBlAG4AYwBlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADEAXwBfAE0AZQB0AGgAYQBuAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAEwAYQB0AGUAeABFAHEAdQBhAHQAaQBvAG4AIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMQBfAF8ATQBlAHQAaABhAG4AZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AQQByAGcAdQBtAGUAbgB0AHMAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8ARgB1AG4AYwB0AGkAbwBuAE4AYQBtAGUAIgAsACIAQQBnAFIAZQBzAGkAZAB1AGUAXwBFAHEAdQBhAHQAaQBvAG4AcwBfAEYAaQBlAGwAZABCAHUAcgBuAGkAbgBnAC4AVgBFAEUAUgBHAF8ANgBfADQAXwAxAF8AMQBfAF8AMgBfAF8ATgBpAHQAcgBvAHUAcwBPAHgAaQBkAGUARQBtAGkAcwBzAGkAbwBuAHMARgByAG8AbQBCAHUAcgBuAGkAbgBnAE8AZgBDAHIAbwBwAFIAZQBzAGkAZAB1AGUAcwBfAFQAaQB0AGwAZQAiACwAIgBBAGcAUgBlAHMAaQBkAHUAZQBfAEUAcQB1AGEAdABpAG8AbgBzAF8ARgBpAGUAbABkAEIAdQByAG4AaQBuAGcALgBWAEUARQBSAEcAXwA2AF8ANABfADEAXwAxAF8AXwAyAF8AXwBOAGkAdAByAG8AdQBzAE8AeABpAGQAZQBFAG0AaQBzAHMAaQBvAG4AcwBGAHIAbwBtAEIAdQByAG4AaQBuAGcATwBmAEMAcgBvAHAAUgBlAHMAaQBkAHUAZQBzAF8AVgBhAHIAaQBhAGIAbABlACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgBpAG4AZwAuAFYARQBFAFIARwBfADYAXwA0AF8AMQBfADEAXwBfADIAXwBfAE4AaQB0AHIAbwB1AHMATwB4AGkAZABlAEUAbQBpAHMAcwBpAG8AbgBzAEYAcgBvAG0AQgB1AHIAbgBpAG4AZwBPAGYAQwByAG8AcABSAGUAcwBpAGQAdQBlAHMAXwBVAG4AaQB0ACIALAAiAEEAZwBSAGUAcwBpAGQAdQBlAF8ARQBxAHUAYQB0AGkAbwBuAHMAXwBGAGkAZQBsAGQAQgB1AHIAbgB